--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -677,7 +677,7 @@
         <v>9.183</v>
       </c>
       <c r="G2" t="n">
-        <v>6.333</v>
+        <v>6.332</v>
       </c>
       <c r="H2" t="n">
         <v>8.625</v>
@@ -1202,7 +1202,7 @@
         <v>-0.969</v>
       </c>
       <c r="R8" t="n">
-        <v>68.96599999999999</v>
+        <v>65.517</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -4255,29 +4255,29 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.821646606320424</v>
+        <v>5.821646606320425</v>
       </c>
       <c r="N31" t="n">
-        <v>5.821646606320424</v>
+        <v>5.821646606320425</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.04999999999999982</v>
+        <v>-0.05000000000000027</v>
       </c>
       <c r="P31" t="n">
         <v>-0.02254090051768642</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
           <t>Estable</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Estable</t>
-        </is>
-      </c>
       <c r="S31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -10627,13 +10627,13 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.351279963901452</v>
+        <v>5.351279963901451</v>
       </c>
       <c r="N121" t="n">
-        <v>5.351279963901452</v>
+        <v>5.351279963901451</v>
       </c>
       <c r="O121" t="n">
-        <v>-0.1350000000000007</v>
+        <v>-0.1349999999999998</v>
       </c>
       <c r="P121" t="n">
         <v>-0.07303307105113177</v>
@@ -13520,13 +13520,13 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>0.4534739945386219</v>
+        <v>0.453473994538621</v>
       </c>
       <c r="N162" t="n">
-        <v>0.4534739945386219</v>
+        <v>0.453473994538621</v>
       </c>
       <c r="O162" t="n">
-        <v>-0.04000000000000004</v>
+        <v>-0.03999999999999915</v>
       </c>
       <c r="P162" t="n">
         <v>-0.1940354272776155</v>
@@ -15644,13 +15644,13 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>0.2728737935871548</v>
+        <v>0.2728737935871557</v>
       </c>
       <c r="N192" t="n">
-        <v>0.2728737935871548</v>
+        <v>0.2728737935871557</v>
       </c>
       <c r="O192" t="n">
-        <v>-0.2550000000000008</v>
+        <v>-0.2550000000000017</v>
       </c>
       <c r="P192" t="n">
         <v>-0.01430670751449181</v>
@@ -26264,13 +26264,13 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>0.6463639964198382</v>
+        <v>0.6463639964198391</v>
       </c>
       <c r="N342" t="n">
-        <v>0.6463639964198382</v>
+        <v>0.6463639964198391</v>
       </c>
       <c r="O342" t="n">
-        <v>-0.1974999999999998</v>
+        <v>-0.1975000000000007</v>
       </c>
       <c r="P342" t="n">
         <v>-0.1130309985299816</v>
@@ -30512,13 +30512,13 @@
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>0.8548386504155192</v>
+        <v>0.8548386504155188</v>
       </c>
       <c r="N402" t="n">
-        <v>0.8548386504155192</v>
+        <v>0.8548386504155188</v>
       </c>
       <c r="O402" t="n">
-        <v>-0.27</v>
+        <v>-0.2699999999999996</v>
       </c>
       <c r="P402" t="n">
         <v>-0.1445534909310906</v>
@@ -33269,13 +33269,13 @@
         <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>0.1840464994508553</v>
+        <v>0.1840464994508548</v>
       </c>
       <c r="N441" t="n">
-        <v>0.1840464994508553</v>
+        <v>0.1840464994508548</v>
       </c>
       <c r="O441" t="n">
-        <v>-0.06750000000000034</v>
+        <v>-0.06749999999999989</v>
       </c>
       <c r="P441" t="n">
         <v>0.01137711772873296</v>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -486,13 +486,13 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>283237</v>
+        <v>299898</v>
       </c>
       <c r="E2" t="n">
-        <v>148371</v>
+        <v>151106</v>
       </c>
       <c r="F2" t="n">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,93 +1064,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Angamos</t>
+          <t>Timicurillo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9043370</v>
+        <v>9036459</v>
       </c>
       <c r="C7" t="n">
         <v>30</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.33</v>
+        <v>10.34</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7</v>
+        <v>7.74</v>
       </c>
       <c r="H7" t="n">
-        <v>9.875</v>
+        <v>9.374000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>7.953</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.63</v>
+        <v>-2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.922</v>
+        <v>-1.174</v>
       </c>
       <c r="L7" t="n">
-        <v>5.823</v>
+        <v>-0.669</v>
       </c>
       <c r="M7" t="n">
-        <v>5.823</v>
+        <v>0.778</v>
       </c>
       <c r="N7" t="n">
-        <v>5.841</v>
+        <v>0.843</v>
       </c>
       <c r="O7" t="n">
-        <v>0.86</v>
+        <v>0.713</v>
       </c>
       <c r="P7" t="n">
-        <v>-42.215</v>
+        <v>-0.358</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.993</v>
+        <v>0.51</v>
       </c>
       <c r="R7" t="n">
-        <v>41.379</v>
+        <v>20.69</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>7162</v>
+        <v>2690</v>
       </c>
       <c r="U7" t="n">
-        <v>0.726</v>
+        <v>0.867</v>
       </c>
       <c r="V7" t="n">
-        <v>0.469</v>
+        <v>0.723</v>
       </c>
       <c r="W7" t="n">
-        <v>0.679</v>
+        <v>0.862</v>
       </c>
       <c r="X7" t="n">
-        <v>2.757</v>
+        <v>1.748</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Borja</t>
+          <t>Angamos</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9040208</v>
+        <v>9043370</v>
       </c>
       <c r="C8" t="n">
         <v>30</v>
@@ -1166,43 +1166,43 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.99</v>
+        <v>4.33</v>
       </c>
       <c r="G8" t="n">
-        <v>5.88</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="n">
-        <v>5.179</v>
+        <v>9.875</v>
       </c>
       <c r="I8" t="n">
-        <v>4.795</v>
+        <v>7.953</v>
       </c>
       <c r="J8" t="n">
-        <v>0.89</v>
+        <v>-1.63</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.384</v>
+        <v>-1.922</v>
       </c>
       <c r="L8" t="n">
-        <v>0.303</v>
+        <v>5.823</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8149999999999999</v>
+        <v>5.823</v>
       </c>
       <c r="N8" t="n">
-        <v>0.948</v>
+        <v>5.841</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003</v>
+        <v>0.86</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.663</v>
+        <v>-42.215</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.041</v>
+        <v>-0.993</v>
       </c>
       <c r="R8" t="n">
-        <v>48.276</v>
+        <v>41.379</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1210,29 +1210,29 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>13802</v>
+        <v>7162</v>
       </c>
       <c r="U8" t="n">
-        <v>0.429</v>
+        <v>0.726</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.082</v>
+        <v>0.469</v>
       </c>
       <c r="W8" t="n">
-        <v>0.427</v>
+        <v>0.679</v>
       </c>
       <c r="X8" t="n">
-        <v>1.477</v>
+        <v>2.757</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Contamana</t>
+          <t>Borja</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9053555</v>
+        <v>9040208</v>
       </c>
       <c r="C9" t="n">
         <v>30</v>
@@ -1248,43 +1248,43 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7.28</v>
+        <v>4.99</v>
       </c>
       <c r="G9" t="n">
-        <v>6.07</v>
+        <v>5.88</v>
       </c>
       <c r="H9" t="n">
-        <v>11.094</v>
+        <v>5.179</v>
       </c>
       <c r="I9" t="n">
-        <v>11.554</v>
+        <v>4.795</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.21</v>
+        <v>0.89</v>
       </c>
       <c r="K9" t="n">
-        <v>0.46</v>
+        <v>-0.384</v>
       </c>
       <c r="L9" t="n">
-        <v>3.859</v>
+        <v>0.303</v>
       </c>
       <c r="M9" t="n">
-        <v>3.859</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>4.149</v>
+        <v>0.948</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.477</v>
+        <v>0.003</v>
       </c>
       <c r="P9" t="n">
-        <v>-116.399</v>
+        <v>-0.663</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.876</v>
+        <v>-0.041</v>
       </c>
       <c r="R9" t="n">
-        <v>44.828</v>
+        <v>48.276</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1292,36 +1292,36 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>9805</v>
+        <v>13802</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05</v>
+        <v>0.429</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.597</v>
+        <v>-0.082</v>
       </c>
       <c r="W9" t="n">
-        <v>0.033</v>
+        <v>0.427</v>
       </c>
       <c r="X9" t="n">
-        <v>11.064</v>
+        <v>1.477</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENAPU</t>
+          <t>Contamana</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9038134</v>
+        <v>9053555</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1330,43 +1330,43 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>7.28</v>
       </c>
       <c r="G10" t="n">
-        <v>5.32</v>
+        <v>6.07</v>
       </c>
       <c r="H10" t="n">
-        <v>112.88</v>
+        <v>11.094</v>
       </c>
       <c r="I10" t="n">
-        <v>108.389</v>
+        <v>11.554</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.68</v>
+        <v>-1.21</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.491</v>
+        <v>0.46</v>
       </c>
       <c r="L10" t="n">
-        <v>88.679</v>
+        <v>3.859</v>
       </c>
       <c r="M10" t="n">
-        <v>88.679</v>
+        <v>3.859</v>
       </c>
       <c r="N10" t="n">
-        <v>92.009</v>
+        <v>4.149</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.358</v>
+        <v>-0.477</v>
       </c>
       <c r="P10" t="n">
-        <v>-13.68</v>
+        <v>-116.399</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.322</v>
+        <v>-1.876</v>
       </c>
       <c r="R10" t="n">
-        <v>91.667</v>
+        <v>44.828</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1374,81 +1374,81 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>9965</v>
+        <v>9805</v>
       </c>
       <c r="U10" t="n">
-        <v>0.129</v>
+        <v>0.05</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.738</v>
+        <v>-0.597</v>
       </c>
       <c r="W10" t="n">
-        <v>0.129</v>
+        <v>0.033</v>
       </c>
       <c r="X10" t="n">
-        <v>36.19</v>
+        <v>11.064</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Flor de Punga</t>
+          <t>ENAPU</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9044756</v>
+        <v>9038134</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>18.9</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>22.8</v>
+        <v>5.32</v>
       </c>
       <c r="H11" t="n">
-        <v>16.468</v>
+        <v>112.88</v>
       </c>
       <c r="I11" t="n">
-        <v>16.311</v>
+        <v>108.389</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>-1.68</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.157</v>
+        <v>-4.491</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.389</v>
+        <v>88.679</v>
       </c>
       <c r="M11" t="n">
-        <v>4.389</v>
+        <v>88.679</v>
       </c>
       <c r="N11" t="n">
-        <v>4.692</v>
+        <v>92.009</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.944</v>
+        <v>-0.358</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.638</v>
+        <v>-13.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.178</v>
+        <v>-3.322</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>91.667</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1456,81 +1456,81 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>3099</v>
+        <v>9965</v>
       </c>
       <c r="U11" t="n">
-        <v>0.795</v>
+        <v>0.129</v>
       </c>
       <c r="V11" t="n">
-        <v>0.61</v>
+        <v>-0.738</v>
       </c>
       <c r="W11" t="n">
-        <v>0.786</v>
+        <v>0.129</v>
       </c>
       <c r="X11" t="n">
-        <v>2.698</v>
+        <v>36.19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lagunas</t>
+          <t>Flor de Punga</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9043597</v>
+        <v>9044756</v>
       </c>
       <c r="C12" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.238</v>
+        <v>18.9</v>
       </c>
       <c r="G12" t="n">
-        <v>4.48</v>
+        <v>22.8</v>
       </c>
       <c r="H12" t="n">
-        <v>6.21</v>
+        <v>16.468</v>
       </c>
       <c r="I12" t="n">
-        <v>5.214</v>
+        <v>16.311</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.758</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.996</v>
+        <v>-0.157</v>
       </c>
       <c r="L12" t="n">
-        <v>0.281</v>
+        <v>-4.389</v>
       </c>
       <c r="M12" t="n">
-        <v>0.445</v>
+        <v>4.389</v>
       </c>
       <c r="N12" t="n">
-        <v>0.539</v>
+        <v>4.692</v>
       </c>
       <c r="O12" t="n">
-        <v>0.331</v>
+        <v>-0.944</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.253</v>
+        <v>-7.638</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.15</v>
+        <v>-1.178</v>
       </c>
       <c r="R12" t="n">
-        <v>17.241</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1538,81 +1538,81 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>4120</v>
+        <v>3099</v>
       </c>
       <c r="U12" t="n">
-        <v>0.83</v>
+        <v>0.795</v>
       </c>
       <c r="V12" t="n">
-        <v>0.654</v>
+        <v>0.61</v>
       </c>
       <c r="W12" t="n">
-        <v>0.828</v>
+        <v>0.786</v>
       </c>
       <c r="X12" t="n">
-        <v>1.198</v>
+        <v>2.698</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Puerto Almendra</t>
+          <t>Lagunas</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9037610</v>
+        <v>9043597</v>
       </c>
       <c r="C13" t="n">
         <v>30</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8.279999999999999</v>
+        <v>5.238</v>
       </c>
       <c r="G13" t="n">
-        <v>4.632</v>
+        <v>4.48</v>
       </c>
       <c r="H13" t="n">
-        <v>3.275</v>
+        <v>6.21</v>
       </c>
       <c r="I13" t="n">
-        <v>7.046</v>
+        <v>5.214</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.648</v>
+        <v>-0.758</v>
       </c>
       <c r="K13" t="n">
-        <v>3.771</v>
+        <v>-0.996</v>
       </c>
       <c r="L13" t="n">
-        <v>0.95</v>
+        <v>0.281</v>
       </c>
       <c r="M13" t="n">
-        <v>2.281</v>
+        <v>0.445</v>
       </c>
       <c r="N13" t="n">
-        <v>2.488</v>
+        <v>0.539</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.242</v>
+        <v>0.331</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.146</v>
+        <v>-0.253</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.304</v>
+        <v>0.15</v>
       </c>
       <c r="R13" t="n">
-        <v>41.379</v>
+        <v>17.241</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1620,29 +1620,29 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>2305</v>
+        <v>4120</v>
       </c>
       <c r="U13" t="n">
-        <v>0.518</v>
+        <v>0.83</v>
       </c>
       <c r="V13" t="n">
-        <v>0.015</v>
+        <v>0.654</v>
       </c>
       <c r="W13" t="n">
-        <v>0.515</v>
+        <v>0.828</v>
       </c>
       <c r="X13" t="n">
-        <v>2.58</v>
+        <v>1.198</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Requena</t>
+          <t>Puerto Almendra</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9043425</v>
+        <v>9037610</v>
       </c>
       <c r="C14" t="n">
         <v>30</v>
@@ -1658,43 +1658,43 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8.151999999999999</v>
+        <v>5.262</v>
       </c>
       <c r="G14" t="n">
-        <v>6.7</v>
+        <v>2.75</v>
       </c>
       <c r="H14" t="n">
-        <v>8.154999999999999</v>
+        <v>6.888</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>4.908</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.452</v>
+        <v>-2.512</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.755</v>
+        <v>-1.98</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.234</v>
+        <v>2.009</v>
       </c>
       <c r="M14" t="n">
-        <v>0.367</v>
+        <v>2.009</v>
       </c>
       <c r="N14" t="n">
-        <v>0.483</v>
+        <v>2.498</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.446</v>
+        <v>-9.868</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.279</v>
+        <v>-0.544</v>
       </c>
       <c r="R14" t="n">
-        <v>44.828</v>
+        <v>55.172</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1702,81 +1702,81 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>14042</v>
+        <v>2349</v>
       </c>
       <c r="U14" t="n">
-        <v>0.781</v>
+        <v>0.521</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.022</v>
       </c>
       <c r="W14" t="n">
-        <v>0.78</v>
+        <v>0.518</v>
       </c>
       <c r="X14" t="n">
-        <v>2.285</v>
+        <v>2.566</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Requena</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9042153</v>
+        <v>9043425</v>
       </c>
       <c r="C15" t="n">
         <v>30</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.935</v>
+        <v>8.151999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>7.19</v>
+        <v>6.7</v>
       </c>
       <c r="H15" t="n">
-        <v>10.462</v>
+        <v>8.154999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>10.174</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1.255</v>
+        <v>-1.452</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.287</v>
+        <v>-1.755</v>
       </c>
       <c r="L15" t="n">
-        <v>3.762</v>
+        <v>-0.234</v>
       </c>
       <c r="M15" t="n">
-        <v>3.762</v>
+        <v>0.367</v>
       </c>
       <c r="N15" t="n">
-        <v>3.837</v>
+        <v>0.483</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.276</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-34.011</v>
+        <v>-0.446</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.547</v>
+        <v>0.279</v>
       </c>
       <c r="R15" t="n">
-        <v>48.276</v>
+        <v>44.828</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1784,81 +1784,81 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>3737</v>
+        <v>14042</v>
       </c>
       <c r="U15" t="n">
-        <v>0.357</v>
+        <v>0.781</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.12</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.336</v>
+        <v>0.78</v>
       </c>
       <c r="X15" t="n">
-        <v>2.697</v>
+        <v>2.285</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Santa Clotilde</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9032282</v>
+        <v>9042153</v>
       </c>
       <c r="C16" t="n">
         <v>30</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9.452</v>
+        <v>5.935</v>
       </c>
       <c r="G16" t="n">
-        <v>7.28</v>
+        <v>7.19</v>
       </c>
       <c r="H16" t="n">
-        <v>8.222</v>
+        <v>10.462</v>
       </c>
       <c r="I16" t="n">
-        <v>6.755</v>
+        <v>10.174</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.173</v>
+        <v>1.255</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.467</v>
+        <v>-0.287</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.534</v>
+        <v>3.762</v>
       </c>
       <c r="M16" t="n">
-        <v>1.534</v>
+        <v>3.762</v>
       </c>
       <c r="N16" t="n">
-        <v>1.64</v>
+        <v>3.837</v>
       </c>
       <c r="O16" t="n">
-        <v>0.581</v>
+        <v>-0.276</v>
       </c>
       <c r="P16" t="n">
-        <v>-4.315</v>
+        <v>-34.011</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.339</v>
+        <v>-0.547</v>
       </c>
       <c r="R16" t="n">
-        <v>27.586</v>
+        <v>48.276</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1866,29 +1866,29 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>8836</v>
+        <v>3737</v>
       </c>
       <c r="U16" t="n">
-        <v>0.305</v>
+        <v>0.357</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.198</v>
+        <v>-0.12</v>
       </c>
       <c r="W16" t="n">
-        <v>0.28</v>
+        <v>0.336</v>
       </c>
       <c r="X16" t="n">
-        <v>1.911</v>
+        <v>2.697</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Santa María de Nanay</t>
+          <t>Santa Clotilde</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9037738</v>
+        <v>9032282</v>
       </c>
       <c r="C17" t="n">
         <v>30</v>
@@ -1904,43 +1904,43 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5.575</v>
+        <v>9.452</v>
       </c>
       <c r="G17" t="n">
-        <v>4.02</v>
+        <v>7.28</v>
       </c>
       <c r="H17" t="n">
-        <v>7.167</v>
+        <v>8.222</v>
       </c>
       <c r="I17" t="n">
-        <v>6.343</v>
+        <v>6.755</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.555</v>
+        <v>-2.173</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.824</v>
+        <v>-1.467</v>
       </c>
       <c r="L17" t="n">
-        <v>1.519</v>
+        <v>-1.534</v>
       </c>
       <c r="M17" t="n">
-        <v>1.519</v>
+        <v>1.534</v>
       </c>
       <c r="N17" t="n">
-        <v>1.705</v>
+        <v>1.64</v>
       </c>
       <c r="O17" t="n">
-        <v>0.633</v>
+        <v>0.581</v>
       </c>
       <c r="P17" t="n">
-        <v>-6.413</v>
+        <v>-4.315</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.234</v>
+        <v>0.339</v>
       </c>
       <c r="R17" t="n">
-        <v>44.828</v>
+        <v>27.586</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -1948,100 +1948,182 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>3208</v>
+        <v>8836</v>
       </c>
       <c r="U17" t="n">
-        <v>0.601</v>
+        <v>0.305</v>
       </c>
       <c r="V17" t="n">
-        <v>0.218</v>
+        <v>-0.198</v>
       </c>
       <c r="W17" t="n">
-        <v>0.598</v>
+        <v>0.28</v>
       </c>
       <c r="X17" t="n">
-        <v>1.489</v>
+        <v>1.911</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Santa María de Nanay</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9037738</v>
+      </c>
+      <c r="C18" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>5.575</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7.167</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6.343</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1.555</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.824</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.519</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.519</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.705</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-6.413</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="R18" t="n">
+        <v>44.828</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>3208</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.489</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Tamshiyacu</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>9038269</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C19" t="n">
         <v>13</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>4.44</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>3.1</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H19" t="n">
         <v>3.479</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>3.212</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>-1.34</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K19" t="n">
         <v>-0.267</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>-0.173</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M19" t="n">
         <v>0.4</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N19" t="n">
         <v>0.507</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O19" t="n">
         <v>-0.243</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P19" t="n">
         <v>-0.665</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q19" t="n">
         <v>-0.347</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>50</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>14543</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>0.78</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V19" t="n">
         <v>0.5659999999999999</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W19" t="n">
         <v>0.778</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X19" t="n">
         <v>1.725</v>
       </c>
     </row>
@@ -2056,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S449"/>
+  <dimension ref="A1:S479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18080,17 +18162,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="B227" t="n">
         <v>9037610</v>
       </c>
       <c r="C227" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D227" t="n">
-        <v>556.1371459960938</v>
+        <v>953.3272094726562</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -18098,13 +18180,13 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G227" t="n">
-        <v>0.0890658942795076</v>
+        <v>0.6769446391030133</v>
       </c>
       <c r="H227" t="n">
-        <v>3.274837074583635</v>
+        <v>6.888043097407148</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
@@ -18113,20 +18195,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K227" t="n">
-        <v>8.280000000000001</v>
+        <v>5.2625</v>
       </c>
       <c r="L227" t="n">
         <v>1</v>
       </c>
       <c r="M227" t="n">
-        <v>-5.005162925416366</v>
+        <v>1.625543097407148</v>
       </c>
       <c r="N227" t="n">
-        <v>5.005162925416366</v>
+        <v>1.625543097407148</v>
       </c>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
@@ -18145,17 +18227,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="B228" t="n">
         <v>9037610</v>
       </c>
       <c r="C228" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D228" t="n">
-        <v>605.16943359375</v>
+        <v>1014.965393066406</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -18163,13 +18245,13 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G228" t="n">
-        <v>0.112237509051412</v>
+        <v>0.7224947442186405</v>
       </c>
       <c r="H228" t="n">
-        <v>3.425749456915279</v>
+        <v>7.096809740714786</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -18178,30 +18260,30 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K228" t="n">
-        <v>8.240000000000002</v>
+        <v>5.172499999999999</v>
       </c>
       <c r="L228" t="n">
         <v>1</v>
       </c>
       <c r="M228" t="n">
-        <v>-4.814250543084723</v>
+        <v>1.924309740714786</v>
       </c>
       <c r="N228" t="n">
-        <v>4.814250543084723</v>
+        <v>1.924309740714786</v>
       </c>
       <c r="O228" t="n">
-        <v>-0.03999999999999915</v>
+        <v>-0.09000000000000075</v>
       </c>
       <c r="P228" t="n">
-        <v>0.1509123823316441</v>
+        <v>0.2087666433076381</v>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
@@ -18216,17 +18298,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="B229" t="n">
         <v>9037610</v>
       </c>
       <c r="C229" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D229" t="n">
-        <v>689.5184936523438</v>
+        <v>1002.415588378906</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -18234,13 +18316,13 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G229" t="n">
-        <v>0.1745112237509051</v>
+        <v>0.7105816398037842</v>
       </c>
       <c r="H229" t="n">
-        <v>4.723412382331644</v>
+        <v>7.05249824807288</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -18249,26 +18331,26 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K229" t="n">
-        <v>8.185</v>
+        <v>5.0875</v>
       </c>
       <c r="L229" t="n">
         <v>1</v>
       </c>
       <c r="M229" t="n">
-        <v>-3.461587617668356</v>
+        <v>1.964998248072879</v>
       </c>
       <c r="N229" t="n">
-        <v>3.461587617668356</v>
+        <v>1.964998248072879</v>
       </c>
       <c r="O229" t="n">
-        <v>-0.05500000000000149</v>
+        <v>-0.08499999999999908</v>
       </c>
       <c r="P229" t="n">
-        <v>1.297662925416365</v>
+        <v>-0.04431149264190637</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
@@ -18277,7 +18359,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S229" t="b">
@@ -18287,17 +18369,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="B230" t="n">
         <v>9037610</v>
       </c>
       <c r="C230" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D230" t="n">
-        <v>777.1080322265625</v>
+        <v>927.869384765625</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -18305,13 +18387,13 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G230" t="n">
-        <v>0.2382331643736423</v>
+        <v>0.6552207428170989</v>
       </c>
       <c r="H230" t="n">
-        <v>5.866010137581462</v>
+        <v>6.761790469516469</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -18320,26 +18402,26 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K230" t="n">
-        <v>8.1325</v>
+        <v>4.985</v>
       </c>
       <c r="L230" t="n">
         <v>1</v>
       </c>
       <c r="M230" t="n">
-        <v>-2.266489862418538</v>
+        <v>1.776790469516468</v>
       </c>
       <c r="N230" t="n">
-        <v>2.266489862418538</v>
+        <v>1.776790469516468</v>
       </c>
       <c r="O230" t="n">
-        <v>-0.05250000000000021</v>
+        <v>-0.1025</v>
       </c>
       <c r="P230" t="n">
-        <v>1.142597755249818</v>
+        <v>-0.2907077785564107</v>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
@@ -18348,27 +18430,27 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="B231" t="n">
         <v>9037610</v>
       </c>
       <c r="C231" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D231" t="n">
-        <v>842.5160522460938</v>
+        <v>836.7091674804688</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -18376,13 +18458,13 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G231" t="n">
-        <v>0.2838522809558291</v>
+        <v>0.5697266993693062</v>
       </c>
       <c r="H231" t="n">
-        <v>6.241272628530051</v>
+        <v>6.463032585844429</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -18391,26 +18473,26 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K231" t="n">
-        <v>8.0425</v>
+        <v>4.88</v>
       </c>
       <c r="L231" t="n">
         <v>1</v>
       </c>
       <c r="M231" t="n">
-        <v>-1.80122737146995</v>
+        <v>1.583032585844429</v>
       </c>
       <c r="N231" t="n">
-        <v>1.80122737146995</v>
+        <v>1.583032585844429</v>
       </c>
       <c r="O231" t="n">
-        <v>-0.08999999999999986</v>
+        <v>-0.1050000000000004</v>
       </c>
       <c r="P231" t="n">
-        <v>0.3752624909485887</v>
+        <v>-0.2987578836720397</v>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
@@ -18419,27 +18501,27 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="B232" t="n">
         <v>9037610</v>
       </c>
       <c r="C232" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D232" t="n">
-        <v>894.1189575195312</v>
+        <v>764.9366455078125</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -18447,13 +18529,13 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G232" t="n">
-        <v>0.3215061549601738</v>
+        <v>0.4968465311843027</v>
       </c>
       <c r="H232" t="n">
-        <v>6.359333816075308</v>
+        <v>6.237533286615277</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -18462,26 +18544,26 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K232" t="n">
-        <v>7.97</v>
+        <v>4.785</v>
       </c>
       <c r="L232" t="n">
         <v>1</v>
       </c>
       <c r="M232" t="n">
-        <v>-1.610666183924692</v>
+        <v>1.452533286615277</v>
       </c>
       <c r="N232" t="n">
-        <v>1.610666183924692</v>
+        <v>1.452533286615277</v>
       </c>
       <c r="O232" t="n">
-        <v>-0.07250000000000068</v>
+        <v>-0.09499999999999975</v>
       </c>
       <c r="P232" t="n">
-        <v>0.1180611875452575</v>
+        <v>-0.2254992992291518</v>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
@@ -18490,27 +18572,27 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="B233" t="n">
         <v>9037610</v>
       </c>
       <c r="C233" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D233" t="n">
-        <v>975.554443359375</v>
+        <v>716.4318237304688</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -18518,13 +18600,13 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G233" t="n">
-        <v>0.3794351918899349</v>
+        <v>0.4505956552207428</v>
       </c>
       <c r="H233" t="n">
-        <v>6.842666545981174</v>
+        <v>5.95781534688157</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -18533,26 +18615,26 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K233" t="n">
-        <v>7.8475</v>
+        <v>4.700000000000001</v>
       </c>
       <c r="L233" t="n">
         <v>1</v>
       </c>
       <c r="M233" t="n">
-        <v>-1.004833454018827</v>
+        <v>1.257815346881569</v>
       </c>
       <c r="N233" t="n">
-        <v>1.004833454018827</v>
+        <v>1.257815346881569</v>
       </c>
       <c r="O233" t="n">
-        <v>-0.1224999999999996</v>
+        <v>-0.08499999999999908</v>
       </c>
       <c r="P233" t="n">
-        <v>0.4833327299058654</v>
+        <v>-0.2797179397337075</v>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
@@ -18561,27 +18643,27 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="B234" t="n">
         <v>9037610</v>
       </c>
       <c r="C234" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D234" t="n">
-        <v>1113.74169921875</v>
+        <v>685.0597534179688</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -18589,13 +18671,13 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G234" t="n">
-        <v>0.4923968139029689</v>
+        <v>0.4190609670637702</v>
       </c>
       <c r="H234" t="n">
-        <v>7.879286748732802</v>
+        <v>5.737633146461107</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -18604,55 +18686,55 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K234" t="n">
-        <v>7.800000000000001</v>
+        <v>4.6025</v>
       </c>
       <c r="L234" t="n">
         <v>1</v>
       </c>
       <c r="M234" t="n">
-        <v>0.07928674873280173</v>
+        <v>1.135133146461107</v>
       </c>
       <c r="N234" t="n">
-        <v>0.07928674873280173</v>
+        <v>1.135133146461107</v>
       </c>
       <c r="O234" t="n">
-        <v>-0.04749999999999943</v>
+        <v>-0.09750000000000103</v>
       </c>
       <c r="P234" t="n">
-        <v>1.036620202751629</v>
+        <v>-0.2201822004204628</v>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S234" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B235" t="n">
         <v>9037610</v>
       </c>
       <c r="C235" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D235" t="n">
-        <v>1247.317504882812</v>
+        <v>661.9630737304688</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -18660,13 +18742,13 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G235" t="n">
-        <v>0.5850832729905865</v>
+        <v>0.3987386124737211</v>
       </c>
       <c r="H235" t="n">
-        <v>8.280000000000001</v>
+        <v>5.649039943938331</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -18675,26 +18757,26 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K235" t="n">
-        <v>7.672499999999999</v>
+        <v>4.5225</v>
       </c>
       <c r="L235" t="n">
         <v>1</v>
       </c>
       <c r="M235" t="n">
-        <v>0.6075000000000017</v>
+        <v>1.126539943938331</v>
       </c>
       <c r="N235" t="n">
-        <v>0.6075000000000017</v>
+        <v>1.126539943938331</v>
       </c>
       <c r="O235" t="n">
-        <v>-0.1275000000000013</v>
+        <v>-0.08000000000000007</v>
       </c>
       <c r="P235" t="n">
-        <v>0.4007132512671987</v>
+        <v>-0.0885932025227758</v>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
@@ -18703,27 +18785,27 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S235" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="B236" t="n">
         <v>9037610</v>
       </c>
       <c r="C236" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D236" t="n">
-        <v>1349.179809570312</v>
+        <v>661.467041015625</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -18731,13 +18813,13 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G236" t="n">
-        <v>0.6343229543808834</v>
+        <v>0.3966362999299229</v>
       </c>
       <c r="H236" t="n">
-        <v>8.671873642288197</v>
+        <v>5.639106517168885</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -18746,26 +18828,26 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K236" t="n">
-        <v>7.540000000000001</v>
+        <v>4.44</v>
       </c>
       <c r="L236" t="n">
         <v>1</v>
       </c>
       <c r="M236" t="n">
-        <v>1.131873642288197</v>
+        <v>1.199106517168885</v>
       </c>
       <c r="N236" t="n">
-        <v>1.131873642288197</v>
+        <v>1.199106517168885</v>
       </c>
       <c r="O236" t="n">
-        <v>-0.1324999999999985</v>
+        <v>-0.08249999999999957</v>
       </c>
       <c r="P236" t="n">
-        <v>0.3918736422881963</v>
+        <v>-0.009933426769445752</v>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
@@ -18774,7 +18856,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S236" t="b">
@@ -18784,17 +18866,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="B237" t="n">
         <v>9037610</v>
       </c>
       <c r="C237" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D237" t="n">
-        <v>1555.332153320312</v>
+        <v>754.177490234375</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -18802,13 +18884,13 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G237" t="n">
-        <v>0.7306299782766111</v>
+        <v>0.4877365101611773</v>
       </c>
       <c r="H237" t="n">
-        <v>9.375610065170166</v>
+        <v>6.206780833917309</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -18817,26 +18899,26 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K237" t="n">
-        <v>7.455</v>
+        <v>4.33</v>
       </c>
       <c r="L237" t="n">
         <v>1</v>
       </c>
       <c r="M237" t="n">
-        <v>1.920610065170166</v>
+        <v>1.876780833917309</v>
       </c>
       <c r="N237" t="n">
-        <v>1.920610065170166</v>
+        <v>1.876780833917309</v>
       </c>
       <c r="O237" t="n">
-        <v>-0.08500000000000085</v>
+        <v>-0.1100000000000003</v>
       </c>
       <c r="P237" t="n">
-        <v>0.7037364228819687</v>
+        <v>0.5676743167484233</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
@@ -18855,17 +18937,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="B238" t="n">
         <v>9037610</v>
       </c>
       <c r="C238" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D238" t="n">
-        <v>1847.246826171875</v>
+        <v>1018.750366210938</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -18873,13 +18955,13 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G238" t="n">
-        <v>0.8421433743664012</v>
+        <v>0.7259985984583042</v>
       </c>
       <c r="H238" t="n">
-        <v>10.31070963070239</v>
+        <v>7.107843377715487</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -18888,26 +18970,26 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K238" t="n">
-        <v>7.3125</v>
+        <v>4.27</v>
       </c>
       <c r="L238" t="n">
         <v>1</v>
       </c>
       <c r="M238" t="n">
-        <v>2.998209630702389</v>
+        <v>2.837843377715488</v>
       </c>
       <c r="N238" t="n">
-        <v>2.998209630702389</v>
+        <v>2.837843377715488</v>
       </c>
       <c r="O238" t="n">
-        <v>-0.1425000000000001</v>
+        <v>-0.0600000000000005</v>
       </c>
       <c r="P238" t="n">
-        <v>0.935099565532223</v>
+        <v>0.9010625437981785</v>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
@@ -18926,17 +19008,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>27/07/2026</t>
         </is>
       </c>
       <c r="B239" t="n">
         <v>9037610</v>
       </c>
       <c r="C239" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D239" t="n">
-        <v>1936.338989257812</v>
+        <v>1381.897705078125</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -18944,13 +19026,13 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G239" t="n">
-        <v>0.8624185372918175</v>
+        <v>0.8731604765241766</v>
       </c>
       <c r="H239" t="n">
-        <v>10.3546433743664</v>
+        <v>9.469551506657323</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -18959,35 +19041,35 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K239" t="n">
-        <v>7.1775</v>
+        <v>4.265</v>
       </c>
       <c r="L239" t="n">
         <v>1</v>
       </c>
       <c r="M239" t="n">
-        <v>3.1771433743664</v>
+        <v>5.204551506657324</v>
       </c>
       <c r="N239" t="n">
-        <v>3.1771433743664</v>
+        <v>5.204551506657324</v>
       </c>
       <c r="O239" t="n">
-        <v>-0.1349999999999998</v>
+        <v>-0.004999999999999893</v>
       </c>
       <c r="P239" t="n">
-        <v>0.04393374366401126</v>
+        <v>2.361708128941836</v>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S239" t="b">
@@ -18997,17 +19079,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="B240" t="n">
         <v>9037610</v>
       </c>
       <c r="C240" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D240" t="n">
-        <v>1716.46044921875</v>
+        <v>1622.851928710938</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -19015,13 +19097,13 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G240" t="n">
-        <v>0.7986965966690803</v>
+        <v>0.9110021023125437</v>
       </c>
       <c r="H240" t="n">
-        <v>9.667051049963796</v>
+        <v>10.26965662228451</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -19030,55 +19112,55 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K240" t="n">
-        <v>7</v>
+        <v>4.29</v>
       </c>
       <c r="L240" t="n">
         <v>1</v>
       </c>
       <c r="M240" t="n">
-        <v>2.667051049963796</v>
+        <v>5.979656622284513</v>
       </c>
       <c r="N240" t="n">
-        <v>2.667051049963796</v>
+        <v>5.979656622284513</v>
       </c>
       <c r="O240" t="n">
-        <v>-0.1775000000000002</v>
+        <v>0.02500000000000036</v>
       </c>
       <c r="P240" t="n">
-        <v>-0.6875923244026048</v>
+        <v>0.8001051156271899</v>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S240" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="B241" t="n">
         <v>9037610</v>
       </c>
       <c r="C241" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D241" t="n">
-        <v>1418.8515625</v>
+        <v>1592.513793945312</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -19086,13 +19168,13 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G241" t="n">
-        <v>0.6741491672700941</v>
+        <v>0.9074982480728802</v>
       </c>
       <c r="H241" t="n">
-        <v>9.004127443881243</v>
+        <v>10.26180974071479</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -19101,35 +19183,35 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K241" t="n">
-        <v>6.8325</v>
+        <v>4.33</v>
       </c>
       <c r="L241" t="n">
         <v>1</v>
       </c>
       <c r="M241" t="n">
-        <v>2.171627443881244</v>
+        <v>5.931809740714787</v>
       </c>
       <c r="N241" t="n">
-        <v>2.171627443881244</v>
+        <v>5.931809740714787</v>
       </c>
       <c r="O241" t="n">
-        <v>-0.1675000000000004</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="P241" t="n">
-        <v>-0.6629236060825523</v>
+        <v>-0.007846881569726349</v>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S241" t="b">
@@ -19139,17 +19221,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="B242" t="n">
         <v>9037610</v>
       </c>
       <c r="C242" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D242" t="n">
-        <v>1278.904907226562</v>
+        <v>1342.423217773438</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -19157,13 +19239,13 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G242" t="n">
-        <v>0.5973931933381608</v>
+        <v>0.8633496846531185</v>
       </c>
       <c r="H242" t="n">
-        <v>8.358010499637944</v>
+        <v>9.288601962158374</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -19172,26 +19254,26 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K242" t="n">
-        <v>6.630000000000001</v>
+        <v>4.2775</v>
       </c>
       <c r="L242" t="n">
         <v>1</v>
       </c>
       <c r="M242" t="n">
-        <v>1.728010499637943</v>
+        <v>5.011101962158374</v>
       </c>
       <c r="N242" t="n">
-        <v>1.728010499637943</v>
+        <v>5.011101962158374</v>
       </c>
       <c r="O242" t="n">
-        <v>-0.2024999999999988</v>
+        <v>-0.05250000000000021</v>
       </c>
       <c r="P242" t="n">
-        <v>-0.6461169442432997</v>
+        <v>-0.9732077785564126</v>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
@@ -19210,17 +19292,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="B243" t="n">
         <v>9037610</v>
       </c>
       <c r="C243" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D243" t="n">
-        <v>1315.468872070312</v>
+        <v>1037.824829101562</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -19228,13 +19310,13 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G243" t="n">
-        <v>0.6176683562635771</v>
+        <v>0.7414155571128241</v>
       </c>
       <c r="H243" t="n">
-        <v>8.553837798696597</v>
+        <v>7.160918009810792</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -19243,26 +19325,26 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K243" t="n">
-        <v>6.4075</v>
+        <v>4.1525</v>
       </c>
       <c r="L243" t="n">
         <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>2.146337798696597</v>
+        <v>3.008418009810792</v>
       </c>
       <c r="N243" t="n">
-        <v>2.146337798696597</v>
+        <v>3.008418009810792</v>
       </c>
       <c r="O243" t="n">
-        <v>-0.222500000000001</v>
+        <v>-0.125</v>
       </c>
       <c r="P243" t="n">
-        <v>0.1958272990586529</v>
+        <v>-2.127683952347582</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -19271,27 +19353,27 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="B244" t="n">
         <v>9037610</v>
       </c>
       <c r="C244" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D244" t="n">
-        <v>1380.773071289062</v>
+        <v>802.1289672851562</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -19299,13 +19381,13 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G244" t="n">
-        <v>0.6524257784214338</v>
+        <v>0.8282469836763662</v>
       </c>
       <c r="H244" t="n">
-        <v>8.841011947863867</v>
+        <v>5.559905961674946</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -19314,26 +19396,26 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K244" t="n">
-        <v>6.2475</v>
+        <v>3.99</v>
       </c>
       <c r="L244" t="n">
         <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>2.593511947863868</v>
+        <v>1.569905961674946</v>
       </c>
       <c r="N244" t="n">
-        <v>2.593511947863868</v>
+        <v>1.569905961674946</v>
       </c>
       <c r="O244" t="n">
-        <v>-0.1600000000000001</v>
+        <v>-0.1624999999999996</v>
       </c>
       <c r="P244" t="n">
-        <v>0.2871741491672708</v>
+        <v>-1.601012048135845</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -19342,27 +19424,27 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S244" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B245" t="n">
         <v>9037610</v>
       </c>
       <c r="C245" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D245" t="n">
-        <v>1347.59033203125</v>
+        <v>659.7947387695312</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -19370,13 +19452,13 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G245" t="n">
-        <v>0.6321506154960174</v>
+        <v>0.7054648687012065</v>
       </c>
       <c r="H245" t="n">
-        <v>8.660077842143373</v>
+        <v>4.933722498225691</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -19385,26 +19467,26 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K245" t="n">
-        <v>6.097499999999999</v>
+        <v>3.8225</v>
       </c>
       <c r="L245" t="n">
         <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>2.562577842143374</v>
+        <v>1.111222498225692</v>
       </c>
       <c r="N245" t="n">
-        <v>2.562577842143374</v>
+        <v>1.111222498225692</v>
       </c>
       <c r="O245" t="n">
-        <v>-0.1500000000000004</v>
+        <v>-0.1675000000000004</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.1809341057204943</v>
+        <v>-0.6261834634492551</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -19423,17 +19505,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="B246" t="n">
         <v>9037610</v>
       </c>
       <c r="C246" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D246" t="n">
-        <v>1241.775268554688</v>
+        <v>589.841796875</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -19441,13 +19523,13 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G246" t="n">
-        <v>0.5821868211440985</v>
+        <v>0.6167494677075941</v>
       </c>
       <c r="H246" t="n">
-        <v>8.279999999999999</v>
+        <v>4.631584457061746</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -19456,30 +19538,30 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K246" t="n">
-        <v>5.909999999999999</v>
+        <v>3.78</v>
       </c>
       <c r="L246" t="n">
         <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>2.37</v>
+        <v>0.8515844570617461</v>
       </c>
       <c r="N246" t="n">
-        <v>2.37</v>
+        <v>0.8515844570617461</v>
       </c>
       <c r="O246" t="n">
-        <v>-0.1875</v>
+        <v>-0.04249999999999998</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.3800778421433737</v>
+        <v>-0.3021380411639454</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
@@ -19488,23 +19570,23 @@
         </is>
       </c>
       <c r="S246" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="B247" t="n">
         <v>9037610</v>
       </c>
       <c r="C247" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D247" t="n">
-        <v>1146.361694335938</v>
+        <v>577.418701171875</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -19512,13 +19594,13 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G247" t="n">
-        <v>0.5119478638667632</v>
+        <v>0.5947480482611781</v>
       </c>
       <c r="H247" t="n">
-        <v>7.999815351194785</v>
+        <v>4.573930092264017</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -19527,26 +19609,26 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K247" t="n">
-        <v>5.81</v>
+        <v>3.68</v>
       </c>
       <c r="L247" t="n">
         <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>2.189815351194786</v>
+        <v>0.8939300922640165</v>
       </c>
       <c r="N247" t="n">
-        <v>2.189815351194786</v>
+        <v>0.8939300922640165</v>
       </c>
       <c r="O247" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P247" t="n">
-        <v>-0.2801846488052142</v>
+        <v>-0.05765436479772923</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -19565,17 +19647,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B248" t="n">
         <v>9037610</v>
       </c>
       <c r="C248" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D248" t="n">
-        <v>1091.406127929688</v>
+        <v>602.1062622070312</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -19583,13 +19665,13 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G248" t="n">
-        <v>0.4721216509775525</v>
+        <v>0.6352022711142654</v>
       </c>
       <c r="H248" t="n">
-        <v>7.782255611875453</v>
+        <v>4.726218949609652</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19598,26 +19680,26 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K248" t="n">
-        <v>5.6</v>
+        <v>3.58</v>
       </c>
       <c r="L248" t="n">
         <v>1</v>
       </c>
       <c r="M248" t="n">
-        <v>2.182255611875453</v>
+        <v>1.146218949609652</v>
       </c>
       <c r="N248" t="n">
-        <v>2.182255611875453</v>
+        <v>1.146218949609652</v>
       </c>
       <c r="O248" t="n">
-        <v>-0.21</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="P248" t="n">
-        <v>-0.2175597393193325</v>
+        <v>0.1522888573456358</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -19626,27 +19708,27 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="B249" t="n">
         <v>9037610</v>
       </c>
       <c r="C249" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D249" t="n">
-        <v>1070.248046875</v>
+        <v>614.3157348632812</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -19654,13 +19736,13 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G249" t="n">
-        <v>0.4554670528602462</v>
+        <v>0.6479772888573456</v>
       </c>
       <c r="H249" t="n">
-        <v>7.631895365677046</v>
+        <v>4.761873669268985</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19669,26 +19751,26 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K249" t="n">
-        <v>5.387499999999999</v>
+        <v>3.3925</v>
       </c>
       <c r="L249" t="n">
         <v>1</v>
       </c>
       <c r="M249" t="n">
-        <v>2.244395365677047</v>
+        <v>1.369373669268985</v>
       </c>
       <c r="N249" t="n">
-        <v>2.244395365677047</v>
+        <v>1.369373669268985</v>
       </c>
       <c r="O249" t="n">
-        <v>-0.2125000000000004</v>
+        <v>-0.1875</v>
       </c>
       <c r="P249" t="n">
-        <v>-0.1503602461984066</v>
+        <v>0.0356547196593322</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -19697,27 +19779,27 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="B250" t="n">
         <v>9037610</v>
       </c>
       <c r="C250" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D250" t="n">
-        <v>1049.676147460938</v>
+        <v>578.5484619140625</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -19725,13 +19807,13 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G250" t="n">
-        <v>0.440984793627806</v>
+        <v>0.5975869410929737</v>
       </c>
       <c r="H250" t="n">
-        <v>7.447729905865315</v>
+        <v>4.602886799148332</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19740,26 +19822,26 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K250" t="n">
-        <v>5.1825</v>
+        <v>3.28</v>
       </c>
       <c r="L250" t="n">
         <v>1</v>
       </c>
       <c r="M250" t="n">
-        <v>2.265229905865315</v>
+        <v>1.322886799148332</v>
       </c>
       <c r="N250" t="n">
-        <v>2.265229905865315</v>
+        <v>1.322886799148332</v>
       </c>
       <c r="O250" t="n">
-        <v>-0.2049999999999992</v>
+        <v>-0.1125000000000003</v>
       </c>
       <c r="P250" t="n">
-        <v>-0.184165459811731</v>
+        <v>-0.1589868701206525</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -19778,17 +19860,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="B251" t="n">
         <v>9037610</v>
       </c>
       <c r="C251" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D251" t="n">
-        <v>1003.006530761719</v>
+        <v>515.4163208007812</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -19796,13 +19878,13 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G251" t="n">
-        <v>0.4033309196234612</v>
+        <v>0.4918381831085876</v>
       </c>
       <c r="H251" t="n">
-        <v>7.075148443157131</v>
+        <v>4.157549680624556</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19811,26 +19893,26 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K251" t="n">
-        <v>5.0625</v>
+        <v>3.15</v>
       </c>
       <c r="L251" t="n">
         <v>1</v>
       </c>
       <c r="M251" t="n">
-        <v>2.012648443157131</v>
+        <v>1.007549680624556</v>
       </c>
       <c r="N251" t="n">
-        <v>2.012648443157131</v>
+        <v>1.007549680624556</v>
       </c>
       <c r="O251" t="n">
-        <v>-0.1200000000000001</v>
+        <v>-0.1299999999999999</v>
       </c>
       <c r="P251" t="n">
-        <v>-0.372581462708184</v>
+        <v>-0.445337118523776</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -19849,17 +19931,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="B252" t="n">
         <v>9037610</v>
       </c>
       <c r="C252" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D252" t="n">
-        <v>960.0022583007812</v>
+        <v>462.6813659667969</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -19867,13 +19949,13 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3685734974656046</v>
+        <v>0.3924769339957417</v>
       </c>
       <c r="H252" t="n">
-        <v>6.722413106444606</v>
+        <v>3.807744854506742</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19882,26 +19964,26 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K252" t="n">
-        <v>4.99</v>
+        <v>2.945</v>
       </c>
       <c r="L252" t="n">
         <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>1.732413106444605</v>
+        <v>0.8627448545067424</v>
       </c>
       <c r="N252" t="n">
-        <v>1.732413106444605</v>
+        <v>0.8627448545067424</v>
       </c>
       <c r="O252" t="n">
-        <v>-0.07249999999999979</v>
+        <v>-0.2050000000000001</v>
       </c>
       <c r="P252" t="n">
-        <v>-0.3527353367125254</v>
+        <v>-0.3498048261178139</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -19920,17 +20002,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>27/06/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="B253" t="n">
         <v>9037610</v>
       </c>
       <c r="C253" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D253" t="n">
-        <v>976.1466674804688</v>
+        <v>433.1435852050781</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -19938,13 +20020,13 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G253" t="n">
-        <v>0.3823316437364229</v>
+        <v>0.3378282469836764</v>
       </c>
       <c r="H253" t="n">
-        <v>6.851035481535121</v>
+        <v>3.645282706411166</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -19953,55 +20035,55 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K253" t="n">
-        <v>4.9725</v>
+        <v>2.84</v>
       </c>
       <c r="L253" t="n">
         <v>1</v>
       </c>
       <c r="M253" t="n">
-        <v>1.878535481535121</v>
+        <v>0.8052827064111665</v>
       </c>
       <c r="N253" t="n">
-        <v>1.878535481535121</v>
+        <v>0.8052827064111665</v>
       </c>
       <c r="O253" t="n">
-        <v>-0.01750000000000007</v>
+        <v>-0.105</v>
       </c>
       <c r="P253" t="n">
-        <v>0.1286223750905151</v>
+        <v>-0.1624621480955759</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S253" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>28/06/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="B254" t="n">
         <v>9037610</v>
       </c>
       <c r="C254" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D254" t="n">
-        <v>1046.956787109375</v>
+        <v>439.565185546875</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -20009,13 +20091,13 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G254" t="n">
-        <v>0.4380883417813179</v>
+        <v>0.3484740951029099</v>
       </c>
       <c r="H254" t="n">
-        <v>7.426759594496741</v>
+        <v>3.682439673527325</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -20024,26 +20106,26 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K254" t="n">
-        <v>4.8975</v>
+        <v>2.77</v>
       </c>
       <c r="L254" t="n">
         <v>1</v>
       </c>
       <c r="M254" t="n">
-        <v>2.529259594496741</v>
+        <v>0.9124396735273246</v>
       </c>
       <c r="N254" t="n">
-        <v>2.529259594496741</v>
+        <v>0.9124396735273246</v>
       </c>
       <c r="O254" t="n">
-        <v>-0.07500000000000018</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="P254" t="n">
-        <v>0.5757241129616206</v>
+        <v>0.03715696711615823</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -20052,7 +20134,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S254" t="b">
@@ -20062,17 +20144,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="B255" t="n">
         <v>9037610</v>
       </c>
       <c r="C255" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D255" t="n">
-        <v>1080.954223632812</v>
+        <v>517.8302612304688</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -20080,13 +20162,13 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>0.4627081824764663</v>
+        <v>0.496096522356281</v>
       </c>
       <c r="H255" t="n">
-        <v>7.663756335988414</v>
+        <v>4.180046132008517</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -20095,30 +20177,30 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K255" t="n">
-        <v>4.787500000000001</v>
+        <v>2.82</v>
       </c>
       <c r="L255" t="n">
         <v>1</v>
       </c>
       <c r="M255" t="n">
-        <v>2.876256335988413</v>
+        <v>1.360046132008517</v>
       </c>
       <c r="N255" t="n">
-        <v>2.876256335988413</v>
+        <v>1.360046132008517</v>
       </c>
       <c r="O255" t="n">
-        <v>-0.1099999999999985</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="P255" t="n">
-        <v>0.2369967414916729</v>
+        <v>0.4976064584811923</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -20133,17 +20215,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="B256" t="n">
         <v>9037610</v>
       </c>
       <c r="C256" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D256" t="n">
-        <v>1000.768493652344</v>
+        <v>651.8656616210938</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -20151,13 +20233,13 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>0.4011585807385952</v>
+        <v>0.6969481902058198</v>
       </c>
       <c r="H256" t="n">
-        <v>7.045727733526429</v>
+        <v>4.907661462029809</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -20166,26 +20248,26 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>PUERTO ALMENDRA</t>
+          <t>PUERTO ALMENDRAS</t>
         </is>
       </c>
       <c r="K256" t="n">
-        <v>4.6325</v>
+        <v>2.75</v>
       </c>
       <c r="L256" t="n">
         <v>1</v>
       </c>
       <c r="M256" t="n">
-        <v>2.413227733526429</v>
+        <v>2.157661462029809</v>
       </c>
       <c r="N256" t="n">
-        <v>2.413227733526429</v>
+        <v>2.157661462029809</v>
       </c>
       <c r="O256" t="n">
-        <v>-0.1550000000000011</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="P256" t="n">
-        <v>-0.618028602461985</v>
+        <v>0.7276153300212922</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -20194,11 +20276,11 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="S256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -33859,6 +33941,2130 @@
         </is>
       </c>
       <c r="S449" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C450" t="n">
+        <v>7</v>
+      </c>
+      <c r="D450" t="n">
+        <v>31504.240234375</v>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F450" t="n">
+        <v>7</v>
+      </c>
+      <c r="G450" t="n">
+        <v>0.7680448493342676</v>
+      </c>
+      <c r="H450" t="n">
+        <v>9.374316748423263</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K450" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="L450" t="n">
+        <v>1</v>
+      </c>
+      <c r="M450" t="n">
+        <v>-0.9656832515767366</v>
+      </c>
+      <c r="N450" t="n">
+        <v>0.9656832515767366</v>
+      </c>
+      <c r="O450" t="inlineStr"/>
+      <c r="P450" t="inlineStr"/>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>Sin dato</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>Sin dato</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C451" t="n">
+        <v>7</v>
+      </c>
+      <c r="D451" t="n">
+        <v>31371.638671875</v>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F451" t="n">
+        <v>7</v>
+      </c>
+      <c r="G451" t="n">
+        <v>0.759635599159075</v>
+      </c>
+      <c r="H451" t="n">
+        <v>9.325746320953048</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K451" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L451" t="n">
+        <v>1</v>
+      </c>
+      <c r="M451" t="n">
+        <v>-0.8742536790469515</v>
+      </c>
+      <c r="N451" t="n">
+        <v>0.8742536790469515</v>
+      </c>
+      <c r="O451" t="n">
+        <v>-0.1400000000000006</v>
+      </c>
+      <c r="P451" t="n">
+        <v>-0.04857042747021545</v>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="S451" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C452" t="n">
+        <v>7</v>
+      </c>
+      <c r="D452" t="n">
+        <v>31282.869140625</v>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F452" t="n">
+        <v>7</v>
+      </c>
+      <c r="G452" t="n">
+        <v>0.7547302032235459</v>
+      </c>
+      <c r="H452" t="n">
+        <v>9.318556412053258</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K452" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="L452" t="n">
+        <v>1</v>
+      </c>
+      <c r="M452" t="n">
+        <v>-0.7714435879467416</v>
+      </c>
+      <c r="N452" t="n">
+        <v>0.7714435879467416</v>
+      </c>
+      <c r="O452" t="n">
+        <v>-0.1099999999999994</v>
+      </c>
+      <c r="P452" t="n">
+        <v>-0.007189908899789543</v>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="S452" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C453" t="n">
+        <v>7</v>
+      </c>
+      <c r="D453" t="n">
+        <v>31179.1015625</v>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F453" t="n">
+        <v>7</v>
+      </c>
+      <c r="G453" t="n">
+        <v>0.7491240364400841</v>
+      </c>
+      <c r="H453" t="n">
+        <v>9.290637701471619</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K453" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="L453" t="n">
+        <v>1</v>
+      </c>
+      <c r="M453" t="n">
+        <v>-0.6993622985283814</v>
+      </c>
+      <c r="N453" t="n">
+        <v>0.6993622985283814</v>
+      </c>
+      <c r="O453" t="n">
+        <v>-0.09999999999999964</v>
+      </c>
+      <c r="P453" t="n">
+        <v>-0.02791871058163942</v>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="S453" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C454" t="n">
+        <v>7</v>
+      </c>
+      <c r="D454" t="n">
+        <v>30998.7421875</v>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F454" t="n">
+        <v>7</v>
+      </c>
+      <c r="G454" t="n">
+        <v>0.7386124737210932</v>
+      </c>
+      <c r="H454" t="n">
+        <v>9.258290119131043</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K454" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="L454" t="n">
+        <v>1</v>
+      </c>
+      <c r="M454" t="n">
+        <v>-0.5817098808689565</v>
+      </c>
+      <c r="N454" t="n">
+        <v>0.5817098808689565</v>
+      </c>
+      <c r="O454" t="n">
+        <v>-0.1500000000000004</v>
+      </c>
+      <c r="P454" t="n">
+        <v>-0.03234758234057544</v>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="S454" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C455" t="n">
+        <v>7</v>
+      </c>
+      <c r="D455" t="n">
+        <v>30724.009765625</v>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F455" t="n">
+        <v>7</v>
+      </c>
+      <c r="G455" t="n">
+        <v>0.7266993693062369</v>
+      </c>
+      <c r="H455" t="n">
+        <v>9.08948142957253</v>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K455" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="L455" t="n">
+        <v>1</v>
+      </c>
+      <c r="M455" t="n">
+        <v>-0.6605185704274703</v>
+      </c>
+      <c r="N455" t="n">
+        <v>0.6605185704274703</v>
+      </c>
+      <c r="O455" t="n">
+        <v>-0.08999999999999986</v>
+      </c>
+      <c r="P455" t="n">
+        <v>-0.1688086895585137</v>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S455" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C456" t="n">
+        <v>7</v>
+      </c>
+      <c r="D456" t="n">
+        <v>30386.80859375</v>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F456" t="n">
+        <v>7</v>
+      </c>
+      <c r="G456" t="n">
+        <v>0.7056762438682551</v>
+      </c>
+      <c r="H456" t="n">
+        <v>9.038535388927821</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K456" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="L456" t="n">
+        <v>1</v>
+      </c>
+      <c r="M456" t="n">
+        <v>-0.7414646110721783</v>
+      </c>
+      <c r="N456" t="n">
+        <v>0.7414646110721783</v>
+      </c>
+      <c r="O456" t="n">
+        <v>0.02999999999999936</v>
+      </c>
+      <c r="P456" t="n">
+        <v>-0.05094604064470865</v>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S456" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C457" t="n">
+        <v>7</v>
+      </c>
+      <c r="D457" t="n">
+        <v>30021.23828125</v>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F457" t="n">
+        <v>7</v>
+      </c>
+      <c r="G457" t="n">
+        <v>0.6818500350385424</v>
+      </c>
+      <c r="H457" t="n">
+        <v>8.82780658724597</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K457" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="L457" t="n">
+        <v>1</v>
+      </c>
+      <c r="M457" t="n">
+        <v>-0.9621934127540293</v>
+      </c>
+      <c r="N457" t="n">
+        <v>0.9621934127540293</v>
+      </c>
+      <c r="O457" t="n">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="P457" t="n">
+        <v>-0.2107288016818512</v>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S457" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C458" t="n">
+        <v>7</v>
+      </c>
+      <c r="D458" t="n">
+        <v>29645.974609375</v>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F458" t="n">
+        <v>7</v>
+      </c>
+      <c r="G458" t="n">
+        <v>0.6587245970567625</v>
+      </c>
+      <c r="H458" t="n">
+        <v>8.740224246671339</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K458" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="L458" t="n">
+        <v>1</v>
+      </c>
+      <c r="M458" t="n">
+        <v>-1.069775753328662</v>
+      </c>
+      <c r="N458" t="n">
+        <v>1.069775753328662</v>
+      </c>
+      <c r="O458" t="n">
+        <v>0.02000000000000135</v>
+      </c>
+      <c r="P458" t="n">
+        <v>-0.08758234057463099</v>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S458" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C459" t="n">
+        <v>7</v>
+      </c>
+      <c r="D459" t="n">
+        <v>29281.111328125</v>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F459" t="n">
+        <v>7</v>
+      </c>
+      <c r="G459" t="n">
+        <v>0.6334968465311843</v>
+      </c>
+      <c r="H459" t="n">
+        <v>8.577035739313244</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K459" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="L459" t="n">
+        <v>1</v>
+      </c>
+      <c r="M459" t="n">
+        <v>-1.252964260686756</v>
+      </c>
+      <c r="N459" t="n">
+        <v>1.252964260686756</v>
+      </c>
+      <c r="O459" t="n">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="P459" t="n">
+        <v>-0.163188507358095</v>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S459" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C460" t="n">
+        <v>7</v>
+      </c>
+      <c r="D460" t="n">
+        <v>28955.763671875</v>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F460" t="n">
+        <v>7</v>
+      </c>
+      <c r="G460" t="n">
+        <v>0.6075683251576735</v>
+      </c>
+      <c r="H460" t="n">
+        <v>8.396422564821304</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K460" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="L460" t="n">
+        <v>1</v>
+      </c>
+      <c r="M460" t="n">
+        <v>-1.423577435178697</v>
+      </c>
+      <c r="N460" t="n">
+        <v>1.423577435178697</v>
+      </c>
+      <c r="O460" t="n">
+        <v>-0.009999999999999787</v>
+      </c>
+      <c r="P460" t="n">
+        <v>-0.1806131744919401</v>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S460" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>25/07/2026</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C461" t="n">
+        <v>7</v>
+      </c>
+      <c r="D461" t="n">
+        <v>28724.4140625</v>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F461" t="n">
+        <v>7</v>
+      </c>
+      <c r="G461" t="n">
+        <v>0.5956552207428171</v>
+      </c>
+      <c r="H461" t="n">
+        <v>8.373181499649615</v>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K461" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="L461" t="n">
+        <v>1</v>
+      </c>
+      <c r="M461" t="n">
+        <v>-1.336818500350386</v>
+      </c>
+      <c r="N461" t="n">
+        <v>1.336818500350386</v>
+      </c>
+      <c r="O461" t="n">
+        <v>-0.1099999999999994</v>
+      </c>
+      <c r="P461" t="n">
+        <v>-0.023241065171689</v>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="S461" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C462" t="n">
+        <v>7</v>
+      </c>
+      <c r="D462" t="n">
+        <v>28673.759765625</v>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F462" t="n">
+        <v>7</v>
+      </c>
+      <c r="G462" t="n">
+        <v>0.593552908199019</v>
+      </c>
+      <c r="H462" t="n">
+        <v>8.361786965662228</v>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K462" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="L462" t="n">
+        <v>1</v>
+      </c>
+      <c r="M462" t="n">
+        <v>-1.188213034337773</v>
+      </c>
+      <c r="N462" t="n">
+        <v>1.188213034337773</v>
+      </c>
+      <c r="O462" t="n">
+        <v>-0.1600000000000001</v>
+      </c>
+      <c r="P462" t="n">
+        <v>-0.01139453398738688</v>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="S462" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C463" t="n">
+        <v>7</v>
+      </c>
+      <c r="D463" t="n">
+        <v>28832.76953125</v>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F463" t="n">
+        <v>7</v>
+      </c>
+      <c r="G463" t="n">
+        <v>0.6005606166783461</v>
+      </c>
+      <c r="H463" t="n">
+        <v>8.385395935529083</v>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K463" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="L463" t="n">
+        <v>1</v>
+      </c>
+      <c r="M463" t="n">
+        <v>-0.9646040644709171</v>
+      </c>
+      <c r="N463" t="n">
+        <v>0.9646040644709171</v>
+      </c>
+      <c r="O463" t="n">
+        <v>-0.2000000000000011</v>
+      </c>
+      <c r="P463" t="n">
+        <v>0.02360896986685468</v>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="S463" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C464" t="n">
+        <v>7</v>
+      </c>
+      <c r="D464" t="n">
+        <v>29066.732421875</v>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F464" t="n">
+        <v>7</v>
+      </c>
+      <c r="G464" t="n">
+        <v>0.613875262789068</v>
+      </c>
+      <c r="H464" t="n">
+        <v>8.434197617379118</v>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K464" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="L464" t="n">
+        <v>1</v>
+      </c>
+      <c r="M464" t="n">
+        <v>-0.8358023826208818</v>
+      </c>
+      <c r="N464" t="n">
+        <v>0.8358023826208818</v>
+      </c>
+      <c r="O464" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="P464" t="n">
+        <v>0.04880168185003519</v>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="S464" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C465" t="n">
+        <v>7</v>
+      </c>
+      <c r="D465" t="n">
+        <v>29154.50390625</v>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F465" t="n">
+        <v>7</v>
+      </c>
+      <c r="G465" t="n">
+        <v>0.6250875963559915</v>
+      </c>
+      <c r="H465" t="n">
+        <v>8.492638402242466</v>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K465" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="L465" t="n">
+        <v>1</v>
+      </c>
+      <c r="M465" t="n">
+        <v>-0.787361597757533</v>
+      </c>
+      <c r="N465" t="n">
+        <v>0.787361597757533</v>
+      </c>
+      <c r="O465" t="n">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="P465" t="n">
+        <v>0.05844078486334858</v>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="S465" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C466" t="n">
+        <v>7</v>
+      </c>
+      <c r="D466" t="n">
+        <v>28971.6796875</v>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F466" t="n">
+        <v>7</v>
+      </c>
+      <c r="G466" t="n">
+        <v>0.6096706377014717</v>
+      </c>
+      <c r="H466" t="n">
+        <v>8.399039943938332</v>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K466" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="L466" t="n">
+        <v>1</v>
+      </c>
+      <c r="M466" t="n">
+        <v>-0.9209600560616682</v>
+      </c>
+      <c r="N466" t="n">
+        <v>0.9209600560616682</v>
+      </c>
+      <c r="O466" t="n">
+        <v>0.04000000000000092</v>
+      </c>
+      <c r="P466" t="n">
+        <v>-0.09359845830413427</v>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S466" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C467" t="n">
+        <v>7</v>
+      </c>
+      <c r="D467" t="n">
+        <v>28584.86328125</v>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F467" t="n">
+        <v>7</v>
+      </c>
+      <c r="G467" t="n">
+        <v>0.5872459705676244</v>
+      </c>
+      <c r="H467" t="n">
+        <v>8.298969866853538</v>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K467" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="L467" t="n">
+        <v>1</v>
+      </c>
+      <c r="M467" t="n">
+        <v>-1.031030133146462</v>
+      </c>
+      <c r="N467" t="n">
+        <v>1.031030133146462</v>
+      </c>
+      <c r="O467" t="n">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="P467" t="n">
+        <v>-0.1000700770847942</v>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S467" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C468" t="n">
+        <v>8</v>
+      </c>
+      <c r="D468" t="n">
+        <v>28149.9453125</v>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F468" t="n">
+        <v>8</v>
+      </c>
+      <c r="G468" t="n">
+        <v>0.8424414478353442</v>
+      </c>
+      <c r="H468" t="n">
+        <v>8.541043293115687</v>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K468" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="L468" t="n">
+        <v>1</v>
+      </c>
+      <c r="M468" t="n">
+        <v>-0.6989567068843137</v>
+      </c>
+      <c r="N468" t="n">
+        <v>0.6989567068843137</v>
+      </c>
+      <c r="O468" t="n">
+        <v>-0.08999999999999986</v>
+      </c>
+      <c r="P468" t="n">
+        <v>0.2420734262621487</v>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="S468" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C469" t="n">
+        <v>8</v>
+      </c>
+      <c r="D469" t="n">
+        <v>27772.720703125</v>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F469" t="n">
+        <v>8</v>
+      </c>
+      <c r="G469" t="n">
+        <v>0.8254080908445706</v>
+      </c>
+      <c r="H469" t="n">
+        <v>8.275372604684172</v>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K469" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="L469" t="n">
+        <v>1</v>
+      </c>
+      <c r="M469" t="n">
+        <v>-0.7746273953158287</v>
+      </c>
+      <c r="N469" t="n">
+        <v>0.7746273953158287</v>
+      </c>
+      <c r="O469" t="n">
+        <v>-0.1899999999999995</v>
+      </c>
+      <c r="P469" t="n">
+        <v>-0.2656706884315145</v>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S469" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C470" t="n">
+        <v>8</v>
+      </c>
+      <c r="D470" t="n">
+        <v>27487.14453125</v>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F470" t="n">
+        <v>8</v>
+      </c>
+      <c r="G470" t="n">
+        <v>0.8062455642299503</v>
+      </c>
+      <c r="H470" t="n">
+        <v>7.983144073811213</v>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K470" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="L470" t="n">
+        <v>1</v>
+      </c>
+      <c r="M470" t="n">
+        <v>-0.9268559261887868</v>
+      </c>
+      <c r="N470" t="n">
+        <v>0.9268559261887868</v>
+      </c>
+      <c r="O470" t="n">
+        <v>-0.1400000000000006</v>
+      </c>
+      <c r="P470" t="n">
+        <v>-0.2922285308729586</v>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S470" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C471" t="n">
+        <v>8</v>
+      </c>
+      <c r="D471" t="n">
+        <v>27309.828125</v>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F471" t="n">
+        <v>8</v>
+      </c>
+      <c r="G471" t="n">
+        <v>0.794180269694819</v>
+      </c>
+      <c r="H471" t="n">
+        <v>7.891256210078069</v>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K471" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="L471" t="n">
+        <v>1</v>
+      </c>
+      <c r="M471" t="n">
+        <v>-0.8787437899219306</v>
+      </c>
+      <c r="N471" t="n">
+        <v>0.8787437899219306</v>
+      </c>
+      <c r="O471" t="n">
+        <v>-0.1400000000000006</v>
+      </c>
+      <c r="P471" t="n">
+        <v>-0.09188786373314439</v>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S471" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C472" t="n">
+        <v>8</v>
+      </c>
+      <c r="D472" t="n">
+        <v>27282.892578125</v>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F472" t="n">
+        <v>8</v>
+      </c>
+      <c r="G472" t="n">
+        <v>0.7920511000709723</v>
+      </c>
+      <c r="H472" t="n">
+        <v>7.86709013484741</v>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K472" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="L472" t="n">
+        <v>1</v>
+      </c>
+      <c r="M472" t="n">
+        <v>-0.7129098651525902</v>
+      </c>
+      <c r="N472" t="n">
+        <v>0.7129098651525902</v>
+      </c>
+      <c r="O472" t="n">
+        <v>-0.1899999999999995</v>
+      </c>
+      <c r="P472" t="n">
+        <v>-0.02416607523065917</v>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="S472" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C473" t="n">
+        <v>8</v>
+      </c>
+      <c r="D473" t="n">
+        <v>27418.703125</v>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F473" t="n">
+        <v>8</v>
+      </c>
+      <c r="G473" t="n">
+        <v>0.8026969481902059</v>
+      </c>
+      <c r="H473" t="n">
+        <v>7.927366926898509</v>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K473" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="L473" t="n">
+        <v>1</v>
+      </c>
+      <c r="M473" t="n">
+        <v>-0.5226330731014901</v>
+      </c>
+      <c r="N473" t="n">
+        <v>0.5226330731014901</v>
+      </c>
+      <c r="O473" t="n">
+        <v>-0.1300000000000008</v>
+      </c>
+      <c r="P473" t="n">
+        <v>0.06027679205109937</v>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="S473" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C474" t="n">
+        <v>8</v>
+      </c>
+      <c r="D474" t="n">
+        <v>27638.591796875</v>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F474" t="n">
+        <v>8</v>
+      </c>
+      <c r="G474" t="n">
+        <v>0.815471965933286</v>
+      </c>
+      <c r="H474" t="n">
+        <v>8.192789212207238</v>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K474" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="L474" t="n">
+        <v>1</v>
+      </c>
+      <c r="M474" t="n">
+        <v>-0.1272107877927624</v>
+      </c>
+      <c r="N474" t="n">
+        <v>0.1272107877927624</v>
+      </c>
+      <c r="O474" t="n">
+        <v>-0.129999999999999</v>
+      </c>
+      <c r="P474" t="n">
+        <v>0.2654222853087287</v>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="S474" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C475" t="n">
+        <v>8</v>
+      </c>
+      <c r="D475" t="n">
+        <v>27833.845703125</v>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F475" t="n">
+        <v>8</v>
+      </c>
+      <c r="G475" t="n">
+        <v>0.8275372604684174</v>
+      </c>
+      <c r="H475" t="n">
+        <v>8.300794889992902</v>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K475" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="L475" t="n">
+        <v>1</v>
+      </c>
+      <c r="M475" t="n">
+        <v>0.04079488999290248</v>
+      </c>
+      <c r="N475" t="n">
+        <v>0.04079488999290248</v>
+      </c>
+      <c r="O475" t="n">
+        <v>-0.0600000000000005</v>
+      </c>
+      <c r="P475" t="n">
+        <v>0.1080056777856644</v>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="S475" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C476" t="n">
+        <v>8</v>
+      </c>
+      <c r="D476" t="n">
+        <v>27948.130859375</v>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F476" t="n">
+        <v>8</v>
+      </c>
+      <c r="G476" t="n">
+        <v>0.8360539389638041</v>
+      </c>
+      <c r="H476" t="n">
+        <v>8.457494677075941</v>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K476" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L476" t="n">
+        <v>1</v>
+      </c>
+      <c r="M476" t="n">
+        <v>0.2574946770759414</v>
+      </c>
+      <c r="N476" t="n">
+        <v>0.2574946770759414</v>
+      </c>
+      <c r="O476" t="n">
+        <v>-0.0600000000000005</v>
+      </c>
+      <c r="P476" t="n">
+        <v>0.1566997870830384</v>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>Ascendente</t>
+        </is>
+      </c>
+      <c r="S476" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C477" t="n">
+        <v>8</v>
+      </c>
+      <c r="D477" t="n">
+        <v>27962.474609375</v>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F477" t="n">
+        <v>8</v>
+      </c>
+      <c r="G477" t="n">
+        <v>0.836763662171753</v>
+      </c>
+      <c r="H477" t="n">
+        <v>8.460319375443577</v>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K477" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="L477" t="n">
+        <v>1</v>
+      </c>
+      <c r="M477" t="n">
+        <v>0.4103193754435761</v>
+      </c>
+      <c r="N477" t="n">
+        <v>0.4103193754435761</v>
+      </c>
+      <c r="O477" t="n">
+        <v>-0.1499999999999986</v>
+      </c>
+      <c r="P477" t="n">
+        <v>0.002824698367636103</v>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>Estable</t>
+        </is>
+      </c>
+      <c r="S477" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C478" t="n">
+        <v>8</v>
+      </c>
+      <c r="D478" t="n">
+        <v>27863.673828125</v>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F478" t="n">
+        <v>8</v>
+      </c>
+      <c r="G478" t="n">
+        <v>0.8317955997161107</v>
+      </c>
+      <c r="H478" t="n">
+        <v>8.388552164655785</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K478" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="L478" t="n">
+        <v>1</v>
+      </c>
+      <c r="M478" t="n">
+        <v>0.4685521646557849</v>
+      </c>
+      <c r="N478" t="n">
+        <v>0.4685521646557849</v>
+      </c>
+      <c r="O478" t="n">
+        <v>-0.1300000000000008</v>
+      </c>
+      <c r="P478" t="n">
+        <v>-0.07176721078779202</v>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S478" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C479" t="n">
+        <v>8</v>
+      </c>
+      <c r="D479" t="n">
+        <v>27666.275390625</v>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="F479" t="n">
+        <v>8</v>
+      </c>
+      <c r="G479" t="n">
+        <v>0.8190205819730305</v>
+      </c>
+      <c r="H479" t="n">
+        <v>8.19985095812633</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>TIMICURILLO</t>
+        </is>
+      </c>
+      <c r="K479" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="L479" t="n">
+        <v>1</v>
+      </c>
+      <c r="M479" t="n">
+        <v>0.4598509581263297</v>
+      </c>
+      <c r="N479" t="n">
+        <v>0.4598509581263297</v>
+      </c>
+      <c r="O479" t="n">
+        <v>-0.1799999999999997</v>
+      </c>
+      <c r="P479" t="n">
+        <v>-0.1887012065294549</v>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="S479" t="b">
         <v>1</v>
       </c>
     </row>
@@ -33873,7 +36079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34685,22 +36891,22 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.667</v>
+        <v>2.717</v>
       </c>
       <c r="G11" t="n">
-        <v>4.137</v>
+        <v>4.034</v>
       </c>
       <c r="H11" t="n">
-        <v>5.362</v>
+        <v>5.201</v>
       </c>
       <c r="I11" t="n">
-        <v>5.362</v>
+        <v>5.201</v>
       </c>
       <c r="J11" t="n">
-        <v>4.075</v>
+        <v>3.962</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.287</v>
+        <v>-1.239</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -34709,23 +36915,23 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>2.488</v>
+        <v>2.498</v>
       </c>
       <c r="P11" t="n">
-        <v>2.281</v>
+        <v>2.009</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.95</v>
+        <v>2.009</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.304</v>
+        <v>-0.544</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -35265,6 +37471,82 @@
         </is>
       </c>
       <c r="T18" t="inlineStr">
+        <is>
+          <t>Pronóstico prospectivo. La validación directa solo aplica cuando exista observado para esas fechas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5.802</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.403</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5.813</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-2.007</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Descendente</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>30</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.669</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>Pronóstico prospectivo. La validación directa solo aplica cuando exista observado para esas fechas.</t>
         </is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -486,7 +486,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>299916</v>
+        <v>299934</v>
       </c>
       <c r="E2" t="n">
         <v>151106</v>
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -683,19 +683,19 @@
         <v>9.765000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>7.75</v>
+        <v>7.751</v>
       </c>
       <c r="J2" t="n">
         <v>-1.52</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.015</v>
+        <v>-2.014</v>
       </c>
       <c r="L2" t="n">
         <v>0.394</v>
       </c>
       <c r="M2" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
       <c r="N2" t="n">
         <v>0.475</v>
@@ -704,7 +704,7 @@
         <v>0.867</v>
       </c>
       <c r="P2" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="Q2" t="n">
         <v>0.827</v>
@@ -724,7 +724,7 @@
         <v>0.823</v>
       </c>
       <c r="V2" t="n">
-        <v>0.648</v>
+        <v>0.649</v>
       </c>
       <c r="W2" t="n">
         <v>0.8110000000000001</v>
@@ -765,19 +765,19 @@
         <v>7.883</v>
       </c>
       <c r="I3" t="n">
-        <v>5.823</v>
+        <v>5.824</v>
       </c>
       <c r="J3" t="n">
         <v>-2.472</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.06</v>
+        <v>-2.058</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.789</v>
+        <v>-1.788</v>
       </c>
       <c r="M3" t="n">
-        <v>1.789</v>
+        <v>1.788</v>
       </c>
       <c r="N3" t="n">
         <v>1.823</v>
@@ -786,7 +786,7 @@
         <v>0.89</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.611</v>
+        <v>-4.609</v>
       </c>
       <c r="Q3" t="n">
         <v>0.758</v>
@@ -847,16 +847,16 @@
         <v>7.691</v>
       </c>
       <c r="I4" t="n">
-        <v>4.849</v>
+        <v>4.847</v>
       </c>
       <c r="J4" t="n">
         <v>-3.405</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.841</v>
+        <v>-2.844</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.074</v>
+        <v>-0.075</v>
       </c>
       <c r="M4" t="n">
         <v>0.338</v>
@@ -929,31 +929,31 @@
         <v>7.178</v>
       </c>
       <c r="I5" t="n">
-        <v>5.964</v>
+        <v>5.965</v>
       </c>
       <c r="J5" t="n">
         <v>-2.275</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.214</v>
+        <v>-1.212</v>
       </c>
       <c r="L5" t="n">
-        <v>0.315</v>
+        <v>0.316</v>
       </c>
       <c r="M5" t="n">
         <v>0.337</v>
       </c>
       <c r="N5" t="n">
-        <v>0.488</v>
+        <v>0.489</v>
       </c>
       <c r="O5" t="n">
         <v>0.9320000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.571</v>
+        <v>0.57</v>
       </c>
       <c r="R5" t="n">
         <v>55.172</v>
@@ -1020,13 +1020,13 @@
         <v>-2.239</v>
       </c>
       <c r="L6" t="n">
-        <v>0.108</v>
+        <v>0.109</v>
       </c>
       <c r="M6" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="N6" t="n">
-        <v>0.413</v>
+        <v>0.414</v>
       </c>
       <c r="O6" t="n">
         <v>0.872</v>
@@ -1035,7 +1035,7 @@
         <v>0.732</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="R6" t="n">
         <v>31.034</v>
@@ -1093,22 +1093,22 @@
         <v>9.374000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.201000000000001</v>
+        <v>8.202</v>
       </c>
       <c r="J7" t="n">
         <v>-2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.174</v>
+        <v>-1.172</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.669</v>
+        <v>-0.668</v>
       </c>
       <c r="M7" t="n">
         <v>0.778</v>
       </c>
       <c r="N7" t="n">
-        <v>0.843</v>
+        <v>0.842</v>
       </c>
       <c r="O7" t="n">
         <v>0.712</v>
@@ -1117,7 +1117,7 @@
         <v>-0.357</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.509</v>
+        <v>0.508</v>
       </c>
       <c r="R7" t="n">
         <v>20.69</v>
@@ -1175,28 +1175,28 @@
         <v>9.863</v>
       </c>
       <c r="I8" t="n">
-        <v>7.931</v>
+        <v>7.932</v>
       </c>
       <c r="J8" t="n">
         <v>-2.008</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.932</v>
+        <v>-1.931</v>
       </c>
       <c r="L8" t="n">
-        <v>5.809</v>
+        <v>5.81</v>
       </c>
       <c r="M8" t="n">
-        <v>5.809</v>
+        <v>5.81</v>
       </c>
       <c r="N8" t="n">
         <v>5.829</v>
       </c>
       <c r="O8" t="n">
-        <v>0.83</v>
+        <v>0.831</v>
       </c>
       <c r="P8" t="n">
-        <v>-45.909</v>
+        <v>-45.914</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.023</v>
@@ -1278,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.664</v>
+        <v>-0.665</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.042</v>
@@ -1339,34 +1339,34 @@
         <v>11.017</v>
       </c>
       <c r="I10" t="n">
-        <v>11.473</v>
+        <v>11.479</v>
       </c>
       <c r="J10" t="n">
         <v>-1.39</v>
       </c>
       <c r="K10" t="n">
-        <v>0.457</v>
+        <v>0.462</v>
       </c>
       <c r="L10" t="n">
-        <v>3.914</v>
+        <v>3.915</v>
       </c>
       <c r="M10" t="n">
-        <v>3.914</v>
+        <v>3.915</v>
       </c>
       <c r="N10" t="n">
-        <v>4.21</v>
+        <v>4.211</v>
       </c>
       <c r="O10" t="n">
         <v>-0.491</v>
       </c>
       <c r="P10" t="n">
-        <v>-105.365</v>
+        <v>-105.398</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.723</v>
+        <v>-1.724</v>
       </c>
       <c r="R10" t="n">
-        <v>44.828</v>
+        <v>41.379</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1418,10 +1418,10 @@
         <v>5.32</v>
       </c>
       <c r="H11" t="n">
-        <v>112.882</v>
+        <v>112.884</v>
       </c>
       <c r="I11" t="n">
-        <v>108.392</v>
+        <v>108.394</v>
       </c>
       <c r="J11" t="n">
         <v>-1.68</v>
@@ -1430,13 +1430,13 @@
         <v>-4.49</v>
       </c>
       <c r="L11" t="n">
-        <v>88.68000000000001</v>
+        <v>88.682</v>
       </c>
       <c r="M11" t="n">
-        <v>88.68000000000001</v>
+        <v>88.682</v>
       </c>
       <c r="N11" t="n">
-        <v>92.01000000000001</v>
+        <v>92.012</v>
       </c>
       <c r="O11" t="n">
         <v>-0.358</v>
@@ -1585,7 +1585,7 @@
         <v>5.956</v>
       </c>
       <c r="I13" t="n">
-        <v>5.124</v>
+        <v>5.125</v>
       </c>
       <c r="J13" t="n">
         <v>-0.6919999999999999</v>
@@ -1597,7 +1597,7 @@
         <v>0.26</v>
       </c>
       <c r="M13" t="n">
-        <v>0.423</v>
+        <v>0.424</v>
       </c>
       <c r="N13" t="n">
         <v>0.513</v>
@@ -1606,10 +1606,10 @@
         <v>0.439</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.216</v>
+        <v>0.215</v>
       </c>
       <c r="R13" t="n">
         <v>20.69</v>
@@ -1667,19 +1667,19 @@
         <v>7.097</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>5.202</v>
       </c>
       <c r="J14" t="n">
         <v>-2.422</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.897</v>
+        <v>-1.895</v>
       </c>
       <c r="L14" t="n">
-        <v>2.036</v>
+        <v>2.035</v>
       </c>
       <c r="M14" t="n">
-        <v>2.036</v>
+        <v>2.035</v>
       </c>
       <c r="N14" t="n">
         <v>2.52</v>
@@ -1688,10 +1688,10 @@
         <v>0.615</v>
       </c>
       <c r="P14" t="n">
-        <v>-10.092</v>
+        <v>-10.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.552</v>
+        <v>-0.553</v>
       </c>
       <c r="R14" t="n">
         <v>55.172</v>
@@ -1749,19 +1749,19 @@
         <v>8.144</v>
       </c>
       <c r="I15" t="n">
-        <v>6.349</v>
+        <v>6.35</v>
       </c>
       <c r="J15" t="n">
         <v>-1.525</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.795</v>
+        <v>-1.793</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.241</v>
+        <v>-0.24</v>
       </c>
       <c r="M15" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="N15" t="n">
         <v>0.484</v>
@@ -1770,10 +1770,10 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.206</v>
+        <v>-0.204</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="R15" t="n">
         <v>44.828</v>
@@ -1913,31 +1913,31 @@
         <v>8.029999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>6.677</v>
+        <v>6.678</v>
       </c>
       <c r="J17" t="n">
         <v>-2.425</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.353</v>
+        <v>-1.352</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.507</v>
+        <v>-1.506</v>
       </c>
       <c r="M17" t="n">
-        <v>1.507</v>
+        <v>1.506</v>
       </c>
       <c r="N17" t="n">
         <v>1.626</v>
       </c>
       <c r="O17" t="n">
-        <v>0.606</v>
+        <v>0.605</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.686</v>
+        <v>-3.684</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.286</v>
+        <v>0.285</v>
       </c>
       <c r="R17" t="n">
         <v>31.034</v>
@@ -1995,19 +1995,19 @@
         <v>7.154</v>
       </c>
       <c r="I18" t="n">
-        <v>6.29</v>
+        <v>6.291</v>
       </c>
       <c r="J18" t="n">
         <v>-1.55</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.864</v>
+        <v>-0.863</v>
       </c>
       <c r="L18" t="n">
-        <v>1.539</v>
+        <v>1.538</v>
       </c>
       <c r="M18" t="n">
-        <v>1.539</v>
+        <v>1.538</v>
       </c>
       <c r="N18" t="n">
         <v>1.726</v>
@@ -2016,10 +2016,10 @@
         <v>0.61</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.627</v>
+        <v>-6.626</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.231</v>
+        <v>0.23</v>
       </c>
       <c r="R18" t="n">
         <v>44.828</v>
@@ -2074,19 +2074,19 @@
         <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.483</v>
+        <v>3.486</v>
       </c>
       <c r="I19" t="n">
-        <v>3.102</v>
+        <v>3.104</v>
       </c>
       <c r="J19" t="n">
         <v>-1.34</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.38</v>
+        <v>-0.382</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.16</v>
+        <v>-0.159</v>
       </c>
       <c r="M19" t="n">
         <v>0.371</v>
@@ -2095,13 +2095,13 @@
         <v>0.488</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.427</v>
+        <v>-0.424</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.111</v>
+        <v>-0.11</v>
       </c>
       <c r="R19" t="n">
         <v>46.154</v>
@@ -3392,10 +3392,10 @@
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8531914893617021</v>
+        <v>0.8532955350815025</v>
       </c>
       <c r="H18" t="n">
-        <v>8.169234042553191</v>
+        <v>8.169893692416725</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>5.714234042553191</v>
+        <v>5.714893692416725</v>
       </c>
       <c r="N18" t="n">
-        <v>5.714234042553191</v>
+        <v>5.714893692416725</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1374999999999997</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7307939882807268</v>
+        <v>-0.7301343384171926</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.850354609929078</v>
+        <v>0.8504606661941885</v>
       </c>
       <c r="H19" t="n">
-        <v>8.156718085106382</v>
+        <v>8.156970233876683</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3485,16 +3485,16 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.744218085106382</v>
+        <v>5.744470233876683</v>
       </c>
       <c r="N19" t="n">
-        <v>5.744218085106382</v>
+        <v>5.744470233876683</v>
       </c>
       <c r="O19" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.01251595744680856</v>
+        <v>-0.01292345854004218</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8460992907801419</v>
+        <v>0.8462083628632175</v>
       </c>
       <c r="H20" t="n">
-        <v>8.130336879432626</v>
+        <v>8.131201275691</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3556,16 +3556,16 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>5.730336879432626</v>
+        <v>5.731201275690999</v>
       </c>
       <c r="N20" t="n">
-        <v>5.730336879432626</v>
+        <v>5.731201275690999</v>
       </c>
       <c r="O20" t="n">
         <v>-0.01250000000000018</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.02638120567375601</v>
+        <v>-0.02576895818568303</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8432624113475178</v>
+        <v>0.8433734939759037</v>
       </c>
       <c r="H21" t="n">
-        <v>8.11814184397163</v>
+        <v>8.118493975903615</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>5.94814184397163</v>
+        <v>5.948493975903615</v>
       </c>
       <c r="N21" t="n">
-        <v>5.94814184397163</v>
+        <v>5.948493975903615</v>
       </c>
       <c r="O21" t="n">
         <v>-0.23</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.0121950354609961</v>
+        <v>-0.01270729978738494</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8382978723404255</v>
+        <v>0.8384124734231042</v>
       </c>
       <c r="H22" t="n">
-        <v>8.094808510638298</v>
+        <v>8.095535081502481</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3698,16 +3698,16 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>6.114808510638298</v>
+        <v>6.115535081502481</v>
       </c>
       <c r="N22" t="n">
-        <v>6.114808510638298</v>
+        <v>6.115535081502481</v>
       </c>
       <c r="O22" t="n">
         <v>-0.1899999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.02333333333333165</v>
+        <v>-0.02295889440113363</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8334514528703048</v>
       </c>
       <c r="H23" t="n">
-        <v>8.056666666666667</v>
+        <v>8.058164422395464</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3769,16 +3769,16 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>6.006666666666667</v>
+        <v>6.008164422395464</v>
       </c>
       <c r="N23" t="n">
-        <v>6.006666666666667</v>
+        <v>6.008164422395464</v>
       </c>
       <c r="O23" t="n">
         <v>0.06999999999999984</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.03814184397163167</v>
+        <v>-0.03737065910701709</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8269503546099291</v>
+        <v>0.8270729978738484</v>
       </c>
       <c r="H24" t="n">
         <v>8.029999999999999</v>
@@ -3849,7 +3849,7 @@
         <v>0.1700000000000004</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.02666666666666728</v>
+        <v>-0.02816442239546468</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8219858156028369</v>
+        <v>0.8221119773210489</v>
       </c>
       <c r="H25" t="n">
-        <v>8.012847517730496</v>
+        <v>8.013047484053862</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3911,16 +3911,16 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>5.662847517730496</v>
+        <v>5.663047484053862</v>
       </c>
       <c r="N25" t="n">
-        <v>5.662847517730496</v>
+        <v>5.663047484053862</v>
       </c>
       <c r="O25" t="n">
         <v>0.1299999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01715248226950372</v>
+        <v>-0.01695251594613723</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3960,10 +3960,10 @@
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8191489361702128</v>
+        <v>0.8192771084337349</v>
       </c>
       <c r="H26" t="n">
-        <v>8.000053191489361</v>
+        <v>8.000662650602409</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3982,16 +3982,16 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>5.700053191489361</v>
+        <v>5.70066265060241</v>
       </c>
       <c r="N26" t="n">
-        <v>5.700053191489361</v>
+        <v>5.70066265060241</v>
       </c>
       <c r="O26" t="n">
         <v>-0.05000000000000027</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.01279432624113497</v>
+        <v>-0.01238483345145269</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8156028368794326</v>
+        <v>0.8157335223245925</v>
       </c>
       <c r="H27" t="n">
-        <v>7.971613475177304</v>
+        <v>7.973063430191353</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4053,16 +4053,16 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>5.741613475177305</v>
+        <v>5.743063430191354</v>
       </c>
       <c r="N27" t="n">
-        <v>5.741613475177305</v>
+        <v>5.743063430191354</v>
       </c>
       <c r="O27" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.02843971631205644</v>
+        <v>-0.027599220411056</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8113475177304964</v>
+        <v>0.8114812189936216</v>
       </c>
       <c r="H28" t="n">
-        <v>7.946971631205674</v>
+        <v>7.947395464209781</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>5.886971631205673</v>
+        <v>5.887395464209781</v>
       </c>
       <c r="N28" t="n">
-        <v>5.886971631205673</v>
+        <v>5.887395464209781</v>
       </c>
       <c r="O28" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.02464184397163027</v>
+        <v>-0.02566796598157239</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8120567375886525</v>
+        <v>0.81218993621545</v>
       </c>
       <c r="H29" t="n">
-        <v>7.949219858156029</v>
+        <v>7.949642097802977</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4195,16 +4195,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>5.999219858156029</v>
+        <v>5.999642097802977</v>
       </c>
       <c r="N29" t="n">
-        <v>5.999219858156029</v>
+        <v>5.999642097802977</v>
       </c>
       <c r="O29" t="n">
         <v>-0.1100000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>0.002248226950355203</v>
+        <v>0.002246633593196101</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8127659574468085</v>
+        <v>0.8128986534372785</v>
       </c>
       <c r="H30" t="n">
-        <v>7.953670212765957</v>
+        <v>7.954721828490432</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4266,16 +4266,16 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.253670212765956</v>
+        <v>5.254721828490432</v>
       </c>
       <c r="N30" t="n">
-        <v>5.253670212765956</v>
+        <v>5.254721828490432</v>
       </c>
       <c r="O30" t="n">
         <v>0.7500000000000002</v>
       </c>
       <c r="P30" t="n">
-        <v>0.004450354609927487</v>
+        <v>0.00507973068745482</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8092198581560284</v>
+        <v>0.8093550673281361</v>
       </c>
       <c r="H31" t="n">
-        <v>7.93068085106383</v>
+        <v>7.931966690290575</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4337,16 +4337,16 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.13068085106383</v>
+        <v>5.131966690290575</v>
       </c>
       <c r="N31" t="n">
-        <v>5.13068085106383</v>
+        <v>5.131966690290575</v>
       </c>
       <c r="O31" t="n">
         <v>0.09999999999999964</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.02298936170212684</v>
+        <v>-0.02275513819985697</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.64822695035461</v>
+        <v>0.6484762579730687</v>
       </c>
       <c r="H48" t="n">
-        <v>6.158884308510639</v>
+        <v>6.158979668674699</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5538,16 +5538,16 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1286156914893608</v>
+        <v>-0.1285203313253005</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1286156914893608</v>
+        <v>0.1285203313253005</v>
       </c>
       <c r="O48" t="n">
         <v>-0.09250000000000114</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.6250049696953877</v>
+        <v>-0.6249096095313273</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6418439716312057</v>
+        <v>0.6420978029766123</v>
       </c>
       <c r="H49" t="n">
-        <v>6.14404255319149</v>
+        <v>6.144819277108434</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5609,16 +5609,16 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0259574468085102</v>
+        <v>-0.02518072289156592</v>
       </c>
       <c r="N49" t="n">
-        <v>0.0259574468085102</v>
+        <v>0.02518072289156592</v>
       </c>
       <c r="O49" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.01484175531914911</v>
+        <v>-0.01416039156626514</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5658,10 +5658,10 @@
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>0.6340425531914894</v>
+        <v>0.6343019135364989</v>
       </c>
       <c r="H50" t="n">
-        <v>6.122136170212766</v>
+        <v>6.12277108433735</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5680,16 +5680,16 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.03213617021276605</v>
+        <v>0.03277108433734988</v>
       </c>
       <c r="N50" t="n">
-        <v>0.03213617021276605</v>
+        <v>0.03277108433734988</v>
       </c>
       <c r="O50" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.02190638297872383</v>
+        <v>-0.02204819277108427</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5729,10 +5729,10 @@
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6326241134751773</v>
+        <v>0.632884479092842</v>
       </c>
       <c r="H51" t="n">
-        <v>6.11958244680851</v>
+        <v>6.119781626506025</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5751,16 +5751,16 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2595824468085102</v>
+        <v>0.2597816265060242</v>
       </c>
       <c r="N51" t="n">
-        <v>0.2595824468085102</v>
+        <v>0.2597816265060242</v>
       </c>
       <c r="O51" t="n">
         <v>-0.2299999999999995</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.002553723404255415</v>
+        <v>-0.002989457831325204</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>0.6439716312056738</v>
+        <v>0.6442239546420978</v>
       </c>
       <c r="H52" t="n">
-        <v>6.151659574468085</v>
+        <v>6.153975903614458</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5822,16 +5822,16 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4916595744680849</v>
+        <v>0.4939759036144578</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4916595744680849</v>
+        <v>0.4939759036144578</v>
       </c>
       <c r="O52" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P52" t="n">
-        <v>0.0320771276595746</v>
+        <v>0.03419427710843337</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6517730496453901</v>
+        <v>0.6520198440822113</v>
       </c>
       <c r="H53" t="n">
-        <v>6.163851063829787</v>
+        <v>6.165180722891566</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5893,16 +5893,16 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5338510638297871</v>
+        <v>0.5351807228915666</v>
       </c>
       <c r="N53" t="n">
-        <v>0.5338510638297871</v>
+        <v>0.5351807228915666</v>
       </c>
       <c r="O53" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P53" t="n">
-        <v>0.01219148936170189</v>
+        <v>0.01120481927710859</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6617021276595745</v>
+        <v>0.6619418851878101</v>
       </c>
       <c r="H54" t="n">
-        <v>6.203078014184397</v>
+        <v>6.204056224899599</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5964,16 +5964,16 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6130780141843974</v>
+        <v>0.6140562248995991</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6130780141843974</v>
+        <v>0.6140562248995991</v>
       </c>
       <c r="O54" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P54" t="n">
-        <v>0.03922695035461032</v>
+        <v>0.03887550200803247</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6680851063829787</v>
+        <v>0.6683203401842664</v>
       </c>
       <c r="H55" t="n">
-        <v>6.217170212765957</v>
+        <v>6.217530120481928</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6035,16 +6035,16 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.767170212765957</v>
+        <v>0.7675301204819274</v>
       </c>
       <c r="N55" t="n">
-        <v>0.767170212765957</v>
+        <v>0.7675301204819274</v>
       </c>
       <c r="O55" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01409219858155986</v>
+        <v>0.01347389558232859</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6645390070921986</v>
+        <v>0.664776754075124</v>
       </c>
       <c r="H56" t="n">
-        <v>6.211744680851064</v>
+        <v>6.21210843373494</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6106,16 +6106,16 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8117446808510635</v>
+        <v>0.8121084337349398</v>
       </c>
       <c r="N56" t="n">
-        <v>0.8117446808510635</v>
+        <v>0.8121084337349398</v>
       </c>
       <c r="O56" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.005425531914893256</v>
+        <v>-0.005421686746987397</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
         <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6531914893617021</v>
+        <v>0.6534372785258682</v>
       </c>
       <c r="H57" t="n">
-        <v>6.168765957446809</v>
+        <v>6.169518072289157</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.7987659574468085</v>
+        <v>0.7995180722891568</v>
       </c>
       <c r="N57" t="n">
-        <v>0.7987659574468085</v>
+        <v>0.7995180722891568</v>
       </c>
       <c r="O57" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.04297872340425535</v>
+        <v>-0.04259036144578321</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6226,10 +6226,10 @@
         <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6375886524822695</v>
+        <v>0.6378454996456414</v>
       </c>
       <c r="H58" t="n">
-        <v>6.132042553191489</v>
+        <v>6.133614457831325</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6248,16 +6248,16 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8020425531914892</v>
+        <v>0.8036144578313253</v>
       </c>
       <c r="N58" t="n">
-        <v>0.8020425531914892</v>
+        <v>0.8036144578313253</v>
       </c>
       <c r="O58" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.03672340425531928</v>
+        <v>-0.03590361445783152</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6297,10 +6297,10 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6191489361702127</v>
+        <v>0.6194188518781006</v>
       </c>
       <c r="H59" t="n">
-        <v>6.072794326241135</v>
+        <v>6.073895582329317</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6319,16 +6319,16 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9227943262411342</v>
+        <v>0.9238955823293171</v>
       </c>
       <c r="N59" t="n">
-        <v>0.9227943262411342</v>
+        <v>0.9238955823293171</v>
       </c>
       <c r="O59" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.0592482269503547</v>
+        <v>-0.05971887550200794</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6049645390070922</v>
+        <v>0.6052445074415308</v>
       </c>
       <c r="H60" t="n">
-        <v>6.023574468085107</v>
+        <v>6.026144578313253</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6390,16 +6390,16 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1.053574468085107</v>
+        <v>1.056144578313253</v>
       </c>
       <c r="N60" t="n">
-        <v>1.053574468085107</v>
+        <v>1.056144578313253</v>
       </c>
       <c r="O60" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.04921985815602792</v>
+        <v>-0.04775100401606469</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6439,10 +6439,10 @@
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5900709219858156</v>
+        <v>0.5903614457831325</v>
       </c>
       <c r="H61" t="n">
-        <v>5.964156028368794</v>
+        <v>5.965341365461847</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6461,16 +6461,16 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1.134156028368794</v>
+        <v>1.135341365461847</v>
       </c>
       <c r="N61" t="n">
-        <v>1.134156028368794</v>
+        <v>1.135341365461847</v>
       </c>
       <c r="O61" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.05941843971631222</v>
+        <v>-0.06080321285140577</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -7640,10 +7640,10 @@
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8971631205673759</v>
+        <v>0.8972360028348689</v>
       </c>
       <c r="H78" t="n">
-        <v>5.875035460992908</v>
+        <v>5.875882352941177</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7662,16 +7662,16 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1.187535460992908</v>
+        <v>1.188382352941177</v>
       </c>
       <c r="N78" t="n">
-        <v>1.187535460992908</v>
+        <v>1.188382352941177</v>
       </c>
       <c r="O78" t="n">
         <v>0.2725</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.06679004706595659</v>
+        <v>-0.06594315511768745</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8680851063829788</v>
+        <v>0.8681785967399008</v>
       </c>
       <c r="H79" t="n">
-        <v>5.688574468085108</v>
+        <v>5.689117647058825</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7733,16 +7733,16 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>1.276074468085108</v>
+        <v>1.276617647058825</v>
       </c>
       <c r="N79" t="n">
-        <v>1.276074468085108</v>
+        <v>1.276617647058825</v>
       </c>
       <c r="O79" t="n">
         <v>-0.2750000000000004</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.1864609929078007</v>
+        <v>-0.1867647058823527</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>0.825531914893617</v>
+        <v>0.8256555634301913</v>
       </c>
       <c r="H80" t="n">
-        <v>5.411340425531915</v>
+        <v>5.412058823529411</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7804,16 +7804,16 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7613404255319143</v>
+        <v>0.7620588235294106</v>
       </c>
       <c r="N80" t="n">
-        <v>0.7613404255319143</v>
+        <v>0.7620588235294106</v>
       </c>
       <c r="O80" t="n">
         <v>0.2375000000000007</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.2772340425531929</v>
+        <v>-0.2770588235294138</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7787234042553192</v>
+        <v>0.778880226789511</v>
       </c>
       <c r="H81" t="n">
-        <v>5.14958865248227</v>
+        <v>5.150294117647059</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7875,16 +7875,16 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>0.4495886524822694</v>
+        <v>0.4502941176470587</v>
       </c>
       <c r="N81" t="n">
-        <v>0.4495886524822694</v>
+        <v>0.4502941176470587</v>
       </c>
       <c r="O81" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.261751773049645</v>
+        <v>-0.261764705882352</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7326241134751773</v>
+        <v>0.7328136073706591</v>
       </c>
       <c r="H82" t="n">
-        <v>4.991546099290781</v>
+        <v>4.99264705882353</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7946,16 +7946,16 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5865460992907812</v>
+        <v>0.5876470588235305</v>
       </c>
       <c r="N82" t="n">
-        <v>0.5865460992907812</v>
+        <v>0.5876470588235305</v>
       </c>
       <c r="O82" t="n">
         <v>-0.2950000000000008</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.1580425531914891</v>
+        <v>-0.157647058823529</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -7995,10 +7995,10 @@
         <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7063829787234043</v>
+        <v>0.7065910701630049</v>
       </c>
       <c r="H83" t="n">
-        <v>4.866056737588653</v>
+        <v>4.86686274509804</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8017,16 +8017,16 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>0.7685567375886535</v>
+        <v>0.7693627450980403</v>
       </c>
       <c r="N83" t="n">
-        <v>0.7685567375886535</v>
+        <v>0.7693627450980403</v>
       </c>
       <c r="O83" t="n">
         <v>-0.3075000000000001</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.1254893617021278</v>
+        <v>-0.1257843137254904</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -8066,10 +8066,10 @@
         <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>0.674468085106383</v>
+        <v>0.6746987951807228</v>
       </c>
       <c r="H84" t="n">
-        <v>4.78390273556231</v>
+        <v>4.784285714285715</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8088,16 +8088,16 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>0.93390273556231</v>
+        <v>0.9342857142857146</v>
       </c>
       <c r="N84" t="n">
-        <v>0.93390273556231</v>
+        <v>0.9342857142857146</v>
       </c>
       <c r="O84" t="n">
         <v>-0.2474999999999992</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.08215400202634271</v>
+        <v>-0.08257703081232481</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6411347517730497</v>
+        <v>0.6406803685329554</v>
       </c>
       <c r="H85" t="n">
-        <v>4.688332151300236</v>
+        <v>4.687892156862745</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8159,16 +8159,16 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9083321513002365</v>
+        <v>0.9078921568627449</v>
       </c>
       <c r="N85" t="n">
-        <v>0.9083321513002365</v>
+        <v>0.9078921568627449</v>
       </c>
       <c r="O85" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.09557058426207377</v>
+        <v>-0.09639355742296996</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6056737588652482</v>
+        <v>0.6052445074415308</v>
       </c>
       <c r="H86" t="n">
-        <v>4.554482269503546</v>
+        <v>4.553235294117647</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8230,16 +8230,16 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.2455177304964549</v>
+        <v>-0.2467647058823541</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2455177304964549</v>
+        <v>0.2467647058823541</v>
       </c>
       <c r="O86" t="n">
         <v>1.020000000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.1338498817966904</v>
+        <v>-0.1346568627450981</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -8279,10 +8279,10 @@
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>0.5985815602836879</v>
+        <v>0.5981573352232459</v>
       </c>
       <c r="H87" t="n">
-        <v>4.523534574468084</v>
+        <v>4.522610294117646</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8301,16 +8301,16 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.1764654255319158</v>
+        <v>-0.1773897058823541</v>
       </c>
       <c r="N87" t="n">
-        <v>0.1764654255319158</v>
+        <v>0.1773897058823541</v>
       </c>
       <c r="O87" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.03094769503546146</v>
+        <v>-0.03062500000000057</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -8350,10 +8350,10 @@
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6156028368794326</v>
+        <v>0.6151665485471297</v>
       </c>
       <c r="H88" t="n">
-        <v>4.577768321513003</v>
+        <v>4.576078431372549</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8372,16 +8372,16 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.6222316784869975</v>
+        <v>-0.6239215686274511</v>
       </c>
       <c r="N88" t="n">
-        <v>0.6222316784869975</v>
+        <v>0.6239215686274511</v>
       </c>
       <c r="O88" t="n">
         <v>0.5</v>
       </c>
       <c r="P88" t="n">
-        <v>0.05423374704491835</v>
+        <v>0.05346813725490307</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6581560283687943</v>
+        <v>0.6576895818568391</v>
       </c>
       <c r="H89" t="n">
-        <v>4.721943262411347</v>
+        <v>4.720588235294119</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8443,16 +8443,16 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.7780567375886527</v>
+        <v>-0.7794117647058814</v>
       </c>
       <c r="N89" t="n">
-        <v>0.7780567375886527</v>
+        <v>0.7794117647058814</v>
       </c>
       <c r="O89" t="n">
         <v>0.2999999999999998</v>
       </c>
       <c r="P89" t="n">
-        <v>0.1441749408983446</v>
+        <v>0.1445098039215695</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8492,10 +8492,10 @@
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6808510638297872</v>
+        <v>0.6810772501771793</v>
       </c>
       <c r="H90" t="n">
-        <v>4.793936170212766</v>
+        <v>4.794264705882353</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8514,16 +8514,16 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-1.086063829787234</v>
+        <v>-1.085735294117647</v>
       </c>
       <c r="N90" t="n">
-        <v>1.086063829787234</v>
+        <v>1.085735294117647</v>
       </c>
       <c r="O90" t="n">
         <v>0.3799999999999999</v>
       </c>
       <c r="P90" t="n">
-        <v>0.07199290780141876</v>
+        <v>0.07367647058823401</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8563,10 +8563,10 @@
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6836879432624113</v>
+        <v>0.6839121190644932</v>
       </c>
       <c r="H91" t="n">
-        <v>4.798056737588652</v>
+        <v>4.798382352941176</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -8585,16 +8585,16 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.2219432624113473</v>
+        <v>-0.2216176470588236</v>
       </c>
       <c r="N91" t="n">
-        <v>0.2219432624113473</v>
+        <v>0.2216176470588236</v>
       </c>
       <c r="O91" t="n">
         <v>-0.8600000000000003</v>
       </c>
       <c r="P91" t="n">
-        <v>0.004120567375886175</v>
+        <v>0.004117647058823337</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -9764,10 +9764,10 @@
         <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8907801418439716</v>
+        <v>0.8908575478384124</v>
       </c>
       <c r="H108" t="n">
-        <v>12.3818085106383</v>
+        <v>12.38252657689582</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -9786,16 +9786,16 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>5.311808510638298</v>
+        <v>5.312526576895819</v>
       </c>
       <c r="N108" t="n">
-        <v>5.311808510638298</v>
+        <v>5.312526576895819</v>
       </c>
       <c r="O108" t="n">
         <v>-0.1250000000000009</v>
       </c>
       <c r="P108" t="n">
-        <v>4.412228973147059</v>
+        <v>4.41294703940458</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -9835,10 +9835,10 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>0.8865248226950354</v>
+        <v>0.8866052445074415</v>
       </c>
       <c r="H109" t="n">
-        <v>12.33127659574468</v>
+        <v>12.33316087880935</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -9857,16 +9857,16 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>5.461276595744679</v>
+        <v>5.463160878809354</v>
       </c>
       <c r="N109" t="n">
-        <v>5.461276595744679</v>
+        <v>5.463160878809354</v>
       </c>
       <c r="O109" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.05053191489361808</v>
+        <v>-0.04936569808646496</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -9875,11 +9875,11 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -9906,10 +9906,10 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8843971631205674</v>
+        <v>0.884479092841956</v>
       </c>
       <c r="H110" t="n">
-        <v>12.28879787234043</v>
+        <v>12.2893214032601</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -9928,16 +9928,16 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>5.548797872340426</v>
+        <v>5.549321403260098</v>
       </c>
       <c r="N110" t="n">
-        <v>5.548797872340426</v>
+        <v>5.549321403260098</v>
       </c>
       <c r="O110" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.04247872340425296</v>
+        <v>-0.04383947554925527</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -9977,10 +9977,10 @@
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>0.8822695035460993</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="H111" t="n">
-        <v>12.27175531914894</v>
+        <v>12.27308823529412</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -9999,16 +9999,16 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>5.671755319148938</v>
+        <v>5.673088235294118</v>
       </c>
       <c r="N111" t="n">
-        <v>5.671755319148938</v>
+        <v>5.673088235294118</v>
       </c>
       <c r="O111" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P111" t="n">
-        <v>-0.01704255319148906</v>
+        <v>-0.0162331679659804</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -10048,10 +10048,10 @@
         <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>0.875886524822695</v>
+        <v>0.8759744861800142</v>
       </c>
       <c r="H112" t="n">
-        <v>12.22127659574468</v>
+        <v>12.22165131112686</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10070,16 +10070,16 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>5.361276595744681</v>
+        <v>5.36165131112686</v>
       </c>
       <c r="N112" t="n">
-        <v>5.361276595744681</v>
+        <v>5.36165131112686</v>
       </c>
       <c r="O112" t="n">
         <v>0.2600000000000007</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.05047872340425563</v>
+        <v>-0.0514369241672572</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>0.8673758865248227</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="H113" t="n">
-        <v>12.19001063829787</v>
+        <v>12.19021084337349</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -10141,16 +10141,16 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>5.210010638297872</v>
+        <v>5.210210843373494</v>
       </c>
       <c r="N113" t="n">
-        <v>5.210010638297872</v>
+        <v>5.210210843373494</v>
       </c>
       <c r="O113" t="n">
         <v>0.1200000000000001</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.03126595744680927</v>
+        <v>-0.03144046775336662</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -10190,10 +10190,10 @@
         <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8567375886524823</v>
+        <v>0.856839121190645</v>
       </c>
       <c r="H114" t="n">
-        <v>12.11492553191489</v>
+        <v>12.11540396881644</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -10212,16 +10212,16 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>5.264925531914894</v>
+        <v>5.265403968816443</v>
       </c>
       <c r="N114" t="n">
-        <v>5.264925531914894</v>
+        <v>5.265403968816443</v>
       </c>
       <c r="O114" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P114" t="n">
-        <v>-0.07508510638297849</v>
+        <v>-0.07480687455705137</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
         <v>8</v>
       </c>
       <c r="G115" t="n">
-        <v>0.8460992907801419</v>
+        <v>0.8462083628632175</v>
       </c>
       <c r="H115" t="n">
-        <v>12.07284042553192</v>
+        <v>12.07446669029057</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -10283,16 +10283,16 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>5.332840425531916</v>
+        <v>5.334466690290574</v>
       </c>
       <c r="N115" t="n">
-        <v>5.332840425531916</v>
+        <v>5.334466690290574</v>
       </c>
       <c r="O115" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.04208510638297724</v>
+        <v>-0.04093727852586859</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -10332,10 +10332,10 @@
         <v>8</v>
       </c>
       <c r="G116" t="n">
-        <v>0.8241134751773049</v>
+        <v>0.8242381289865344</v>
       </c>
       <c r="H116" t="n">
-        <v>11.86072340425532</v>
+        <v>11.86125442948263</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -10354,16 +10354,16 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>5.255723404255319</v>
+        <v>5.256254429482635</v>
       </c>
       <c r="N116" t="n">
-        <v>5.255723404255319</v>
+        <v>5.256254429482635</v>
       </c>
       <c r="O116" t="n">
         <v>-0.1349999999999998</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.2121170212765975</v>
+        <v>-0.2132122608079392</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10403,10 +10403,10 @@
         <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>0.8092198581560284</v>
+        <v>0.8093550673281361</v>
       </c>
       <c r="H117" t="n">
-        <v>11.80591489361702</v>
+        <v>11.80677888022679</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -10425,16 +10425,16 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>5.425914893617022</v>
+        <v>5.426778880226791</v>
       </c>
       <c r="N117" t="n">
-        <v>5.425914893617022</v>
+        <v>5.426778880226791</v>
       </c>
       <c r="O117" t="n">
         <v>-0.2250000000000005</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.05480851063829739</v>
+        <v>-0.05447554925584441</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10474,10 +10474,10 @@
         <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7950354609929078</v>
+        <v>0.7951807228915663</v>
       </c>
       <c r="H118" t="n">
-        <v>11.72342553191489</v>
+        <v>11.72373493975904</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -10496,16 +10496,16 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>5.483425531914893</v>
+        <v>5.483734939759035</v>
       </c>
       <c r="N118" t="n">
-        <v>5.483425531914893</v>
+        <v>5.483734939759035</v>
       </c>
       <c r="O118" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.08248936170212851</v>
+        <v>-0.08304394046775521</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10545,10 +10545,10 @@
         <v>8</v>
       </c>
       <c r="G119" t="n">
-        <v>0.7815602836879433</v>
+        <v>0.781715095676825</v>
       </c>
       <c r="H119" t="n">
-        <v>11.65722340425532</v>
+        <v>11.65765946137491</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -10567,16 +10567,16 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>5.537223404255319</v>
+        <v>5.537659461374912</v>
       </c>
       <c r="N119" t="n">
-        <v>5.537223404255319</v>
+        <v>5.537659461374912</v>
       </c>
       <c r="O119" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.06620212765957412</v>
+        <v>-0.06607547838412309</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -10616,10 +10616,10 @@
         <v>8</v>
       </c>
       <c r="G120" t="n">
-        <v>0.7673758865248227</v>
+        <v>0.7675407512402551</v>
       </c>
       <c r="H120" t="n">
-        <v>11.55426595744681</v>
+        <v>11.55479270021261</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10638,16 +10638,16 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>5.484265957446809</v>
+        <v>5.484792700212614</v>
       </c>
       <c r="N120" t="n">
-        <v>5.484265957446809</v>
+        <v>5.484792700212614</v>
       </c>
       <c r="O120" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.1029574468085102</v>
+        <v>-0.1028667611622982</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         <v>8</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7588652482269503</v>
+        <v>0.7590361445783133</v>
       </c>
       <c r="H121" t="n">
-        <v>11.47324468085106</v>
+        <v>11.47870481927711</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -10709,16 +10709,16 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.443244680851063</v>
+        <v>5.448704819277109</v>
       </c>
       <c r="N121" t="n">
-        <v>5.443244680851063</v>
+        <v>5.448704819277109</v>
       </c>
       <c r="O121" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.08102127659574521</v>
+        <v>-0.07608788093550523</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>8</v>
       </c>
       <c r="G122" t="n">
-        <v>0.9595744680851064</v>
+        <v>0.9596031183557761</v>
       </c>
       <c r="H122" t="n">
-        <v>112.8818510638298</v>
+        <v>112.8835577604536</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>105.8818510638298</v>
+        <v>105.8835577604536</v>
       </c>
       <c r="N122" t="n">
-        <v>105.8818510638298</v>
+        <v>105.8835577604536</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         <v>8</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9354609929078014</v>
+        <v>0.9355067328136074</v>
       </c>
       <c r="H123" t="n">
-        <v>112.4607730496454</v>
+        <v>112.4611622962438</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -10845,16 +10845,16 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>105.6507730496454</v>
+        <v>105.6511622962438</v>
       </c>
       <c r="N123" t="n">
-        <v>105.6507730496454</v>
+        <v>105.6511622962438</v>
       </c>
       <c r="O123" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.4210780141844026</v>
+        <v>-0.4223954642097851</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -10894,10 +10894,10 @@
         <v>8</v>
       </c>
       <c r="G124" t="n">
-        <v>0.9177304964539007</v>
+        <v>0.9177888022678952</v>
       </c>
       <c r="H124" t="n">
-        <v>112.1398865248227</v>
+        <v>112.1403827072998</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -10916,16 +10916,16 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>105.5298865248227</v>
+        <v>105.5303827072998</v>
       </c>
       <c r="N124" t="n">
-        <v>105.5298865248227</v>
+        <v>105.5303827072998</v>
       </c>
       <c r="O124" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P124" t="n">
-        <v>-0.3208865248226829</v>
+        <v>-0.3207795889440064</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -10965,10 +10965,10 @@
         <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>0.900709219858156</v>
+        <v>0.9007795889440113</v>
       </c>
       <c r="H125" t="n">
-        <v>111.9975177304965</v>
+        <v>111.9978171509568</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -10987,16 +10987,16 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>105.5775177304965</v>
+        <v>105.5778171509568</v>
       </c>
       <c r="N125" t="n">
-        <v>105.5775177304965</v>
+        <v>105.5778171509568</v>
       </c>
       <c r="O125" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P125" t="n">
-        <v>-0.1423687943262451</v>
+        <v>-0.1425655563430297</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -11036,10 +11036,10 @@
         <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>0.8574468085106383</v>
+        <v>0.8575478384124734</v>
       </c>
       <c r="H126" t="n">
-        <v>111.6703085106383</v>
+        <v>111.6715981573352</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -11058,16 +11058,16 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>105.4403085106383</v>
+        <v>105.4415981573352</v>
       </c>
       <c r="N126" t="n">
-        <v>105.4403085106383</v>
+        <v>105.4415981573352</v>
       </c>
       <c r="O126" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.3272092198581618</v>
+        <v>-0.3262189936215378</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -11107,10 +11107,10 @@
         <v>8</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8113475177304964</v>
+        <v>0.8114812189936216</v>
       </c>
       <c r="H127" t="n">
-        <v>111.4315224586288</v>
+        <v>111.4319017245452</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -11129,16 +11129,16 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>105.3715224586288</v>
+        <v>105.3719017245452</v>
       </c>
       <c r="N127" t="n">
-        <v>105.3715224586288</v>
+        <v>105.3719017245452</v>
       </c>
       <c r="O127" t="n">
         <v>-0.1700000000000008</v>
       </c>
       <c r="P127" t="n">
-        <v>-0.2387860520094449</v>
+        <v>-0.2396964327899838</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -11178,10 +11178,10 @@
         <v>8</v>
       </c>
       <c r="G128" t="n">
-        <v>0.7524822695035461</v>
+        <v>0.7526576895818569</v>
       </c>
       <c r="H128" t="n">
-        <v>111.1572482269504</v>
+        <v>111.1602338766832</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -11200,16 +11200,16 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>105.2272482269504</v>
+        <v>105.2302338766832</v>
       </c>
       <c r="N128" t="n">
-        <v>105.2272482269504</v>
+        <v>105.2302338766832</v>
       </c>
       <c r="O128" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.2742742316784899</v>
+        <v>-0.2716678478620338</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -11249,10 +11249,10 @@
         <v>8</v>
       </c>
       <c r="G129" t="n">
-        <v>0.674468085106383</v>
+        <v>0.6746987951807228</v>
       </c>
       <c r="H129" t="n">
-        <v>110.7497234042553</v>
+        <v>110.7525301204819</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -11271,16 +11271,16 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>52.38472340425532</v>
+        <v>52.38753012048192</v>
       </c>
       <c r="N129" t="n">
-        <v>52.38472340425532</v>
+        <v>52.38753012048192</v>
       </c>
       <c r="O129" t="n">
         <v>52.435</v>
       </c>
       <c r="P129" t="n">
-        <v>-0.4075248226950379</v>
+        <v>-0.4077037562012862</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -11320,10 +11320,10 @@
         <v>8</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5964539007092199</v>
+        <v>0.5967399007795889</v>
       </c>
       <c r="H130" t="n">
-        <v>110.3616453900709</v>
+        <v>110.3665131112686</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -11342,16 +11342,16 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>52.06664539007092</v>
+        <v>52.0715131112686</v>
       </c>
       <c r="N130" t="n">
-        <v>52.06664539007092</v>
+        <v>52.0715131112686</v>
       </c>
       <c r="O130" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.3880780141844014</v>
+        <v>-0.3860170092133188</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         <v>8</v>
       </c>
       <c r="G131" t="n">
-        <v>0.5156028368794326</v>
+        <v>0.515946137491141</v>
       </c>
       <c r="H131" t="n">
-        <v>109.965926713948</v>
+        <v>109.9669005433499</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -11413,16 +11413,16 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>51.78092671394799</v>
+        <v>51.78190054334986</v>
       </c>
       <c r="N131" t="n">
-        <v>51.78092671394799</v>
+        <v>51.78190054334986</v>
       </c>
       <c r="O131" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.3957186761229252</v>
+        <v>-0.3996125679187372</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -11462,10 +11462,10 @@
         <v>8</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4304964539007092</v>
+        <v>0.4309000708717222</v>
       </c>
       <c r="H132" t="n">
-        <v>109.4423498817967</v>
+        <v>109.4446397354122</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -11484,16 +11484,16 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>51.39734988179669</v>
+        <v>51.39963973541224</v>
       </c>
       <c r="N132" t="n">
-        <v>51.39734988179669</v>
+        <v>51.39963973541224</v>
       </c>
       <c r="O132" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.5235768321513063</v>
+        <v>-0.5222608079376272</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -11533,10 +11533,10 @@
         <v>8</v>
       </c>
       <c r="G133" t="n">
-        <v>0.349645390070922</v>
+        <v>0.3501063075832743</v>
       </c>
       <c r="H133" t="n">
-        <v>108.9027411347518</v>
+        <v>108.9047023387668</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -11555,16 +11555,16 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>103.4627411347518</v>
+        <v>103.4647023387668</v>
       </c>
       <c r="N133" t="n">
-        <v>103.4627411347518</v>
+        <v>103.4647023387668</v>
       </c>
       <c r="O133" t="n">
         <v>-52.605</v>
       </c>
       <c r="P133" t="n">
-        <v>-0.5396087470449089</v>
+        <v>-0.5399373966453993</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -11604,10 +11604,10 @@
         <v>8</v>
       </c>
       <c r="G134" t="n">
-        <v>0.2659574468085106</v>
+        <v>0.2664776754075124</v>
       </c>
       <c r="H134" t="n">
-        <v>108.3916489361702</v>
+        <v>108.393862508859</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -11626,16 +11626,16 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>103.0716489361702</v>
+        <v>103.073862508859</v>
       </c>
       <c r="N134" t="n">
-        <v>103.0716489361702</v>
+        <v>103.073862508859</v>
       </c>
       <c r="O134" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P134" t="n">
-        <v>-0.5110921985815651</v>
+        <v>-0.5108398299078658</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
         <v>8</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9312056737588652</v>
+        <v>0.9312544294826365</v>
       </c>
       <c r="H154" t="n">
-        <v>9.031624113475177</v>
+        <v>9.031693834160171</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -13034,16 +13034,16 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>0.5716241134751758</v>
+        <v>0.5716938341601701</v>
       </c>
       <c r="N154" t="n">
-        <v>0.5716241134751758</v>
+        <v>0.5716938341601701</v>
       </c>
       <c r="O154" t="n">
         <v>0.005000000000000782</v>
       </c>
       <c r="P154" t="n">
-        <v>0.582614828261443</v>
+        <v>0.5826845489464372</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -13083,10 +13083,10 @@
         <v>8</v>
       </c>
       <c r="G155" t="n">
-        <v>0.9212765957446809</v>
+        <v>0.9213323883770376</v>
       </c>
       <c r="H155" t="n">
-        <v>9.009478723404253</v>
+        <v>9.009999999999998</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -13105,16 +13105,16 @@
         <v>1</v>
       </c>
       <c r="M155" t="n">
-        <v>0.5794787234042538</v>
+        <v>0.5799999999999983</v>
       </c>
       <c r="N155" t="n">
-        <v>0.5794787234042538</v>
+        <v>0.5799999999999983</v>
       </c>
       <c r="O155" t="n">
         <v>-0.03000000000000114</v>
       </c>
       <c r="P155" t="n">
-        <v>-0.0221453900709232</v>
+        <v>-0.0216938341601729</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -13154,10 +13154,10 @@
         <v>8</v>
       </c>
       <c r="G156" t="n">
-        <v>0.9141843971631206</v>
+        <v>0.9142452161587526</v>
       </c>
       <c r="H156" t="n">
-        <v>8.965985815602838</v>
+        <v>8.966594613749114</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -13176,16 +13176,16 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0.5559858156028383</v>
+        <v>0.5565946137491142</v>
       </c>
       <c r="N156" t="n">
-        <v>0.5559858156028383</v>
+        <v>0.5565946137491142</v>
       </c>
       <c r="O156" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P156" t="n">
-        <v>-0.04349290780141502</v>
+        <v>-0.04340538625088364</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -13225,10 +13225,10 @@
         <v>8</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9049645390070922</v>
+        <v>0.9050318922749823</v>
       </c>
       <c r="H157" t="n">
-        <v>8.920698581560284</v>
+        <v>8.920891211906451</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -13247,16 +13247,16 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>0.6206985815602835</v>
+        <v>0.62089121190645</v>
       </c>
       <c r="N157" t="n">
-        <v>0.6206985815602835</v>
+        <v>0.62089121190645</v>
       </c>
       <c r="O157" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P157" t="n">
-        <v>-0.0452872340425543</v>
+        <v>-0.04570340184266364</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>8</v>
       </c>
       <c r="G158" t="n">
-        <v>0.8950354609929078</v>
+        <v>0.8951098511693835</v>
       </c>
       <c r="H158" t="n">
-        <v>8.856308510638298</v>
+        <v>8.85750708717222</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -13318,16 +13318,16 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>0.6863085106382982</v>
+        <v>0.6875070871722198</v>
       </c>
       <c r="N158" t="n">
-        <v>0.6863085106382982</v>
+        <v>0.6875070871722198</v>
       </c>
       <c r="O158" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P158" t="n">
-        <v>-0.06439007092198601</v>
+        <v>-0.06338412473423105</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -13367,10 +13367,10 @@
         <v>8</v>
       </c>
       <c r="G159" t="n">
-        <v>0.8886524822695036</v>
+        <v>0.888731396172927</v>
       </c>
       <c r="H159" t="n">
-        <v>8.78791134751773</v>
+        <v>8.788701275690999</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -13389,16 +13389,16 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>0.8379113475177293</v>
+        <v>0.8387012756909984</v>
       </c>
       <c r="N159" t="n">
-        <v>0.8379113475177293</v>
+        <v>0.8387012756909984</v>
       </c>
       <c r="O159" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P159" t="n">
-        <v>-0.06839716312056865</v>
+        <v>-0.06880581148122111</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -13438,10 +13438,10 @@
         <v>8</v>
       </c>
       <c r="G160" t="n">
-        <v>0.8652482269503546</v>
+        <v>0.8653437278525868</v>
       </c>
       <c r="H160" t="n">
-        <v>8.428439716312056</v>
+        <v>8.429532246633594</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -13460,16 +13460,16 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>0.6584397163120563</v>
+        <v>0.659532246633594</v>
       </c>
       <c r="N160" t="n">
-        <v>0.6584397163120563</v>
+        <v>0.659532246633594</v>
       </c>
       <c r="O160" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P160" t="n">
-        <v>-0.3594716312056736</v>
+        <v>-0.359169029057405</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -13509,10 +13509,10 @@
         <v>8</v>
       </c>
       <c r="G161" t="n">
-        <v>0.8581560283687943</v>
+        <v>0.8582565556343019</v>
       </c>
       <c r="H161" t="n">
-        <v>8.219751773049646</v>
+        <v>8.22305811481219</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -13531,16 +13531,16 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>0.4897517730496457</v>
+        <v>0.4930581148121895</v>
       </c>
       <c r="N161" t="n">
-        <v>0.4897517730496457</v>
+        <v>0.4930581148121895</v>
       </c>
       <c r="O161" t="n">
         <v>-0.03999999999999915</v>
       </c>
       <c r="P161" t="n">
-        <v>-0.2086879432624098</v>
+        <v>-0.2064741318214036</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -13580,10 +13580,10 @@
         <v>8</v>
       </c>
       <c r="G162" t="n">
-        <v>0.8489361702127659</v>
+        <v>0.8490432317505315</v>
       </c>
       <c r="H162" t="n">
-        <v>8.002744680851061</v>
+        <v>8.00458185683912</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -13602,16 +13602,16 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>0.3027446808510605</v>
+        <v>0.3045818568391203</v>
       </c>
       <c r="N162" t="n">
-        <v>0.3027446808510605</v>
+        <v>0.3045818568391203</v>
       </c>
       <c r="O162" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P162" t="n">
-        <v>-0.2170070921985854</v>
+        <v>-0.2184762579730695</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -13651,10 +13651,10 @@
         <v>8</v>
       </c>
       <c r="G163" t="n">
-        <v>0.8439716312056738</v>
+        <v>0.8440822111977321</v>
       </c>
       <c r="H163" t="n">
-        <v>7.940691489361702</v>
+        <v>7.943063430191353</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -13673,16 +13673,16 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>0.3006914893617028</v>
+        <v>0.3030634301913535</v>
       </c>
       <c r="N163" t="n">
-        <v>0.3006914893617028</v>
+        <v>0.3030634301913535</v>
       </c>
       <c r="O163" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P163" t="n">
-        <v>-0.06205319148935828</v>
+        <v>-0.0615184266477673</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -13722,10 +13722,10 @@
         <v>8</v>
       </c>
       <c r="G164" t="n">
-        <v>0.8375886524822695</v>
+        <v>0.8377037562012757</v>
       </c>
       <c r="H164" t="n">
-        <v>7.835017730496454</v>
+        <v>7.836663713678242</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -13744,16 +13744,16 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>0.2750177304964545</v>
+        <v>0.2766637136782428</v>
       </c>
       <c r="N164" t="n">
-        <v>0.2750177304964545</v>
+        <v>0.2766637136782428</v>
       </c>
       <c r="O164" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P164" t="n">
-        <v>-0.1056737588652483</v>
+        <v>-0.1063997165131108</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -13793,10 +13793,10 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>0.8347517730496454</v>
+        <v>0.8348688873139617</v>
       </c>
       <c r="H165" t="n">
-        <v>7.828695035460993</v>
+        <v>7.828862508858966</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -13815,16 +13815,16 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>0.3486950354609926</v>
+        <v>0.3488625088589652</v>
       </c>
       <c r="N165" t="n">
-        <v>0.3486950354609926</v>
+        <v>0.3488625088589652</v>
       </c>
       <c r="O165" t="n">
         <v>-0.07999999999999918</v>
       </c>
       <c r="P165" t="n">
-        <v>-0.006322695035461123</v>
+        <v>-0.007801204819276819</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -13864,10 +13864,10 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>0.8262411347517731</v>
+        <v>0.8263642806520198</v>
       </c>
       <c r="H166" t="n">
-        <v>7.749698581560284</v>
+        <v>7.751107370659107</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -13886,16 +13886,16 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>0.3796985815602838</v>
+        <v>0.381107370659107</v>
       </c>
       <c r="N166" t="n">
-        <v>0.3796985815602838</v>
+        <v>0.381107370659107</v>
       </c>
       <c r="O166" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P166" t="n">
-        <v>-0.07899645390070908</v>
+        <v>-0.07775513819985846</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -15065,10 +15065,10 @@
         <v>8</v>
       </c>
       <c r="G183" t="n">
-        <v>0.8</v>
+        <v>0.8001417434443657</v>
       </c>
       <c r="H183" t="n">
-        <v>5.55125</v>
+        <v>5.551307583274274</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -15087,16 +15087,16 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>0.3362500000000006</v>
+        <v>0.3363075832742739</v>
       </c>
       <c r="N183" t="n">
-        <v>0.3362500000000006</v>
+        <v>0.3363075832742739</v>
       </c>
       <c r="O183" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P183" t="n">
-        <v>-0.09283023826208847</v>
+        <v>-0.09277265498781517</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -15136,10 +15136,10 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>0.8531914893617021</v>
+        <v>0.8532955350815025</v>
       </c>
       <c r="H184" t="n">
-        <v>5.757872340425532</v>
+        <v>5.758210489014884</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -15158,16 +15158,16 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>0.5928723404255321</v>
+        <v>0.5932104890148837</v>
       </c>
       <c r="N184" t="n">
-        <v>0.5928723404255321</v>
+        <v>0.5932104890148837</v>
       </c>
       <c r="O184" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P184" t="n">
-        <v>0.2066223404255316</v>
+        <v>0.20690290574061</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -15207,10 +15207,10 @@
         <v>8</v>
       </c>
       <c r="G185" t="n">
-        <v>0.8673758865248227</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="H185" t="n">
-        <v>5.79845744680851</v>
+        <v>5.798915662650603</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -15229,16 +15229,16 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>0.6784574468085101</v>
+        <v>0.6789156626506028</v>
       </c>
       <c r="N185" t="n">
-        <v>0.6784574468085101</v>
+        <v>0.6789156626506028</v>
       </c>
       <c r="O185" t="n">
         <v>-0.04499999999999993</v>
       </c>
       <c r="P185" t="n">
-        <v>0.04058510638297808</v>
+        <v>0.04070517363571913</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -15278,10 +15278,10 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>0.8645390070921986</v>
+        <v>0.8646350106307583</v>
       </c>
       <c r="H186" t="n">
-        <v>5.784689716312056</v>
+        <v>5.785095676824946</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -15300,16 +15300,16 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>0.704689716312056</v>
+        <v>0.7050956768249463</v>
       </c>
       <c r="N186" t="n">
-        <v>0.704689716312056</v>
+        <v>0.7050956768249463</v>
       </c>
       <c r="O186" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P186" t="n">
-        <v>-0.01376773049645408</v>
+        <v>-0.01381998582565647</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -15349,10 +15349,10 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8432624113475178</v>
+        <v>0.8433734939759037</v>
       </c>
       <c r="H187" t="n">
-        <v>5.682801418439716</v>
+        <v>5.682981927710844</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -15371,16 +15371,16 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>0.2528014184397165</v>
+        <v>0.2529819277108443</v>
       </c>
       <c r="N187" t="n">
-        <v>0.2528014184397165</v>
+        <v>0.2529819277108443</v>
       </c>
       <c r="O187" t="n">
         <v>0.3499999999999996</v>
       </c>
       <c r="P187" t="n">
-        <v>-0.1018882978723399</v>
+        <v>-0.1021137491141024</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -15420,10 +15420,10 @@
         <v>8</v>
       </c>
       <c r="G188" t="n">
-        <v>0.7957446808510639</v>
+        <v>0.7958894401133948</v>
       </c>
       <c r="H188" t="n">
-        <v>5.539468085106383</v>
+        <v>5.540761871013466</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -15442,16 +15442,16 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.06303191489361737</v>
+        <v>-0.06173812898653441</v>
       </c>
       <c r="N188" t="n">
-        <v>0.06303191489361737</v>
+        <v>0.06173812898653441</v>
       </c>
       <c r="O188" t="n">
         <v>0.1725000000000003</v>
       </c>
       <c r="P188" t="n">
-        <v>-0.1433333333333335</v>
+        <v>-0.1422200566973784</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -15491,10 +15491,10 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>0.7489361702127659</v>
+        <v>0.7491141034727143</v>
       </c>
       <c r="H189" t="n">
-        <v>5.388617021276596</v>
+        <v>5.390207299787385</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -15513,16 +15513,16 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.1613829787234033</v>
+        <v>-0.1597927002126145</v>
       </c>
       <c r="N189" t="n">
-        <v>0.1613829787234033</v>
+        <v>0.1597927002126145</v>
       </c>
       <c r="O189" t="n">
         <v>-0.05250000000000021</v>
       </c>
       <c r="P189" t="n">
-        <v>-0.1508510638297862</v>
+        <v>-0.1505545712260803</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -15562,10 +15562,10 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>0.7212765957446808</v>
+        <v>0.7214741318214033</v>
       </c>
       <c r="H190" t="n">
-        <v>5.281037234042553</v>
+        <v>5.28119773210489</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -15584,16 +15584,16 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>0.001037234042552626</v>
+        <v>0.001197732104889937</v>
       </c>
       <c r="N190" t="n">
-        <v>0.001037234042552626</v>
+        <v>0.001197732104889937</v>
       </c>
       <c r="O190" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P190" t="n">
-        <v>-0.1075797872340436</v>
+        <v>-0.1090095676824951</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -15633,10 +15633,10 @@
         <v>8</v>
       </c>
       <c r="G191" t="n">
-        <v>0.7163120567375887</v>
+        <v>0.7165131112686038</v>
       </c>
       <c r="H191" t="n">
-        <v>5.278501773049645</v>
+        <v>5.27858345145287</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -15655,16 +15655,16 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>0.2535017730496465</v>
+        <v>0.2535834514528714</v>
       </c>
       <c r="N191" t="n">
-        <v>0.2535017730496465</v>
+        <v>0.2535834514528714</v>
       </c>
       <c r="O191" t="n">
         <v>-0.2550000000000017</v>
       </c>
       <c r="P191" t="n">
-        <v>-0.002535460992907801</v>
+        <v>-0.002614280652020184</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -15704,10 +15704,10 @@
         <v>8</v>
       </c>
       <c r="G192" t="n">
-        <v>0.724822695035461</v>
+        <v>0.7250177179305457</v>
       </c>
       <c r="H192" t="n">
-        <v>5.291010638297872</v>
+        <v>5.29196137491141</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -15726,16 +15726,16 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>0.4410106382978727</v>
+        <v>0.4419613749114104</v>
       </c>
       <c r="N192" t="n">
-        <v>0.4410106382978727</v>
+        <v>0.4419613749114104</v>
       </c>
       <c r="O192" t="n">
         <v>-0.1749999999999989</v>
       </c>
       <c r="P192" t="n">
-        <v>0.01250886524822725</v>
+        <v>0.01337792345854005</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -15775,10 +15775,10 @@
         <v>8</v>
       </c>
       <c r="G193" t="n">
-        <v>0.7319148936170212</v>
+        <v>0.7321048901488306</v>
       </c>
       <c r="H193" t="n">
-        <v>5.332712765957445</v>
+        <v>5.335028348688872</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -15797,16 +15797,16 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>0.7627127659574446</v>
+        <v>0.7650283486888716</v>
       </c>
       <c r="N193" t="n">
-        <v>0.7627127659574446</v>
+        <v>0.7650283486888716</v>
       </c>
       <c r="O193" t="n">
         <v>-0.2799999999999994</v>
       </c>
       <c r="P193" t="n">
-        <v>0.0417021276595726</v>
+        <v>0.04306697377746183</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -15846,10 +15846,10 @@
         <v>8</v>
       </c>
       <c r="G194" t="n">
-        <v>0.7226950354609929</v>
+        <v>0.7228915662650602</v>
       </c>
       <c r="H194" t="n">
-        <v>5.282189716312057</v>
+        <v>5.282349397590361</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15868,16 +15868,16 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>0.8521897163120569</v>
+        <v>0.8523493975903618</v>
       </c>
       <c r="N194" t="n">
-        <v>0.8521897163120569</v>
+        <v>0.8523493975903618</v>
       </c>
       <c r="O194" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P194" t="n">
-        <v>-0.05052304964538834</v>
+        <v>-0.0526789510985104</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -15917,10 +15917,10 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>0.6950354609929078</v>
+        <v>0.6952515946137491</v>
       </c>
       <c r="H195" t="n">
-        <v>5.214432624113475</v>
+        <v>5.214783841247342</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -15939,16 +15939,16 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>0.7344326241134747</v>
+        <v>0.7347838412473413</v>
       </c>
       <c r="N195" t="n">
-        <v>0.7344326241134747</v>
+        <v>0.7347838412473413</v>
       </c>
       <c r="O195" t="n">
         <v>0.05000000000000071</v>
       </c>
       <c r="P195" t="n">
-        <v>-0.0677570921985815</v>
+        <v>-0.06756555634301975</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -15988,10 +15988,10 @@
         <v>8</v>
       </c>
       <c r="G196" t="n">
-        <v>0.6567375886524822</v>
+        <v>0.6569808646350106</v>
       </c>
       <c r="H196" t="n">
-        <v>5.124397163120567</v>
+        <v>5.125187810063784</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -16010,16 +16010,16 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>0.3343971631205669</v>
+        <v>0.3351878100637844</v>
       </c>
       <c r="N196" t="n">
-        <v>0.3343971631205669</v>
+        <v>0.3351878100637844</v>
       </c>
       <c r="O196" t="n">
         <v>0.3099999999999996</v>
       </c>
       <c r="P196" t="n">
-        <v>-0.09003546099290816</v>
+        <v>-0.0895960311835573</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -17189,10 +17189,10 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>0.7553191489361702</v>
+        <v>0.7554925584691708</v>
       </c>
       <c r="H213" t="n">
-        <v>5.969503546099291</v>
+        <v>5.969731868651075</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -17211,16 +17211,16 @@
         <v>1</v>
       </c>
       <c r="M213" t="n">
-        <v>-2.76799645390071</v>
+        <v>-2.767768131348926</v>
       </c>
       <c r="N213" t="n">
-        <v>2.76799645390071</v>
+        <v>2.767768131348926</v>
       </c>
       <c r="O213" t="n">
         <v>-0.125</v>
       </c>
       <c r="P213" t="n">
-        <v>-1.395450027832034</v>
+        <v>-1.39522170528025</v>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
@@ -17260,10 +17260,10 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>0.7546099290780142</v>
+        <v>0.7547838412473423</v>
       </c>
       <c r="H214" t="n">
-        <v>5.968569739952718</v>
+        <v>5.968798724309001</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -17282,16 +17282,16 @@
         <v>1</v>
       </c>
       <c r="M214" t="n">
-        <v>-2.61893026004728</v>
+        <v>-2.618701275690998</v>
       </c>
       <c r="N214" t="n">
-        <v>2.61893026004728</v>
+        <v>2.618701275690998</v>
       </c>
       <c r="O214" t="n">
         <v>-0.1500000000000021</v>
       </c>
       <c r="P214" t="n">
-        <v>-0.0009338061465724579</v>
+        <v>-0.0009331443420741437</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>0.7652482269503547</v>
+        <v>0.7654145995747696</v>
       </c>
       <c r="H215" t="n">
-        <v>6.005460992907802</v>
+        <v>6.00677533664068</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -17353,16 +17353,16 @@
         <v>1</v>
       </c>
       <c r="M215" t="n">
-        <v>-2.474539007092199</v>
+        <v>-2.47322466335932</v>
       </c>
       <c r="N215" t="n">
-        <v>2.474539007092199</v>
+        <v>2.47322466335932</v>
       </c>
       <c r="O215" t="n">
         <v>-0.1074999999999982</v>
       </c>
       <c r="P215" t="n">
-        <v>0.03689125295508333</v>
+        <v>0.03797661233167915</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -17402,10 +17402,10 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>0.7858156028368795</v>
+        <v>0.7859673990077959</v>
       </c>
       <c r="H216" t="n">
-        <v>6.096400709219859</v>
+        <v>6.098499291282778</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -17424,16 +17424,16 @@
         <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>-2.113599290780142</v>
+        <v>-2.111500708717223</v>
       </c>
       <c r="N216" t="n">
-        <v>2.113599290780142</v>
+        <v>2.111500708717223</v>
       </c>
       <c r="O216" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P216" t="n">
-        <v>0.09093971631205733</v>
+        <v>0.09172395464209782</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -17473,10 +17473,10 @@
         <v>8</v>
       </c>
       <c r="G217" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.8086463501063076</v>
       </c>
       <c r="H217" t="n">
-        <v>6.198156028368794</v>
+        <v>6.198870777226554</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -17495,16 +17495,16 @@
         <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>-1.961843971631206</v>
+        <v>-1.961129222773446</v>
       </c>
       <c r="N217" t="n">
-        <v>1.961843971631206</v>
+        <v>1.961129222773446</v>
       </c>
       <c r="O217" t="n">
         <v>-0.05000000000000071</v>
       </c>
       <c r="P217" t="n">
-        <v>0.1017553191489355</v>
+        <v>0.1003714859437759</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -17544,10 +17544,10 @@
         <v>8</v>
       </c>
       <c r="G218" t="n">
-        <v>0.8269503546099291</v>
+        <v>0.8270729978738484</v>
       </c>
       <c r="H218" t="n">
-        <v>6.29193853427896</v>
+        <v>6.292584455468935</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -17566,16 +17566,16 @@
         <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>-1.63806146572104</v>
+        <v>-1.637415544531065</v>
       </c>
       <c r="N218" t="n">
-        <v>1.63806146572104</v>
+        <v>1.637415544531065</v>
       </c>
       <c r="O218" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P218" t="n">
-        <v>0.09378250591016535</v>
+        <v>0.09371367824238153</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -17615,10 +17615,10 @@
         <v>8</v>
       </c>
       <c r="G219" t="n">
-        <v>0.8439716312056738</v>
+        <v>0.8440822111977321</v>
       </c>
       <c r="H219" t="n">
-        <v>6.384343971631205</v>
+        <v>6.384562367115521</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -17637,16 +17637,16 @@
         <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>-1.605656028368795</v>
+        <v>-1.605437632884479</v>
       </c>
       <c r="N219" t="n">
-        <v>1.605656028368795</v>
+        <v>1.605437632884479</v>
       </c>
       <c r="O219" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P219" t="n">
-        <v>0.09240543735224538</v>
+        <v>0.09197791164658575</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -17686,10 +17686,10 @@
         <v>8</v>
       </c>
       <c r="G220" t="n">
-        <v>0.851063829787234</v>
+        <v>0.851169383416017</v>
       </c>
       <c r="H220" t="n">
-        <v>6.440212765957448</v>
+        <v>6.442714386959604</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -17708,16 +17708,16 @@
         <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>-1.549787234042553</v>
+        <v>-1.547285613040397</v>
       </c>
       <c r="N220" t="n">
-        <v>1.549787234042553</v>
+        <v>1.547285613040397</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
       </c>
       <c r="P220" t="n">
-        <v>0.05586879432624237</v>
+        <v>0.05815201984408258</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -17757,10 +17757,10 @@
         <v>8</v>
       </c>
       <c r="G221" t="n">
-        <v>0.8418439716312057</v>
+        <v>0.8419560595322466</v>
       </c>
       <c r="H221" t="n">
-        <v>6.380141843971631</v>
+        <v>6.380363217576187</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -17779,16 +17779,16 @@
         <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>-1.477358156028369</v>
+        <v>-1.477136782423813</v>
       </c>
       <c r="N221" t="n">
-        <v>1.477358156028369</v>
+        <v>1.477136782423813</v>
       </c>
       <c r="O221" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P221" t="n">
-        <v>-0.06007092198581621</v>
+        <v>-0.06235116938341623</v>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
@@ -17828,10 +17828,10 @@
         <v>8</v>
       </c>
       <c r="G222" t="n">
-        <v>0.8219858156028369</v>
+        <v>0.8221119773210489</v>
       </c>
       <c r="H222" t="n">
-        <v>6.247895981087471</v>
+        <v>6.248228206945429</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -17850,16 +17850,16 @@
         <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>-1.49210401891253</v>
+        <v>-1.491771793054571</v>
       </c>
       <c r="N222" t="n">
-        <v>1.49210401891253</v>
+        <v>1.491771793054571</v>
       </c>
       <c r="O222" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.1322458628841607</v>
+        <v>-0.1321350106307584</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -17899,10 +17899,10 @@
         <v>8</v>
       </c>
       <c r="G223" t="n">
-        <v>0.8042553191489362</v>
+        <v>0.8043940467753367</v>
       </c>
       <c r="H223" t="n">
-        <v>6.177872340425532</v>
+        <v>6.178237656508387</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -17921,16 +17921,16 @@
         <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>-1.442127659574468</v>
+        <v>-1.441762343491614</v>
       </c>
       <c r="N223" t="n">
-        <v>1.442127659574468</v>
+        <v>1.441762343491614</v>
       </c>
       <c r="O223" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.07002364066193856</v>
+        <v>-0.06999055043704239</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -17970,10 +17970,10 @@
         <v>8</v>
       </c>
       <c r="G224" t="n">
-        <v>0.7794326241134751</v>
+        <v>0.7795889440113395</v>
       </c>
       <c r="H224" t="n">
-        <v>6.075939716312056</v>
+        <v>6.076094082211197</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -17992,16 +17992,16 @@
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>-1.324060283687944</v>
+        <v>-1.323905917788803</v>
       </c>
       <c r="N224" t="n">
-        <v>1.324060283687944</v>
+        <v>1.323905917788803</v>
       </c>
       <c r="O224" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.1019326241134761</v>
+        <v>-0.1021435742971892</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -18041,10 +18041,10 @@
         <v>8</v>
       </c>
       <c r="G225" t="n">
-        <v>0.75177304964539</v>
+        <v>0.7519489723600283</v>
       </c>
       <c r="H225" t="n">
-        <v>5.964503546099291</v>
+        <v>5.965066146940704</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -18063,16 +18063,16 @@
         <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>-1.39549645390071</v>
+        <v>-1.394933853059296</v>
       </c>
       <c r="N225" t="n">
-        <v>1.39549645390071</v>
+        <v>1.394933853059296</v>
       </c>
       <c r="O225" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.1114361702127651</v>
+        <v>-0.111027935270493</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>8</v>
       </c>
       <c r="G226" t="n">
-        <v>0.7269503546099291</v>
+        <v>0.7271438695960312</v>
       </c>
       <c r="H226" t="n">
-        <v>5.82290780141844</v>
+        <v>5.824436569808647</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -18134,16 +18134,16 @@
         <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>-1.55709219858156</v>
+        <v>-1.555563430191353</v>
       </c>
       <c r="N226" t="n">
-        <v>1.55709219858156</v>
+        <v>1.555563430191353</v>
       </c>
       <c r="O226" t="n">
         <v>0.01999999999999957</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.1415957446808509</v>
+        <v>-0.1406295771320574</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -19313,10 +19313,10 @@
         <v>8</v>
       </c>
       <c r="G243" t="n">
-        <v>0.8283687943262411</v>
+        <v>0.8284904323175053</v>
       </c>
       <c r="H243" t="n">
-        <v>5.559968085106383</v>
+        <v>5.561174698795179</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -19335,16 +19335,16 @@
         <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>1.569968085106383</v>
+        <v>1.571174698795179</v>
       </c>
       <c r="N243" t="n">
-        <v>1.569968085106383</v>
+        <v>1.571174698795179</v>
       </c>
       <c r="O243" t="n">
         <v>-0.1624999999999996</v>
       </c>
       <c r="P243" t="n">
-        <v>-1.600949924704409</v>
+        <v>-1.599743311015613</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -19384,10 +19384,10 @@
         <v>8</v>
       </c>
       <c r="G244" t="n">
-        <v>0.7049645390070922</v>
+        <v>0.7044649184975195</v>
       </c>
       <c r="H244" t="n">
-        <v>4.932191489361702</v>
+        <v>4.930662650602409</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -19406,16 +19406,16 @@
         <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>1.109691489361702</v>
+        <v>1.108162650602409</v>
       </c>
       <c r="N244" t="n">
-        <v>1.109691489361702</v>
+        <v>1.108162650602409</v>
       </c>
       <c r="O244" t="n">
         <v>-0.1675000000000004</v>
       </c>
       <c r="P244" t="n">
-        <v>-0.627776595744681</v>
+        <v>-0.6305120481927702</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -19455,10 +19455,10 @@
         <v>8</v>
       </c>
       <c r="G245" t="n">
-        <v>0.6163120567375886</v>
+        <v>0.6158752657689582</v>
       </c>
       <c r="H245" t="n">
-        <v>4.631138297872341</v>
+        <v>4.630692771084338</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -19477,16 +19477,16 @@
         <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>0.8511382978723412</v>
+        <v>0.8506927710843377</v>
       </c>
       <c r="N245" t="n">
-        <v>0.8511382978723412</v>
+        <v>0.8506927710843377</v>
       </c>
       <c r="O245" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.3010531914893608</v>
+        <v>-0.2999698795180716</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -19526,10 +19526,10 @@
         <v>8</v>
       </c>
       <c r="G246" t="n">
-        <v>0.5943262411347517</v>
+        <v>0.5939050318922749</v>
       </c>
       <c r="H246" t="n">
-        <v>4.569627659574468</v>
+        <v>4.565331325301204</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -19548,16 +19548,16 @@
         <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>0.8896276595744674</v>
+        <v>0.8853313253012041</v>
       </c>
       <c r="N246" t="n">
-        <v>0.8896276595744674</v>
+        <v>0.8853313253012041</v>
       </c>
       <c r="O246" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.0615106382978734</v>
+        <v>-0.0653614457831333</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -19597,10 +19597,10 @@
         <v>8</v>
       </c>
       <c r="G247" t="n">
-        <v>0.6347517730496454</v>
+        <v>0.6343019135364989</v>
       </c>
       <c r="H247" t="n">
-        <v>4.724840425531915</v>
+        <v>4.723463855421687</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -19619,16 +19619,16 @@
         <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>1.144840425531915</v>
+        <v>1.143463855421687</v>
       </c>
       <c r="N247" t="n">
-        <v>1.144840425531915</v>
+        <v>1.143463855421687</v>
       </c>
       <c r="O247" t="n">
         <v>-0.1000000000000001</v>
       </c>
       <c r="P247" t="n">
-        <v>0.1552127659574474</v>
+        <v>0.1581325301204828</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -19668,10 +19668,10 @@
         <v>8</v>
       </c>
       <c r="G248" t="n">
-        <v>0.6475177304964539</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="H248" t="n">
-        <v>4.760936170212766</v>
+        <v>4.76</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19690,16 +19690,16 @@
         <v>1</v>
       </c>
       <c r="M248" t="n">
-        <v>1.368436170212766</v>
+        <v>1.3675</v>
       </c>
       <c r="N248" t="n">
-        <v>1.368436170212766</v>
+        <v>1.3675</v>
       </c>
       <c r="O248" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P248" t="n">
-        <v>0.03609574468085075</v>
+        <v>0.03653614457831278</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -19739,10 +19739,10 @@
         <v>8</v>
       </c>
       <c r="G249" t="n">
-        <v>0.5971631205673759</v>
+        <v>0.5967399007795889</v>
       </c>
       <c r="H249" t="n">
-        <v>4.598563829787234</v>
+        <v>4.594246987951808</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19761,16 +19761,16 @@
         <v>1</v>
       </c>
       <c r="M249" t="n">
-        <v>1.318563829787234</v>
+        <v>1.314246987951808</v>
       </c>
       <c r="N249" t="n">
-        <v>1.318563829787234</v>
+        <v>1.314246987951808</v>
       </c>
       <c r="O249" t="n">
         <v>-0.1125000000000003</v>
       </c>
       <c r="P249" t="n">
-        <v>-0.1623723404255317</v>
+        <v>-0.1657530120481923</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -19810,10 +19810,10 @@
         <v>8</v>
       </c>
       <c r="G250" t="n">
-        <v>0.4914893617021276</v>
+        <v>0.4911410347271439</v>
       </c>
       <c r="H250" t="n">
-        <v>4.155414893617022</v>
+        <v>4.15328313253012</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19832,16 +19832,16 @@
         <v>1</v>
       </c>
       <c r="M250" t="n">
-        <v>1.005414893617022</v>
+        <v>1.00328313253012</v>
       </c>
       <c r="N250" t="n">
-        <v>1.005414893617022</v>
+        <v>1.00328313253012</v>
       </c>
       <c r="O250" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P250" t="n">
-        <v>-0.4431489361702123</v>
+        <v>-0.4409638554216873</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -19881,10 +19881,10 @@
         <v>8</v>
       </c>
       <c r="G251" t="n">
-        <v>0.3921985815602837</v>
+        <v>0.3919206236711552</v>
       </c>
       <c r="H251" t="n">
-        <v>3.807531914893617</v>
+        <v>3.806777108433735</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19903,16 +19903,16 @@
         <v>1</v>
       </c>
       <c r="M251" t="n">
-        <v>0.8625319148936175</v>
+        <v>0.8617771084337353</v>
       </c>
       <c r="N251" t="n">
-        <v>0.8625319148936175</v>
+        <v>0.8617771084337353</v>
       </c>
       <c r="O251" t="n">
         <v>-0.2050000000000001</v>
       </c>
       <c r="P251" t="n">
-        <v>-0.3478829787234043</v>
+        <v>-0.3465060240963851</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         <v>8</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3375886524822695</v>
+        <v>0.3373493975903614</v>
       </c>
       <c r="H252" t="n">
-        <v>3.644468085106383</v>
+        <v>3.643654618473895</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19974,16 +19974,16 @@
         <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>0.8044680851063832</v>
+        <v>0.8036546184738955</v>
       </c>
       <c r="N252" t="n">
-        <v>0.8044680851063832</v>
+        <v>0.8036546184738955</v>
       </c>
       <c r="O252" t="n">
         <v>-0.105</v>
       </c>
       <c r="P252" t="n">
-        <v>-0.1630638297872342</v>
+        <v>-0.1631224899598398</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -20023,10 +20023,10 @@
         <v>8</v>
       </c>
       <c r="G253" t="n">
-        <v>0.3482269503546099</v>
+        <v>0.3479801559177888</v>
       </c>
       <c r="H253" t="n">
-        <v>3.681053191489362</v>
+        <v>3.679799196787149</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -20045,16 +20045,16 @@
         <v>1</v>
       </c>
       <c r="M253" t="n">
-        <v>0.911053191489362</v>
+        <v>0.9097991967871488</v>
       </c>
       <c r="N253" t="n">
-        <v>0.911053191489362</v>
+        <v>0.9097991967871488</v>
       </c>
       <c r="O253" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P253" t="n">
-        <v>0.03658510638297896</v>
+        <v>0.03614457831325346</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -20094,10 +20094,10 @@
         <v>8</v>
       </c>
       <c r="G254" t="n">
-        <v>0.4957446808510638</v>
+        <v>0.4953933380581148</v>
       </c>
       <c r="H254" t="n">
-        <v>4.179148936170213</v>
+        <v>4.178253012048193</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -20116,16 +20116,16 @@
         <v>1</v>
       </c>
       <c r="M254" t="n">
-        <v>1.359148936170213</v>
+        <v>1.358253012048193</v>
       </c>
       <c r="N254" t="n">
-        <v>1.359148936170213</v>
+        <v>1.358253012048193</v>
       </c>
       <c r="O254" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P254" t="n">
-        <v>0.4980957446808509</v>
+        <v>0.4984538152610445</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -20165,10 +20165,10 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>0.6964539007092199</v>
+        <v>0.6959603118355776</v>
       </c>
       <c r="H255" t="n">
-        <v>4.906148936170213</v>
+        <v>4.904759036144578</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -20187,16 +20187,16 @@
         <v>1</v>
       </c>
       <c r="M255" t="n">
-        <v>2.156148936170213</v>
+        <v>2.154759036144578</v>
       </c>
       <c r="N255" t="n">
-        <v>2.156148936170213</v>
+        <v>2.154759036144578</v>
       </c>
       <c r="O255" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P255" t="n">
-        <v>0.7270000000000003</v>
+        <v>0.726506024096385</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
@@ -20236,10 +20236,10 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>0.7879432624113475</v>
+        <v>0.7880935506732814</v>
       </c>
       <c r="H256" t="n">
-        <v>5.200170212765956</v>
+        <v>5.201626506024096</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -20258,16 +20258,16 @@
         <v>1</v>
       </c>
       <c r="M256" t="n">
-        <v>2.450170212765956</v>
+        <v>2.451626506024096</v>
       </c>
       <c r="N256" t="n">
-        <v>2.450170212765956</v>
+        <v>2.451626506024096</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
       </c>
       <c r="P256" t="n">
-        <v>0.2940212765957426</v>
+        <v>0.2968674698795173</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -21437,10 +21437,10 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>0.9425531914893617</v>
+        <v>0.9425939050318922</v>
       </c>
       <c r="H273" t="n">
-        <v>6.912606382978724</v>
+        <v>6.912831325301204</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -21459,16 +21459,16 @@
         <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>-0.852393617021276</v>
+        <v>-0.8521686746987953</v>
       </c>
       <c r="N273" t="n">
-        <v>0.852393617021276</v>
+        <v>0.8521686746987953</v>
       </c>
       <c r="O273" t="n">
         <v>0.0550000000000006</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.978327978151853</v>
+        <v>-0.9781030358293723</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -21508,10 +21508,10 @@
         <v>8</v>
       </c>
       <c r="G274" t="n">
-        <v>0.9390070921985816</v>
+        <v>0.9390503189227498</v>
       </c>
       <c r="H274" t="n">
-        <v>6.848014184397163</v>
+        <v>6.848253012048192</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -21530,16 +21530,16 @@
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>-0.9319858156028369</v>
+        <v>-0.9317469879518079</v>
       </c>
       <c r="N274" t="n">
-        <v>0.9319858156028369</v>
+        <v>0.9317469879518079</v>
       </c>
       <c r="O274" t="n">
         <v>0.01500000000000057</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.06459219858156029</v>
+        <v>-0.064578313253012</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -21579,10 +21579,10 @@
         <v>8</v>
       </c>
       <c r="G275" t="n">
-        <v>0.9354609929078014</v>
+        <v>0.9355067328136074</v>
       </c>
       <c r="H275" t="n">
-        <v>6.829210992907801</v>
+        <v>6.829337349397591</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -21601,16 +21601,16 @@
         <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>-0.9407890070921985</v>
+        <v>-0.9406626506024089</v>
       </c>
       <c r="N275" t="n">
-        <v>0.9407890070921985</v>
+        <v>0.9406626506024089</v>
       </c>
       <c r="O275" t="n">
         <v>-0.01000000000000068</v>
       </c>
       <c r="P275" t="n">
-        <v>-0.01880319148936227</v>
+        <v>-0.01891566265060174</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -21650,10 +21650,10 @@
         <v>8</v>
       </c>
       <c r="G276" t="n">
-        <v>0.9319148936170213</v>
+        <v>0.9319631467044649</v>
       </c>
       <c r="H276" t="n">
-        <v>6.817659574468085</v>
+        <v>6.818192771084337</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -21672,16 +21672,16 @@
         <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>-0.8823404255319147</v>
+        <v>-0.8818072289156635</v>
       </c>
       <c r="N276" t="n">
-        <v>0.8823404255319147</v>
+        <v>0.8818072289156635</v>
       </c>
       <c r="O276" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P276" t="n">
-        <v>-0.01155141843971563</v>
+        <v>-0.01114457831325399</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -21721,10 +21721,10 @@
         <v>8</v>
       </c>
       <c r="G277" t="n">
-        <v>0.9283687943262411</v>
+        <v>0.9284195605953225</v>
       </c>
       <c r="H277" t="n">
-        <v>6.778475177304964</v>
+        <v>6.779036144578313</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -21743,16 +21743,16 @@
         <v>1</v>
       </c>
       <c r="M277" t="n">
-        <v>-0.811524822695036</v>
+        <v>-0.8109638554216865</v>
       </c>
       <c r="N277" t="n">
-        <v>0.811524822695036</v>
+        <v>0.8109638554216865</v>
       </c>
       <c r="O277" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P277" t="n">
-        <v>-0.03918439716312161</v>
+        <v>-0.03915662650602325</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -21792,10 +21792,10 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>0.924822695035461</v>
+        <v>0.92487597448618</v>
       </c>
       <c r="H278" t="n">
-        <v>6.749290780141844</v>
+        <v>6.749879518072288</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -21814,16 +21814,16 @@
         <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>-0.7007092198581564</v>
+        <v>-0.700120481927712</v>
       </c>
       <c r="N278" t="n">
-        <v>0.7007092198581564</v>
+        <v>0.700120481927712</v>
       </c>
       <c r="O278" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P278" t="n">
-        <v>-0.02918439716312005</v>
+        <v>-0.02915662650602524</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -21863,10 +21863,10 @@
         <v>8</v>
       </c>
       <c r="G279" t="n">
-        <v>0.9212765957446809</v>
+        <v>0.9213323883770376</v>
       </c>
       <c r="H279" t="n">
-        <v>6.713368794326241</v>
+        <v>6.713574297188755</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -21885,16 +21885,16 @@
         <v>1</v>
       </c>
       <c r="M279" t="n">
-        <v>-0.6566312056737589</v>
+        <v>-0.6564257028112452</v>
       </c>
       <c r="N279" t="n">
-        <v>0.6566312056737589</v>
+        <v>0.6564257028112452</v>
       </c>
       <c r="O279" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P279" t="n">
-        <v>-0.03592198581560258</v>
+        <v>-0.03630522088353327</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -21934,10 +21934,10 @@
         <v>8</v>
       </c>
       <c r="G280" t="n">
-        <v>0.9177304964539007</v>
+        <v>0.9177888022678952</v>
       </c>
       <c r="H280" t="n">
-        <v>6.671843971631207</v>
+        <v>6.673132530120484</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -21956,16 +21956,16 @@
         <v>1</v>
       </c>
       <c r="M280" t="n">
-        <v>-0.598156028368793</v>
+        <v>-0.5968674698795153</v>
       </c>
       <c r="N280" t="n">
-        <v>0.598156028368793</v>
+        <v>0.5968674698795153</v>
       </c>
       <c r="O280" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P280" t="n">
-        <v>-0.04152482269503466</v>
+        <v>-0.04044176706827063</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -22005,10 +22005,10 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>0.9141843971631206</v>
+        <v>0.9142452161587526</v>
       </c>
       <c r="H281" t="n">
-        <v>6.621737588652483</v>
+        <v>6.622409638554217</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -22027,16 +22027,16 @@
         <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>-0.638262411347517</v>
+        <v>-0.637590361445783</v>
       </c>
       <c r="N281" t="n">
-        <v>0.638262411347517</v>
+        <v>0.637590361445783</v>
       </c>
       <c r="O281" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P281" t="n">
-        <v>-0.05010638297872383</v>
+        <v>-0.05072289156626741</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -22076,10 +22076,10 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>0.9106382978723404</v>
+        <v>0.9107016300496102</v>
       </c>
       <c r="H282" t="n">
-        <v>6.546276595744681</v>
+        <v>6.546626506024096</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -22098,16 +22098,16 @@
         <v>1</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.5637234042553194</v>
+        <v>-0.5633734939759041</v>
       </c>
       <c r="N282" t="n">
-        <v>0.5637234042553194</v>
+        <v>0.5633734939759041</v>
       </c>
       <c r="O282" t="n">
         <v>-0.1499999999999995</v>
       </c>
       <c r="P282" t="n">
-        <v>-0.07546099290780184</v>
+        <v>-0.07578313253012059</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -22147,10 +22147,10 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>0.9070921985815603</v>
+        <v>0.9071580439404677</v>
       </c>
       <c r="H283" t="n">
-        <v>6.506737588652483</v>
+        <v>6.508192771084337</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -22169,16 +22169,16 @@
         <v>1</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.5032624113475173</v>
+        <v>-0.5018072289156628</v>
       </c>
       <c r="N283" t="n">
-        <v>0.5032624113475173</v>
+        <v>0.5018072289156628</v>
       </c>
       <c r="O283" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P283" t="n">
-        <v>-0.03953900709219837</v>
+        <v>-0.03843373493975921</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -22218,10 +22218,10 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>0.9049645390070922</v>
+        <v>0.9050318922749823</v>
       </c>
       <c r="H284" t="n">
-        <v>6.419929078014184</v>
+        <v>6.423614457831324</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -22240,16 +22240,16 @@
         <v>1</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.4000709219858161</v>
+        <v>-0.3963855421686766</v>
       </c>
       <c r="N284" t="n">
-        <v>0.4000709219858161</v>
+        <v>0.3963855421686766</v>
       </c>
       <c r="O284" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P284" t="n">
-        <v>-0.08680851063829831</v>
+        <v>-0.08457831325301335</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -22289,10 +22289,10 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>0.9014184397163121</v>
+        <v>0.9014883061658399</v>
       </c>
       <c r="H285" t="n">
-        <v>6.400336879432625</v>
+        <v>6.400722891566265</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -22311,16 +22311,16 @@
         <v>1</v>
       </c>
       <c r="M285" t="n">
-        <v>-0.2996631205673754</v>
+        <v>-0.2992771084337349</v>
       </c>
       <c r="N285" t="n">
-        <v>0.2996631205673754</v>
+        <v>0.2992771084337349</v>
       </c>
       <c r="O285" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P285" t="n">
-        <v>-0.01959219858155947</v>
+        <v>-0.02289156626505839</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
@@ -22360,10 +22360,10 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>0.898581560283688</v>
+        <v>0.8986534372785259</v>
       </c>
       <c r="H286" t="n">
-        <v>6.348652482269504</v>
+        <v>6.350240963855422</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -22382,16 +22382,16 @@
         <v>1</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.1913475177304962</v>
+        <v>-0.1897590361445785</v>
       </c>
       <c r="N286" t="n">
-        <v>0.1913475177304962</v>
+        <v>0.1897590361445785</v>
       </c>
       <c r="O286" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P286" t="n">
-        <v>-0.0516843971631209</v>
+        <v>-0.0504819277108437</v>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
@@ -25685,10 +25685,10 @@
         <v>8</v>
       </c>
       <c r="G333" t="n">
-        <v>0.7631205673758865</v>
+        <v>0.7632884479092842</v>
       </c>
       <c r="H333" t="n">
-        <v>6.480446808510639</v>
+        <v>6.481396172927003</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -25707,16 +25707,16 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.7820531914893616</v>
+        <v>-0.7811038270729975</v>
       </c>
       <c r="N333" t="n">
-        <v>0.7820531914893616</v>
+        <v>0.7811038270729975</v>
       </c>
       <c r="O333" t="n">
         <v>-0.4400000000000004</v>
       </c>
       <c r="P333" t="n">
-        <v>-0.9870584472707202</v>
+        <v>-0.9861090828543562</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -25756,10 +25756,10 @@
         <v>8</v>
       </c>
       <c r="G334" t="n">
-        <v>0.7716312056737589</v>
+        <v>0.771793054571226</v>
       </c>
       <c r="H334" t="n">
-        <v>6.535715425531915</v>
+        <v>6.536058646350106</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -25778,16 +25778,16 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.4392845744680844</v>
+        <v>-0.4389413536498932</v>
       </c>
       <c r="N334" t="n">
-        <v>0.4392845744680844</v>
+        <v>0.4389413536498932</v>
       </c>
       <c r="O334" t="n">
         <v>-0.2875000000000005</v>
       </c>
       <c r="P334" t="n">
-        <v>0.05526861702127661</v>
+        <v>0.05466247342310382</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -25827,10 +25827,10 @@
         <v>8</v>
       </c>
       <c r="G335" t="n">
-        <v>0.7914893617021277</v>
+        <v>0.7916371367824239</v>
       </c>
       <c r="H335" t="n">
-        <v>6.640436170212766</v>
+        <v>6.640854004252303</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -25849,16 +25849,16 @@
         <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.1595638297872339</v>
+        <v>-0.1591459957476964</v>
       </c>
       <c r="N335" t="n">
-        <v>0.1595638297872339</v>
+        <v>0.1591459957476964</v>
       </c>
       <c r="O335" t="n">
         <v>-0.1749999999999998</v>
       </c>
       <c r="P335" t="n">
-        <v>0.1047207446808507</v>
+        <v>0.104795357902197</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -25898,10 +25898,10 @@
         <v>8</v>
       </c>
       <c r="G336" t="n">
-        <v>0.8141843971631205</v>
+        <v>0.8143160878809355</v>
       </c>
       <c r="H336" t="n">
-        <v>6.844212765957447</v>
+        <v>6.84495747696669</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -25920,16 +25920,16 @@
         <v>1</v>
       </c>
       <c r="M336" t="n">
-        <v>0.2142127659574466</v>
+        <v>0.2149574769666902</v>
       </c>
       <c r="N336" t="n">
-        <v>0.2142127659574466</v>
+        <v>0.2149574769666902</v>
       </c>
       <c r="O336" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P336" t="n">
-        <v>0.2037765957446807</v>
+        <v>0.2041034727143867</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -25969,10 +25969,10 @@
         <v>8</v>
       </c>
       <c r="G337" t="n">
-        <v>0.8340425531914893</v>
+        <v>0.8341601700921333</v>
       </c>
       <c r="H337" t="n">
-        <v>7.061510638297873</v>
+        <v>7.062175761871013</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -25991,16 +25991,16 @@
         <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>0.5715106382978723</v>
+        <v>0.572175761871013</v>
       </c>
       <c r="N337" t="n">
-        <v>0.5715106382978723</v>
+        <v>0.572175761871013</v>
       </c>
       <c r="O337" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P337" t="n">
-        <v>0.217297872340426</v>
+        <v>0.2172182849043232</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>8</v>
       </c>
       <c r="G338" t="n">
-        <v>0.850354609929078</v>
+        <v>0.8504606661941885</v>
       </c>
       <c r="H338" t="n">
-        <v>7.147751063829787</v>
+        <v>7.147871013465627</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -26062,16 +26062,16 @@
         <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>0.6677510638297868</v>
+        <v>0.6678710134656267</v>
       </c>
       <c r="N338" t="n">
-        <v>0.6677510638297868</v>
+        <v>0.6678710134656267</v>
       </c>
       <c r="O338" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P338" t="n">
-        <v>0.08624042553191469</v>
+        <v>0.08569525159461389</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>8</v>
       </c>
       <c r="G339" t="n">
-        <v>0.8574468085106383</v>
+        <v>0.8575478384124734</v>
       </c>
       <c r="H339" t="n">
         <v>7.202500000000001</v>
@@ -26142,7 +26142,7 @@
         <v>0.0699999999999994</v>
       </c>
       <c r="P339" t="n">
-        <v>0.05474893617021337</v>
+        <v>0.05462898653437342</v>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
@@ -26182,10 +26182,10 @@
         <v>8</v>
       </c>
       <c r="G340" t="n">
-        <v>0.849645390070922</v>
+        <v>0.8497519489723601</v>
       </c>
       <c r="H340" t="n">
-        <v>7.146948936170213</v>
+        <v>7.147069454287739</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -26204,16 +26204,16 @@
         <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>0.6169489361702123</v>
+        <v>0.6170694542877388</v>
       </c>
       <c r="N340" t="n">
-        <v>0.6169489361702123</v>
+        <v>0.6170694542877388</v>
       </c>
       <c r="O340" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P340" t="n">
-        <v>-0.05555106382978803</v>
+        <v>-0.05543054571226147</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -26253,10 +26253,10 @@
         <v>8</v>
       </c>
       <c r="G341" t="n">
-        <v>0.8297872340425532</v>
+        <v>0.8299078667611623</v>
       </c>
       <c r="H341" t="n">
-        <v>7.019929078014184</v>
+        <v>7.020838648712497</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -26275,16 +26275,16 @@
         <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>0.6874290780141843</v>
+        <v>0.6883386487124978</v>
       </c>
       <c r="N341" t="n">
-        <v>0.6874290780141843</v>
+        <v>0.6883386487124978</v>
       </c>
       <c r="O341" t="n">
         <v>-0.1975000000000007</v>
       </c>
       <c r="P341" t="n">
-        <v>-0.1270198581560287</v>
+        <v>-0.1262308055752417</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -26324,10 +26324,10 @@
         <v>8</v>
       </c>
       <c r="G342" t="n">
-        <v>0.8099290780141843</v>
+        <v>0.8100637845499645</v>
       </c>
       <c r="H342" t="n">
-        <v>6.818787234042554</v>
+        <v>6.818977675407512</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -26346,16 +26346,16 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>0.6287872340425533</v>
+        <v>0.628977675407512</v>
       </c>
       <c r="N342" t="n">
-        <v>0.6287872340425533</v>
+        <v>0.628977675407512</v>
       </c>
       <c r="O342" t="n">
         <v>-0.1424999999999992</v>
       </c>
       <c r="P342" t="n">
-        <v>-0.2011418439716302</v>
+        <v>-0.201860973304985</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -26395,10 +26395,10 @@
         <v>8</v>
       </c>
       <c r="G343" t="n">
-        <v>0.7865248226950354</v>
+        <v>0.7866761162296244</v>
       </c>
       <c r="H343" t="n">
-        <v>6.6111914893617</v>
+        <v>6.614613749114103</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
@@ -26417,16 +26417,16 @@
         <v>1</v>
       </c>
       <c r="M343" t="n">
-        <v>0.6211914893617001</v>
+        <v>0.6246137491141024</v>
       </c>
       <c r="N343" t="n">
-        <v>0.6211914893617001</v>
+        <v>0.6246137491141024</v>
       </c>
       <c r="O343" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P343" t="n">
-        <v>-0.2075957446808534</v>
+        <v>-0.2043639262934098</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -26466,10 +26466,10 @@
         <v>8</v>
       </c>
       <c r="G344" t="n">
-        <v>0.7624113475177305</v>
+        <v>0.7625797306874557</v>
       </c>
       <c r="H344" t="n">
-        <v>6.477624113475178</v>
+        <v>6.478258918025041</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -26488,16 +26488,16 @@
         <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5576241134751783</v>
+        <v>0.5582589180250412</v>
       </c>
       <c r="N344" t="n">
-        <v>0.5576241134751783</v>
+        <v>0.5582589180250412</v>
       </c>
       <c r="O344" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P344" t="n">
-        <v>-0.1335673758865221</v>
+        <v>-0.1363548310890614</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -26537,10 +26537,10 @@
         <v>8</v>
       </c>
       <c r="G345" t="n">
-        <v>0.7404255319148936</v>
+        <v>0.7406094968107725</v>
       </c>
       <c r="H345" t="n">
-        <v>6.374212765957447</v>
+        <v>6.376293408929837</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
@@ -26559,16 +26559,16 @@
         <v>1</v>
       </c>
       <c r="M345" t="n">
-        <v>0.3942127659574464</v>
+        <v>0.3962934089298367</v>
       </c>
       <c r="N345" t="n">
-        <v>0.3942127659574464</v>
+        <v>0.3962934089298367</v>
       </c>
       <c r="O345" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P345" t="n">
-        <v>-0.1034113475177314</v>
+        <v>-0.1019655090952041</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -26608,10 +26608,10 @@
         <v>8</v>
       </c>
       <c r="G346" t="n">
-        <v>0.7170212765957447</v>
+        <v>0.7172218284904324</v>
       </c>
       <c r="H346" t="n">
-        <v>6.228688829787234</v>
+        <v>6.228972360028349</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -26630,16 +26630,16 @@
         <v>1</v>
       </c>
       <c r="M346" t="n">
-        <v>0.1086888297872344</v>
+        <v>0.108972360028349</v>
       </c>
       <c r="N346" t="n">
-        <v>0.1086888297872344</v>
+        <v>0.108972360028349</v>
       </c>
       <c r="O346" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P346" t="n">
-        <v>-0.1455239361702123</v>
+        <v>-0.147321048901488</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -27809,10 +27809,10 @@
         <v>8</v>
       </c>
       <c r="G363" t="n">
-        <v>0.6439716312056738</v>
+        <v>0.6442239546420978</v>
       </c>
       <c r="H363" t="n">
-        <v>6.968560283687943</v>
+        <v>6.968780120481927</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -27831,16 +27831,16 @@
         <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>-1.493939716312057</v>
+        <v>-1.493719879518073</v>
       </c>
       <c r="N363" t="n">
-        <v>1.493939716312057</v>
+        <v>1.493719879518073</v>
       </c>
       <c r="O363" t="n">
         <v>-0.254999999999999</v>
       </c>
       <c r="P363" t="n">
-        <v>0.1259796950404315</v>
+        <v>0.1261995318344153</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -27880,10 +27880,10 @@
         <v>8</v>
       </c>
       <c r="G364" t="n">
-        <v>0.6524822695035462</v>
+        <v>0.6527285613040397</v>
       </c>
       <c r="H364" t="n">
-        <v>6.997801418439717</v>
+        <v>6.999518072289156</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -27902,16 +27902,16 @@
         <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>-1.314698581560283</v>
+        <v>-1.312981927710844</v>
       </c>
       <c r="N364" t="n">
-        <v>1.314698581560283</v>
+        <v>1.312981927710844</v>
       </c>
       <c r="O364" t="n">
         <v>-0.1500000000000004</v>
       </c>
       <c r="P364" t="n">
-        <v>0.02924113475177315</v>
+        <v>0.03073795180722882</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -27951,10 +27951,10 @@
         <v>8</v>
       </c>
       <c r="G365" t="n">
-        <v>0.6652482269503546</v>
+        <v>0.6654854712969526</v>
       </c>
       <c r="H365" t="n">
-        <v>7.062585106382979</v>
+        <v>7.06382530120482</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -27973,16 +27973,16 @@
         <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>-1.067414893617022</v>
+        <v>-1.066174698795181</v>
       </c>
       <c r="N365" t="n">
-        <v>1.067414893617022</v>
+        <v>1.066174698795181</v>
       </c>
       <c r="O365" t="n">
         <v>-0.1824999999999992</v>
       </c>
       <c r="P365" t="n">
-        <v>0.06478368794326261</v>
+        <v>0.06430722891566365</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -28022,10 +28022,10 @@
         <v>8</v>
       </c>
       <c r="G366" t="n">
-        <v>0.6794326241134752</v>
+        <v>0.6796598157335223</v>
       </c>
       <c r="H366" t="n">
-        <v>7.160675531914893</v>
+        <v>7.16156626506024</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -28044,16 +28044,16 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.9268244680851074</v>
+        <v>-0.9259337349397603</v>
       </c>
       <c r="N366" t="n">
-        <v>0.9268244680851074</v>
+        <v>0.9259337349397603</v>
       </c>
       <c r="O366" t="n">
         <v>-0.04250000000000043</v>
       </c>
       <c r="P366" t="n">
-        <v>0.09809042553191372</v>
+        <v>0.0977409638554203</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -28093,10 +28093,10 @@
         <v>8</v>
       </c>
       <c r="G367" t="n">
-        <v>0.6872340425531915</v>
+        <v>0.6874557051736357</v>
       </c>
       <c r="H367" t="n">
-        <v>7.191252659574468</v>
+        <v>7.191445783132531</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -28115,16 +28115,16 @@
         <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>-1.038747340425532</v>
+        <v>-1.038554216867469</v>
       </c>
       <c r="N367" t="n">
-        <v>1.038747340425532</v>
+        <v>1.038554216867469</v>
       </c>
       <c r="O367" t="n">
         <v>0.1425000000000001</v>
       </c>
       <c r="P367" t="n">
-        <v>0.03057712765957543</v>
+        <v>0.02987951807229106</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -28164,10 +28164,10 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>0.6886524822695036</v>
+        <v>0.6888731396172927</v>
       </c>
       <c r="H368" t="n">
-        <v>7.192488475177305</v>
+        <v>7.193343373493977</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -28186,16 +28186,16 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.8500115248226949</v>
+        <v>-0.8491566265060237</v>
       </c>
       <c r="N368" t="n">
-        <v>0.8500115248226949</v>
+        <v>0.8491566265060237</v>
       </c>
       <c r="O368" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P368" t="n">
-        <v>0.001235815602837143</v>
+        <v>0.001897590361445545</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -28235,10 +28235,10 @@
         <v>8</v>
       </c>
       <c r="G369" t="n">
-        <v>0.6829787234042554</v>
+        <v>0.6832034018426648</v>
       </c>
       <c r="H369" t="n">
-        <v>7.174578457446808</v>
+        <v>7.175459337349397</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -28257,16 +28257,16 @@
         <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.7754215425531923</v>
+        <v>-0.7745406626506028</v>
       </c>
       <c r="N369" t="n">
-        <v>0.7754215425531923</v>
+        <v>0.7745406626506028</v>
       </c>
       <c r="O369" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P369" t="n">
-        <v>-0.01791001773049761</v>
+        <v>-0.01788403614457934</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -28306,10 +28306,10 @@
         <v>8</v>
       </c>
       <c r="G370" t="n">
-        <v>0.6709219858156028</v>
+        <v>0.6711552090715804</v>
       </c>
       <c r="H370" t="n">
-        <v>7.102652482269503</v>
+        <v>7.105903614457831</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -28328,16 +28328,16 @@
         <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.8773475177304979</v>
+        <v>-0.8740963855421695</v>
       </c>
       <c r="N370" t="n">
-        <v>0.8773475177304979</v>
+        <v>0.8740963855421695</v>
       </c>
       <c r="O370" t="n">
         <v>0.03000000000000025</v>
       </c>
       <c r="P370" t="n">
-        <v>-0.07192597517730537</v>
+        <v>-0.06955572289156642</v>
       </c>
       <c r="Q370" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>8</v>
       </c>
       <c r="G371" t="n">
-        <v>0.6517730496453901</v>
+        <v>0.6520198440822113</v>
       </c>
       <c r="H371" t="n">
-        <v>6.992858156028369</v>
+        <v>6.994578313253013</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -28399,16 +28399,16 @@
         <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>-1.042141843971631</v>
+        <v>-1.040421686746988</v>
       </c>
       <c r="N371" t="n">
-        <v>1.042141843971631</v>
+        <v>1.040421686746988</v>
       </c>
       <c r="O371" t="n">
         <v>0.05499999999999972</v>
       </c>
       <c r="P371" t="n">
-        <v>-0.1097943262411336</v>
+        <v>-0.1113253012048183</v>
       </c>
       <c r="Q371" t="inlineStr">
         <is>
@@ -28448,10 +28448,10 @@
         <v>8</v>
       </c>
       <c r="G372" t="n">
-        <v>0.6297872340425532</v>
+        <v>0.630049610205528</v>
       </c>
       <c r="H372" t="n">
-        <v>6.932404255319149</v>
+        <v>6.933222891566265</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -28470,16 +28470,16 @@
         <v>1</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.9775957446808512</v>
+        <v>-0.9767771084337351</v>
       </c>
       <c r="N372" t="n">
-        <v>0.9775957446808512</v>
+        <v>0.9767771084337351</v>
       </c>
       <c r="O372" t="n">
         <v>-0.125</v>
       </c>
       <c r="P372" t="n">
-        <v>-0.06045390070921997</v>
+        <v>-0.06135542168674757</v>
       </c>
       <c r="Q372" t="inlineStr">
         <is>
@@ -28519,10 +28519,10 @@
         <v>8</v>
       </c>
       <c r="G373" t="n">
-        <v>0.6148936170212767</v>
+        <v>0.6151665485471297</v>
       </c>
       <c r="H373" t="n">
-        <v>6.873832446808511</v>
+        <v>6.875496987951808</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -28541,16 +28541,16 @@
         <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.8161675531914891</v>
+        <v>-0.8145030120481929</v>
       </c>
       <c r="N373" t="n">
-        <v>0.8161675531914891</v>
+        <v>0.8145030120481929</v>
       </c>
       <c r="O373" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P373" t="n">
-        <v>-0.0585718085106377</v>
+        <v>-0.05772590361445751</v>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
@@ -28590,10 +28590,10 @@
         <v>8</v>
       </c>
       <c r="G374" t="n">
-        <v>0.5971631205673759</v>
+        <v>0.5974486180014175</v>
       </c>
       <c r="H374" t="n">
-        <v>6.797778368794327</v>
+        <v>6.798027108433735</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -28612,16 +28612,16 @@
         <v>1</v>
       </c>
       <c r="M374" t="n">
-        <v>-0.6622216312056732</v>
+        <v>-0.6619728915662648</v>
       </c>
       <c r="N374" t="n">
-        <v>0.6622216312056732</v>
+        <v>0.6619728915662648</v>
       </c>
       <c r="O374" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P374" t="n">
-        <v>-0.07605407801418451</v>
+        <v>-0.07746987951807238</v>
       </c>
       <c r="Q374" t="inlineStr">
         <is>
@@ -28661,10 +28661,10 @@
         <v>8</v>
       </c>
       <c r="G375" t="n">
-        <v>0.5822695035460993</v>
+        <v>0.5825655563430191</v>
       </c>
       <c r="H375" t="n">
-        <v>6.75802304964539</v>
+        <v>6.760060240963855</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -28683,16 +28683,16 @@
         <v>1</v>
       </c>
       <c r="M375" t="n">
-        <v>-0.5219769503546106</v>
+        <v>-0.519939759036145</v>
       </c>
       <c r="N375" t="n">
-        <v>0.5219769503546106</v>
+        <v>0.519939759036145</v>
       </c>
       <c r="O375" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.03975531914893704</v>
+        <v>-0.03796686746987987</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
@@ -28732,10 +28732,10 @@
         <v>8</v>
       </c>
       <c r="G376" t="n">
-        <v>0.5638297872340425</v>
+        <v>0.5641389085754784</v>
       </c>
       <c r="H376" t="n">
-        <v>6.677473404255319</v>
+        <v>6.678012048192771</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -28754,16 +28754,16 @@
         <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>-0.4325265957446813</v>
+        <v>-0.4319879518072298</v>
       </c>
       <c r="N376" t="n">
-        <v>0.4325265957446813</v>
+        <v>0.4319879518072298</v>
       </c>
       <c r="O376" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.0805496453900707</v>
+        <v>-0.08204819277108477</v>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
@@ -29933,10 +29933,10 @@
         <v>8</v>
       </c>
       <c r="G393" t="n">
-        <v>0.6588652482269504</v>
+        <v>0.6583982990786676</v>
       </c>
       <c r="H393" t="n">
-        <v>5.821893617021277</v>
+        <v>5.814525159461375</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -29955,16 +29955,16 @@
         <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>1.031893617021276</v>
+        <v>1.024525159461374</v>
       </c>
       <c r="N393" t="n">
-        <v>1.031893617021276</v>
+        <v>1.024525159461374</v>
       </c>
       <c r="O393" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P393" t="n">
-        <v>-0.6436284572604327</v>
+        <v>-0.6509969148203343</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
@@ -30004,10 +30004,10 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>0.5645390070921986</v>
+        <v>0.5641389085754784</v>
       </c>
       <c r="H394" t="n">
-        <v>5.501053191489362</v>
+        <v>5.500263997165131</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -30026,16 +30026,16 @@
         <v>1</v>
       </c>
       <c r="M394" t="n">
-        <v>0.831053191489362</v>
+        <v>0.8302639971651313</v>
       </c>
       <c r="N394" t="n">
-        <v>0.831053191489362</v>
+        <v>0.8302639971651313</v>
       </c>
       <c r="O394" t="n">
         <v>-0.120000000000001</v>
       </c>
       <c r="P394" t="n">
-        <v>-0.3208404255319151</v>
+        <v>-0.3142611622962441</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -30075,10 +30075,10 @@
         <v>8</v>
       </c>
       <c r="G395" t="n">
-        <v>0.5432624113475177</v>
+        <v>0.5428773919206237</v>
       </c>
       <c r="H395" t="n">
-        <v>5.457195035460993</v>
+        <v>5.45694188518781</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -30097,16 +30097,16 @@
         <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>0.9171950354609928</v>
+        <v>0.9169418851878097</v>
       </c>
       <c r="N395" t="n">
-        <v>0.9171950354609928</v>
+        <v>0.9169418851878097</v>
       </c>
       <c r="O395" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P395" t="n">
-        <v>-0.04385815602836907</v>
+        <v>-0.0433221119773215</v>
       </c>
       <c r="Q395" t="inlineStr">
         <is>
@@ -30146,10 +30146,10 @@
         <v>8</v>
       </c>
       <c r="G396" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.595322466335932</v>
       </c>
       <c r="H396" t="n">
-        <v>5.636702127659574</v>
+        <v>5.636424521615876</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -30168,16 +30168,16 @@
         <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>1.196702127659574</v>
+        <v>1.196424521615875</v>
       </c>
       <c r="N396" t="n">
-        <v>1.196702127659574</v>
+        <v>1.196424521615875</v>
       </c>
       <c r="O396" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P396" t="n">
-        <v>0.1795070921985813</v>
+        <v>0.1794826364280659</v>
       </c>
       <c r="Q396" t="inlineStr">
         <is>
@@ -30217,10 +30217,10 @@
         <v>8</v>
       </c>
       <c r="G397" t="n">
-        <v>0.6340425531914894</v>
+        <v>0.6335931963146705</v>
       </c>
       <c r="H397" t="n">
-        <v>5.756882978723405</v>
+        <v>5.756587526576896</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -30239,16 +30239,16 @@
         <v>1</v>
       </c>
       <c r="M397" t="n">
-        <v>1.316882978723404</v>
+        <v>1.316587526576896</v>
       </c>
       <c r="N397" t="n">
-        <v>1.316882978723404</v>
+        <v>1.316587526576896</v>
       </c>
       <c r="O397" t="n">
         <v>0</v>
       </c>
       <c r="P397" t="n">
-        <v>0.1201808510638305</v>
+        <v>0.1201630049610207</v>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>8</v>
       </c>
       <c r="G398" t="n">
-        <v>0.5943262411347517</v>
+        <v>0.5939050318922749</v>
       </c>
       <c r="H398" t="n">
-        <v>5.635769503546099</v>
+        <v>5.635492558469171</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -30310,16 +30310,16 @@
         <v>1</v>
       </c>
       <c r="M398" t="n">
-        <v>1.235769503546098</v>
+        <v>1.23549255846917</v>
       </c>
       <c r="N398" t="n">
-        <v>1.235769503546098</v>
+        <v>1.23549255846917</v>
       </c>
       <c r="O398" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P398" t="n">
-        <v>-0.1211134751773058</v>
+        <v>-0.1210949681077258</v>
       </c>
       <c r="Q398" t="inlineStr">
         <is>
@@ -30359,10 +30359,10 @@
         <v>8</v>
       </c>
       <c r="G399" t="n">
-        <v>0.4794326241134752</v>
+        <v>0.4790928419560596</v>
       </c>
       <c r="H399" t="n">
-        <v>5.19136170212766</v>
+        <v>5.190021261516655</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -30381,16 +30381,16 @@
         <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>0.8113617021276598</v>
+        <v>0.8100212615166553</v>
       </c>
       <c r="N399" t="n">
-        <v>0.8113617021276598</v>
+        <v>0.8100212615166553</v>
       </c>
       <c r="O399" t="n">
         <v>-0.02000000000000046</v>
       </c>
       <c r="P399" t="n">
-        <v>-0.4444078014184392</v>
+        <v>-0.4454712969525154</v>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
@@ -30430,10 +30430,10 @@
         <v>8</v>
       </c>
       <c r="G400" t="n">
-        <v>0.3709219858156028</v>
+        <v>0.3706591070163005</v>
       </c>
       <c r="H400" t="n">
-        <v>4.843881205673759</v>
+        <v>4.843708362863217</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -30452,16 +30452,16 @@
         <v>1</v>
       </c>
       <c r="M400" t="n">
-        <v>0.7038812056737589</v>
+        <v>0.7037083628632175</v>
       </c>
       <c r="N400" t="n">
-        <v>0.7038812056737589</v>
+        <v>0.7037083628632175</v>
       </c>
       <c r="O400" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P400" t="n">
-        <v>-0.3474804964539011</v>
+        <v>-0.3463128986534381</v>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
@@ -30501,10 +30501,10 @@
         <v>8</v>
       </c>
       <c r="G401" t="n">
-        <v>0.3262411347517731</v>
+        <v>0.3260099220411056</v>
       </c>
       <c r="H401" t="n">
-        <v>4.70654255319149</v>
+        <v>4.704718284904324</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -30523,16 +30523,16 @@
         <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>0.8365425531914896</v>
+        <v>0.8347182849043238</v>
       </c>
       <c r="N401" t="n">
-        <v>0.8365425531914896</v>
+        <v>0.8347182849043238</v>
       </c>
       <c r="O401" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P401" t="n">
-        <v>-0.1373386524822688</v>
+        <v>-0.1389900779588933</v>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
@@ -30572,10 +30572,10 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>0.3524822695035461</v>
+        <v>0.3522324592487597</v>
       </c>
       <c r="H402" t="n">
-        <v>4.806757092198581</v>
+        <v>4.80659284195606</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -30594,16 +30594,16 @@
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>1.086757092198581</v>
+        <v>1.08659284195606</v>
       </c>
       <c r="N402" t="n">
-        <v>1.086757092198581</v>
+        <v>1.08659284195606</v>
       </c>
       <c r="O402" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P402" t="n">
-        <v>0.1002145390070917</v>
+        <v>0.1018745570517359</v>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -30643,10 +30643,10 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>0.5304964539007092</v>
+        <v>0.5301204819277109</v>
       </c>
       <c r="H403" t="n">
-        <v>5.442602836879432</v>
+        <v>5.44210843373494</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -30665,16 +30665,16 @@
         <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>1.742602836879432</v>
+        <v>1.74210843373494</v>
       </c>
       <c r="N403" t="n">
-        <v>1.742602836879432</v>
+        <v>1.74210843373494</v>
       </c>
       <c r="O403" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P403" t="n">
-        <v>0.635845744680851</v>
+        <v>0.63551559177888</v>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>8</v>
       </c>
       <c r="G404" t="n">
-        <v>0.7602836879432624</v>
+        <v>0.7604535790219702</v>
       </c>
       <c r="H404" t="n">
-        <v>6.099886524822694</v>
+        <v>6.099998228206945</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -30736,16 +30736,16 @@
         <v>1</v>
       </c>
       <c r="M404" t="n">
-        <v>2.259886524822694</v>
+        <v>2.259998228206945</v>
       </c>
       <c r="N404" t="n">
-        <v>2.259886524822694</v>
+        <v>2.259998228206945</v>
       </c>
       <c r="O404" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P404" t="n">
-        <v>0.657283687943262</v>
+        <v>0.6578897944720055</v>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
@@ -30785,10 +30785,10 @@
         <v>8</v>
       </c>
       <c r="G405" t="n">
-        <v>0.8312056737588652</v>
+        <v>0.8313253012048193</v>
       </c>
       <c r="H405" t="n">
-        <v>6.343659574468085</v>
+        <v>6.344367469879518</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -30807,16 +30807,16 @@
         <v>1</v>
       </c>
       <c r="M405" t="n">
-        <v>2.323659574468086</v>
+        <v>2.324367469879519</v>
       </c>
       <c r="N405" t="n">
-        <v>2.323659574468086</v>
+        <v>2.324367469879519</v>
       </c>
       <c r="O405" t="n">
         <v>0.1799999999999997</v>
       </c>
       <c r="P405" t="n">
-        <v>0.2437730496453909</v>
+        <v>0.2443692416725733</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
@@ -30856,10 +30856,10 @@
         <v>8</v>
       </c>
       <c r="G406" t="n">
-        <v>0.8156028368794326</v>
+        <v>0.8157335223245925</v>
       </c>
       <c r="H406" t="n">
-        <v>6.290088652482269</v>
+        <v>6.290947909284196</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -30878,16 +30878,16 @@
         <v>1</v>
       </c>
       <c r="M406" t="n">
-        <v>2.190088652482269</v>
+        <v>2.190947909284196</v>
       </c>
       <c r="N406" t="n">
-        <v>2.190088652482269</v>
+        <v>2.190947909284196</v>
       </c>
       <c r="O406" t="n">
         <v>0.08000000000000007</v>
       </c>
       <c r="P406" t="n">
-        <v>-0.05357092198581626</v>
+        <v>-0.05341956059532293</v>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
@@ -32057,10 +32057,10 @@
         <v>8</v>
       </c>
       <c r="G423" t="n">
-        <v>0.8290780141843972</v>
+        <v>0.8291991495393338</v>
       </c>
       <c r="H423" t="n">
-        <v>5.561335106382979</v>
+        <v>5.562115520907158</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -32079,16 +32079,16 @@
         <v>1</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.8061648936170211</v>
+        <v>-0.8053844790928419</v>
       </c>
       <c r="N423" t="n">
-        <v>0.8061648936170211</v>
+        <v>0.8053844790928419</v>
       </c>
       <c r="O423" t="n">
         <v>-0.07500000000000018</v>
       </c>
       <c r="P423" t="n">
-        <v>-1.477594466146804</v>
+        <v>-1.476814051622624</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
@@ -32128,10 +32128,10 @@
         <v>8</v>
       </c>
       <c r="G424" t="n">
-        <v>0.8269503546099291</v>
+        <v>0.8270729978738484</v>
       </c>
       <c r="H424" t="n">
-        <v>5.546751773049645</v>
+        <v>5.547278525868179</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -32150,16 +32150,16 @@
         <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>-0.7707482269503547</v>
+        <v>-0.7702214741318212</v>
       </c>
       <c r="N424" t="n">
-        <v>0.7707482269503547</v>
+        <v>0.7702214741318212</v>
       </c>
       <c r="O424" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P424" t="n">
-        <v>-0.01458333333333339</v>
+        <v>-0.01483699503897906</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -32199,10 +32199,10 @@
         <v>8</v>
       </c>
       <c r="G425" t="n">
-        <v>0.8205673758865248</v>
+        <v>0.820694542877392</v>
       </c>
       <c r="H425" t="n">
-        <v>5.499336879432624</v>
+        <v>5.499883061658399</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -32221,16 +32221,16 @@
         <v>1</v>
       </c>
       <c r="M425" t="n">
-        <v>-0.7606631205673757</v>
+        <v>-0.7601169383416009</v>
       </c>
       <c r="N425" t="n">
-        <v>0.7606631205673757</v>
+        <v>0.7601169383416009</v>
       </c>
       <c r="O425" t="n">
         <v>-0.05750000000000011</v>
       </c>
       <c r="P425" t="n">
-        <v>-0.04741489361702111</v>
+        <v>-0.0473954642097798</v>
       </c>
       <c r="Q425" t="inlineStr">
         <is>
@@ -32270,10 +32270,10 @@
         <v>8</v>
       </c>
       <c r="G426" t="n">
-        <v>0.8177304964539007</v>
+        <v>0.817859673990078</v>
       </c>
       <c r="H426" t="n">
-        <v>5.485728723404256</v>
+        <v>5.486560949681078</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -32292,16 +32292,16 @@
         <v>1</v>
       </c>
       <c r="M426" t="n">
-        <v>-0.6442712765957443</v>
+        <v>-0.6434390503189222</v>
       </c>
       <c r="N426" t="n">
-        <v>0.6442712765957443</v>
+        <v>0.6434390503189222</v>
       </c>
       <c r="O426" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P426" t="n">
-        <v>-0.01360815602836851</v>
+        <v>-0.01332211197732125</v>
       </c>
       <c r="Q426" t="inlineStr">
         <is>
@@ -32341,10 +32341,10 @@
         <v>8</v>
       </c>
       <c r="G427" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.8086463501063076</v>
       </c>
       <c r="H427" t="n">
-        <v>5.38127659574468</v>
+        <v>5.381568036853295</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -32363,16 +32363,16 @@
         <v>1</v>
       </c>
       <c r="M427" t="n">
-        <v>-0.6087234042553202</v>
+        <v>-0.608431963146705</v>
       </c>
       <c r="N427" t="n">
-        <v>0.6087234042553202</v>
+        <v>0.608431963146705</v>
       </c>
       <c r="O427" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P427" t="n">
-        <v>-0.1044521276595756</v>
+        <v>-0.1049929128277824</v>
       </c>
       <c r="Q427" t="inlineStr">
         <is>
@@ -32412,10 +32412,10 @@
         <v>8</v>
       </c>
       <c r="G428" t="n">
-        <v>0.7879432624113475</v>
+        <v>0.7880935506732814</v>
       </c>
       <c r="H428" t="n">
-        <v>5.226324468085107</v>
+        <v>5.227292700212615</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -32434,16 +32434,16 @@
         <v>1</v>
       </c>
       <c r="M428" t="n">
-        <v>-0.4811755319148929</v>
+        <v>-0.4802072997873843</v>
       </c>
       <c r="N428" t="n">
-        <v>0.4811755319148929</v>
+        <v>0.4802072997873843</v>
       </c>
       <c r="O428" t="n">
         <v>-0.2825000000000006</v>
       </c>
       <c r="P428" t="n">
-        <v>-0.1549521276595733</v>
+        <v>-0.1542753366406799</v>
       </c>
       <c r="Q428" t="inlineStr">
         <is>
@@ -32483,10 +32483,10 @@
         <v>8</v>
       </c>
       <c r="G429" t="n">
-        <v>0.7702127659574468</v>
+        <v>0.7703756201275691</v>
       </c>
       <c r="H429" t="n">
-        <v>5.097579787234042</v>
+        <v>5.098454110559886</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
@@ -32505,16 +32505,16 @@
         <v>1</v>
       </c>
       <c r="M429" t="n">
-        <v>-0.4624202127659576</v>
+        <v>-0.4615458894401137</v>
       </c>
       <c r="N429" t="n">
-        <v>0.4624202127659576</v>
+        <v>0.4615458894401137</v>
       </c>
       <c r="O429" t="n">
         <v>-0.1475</v>
       </c>
       <c r="P429" t="n">
-        <v>-0.1287446808510646</v>
+        <v>-0.1288385896527293</v>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
@@ -32554,10 +32554,10 @@
         <v>8</v>
       </c>
       <c r="G430" t="n">
-        <v>0.7453900709219858</v>
+        <v>0.7455705173635719</v>
       </c>
       <c r="H430" t="n">
-        <v>4.946450354609929</v>
+        <v>4.947225372076542</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -32576,16 +32576,16 @@
         <v>1</v>
       </c>
       <c r="M430" t="n">
-        <v>-0.3935496453900704</v>
+        <v>-0.3927746279234583</v>
       </c>
       <c r="N430" t="n">
-        <v>0.3935496453900704</v>
+        <v>0.3927746279234583</v>
       </c>
       <c r="O430" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P430" t="n">
-        <v>-0.1511294326241126</v>
+        <v>-0.1512287384833444</v>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
@@ -32625,10 +32625,10 @@
         <v>8</v>
       </c>
       <c r="G431" t="n">
-        <v>0.7205673758865249</v>
+        <v>0.7200566973777462</v>
       </c>
       <c r="H431" t="n">
-        <v>4.824836879432625</v>
+        <v>4.822643515237421</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
@@ -32647,16 +32647,16 @@
         <v>1</v>
       </c>
       <c r="M431" t="n">
-        <v>-0.287663120567375</v>
+        <v>-0.2898564847625789</v>
       </c>
       <c r="N431" t="n">
-        <v>0.287663120567375</v>
+        <v>0.2898564847625789</v>
       </c>
       <c r="O431" t="n">
         <v>-0.2275</v>
       </c>
       <c r="P431" t="n">
-        <v>-0.1216134751773046</v>
+        <v>-0.1245818568391206</v>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
@@ -32696,10 +32696,10 @@
         <v>8</v>
       </c>
       <c r="G432" t="n">
-        <v>0.6964539007092199</v>
+        <v>0.6959603118355776</v>
       </c>
       <c r="H432" t="n">
-        <v>4.657202127659574</v>
+        <v>4.655612154500354</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -32718,16 +32718,16 @@
         <v>1</v>
       </c>
       <c r="M432" t="n">
-        <v>-0.3527978723404255</v>
+        <v>-0.3543878454996454</v>
       </c>
       <c r="N432" t="n">
-        <v>0.3527978723404255</v>
+        <v>0.3543878454996454</v>
       </c>
       <c r="O432" t="n">
         <v>-0.1025</v>
       </c>
       <c r="P432" t="n">
-        <v>-0.1676347517730505</v>
+        <v>-0.1670313607370666</v>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
@@ -32767,10 +32767,10 @@
         <v>8</v>
       </c>
       <c r="G433" t="n">
-        <v>0.6865248226950355</v>
+        <v>0.6860382707299787</v>
       </c>
       <c r="H433" t="n">
-        <v>4.627936170212766</v>
+        <v>4.624801559177888</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -32789,16 +32789,16 @@
         <v>1</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.2120638297872341</v>
+        <v>-0.2151984408221121</v>
       </c>
       <c r="N433" t="n">
-        <v>0.2120638297872341</v>
+        <v>0.2151984408221121</v>
       </c>
       <c r="O433" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P433" t="n">
-        <v>-0.0292659574468086</v>
+        <v>-0.03081059532246666</v>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
@@ -32838,10 +32838,10 @@
         <v>8</v>
       </c>
       <c r="G434" t="n">
-        <v>0.6914893617021277</v>
+        <v>0.6909992912827781</v>
       </c>
       <c r="H434" t="n">
-        <v>4.643297872340425</v>
+        <v>4.641894637373022</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -32860,16 +32860,16 @@
         <v>1</v>
       </c>
       <c r="M434" t="n">
-        <v>-0.07670212765957451</v>
+        <v>-0.07810536262697809</v>
       </c>
       <c r="N434" t="n">
-        <v>0.07670212765957451</v>
+        <v>0.07810536262697809</v>
       </c>
       <c r="O434" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P434" t="n">
-        <v>0.01536170212765953</v>
+        <v>0.01709307819513395</v>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
@@ -32909,10 +32909,10 @@
         <v>8</v>
       </c>
       <c r="G435" t="n">
-        <v>0.7106382978723405</v>
+        <v>0.7101346562721474</v>
       </c>
       <c r="H435" t="n">
-        <v>4.754382978723404</v>
+        <v>4.750056697377746</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -32931,16 +32931,16 @@
         <v>1</v>
       </c>
       <c r="M435" t="n">
-        <v>0.1943829787234046</v>
+        <v>0.1900566973777469</v>
       </c>
       <c r="N435" t="n">
-        <v>0.1943829787234046</v>
+        <v>0.1900566973777469</v>
       </c>
       <c r="O435" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P435" t="n">
-        <v>0.111085106382979</v>
+        <v>0.1081620600047248</v>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
@@ -32980,10 +32980,10 @@
         <v>8</v>
       </c>
       <c r="G436" t="n">
-        <v>0.7262411347517731</v>
+        <v>0.7257264351523742</v>
       </c>
       <c r="H436" t="n">
-        <v>4.849205673758865</v>
+        <v>4.846995038979447</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -33002,16 +33002,16 @@
         <v>1</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4592056737588655</v>
+        <v>0.4569950389794473</v>
       </c>
       <c r="N436" t="n">
-        <v>0.4592056737588655</v>
+        <v>0.4569950389794473</v>
       </c>
       <c r="O436" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P436" t="n">
-        <v>0.09482269503546092</v>
+        <v>0.09693834160170045</v>
       </c>
       <c r="Q436" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>8</v>
       </c>
       <c r="G437" t="n">
-        <v>0.8226950354609929</v>
+        <v>0.8228206945428774</v>
       </c>
       <c r="H437" t="n">
-        <v>3.482765957446808</v>
+        <v>3.48615875265769</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -33073,10 +33073,10 @@
         <v>1</v>
       </c>
       <c r="M437" t="n">
-        <v>-0.9572340425531927</v>
+        <v>-0.9538412473423099</v>
       </c>
       <c r="N437" t="n">
-        <v>0.9572340425531927</v>
+        <v>0.9538412473423099</v>
       </c>
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
@@ -33116,10 +33116,10 @@
         <v>8</v>
       </c>
       <c r="G438" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.8086463501063076</v>
       </c>
       <c r="H438" t="n">
-        <v>3.34595744680851</v>
+        <v>3.346690290574061</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -33138,16 +33138,16 @@
         <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>-0.8965425531914901</v>
+        <v>-0.8958097094259396</v>
       </c>
       <c r="N438" t="n">
-        <v>0.8965425531914901</v>
+        <v>0.8958097094259396</v>
       </c>
       <c r="O438" t="n">
         <v>-0.1974999999999998</v>
       </c>
       <c r="P438" t="n">
-        <v>-0.1368085106382972</v>
+        <v>-0.1394684620836295</v>
       </c>
       <c r="Q438" t="inlineStr">
         <is>
@@ -33187,10 +33187,10 @@
         <v>8</v>
       </c>
       <c r="G439" t="n">
-        <v>0.799290780141844</v>
+        <v>0.7994330262225372</v>
       </c>
       <c r="H439" t="n">
-        <v>3.293085106382978</v>
+        <v>3.29346917080085</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -33209,16 +33209,16 @@
         <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>-0.8169148936170219</v>
+        <v>-0.81653082919915</v>
       </c>
       <c r="N439" t="n">
-        <v>0.8169148936170219</v>
+        <v>0.81653082919915</v>
       </c>
       <c r="O439" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P439" t="n">
-        <v>-0.05287234042553202</v>
+        <v>-0.05322111977321065</v>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
@@ -33258,10 +33258,10 @@
         <v>8</v>
       </c>
       <c r="G440" t="n">
-        <v>0.8035460992907801</v>
+        <v>0.8036853295535081</v>
       </c>
       <c r="H440" t="n">
-        <v>3.309148936170213</v>
+        <v>3.309900779588944</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -33280,16 +33280,16 @@
         <v>1</v>
       </c>
       <c r="M440" t="n">
-        <v>-0.6608510638297873</v>
+        <v>-0.6600992204110563</v>
       </c>
       <c r="N440" t="n">
-        <v>0.6608510638297873</v>
+        <v>0.6600992204110563</v>
       </c>
       <c r="O440" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P440" t="n">
-        <v>0.01606382978723442</v>
+        <v>0.01643160878809358</v>
       </c>
       <c r="Q440" t="inlineStr">
         <is>
@@ -33329,10 +33329,10 @@
         <v>8</v>
       </c>
       <c r="G441" t="n">
-        <v>0.8212765957446808</v>
+        <v>0.8214032600992204</v>
       </c>
       <c r="H441" t="n">
-        <v>3.459787234042553</v>
+        <v>3.46115520907158</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -33351,16 +33351,16 @@
         <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>-0.3702127659574472</v>
+        <v>-0.3688447909284198</v>
       </c>
       <c r="N441" t="n">
-        <v>0.3702127659574472</v>
+        <v>0.3688447909284198</v>
       </c>
       <c r="O441" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P441" t="n">
-        <v>0.15063829787234</v>
+        <v>0.1512544294826363</v>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
@@ -33400,10 +33400,10 @@
         <v>8</v>
       </c>
       <c r="G442" t="n">
-        <v>0.8375886524822695</v>
+        <v>0.8377037562012757</v>
       </c>
       <c r="H442" t="n">
-        <v>3.643971631205674</v>
+        <v>3.644800377982519</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -33422,16 +33422,16 @@
         <v>1</v>
       </c>
       <c r="M442" t="n">
-        <v>-0.01602836879432568</v>
+        <v>-0.01519962201748148</v>
       </c>
       <c r="N442" t="n">
-        <v>0.01602836879432568</v>
+        <v>0.01519962201748148</v>
       </c>
       <c r="O442" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P442" t="n">
-        <v>0.1841843971631216</v>
+        <v>0.1836451689109384</v>
       </c>
       <c r="Q442" t="inlineStr">
         <is>
@@ -33471,10 +33471,10 @@
         <v>8</v>
       </c>
       <c r="G443" t="n">
-        <v>0.8475177304964538</v>
+        <v>0.8476257973068746</v>
       </c>
       <c r="H443" t="n">
-        <v>3.720797872340426</v>
+        <v>3.721089652728562</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -33493,16 +33493,16 @@
         <v>1</v>
       </c>
       <c r="M443" t="n">
-        <v>0.08079787234042568</v>
+        <v>0.08108965272856139</v>
       </c>
       <c r="N443" t="n">
-        <v>0.08079787234042568</v>
+        <v>0.08108965272856139</v>
       </c>
       <c r="O443" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P443" t="n">
-        <v>0.07682624113475134</v>
+        <v>0.07628927474604286</v>
       </c>
       <c r="Q443" t="inlineStr">
         <is>
@@ -33542,10 +33542,10 @@
         <v>8</v>
       </c>
       <c r="G444" t="n">
-        <v>0.8553191489361702</v>
+        <v>0.8554216867469879</v>
       </c>
       <c r="H444" t="n">
-        <v>3.753723404255319</v>
+        <v>3.754277108433735</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -33564,16 +33564,16 @@
         <v>1</v>
       </c>
       <c r="M444" t="n">
-        <v>0.1537234042553188</v>
+        <v>0.1542771084337344</v>
       </c>
       <c r="N444" t="n">
-        <v>0.1537234042553188</v>
+        <v>0.1542771084337344</v>
       </c>
       <c r="O444" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P444" t="n">
-        <v>0.03292553191489311</v>
+        <v>0.03318745570517301</v>
       </c>
       <c r="Q444" t="inlineStr">
         <is>
@@ -33613,10 +33613,10 @@
         <v>8</v>
       </c>
       <c r="G445" t="n">
-        <v>0.8581560283687943</v>
+        <v>0.8582565556343019</v>
       </c>
       <c r="H445" t="n">
-        <v>3.76654255319149</v>
+        <v>3.767085400425231</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -33635,16 +33635,16 @@
         <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>0.2340425531914896</v>
+        <v>0.2345854004252304</v>
       </c>
       <c r="N445" t="n">
-        <v>0.2340425531914896</v>
+        <v>0.2345854004252304</v>
       </c>
       <c r="O445" t="n">
         <v>-0.06749999999999989</v>
       </c>
       <c r="P445" t="n">
-        <v>0.01281914893617087</v>
+        <v>0.01280829199149602</v>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
@@ -33684,10 +33684,10 @@
         <v>8</v>
       </c>
       <c r="G446" t="n">
-        <v>0.850354609929078</v>
+        <v>0.8504606661941885</v>
       </c>
       <c r="H446" t="n">
-        <v>3.731914893617021</v>
+        <v>3.732487597448618</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -33706,16 +33706,16 @@
         <v>1</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2919148936170211</v>
+        <v>0.2924875974486176</v>
       </c>
       <c r="N446" t="n">
-        <v>0.2919148936170211</v>
+        <v>0.2924875974486176</v>
       </c>
       <c r="O446" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P446" t="n">
-        <v>-0.03462765957446878</v>
+        <v>-0.03459780297661297</v>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
@@ -33755,10 +33755,10 @@
         <v>8</v>
       </c>
       <c r="G447" t="n">
-        <v>0.8397163120567376</v>
+        <v>0.8398299078667611</v>
       </c>
       <c r="H447" t="n">
-        <v>3.659290780141844</v>
+        <v>3.660285258681786</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -33777,16 +33777,16 @@
         <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>0.3692907801418444</v>
+        <v>0.3702852586817862</v>
       </c>
       <c r="N447" t="n">
-        <v>0.3692907801418444</v>
+        <v>0.3702852586817862</v>
       </c>
       <c r="O447" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.07262411347517661</v>
+        <v>-0.07220233876683135</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
@@ -33826,10 +33826,10 @@
         <v>8</v>
       </c>
       <c r="G448" t="n">
-        <v>0.8148936170212766</v>
+        <v>0.815024805102764</v>
       </c>
       <c r="H448" t="n">
-        <v>3.415212765957447</v>
+        <v>3.415566973777463</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -33848,16 +33848,16 @@
         <v>1</v>
       </c>
       <c r="M448" t="n">
-        <v>0.235212765957447</v>
+        <v>0.2355669737774626</v>
       </c>
       <c r="N448" t="n">
-        <v>0.235212765957447</v>
+        <v>0.2355669737774626</v>
       </c>
       <c r="O448" t="n">
         <v>-0.1099999999999999</v>
       </c>
       <c r="P448" t="n">
-        <v>-0.2440780141843972</v>
+        <v>-0.2447182849043235</v>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
@@ -33897,10 +33897,10 @@
         <v>8</v>
       </c>
       <c r="G449" t="n">
-        <v>0.7829787234042553</v>
+        <v>0.7831325301204819</v>
       </c>
       <c r="H449" t="n">
-        <v>3.213085106382979</v>
+        <v>3.213915662650602</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -33919,16 +33919,16 @@
         <v>1</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1130851063829788</v>
+        <v>0.1139156626506024</v>
       </c>
       <c r="N449" t="n">
-        <v>0.1130851063829788</v>
+        <v>0.1139156626506024</v>
       </c>
       <c r="O449" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P449" t="n">
-        <v>-0.2021276595744683</v>
+        <v>-0.2016513111268603</v>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
@@ -33968,10 +33968,10 @@
         <v>8</v>
       </c>
       <c r="G450" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.7661233167965982</v>
       </c>
       <c r="H450" t="n">
-        <v>3.102340425531915</v>
+        <v>3.10413182140326</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -33990,16 +33990,16 @@
         <v>1</v>
       </c>
       <c r="M450" t="n">
-        <v>0.002340425531914825</v>
+        <v>0.004131821403260183</v>
       </c>
       <c r="N450" t="n">
-        <v>0.002340425531914825</v>
+        <v>0.004131821403260183</v>
       </c>
       <c r="O450" t="n">
         <v>0</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.1107446808510639</v>
+        <v>-0.1097838412473422</v>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
@@ -35311,10 +35311,10 @@
         <v>8</v>
       </c>
       <c r="G469" t="n">
-        <v>0.8425531914893617</v>
+        <v>0.8426647767540751</v>
       </c>
       <c r="H469" t="n">
-        <v>8.543489361702129</v>
+        <v>8.545931963146705</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -35333,16 +35333,16 @@
         <v>1</v>
       </c>
       <c r="M469" t="n">
-        <v>-0.6965106382978714</v>
+        <v>-0.6940680368532952</v>
       </c>
       <c r="N469" t="n">
-        <v>0.6965106382978714</v>
+        <v>0.6940680368532952</v>
       </c>
       <c r="O469" t="n">
         <v>-0.08999999999999986</v>
       </c>
       <c r="P469" t="n">
-        <v>0.2445194948485909</v>
+        <v>0.2469620962931671</v>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
@@ -35382,10 +35382,10 @@
         <v>8</v>
       </c>
       <c r="G470" t="n">
-        <v>0.825531914893617</v>
+        <v>0.8256555634301913</v>
       </c>
       <c r="H470" t="n">
-        <v>8.276851063829787</v>
+        <v>8.278327427356484</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -35404,16 +35404,16 @@
         <v>1</v>
       </c>
       <c r="M470" t="n">
-        <v>-0.7731489361702142</v>
+        <v>-0.7716725726435172</v>
       </c>
       <c r="N470" t="n">
-        <v>0.7731489361702142</v>
+        <v>0.7716725726435172</v>
       </c>
       <c r="O470" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P470" t="n">
-        <v>-0.2666382978723423</v>
+        <v>-0.2676045357902215</v>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -35453,10 +35453,10 @@
         <v>8</v>
       </c>
       <c r="G471" t="n">
-        <v>0.8063829787234043</v>
+        <v>0.8065201984408221</v>
       </c>
       <c r="H471" t="n">
-        <v>7.986425531914894</v>
+        <v>7.989702338766833</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -35475,16 +35475,16 @@
         <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.9235744680851061</v>
+        <v>-0.9202976612331675</v>
       </c>
       <c r="N471" t="n">
-        <v>0.9235744680851061</v>
+        <v>0.9202976612331675</v>
       </c>
       <c r="O471" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P471" t="n">
-        <v>-0.2904255319148925</v>
+        <v>-0.2886250885896509</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
@@ -35524,10 +35524,10 @@
         <v>8</v>
       </c>
       <c r="G472" t="n">
-        <v>0.7943262411347518</v>
+        <v>0.7944720056697377</v>
       </c>
       <c r="H472" t="n">
-        <v>7.892127659574468</v>
+        <v>7.892997873848334</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -35546,16 +35546,16 @@
         <v>1</v>
       </c>
       <c r="M472" t="n">
-        <v>-0.8778723404255313</v>
+        <v>-0.8770021261516652</v>
       </c>
       <c r="N472" t="n">
-        <v>0.8778723404255313</v>
+        <v>0.8770021261516652</v>
       </c>
       <c r="O472" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P472" t="n">
-        <v>-0.09429787234042575</v>
+        <v>-0.09670446491849827</v>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
@@ -35595,10 +35595,10 @@
         <v>8</v>
       </c>
       <c r="G473" t="n">
-        <v>0.7921985815602837</v>
+        <v>0.7923458540042523</v>
       </c>
       <c r="H473" t="n">
-        <v>7.868851063829787</v>
+        <v>7.870609496810772</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -35617,16 +35617,16 @@
         <v>1</v>
       </c>
       <c r="M473" t="n">
-        <v>-0.711148936170213</v>
+        <v>-0.709390503189228</v>
       </c>
       <c r="N473" t="n">
-        <v>0.711148936170213</v>
+        <v>0.709390503189228</v>
       </c>
       <c r="O473" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P473" t="n">
-        <v>-0.02327659574468122</v>
+        <v>-0.02238837703756236</v>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
@@ -35666,10 +35666,10 @@
         <v>8</v>
       </c>
       <c r="G474" t="n">
-        <v>0.8028368794326242</v>
+        <v>0.8029766123316796</v>
       </c>
       <c r="H474" t="n">
-        <v>7.927645390070921</v>
+        <v>7.927923458540042</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -35688,16 +35688,16 @@
         <v>1</v>
       </c>
       <c r="M474" t="n">
-        <v>-0.5223546099290779</v>
+        <v>-0.5220765414599571</v>
       </c>
       <c r="N474" t="n">
-        <v>0.5223546099290779</v>
+        <v>0.5220765414599571</v>
       </c>
       <c r="O474" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P474" t="n">
-        <v>0.05879432624113434</v>
+        <v>0.05731396172927017</v>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
@@ -35737,10 +35737,10 @@
         <v>8</v>
       </c>
       <c r="G475" t="n">
-        <v>0.8156028368794326</v>
+        <v>0.8157335223245925</v>
       </c>
       <c r="H475" t="n">
-        <v>8.193049645390071</v>
+        <v>8.193309709425938</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -35759,16 +35759,16 @@
         <v>1</v>
       </c>
       <c r="M475" t="n">
-        <v>-0.1269503546099298</v>
+        <v>-0.1266902905740626</v>
       </c>
       <c r="N475" t="n">
-        <v>0.1269503546099298</v>
+        <v>0.1266902905740626</v>
       </c>
       <c r="O475" t="n">
         <v>-0.129999999999999</v>
       </c>
       <c r="P475" t="n">
-        <v>0.2654042553191491</v>
+        <v>0.2653862508858955</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
@@ -35808,10 +35808,10 @@
         <v>8</v>
       </c>
       <c r="G476" t="n">
-        <v>0.8276595744680851</v>
+        <v>0.8277817150956768</v>
       </c>
       <c r="H476" t="n">
-        <v>8.302255319148935</v>
+        <v>8.30371367824238</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -35830,16 +35830,16 @@
         <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>0.04225531914893565</v>
+        <v>0.04371367824237993</v>
       </c>
       <c r="N476" t="n">
-        <v>0.04225531914893565</v>
+        <v>0.04371367824237993</v>
       </c>
       <c r="O476" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P476" t="n">
-        <v>0.1092056737588649</v>
+        <v>0.110403968816442</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
@@ -35879,10 +35879,10 @@
         <v>8</v>
       </c>
       <c r="G477" t="n">
-        <v>0.8361702127659575</v>
+        <v>0.8362863217576187</v>
       </c>
       <c r="H477" t="n">
-        <v>8.457957446808511</v>
+        <v>8.458419560595322</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -35901,16 +35901,16 @@
         <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2579574468085113</v>
+        <v>0.258419560595323</v>
       </c>
       <c r="N477" t="n">
-        <v>0.2579574468085113</v>
+        <v>0.258419560595323</v>
       </c>
       <c r="O477" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P477" t="n">
-        <v>0.1557021276595751</v>
+        <v>0.1547058823529426</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -35950,10 +35950,10 @@
         <v>8</v>
       </c>
       <c r="G478" t="n">
-        <v>0.8368794326241135</v>
+        <v>0.8369950389794472</v>
       </c>
       <c r="H478" t="n">
-        <v>8.460780141843971</v>
+        <v>8.4612402551382</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -35972,16 +35972,16 @@
         <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>0.4107801418439703</v>
+        <v>0.4112402551381997</v>
       </c>
       <c r="N478" t="n">
-        <v>0.4107801418439703</v>
+        <v>0.4112402551381997</v>
       </c>
       <c r="O478" t="n">
         <v>-0.1499999999999986</v>
       </c>
       <c r="P478" t="n">
-        <v>0.002822695035460399</v>
+        <v>0.002820694542878144</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -36021,10 +36021,10 @@
         <v>8</v>
       </c>
       <c r="G479" t="n">
-        <v>0.8319148936170213</v>
+        <v>0.8320340184266478</v>
       </c>
       <c r="H479" t="n">
-        <v>8.391638297872341</v>
+        <v>8.394720056697379</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -36043,16 +36043,16 @@
         <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>0.4716382978723406</v>
+        <v>0.4747200566973788</v>
       </c>
       <c r="N479" t="n">
-        <v>0.4716382978723406</v>
+        <v>0.4747200566973788</v>
       </c>
       <c r="O479" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P479" t="n">
-        <v>-0.06914184397163048</v>
+        <v>-0.06652019844082169</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -36092,10 +36092,10 @@
         <v>8</v>
       </c>
       <c r="G480" t="n">
-        <v>0.8191489361702128</v>
+        <v>0.8192771084337349</v>
       </c>
       <c r="H480" t="n">
-        <v>8.20063829787234</v>
+        <v>8.202168674698795</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -36114,16 +36114,16 @@
         <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0.4606382978723396</v>
+        <v>0.4621686746987947</v>
       </c>
       <c r="N480" t="n">
-        <v>0.4606382978723396</v>
+        <v>0.4621686746987947</v>
       </c>
       <c r="O480" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P480" t="n">
-        <v>-0.1910000000000007</v>
+        <v>-0.1925513819985838</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -36266,34 +36266,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.765</v>
+        <v>7.736</v>
       </c>
       <c r="G2" t="n">
-        <v>7.837</v>
+        <v>7.822</v>
       </c>
       <c r="H2" t="n">
-        <v>7.922</v>
+        <v>7.921</v>
       </c>
       <c r="I2" t="n">
-        <v>7.922</v>
+        <v>7.915</v>
       </c>
       <c r="J2" t="n">
-        <v>7.775</v>
+        <v>7.76</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.147</v>
+        <v>-0.155</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -36312,10 +36312,10 @@
         <v>5.829</v>
       </c>
       <c r="P2" t="n">
-        <v>5.809</v>
+        <v>5.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.809</v>
+        <v>5.81</v>
       </c>
       <c r="R2" t="n">
         <v>-1.023</v>
@@ -36342,34 +36342,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.62</v>
+        <v>5.603</v>
       </c>
       <c r="G3" t="n">
-        <v>5.741</v>
+        <v>5.717</v>
       </c>
       <c r="H3" t="n">
-        <v>5.917</v>
+        <v>5.916</v>
       </c>
       <c r="I3" t="n">
-        <v>5.917</v>
+        <v>5.897</v>
       </c>
       <c r="J3" t="n">
-        <v>5.622</v>
+        <v>5.61</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.295</v>
+        <v>-0.287</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -36385,16 +36385,16 @@
         <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>0.488</v>
+        <v>0.489</v>
       </c>
       <c r="P3" t="n">
         <v>0.337</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.315</v>
+        <v>0.316</v>
       </c>
       <c r="R3" t="n">
-        <v>0.571</v>
+        <v>0.57</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -36418,34 +36418,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.365</v>
+        <v>4.169</v>
       </c>
       <c r="G4" t="n">
-        <v>4.578</v>
+        <v>4.521</v>
       </c>
       <c r="H4" t="n">
-        <v>5.664</v>
+        <v>5.665</v>
       </c>
       <c r="I4" t="n">
-        <v>4.769</v>
+        <v>4.731</v>
       </c>
       <c r="J4" t="n">
-        <v>4.702</v>
+        <v>4.62</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.067</v>
+        <v>-0.111</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -36494,34 +36494,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.793</v>
+        <v>10.784</v>
       </c>
       <c r="G5" t="n">
-        <v>11.28</v>
+        <v>11.312</v>
       </c>
       <c r="H5" t="n">
-        <v>11.775</v>
+        <v>11.811</v>
       </c>
       <c r="I5" t="n">
-        <v>11.37</v>
+        <v>11.206</v>
       </c>
       <c r="J5" t="n">
-        <v>11.739</v>
+        <v>11.778</v>
       </c>
       <c r="K5" t="n">
-        <v>0.369</v>
+        <v>0.572</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -36537,16 +36537,16 @@
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>4.21</v>
+        <v>4.211</v>
       </c>
       <c r="P5" t="n">
-        <v>3.914</v>
+        <v>3.915</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.914</v>
+        <v>3.915</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.723</v>
+        <v>-1.724</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -36570,34 +36570,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>54.731</v>
+        <v>53.888</v>
       </c>
       <c r="G6" t="n">
-        <v>85.8</v>
+        <v>81.90300000000001</v>
       </c>
       <c r="H6" t="n">
         <v>113.668</v>
       </c>
       <c r="I6" t="n">
-        <v>107.4</v>
+        <v>71.45399999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>109.616</v>
+        <v>110.131</v>
       </c>
       <c r="K6" t="n">
-        <v>2.216</v>
+        <v>38.677</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -36613,13 +36613,13 @@
         <v>13</v>
       </c>
       <c r="O6" t="n">
-        <v>92.01000000000001</v>
+        <v>92.012</v>
       </c>
       <c r="P6" t="n">
-        <v>88.68000000000001</v>
+        <v>88.682</v>
       </c>
       <c r="Q6" t="n">
-        <v>88.68000000000001</v>
+        <v>88.682</v>
       </c>
       <c r="R6" t="n">
         <v>-3.322</v>
@@ -36646,34 +36646,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.809</v>
+        <v>7.746</v>
       </c>
       <c r="G7" t="n">
-        <v>8.092000000000001</v>
+        <v>8.052</v>
       </c>
       <c r="H7" t="n">
-        <v>8.269</v>
+        <v>8.268000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.269</v>
+        <v>8.247999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>7.809</v>
+        <v>7.762</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.46</v>
+        <v>-0.486</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -36722,34 +36722,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.682</v>
+        <v>6.487</v>
       </c>
       <c r="G8" t="n">
-        <v>7.259</v>
+        <v>7.158</v>
       </c>
       <c r="H8" t="n">
-        <v>7.702</v>
+        <v>7.7</v>
       </c>
       <c r="I8" t="n">
-        <v>7.702</v>
+        <v>7.574</v>
       </c>
       <c r="J8" t="n">
-        <v>6.703</v>
+        <v>6.548</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.999</v>
+        <v>-1.025</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>0.475</v>
       </c>
       <c r="P8" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
       <c r="Q8" t="n">
         <v>0.394</v>
@@ -36798,12 +36798,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -36813,19 +36813,19 @@
         <v>5.014</v>
       </c>
       <c r="G9" t="n">
-        <v>5.298</v>
+        <v>5.319</v>
       </c>
       <c r="H9" t="n">
-        <v>5.608</v>
+        <v>5.61</v>
       </c>
       <c r="I9" t="n">
-        <v>5.025</v>
+        <v>5.017</v>
       </c>
       <c r="J9" t="n">
-        <v>5.097</v>
+        <v>5.142</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -36844,13 +36844,13 @@
         <v>0.513</v>
       </c>
       <c r="P9" t="n">
-        <v>0.423</v>
+        <v>0.424</v>
       </c>
       <c r="Q9" t="n">
         <v>0.26</v>
       </c>
       <c r="R9" t="n">
-        <v>0.216</v>
+        <v>0.215</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -36874,34 +36874,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.417</v>
+        <v>5.41</v>
       </c>
       <c r="G10" t="n">
-        <v>5.486</v>
+        <v>5.465</v>
       </c>
       <c r="H10" t="n">
-        <v>5.698</v>
+        <v>5.697</v>
       </c>
       <c r="I10" t="n">
-        <v>5.698</v>
+        <v>5.625</v>
       </c>
       <c r="J10" t="n">
         <v>5.439</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.258</v>
+        <v>-0.186</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -36920,10 +36920,10 @@
         <v>1.823</v>
       </c>
       <c r="P10" t="n">
-        <v>1.789</v>
+        <v>1.788</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.789</v>
+        <v>-1.788</v>
       </c>
       <c r="R10" t="n">
         <v>0.758</v>
@@ -36950,34 +36950,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.144</v>
+        <v>2.886</v>
       </c>
       <c r="G11" t="n">
-        <v>4.298</v>
+        <v>4.158</v>
       </c>
       <c r="H11" t="n">
         <v>8.430999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>5.069</v>
+        <v>4.886</v>
       </c>
       <c r="J11" t="n">
-        <v>5.583</v>
+        <v>6.337</v>
       </c>
       <c r="K11" t="n">
-        <v>0.515</v>
+        <v>1.451</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -36996,13 +36996,13 @@
         <v>2.52</v>
       </c>
       <c r="P11" t="n">
-        <v>2.036</v>
+        <v>2.035</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.036</v>
+        <v>2.035</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.552</v>
+        <v>-0.553</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -37026,34 +37026,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.074</v>
+        <v>6.039</v>
       </c>
       <c r="G12" t="n">
-        <v>6.166</v>
+        <v>6.14</v>
       </c>
       <c r="H12" t="n">
-        <v>6.284</v>
+        <v>6.281</v>
       </c>
       <c r="I12" t="n">
-        <v>6.284</v>
+        <v>6.276</v>
       </c>
       <c r="J12" t="n">
-        <v>6.076</v>
+        <v>6.05</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.208</v>
+        <v>-0.227</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -37072,13 +37072,13 @@
         <v>0.484</v>
       </c>
       <c r="P12" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.241</v>
+        <v>-0.24</v>
       </c>
       <c r="R12" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -37102,34 +37102,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.664999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="G13" t="n">
-        <v>9.968</v>
+        <v>9.929</v>
       </c>
       <c r="H13" t="n">
         <v>10.189</v>
       </c>
       <c r="I13" t="n">
-        <v>10.169</v>
+        <v>10.184</v>
       </c>
       <c r="J13" t="n">
-        <v>9.786</v>
+        <v>9.736000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.383</v>
+        <v>-0.448</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -37178,34 +37178,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.822</v>
+        <v>5.816</v>
       </c>
       <c r="G14" t="n">
-        <v>5.92</v>
+        <v>5.892</v>
       </c>
       <c r="H14" t="n">
-        <v>6.169</v>
+        <v>6.168</v>
       </c>
       <c r="I14" t="n">
-        <v>6.169</v>
+        <v>6.07</v>
       </c>
       <c r="J14" t="n">
-        <v>5.913</v>
+        <v>5.868</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.256</v>
+        <v>-0.202</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -37221,16 +37221,16 @@
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>0.413</v>
+        <v>0.414</v>
       </c>
       <c r="P14" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.108</v>
+        <v>0.109</v>
       </c>
       <c r="R14" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -37254,34 +37254,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.555</v>
+        <v>6.541</v>
       </c>
       <c r="G15" t="n">
-        <v>6.594</v>
+        <v>6.586</v>
       </c>
       <c r="H15" t="n">
-        <v>6.649</v>
+        <v>6.648</v>
       </c>
       <c r="I15" t="n">
-        <v>6.649</v>
+        <v>6.632</v>
       </c>
       <c r="J15" t="n">
-        <v>6.557</v>
+        <v>6.544</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.092</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -37300,13 +37300,13 @@
         <v>1.626</v>
       </c>
       <c r="P15" t="n">
-        <v>1.507</v>
+        <v>1.506</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.507</v>
+        <v>-1.506</v>
       </c>
       <c r="R15" t="n">
-        <v>0.286</v>
+        <v>0.285</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -37330,34 +37330,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.26</v>
+        <v>4.212</v>
       </c>
       <c r="G16" t="n">
-        <v>5.406</v>
+        <v>5.311</v>
       </c>
       <c r="H16" t="n">
-        <v>7.217</v>
+        <v>7.488</v>
       </c>
       <c r="I16" t="n">
-        <v>5.997</v>
+        <v>5.591</v>
       </c>
       <c r="J16" t="n">
-        <v>6.236</v>
+        <v>6.766</v>
       </c>
       <c r="K16" t="n">
-        <v>0.239</v>
+        <v>1.175</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -37376,13 +37376,13 @@
         <v>1.726</v>
       </c>
       <c r="P16" t="n">
-        <v>1.539</v>
+        <v>1.538</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.539</v>
+        <v>1.538</v>
       </c>
       <c r="R16" t="n">
-        <v>0.231</v>
+        <v>0.23</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -37406,34 +37406,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.065</v>
+        <v>4.004</v>
       </c>
       <c r="G17" t="n">
-        <v>4.576</v>
+        <v>4.525</v>
       </c>
       <c r="H17" t="n">
-        <v>4.909</v>
+        <v>4.932</v>
       </c>
       <c r="I17" t="n">
-        <v>4.892</v>
+        <v>4.921</v>
       </c>
       <c r="J17" t="n">
-        <v>4.109</v>
+        <v>4.05</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.783</v>
+        <v>-0.871</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>0.338</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.074</v>
+        <v>-0.075</v>
       </c>
       <c r="R17" t="n">
         <v>0.835</v>
@@ -37482,34 +37482,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.591</v>
+        <v>2.582</v>
       </c>
       <c r="G18" t="n">
-        <v>2.748</v>
+        <v>2.713</v>
       </c>
       <c r="H18" t="n">
-        <v>3.028</v>
+        <v>3.026</v>
       </c>
       <c r="I18" t="n">
-        <v>3.028</v>
+        <v>2.948</v>
       </c>
       <c r="J18" t="n">
         <v>2.591</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.437</v>
+        <v>-0.357</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -37531,10 +37531,10 @@
         <v>0.371</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.16</v>
+        <v>-0.159</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.111</v>
+        <v>-0.11</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -37558,34 +37558,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.814</v>
+        <v>5.782</v>
       </c>
       <c r="G19" t="n">
-        <v>6.207</v>
+        <v>6.061</v>
       </c>
       <c r="H19" t="n">
-        <v>7.675</v>
+        <v>7.669</v>
       </c>
       <c r="I19" t="n">
-        <v>7.675</v>
+        <v>6.974</v>
       </c>
       <c r="J19" t="n">
-        <v>5.883</v>
+        <v>5.873</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.792</v>
+        <v>-1.101</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -37601,16 +37601,16 @@
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>0.843</v>
+        <v>0.842</v>
       </c>
       <c r="P19" t="n">
         <v>0.778</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.669</v>
+        <v>-0.668</v>
       </c>
       <c r="R19" t="n">
-        <v>0.509</v>
+        <v>0.508</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -486,7 +486,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>299934</v>
+        <v>299952</v>
       </c>
       <c r="E2" t="n">
         <v>151106</v>
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -683,28 +683,28 @@
         <v>9.765000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>7.751</v>
+        <v>7.753</v>
       </c>
       <c r="J2" t="n">
         <v>-1.52</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.014</v>
+        <v>-2.012</v>
       </c>
       <c r="L2" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
       <c r="M2" t="n">
         <v>0.395</v>
       </c>
       <c r="N2" t="n">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="O2" t="n">
-        <v>0.867</v>
+        <v>0.866</v>
       </c>
       <c r="P2" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="Q2" t="n">
         <v>0.827</v>
@@ -765,13 +765,13 @@
         <v>7.883</v>
       </c>
       <c r="I3" t="n">
-        <v>5.824</v>
+        <v>5.826</v>
       </c>
       <c r="J3" t="n">
         <v>-2.472</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.058</v>
+        <v>-2.057</v>
       </c>
       <c r="L3" t="n">
         <v>-1.788</v>
@@ -786,7 +786,7 @@
         <v>0.89</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.609</v>
+        <v>-4.607</v>
       </c>
       <c r="Q3" t="n">
         <v>0.758</v>
@@ -847,13 +847,13 @@
         <v>7.691</v>
       </c>
       <c r="I4" t="n">
-        <v>4.847</v>
+        <v>4.845</v>
       </c>
       <c r="J4" t="n">
         <v>-3.405</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.844</v>
+        <v>-2.846</v>
       </c>
       <c r="L4" t="n">
         <v>-0.075</v>
@@ -862,16 +862,16 @@
         <v>0.338</v>
       </c>
       <c r="N4" t="n">
-        <v>0.406</v>
+        <v>0.405</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="P4" t="n">
         <v>0.833</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.835</v>
+        <v>0.834</v>
       </c>
       <c r="R4" t="n">
         <v>44.828</v>
@@ -929,19 +929,19 @@
         <v>7.178</v>
       </c>
       <c r="I5" t="n">
-        <v>5.965</v>
+        <v>5.967</v>
       </c>
       <c r="J5" t="n">
         <v>-2.275</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.212</v>
+        <v>-1.211</v>
       </c>
       <c r="L5" t="n">
         <v>0.316</v>
       </c>
       <c r="M5" t="n">
-        <v>0.337</v>
+        <v>0.338</v>
       </c>
       <c r="N5" t="n">
         <v>0.489</v>
@@ -950,7 +950,7 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="Q5" t="n">
         <v>0.57</v>
@@ -1093,16 +1093,16 @@
         <v>9.374000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.202</v>
+        <v>8.204000000000001</v>
       </c>
       <c r="J7" t="n">
         <v>-2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.172</v>
+        <v>-1.171</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.668</v>
+        <v>-0.667</v>
       </c>
       <c r="M7" t="n">
         <v>0.778</v>
@@ -1111,13 +1111,13 @@
         <v>0.842</v>
       </c>
       <c r="O7" t="n">
-        <v>0.712</v>
+        <v>0.711</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.357</v>
+        <v>-0.356</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.508</v>
+        <v>0.507</v>
       </c>
       <c r="R7" t="n">
         <v>20.69</v>
@@ -1175,13 +1175,13 @@
         <v>9.863</v>
       </c>
       <c r="I8" t="n">
-        <v>7.932</v>
+        <v>7.933</v>
       </c>
       <c r="J8" t="n">
         <v>-2.008</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.931</v>
+        <v>-1.929</v>
       </c>
       <c r="L8" t="n">
         <v>5.81</v>
@@ -1190,13 +1190,13 @@
         <v>5.81</v>
       </c>
       <c r="N8" t="n">
-        <v>5.829</v>
+        <v>5.83</v>
       </c>
       <c r="O8" t="n">
         <v>0.831</v>
       </c>
       <c r="P8" t="n">
-        <v>-45.914</v>
+        <v>-45.919</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.023</v>
@@ -1257,22 +1257,22 @@
         <v>5.178</v>
       </c>
       <c r="I9" t="n">
-        <v>4.798</v>
+        <v>4.799</v>
       </c>
       <c r="J9" t="n">
         <v>0.04</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.38</v>
+        <v>-0.379</v>
       </c>
       <c r="L9" t="n">
         <v>0.29</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.948</v>
+        <v>0.949</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1339,13 +1339,13 @@
         <v>11.017</v>
       </c>
       <c r="I10" t="n">
-        <v>11.479</v>
+        <v>11.484</v>
       </c>
       <c r="J10" t="n">
         <v>-1.39</v>
       </c>
       <c r="K10" t="n">
-        <v>0.462</v>
+        <v>0.468</v>
       </c>
       <c r="L10" t="n">
         <v>3.915</v>
@@ -1360,10 +1360,10 @@
         <v>-0.491</v>
       </c>
       <c r="P10" t="n">
-        <v>-105.398</v>
+        <v>-105.431</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.724</v>
+        <v>-1.725</v>
       </c>
       <c r="R10" t="n">
         <v>41.379</v>
@@ -1418,31 +1418,31 @@
         <v>5.32</v>
       </c>
       <c r="H11" t="n">
-        <v>112.884</v>
+        <v>112.885</v>
       </c>
       <c r="I11" t="n">
-        <v>108.394</v>
+        <v>108.396</v>
       </c>
       <c r="J11" t="n">
         <v>-1.68</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.49</v>
+        <v>-4.489</v>
       </c>
       <c r="L11" t="n">
-        <v>88.682</v>
+        <v>88.684</v>
       </c>
       <c r="M11" t="n">
-        <v>88.682</v>
+        <v>88.684</v>
       </c>
       <c r="N11" t="n">
-        <v>92.012</v>
+        <v>92.01300000000001</v>
       </c>
       <c r="O11" t="n">
         <v>-0.358</v>
       </c>
       <c r="P11" t="n">
-        <v>-13.681</v>
+        <v>-13.682</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.322</v>
@@ -1462,13 +1462,13 @@
         <v>0.129</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.737</v>
+        <v>-0.738</v>
       </c>
       <c r="W11" t="n">
         <v>0.129</v>
       </c>
       <c r="X11" t="n">
-        <v>36.189</v>
+        <v>36.19</v>
       </c>
     </row>
     <row r="12">
@@ -1585,28 +1585,28 @@
         <v>5.956</v>
       </c>
       <c r="I13" t="n">
-        <v>5.125</v>
+        <v>5.126</v>
       </c>
       <c r="J13" t="n">
         <v>-0.6919999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.831</v>
+        <v>-0.83</v>
       </c>
       <c r="L13" t="n">
-        <v>0.26</v>
+        <v>0.261</v>
       </c>
       <c r="M13" t="n">
         <v>0.424</v>
       </c>
       <c r="N13" t="n">
-        <v>0.513</v>
+        <v>0.514</v>
       </c>
       <c r="O13" t="n">
         <v>0.439</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>0.215</v>
@@ -1667,13 +1667,13 @@
         <v>7.097</v>
       </c>
       <c r="I14" t="n">
-        <v>5.202</v>
+        <v>5.203</v>
       </c>
       <c r="J14" t="n">
         <v>-2.422</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.895</v>
+        <v>-1.894</v>
       </c>
       <c r="L14" t="n">
         <v>2.035</v>
@@ -1688,7 +1688,7 @@
         <v>0.615</v>
       </c>
       <c r="P14" t="n">
-        <v>-10.09</v>
+        <v>-10.089</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.553</v>
@@ -1749,13 +1749,13 @@
         <v>8.144</v>
       </c>
       <c r="I15" t="n">
-        <v>6.35</v>
+        <v>6.352</v>
       </c>
       <c r="J15" t="n">
         <v>-1.525</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.793</v>
+        <v>-1.792</v>
       </c>
       <c r="L15" t="n">
         <v>-0.24</v>
@@ -1770,13 +1770,13 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.204</v>
+        <v>-0.202</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
       <c r="R15" t="n">
-        <v>44.828</v>
+        <v>41.379</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>6.678</v>
+        <v>6.679</v>
       </c>
       <c r="J17" t="n">
         <v>-2.425</v>
@@ -1931,13 +1931,13 @@
         <v>1.626</v>
       </c>
       <c r="O17" t="n">
-        <v>0.605</v>
+        <v>0.604</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.684</v>
+        <v>-3.683</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.285</v>
+        <v>0.284</v>
       </c>
       <c r="R17" t="n">
         <v>31.034</v>
@@ -1995,13 +1995,13 @@
         <v>7.154</v>
       </c>
       <c r="I18" t="n">
-        <v>6.291</v>
+        <v>6.292</v>
       </c>
       <c r="J18" t="n">
         <v>-1.55</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.863</v>
+        <v>-0.862</v>
       </c>
       <c r="L18" t="n">
         <v>1.538</v>
@@ -2016,7 +2016,7 @@
         <v>0.61</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.626</v>
+        <v>-6.627</v>
       </c>
       <c r="Q18" t="n">
         <v>0.23</v>
@@ -2036,7 +2036,7 @@
         <v>0.601</v>
       </c>
       <c r="V18" t="n">
-        <v>0.218</v>
+        <v>0.217</v>
       </c>
       <c r="W18" t="n">
         <v>0.598</v>
@@ -2074,31 +2074,31 @@
         <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.486</v>
+        <v>3.49</v>
       </c>
       <c r="I19" t="n">
-        <v>3.104</v>
+        <v>3.106</v>
       </c>
       <c r="J19" t="n">
         <v>-1.34</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.382</v>
+        <v>-0.384</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.159</v>
+        <v>-0.158</v>
       </c>
       <c r="M19" t="n">
         <v>0.371</v>
       </c>
       <c r="N19" t="n">
-        <v>0.488</v>
+        <v>0.487</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.424</v>
+        <v>-0.42</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.11</v>
@@ -3392,10 +3392,10 @@
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8532955350815025</v>
+        <v>0.853399433427762</v>
       </c>
       <c r="H18" t="n">
-        <v>8.169893692416725</v>
+        <v>8.170276203966006</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>5.714893692416725</v>
+        <v>5.715276203966006</v>
       </c>
       <c r="N18" t="n">
-        <v>5.714893692416725</v>
+        <v>5.715276203966006</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1374999999999997</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7301343384171926</v>
+        <v>-0.7297518268679113</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8504606661941885</v>
+        <v>0.8505665722379604</v>
       </c>
       <c r="H19" t="n">
-        <v>8.156970233876683</v>
+        <v>8.15722202549575</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3485,16 +3485,16 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.744470233876683</v>
+        <v>5.744722025495751</v>
       </c>
       <c r="N19" t="n">
-        <v>5.744470233876683</v>
+        <v>5.744722025495751</v>
       </c>
       <c r="O19" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.01292345854004218</v>
+        <v>-0.01305417847025581</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8462083628632175</v>
+        <v>0.8463172804532578</v>
       </c>
       <c r="H20" t="n">
-        <v>8.131201275691</v>
+        <v>8.13206444759207</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3556,16 +3556,16 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>5.731201275690999</v>
+        <v>5.732064447592069</v>
       </c>
       <c r="N20" t="n">
-        <v>5.731201275690999</v>
+        <v>5.732064447592069</v>
       </c>
       <c r="O20" t="n">
         <v>-0.01250000000000018</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.02576895818568303</v>
+        <v>-0.02515757790368056</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8433734939759037</v>
+        <v>0.8434844192634561</v>
       </c>
       <c r="H21" t="n">
-        <v>8.118493975903615</v>
+        <v>8.118845609065156</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>5.948493975903615</v>
+        <v>5.948845609065156</v>
       </c>
       <c r="N21" t="n">
-        <v>5.948493975903615</v>
+        <v>5.948845609065156</v>
       </c>
       <c r="O21" t="n">
         <v>-0.23</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.01270729978738494</v>
+        <v>-0.01321883852691386</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8384124734231042</v>
+        <v>0.8385269121813032</v>
       </c>
       <c r="H22" t="n">
-        <v>8.095535081502481</v>
+        <v>8.096260623229462</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3698,16 +3698,16 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>6.115535081502481</v>
+        <v>6.116260623229461</v>
       </c>
       <c r="N22" t="n">
-        <v>6.115535081502481</v>
+        <v>6.116260623229461</v>
       </c>
       <c r="O22" t="n">
         <v>-0.1899999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.02295889440113363</v>
+        <v>-0.02258498583569413</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8334514528703048</v>
+        <v>0.8335694050991501</v>
       </c>
       <c r="H23" t="n">
-        <v>8.058164422395464</v>
+        <v>8.059660056657224</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3769,16 +3769,16 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>6.008164422395464</v>
+        <v>6.009660056657224</v>
       </c>
       <c r="N23" t="n">
-        <v>6.008164422395464</v>
+        <v>6.009660056657224</v>
       </c>
       <c r="O23" t="n">
         <v>0.06999999999999984</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.03737065910701709</v>
+        <v>-0.03660056657223798</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8270729978738484</v>
+        <v>0.8271954674220963</v>
       </c>
       <c r="H24" t="n">
         <v>8.029999999999999</v>
@@ -3849,7 +3849,7 @@
         <v>0.1700000000000004</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.02816442239546468</v>
+        <v>-0.02966005665722449</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8221119773210489</v>
+        <v>0.8222379603399433</v>
       </c>
       <c r="H25" t="n">
-        <v>8.013047484053862</v>
+        <v>8.013247167138809</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3911,16 +3911,16 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>5.663047484053862</v>
+        <v>5.66324716713881</v>
       </c>
       <c r="N25" t="n">
-        <v>5.663047484053862</v>
+        <v>5.66324716713881</v>
       </c>
       <c r="O25" t="n">
         <v>0.1299999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01695251594613723</v>
+        <v>-0.01675283286119011</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3960,10 +3960,10 @@
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8192771084337349</v>
+        <v>0.8194050991501416</v>
       </c>
       <c r="H26" t="n">
-        <v>8.000662650602409</v>
+        <v>8.001271246458924</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3982,16 +3982,16 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>5.70066265060241</v>
+        <v>5.701271246458924</v>
       </c>
       <c r="N26" t="n">
-        <v>5.70066265060241</v>
+        <v>5.701271246458924</v>
       </c>
       <c r="O26" t="n">
         <v>-0.05000000000000027</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.01238483345145269</v>
+        <v>-0.01197592067988573</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8157335223245925</v>
+        <v>0.8158640226628895</v>
       </c>
       <c r="H27" t="n">
-        <v>7.973063430191353</v>
+        <v>7.974511331444758</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4053,16 +4053,16 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>5.743063430191354</v>
+        <v>5.744511331444759</v>
       </c>
       <c r="N27" t="n">
-        <v>5.743063430191354</v>
+        <v>5.744511331444759</v>
       </c>
       <c r="O27" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.027599220411056</v>
+        <v>-0.02675991501416508</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8114812189936216</v>
+        <v>0.8116147308781869</v>
       </c>
       <c r="H28" t="n">
-        <v>7.947395464209781</v>
+        <v>7.947818696883853</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>5.887395464209781</v>
+        <v>5.887818696883853</v>
       </c>
       <c r="N28" t="n">
-        <v>5.887395464209781</v>
+        <v>5.887818696883853</v>
       </c>
       <c r="O28" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.02566796598157239</v>
+        <v>-0.02669263456090576</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.81218993621545</v>
+        <v>0.8123229461756374</v>
       </c>
       <c r="H29" t="n">
-        <v>7.949642097802977</v>
+        <v>7.950159348441927</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4195,16 +4195,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>5.999642097802977</v>
+        <v>6.000159348441927</v>
       </c>
       <c r="N29" t="n">
-        <v>5.999642097802977</v>
+        <v>6.000159348441927</v>
       </c>
       <c r="O29" t="n">
         <v>-0.1100000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>0.002246633593196101</v>
+        <v>0.002340651558074391</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8128986534372785</v>
+        <v>0.8130311614730878</v>
       </c>
       <c r="H30" t="n">
-        <v>7.954721828490432</v>
+        <v>7.955771954674221</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4266,16 +4266,16 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.254721828490432</v>
+        <v>5.255771954674221</v>
       </c>
       <c r="N30" t="n">
-        <v>5.254721828490432</v>
+        <v>5.255771954674221</v>
       </c>
       <c r="O30" t="n">
         <v>0.7500000000000002</v>
       </c>
       <c r="P30" t="n">
-        <v>0.00507973068745482</v>
+        <v>0.005612606232293871</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8093550673281361</v>
+        <v>0.8094900849858357</v>
       </c>
       <c r="H31" t="n">
-        <v>7.931966690290575</v>
+        <v>7.933250708215298</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4337,16 +4337,16 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.131966690290575</v>
+        <v>5.133250708215298</v>
       </c>
       <c r="N31" t="n">
-        <v>5.131966690290575</v>
+        <v>5.133250708215298</v>
       </c>
       <c r="O31" t="n">
         <v>0.09999999999999964</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.02275513819985697</v>
+        <v>-0.02252124645892284</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6484762579730687</v>
+        <v>0.6487252124645893</v>
       </c>
       <c r="H48" t="n">
-        <v>6.158979668674699</v>
+        <v>6.159074893767706</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5538,16 +5538,16 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1285203313253005</v>
+        <v>-0.1284251062322941</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1285203313253005</v>
+        <v>0.1284251062322941</v>
       </c>
       <c r="O48" t="n">
         <v>-0.09250000000000114</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.6249096095313273</v>
+        <v>-0.6248143844383209</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6420978029766123</v>
+        <v>0.6423512747875354</v>
       </c>
       <c r="H49" t="n">
-        <v>6.144819277108434</v>
+        <v>6.145594900849859</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5609,16 +5609,16 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.02518072289156592</v>
+        <v>-0.02440509915014122</v>
       </c>
       <c r="N49" t="n">
-        <v>0.02518072289156592</v>
+        <v>0.02440509915014122</v>
       </c>
       <c r="O49" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.01416039156626514</v>
+        <v>-0.01347999291784685</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5658,10 +5658,10 @@
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>0.6343019135364989</v>
+        <v>0.6345609065155807</v>
       </c>
       <c r="H50" t="n">
-        <v>6.12277108433735</v>
+        <v>6.123405099150141</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5680,16 +5680,16 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.03277108433734988</v>
+        <v>0.03340509915014156</v>
       </c>
       <c r="N50" t="n">
-        <v>0.03277108433734988</v>
+        <v>0.03340509915014156</v>
       </c>
       <c r="O50" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.02204819277108427</v>
+        <v>-0.02218980169971729</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5729,10 +5729,10 @@
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>0.632884479092842</v>
+        <v>0.6331444759206799</v>
       </c>
       <c r="H51" t="n">
-        <v>6.119781626506025</v>
+        <v>6.11998052407932</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5751,16 +5751,16 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2597816265060242</v>
+        <v>0.25998052407932</v>
       </c>
       <c r="N51" t="n">
-        <v>0.2597816265060242</v>
+        <v>0.25998052407932</v>
       </c>
       <c r="O51" t="n">
         <v>-0.2299999999999995</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.002989457831325204</v>
+        <v>-0.003424575070821056</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>0.6442239546420978</v>
+        <v>0.6444759206798867</v>
       </c>
       <c r="H52" t="n">
-        <v>6.153975903614458</v>
+        <v>6.15628895184136</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5822,16 +5822,16 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4939759036144578</v>
+        <v>0.4962889518413602</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4939759036144578</v>
+        <v>0.4962889518413602</v>
       </c>
       <c r="O52" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P52" t="n">
-        <v>0.03419427710843337</v>
+        <v>0.03630842776204002</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6520198440822113</v>
+        <v>0.6522662889518414</v>
       </c>
       <c r="H53" t="n">
-        <v>6.165180722891566</v>
+        <v>6.165934844192635</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5893,16 +5893,16 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5351807228915666</v>
+        <v>0.535934844192635</v>
       </c>
       <c r="N53" t="n">
-        <v>0.5351807228915666</v>
+        <v>0.535934844192635</v>
       </c>
       <c r="O53" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P53" t="n">
-        <v>0.01120481927710859</v>
+        <v>0.009645892351274554</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6619418851878101</v>
+        <v>0.6621813031161473</v>
       </c>
       <c r="H54" t="n">
-        <v>6.204056224899599</v>
+        <v>6.205033050047215</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5964,16 +5964,16 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6140562248995991</v>
+        <v>0.6150330500472148</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6140562248995991</v>
+        <v>0.6150330500472148</v>
       </c>
       <c r="O54" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P54" t="n">
-        <v>0.03887550200803247</v>
+        <v>0.03909820585457968</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6683203401842664</v>
+        <v>0.6685552407932012</v>
       </c>
       <c r="H55" t="n">
-        <v>6.217530120481928</v>
+        <v>6.217889518413598</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6035,16 +6035,16 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7675301204819274</v>
+        <v>0.7678895184135976</v>
       </c>
       <c r="N55" t="n">
-        <v>0.7675301204819274</v>
+        <v>0.7678895184135976</v>
       </c>
       <c r="O55" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01347389558232859</v>
+        <v>0.01285646836638321</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>0.664776754075124</v>
+        <v>0.6650141643059491</v>
       </c>
       <c r="H56" t="n">
-        <v>6.21210843373494</v>
+        <v>6.212471671388102</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6106,16 +6106,16 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8121084337349398</v>
+        <v>0.8124716713881019</v>
       </c>
       <c r="N56" t="n">
-        <v>0.8121084337349398</v>
+        <v>0.8124716713881019</v>
       </c>
       <c r="O56" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.005421686746987397</v>
+        <v>-0.005417847025495526</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
         <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6534372785258682</v>
+        <v>0.6536827195467422</v>
       </c>
       <c r="H57" t="n">
-        <v>6.169518072289157</v>
+        <v>6.170538243626062</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.7995180722891568</v>
+        <v>0.800538243626062</v>
       </c>
       <c r="N57" t="n">
-        <v>0.7995180722891568</v>
+        <v>0.800538243626062</v>
       </c>
       <c r="O57" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.04259036144578321</v>
+        <v>-0.04193342776204023</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6226,10 +6226,10 @@
         <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6378454996456414</v>
+        <v>0.6381019830028328</v>
       </c>
       <c r="H58" t="n">
-        <v>6.133614457831325</v>
+        <v>6.135061378659112</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6248,16 +6248,16 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8036144578313253</v>
+        <v>0.8050613786591123</v>
       </c>
       <c r="N58" t="n">
-        <v>0.8036144578313253</v>
+        <v>0.8050613786591123</v>
       </c>
       <c r="O58" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.03590361445783152</v>
+        <v>-0.03547686496694968</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6297,10 +6297,10 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6194188518781006</v>
+        <v>0.6196883852691218</v>
       </c>
       <c r="H59" t="n">
-        <v>6.073895582329317</v>
+        <v>6.074995278564684</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6319,16 +6319,16 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9238955823293171</v>
+        <v>0.9249952785646833</v>
       </c>
       <c r="N59" t="n">
-        <v>0.9238955823293171</v>
+        <v>0.9249952785646833</v>
       </c>
       <c r="O59" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.05971887550200794</v>
+        <v>-0.0600661000944287</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6052445074415308</v>
+        <v>0.6055240793201133</v>
       </c>
       <c r="H60" t="n">
-        <v>6.026144578313253</v>
+        <v>6.027903682719547</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6390,16 +6390,16 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1.056144578313253</v>
+        <v>1.057903682719547</v>
       </c>
       <c r="N60" t="n">
-        <v>1.056144578313253</v>
+        <v>1.057903682719547</v>
       </c>
       <c r="O60" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.04775100401606469</v>
+        <v>-0.04709159584513678</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6439,10 +6439,10 @@
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5903614457831325</v>
+        <v>0.5906515580736544</v>
       </c>
       <c r="H61" t="n">
-        <v>5.965341365461847</v>
+        <v>5.966525023607177</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6461,16 +6461,16 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1.135341365461847</v>
+        <v>1.136525023607176</v>
       </c>
       <c r="N61" t="n">
-        <v>1.135341365461847</v>
+        <v>1.136525023607176</v>
       </c>
       <c r="O61" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.06080321285140577</v>
+        <v>-0.06137865911237039</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -7640,10 +7640,10 @@
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8972360028348689</v>
+        <v>0.8973087818696884</v>
       </c>
       <c r="H78" t="n">
-        <v>5.875882352941177</v>
+        <v>5.87672804532578</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7662,16 +7662,16 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1.188382352941177</v>
+        <v>1.18922804532578</v>
       </c>
       <c r="N78" t="n">
-        <v>1.188382352941177</v>
+        <v>1.18922804532578</v>
       </c>
       <c r="O78" t="n">
         <v>0.2725</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.06594315511768745</v>
+        <v>-0.06509746273308537</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8681785967399008</v>
+        <v>0.8682719546742209</v>
       </c>
       <c r="H79" t="n">
-        <v>5.689117647058825</v>
+        <v>5.689660056657225</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7733,16 +7733,16 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>1.276617647058825</v>
+        <v>1.277160056657225</v>
       </c>
       <c r="N79" t="n">
-        <v>1.276617647058825</v>
+        <v>1.277160056657225</v>
       </c>
       <c r="O79" t="n">
         <v>-0.2750000000000004</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.1867647058823527</v>
+        <v>-0.1870679886685549</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8256555634301913</v>
+        <v>0.8257790368271954</v>
       </c>
       <c r="H80" t="n">
-        <v>5.412058823529411</v>
+        <v>5.412776203966005</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7804,16 +7804,16 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7620588235294106</v>
+        <v>0.7627762039660047</v>
       </c>
       <c r="N80" t="n">
-        <v>0.7620588235294106</v>
+        <v>0.7627762039660047</v>
       </c>
       <c r="O80" t="n">
         <v>0.2375000000000007</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.2770588235294138</v>
+        <v>-0.2768838526912196</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>0.778880226789511</v>
+        <v>0.7790368271954674</v>
       </c>
       <c r="H81" t="n">
-        <v>5.150294117647059</v>
+        <v>5.151203966005665</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7875,16 +7875,16 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>0.4502941176470587</v>
+        <v>0.4512039660056653</v>
       </c>
       <c r="N81" t="n">
-        <v>0.4502941176470587</v>
+        <v>0.4512039660056653</v>
       </c>
       <c r="O81" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.261764705882352</v>
+        <v>-0.2615722379603396</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7328136073706591</v>
+        <v>0.7330028328611898</v>
       </c>
       <c r="H82" t="n">
-        <v>4.99264705882353</v>
+        <v>4.993746458923513</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7946,16 +7946,16 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5876470588235305</v>
+        <v>0.5887464589235138</v>
       </c>
       <c r="N82" t="n">
-        <v>0.5876470588235305</v>
+        <v>0.5887464589235138</v>
       </c>
       <c r="O82" t="n">
         <v>-0.2950000000000008</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.157647058823529</v>
+        <v>-0.1574575070821522</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -7995,10 +7995,10 @@
         <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7065910701630049</v>
+        <v>0.7067988668555241</v>
       </c>
       <c r="H83" t="n">
-        <v>4.86686274509804</v>
+        <v>4.86766761095373</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8017,16 +8017,16 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>0.7693627450980403</v>
+        <v>0.770167610953731</v>
       </c>
       <c r="N83" t="n">
-        <v>0.7693627450980403</v>
+        <v>0.770167610953731</v>
       </c>
       <c r="O83" t="n">
         <v>-0.3075000000000001</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.1257843137254904</v>
+        <v>-0.126078847969783</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -8066,10 +8066,10 @@
         <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>0.6746987951807228</v>
+        <v>0.6749291784702549</v>
       </c>
       <c r="H84" t="n">
-        <v>4.784285714285715</v>
+        <v>4.784668150546337</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8088,16 +8088,16 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>0.9342857142857146</v>
+        <v>0.934668150546337</v>
       </c>
       <c r="N84" t="n">
-        <v>0.9342857142857146</v>
+        <v>0.934668150546337</v>
       </c>
       <c r="O84" t="n">
         <v>-0.2474999999999992</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.08257703081232481</v>
+        <v>-0.08299946040739314</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6406803685329554</v>
+        <v>0.6402266288951841</v>
       </c>
       <c r="H85" t="n">
-        <v>4.687892156862745</v>
+        <v>4.687287535410765</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8159,16 +8159,16 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9078921568627449</v>
+        <v>0.9072875354107652</v>
       </c>
       <c r="N85" t="n">
-        <v>0.9078921568627449</v>
+        <v>0.9072875354107652</v>
       </c>
       <c r="O85" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.09639355742296996</v>
+        <v>-0.09738061513557206</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6052445074415308</v>
+        <v>0.6048158640226629</v>
       </c>
       <c r="H86" t="n">
-        <v>4.553235294117647</v>
+        <v>4.551990084985835</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8230,16 +8230,16 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.2467647058823541</v>
+        <v>-0.2480099150141655</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2467647058823541</v>
+        <v>0.2480099150141655</v>
       </c>
       <c r="O86" t="n">
         <v>1.020000000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.1346568627450981</v>
+        <v>-0.1352974504249298</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -8279,10 +8279,10 @@
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>0.5981573352232459</v>
+        <v>0.5977337110481586</v>
       </c>
       <c r="H87" t="n">
-        <v>4.522610294117646</v>
+        <v>4.521416430594901</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8301,16 +8301,16 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.1773897058823541</v>
+        <v>-0.1785835694050997</v>
       </c>
       <c r="N87" t="n">
-        <v>0.1773897058823541</v>
+        <v>0.1785835694050997</v>
       </c>
       <c r="O87" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.03062500000000057</v>
+        <v>-0.03057365439093473</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -8350,10 +8350,10 @@
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6151665485471297</v>
+        <v>0.6147308781869688</v>
       </c>
       <c r="H88" t="n">
-        <v>4.576078431372549</v>
+        <v>4.574390934844192</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8372,16 +8372,16 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.6239215686274511</v>
+        <v>-0.6256090651558077</v>
       </c>
       <c r="N88" t="n">
-        <v>0.6239215686274511</v>
+        <v>0.6256090651558077</v>
       </c>
       <c r="O88" t="n">
         <v>0.5</v>
       </c>
       <c r="P88" t="n">
-        <v>0.05346813725490307</v>
+        <v>0.05297450424929195</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6576895818568391</v>
+        <v>0.6579320113314447</v>
       </c>
       <c r="H89" t="n">
-        <v>4.720588235294119</v>
+        <v>4.721292492917847</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8443,16 +8443,16 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.7794117647058814</v>
+        <v>-0.778707507082153</v>
       </c>
       <c r="N89" t="n">
-        <v>0.7794117647058814</v>
+        <v>0.778707507082153</v>
       </c>
       <c r="O89" t="n">
         <v>0.2999999999999998</v>
       </c>
       <c r="P89" t="n">
-        <v>0.1445098039215695</v>
+        <v>0.1469015580736546</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8492,10 +8492,10 @@
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6810772501771793</v>
+        <v>0.6813031161473088</v>
       </c>
       <c r="H90" t="n">
-        <v>4.794264705882353</v>
+        <v>4.794592776203966</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8514,16 +8514,16 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-1.085735294117647</v>
+        <v>-1.085407223796034</v>
       </c>
       <c r="N90" t="n">
-        <v>1.085735294117647</v>
+        <v>1.085407223796034</v>
       </c>
       <c r="O90" t="n">
         <v>0.3799999999999999</v>
       </c>
       <c r="P90" t="n">
-        <v>0.07367647058823401</v>
+        <v>0.07330028328611871</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8563,10 +8563,10 @@
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6839121190644932</v>
+        <v>0.6841359773371105</v>
       </c>
       <c r="H91" t="n">
-        <v>4.798382352941176</v>
+        <v>4.798707507082153</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -8585,16 +8585,16 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.2216176470588236</v>
+        <v>-0.221292492917847</v>
       </c>
       <c r="N91" t="n">
-        <v>0.2216176470588236</v>
+        <v>0.221292492917847</v>
       </c>
       <c r="O91" t="n">
         <v>-0.8600000000000003</v>
       </c>
       <c r="P91" t="n">
-        <v>0.004117647058823337</v>
+        <v>0.004114730878186812</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -9764,10 +9764,10 @@
         <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8908575478384124</v>
+        <v>0.8909348441926346</v>
       </c>
       <c r="H108" t="n">
-        <v>12.38252657689582</v>
+        <v>12.38269121813031</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -9786,16 +9786,16 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>5.312526576895819</v>
+        <v>5.312691218130312</v>
       </c>
       <c r="N108" t="n">
-        <v>5.312526576895819</v>
+        <v>5.312691218130312</v>
       </c>
       <c r="O108" t="n">
         <v>-0.1250000000000009</v>
       </c>
       <c r="P108" t="n">
-        <v>4.41294703940458</v>
+        <v>4.413111680639073</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -9835,10 +9835,10 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>0.8866052445074415</v>
+        <v>0.886685552407932</v>
       </c>
       <c r="H109" t="n">
-        <v>12.33316087880935</v>
+        <v>12.33504249291785</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -9857,16 +9857,16 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>5.463160878809354</v>
+        <v>5.465042492917846</v>
       </c>
       <c r="N109" t="n">
-        <v>5.463160878809354</v>
+        <v>5.465042492917846</v>
       </c>
       <c r="O109" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.04936569808646496</v>
+        <v>-0.04764872521246488</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -9906,10 +9906,10 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>0.884479092841956</v>
+        <v>0.8845609065155807</v>
       </c>
       <c r="H110" t="n">
-        <v>12.2893214032601</v>
+        <v>12.28984419263456</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -9928,16 +9928,16 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>5.549321403260098</v>
+        <v>5.549844192634561</v>
       </c>
       <c r="N110" t="n">
-        <v>5.549321403260098</v>
+        <v>5.549844192634561</v>
       </c>
       <c r="O110" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.04383947554925527</v>
+        <v>-0.04519830028328542</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -9977,10 +9977,10 @@
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8824362606232294</v>
       </c>
       <c r="H111" t="n">
-        <v>12.27308823529412</v>
+        <v>12.27441926345609</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -9999,16 +9999,16 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>5.673088235294118</v>
+        <v>5.674419263456091</v>
       </c>
       <c r="N111" t="n">
-        <v>5.673088235294118</v>
+        <v>5.674419263456091</v>
       </c>
       <c r="O111" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P111" t="n">
-        <v>-0.0162331679659804</v>
+        <v>-0.01542492917847049</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -10048,10 +10048,10 @@
         <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8759744861800142</v>
+        <v>0.8760623229461756</v>
       </c>
       <c r="H112" t="n">
-        <v>12.22165131112686</v>
+        <v>12.22202549575071</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10070,16 +10070,16 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>5.36165131112686</v>
+        <v>5.362025495750708</v>
       </c>
       <c r="N112" t="n">
-        <v>5.36165131112686</v>
+        <v>5.362025495750708</v>
       </c>
       <c r="O112" t="n">
         <v>0.2600000000000007</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.0514369241672572</v>
+        <v>-0.05239376770538229</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>0.8674698795180723</v>
+        <v>0.8675637393767706</v>
       </c>
       <c r="H113" t="n">
-        <v>12.19021084337349</v>
+        <v>12.19041076487252</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -10141,16 +10141,16 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>5.210210843373494</v>
+        <v>5.21041076487252</v>
       </c>
       <c r="N113" t="n">
-        <v>5.210210843373494</v>
+        <v>5.21041076487252</v>
       </c>
       <c r="O113" t="n">
         <v>0.1200000000000001</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.03144046775336662</v>
+        <v>-0.03161473087818756</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -10190,10 +10190,10 @@
         <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>0.856839121190645</v>
+        <v>0.8569405099150141</v>
       </c>
       <c r="H114" t="n">
-        <v>12.11540396881644</v>
+        <v>12.11669971671388</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -10212,16 +10212,16 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>5.265403968816443</v>
+        <v>5.26669971671388</v>
       </c>
       <c r="N114" t="n">
-        <v>5.265403968816443</v>
+        <v>5.26669971671388</v>
       </c>
       <c r="O114" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P114" t="n">
-        <v>-0.07480687455705137</v>
+        <v>-0.07371104815864093</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
         <v>8</v>
       </c>
       <c r="G115" t="n">
-        <v>0.8462083628632175</v>
+        <v>0.8463172804532578</v>
       </c>
       <c r="H115" t="n">
-        <v>12.07446669029057</v>
+        <v>12.07531161473088</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -10283,16 +10283,16 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>5.334466690290574</v>
+        <v>5.335311614730879</v>
       </c>
       <c r="N115" t="n">
-        <v>5.334466690290574</v>
+        <v>5.335311614730879</v>
       </c>
       <c r="O115" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.04093727852586859</v>
+        <v>-0.04138810198300114</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -10332,10 +10332,10 @@
         <v>8</v>
       </c>
       <c r="G116" t="n">
-        <v>0.8242381289865344</v>
+        <v>0.8243626062322946</v>
       </c>
       <c r="H116" t="n">
-        <v>11.86125442948263</v>
+        <v>11.86178470254957</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -10354,16 +10354,16 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>5.256254429482635</v>
+        <v>5.256784702549574</v>
       </c>
       <c r="N116" t="n">
-        <v>5.256254429482635</v>
+        <v>5.256784702549574</v>
       </c>
       <c r="O116" t="n">
         <v>-0.1349999999999998</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.2132122608079392</v>
+        <v>-0.2135269121813046</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10403,10 +10403,10 @@
         <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>0.8093550673281361</v>
+        <v>0.8094900849858357</v>
       </c>
       <c r="H117" t="n">
-        <v>11.80677888022679</v>
+        <v>11.80764164305949</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -10425,16 +10425,16 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>5.426778880226791</v>
+        <v>5.42764164305949</v>
       </c>
       <c r="N117" t="n">
-        <v>5.426778880226791</v>
+        <v>5.42764164305949</v>
       </c>
       <c r="O117" t="n">
         <v>-0.2250000000000005</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.05447554925584441</v>
+        <v>-0.0541430594900838</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10474,10 +10474,10 @@
         <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7951807228915663</v>
+        <v>0.7953257790368272</v>
       </c>
       <c r="H118" t="n">
-        <v>11.72373493975904</v>
+        <v>11.72404390934844</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -10496,16 +10496,16 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>5.483734939759035</v>
+        <v>5.484043909348442</v>
       </c>
       <c r="N118" t="n">
-        <v>5.483734939759035</v>
+        <v>5.484043909348442</v>
       </c>
       <c r="O118" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.08304394046775521</v>
+        <v>-0.08359773371104851</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10545,10 +10545,10 @@
         <v>8</v>
       </c>
       <c r="G119" t="n">
-        <v>0.781715095676825</v>
+        <v>0.7818696883852692</v>
       </c>
       <c r="H119" t="n">
-        <v>11.65765946137491</v>
+        <v>11.65864730878187</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -10567,16 +10567,16 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>5.537659461374912</v>
+        <v>5.538647308781871</v>
       </c>
       <c r="N119" t="n">
-        <v>5.537659461374912</v>
+        <v>5.538647308781871</v>
       </c>
       <c r="O119" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.06607547838412309</v>
+        <v>-0.06539660056657048</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -10616,10 +10616,10 @@
         <v>8</v>
       </c>
       <c r="G120" t="n">
-        <v>0.7675407512402551</v>
+        <v>0.7677053824362606</v>
       </c>
       <c r="H120" t="n">
-        <v>11.55479270021261</v>
+        <v>11.55521246458924</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10638,16 +10638,16 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>5.484792700212614</v>
+        <v>5.485212464589235</v>
       </c>
       <c r="N120" t="n">
-        <v>5.484792700212614</v>
+        <v>5.485212464589235</v>
       </c>
       <c r="O120" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.1028667611622982</v>
+        <v>-0.1034348441926358</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         <v>8</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7590361445783133</v>
+        <v>0.7592067988668555</v>
       </c>
       <c r="H121" t="n">
-        <v>11.47870481927711</v>
+        <v>11.48415722379603</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -10709,16 +10709,16 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.448704819277109</v>
+        <v>5.454157223796032</v>
       </c>
       <c r="N121" t="n">
-        <v>5.448704819277109</v>
+        <v>5.454157223796032</v>
       </c>
       <c r="O121" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.07608788093550523</v>
+        <v>-0.07105524079320347</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>8</v>
       </c>
       <c r="G122" t="n">
-        <v>0.9596031183557761</v>
+        <v>0.9596317280453258</v>
       </c>
       <c r="H122" t="n">
-        <v>112.8835577604536</v>
+        <v>112.8852620396601</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>105.8835577604536</v>
+        <v>105.8852620396601</v>
       </c>
       <c r="N122" t="n">
-        <v>105.8835577604536</v>
+        <v>105.8852620396601</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         <v>8</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9355067328136074</v>
+        <v>0.9355524079320113</v>
       </c>
       <c r="H123" t="n">
-        <v>112.4611622962438</v>
+        <v>112.4615509915014</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -10845,16 +10845,16 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>105.6511622962438</v>
+        <v>105.6515509915014</v>
       </c>
       <c r="N123" t="n">
-        <v>105.6511622962438</v>
+        <v>105.6515509915014</v>
       </c>
       <c r="O123" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.4223954642097851</v>
+        <v>-0.4237110481586512</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -10894,10 +10894,10 @@
         <v>8</v>
       </c>
       <c r="G124" t="n">
-        <v>0.9177888022678952</v>
+        <v>0.9178470254957507</v>
       </c>
       <c r="H124" t="n">
-        <v>112.1403827072998</v>
+        <v>112.1408781869688</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -10916,16 +10916,16 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>105.5303827072998</v>
+        <v>105.5308781869688</v>
       </c>
       <c r="N124" t="n">
-        <v>105.5303827072998</v>
+        <v>105.5308781869688</v>
       </c>
       <c r="O124" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P124" t="n">
-        <v>-0.3207795889440064</v>
+        <v>-0.3206728045325633</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -10965,10 +10965,10 @@
         <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>0.9007795889440113</v>
+        <v>0.9008498583569405</v>
       </c>
       <c r="H125" t="n">
-        <v>111.9978171509568</v>
+        <v>111.9981161473088</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -10987,16 +10987,16 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>105.5778171509568</v>
+        <v>105.5781161473088</v>
       </c>
       <c r="N125" t="n">
-        <v>105.5778171509568</v>
+        <v>105.5781161473088</v>
       </c>
       <c r="O125" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P125" t="n">
-        <v>-0.1425655563430297</v>
+        <v>-0.1427620396600702</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -11036,10 +11036,10 @@
         <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>0.8575478384124734</v>
+        <v>0.8576487252124646</v>
       </c>
       <c r="H126" t="n">
-        <v>111.6715981573352</v>
+        <v>111.6728859773371</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -11058,16 +11058,16 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>105.4415981573352</v>
+        <v>105.4428859773371</v>
       </c>
       <c r="N126" t="n">
-        <v>105.4415981573352</v>
+        <v>105.4428859773371</v>
       </c>
       <c r="O126" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.3262189936215378</v>
+        <v>-0.3252301699716753</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -11107,10 +11107,10 @@
         <v>8</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8114812189936216</v>
+        <v>0.8116147308781869</v>
       </c>
       <c r="H127" t="n">
-        <v>111.4319017245452</v>
+        <v>111.4322804532578</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -11129,16 +11129,16 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>105.3719017245452</v>
+        <v>105.3722804532578</v>
       </c>
       <c r="N127" t="n">
-        <v>105.3719017245452</v>
+        <v>105.3722804532578</v>
       </c>
       <c r="O127" t="n">
         <v>-0.1700000000000008</v>
       </c>
       <c r="P127" t="n">
-        <v>-0.2396964327899838</v>
+        <v>-0.2406055240793137</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -11178,10 +11178,10 @@
         <v>8</v>
       </c>
       <c r="G128" t="n">
-        <v>0.7526576895818569</v>
+        <v>0.7528328611898017</v>
       </c>
       <c r="H128" t="n">
-        <v>111.1602338766832</v>
+        <v>111.1632152974504</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -11200,16 +11200,16 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>105.2302338766832</v>
+        <v>105.2332152974504</v>
       </c>
       <c r="N128" t="n">
-        <v>105.2302338766832</v>
+        <v>105.2332152974504</v>
       </c>
       <c r="O128" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.2716678478620338</v>
+        <v>-0.269065155807354</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -11249,10 +11249,10 @@
         <v>8</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6746987951807228</v>
+        <v>0.6749291784702549</v>
       </c>
       <c r="H129" t="n">
-        <v>110.7525301204819</v>
+        <v>110.7554709631728</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -11271,16 +11271,16 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>52.38753012048192</v>
+        <v>52.3904709631728</v>
       </c>
       <c r="N129" t="n">
-        <v>52.38753012048192</v>
+        <v>52.3904709631728</v>
       </c>
       <c r="O129" t="n">
         <v>52.435</v>
       </c>
       <c r="P129" t="n">
-        <v>-0.4077037562012862</v>
+        <v>-0.4077443342776377</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -11320,10 +11320,10 @@
         <v>8</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5967399007795889</v>
+        <v>0.5970254957507082</v>
       </c>
       <c r="H130" t="n">
-        <v>110.3665131112686</v>
+        <v>110.3703434844193</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -11342,16 +11342,16 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>52.0715131112686</v>
+        <v>52.07534348441926</v>
       </c>
       <c r="N130" t="n">
-        <v>52.0715131112686</v>
+        <v>52.07534348441926</v>
       </c>
       <c r="O130" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.3860170092133188</v>
+        <v>-0.3851274787535317</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         <v>8</v>
       </c>
       <c r="G131" t="n">
-        <v>0.515946137491141</v>
+        <v>0.5162889518413598</v>
       </c>
       <c r="H131" t="n">
-        <v>109.9669005433499</v>
+        <v>109.96787299339</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -11413,16 +11413,16 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>51.78190054334986</v>
+        <v>51.78287299338999</v>
       </c>
       <c r="N131" t="n">
-        <v>51.78190054334986</v>
+        <v>51.78287299338999</v>
       </c>
       <c r="O131" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.3996125679187372</v>
+        <v>-0.4024704910292769</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -11462,10 +11462,10 @@
         <v>8</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4309000708717222</v>
+        <v>0.4313031161473088</v>
       </c>
       <c r="H132" t="n">
-        <v>109.4446397354122</v>
+        <v>109.4469263456091</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -11484,16 +11484,16 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>51.39963973541224</v>
+        <v>51.40192634560906</v>
       </c>
       <c r="N132" t="n">
-        <v>51.39963973541224</v>
+        <v>51.40192634560906</v>
       </c>
       <c r="O132" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.5222608079376272</v>
+        <v>-0.5209466477809315</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -11533,10 +11533,10 @@
         <v>8</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3501063075832743</v>
+        <v>0.3505665722379603</v>
       </c>
       <c r="H133" t="n">
-        <v>108.9047023387668</v>
+        <v>108.9066607648725</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -11555,16 +11555,16 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>103.4647023387668</v>
+        <v>103.4666607648725</v>
       </c>
       <c r="N133" t="n">
-        <v>103.4647023387668</v>
+        <v>103.4666607648725</v>
       </c>
       <c r="O133" t="n">
         <v>-52.605</v>
       </c>
       <c r="P133" t="n">
-        <v>-0.5399373966453993</v>
+        <v>-0.5402655807365306</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -11604,10 +11604,10 @@
         <v>8</v>
       </c>
       <c r="G134" t="n">
-        <v>0.2664776754075124</v>
+        <v>0.2669971671388102</v>
       </c>
       <c r="H134" t="n">
-        <v>108.393862508859</v>
+        <v>108.3960729461756</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -11626,16 +11626,16 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>103.073862508859</v>
+        <v>103.0760729461756</v>
       </c>
       <c r="N134" t="n">
-        <v>103.073862508859</v>
+        <v>103.0760729461756</v>
       </c>
       <c r="O134" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P134" t="n">
-        <v>-0.5108398299078658</v>
+        <v>-0.5105878186968908</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
         <v>8</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9312544294826365</v>
+        <v>0.9313031161473088</v>
       </c>
       <c r="H154" t="n">
-        <v>9.031693834160171</v>
+        <v>9.031763456090651</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -13034,16 +13034,16 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>0.5716938341601701</v>
+        <v>0.5717634560906504</v>
       </c>
       <c r="N154" t="n">
-        <v>0.5716938341601701</v>
+        <v>0.5717634560906504</v>
       </c>
       <c r="O154" t="n">
         <v>0.005000000000000782</v>
       </c>
       <c r="P154" t="n">
-        <v>0.5826845489464372</v>
+        <v>0.5827541708769175</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>8</v>
       </c>
       <c r="G155" t="n">
-        <v>0.9213323883770376</v>
+        <v>0.9213881019830028</v>
       </c>
       <c r="H155" t="n">
         <v>9.009999999999998</v>
@@ -13114,7 +13114,7 @@
         <v>-0.03000000000000114</v>
       </c>
       <c r="P155" t="n">
-        <v>-0.0216938341601729</v>
+        <v>-0.02176345609065322</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -13154,10 +13154,10 @@
         <v>8</v>
       </c>
       <c r="G156" t="n">
-        <v>0.9142452161587526</v>
+        <v>0.9143059490084986</v>
       </c>
       <c r="H156" t="n">
-        <v>8.966594613749114</v>
+        <v>8.967202549575072</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -13176,16 +13176,16 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0.5565946137491142</v>
+        <v>0.5572025495750719</v>
       </c>
       <c r="N156" t="n">
-        <v>0.5565946137491142</v>
+        <v>0.5572025495750719</v>
       </c>
       <c r="O156" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P156" t="n">
-        <v>-0.04340538625088364</v>
+        <v>-0.042797450424926</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -13225,10 +13225,10 @@
         <v>8</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9050318922749823</v>
+        <v>0.9050991501416431</v>
       </c>
       <c r="H157" t="n">
-        <v>8.920891211906451</v>
+        <v>8.9210835694051</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -13247,16 +13247,16 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>0.62089121190645</v>
+        <v>0.6210835694050996</v>
       </c>
       <c r="N157" t="n">
-        <v>0.62089121190645</v>
+        <v>0.6210835694050996</v>
       </c>
       <c r="O157" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P157" t="n">
-        <v>-0.04570340184266364</v>
+        <v>-0.04611898016997173</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>8</v>
       </c>
       <c r="G158" t="n">
-        <v>0.8951098511693835</v>
+        <v>0.8951841359773371</v>
       </c>
       <c r="H158" t="n">
-        <v>8.85750708717222</v>
+        <v>8.857613314447594</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -13318,16 +13318,16 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>0.6875070871722198</v>
+        <v>0.687613314447594</v>
       </c>
       <c r="N158" t="n">
-        <v>0.6875070871722198</v>
+        <v>0.687613314447594</v>
       </c>
       <c r="O158" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P158" t="n">
-        <v>-0.06338412473423105</v>
+        <v>-0.06347025495750636</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -13367,10 +13367,10 @@
         <v>8</v>
       </c>
       <c r="G159" t="n">
-        <v>0.888731396172927</v>
+        <v>0.8888101983002833</v>
       </c>
       <c r="H159" t="n">
-        <v>8.788701275690999</v>
+        <v>8.789490084985836</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -13389,16 +13389,16 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>0.8387012756909984</v>
+        <v>0.8394900849858358</v>
       </c>
       <c r="N159" t="n">
-        <v>0.8387012756909984</v>
+        <v>0.8394900849858358</v>
       </c>
       <c r="O159" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P159" t="n">
-        <v>-0.06880581148122111</v>
+        <v>-0.06812322946175797</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -13438,10 +13438,10 @@
         <v>8</v>
       </c>
       <c r="G160" t="n">
-        <v>0.8653437278525868</v>
+        <v>0.8654390934844193</v>
       </c>
       <c r="H160" t="n">
-        <v>8.429532246633594</v>
+        <v>8.430545325779036</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -13460,16 +13460,16 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>0.659532246633594</v>
+        <v>0.6605453257790366</v>
       </c>
       <c r="N160" t="n">
-        <v>0.659532246633594</v>
+        <v>0.6605453257790366</v>
       </c>
       <c r="O160" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P160" t="n">
-        <v>-0.359169029057405</v>
+        <v>-0.3589447592067998</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -13509,10 +13509,10 @@
         <v>8</v>
       </c>
       <c r="G161" t="n">
-        <v>0.8582565556343019</v>
+        <v>0.8583569405099151</v>
       </c>
       <c r="H161" t="n">
-        <v>8.22305811481219</v>
+        <v>8.226359773371106</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -13531,16 +13531,16 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>0.4930581148121895</v>
+        <v>0.4963597733711058</v>
       </c>
       <c r="N161" t="n">
-        <v>0.4930581148121895</v>
+        <v>0.4963597733711058</v>
       </c>
       <c r="O161" t="n">
         <v>-0.03999999999999915</v>
       </c>
       <c r="P161" t="n">
-        <v>-0.2064741318214036</v>
+        <v>-0.2041855524079299</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -13580,10 +13580,10 @@
         <v>8</v>
       </c>
       <c r="G162" t="n">
-        <v>0.8490432317505315</v>
+        <v>0.8491501416430595</v>
       </c>
       <c r="H162" t="n">
-        <v>8.00458185683912</v>
+        <v>8.006416430594898</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -13602,16 +13602,16 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>0.3045818568391203</v>
+        <v>0.306416430594898</v>
       </c>
       <c r="N162" t="n">
-        <v>0.3045818568391203</v>
+        <v>0.306416430594898</v>
       </c>
       <c r="O162" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P162" t="n">
-        <v>-0.2184762579730695</v>
+        <v>-0.2199433427762081</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -13651,10 +13651,10 @@
         <v>8</v>
       </c>
       <c r="G163" t="n">
-        <v>0.8440822111977321</v>
+        <v>0.8441926345609065</v>
       </c>
       <c r="H163" t="n">
-        <v>7.943063430191353</v>
+        <v>7.945432011331446</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -13673,16 +13673,16 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>0.3030634301913535</v>
+        <v>0.3054320113314466</v>
       </c>
       <c r="N163" t="n">
-        <v>0.3030634301913535</v>
+        <v>0.3054320113314466</v>
       </c>
       <c r="O163" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P163" t="n">
-        <v>-0.0615184266477673</v>
+        <v>-0.06098441926345188</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -13722,10 +13722,10 @@
         <v>8</v>
       </c>
       <c r="G164" t="n">
-        <v>0.8377037562012757</v>
+        <v>0.8378186968838527</v>
       </c>
       <c r="H164" t="n">
-        <v>7.836663713678242</v>
+        <v>7.838307365439094</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -13744,16 +13744,16 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>0.2766637136782428</v>
+        <v>0.278307365439094</v>
       </c>
       <c r="N164" t="n">
-        <v>0.2766637136782428</v>
+        <v>0.278307365439094</v>
       </c>
       <c r="O164" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P164" t="n">
-        <v>-0.1063997165131108</v>
+        <v>-0.1071246458923527</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -13793,10 +13793,10 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>0.8348688873139617</v>
+        <v>0.8349858356940509</v>
       </c>
       <c r="H165" t="n">
-        <v>7.828862508858966</v>
+        <v>7.829029745042493</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -13815,16 +13815,16 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>0.3488625088589652</v>
+        <v>0.3490297450424924</v>
       </c>
       <c r="N165" t="n">
-        <v>0.3488625088589652</v>
+        <v>0.3490297450424924</v>
       </c>
       <c r="O165" t="n">
         <v>-0.07999999999999918</v>
       </c>
       <c r="P165" t="n">
-        <v>-0.007801204819276819</v>
+        <v>-0.009277620396600739</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -13864,10 +13864,10 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>0.8263642806520198</v>
+        <v>0.8264872521246459</v>
       </c>
       <c r="H166" t="n">
-        <v>7.751107370659107</v>
+        <v>7.752514164305949</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -13886,16 +13886,16 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>0.381107370659107</v>
+        <v>0.3825141643059489</v>
       </c>
       <c r="N166" t="n">
-        <v>0.381107370659107</v>
+        <v>0.3825141643059489</v>
       </c>
       <c r="O166" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P166" t="n">
-        <v>-0.07775513819985846</v>
+        <v>-0.07651558073654385</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -15065,10 +15065,10 @@
         <v>8</v>
       </c>
       <c r="G183" t="n">
-        <v>0.8001417434443657</v>
+        <v>0.8002832861189801</v>
       </c>
       <c r="H183" t="n">
-        <v>5.551307583274274</v>
+        <v>5.551365084985836</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -15087,16 +15087,16 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>0.3363075832742739</v>
+        <v>0.3363650849858359</v>
       </c>
       <c r="N183" t="n">
-        <v>0.3363075832742739</v>
+        <v>0.3363650849858359</v>
       </c>
       <c r="O183" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P183" t="n">
-        <v>-0.09277265498781517</v>
+        <v>-0.09271515327625313</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -15136,10 +15136,10 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>0.8532955350815025</v>
+        <v>0.853399433427762</v>
       </c>
       <c r="H184" t="n">
-        <v>5.758210489014884</v>
+        <v>5.758548158640227</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -15158,16 +15158,16 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>0.5932104890148837</v>
+        <v>0.5935481586402265</v>
       </c>
       <c r="N184" t="n">
-        <v>0.5932104890148837</v>
+        <v>0.5935481586402265</v>
       </c>
       <c r="O184" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P184" t="n">
-        <v>0.20690290574061</v>
+        <v>0.2071830736543907</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -15207,10 +15207,10 @@
         <v>8</v>
       </c>
       <c r="G185" t="n">
-        <v>0.8674698795180723</v>
+        <v>0.8675637393767706</v>
       </c>
       <c r="H185" t="n">
-        <v>5.798915662650603</v>
+        <v>5.799373229461756</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -15229,16 +15229,16 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>0.6789156626506028</v>
+        <v>0.6793732294617563</v>
       </c>
       <c r="N185" t="n">
-        <v>0.6789156626506028</v>
+        <v>0.6793732294617563</v>
       </c>
       <c r="O185" t="n">
         <v>-0.04499999999999993</v>
       </c>
       <c r="P185" t="n">
-        <v>0.04070517363571913</v>
+        <v>0.04082507082152986</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -15278,10 +15278,10 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>0.8646350106307583</v>
+        <v>0.8647308781869688</v>
       </c>
       <c r="H186" t="n">
-        <v>5.785095676824946</v>
+        <v>5.785563031161472</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -15300,16 +15300,16 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>0.7050956768249463</v>
+        <v>0.7055630311614722</v>
       </c>
       <c r="N186" t="n">
-        <v>0.7050956768249463</v>
+        <v>0.7055630311614722</v>
       </c>
       <c r="O186" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P186" t="n">
-        <v>-0.01381998582565647</v>
+        <v>-0.01381019830028407</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -15349,10 +15349,10 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8433734939759037</v>
+        <v>0.8434844192634561</v>
       </c>
       <c r="H187" t="n">
-        <v>5.682981927710844</v>
+        <v>5.683162181303116</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -15371,16 +15371,16 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>0.2529819277108443</v>
+        <v>0.2531621813031162</v>
       </c>
       <c r="N187" t="n">
-        <v>0.2529819277108443</v>
+        <v>0.2531621813031162</v>
       </c>
       <c r="O187" t="n">
         <v>0.3499999999999996</v>
       </c>
       <c r="P187" t="n">
-        <v>-0.1021137491141024</v>
+        <v>-0.1024008498583564</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -15420,10 +15420,10 @@
         <v>8</v>
       </c>
       <c r="G188" t="n">
-        <v>0.7958894401133948</v>
+        <v>0.7960339943342776</v>
       </c>
       <c r="H188" t="n">
-        <v>5.540761871013466</v>
+        <v>5.542053824362605</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -15442,16 +15442,16 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.06173812898653441</v>
+        <v>-0.06044617563739507</v>
       </c>
       <c r="N188" t="n">
-        <v>0.06173812898653441</v>
+        <v>0.06044617563739507</v>
       </c>
       <c r="O188" t="n">
         <v>0.1725000000000003</v>
       </c>
       <c r="P188" t="n">
-        <v>-0.1422200566973784</v>
+        <v>-0.1411083569405109</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -15491,10 +15491,10 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>0.7491141034727143</v>
+        <v>0.7492917847025495</v>
       </c>
       <c r="H189" t="n">
-        <v>5.390207299787385</v>
+        <v>5.391795325779037</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -15513,16 +15513,16 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.1597927002126145</v>
+        <v>-0.1582046742209631</v>
       </c>
       <c r="N189" t="n">
-        <v>0.1597927002126145</v>
+        <v>0.1582046742209631</v>
       </c>
       <c r="O189" t="n">
         <v>-0.05250000000000021</v>
       </c>
       <c r="P189" t="n">
-        <v>-0.1505545712260803</v>
+        <v>-0.1502584985835682</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -15562,10 +15562,10 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>0.7214741318214033</v>
+        <v>0.7216713881019831</v>
       </c>
       <c r="H190" t="n">
-        <v>5.28119773210489</v>
+        <v>5.281358002832861</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -15584,16 +15584,16 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>0.001197732104889937</v>
+        <v>0.001358002832860805</v>
       </c>
       <c r="N190" t="n">
-        <v>0.001197732104889937</v>
+        <v>0.001358002832860805</v>
       </c>
       <c r="O190" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P190" t="n">
-        <v>-0.1090095676824951</v>
+        <v>-0.1104373229461757</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -15633,10 +15633,10 @@
         <v>8</v>
       </c>
       <c r="G191" t="n">
-        <v>0.7165131112686038</v>
+        <v>0.71671388101983</v>
       </c>
       <c r="H191" t="n">
-        <v>5.27858345145287</v>
+        <v>5.278665014164306</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -15655,16 +15655,16 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>0.2535834514528714</v>
+        <v>0.2536650141643078</v>
       </c>
       <c r="N191" t="n">
-        <v>0.2535834514528714</v>
+        <v>0.2536650141643078</v>
       </c>
       <c r="O191" t="n">
         <v>-0.2550000000000017</v>
       </c>
       <c r="P191" t="n">
-        <v>-0.002614280652020184</v>
+        <v>-0.002692988668554719</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -15704,10 +15704,10 @@
         <v>8</v>
       </c>
       <c r="G192" t="n">
-        <v>0.7250177179305457</v>
+        <v>0.7252124645892352</v>
       </c>
       <c r="H192" t="n">
-        <v>5.29196137491141</v>
+        <v>5.292910764872522</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -15726,16 +15726,16 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>0.4419613749114104</v>
+        <v>0.4429107648725221</v>
       </c>
       <c r="N192" t="n">
-        <v>0.4419613749114104</v>
+        <v>0.4429107648725221</v>
       </c>
       <c r="O192" t="n">
         <v>-0.1749999999999989</v>
       </c>
       <c r="P192" t="n">
-        <v>0.01337792345854005</v>
+        <v>0.01424575070821543</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -15775,10 +15775,10 @@
         <v>8</v>
       </c>
       <c r="G193" t="n">
-        <v>0.7321048901488306</v>
+        <v>0.7322946175637394</v>
       </c>
       <c r="H193" t="n">
-        <v>5.335028348688872</v>
+        <v>5.337340651558072</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -15797,16 +15797,16 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>0.7650283486888716</v>
+        <v>0.7673406515580714</v>
       </c>
       <c r="N193" t="n">
-        <v>0.7650283486888716</v>
+        <v>0.7673406515580714</v>
       </c>
       <c r="O193" t="n">
         <v>-0.2799999999999994</v>
       </c>
       <c r="P193" t="n">
-        <v>0.04306697377746183</v>
+        <v>0.04442988668554992</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -15846,10 +15846,10 @@
         <v>8</v>
       </c>
       <c r="G194" t="n">
-        <v>0.7228915662650602</v>
+        <v>0.7230878186968839</v>
       </c>
       <c r="H194" t="n">
-        <v>5.282349397590361</v>
+        <v>5.282553116147309</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15868,16 +15868,16 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>0.8523493975903618</v>
+        <v>0.852553116147309</v>
       </c>
       <c r="N194" t="n">
-        <v>0.8523493975903618</v>
+        <v>0.852553116147309</v>
       </c>
       <c r="O194" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P194" t="n">
-        <v>-0.0526789510985104</v>
+        <v>-0.05478753541076298</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -15917,10 +15917,10 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>0.6952515946137491</v>
+        <v>0.6954674220963173</v>
       </c>
       <c r="H195" t="n">
-        <v>5.214783841247342</v>
+        <v>5.215</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -15939,16 +15939,16 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>0.7347838412473413</v>
+        <v>0.7349999999999994</v>
       </c>
       <c r="N195" t="n">
-        <v>0.7347838412473413</v>
+        <v>0.7349999999999994</v>
       </c>
       <c r="O195" t="n">
         <v>0.05000000000000071</v>
       </c>
       <c r="P195" t="n">
-        <v>-0.06756555634301975</v>
+        <v>-0.06755311614730886</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -15988,10 +15988,10 @@
         <v>8</v>
       </c>
       <c r="G196" t="n">
-        <v>0.6569808646350106</v>
+        <v>0.6572237960339944</v>
       </c>
       <c r="H196" t="n">
-        <v>5.125187810063784</v>
+        <v>5.125977337110482</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -16010,16 +16010,16 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>0.3351878100637844</v>
+        <v>0.3359773371104815</v>
       </c>
       <c r="N196" t="n">
-        <v>0.3351878100637844</v>
+        <v>0.3359773371104815</v>
       </c>
       <c r="O196" t="n">
         <v>0.3099999999999996</v>
       </c>
       <c r="P196" t="n">
-        <v>-0.0895960311835573</v>
+        <v>-0.08902266288951832</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -17189,10 +17189,10 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>0.7554925584691708</v>
+        <v>0.7556657223796034</v>
       </c>
       <c r="H213" t="n">
-        <v>5.969731868651075</v>
+        <v>5.969959867799811</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -17211,16 +17211,16 @@
         <v>1</v>
       </c>
       <c r="M213" t="n">
-        <v>-2.767768131348926</v>
+        <v>-2.76754013220019</v>
       </c>
       <c r="N213" t="n">
-        <v>2.767768131348926</v>
+        <v>2.76754013220019</v>
       </c>
       <c r="O213" t="n">
         <v>-0.125</v>
       </c>
       <c r="P213" t="n">
-        <v>-1.39522170528025</v>
+        <v>-1.394993706131514</v>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
@@ -17260,10 +17260,10 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>0.7547838412473423</v>
+        <v>0.7549575070821529</v>
       </c>
       <c r="H214" t="n">
-        <v>5.968798724309001</v>
+        <v>5.969027384324835</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -17282,16 +17282,16 @@
         <v>1</v>
       </c>
       <c r="M214" t="n">
-        <v>-2.618701275690998</v>
+        <v>-2.618472615675164</v>
       </c>
       <c r="N214" t="n">
-        <v>2.618701275690998</v>
+        <v>2.618472615675164</v>
       </c>
       <c r="O214" t="n">
         <v>-0.1500000000000021</v>
       </c>
       <c r="P214" t="n">
-        <v>-0.0009331443420741437</v>
+        <v>-0.000932483474976209</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>0.7654145995747696</v>
+        <v>0.7655807365439093</v>
       </c>
       <c r="H215" t="n">
-        <v>6.00677533664068</v>
+        <v>6.008087818696884</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -17353,16 +17353,16 @@
         <v>1</v>
       </c>
       <c r="M215" t="n">
-        <v>-2.47322466335932</v>
+        <v>-2.471912181303116</v>
       </c>
       <c r="N215" t="n">
-        <v>2.47322466335932</v>
+        <v>2.471912181303116</v>
       </c>
       <c r="O215" t="n">
         <v>-0.1074999999999982</v>
       </c>
       <c r="P215" t="n">
-        <v>0.03797661233167915</v>
+        <v>0.03906043437204954</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -17402,10 +17402,10 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>0.7859673990077959</v>
+        <v>0.7861189801699717</v>
       </c>
       <c r="H216" t="n">
-        <v>6.098499291282778</v>
+        <v>6.100339943342776</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -17424,16 +17424,16 @@
         <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>-2.111500708717223</v>
+        <v>-2.109660056657225</v>
       </c>
       <c r="N216" t="n">
-        <v>2.111500708717223</v>
+        <v>2.109660056657225</v>
       </c>
       <c r="O216" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P216" t="n">
-        <v>0.09172395464209782</v>
+        <v>0.09225212464589205</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -17473,10 +17473,10 @@
         <v>8</v>
       </c>
       <c r="G217" t="n">
-        <v>0.8086463501063076</v>
+        <v>0.8087818696883853</v>
       </c>
       <c r="H217" t="n">
-        <v>6.198870777226554</v>
+        <v>6.199584513692162</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -17495,16 +17495,16 @@
         <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>-1.961129222773446</v>
+        <v>-1.960415486307838</v>
       </c>
       <c r="N217" t="n">
-        <v>1.961129222773446</v>
+        <v>1.960415486307838</v>
       </c>
       <c r="O217" t="n">
         <v>-0.05000000000000071</v>
       </c>
       <c r="P217" t="n">
-        <v>0.1003714859437759</v>
+        <v>0.09924457034938605</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -17544,10 +17544,10 @@
         <v>8</v>
       </c>
       <c r="G218" t="n">
-        <v>0.8270729978738484</v>
+        <v>0.8271954674220963</v>
       </c>
       <c r="H218" t="n">
-        <v>6.292584455468935</v>
+        <v>6.293229461756374</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -17566,16 +17566,16 @@
         <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>-1.637415544531065</v>
+        <v>-1.636770538243626</v>
       </c>
       <c r="N218" t="n">
-        <v>1.637415544531065</v>
+        <v>1.636770538243626</v>
       </c>
       <c r="O218" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P218" t="n">
-        <v>0.09371367824238153</v>
+        <v>0.09364494806421142</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -17615,10 +17615,10 @@
         <v>8</v>
       </c>
       <c r="G219" t="n">
-        <v>0.8440822111977321</v>
+        <v>0.8441926345609065</v>
       </c>
       <c r="H219" t="n">
-        <v>6.384562367115521</v>
+        <v>6.384780453257791</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -17637,16 +17637,16 @@
         <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>-1.605437632884479</v>
+        <v>-1.60521954674221</v>
       </c>
       <c r="N219" t="n">
-        <v>1.605437632884479</v>
+        <v>1.60521954674221</v>
       </c>
       <c r="O219" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P219" t="n">
-        <v>0.09197791164658575</v>
+        <v>0.09155099150141677</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -17686,10 +17686,10 @@
         <v>8</v>
       </c>
       <c r="G220" t="n">
-        <v>0.851169383416017</v>
+        <v>0.8512747875354107</v>
       </c>
       <c r="H220" t="n">
-        <v>6.442714386959604</v>
+        <v>6.445212464589235</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -17708,16 +17708,16 @@
         <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>-1.547285613040397</v>
+        <v>-1.544787535410765</v>
       </c>
       <c r="N220" t="n">
-        <v>1.547285613040397</v>
+        <v>1.544787535410765</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
       </c>
       <c r="P220" t="n">
-        <v>0.05815201984408258</v>
+        <v>0.06043201133144471</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -17757,10 +17757,10 @@
         <v>8</v>
       </c>
       <c r="G221" t="n">
-        <v>0.8419560595322466</v>
+        <v>0.8420679886685553</v>
       </c>
       <c r="H221" t="n">
-        <v>6.380363217576187</v>
+        <v>6.380584277620397</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -17779,16 +17779,16 @@
         <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>-1.477136782423813</v>
+        <v>-1.476915722379603</v>
       </c>
       <c r="N221" t="n">
-        <v>1.477136782423813</v>
+        <v>1.476915722379603</v>
       </c>
       <c r="O221" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P221" t="n">
-        <v>-0.06235116938341623</v>
+        <v>-0.06462818696883854</v>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
@@ -17828,10 +17828,10 @@
         <v>8</v>
       </c>
       <c r="G222" t="n">
-        <v>0.8221119773210489</v>
+        <v>0.8222379603399433</v>
       </c>
       <c r="H222" t="n">
-        <v>6.248228206945429</v>
+        <v>6.248559962228518</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -17850,16 +17850,16 @@
         <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>-1.491771793054571</v>
+        <v>-1.491440037771483</v>
       </c>
       <c r="N222" t="n">
-        <v>1.491771793054571</v>
+        <v>1.491440037771483</v>
       </c>
       <c r="O222" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.1321350106307584</v>
+        <v>-0.1320243153918792</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -17899,10 +17899,10 @@
         <v>8</v>
       </c>
       <c r="G223" t="n">
-        <v>0.8043940467753367</v>
+        <v>0.8045325779036827</v>
       </c>
       <c r="H223" t="n">
-        <v>6.178237656508387</v>
+        <v>6.178602455146364</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -17921,16 +17921,16 @@
         <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>-1.441762343491614</v>
+        <v>-1.441397544853636</v>
       </c>
       <c r="N223" t="n">
-        <v>1.441762343491614</v>
+        <v>1.441397544853636</v>
       </c>
       <c r="O223" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.06999055043704239</v>
+        <v>-0.06995750708215365</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -17970,10 +17970,10 @@
         <v>8</v>
       </c>
       <c r="G224" t="n">
-        <v>0.7795889440113395</v>
+        <v>0.7797450424929179</v>
       </c>
       <c r="H224" t="n">
-        <v>6.076094082211197</v>
+        <v>6.076248229461756</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -17992,16 +17992,16 @@
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>-1.323905917788803</v>
+        <v>-1.323751770538244</v>
       </c>
       <c r="N224" t="n">
-        <v>1.323905917788803</v>
+        <v>1.323751770538244</v>
       </c>
       <c r="O224" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.1021435742971892</v>
+        <v>-0.1023542256846079</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -18041,10 +18041,10 @@
         <v>8</v>
       </c>
       <c r="G225" t="n">
-        <v>0.7519489723600283</v>
+        <v>0.7521246458923513</v>
       </c>
       <c r="H225" t="n">
-        <v>5.965066146940704</v>
+        <v>5.965297450424929</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -18063,16 +18063,16 @@
         <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>-1.394933853059296</v>
+        <v>-1.394702549575071</v>
       </c>
       <c r="N225" t="n">
-        <v>1.394933853059296</v>
+        <v>1.394702549575071</v>
       </c>
       <c r="O225" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.111027935270493</v>
+        <v>-0.1109507790368269</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>8</v>
       </c>
       <c r="G226" t="n">
-        <v>0.7271438695960312</v>
+        <v>0.7273371104815864</v>
       </c>
       <c r="H226" t="n">
-        <v>5.824436569808647</v>
+        <v>5.825963172804533</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -18134,16 +18134,16 @@
         <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>-1.555563430191353</v>
+        <v>-1.554036827195467</v>
       </c>
       <c r="N226" t="n">
-        <v>1.555563430191353</v>
+        <v>1.554036827195467</v>
       </c>
       <c r="O226" t="n">
         <v>0.01999999999999957</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.1406295771320574</v>
+        <v>-0.1393342776203959</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -19313,10 +19313,10 @@
         <v>8</v>
       </c>
       <c r="G243" t="n">
-        <v>0.8284904323175053</v>
+        <v>0.8286118980169972</v>
       </c>
       <c r="H243" t="n">
-        <v>5.561174698795179</v>
+        <v>5.563590651558073</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -19335,16 +19335,16 @@
         <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>1.571174698795179</v>
+        <v>1.573590651558073</v>
       </c>
       <c r="N243" t="n">
-        <v>1.571174698795179</v>
+        <v>1.573590651558073</v>
       </c>
       <c r="O243" t="n">
         <v>-0.1624999999999996</v>
       </c>
       <c r="P243" t="n">
-        <v>-1.599743311015613</v>
+        <v>-1.597327358252719</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -19384,10 +19384,10 @@
         <v>8</v>
       </c>
       <c r="G244" t="n">
-        <v>0.7044649184975195</v>
+        <v>0.7046742209631728</v>
       </c>
       <c r="H244" t="n">
-        <v>4.930662650602409</v>
+        <v>4.931303116147308</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -19406,16 +19406,16 @@
         <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>1.108162650602409</v>
+        <v>1.108803116147309</v>
       </c>
       <c r="N244" t="n">
-        <v>1.108162650602409</v>
+        <v>1.108803116147309</v>
       </c>
       <c r="O244" t="n">
         <v>-0.1675000000000004</v>
       </c>
       <c r="P244" t="n">
-        <v>-0.6305120481927702</v>
+        <v>-0.6322875354107644</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -19455,10 +19455,10 @@
         <v>8</v>
       </c>
       <c r="G245" t="n">
-        <v>0.6158752657689582</v>
+        <v>0.6154390934844193</v>
       </c>
       <c r="H245" t="n">
-        <v>4.630692771084338</v>
+        <v>4.630247875354108</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -19477,16 +19477,16 @@
         <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>0.8506927710843377</v>
+        <v>0.8502478753541083</v>
       </c>
       <c r="N245" t="n">
-        <v>0.8506927710843377</v>
+        <v>0.8502478753541083</v>
       </c>
       <c r="O245" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.2999698795180716</v>
+        <v>-0.3010552407932003</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -19526,10 +19526,10 @@
         <v>8</v>
       </c>
       <c r="G246" t="n">
-        <v>0.5939050318922749</v>
+        <v>0.5934844192634561</v>
       </c>
       <c r="H246" t="n">
-        <v>4.565331325301204</v>
+        <v>4.561041076487252</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -19548,16 +19548,16 @@
         <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>0.8853313253012041</v>
+        <v>0.8810410764872523</v>
       </c>
       <c r="N246" t="n">
-        <v>0.8853313253012041</v>
+        <v>0.8810410764872523</v>
       </c>
       <c r="O246" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.0653614457831333</v>
+        <v>-0.06920679886685566</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -19597,10 +19597,10 @@
         <v>8</v>
       </c>
       <c r="G247" t="n">
-        <v>0.6343019135364989</v>
+        <v>0.6338526912181303</v>
       </c>
       <c r="H247" t="n">
-        <v>4.723463855421687</v>
+        <v>4.722089235127479</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -19619,16 +19619,16 @@
         <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>1.143463855421687</v>
+        <v>1.142089235127479</v>
       </c>
       <c r="N247" t="n">
-        <v>1.143463855421687</v>
+        <v>1.142089235127479</v>
       </c>
       <c r="O247" t="n">
         <v>-0.1000000000000001</v>
       </c>
       <c r="P247" t="n">
-        <v>0.1581325301204828</v>
+        <v>0.1610481586402264</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -19668,10 +19668,10 @@
         <v>8</v>
       </c>
       <c r="G248" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.646600566572238</v>
       </c>
       <c r="H248" t="n">
-        <v>4.76</v>
+        <v>4.759532577903682</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19690,16 +19690,16 @@
         <v>1</v>
       </c>
       <c r="M248" t="n">
-        <v>1.3675</v>
+        <v>1.367032577903682</v>
       </c>
       <c r="N248" t="n">
-        <v>1.3675</v>
+        <v>1.367032577903682</v>
       </c>
       <c r="O248" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P248" t="n">
-        <v>0.03653614457831278</v>
+        <v>0.03744334277620354</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -19739,10 +19739,10 @@
         <v>8</v>
       </c>
       <c r="G249" t="n">
-        <v>0.5967399007795889</v>
+        <v>0.5963172804532578</v>
       </c>
       <c r="H249" t="n">
-        <v>4.594246987951808</v>
+        <v>4.589936260623229</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19761,16 +19761,16 @@
         <v>1</v>
       </c>
       <c r="M249" t="n">
-        <v>1.314246987951808</v>
+        <v>1.30993626062323</v>
       </c>
       <c r="N249" t="n">
-        <v>1.314246987951808</v>
+        <v>1.30993626062323</v>
       </c>
       <c r="O249" t="n">
         <v>-0.1125000000000003</v>
       </c>
       <c r="P249" t="n">
-        <v>-0.1657530120481923</v>
+        <v>-0.1695963172804529</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -19810,10 +19810,10 @@
         <v>8</v>
       </c>
       <c r="G250" t="n">
-        <v>0.4911410347271439</v>
+        <v>0.4907932011331445</v>
       </c>
       <c r="H250" t="n">
-        <v>4.15328313253012</v>
+        <v>4.151154390934845</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19832,16 +19832,16 @@
         <v>1</v>
       </c>
       <c r="M250" t="n">
-        <v>1.00328313253012</v>
+        <v>1.001154390934845</v>
       </c>
       <c r="N250" t="n">
-        <v>1.00328313253012</v>
+        <v>1.001154390934845</v>
       </c>
       <c r="O250" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P250" t="n">
-        <v>-0.4409638554216873</v>
+        <v>-0.438781869688385</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -19881,10 +19881,10 @@
         <v>8</v>
       </c>
       <c r="G251" t="n">
-        <v>0.3919206236711552</v>
+        <v>0.391643059490085</v>
       </c>
       <c r="H251" t="n">
-        <v>3.806777108433735</v>
+        <v>3.80592776203966</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19903,16 +19903,16 @@
         <v>1</v>
       </c>
       <c r="M251" t="n">
-        <v>0.8617771084337353</v>
+        <v>0.8609277620396605</v>
       </c>
       <c r="N251" t="n">
-        <v>0.8617771084337353</v>
+        <v>0.8609277620396605</v>
       </c>
       <c r="O251" t="n">
         <v>-0.2050000000000001</v>
       </c>
       <c r="P251" t="n">
-        <v>-0.3465060240963851</v>
+        <v>-0.3452266288951842</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         <v>8</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3373493975903614</v>
+        <v>0.3371104815864023</v>
       </c>
       <c r="H252" t="n">
-        <v>3.643654618473895</v>
+        <v>3.642842304060435</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19974,16 +19974,16 @@
         <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>0.8036546184738955</v>
+        <v>0.8028423040604347</v>
       </c>
       <c r="N252" t="n">
-        <v>0.8036546184738955</v>
+        <v>0.8028423040604347</v>
       </c>
       <c r="O252" t="n">
         <v>-0.105</v>
       </c>
       <c r="P252" t="n">
-        <v>-0.1631224899598398</v>
+        <v>-0.1630854579792258</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -20023,10 +20023,10 @@
         <v>8</v>
       </c>
       <c r="G253" t="n">
-        <v>0.3479801559177888</v>
+        <v>0.3477337110481586</v>
       </c>
       <c r="H253" t="n">
-        <v>3.679799196787149</v>
+        <v>3.678961284230406</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -20045,16 +20045,16 @@
         <v>1</v>
       </c>
       <c r="M253" t="n">
-        <v>0.9097991967871488</v>
+        <v>0.9089612842304065</v>
       </c>
       <c r="N253" t="n">
-        <v>0.9097991967871488</v>
+        <v>0.9089612842304065</v>
       </c>
       <c r="O253" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P253" t="n">
-        <v>0.03614457831325346</v>
+        <v>0.03611898016997195</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -20094,10 +20094,10 @@
         <v>8</v>
       </c>
       <c r="G254" t="n">
-        <v>0.4953933380581148</v>
+        <v>0.495042492917847</v>
       </c>
       <c r="H254" t="n">
-        <v>4.178253012048193</v>
+        <v>4.177160056657224</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -20116,16 +20116,16 @@
         <v>1</v>
       </c>
       <c r="M254" t="n">
-        <v>1.358253012048193</v>
+        <v>1.357160056657224</v>
       </c>
       <c r="N254" t="n">
-        <v>1.358253012048193</v>
+        <v>1.357160056657224</v>
       </c>
       <c r="O254" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P254" t="n">
-        <v>0.4984538152610445</v>
+        <v>0.4981987724268171</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -20165,10 +20165,10 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>0.6959603118355776</v>
+        <v>0.6961756373937678</v>
       </c>
       <c r="H255" t="n">
-        <v>4.904759036144578</v>
+        <v>4.905297450424929</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -20187,16 +20187,16 @@
         <v>1</v>
       </c>
       <c r="M255" t="n">
-        <v>2.154759036144578</v>
+        <v>2.155297450424929</v>
       </c>
       <c r="N255" t="n">
-        <v>2.154759036144578</v>
+        <v>2.155297450424929</v>
       </c>
       <c r="O255" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P255" t="n">
-        <v>0.726506024096385</v>
+        <v>0.7281373937677058</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
@@ -20236,10 +20236,10 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>0.7880935506732814</v>
+        <v>0.7882436260623229</v>
       </c>
       <c r="H256" t="n">
-        <v>5.201626506024096</v>
+        <v>5.203080736543908</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -20258,16 +20258,16 @@
         <v>1</v>
       </c>
       <c r="M256" t="n">
-        <v>2.451626506024096</v>
+        <v>2.453080736543908</v>
       </c>
       <c r="N256" t="n">
-        <v>2.451626506024096</v>
+        <v>2.453080736543908</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
       </c>
       <c r="P256" t="n">
-        <v>0.2968674698795173</v>
+        <v>0.2977832861189782</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -21437,10 +21437,10 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>0.9425939050318922</v>
+        <v>0.9426345609065155</v>
       </c>
       <c r="H273" t="n">
-        <v>6.912831325301204</v>
+        <v>6.913055949008498</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -21459,16 +21459,16 @@
         <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>-0.8521686746987953</v>
+        <v>-0.8519440509915013</v>
       </c>
       <c r="N273" t="n">
-        <v>0.8521686746987953</v>
+        <v>0.8519440509915013</v>
       </c>
       <c r="O273" t="n">
         <v>0.0550000000000006</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.9781030358293723</v>
+        <v>-0.9778784121220783</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -21508,10 +21508,10 @@
         <v>8</v>
       </c>
       <c r="G274" t="n">
-        <v>0.9390503189227498</v>
+        <v>0.9390934844192634</v>
       </c>
       <c r="H274" t="n">
-        <v>6.848253012048192</v>
+        <v>6.84849150141643</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -21530,16 +21530,16 @@
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>-0.9317469879518079</v>
+        <v>-0.93150849858357</v>
       </c>
       <c r="N274" t="n">
-        <v>0.9317469879518079</v>
+        <v>0.93150849858357</v>
       </c>
       <c r="O274" t="n">
         <v>0.01500000000000057</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.064578313253012</v>
+        <v>-0.06456444759206814</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -21579,10 +21579,10 @@
         <v>8</v>
       </c>
       <c r="G275" t="n">
-        <v>0.9355067328136074</v>
+        <v>0.9355524079320113</v>
       </c>
       <c r="H275" t="n">
-        <v>6.829337349397591</v>
+        <v>6.829463526912181</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -21601,16 +21601,16 @@
         <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>-0.9406626506024089</v>
+        <v>-0.9405364730878185</v>
       </c>
       <c r="N275" t="n">
-        <v>0.9406626506024089</v>
+        <v>0.9405364730878185</v>
       </c>
       <c r="O275" t="n">
         <v>-0.01000000000000068</v>
       </c>
       <c r="P275" t="n">
-        <v>-0.01891566265060174</v>
+        <v>-0.0190279745042492</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -21650,10 +21650,10 @@
         <v>8</v>
       </c>
       <c r="G276" t="n">
-        <v>0.9319631467044649</v>
+        <v>0.9320113314447592</v>
       </c>
       <c r="H276" t="n">
-        <v>6.818192771084337</v>
+        <v>6.81872521246459</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -21672,16 +21672,16 @@
         <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>-0.8818072289156635</v>
+        <v>-0.8812747875354106</v>
       </c>
       <c r="N276" t="n">
-        <v>0.8818072289156635</v>
+        <v>0.8812747875354106</v>
       </c>
       <c r="O276" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P276" t="n">
-        <v>-0.01114457831325399</v>
+        <v>-0.01073831444759143</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -21721,10 +21721,10 @@
         <v>8</v>
       </c>
       <c r="G277" t="n">
-        <v>0.9284195605953225</v>
+        <v>0.9284702549575071</v>
       </c>
       <c r="H277" t="n">
-        <v>6.779036144578313</v>
+        <v>6.779596317280453</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -21743,16 +21743,16 @@
         <v>1</v>
       </c>
       <c r="M277" t="n">
-        <v>-0.8109638554216865</v>
+        <v>-0.8104036827195467</v>
       </c>
       <c r="N277" t="n">
-        <v>0.8109638554216865</v>
+        <v>0.8104036827195467</v>
       </c>
       <c r="O277" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P277" t="n">
-        <v>-0.03915662650602325</v>
+        <v>-0.03912889518413643</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -21792,10 +21792,10 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>0.92487597448618</v>
+        <v>0.9249291784702549</v>
       </c>
       <c r="H278" t="n">
-        <v>6.749879518072288</v>
+        <v>6.750233711048158</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -21814,16 +21814,16 @@
         <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>-0.700120481927712</v>
+        <v>-0.6997662889518423</v>
       </c>
       <c r="N278" t="n">
-        <v>0.700120481927712</v>
+        <v>0.6997662889518423</v>
       </c>
       <c r="O278" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P278" t="n">
-        <v>-0.02915662650602524</v>
+        <v>-0.02936260623229536</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -21863,10 +21863,10 @@
         <v>8</v>
       </c>
       <c r="G279" t="n">
-        <v>0.9213323883770376</v>
+        <v>0.9213881019830028</v>
       </c>
       <c r="H279" t="n">
-        <v>6.713574297188755</v>
+        <v>6.713779508970727</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -21885,16 +21885,16 @@
         <v>1</v>
       </c>
       <c r="M279" t="n">
-        <v>-0.6564257028112452</v>
+        <v>-0.6562204910292735</v>
       </c>
       <c r="N279" t="n">
-        <v>0.6564257028112452</v>
+        <v>0.6562204910292735</v>
       </c>
       <c r="O279" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P279" t="n">
-        <v>-0.03630522088353327</v>
+        <v>-0.03645420207743122</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -21934,10 +21934,10 @@
         <v>8</v>
       </c>
       <c r="G280" t="n">
-        <v>0.9177888022678952</v>
+        <v>0.9178470254957507</v>
       </c>
       <c r="H280" t="n">
-        <v>6.673132530120484</v>
+        <v>6.674419263456092</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -21956,16 +21956,16 @@
         <v>1</v>
       </c>
       <c r="M280" t="n">
-        <v>-0.5968674698795153</v>
+        <v>-0.5955807365439076</v>
       </c>
       <c r="N280" t="n">
-        <v>0.5968674698795153</v>
+        <v>0.5955807365439076</v>
       </c>
       <c r="O280" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P280" t="n">
-        <v>-0.04044176706827063</v>
+        <v>-0.03936024551463468</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -22005,10 +22005,10 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>0.9142452161587526</v>
+        <v>0.9143059490084986</v>
       </c>
       <c r="H281" t="n">
-        <v>6.622409638554217</v>
+        <v>6.62308073654391</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -22027,16 +22027,16 @@
         <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>-0.637590361445783</v>
+        <v>-0.6369192634560896</v>
       </c>
       <c r="N281" t="n">
-        <v>0.637590361445783</v>
+        <v>0.6369192634560896</v>
       </c>
       <c r="O281" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P281" t="n">
-        <v>-0.05072289156626741</v>
+        <v>-0.05133852691218177</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -22076,10 +22076,10 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>0.9107016300496102</v>
+        <v>0.9107648725212465</v>
       </c>
       <c r="H282" t="n">
-        <v>6.546626506024096</v>
+        <v>6.546975920679887</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -22098,16 +22098,16 @@
         <v>1</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.5633734939759041</v>
+        <v>-0.5630240793201136</v>
       </c>
       <c r="N282" t="n">
-        <v>0.5633734939759041</v>
+        <v>0.5630240793201136</v>
       </c>
       <c r="O282" t="n">
         <v>-0.1499999999999995</v>
       </c>
       <c r="P282" t="n">
-        <v>-0.07578313253012059</v>
+        <v>-0.0761048158640234</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -22147,10 +22147,10 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>0.9071580439404677</v>
+        <v>0.9072237960339944</v>
       </c>
       <c r="H283" t="n">
-        <v>6.508192771084337</v>
+        <v>6.509645892351275</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -22169,16 +22169,16 @@
         <v>1</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.5018072289156628</v>
+        <v>-0.5003541076487243</v>
       </c>
       <c r="N283" t="n">
-        <v>0.5018072289156628</v>
+        <v>0.5003541076487243</v>
       </c>
       <c r="O283" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P283" t="n">
-        <v>-0.03843373493975921</v>
+        <v>-0.03733002832861132</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -22218,10 +22218,10 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>0.9050318922749823</v>
+        <v>0.9050991501416431</v>
       </c>
       <c r="H284" t="n">
-        <v>6.423614457831324</v>
+        <v>6.428073654390937</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -22240,16 +22240,16 @@
         <v>1</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.3963855421686766</v>
+        <v>-0.3919263456090629</v>
       </c>
       <c r="N284" t="n">
-        <v>0.3963855421686766</v>
+        <v>0.3919263456090629</v>
       </c>
       <c r="O284" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P284" t="n">
-        <v>-0.08457831325301335</v>
+        <v>-0.08157223796033808</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -22289,10 +22289,10 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>0.9014883061658399</v>
+        <v>0.9015580736543909</v>
       </c>
       <c r="H285" t="n">
-        <v>6.400722891566265</v>
+        <v>6.40110835694051</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -22311,16 +22311,16 @@
         <v>1</v>
       </c>
       <c r="M285" t="n">
-        <v>-0.2992771084337349</v>
+        <v>-0.2988916430594903</v>
       </c>
       <c r="N285" t="n">
-        <v>0.2992771084337349</v>
+        <v>0.2988916430594903</v>
       </c>
       <c r="O285" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P285" t="n">
-        <v>-0.02289156626505839</v>
+        <v>-0.02696529745042753</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
@@ -22360,10 +22360,10 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>0.8986534372785259</v>
+        <v>0.8987252124645893</v>
       </c>
       <c r="H286" t="n">
-        <v>6.350240963855422</v>
+        <v>6.351827195467422</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -22382,16 +22382,16 @@
         <v>1</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.1897590361445785</v>
+        <v>-0.1881728045325781</v>
       </c>
       <c r="N286" t="n">
-        <v>0.1897590361445785</v>
+        <v>0.1881728045325781</v>
       </c>
       <c r="O286" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P286" t="n">
-        <v>-0.0504819277108437</v>
+        <v>-0.04928116147308792</v>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
@@ -22400,11 +22400,11 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S286" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -25685,10 +25685,10 @@
         <v>8</v>
       </c>
       <c r="G333" t="n">
-        <v>0.7632884479092842</v>
+        <v>0.7634560906515581</v>
       </c>
       <c r="H333" t="n">
-        <v>6.481396172927003</v>
+        <v>6.482344192634561</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -25707,16 +25707,16 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.7811038270729975</v>
+        <v>-0.7801558073654391</v>
       </c>
       <c r="N333" t="n">
-        <v>0.7811038270729975</v>
+        <v>0.7801558073654391</v>
       </c>
       <c r="O333" t="n">
         <v>-0.4400000000000004</v>
       </c>
       <c r="P333" t="n">
-        <v>-0.9861090828543562</v>
+        <v>-0.9851610631467977</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -25756,10 +25756,10 @@
         <v>8</v>
       </c>
       <c r="G334" t="n">
-        <v>0.771793054571226</v>
+        <v>0.7719546742209632</v>
       </c>
       <c r="H334" t="n">
-        <v>6.536058646350106</v>
+        <v>6.53640138101983</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -25778,16 +25778,16 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.4389413536498932</v>
+        <v>-0.4385986189801701</v>
       </c>
       <c r="N334" t="n">
-        <v>0.4389413536498932</v>
+        <v>0.4385986189801701</v>
       </c>
       <c r="O334" t="n">
         <v>-0.2875000000000005</v>
       </c>
       <c r="P334" t="n">
-        <v>0.05466247342310382</v>
+        <v>0.05405718838526852</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -25827,10 +25827,10 @@
         <v>8</v>
       </c>
       <c r="G335" t="n">
-        <v>0.7916371367824239</v>
+        <v>0.7917847025495751</v>
       </c>
       <c r="H335" t="n">
-        <v>6.640854004252303</v>
+        <v>6.641271246458923</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -25849,16 +25849,16 @@
         <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.1591459957476964</v>
+        <v>-0.1587287535410766</v>
       </c>
       <c r="N335" t="n">
-        <v>0.1591459957476964</v>
+        <v>0.1587287535410766</v>
       </c>
       <c r="O335" t="n">
         <v>-0.1749999999999998</v>
       </c>
       <c r="P335" t="n">
-        <v>0.104795357902197</v>
+        <v>0.1048698654390936</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -25898,10 +25898,10 @@
         <v>8</v>
       </c>
       <c r="G336" t="n">
-        <v>0.8143160878809355</v>
+        <v>0.8144475920679887</v>
       </c>
       <c r="H336" t="n">
-        <v>6.84495747696669</v>
+        <v>6.845701133144476</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -25920,16 +25920,16 @@
         <v>1</v>
       </c>
       <c r="M336" t="n">
-        <v>0.2149574769666902</v>
+        <v>0.215701133144476</v>
       </c>
       <c r="N336" t="n">
-        <v>0.2149574769666902</v>
+        <v>0.215701133144476</v>
       </c>
       <c r="O336" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P336" t="n">
-        <v>0.2041034727143867</v>
+        <v>0.2044298866855527</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -25969,10 +25969,10 @@
         <v>8</v>
       </c>
       <c r="G337" t="n">
-        <v>0.8341601700921333</v>
+        <v>0.8342776203966006</v>
       </c>
       <c r="H337" t="n">
-        <v>7.062175761871013</v>
+        <v>7.062839943342777</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -25991,16 +25991,16 @@
         <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>0.572175761871013</v>
+        <v>0.5728399433427764</v>
       </c>
       <c r="N337" t="n">
-        <v>0.572175761871013</v>
+        <v>0.5728399433427764</v>
       </c>
       <c r="O337" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P337" t="n">
-        <v>0.2172182849043232</v>
+        <v>0.2171388101983007</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>8</v>
       </c>
       <c r="G338" t="n">
-        <v>0.8504606661941885</v>
+        <v>0.8505665722379604</v>
       </c>
       <c r="H338" t="n">
-        <v>7.147871013465627</v>
+        <v>7.147990793201133</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -26062,16 +26062,16 @@
         <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>0.6678710134656267</v>
+        <v>0.6679907932011329</v>
       </c>
       <c r="N338" t="n">
-        <v>0.6678710134656267</v>
+        <v>0.6679907932011329</v>
       </c>
       <c r="O338" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P338" t="n">
-        <v>0.08569525159461389</v>
+        <v>0.08515084985835664</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -26111,10 +26111,10 @@
         <v>8</v>
       </c>
       <c r="G339" t="n">
-        <v>0.8575478384124734</v>
+        <v>0.8576487252124646</v>
       </c>
       <c r="H339" t="n">
-        <v>7.202500000000001</v>
+        <v>7.202503541076488</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -26133,16 +26133,16 @@
         <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>0.6525000000000007</v>
+        <v>0.6525035410764879</v>
       </c>
       <c r="N339" t="n">
-        <v>0.6525000000000007</v>
+        <v>0.6525035410764879</v>
       </c>
       <c r="O339" t="n">
         <v>0.0699999999999994</v>
       </c>
       <c r="P339" t="n">
-        <v>0.05462898653437342</v>
+        <v>0.05451274787535443</v>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
@@ -26182,10 +26182,10 @@
         <v>8</v>
       </c>
       <c r="G340" t="n">
-        <v>0.8497519489723601</v>
+        <v>0.8498583569405099</v>
       </c>
       <c r="H340" t="n">
-        <v>7.147069454287739</v>
+        <v>7.147189801699716</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -26204,16 +26204,16 @@
         <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>0.6170694542877388</v>
+        <v>0.6171898016997162</v>
       </c>
       <c r="N340" t="n">
-        <v>0.6170694542877388</v>
+        <v>0.6171898016997162</v>
       </c>
       <c r="O340" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P340" t="n">
-        <v>-0.05543054571226147</v>
+        <v>-0.05531373937677131</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -26253,10 +26253,10 @@
         <v>8</v>
       </c>
       <c r="G341" t="n">
-        <v>0.8299078667611623</v>
+        <v>0.830028328611898</v>
       </c>
       <c r="H341" t="n">
-        <v>7.020838648712497</v>
+        <v>7.021746931067044</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -26275,16 +26275,16 @@
         <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>0.6883386487124978</v>
+        <v>0.6892469310670446</v>
       </c>
       <c r="N341" t="n">
-        <v>0.6883386487124978</v>
+        <v>0.6892469310670446</v>
       </c>
       <c r="O341" t="n">
         <v>-0.1975000000000007</v>
       </c>
       <c r="P341" t="n">
-        <v>-0.1262308055752417</v>
+        <v>-0.1254428706326722</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -26324,10 +26324,10 @@
         <v>8</v>
       </c>
       <c r="G342" t="n">
-        <v>0.8100637845499645</v>
+        <v>0.8101983002832861</v>
       </c>
       <c r="H342" t="n">
-        <v>6.818977675407512</v>
+        <v>6.819167847025496</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -26346,16 +26346,16 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>0.628977675407512</v>
+        <v>0.6291678470254958</v>
       </c>
       <c r="N342" t="n">
-        <v>0.628977675407512</v>
+        <v>0.6291678470254958</v>
       </c>
       <c r="O342" t="n">
         <v>-0.1424999999999992</v>
       </c>
       <c r="P342" t="n">
-        <v>-0.201860973304985</v>
+        <v>-0.202579084041548</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -26395,10 +26395,10 @@
         <v>8</v>
       </c>
       <c r="G343" t="n">
-        <v>0.7866761162296244</v>
+        <v>0.7868271954674221</v>
       </c>
       <c r="H343" t="n">
-        <v>6.614613749114103</v>
+        <v>6.618031161473086</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
@@ -26417,16 +26417,16 @@
         <v>1</v>
       </c>
       <c r="M343" t="n">
-        <v>0.6246137491141024</v>
+        <v>0.6280311614730856</v>
       </c>
       <c r="N343" t="n">
-        <v>0.6246137491141024</v>
+        <v>0.6280311614730856</v>
       </c>
       <c r="O343" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P343" t="n">
-        <v>-0.2043639262934098</v>
+        <v>-0.2011366855524104</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -26466,10 +26466,10 @@
         <v>8</v>
       </c>
       <c r="G344" t="n">
-        <v>0.7625797306874557</v>
+        <v>0.7627478753541076</v>
       </c>
       <c r="H344" t="n">
-        <v>6.478258918025041</v>
+        <v>6.478892823418319</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -26488,16 +26488,16 @@
         <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5582589180250412</v>
+        <v>0.5588928234183195</v>
       </c>
       <c r="N344" t="n">
-        <v>0.5582589180250412</v>
+        <v>0.5588928234183195</v>
       </c>
       <c r="O344" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P344" t="n">
-        <v>-0.1363548310890614</v>
+        <v>-0.1391383380547664</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -26537,10 +26537,10 @@
         <v>8</v>
       </c>
       <c r="G345" t="n">
-        <v>0.7406094968107725</v>
+        <v>0.7407932011331445</v>
       </c>
       <c r="H345" t="n">
-        <v>6.376293408929837</v>
+        <v>6.378371104815865</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
@@ -26559,16 +26559,16 @@
         <v>1</v>
       </c>
       <c r="M345" t="n">
-        <v>0.3962934089298367</v>
+        <v>0.3983711048158645</v>
       </c>
       <c r="N345" t="n">
-        <v>0.3962934089298367</v>
+        <v>0.3983711048158645</v>
       </c>
       <c r="O345" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P345" t="n">
-        <v>-0.1019655090952041</v>
+        <v>-0.1005217186024545</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -26608,10 +26608,10 @@
         <v>8</v>
       </c>
       <c r="G346" t="n">
-        <v>0.7172218284904324</v>
+        <v>0.7174220963172805</v>
       </c>
       <c r="H346" t="n">
-        <v>6.228972360028349</v>
+        <v>6.229255488668556</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -26630,16 +26630,16 @@
         <v>1</v>
       </c>
       <c r="M346" t="n">
-        <v>0.108972360028349</v>
+        <v>0.1092554886685555</v>
       </c>
       <c r="N346" t="n">
-        <v>0.108972360028349</v>
+        <v>0.1092554886685555</v>
       </c>
       <c r="O346" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P346" t="n">
-        <v>-0.147321048901488</v>
+        <v>-0.1491156161473093</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -27809,10 +27809,10 @@
         <v>8</v>
       </c>
       <c r="G363" t="n">
-        <v>0.6442239546420978</v>
+        <v>0.6444759206798867</v>
       </c>
       <c r="H363" t="n">
-        <v>6.968780120481927</v>
+        <v>6.968999645892351</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -27831,16 +27831,16 @@
         <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>-1.493719879518073</v>
+        <v>-1.493500354107649</v>
       </c>
       <c r="N363" t="n">
-        <v>1.493719879518073</v>
+        <v>1.493500354107649</v>
       </c>
       <c r="O363" t="n">
         <v>-0.254999999999999</v>
       </c>
       <c r="P363" t="n">
-        <v>0.1261995318344153</v>
+        <v>0.1264190572448394</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -27880,10 +27880,10 @@
         <v>8</v>
       </c>
       <c r="G364" t="n">
-        <v>0.6527285613040397</v>
+        <v>0.6529745042492918</v>
       </c>
       <c r="H364" t="n">
-        <v>6.999518072289156</v>
+        <v>7.001232294617564</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -27902,16 +27902,16 @@
         <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>-1.312981927710844</v>
+        <v>-1.311267705382436</v>
       </c>
       <c r="N364" t="n">
-        <v>1.312981927710844</v>
+        <v>1.311267705382436</v>
       </c>
       <c r="O364" t="n">
         <v>-0.1500000000000004</v>
       </c>
       <c r="P364" t="n">
-        <v>0.03073795180722882</v>
+        <v>0.0322326487252127</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -27951,10 +27951,10 @@
         <v>8</v>
       </c>
       <c r="G365" t="n">
-        <v>0.6654854712969526</v>
+        <v>0.6657223796033994</v>
       </c>
       <c r="H365" t="n">
-        <v>7.06382530120482</v>
+        <v>7.065042492917848</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -27973,16 +27973,16 @@
         <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>-1.066174698795181</v>
+        <v>-1.064957507082153</v>
       </c>
       <c r="N365" t="n">
-        <v>1.066174698795181</v>
+        <v>1.064957507082153</v>
       </c>
       <c r="O365" t="n">
         <v>-0.1824999999999992</v>
       </c>
       <c r="P365" t="n">
-        <v>0.06430722891566365</v>
+        <v>0.06381019830028389</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -28022,10 +28022,10 @@
         <v>8</v>
       </c>
       <c r="G366" t="n">
-        <v>0.6796598157335223</v>
+        <v>0.6798866855524079</v>
       </c>
       <c r="H366" t="n">
-        <v>7.16156626506024</v>
+        <v>7.162455736543909</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -28044,16 +28044,16 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.9259337349397603</v>
+        <v>-0.9250442634560914</v>
       </c>
       <c r="N366" t="n">
-        <v>0.9259337349397603</v>
+        <v>0.9250442634560914</v>
       </c>
       <c r="O366" t="n">
         <v>-0.04250000000000043</v>
       </c>
       <c r="P366" t="n">
-        <v>0.0977409638554203</v>
+        <v>0.09741324362606107</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -28093,10 +28093,10 @@
         <v>8</v>
       </c>
       <c r="G367" t="n">
-        <v>0.6874557051736357</v>
+        <v>0.6876770538243626</v>
       </c>
       <c r="H367" t="n">
-        <v>7.191445783132531</v>
+        <v>7.191638633144477</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -28115,16 +28115,16 @@
         <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>-1.038554216867469</v>
+        <v>-1.038361366855524</v>
       </c>
       <c r="N367" t="n">
-        <v>1.038554216867469</v>
+        <v>1.038361366855524</v>
       </c>
       <c r="O367" t="n">
         <v>0.1425000000000001</v>
       </c>
       <c r="P367" t="n">
-        <v>0.02987951807229106</v>
+        <v>0.02918289660056761</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -28164,10 +28164,10 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>0.6888731396172927</v>
+        <v>0.6890934844192634</v>
       </c>
       <c r="H368" t="n">
-        <v>7.193343373493977</v>
+        <v>7.194239258734656</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -28186,16 +28186,16 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.8491566265060237</v>
+        <v>-0.8482607412653449</v>
       </c>
       <c r="N368" t="n">
-        <v>0.8491566265060237</v>
+        <v>0.8482607412653449</v>
       </c>
       <c r="O368" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P368" t="n">
-        <v>0.001897590361445545</v>
+        <v>0.002600625590178929</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -28235,10 +28235,10 @@
         <v>8</v>
       </c>
       <c r="G369" t="n">
-        <v>0.6832034018426648</v>
+        <v>0.68342776203966</v>
       </c>
       <c r="H369" t="n">
-        <v>7.175459337349397</v>
+        <v>7.176338969546742</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -28257,16 +28257,16 @@
         <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.7745406626506028</v>
+        <v>-0.7736610304532583</v>
       </c>
       <c r="N369" t="n">
-        <v>0.7745406626506028</v>
+        <v>0.7736610304532583</v>
       </c>
       <c r="O369" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P369" t="n">
-        <v>-0.01788403614457934</v>
+        <v>-0.01790028918791364</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -28306,10 +28306,10 @@
         <v>8</v>
       </c>
       <c r="G370" t="n">
-        <v>0.6711552090715804</v>
+        <v>0.6713881019830028</v>
       </c>
       <c r="H370" t="n">
-        <v>7.105903614457831</v>
+        <v>7.109150141643059</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -28328,16 +28328,16 @@
         <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.8740963855421695</v>
+        <v>-0.8708498583569417</v>
       </c>
       <c r="N370" t="n">
-        <v>0.8740963855421695</v>
+        <v>0.8708498583569417</v>
       </c>
       <c r="O370" t="n">
         <v>0.03000000000000025</v>
       </c>
       <c r="P370" t="n">
-        <v>-0.06955572289156642</v>
+        <v>-0.06718882790368319</v>
       </c>
       <c r="Q370" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>8</v>
       </c>
       <c r="G371" t="n">
-        <v>0.6520198440822113</v>
+        <v>0.6522662889518414</v>
       </c>
       <c r="H371" t="n">
-        <v>6.994578313253013</v>
+        <v>6.996296033994335</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -28399,16 +28399,16 @@
         <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>-1.040421686746988</v>
+        <v>-1.038703966005666</v>
       </c>
       <c r="N371" t="n">
-        <v>1.040421686746988</v>
+        <v>1.038703966005666</v>
       </c>
       <c r="O371" t="n">
         <v>0.05499999999999972</v>
       </c>
       <c r="P371" t="n">
-        <v>-0.1113253012048183</v>
+        <v>-0.1128541076487242</v>
       </c>
       <c r="Q371" t="inlineStr">
         <is>
@@ -28448,10 +28448,10 @@
         <v>8</v>
       </c>
       <c r="G372" t="n">
-        <v>0.630049610205528</v>
+        <v>0.6303116147308782</v>
       </c>
       <c r="H372" t="n">
-        <v>6.933222891566265</v>
+        <v>6.93413597733711</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -28470,16 +28470,16 @@
         <v>1</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.9767771084337351</v>
+        <v>-0.9758640226628899</v>
       </c>
       <c r="N372" t="n">
-        <v>0.9767771084337351</v>
+        <v>0.9758640226628899</v>
       </c>
       <c r="O372" t="n">
         <v>-0.125</v>
       </c>
       <c r="P372" t="n">
-        <v>-0.06135542168674757</v>
+        <v>-0.06216005665722424</v>
       </c>
       <c r="Q372" t="inlineStr">
         <is>
@@ -28519,10 +28519,10 @@
         <v>8</v>
       </c>
       <c r="G373" t="n">
-        <v>0.6151665485471297</v>
+        <v>0.6154390934844193</v>
       </c>
       <c r="H373" t="n">
-        <v>6.875496987951808</v>
+        <v>6.877159171388103</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -28541,16 +28541,16 @@
         <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.8145030120481929</v>
+        <v>-0.8128408286118978</v>
       </c>
       <c r="N373" t="n">
-        <v>0.8145030120481929</v>
+        <v>0.8128408286118978</v>
       </c>
       <c r="O373" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P373" t="n">
-        <v>-0.05772590361445751</v>
+        <v>-0.05697680594900767</v>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
@@ -28590,10 +28590,10 @@
         <v>8</v>
       </c>
       <c r="G374" t="n">
-        <v>0.5974486180014175</v>
+        <v>0.5977337110481586</v>
       </c>
       <c r="H374" t="n">
-        <v>6.798027108433735</v>
+        <v>6.798275495750708</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -28612,16 +28612,16 @@
         <v>1</v>
       </c>
       <c r="M374" t="n">
-        <v>-0.6619728915662648</v>
+        <v>-0.6617245042492916</v>
       </c>
       <c r="N374" t="n">
-        <v>0.6619728915662648</v>
+        <v>0.6617245042492916</v>
       </c>
       <c r="O374" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P374" t="n">
-        <v>-0.07746987951807238</v>
+        <v>-0.07888367563739429</v>
       </c>
       <c r="Q374" t="inlineStr">
         <is>
@@ -28661,10 +28661,10 @@
         <v>8</v>
       </c>
       <c r="G375" t="n">
-        <v>0.5825655563430191</v>
+        <v>0.5828611898016998</v>
       </c>
       <c r="H375" t="n">
-        <v>6.760060240963855</v>
+        <v>6.760317811614731</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -28683,16 +28683,16 @@
         <v>1</v>
       </c>
       <c r="M375" t="n">
-        <v>-0.519939759036145</v>
+        <v>-0.5196821883852696</v>
       </c>
       <c r="N375" t="n">
-        <v>0.519939759036145</v>
+        <v>0.5196821883852696</v>
       </c>
       <c r="O375" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.03796686746987987</v>
+        <v>-0.03795768413597767</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
@@ -28732,10 +28732,10 @@
         <v>8</v>
       </c>
       <c r="G376" t="n">
-        <v>0.5641389085754784</v>
+        <v>0.5644475920679887</v>
       </c>
       <c r="H376" t="n">
-        <v>6.678012048192771</v>
+        <v>6.67854992917847</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -28754,16 +28754,16 @@
         <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>-0.4319879518072298</v>
+        <v>-0.4314500708215308</v>
       </c>
       <c r="N376" t="n">
-        <v>0.4319879518072298</v>
+        <v>0.4314500708215308</v>
       </c>
       <c r="O376" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.08204819277108477</v>
+        <v>-0.0817678824362611</v>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
@@ -29933,10 +29933,10 @@
         <v>8</v>
       </c>
       <c r="G393" t="n">
-        <v>0.6583982990786676</v>
+        <v>0.6586402266288952</v>
       </c>
       <c r="H393" t="n">
-        <v>5.814525159461375</v>
+        <v>5.818342776203966</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -29955,16 +29955,16 @@
         <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>1.024525159461374</v>
+        <v>1.028342776203965</v>
       </c>
       <c r="N393" t="n">
-        <v>1.024525159461374</v>
+        <v>1.028342776203965</v>
       </c>
       <c r="O393" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P393" t="n">
-        <v>-0.6509969148203343</v>
+        <v>-0.6471792980777433</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
@@ -30004,10 +30004,10 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>0.5641389085754784</v>
+        <v>0.5644475920679887</v>
       </c>
       <c r="H394" t="n">
-        <v>5.500263997165131</v>
+        <v>5.500872875354108</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -30026,16 +30026,16 @@
         <v>1</v>
       </c>
       <c r="M394" t="n">
-        <v>0.8302639971651313</v>
+        <v>0.8308728753541077</v>
       </c>
       <c r="N394" t="n">
-        <v>0.8302639971651313</v>
+        <v>0.8308728753541077</v>
       </c>
       <c r="O394" t="n">
         <v>-0.120000000000001</v>
       </c>
       <c r="P394" t="n">
-        <v>-0.3142611622962441</v>
+        <v>-0.3174699008498587</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -30075,10 +30075,10 @@
         <v>8</v>
       </c>
       <c r="G395" t="n">
-        <v>0.5428773919206237</v>
+        <v>0.5424929178470255</v>
       </c>
       <c r="H395" t="n">
-        <v>5.45694188518781</v>
+        <v>5.456689093484419</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -30097,16 +30097,16 @@
         <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>0.9169418851878097</v>
+        <v>0.9166890934844192</v>
       </c>
       <c r="N395" t="n">
-        <v>0.9169418851878097</v>
+        <v>0.9166890934844192</v>
       </c>
       <c r="O395" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P395" t="n">
-        <v>-0.0433221119773215</v>
+        <v>-0.04418378186968841</v>
       </c>
       <c r="Q395" t="inlineStr">
         <is>
@@ -30146,10 +30146,10 @@
         <v>8</v>
       </c>
       <c r="G396" t="n">
-        <v>0.595322466335932</v>
+        <v>0.5956090651558074</v>
       </c>
       <c r="H396" t="n">
-        <v>5.636424521615876</v>
+        <v>5.636612960339943</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -30168,16 +30168,16 @@
         <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>1.196424521615875</v>
+        <v>1.196612960339943</v>
       </c>
       <c r="N396" t="n">
-        <v>1.196424521615875</v>
+        <v>1.196612960339943</v>
       </c>
       <c r="O396" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P396" t="n">
-        <v>0.1794826364280659</v>
+        <v>0.1799238668555239</v>
       </c>
       <c r="Q396" t="inlineStr">
         <is>
@@ -30217,10 +30217,10 @@
         <v>8</v>
       </c>
       <c r="G397" t="n">
-        <v>0.6335931963146705</v>
+        <v>0.6338526912181303</v>
       </c>
       <c r="H397" t="n">
-        <v>5.756587526576896</v>
+        <v>5.756758144475921</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -30239,16 +30239,16 @@
         <v>1</v>
       </c>
       <c r="M397" t="n">
-        <v>1.316587526576896</v>
+        <v>1.316758144475921</v>
       </c>
       <c r="N397" t="n">
-        <v>1.316587526576896</v>
+        <v>1.316758144475921</v>
       </c>
       <c r="O397" t="n">
         <v>0</v>
       </c>
       <c r="P397" t="n">
-        <v>0.1201630049610207</v>
+        <v>0.1201451841359784</v>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>8</v>
       </c>
       <c r="G398" t="n">
-        <v>0.5939050318922749</v>
+        <v>0.5941926345609065</v>
       </c>
       <c r="H398" t="n">
-        <v>5.635492558469171</v>
+        <v>5.635681657223796</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -30310,16 +30310,16 @@
         <v>1</v>
       </c>
       <c r="M398" t="n">
-        <v>1.23549255846917</v>
+        <v>1.235681657223796</v>
       </c>
       <c r="N398" t="n">
-        <v>1.23549255846917</v>
+        <v>1.235681657223796</v>
       </c>
       <c r="O398" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P398" t="n">
-        <v>-0.1210949681077258</v>
+        <v>-0.1210764872521253</v>
       </c>
       <c r="Q398" t="inlineStr">
         <is>
@@ -30359,10 +30359,10 @@
         <v>8</v>
       </c>
       <c r="G399" t="n">
-        <v>0.4790928419560596</v>
+        <v>0.4787535410764873</v>
       </c>
       <c r="H399" t="n">
-        <v>5.190021261516655</v>
+        <v>5.189780453257791</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -30381,16 +30381,16 @@
         <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>0.8100212615166553</v>
+        <v>0.8097804532577912</v>
       </c>
       <c r="N399" t="n">
-        <v>0.8100212615166553</v>
+        <v>0.8097804532577912</v>
       </c>
       <c r="O399" t="n">
         <v>-0.02000000000000046</v>
       </c>
       <c r="P399" t="n">
-        <v>-0.4454712969525154</v>
+        <v>-0.4459012039660051</v>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
@@ -30430,10 +30430,10 @@
         <v>8</v>
       </c>
       <c r="G400" t="n">
-        <v>0.3706591070163005</v>
+        <v>0.3703966005665723</v>
       </c>
       <c r="H400" t="n">
-        <v>4.843708362863217</v>
+        <v>4.843535764872521</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -30452,16 +30452,16 @@
         <v>1</v>
       </c>
       <c r="M400" t="n">
-        <v>0.7037083628632175</v>
+        <v>0.7035357648725213</v>
       </c>
       <c r="N400" t="n">
-        <v>0.7037083628632175</v>
+        <v>0.7035357648725213</v>
       </c>
       <c r="O400" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P400" t="n">
-        <v>-0.3463128986534381</v>
+        <v>-0.3462446883852701</v>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
@@ -30501,10 +30501,10 @@
         <v>8</v>
       </c>
       <c r="G401" t="n">
-        <v>0.3260099220411056</v>
+        <v>0.3257790368271954</v>
       </c>
       <c r="H401" t="n">
-        <v>4.704718284904324</v>
+        <v>4.702896600566572</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -30523,16 +30523,16 @@
         <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>0.8347182849043238</v>
+        <v>0.8328966005665723</v>
       </c>
       <c r="N401" t="n">
-        <v>0.8347182849043238</v>
+        <v>0.8328966005665723</v>
       </c>
       <c r="O401" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P401" t="n">
-        <v>-0.1389900779588933</v>
+        <v>-0.1406391643059486</v>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
@@ -30572,10 +30572,10 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>0.3522324592487597</v>
+        <v>0.3519830028328612</v>
       </c>
       <c r="H402" t="n">
-        <v>4.80659284195606</v>
+        <v>4.806428824362606</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -30594,16 +30594,16 @@
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>1.08659284195606</v>
+        <v>1.086428824362606</v>
       </c>
       <c r="N402" t="n">
-        <v>1.08659284195606</v>
+        <v>1.086428824362606</v>
       </c>
       <c r="O402" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P402" t="n">
-        <v>0.1018745570517359</v>
+        <v>0.1035322237960337</v>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -30643,10 +30643,10 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>0.5301204819277109</v>
+        <v>0.5297450424929179</v>
       </c>
       <c r="H403" t="n">
-        <v>5.44210843373494</v>
+        <v>5.441614730878187</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -30665,16 +30665,16 @@
         <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>1.74210843373494</v>
+        <v>1.741614730878187</v>
       </c>
       <c r="N403" t="n">
-        <v>1.74210843373494</v>
+        <v>1.741614730878187</v>
       </c>
       <c r="O403" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P403" t="n">
-        <v>0.63551559177888</v>
+        <v>0.6351859065155807</v>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>8</v>
       </c>
       <c r="G404" t="n">
-        <v>0.7604535790219702</v>
+        <v>0.7606232294617564</v>
       </c>
       <c r="H404" t="n">
-        <v>6.099998228206945</v>
+        <v>6.100878186968838</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -30736,16 +30736,16 @@
         <v>1</v>
       </c>
       <c r="M404" t="n">
-        <v>2.259998228206945</v>
+        <v>2.260878186968839</v>
       </c>
       <c r="N404" t="n">
-        <v>2.259998228206945</v>
+        <v>2.260878186968839</v>
       </c>
       <c r="O404" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P404" t="n">
-        <v>0.6578897944720055</v>
+        <v>0.6592634560906516</v>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
@@ -30785,10 +30785,10 @@
         <v>8</v>
       </c>
       <c r="G405" t="n">
-        <v>0.8313253012048193</v>
+        <v>0.8314447592067988</v>
       </c>
       <c r="H405" t="n">
-        <v>6.344367469879518</v>
+        <v>6.345074362606232</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -30807,16 +30807,16 @@
         <v>1</v>
       </c>
       <c r="M405" t="n">
-        <v>2.324367469879519</v>
+        <v>2.325074362606233</v>
       </c>
       <c r="N405" t="n">
-        <v>2.324367469879519</v>
+        <v>2.325074362606233</v>
       </c>
       <c r="O405" t="n">
         <v>0.1799999999999997</v>
       </c>
       <c r="P405" t="n">
-        <v>0.2443692416725733</v>
+        <v>0.244196175637394</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
@@ -30856,10 +30856,10 @@
         <v>8</v>
       </c>
       <c r="G406" t="n">
-        <v>0.8157335223245925</v>
+        <v>0.8158640226628895</v>
       </c>
       <c r="H406" t="n">
-        <v>6.290947909284196</v>
+        <v>6.291805949008499</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -30878,16 +30878,16 @@
         <v>1</v>
       </c>
       <c r="M406" t="n">
-        <v>2.190947909284196</v>
+        <v>2.191805949008499</v>
       </c>
       <c r="N406" t="n">
-        <v>2.190947909284196</v>
+        <v>2.191805949008499</v>
       </c>
       <c r="O406" t="n">
         <v>0.08000000000000007</v>
       </c>
       <c r="P406" t="n">
-        <v>-0.05341956059532293</v>
+        <v>-0.05326841359773393</v>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
@@ -32057,10 +32057,10 @@
         <v>8</v>
       </c>
       <c r="G423" t="n">
-        <v>0.8291991495393338</v>
+        <v>0.8293201133144475</v>
       </c>
       <c r="H423" t="n">
-        <v>5.562115520907158</v>
+        <v>5.562894830028328</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -32079,16 +32079,16 @@
         <v>1</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.8053844790928419</v>
+        <v>-0.8046051699716719</v>
       </c>
       <c r="N423" t="n">
-        <v>0.8053844790928419</v>
+        <v>0.8046051699716719</v>
       </c>
       <c r="O423" t="n">
         <v>-0.07500000000000018</v>
       </c>
       <c r="P423" t="n">
-        <v>-1.476814051622624</v>
+        <v>-1.476034742501454</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
@@ -32128,10 +32128,10 @@
         <v>8</v>
       </c>
       <c r="G424" t="n">
-        <v>0.8270729978738484</v>
+        <v>0.8271954674220963</v>
       </c>
       <c r="H424" t="n">
-        <v>5.547278525868179</v>
+        <v>5.547804532577904</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -32150,16 +32150,16 @@
         <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>-0.7702214741318212</v>
+        <v>-0.7696954674220962</v>
       </c>
       <c r="N424" t="n">
-        <v>0.7702214741318212</v>
+        <v>0.7696954674220962</v>
       </c>
       <c r="O424" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P424" t="n">
-        <v>-0.01483699503897906</v>
+        <v>-0.01509029745042412</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -32199,10 +32199,10 @@
         <v>8</v>
       </c>
       <c r="G425" t="n">
-        <v>0.820694542877392</v>
+        <v>0.8208215297450425</v>
       </c>
       <c r="H425" t="n">
-        <v>5.499883061658399</v>
+        <v>5.500856940509916</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -32221,16 +32221,16 @@
         <v>1</v>
       </c>
       <c r="M425" t="n">
-        <v>-0.7601169383416009</v>
+        <v>-0.7591430594900839</v>
       </c>
       <c r="N425" t="n">
-        <v>0.7601169383416009</v>
+        <v>0.7591430594900839</v>
       </c>
       <c r="O425" t="n">
         <v>-0.05750000000000011</v>
       </c>
       <c r="P425" t="n">
-        <v>-0.0473954642097798</v>
+        <v>-0.04694759206798782</v>
       </c>
       <c r="Q425" t="inlineStr">
         <is>
@@ -32270,10 +32270,10 @@
         <v>8</v>
       </c>
       <c r="G426" t="n">
-        <v>0.817859673990078</v>
+        <v>0.8179886685552408</v>
       </c>
       <c r="H426" t="n">
-        <v>5.486560949681078</v>
+        <v>5.487391997167139</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -32292,16 +32292,16 @@
         <v>1</v>
       </c>
       <c r="M426" t="n">
-        <v>-0.6434390503189222</v>
+        <v>-0.6426080028328611</v>
       </c>
       <c r="N426" t="n">
-        <v>0.6434390503189222</v>
+        <v>0.6426080028328611</v>
       </c>
       <c r="O426" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P426" t="n">
-        <v>-0.01332211197732125</v>
+        <v>-0.01346494334277715</v>
       </c>
       <c r="Q426" t="inlineStr">
         <is>
@@ -32341,10 +32341,10 @@
         <v>8</v>
       </c>
       <c r="G427" t="n">
-        <v>0.8086463501063076</v>
+        <v>0.8087818696883853</v>
       </c>
       <c r="H427" t="n">
-        <v>5.381568036853295</v>
+        <v>5.381859065155806</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -32363,16 +32363,16 @@
         <v>1</v>
       </c>
       <c r="M427" t="n">
-        <v>-0.608431963146705</v>
+        <v>-0.6081409348441937</v>
       </c>
       <c r="N427" t="n">
-        <v>0.608431963146705</v>
+        <v>0.6081409348441937</v>
       </c>
       <c r="O427" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P427" t="n">
-        <v>-0.1049929128277824</v>
+        <v>-0.1055329320113323</v>
       </c>
       <c r="Q427" t="inlineStr">
         <is>
@@ -32412,10 +32412,10 @@
         <v>8</v>
       </c>
       <c r="G428" t="n">
-        <v>0.7880935506732814</v>
+        <v>0.7882436260623229</v>
       </c>
       <c r="H428" t="n">
-        <v>5.227292700212615</v>
+        <v>5.227753186968839</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -32434,16 +32434,16 @@
         <v>1</v>
       </c>
       <c r="M428" t="n">
-        <v>-0.4802072997873843</v>
+        <v>-0.4797468130311611</v>
       </c>
       <c r="N428" t="n">
-        <v>0.4802072997873843</v>
+        <v>0.4797468130311611</v>
       </c>
       <c r="O428" t="n">
         <v>-0.2825000000000006</v>
       </c>
       <c r="P428" t="n">
-        <v>-0.1542753366406799</v>
+        <v>-0.154105878186968</v>
       </c>
       <c r="Q428" t="inlineStr">
         <is>
@@ -32483,10 +32483,10 @@
         <v>8</v>
       </c>
       <c r="G429" t="n">
-        <v>0.7703756201275691</v>
+        <v>0.7705382436260623</v>
       </c>
       <c r="H429" t="n">
-        <v>5.098454110559886</v>
+        <v>5.099327195467422</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
@@ -32505,16 +32505,16 @@
         <v>1</v>
       </c>
       <c r="M429" t="n">
-        <v>-0.4615458894401137</v>
+        <v>-0.4606728045325781</v>
       </c>
       <c r="N429" t="n">
-        <v>0.4615458894401137</v>
+        <v>0.4606728045325781</v>
       </c>
       <c r="O429" t="n">
         <v>-0.1475</v>
       </c>
       <c r="P429" t="n">
-        <v>-0.1288385896527293</v>
+        <v>-0.128425991501417</v>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
@@ -32554,10 +32554,10 @@
         <v>8</v>
       </c>
       <c r="G430" t="n">
-        <v>0.7455705173635719</v>
+        <v>0.7457507082152974</v>
       </c>
       <c r="H430" t="n">
-        <v>4.947225372076542</v>
+        <v>4.947999291784702</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -32576,16 +32576,16 @@
         <v>1</v>
       </c>
       <c r="M430" t="n">
-        <v>-0.3927746279234583</v>
+        <v>-0.3920007082152974</v>
       </c>
       <c r="N430" t="n">
-        <v>0.3927746279234583</v>
+        <v>0.3920007082152974</v>
       </c>
       <c r="O430" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P430" t="n">
-        <v>-0.1512287384833444</v>
+        <v>-0.1513279036827191</v>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
@@ -32625,10 +32625,10 @@
         <v>8</v>
       </c>
       <c r="G431" t="n">
-        <v>0.7200566973777462</v>
+        <v>0.7195467422096318</v>
       </c>
       <c r="H431" t="n">
-        <v>4.822643515237421</v>
+        <v>4.820453257790369</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
@@ -32647,16 +32647,16 @@
         <v>1</v>
       </c>
       <c r="M431" t="n">
-        <v>-0.2898564847625789</v>
+        <v>-0.2920467422096307</v>
       </c>
       <c r="N431" t="n">
-        <v>0.2898564847625789</v>
+        <v>0.2920467422096307</v>
       </c>
       <c r="O431" t="n">
         <v>-0.2275</v>
       </c>
       <c r="P431" t="n">
-        <v>-0.1245818568391206</v>
+        <v>-0.1275460339943333</v>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
@@ -32696,10 +32696,10 @@
         <v>8</v>
       </c>
       <c r="G432" t="n">
-        <v>0.6959603118355776</v>
+        <v>0.6954674220963173</v>
       </c>
       <c r="H432" t="n">
-        <v>4.655612154500354</v>
+        <v>4.654024433427762</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -32718,16 +32718,16 @@
         <v>1</v>
       </c>
       <c r="M432" t="n">
-        <v>-0.3543878454996454</v>
+        <v>-0.3559755665722379</v>
       </c>
       <c r="N432" t="n">
-        <v>0.3543878454996454</v>
+        <v>0.3559755665722379</v>
       </c>
       <c r="O432" t="n">
         <v>-0.1025</v>
       </c>
       <c r="P432" t="n">
-        <v>-0.1670313607370666</v>
+        <v>-0.1664288243626073</v>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
@@ -32767,10 +32767,10 @@
         <v>8</v>
       </c>
       <c r="G433" t="n">
-        <v>0.6860382707299787</v>
+        <v>0.6855524079320113</v>
       </c>
       <c r="H433" t="n">
-        <v>4.624801559177888</v>
+        <v>4.622361898016996</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -32789,16 +32789,16 @@
         <v>1</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.2151984408221121</v>
+        <v>-0.2176381019830034</v>
       </c>
       <c r="N433" t="n">
-        <v>0.2151984408221121</v>
+        <v>0.2176381019830034</v>
       </c>
       <c r="O433" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P433" t="n">
-        <v>-0.03081059532246666</v>
+        <v>-0.03166253541076536</v>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
@@ -32838,10 +32838,10 @@
         <v>8</v>
       </c>
       <c r="G434" t="n">
-        <v>0.6909992912827781</v>
+        <v>0.6905099150141643</v>
       </c>
       <c r="H434" t="n">
-        <v>4.641894637373022</v>
+        <v>4.640493389990556</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -32860,16 +32860,16 @@
         <v>1</v>
       </c>
       <c r="M434" t="n">
-        <v>-0.07810536262697809</v>
+        <v>-0.07950661000944326</v>
       </c>
       <c r="N434" t="n">
-        <v>0.07810536262697809</v>
+        <v>0.07950661000944326</v>
       </c>
       <c r="O434" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P434" t="n">
-        <v>0.01709307819513395</v>
+        <v>0.01813149197356001</v>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
@@ -32909,10 +32909,10 @@
         <v>8</v>
       </c>
       <c r="G435" t="n">
-        <v>0.7101346562721474</v>
+        <v>0.7096317280453258</v>
       </c>
       <c r="H435" t="n">
-        <v>4.750056697377746</v>
+        <v>4.747157695939566</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -32931,16 +32931,16 @@
         <v>1</v>
       </c>
       <c r="M435" t="n">
-        <v>0.1900566973777469</v>
+        <v>0.1871576959395664</v>
       </c>
       <c r="N435" t="n">
-        <v>0.1900566973777469</v>
+        <v>0.1871576959395664</v>
       </c>
       <c r="O435" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P435" t="n">
-        <v>0.1081620600047248</v>
+        <v>0.1066643059490096</v>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
@@ -32980,10 +32980,10 @@
         <v>8</v>
       </c>
       <c r="G436" t="n">
-        <v>0.7257264351523742</v>
+        <v>0.7252124645892352</v>
       </c>
       <c r="H436" t="n">
-        <v>4.846995038979447</v>
+        <v>4.844787535410765</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -33002,16 +33002,16 @@
         <v>1</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4569950389794473</v>
+        <v>0.4547875354107651</v>
       </c>
       <c r="N436" t="n">
-        <v>0.4569950389794473</v>
+        <v>0.4547875354107651</v>
       </c>
       <c r="O436" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P436" t="n">
-        <v>0.09693834160170045</v>
+        <v>0.09762983947119874</v>
       </c>
       <c r="Q436" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>8</v>
       </c>
       <c r="G437" t="n">
-        <v>0.8228206945428774</v>
+        <v>0.8229461756373938</v>
       </c>
       <c r="H437" t="n">
-        <v>3.48615875265769</v>
+        <v>3.489546742209632</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -33073,10 +33073,10 @@
         <v>1</v>
       </c>
       <c r="M437" t="n">
-        <v>-0.9538412473423099</v>
+        <v>-0.9504532577903682</v>
       </c>
       <c r="N437" t="n">
-        <v>0.9538412473423099</v>
+        <v>0.9504532577903682</v>
       </c>
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
@@ -33116,10 +33116,10 @@
         <v>8</v>
       </c>
       <c r="G438" t="n">
-        <v>0.8086463501063076</v>
+        <v>0.8087818696883853</v>
       </c>
       <c r="H438" t="n">
-        <v>3.346690290574061</v>
+        <v>3.347422096317281</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -33138,16 +33138,16 @@
         <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>-0.8958097094259396</v>
+        <v>-0.8950779036827199</v>
       </c>
       <c r="N438" t="n">
-        <v>0.8958097094259396</v>
+        <v>0.8950779036827199</v>
       </c>
       <c r="O438" t="n">
         <v>-0.1974999999999998</v>
       </c>
       <c r="P438" t="n">
-        <v>-0.1394684620836295</v>
+        <v>-0.1421246458923515</v>
       </c>
       <c r="Q438" t="inlineStr">
         <is>
@@ -33187,10 +33187,10 @@
         <v>8</v>
       </c>
       <c r="G439" t="n">
-        <v>0.7994330262225372</v>
+        <v>0.7995750708215298</v>
       </c>
       <c r="H439" t="n">
-        <v>3.29346917080085</v>
+        <v>3.293852691218131</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -33209,16 +33209,16 @@
         <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>-0.81653082919915</v>
+        <v>-0.8161473087818698</v>
       </c>
       <c r="N439" t="n">
-        <v>0.81653082919915</v>
+        <v>0.8161473087818698</v>
       </c>
       <c r="O439" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P439" t="n">
-        <v>-0.05322111977321065</v>
+        <v>-0.0535694050991502</v>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
@@ -33258,10 +33258,10 @@
         <v>8</v>
       </c>
       <c r="G440" t="n">
-        <v>0.8036853295535081</v>
+        <v>0.8038243626062322</v>
       </c>
       <c r="H440" t="n">
-        <v>3.309900779588944</v>
+        <v>3.311303116147308</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -33280,16 +33280,16 @@
         <v>1</v>
       </c>
       <c r="M440" t="n">
-        <v>-0.6600992204110563</v>
+        <v>-0.6586968838526919</v>
       </c>
       <c r="N440" t="n">
-        <v>0.6600992204110563</v>
+        <v>0.6586968838526919</v>
       </c>
       <c r="O440" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P440" t="n">
-        <v>0.01643160878809358</v>
+        <v>0.01745042492917781</v>
       </c>
       <c r="Q440" t="inlineStr">
         <is>
@@ -33329,10 +33329,10 @@
         <v>8</v>
       </c>
       <c r="G441" t="n">
-        <v>0.8214032600992204</v>
+        <v>0.8215297450424929</v>
       </c>
       <c r="H441" t="n">
-        <v>3.46115520907158</v>
+        <v>3.462521246458923</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -33351,16 +33351,16 @@
         <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>-0.3688447909284198</v>
+        <v>-0.3674787535410768</v>
       </c>
       <c r="N441" t="n">
-        <v>0.3688447909284198</v>
+        <v>0.3674787535410768</v>
       </c>
       <c r="O441" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P441" t="n">
-        <v>0.1512544294826363</v>
+        <v>0.1512181303116149</v>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
@@ -33400,10 +33400,10 @@
         <v>8</v>
       </c>
       <c r="G442" t="n">
-        <v>0.8377037562012757</v>
+        <v>0.8378186968838527</v>
       </c>
       <c r="H442" t="n">
-        <v>3.644800377982519</v>
+        <v>3.645627950897073</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -33422,16 +33422,16 @@
         <v>1</v>
       </c>
       <c r="M442" t="n">
-        <v>-0.01519962201748148</v>
+        <v>-0.01437204910292733</v>
       </c>
       <c r="N442" t="n">
-        <v>0.01519962201748148</v>
+        <v>0.01437204910292733</v>
       </c>
       <c r="O442" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P442" t="n">
-        <v>0.1836451689109384</v>
+        <v>0.1831067044381496</v>
       </c>
       <c r="Q442" t="inlineStr">
         <is>
@@ -33471,10 +33471,10 @@
         <v>8</v>
       </c>
       <c r="G443" t="n">
-        <v>0.8476257973068746</v>
+        <v>0.8477337110481586</v>
       </c>
       <c r="H443" t="n">
-        <v>3.721089652728562</v>
+        <v>3.721381019830029</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -33493,16 +33493,16 @@
         <v>1</v>
       </c>
       <c r="M443" t="n">
-        <v>0.08108965272856139</v>
+        <v>0.08138101983002866</v>
       </c>
       <c r="N443" t="n">
-        <v>0.08108965272856139</v>
+        <v>0.08138101983002866</v>
       </c>
       <c r="O443" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P443" t="n">
-        <v>0.07628927474604286</v>
+        <v>0.07575306893295597</v>
       </c>
       <c r="Q443" t="inlineStr">
         <is>
@@ -33542,10 +33542,10 @@
         <v>8</v>
       </c>
       <c r="G444" t="n">
-        <v>0.8554216867469879</v>
+        <v>0.8555240793201133</v>
       </c>
       <c r="H444" t="n">
-        <v>3.754277108433735</v>
+        <v>3.754830028328612</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -33564,16 +33564,16 @@
         <v>1</v>
       </c>
       <c r="M444" t="n">
-        <v>0.1542771084337344</v>
+        <v>0.1548300283286115</v>
       </c>
       <c r="N444" t="n">
-        <v>0.1542771084337344</v>
+        <v>0.1548300283286115</v>
       </c>
       <c r="O444" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P444" t="n">
-        <v>0.03318745570517301</v>
+        <v>0.03344900849858279</v>
       </c>
       <c r="Q444" t="inlineStr">
         <is>
@@ -33613,10 +33613,10 @@
         <v>8</v>
       </c>
       <c r="G445" t="n">
-        <v>0.8582565556343019</v>
+        <v>0.8583569405099151</v>
       </c>
       <c r="H445" t="n">
-        <v>3.767085400425231</v>
+        <v>3.767563739376771</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -33635,16 +33635,16 @@
         <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>0.2345854004252304</v>
+        <v>0.2350637393767707</v>
       </c>
       <c r="N445" t="n">
-        <v>0.2345854004252304</v>
+        <v>0.2350637393767707</v>
       </c>
       <c r="O445" t="n">
         <v>-0.06749999999999989</v>
       </c>
       <c r="P445" t="n">
-        <v>0.01280829199149602</v>
+        <v>0.01273371104815935</v>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
@@ -33684,10 +33684,10 @@
         <v>8</v>
       </c>
       <c r="G446" t="n">
-        <v>0.8504606661941885</v>
+        <v>0.8505665722379604</v>
       </c>
       <c r="H446" t="n">
-        <v>3.732487597448618</v>
+        <v>3.733059490084986</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -33706,16 +33706,16 @@
         <v>1</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2924875974486176</v>
+        <v>0.2930594900849859</v>
       </c>
       <c r="N446" t="n">
-        <v>0.2924875974486176</v>
+        <v>0.2930594900849859</v>
       </c>
       <c r="O446" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P446" t="n">
-        <v>-0.03459780297661297</v>
+        <v>-0.03450424929178508</v>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
@@ -33755,10 +33755,10 @@
         <v>8</v>
       </c>
       <c r="G447" t="n">
-        <v>0.8398299078667611</v>
+        <v>0.839943342776204</v>
       </c>
       <c r="H447" t="n">
-        <v>3.660285258681786</v>
+        <v>3.662429178470255</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -33777,16 +33777,16 @@
         <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>0.3702852586817862</v>
+        <v>0.3724291784702554</v>
       </c>
       <c r="N447" t="n">
-        <v>0.3702852586817862</v>
+        <v>0.3724291784702554</v>
       </c>
       <c r="O447" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.07220233876683135</v>
+        <v>-0.07063031161473043</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
@@ -33826,10 +33826,10 @@
         <v>8</v>
       </c>
       <c r="G448" t="n">
-        <v>0.815024805102764</v>
+        <v>0.8151558073654391</v>
       </c>
       <c r="H448" t="n">
-        <v>3.415566973777463</v>
+        <v>3.415920679886686</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -33848,16 +33848,16 @@
         <v>1</v>
       </c>
       <c r="M448" t="n">
-        <v>0.2355669737774626</v>
+        <v>0.2359206798866857</v>
       </c>
       <c r="N448" t="n">
-        <v>0.2355669737774626</v>
+        <v>0.2359206798866857</v>
       </c>
       <c r="O448" t="n">
         <v>-0.1099999999999999</v>
       </c>
       <c r="P448" t="n">
-        <v>-0.2447182849043235</v>
+        <v>-0.2465084985835695</v>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
@@ -33897,10 +33897,10 @@
         <v>8</v>
       </c>
       <c r="G449" t="n">
-        <v>0.7831325301204819</v>
+        <v>0.78328611898017</v>
       </c>
       <c r="H449" t="n">
-        <v>3.213915662650602</v>
+        <v>3.214745042492918</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -33919,16 +33919,16 @@
         <v>1</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1139156626506024</v>
+        <v>0.1147450424929177</v>
       </c>
       <c r="N449" t="n">
-        <v>0.1139156626506024</v>
+        <v>0.1147450424929177</v>
       </c>
       <c r="O449" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P449" t="n">
-        <v>-0.2016513111268603</v>
+        <v>-0.2011756373937681</v>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
@@ -33968,10 +33968,10 @@
         <v>8</v>
       </c>
       <c r="G450" t="n">
-        <v>0.7661233167965982</v>
+        <v>0.7662889518413598</v>
       </c>
       <c r="H450" t="n">
-        <v>3.10413182140326</v>
+        <v>3.105920679886686</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -33990,16 +33990,16 @@
         <v>1</v>
       </c>
       <c r="M450" t="n">
-        <v>0.004131821403260183</v>
+        <v>0.005920679886685765</v>
       </c>
       <c r="N450" t="n">
-        <v>0.004131821403260183</v>
+        <v>0.005920679886685765</v>
       </c>
       <c r="O450" t="n">
         <v>0</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.1097838412473422</v>
+        <v>-0.108824362606232</v>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
@@ -35311,10 +35311,10 @@
         <v>8</v>
       </c>
       <c r="G469" t="n">
-        <v>0.8426647767540751</v>
+        <v>0.8427762039660056</v>
       </c>
       <c r="H469" t="n">
-        <v>8.545931963146705</v>
+        <v>8.548371104815864</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -35333,16 +35333,16 @@
         <v>1</v>
       </c>
       <c r="M469" t="n">
-        <v>-0.6940680368532952</v>
+        <v>-0.6916288951841363</v>
       </c>
       <c r="N469" t="n">
-        <v>0.6940680368532952</v>
+        <v>0.6916288951841363</v>
       </c>
       <c r="O469" t="n">
         <v>-0.08999999999999986</v>
       </c>
       <c r="P469" t="n">
-        <v>0.2469620962931671</v>
+        <v>0.2494012379623261</v>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
@@ -35382,10 +35382,10 @@
         <v>8</v>
       </c>
       <c r="G470" t="n">
-        <v>0.8256555634301913</v>
+        <v>0.8257790368271954</v>
       </c>
       <c r="H470" t="n">
-        <v>8.278327427356484</v>
+        <v>8.279801699716714</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -35404,16 +35404,16 @@
         <v>1</v>
       </c>
       <c r="M470" t="n">
-        <v>-0.7716725726435172</v>
+        <v>-0.7701983002832868</v>
       </c>
       <c r="N470" t="n">
-        <v>0.7716725726435172</v>
+        <v>0.7701983002832868</v>
       </c>
       <c r="O470" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P470" t="n">
-        <v>-0.2676045357902215</v>
+        <v>-0.2685694050991501</v>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -35453,10 +35453,10 @@
         <v>8</v>
       </c>
       <c r="G471" t="n">
-        <v>0.8065201984408221</v>
+        <v>0.806657223796034</v>
       </c>
       <c r="H471" t="n">
-        <v>7.989702338766833</v>
+        <v>7.992974504249292</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -35475,16 +35475,16 @@
         <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.9202976612331675</v>
+        <v>-0.9170254957507078</v>
       </c>
       <c r="N471" t="n">
-        <v>0.9202976612331675</v>
+        <v>0.9170254957507078</v>
       </c>
       <c r="O471" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P471" t="n">
-        <v>-0.2886250885896509</v>
+        <v>-0.2868271954674215</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
@@ -35524,10 +35524,10 @@
         <v>8</v>
       </c>
       <c r="G472" t="n">
-        <v>0.7944720056697377</v>
+        <v>0.7946175637393768</v>
       </c>
       <c r="H472" t="n">
-        <v>7.892997873848334</v>
+        <v>7.893866855524079</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -35546,16 +35546,16 @@
         <v>1</v>
       </c>
       <c r="M472" t="n">
-        <v>-0.8770021261516652</v>
+        <v>-0.8761331444759204</v>
       </c>
       <c r="N472" t="n">
-        <v>0.8770021261516652</v>
+        <v>0.8761331444759204</v>
       </c>
       <c r="O472" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P472" t="n">
-        <v>-0.09670446491849827</v>
+        <v>-0.09910764872521316</v>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
@@ -35595,10 +35595,10 @@
         <v>8</v>
       </c>
       <c r="G473" t="n">
-        <v>0.7923458540042523</v>
+        <v>0.7924929178470255</v>
       </c>
       <c r="H473" t="n">
-        <v>7.870609496810772</v>
+        <v>7.872365439093484</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -35617,16 +35617,16 @@
         <v>1</v>
       </c>
       <c r="M473" t="n">
-        <v>-0.709390503189228</v>
+        <v>-0.7076345609065164</v>
       </c>
       <c r="N473" t="n">
-        <v>0.709390503189228</v>
+        <v>0.7076345609065164</v>
       </c>
       <c r="O473" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P473" t="n">
-        <v>-0.02238837703756236</v>
+        <v>-0.02150141643059555</v>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
@@ -35666,10 +35666,10 @@
         <v>8</v>
       </c>
       <c r="G474" t="n">
-        <v>0.8029766123316796</v>
+        <v>0.8031161473087819</v>
       </c>
       <c r="H474" t="n">
-        <v>7.927923458540042</v>
+        <v>7.928201133144475</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -35688,16 +35688,16 @@
         <v>1</v>
       </c>
       <c r="M474" t="n">
-        <v>-0.5220765414599571</v>
+        <v>-0.5217988668555238</v>
       </c>
       <c r="N474" t="n">
-        <v>0.5220765414599571</v>
+        <v>0.5217988668555238</v>
       </c>
       <c r="O474" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P474" t="n">
-        <v>0.05731396172927017</v>
+        <v>0.05583569405099187</v>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
@@ -35737,10 +35737,10 @@
         <v>8</v>
       </c>
       <c r="G475" t="n">
-        <v>0.8157335223245925</v>
+        <v>0.8158640226628895</v>
       </c>
       <c r="H475" t="n">
-        <v>8.193309709425938</v>
+        <v>8.193569405099149</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -35759,16 +35759,16 @@
         <v>1</v>
       </c>
       <c r="M475" t="n">
-        <v>-0.1266902905740626</v>
+        <v>-0.1264305949008513</v>
       </c>
       <c r="N475" t="n">
-        <v>0.1266902905740626</v>
+        <v>0.1264305949008513</v>
       </c>
       <c r="O475" t="n">
         <v>-0.129999999999999</v>
       </c>
       <c r="P475" t="n">
-        <v>0.2653862508858955</v>
+        <v>0.2653682719546735</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
@@ -35808,10 +35808,10 @@
         <v>8</v>
       </c>
       <c r="G476" t="n">
-        <v>0.8277817150956768</v>
+        <v>0.8279036827195467</v>
       </c>
       <c r="H476" t="n">
-        <v>8.30371367824238</v>
+        <v>8.305169971671388</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -35830,16 +35830,16 @@
         <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>0.04371367824237993</v>
+        <v>0.04516997167138825</v>
       </c>
       <c r="N476" t="n">
-        <v>0.04371367824237993</v>
+        <v>0.04516997167138825</v>
       </c>
       <c r="O476" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P476" t="n">
-        <v>0.110403968816442</v>
+        <v>0.111600566572239</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
@@ -35879,10 +35879,10 @@
         <v>8</v>
       </c>
       <c r="G477" t="n">
-        <v>0.8362863217576187</v>
+        <v>0.8364022662889519</v>
       </c>
       <c r="H477" t="n">
-        <v>8.458419560595322</v>
+        <v>8.458881019830029</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -35901,16 +35901,16 @@
         <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>0.258419560595323</v>
+        <v>0.2588810198300298</v>
       </c>
       <c r="N477" t="n">
-        <v>0.258419560595323</v>
+        <v>0.2588810198300298</v>
       </c>
       <c r="O477" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P477" t="n">
-        <v>0.1547058823529426</v>
+        <v>0.153711048158641</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -35950,10 +35950,10 @@
         <v>8</v>
       </c>
       <c r="G478" t="n">
-        <v>0.8369950389794472</v>
+        <v>0.8371104815864022</v>
       </c>
       <c r="H478" t="n">
-        <v>8.4612402551382</v>
+        <v>8.461699716713881</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -35972,16 +35972,16 @@
         <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>0.4112402551381997</v>
+        <v>0.4116997167138798</v>
       </c>
       <c r="N478" t="n">
-        <v>0.4112402551381997</v>
+        <v>0.4116997167138798</v>
       </c>
       <c r="O478" t="n">
         <v>-0.1499999999999986</v>
       </c>
       <c r="P478" t="n">
-        <v>0.002820694542878144</v>
+        <v>0.002818696883851501</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -36021,10 +36021,10 @@
         <v>8</v>
       </c>
       <c r="G479" t="n">
-        <v>0.8320340184266478</v>
+        <v>0.8321529745042493</v>
       </c>
       <c r="H479" t="n">
-        <v>8.394720056697379</v>
+        <v>8.39779745042493</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -36043,16 +36043,16 @@
         <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>0.4747200566973788</v>
+        <v>0.47779745042493</v>
       </c>
       <c r="N479" t="n">
-        <v>0.4747200566973788</v>
+        <v>0.47779745042493</v>
       </c>
       <c r="O479" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P479" t="n">
-        <v>-0.06652019844082169</v>
+        <v>-0.06390226628895057</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -36092,10 +36092,10 @@
         <v>8</v>
       </c>
       <c r="G480" t="n">
-        <v>0.8192771084337349</v>
+        <v>0.8194050991501416</v>
       </c>
       <c r="H480" t="n">
-        <v>8.202168674698795</v>
+        <v>8.20369688385269</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -36114,16 +36114,16 @@
         <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0.4621686746987947</v>
+        <v>0.4636968838526894</v>
       </c>
       <c r="N480" t="n">
-        <v>0.4621686746987947</v>
+        <v>0.4636968838526894</v>
       </c>
       <c r="O480" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P480" t="n">
-        <v>-0.1925513819985838</v>
+        <v>-0.1941005665722404</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -36266,34 +36266,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.736</v>
+        <v>7.73</v>
       </c>
       <c r="G2" t="n">
-        <v>7.822</v>
+        <v>7.805</v>
       </c>
       <c r="H2" t="n">
-        <v>7.921</v>
+        <v>7.881</v>
       </c>
       <c r="I2" t="n">
-        <v>7.915</v>
+        <v>7.881</v>
       </c>
       <c r="J2" t="n">
-        <v>7.76</v>
+        <v>7.755</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.155</v>
+        <v>-0.126</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>30</v>
       </c>
       <c r="O2" t="n">
-        <v>5.829</v>
+        <v>5.83</v>
       </c>
       <c r="P2" t="n">
         <v>5.81</v>
@@ -36342,34 +36342,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.603</v>
+        <v>5.587</v>
       </c>
       <c r="G3" t="n">
-        <v>5.717</v>
+        <v>5.677</v>
       </c>
       <c r="H3" t="n">
-        <v>5.916</v>
+        <v>5.84</v>
       </c>
       <c r="I3" t="n">
-        <v>5.897</v>
+        <v>5.84</v>
       </c>
       <c r="J3" t="n">
-        <v>5.61</v>
+        <v>5.588</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.287</v>
+        <v>-0.252</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>0.489</v>
       </c>
       <c r="P3" t="n">
-        <v>0.337</v>
+        <v>0.338</v>
       </c>
       <c r="Q3" t="n">
         <v>0.316</v>
@@ -36418,34 +36418,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.169</v>
+        <v>4.205</v>
       </c>
       <c r="G4" t="n">
-        <v>4.521</v>
+        <v>4.425</v>
       </c>
       <c r="H4" t="n">
-        <v>5.665</v>
+        <v>4.664</v>
       </c>
       <c r="I4" t="n">
-        <v>4.731</v>
+        <v>4.664</v>
       </c>
       <c r="J4" t="n">
-        <v>4.62</v>
+        <v>4.454</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.111</v>
+        <v>-0.21</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -36461,10 +36461,10 @@
         <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>0.948</v>
+        <v>0.949</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="Q4" t="n">
         <v>0.29</v>
@@ -36494,34 +36494,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.784</v>
+        <v>10.779</v>
       </c>
       <c r="G5" t="n">
-        <v>11.312</v>
+        <v>11.398</v>
       </c>
       <c r="H5" t="n">
-        <v>11.811</v>
+        <v>11.859</v>
       </c>
       <c r="I5" t="n">
-        <v>11.206</v>
+        <v>10.979</v>
       </c>
       <c r="J5" t="n">
-        <v>11.778</v>
+        <v>11.856</v>
       </c>
       <c r="K5" t="n">
-        <v>0.572</v>
+        <v>0.877</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -36546,7 +36546,7 @@
         <v>3.915</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.724</v>
+        <v>-1.725</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -36570,34 +36570,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>53.888</v>
+        <v>53.884</v>
       </c>
       <c r="G6" t="n">
-        <v>81.90300000000001</v>
+        <v>64.67400000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>113.668</v>
+        <v>110.847</v>
       </c>
       <c r="I6" t="n">
-        <v>71.45399999999999</v>
+        <v>58.659</v>
       </c>
       <c r="J6" t="n">
-        <v>110.131</v>
+        <v>82.191</v>
       </c>
       <c r="K6" t="n">
-        <v>38.677</v>
+        <v>23.531</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -36613,13 +36613,13 @@
         <v>13</v>
       </c>
       <c r="O6" t="n">
-        <v>92.012</v>
+        <v>92.01300000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>88.682</v>
+        <v>88.684</v>
       </c>
       <c r="Q6" t="n">
-        <v>88.682</v>
+        <v>88.684</v>
       </c>
       <c r="R6" t="n">
         <v>-3.322</v>
@@ -36646,34 +36646,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.746</v>
+        <v>7.735</v>
       </c>
       <c r="G7" t="n">
-        <v>8.052</v>
+        <v>7.988</v>
       </c>
       <c r="H7" t="n">
-        <v>8.268000000000001</v>
+        <v>8.202</v>
       </c>
       <c r="I7" t="n">
-        <v>8.247999999999999</v>
+        <v>8.202</v>
       </c>
       <c r="J7" t="n">
-        <v>7.762</v>
+        <v>7.736</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.486</v>
+        <v>-0.466</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -36722,34 +36722,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.487</v>
+        <v>6.2</v>
       </c>
       <c r="G8" t="n">
-        <v>7.158</v>
+        <v>6.986</v>
       </c>
       <c r="H8" t="n">
-        <v>7.7</v>
+        <v>7.469</v>
       </c>
       <c r="I8" t="n">
-        <v>7.574</v>
+        <v>7.469</v>
       </c>
       <c r="J8" t="n">
-        <v>6.548</v>
+        <v>6.203</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.025</v>
+        <v>-1.266</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -36765,13 +36765,13 @@
         <v>29</v>
       </c>
       <c r="O8" t="n">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="P8" t="n">
         <v>0.395</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
       <c r="R8" t="n">
         <v>0.827</v>
@@ -36798,38 +36798,38 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.014</v>
+        <v>5.025</v>
       </c>
       <c r="G9" t="n">
-        <v>5.319</v>
+        <v>5.325</v>
       </c>
       <c r="H9" t="n">
         <v>5.61</v>
       </c>
       <c r="I9" t="n">
-        <v>5.017</v>
+        <v>5.133</v>
       </c>
       <c r="J9" t="n">
-        <v>5.142</v>
+        <v>5.103</v>
       </c>
       <c r="K9" t="n">
-        <v>0.125</v>
+        <v>-0.03</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -36841,13 +36841,13 @@
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>0.513</v>
+        <v>0.514</v>
       </c>
       <c r="P9" t="n">
         <v>0.424</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.26</v>
+        <v>0.261</v>
       </c>
       <c r="R9" t="n">
         <v>0.215</v>
@@ -36874,34 +36874,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.41</v>
+        <v>5.404</v>
       </c>
       <c r="G10" t="n">
-        <v>5.465</v>
+        <v>5.439</v>
       </c>
       <c r="H10" t="n">
-        <v>5.697</v>
+        <v>5.52</v>
       </c>
       <c r="I10" t="n">
-        <v>5.625</v>
+        <v>5.52</v>
       </c>
       <c r="J10" t="n">
-        <v>5.439</v>
+        <v>5.427</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.186</v>
+        <v>-0.093</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -36950,38 +36950,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.886</v>
+        <v>2.872</v>
       </c>
       <c r="G11" t="n">
-        <v>4.158</v>
+        <v>3.627</v>
       </c>
       <c r="H11" t="n">
-        <v>8.430999999999999</v>
+        <v>4.261</v>
       </c>
       <c r="I11" t="n">
-        <v>4.886</v>
+        <v>4.261</v>
       </c>
       <c r="J11" t="n">
-        <v>6.337</v>
+        <v>3.453</v>
       </c>
       <c r="K11" t="n">
-        <v>1.451</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -37026,34 +37026,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.039</v>
+        <v>6.024</v>
       </c>
       <c r="G12" t="n">
-        <v>6.14</v>
+        <v>6.103</v>
       </c>
       <c r="H12" t="n">
-        <v>6.281</v>
+        <v>6.237</v>
       </c>
       <c r="I12" t="n">
-        <v>6.276</v>
+        <v>6.237</v>
       </c>
       <c r="J12" t="n">
-        <v>6.05</v>
+        <v>6.025</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.227</v>
+        <v>-0.212</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>-0.24</v>
       </c>
       <c r="R12" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -37102,34 +37102,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.59</v>
+        <v>9.577999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>9.929</v>
+        <v>9.861000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>10.189</v>
+        <v>10.17</v>
       </c>
       <c r="I13" t="n">
-        <v>10.184</v>
+        <v>10.17</v>
       </c>
       <c r="J13" t="n">
-        <v>9.736000000000001</v>
+        <v>9.631</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.448</v>
+        <v>-0.539</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -37178,34 +37178,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.816</v>
+        <v>5.741</v>
       </c>
       <c r="G14" t="n">
-        <v>5.892</v>
+        <v>5.851</v>
       </c>
       <c r="H14" t="n">
-        <v>6.168</v>
+        <v>5.943</v>
       </c>
       <c r="I14" t="n">
-        <v>6.07</v>
+        <v>5.943</v>
       </c>
       <c r="J14" t="n">
-        <v>5.868</v>
+        <v>5.742</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.202</v>
+        <v>-0.201</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -37254,34 +37254,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.541</v>
+        <v>6.532</v>
       </c>
       <c r="G15" t="n">
-        <v>6.586</v>
+        <v>6.575</v>
       </c>
       <c r="H15" t="n">
-        <v>6.648</v>
+        <v>6.596</v>
       </c>
       <c r="I15" t="n">
-        <v>6.632</v>
+        <v>6.596</v>
       </c>
       <c r="J15" t="n">
-        <v>6.544</v>
+        <v>6.534</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.063</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>-1.506</v>
       </c>
       <c r="R15" t="n">
-        <v>0.285</v>
+        <v>0.284</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -37330,34 +37330,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.212</v>
+        <v>4.058</v>
       </c>
       <c r="G16" t="n">
-        <v>5.311</v>
+        <v>4.848</v>
       </c>
       <c r="H16" t="n">
-        <v>7.488</v>
+        <v>6.288</v>
       </c>
       <c r="I16" t="n">
-        <v>5.591</v>
+        <v>5.155</v>
       </c>
       <c r="J16" t="n">
-        <v>6.766</v>
+        <v>5.648</v>
       </c>
       <c r="K16" t="n">
-        <v>1.175</v>
+        <v>0.493</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -37406,34 +37406,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.004</v>
+        <v>3.934</v>
       </c>
       <c r="G17" t="n">
-        <v>4.525</v>
+        <v>4.411</v>
       </c>
       <c r="H17" t="n">
-        <v>4.932</v>
+        <v>4.88</v>
       </c>
       <c r="I17" t="n">
-        <v>4.921</v>
+        <v>4.88</v>
       </c>
       <c r="J17" t="n">
-        <v>4.05</v>
+        <v>3.978</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.871</v>
+        <v>-0.901</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>0.406</v>
+        <v>0.405</v>
       </c>
       <c r="P17" t="n">
         <v>0.338</v>
@@ -37458,7 +37458,7 @@
         <v>-0.075</v>
       </c>
       <c r="R17" t="n">
-        <v>0.835</v>
+        <v>0.834</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -37482,34 +37482,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.582</v>
+        <v>2.565</v>
       </c>
       <c r="G18" t="n">
-        <v>2.713</v>
+        <v>2.665</v>
       </c>
       <c r="H18" t="n">
-        <v>3.026</v>
+        <v>2.881</v>
       </c>
       <c r="I18" t="n">
-        <v>2.948</v>
+        <v>2.881</v>
       </c>
       <c r="J18" t="n">
-        <v>2.591</v>
+        <v>2.568</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.357</v>
+        <v>-0.313</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -37525,13 +37525,13 @@
         <v>14</v>
       </c>
       <c r="O18" t="n">
-        <v>0.488</v>
+        <v>0.487</v>
       </c>
       <c r="P18" t="n">
         <v>0.371</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.159</v>
+        <v>-0.158</v>
       </c>
       <c r="R18" t="n">
         <v>-0.11</v>
@@ -37558,34 +37558,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
+        <v>5.767</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.909</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.207</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.207</v>
+      </c>
+      <c r="J19" t="n">
         <v>5.782</v>
       </c>
-      <c r="G19" t="n">
-        <v>6.061</v>
-      </c>
-      <c r="H19" t="n">
-        <v>7.669</v>
-      </c>
-      <c r="I19" t="n">
-        <v>6.974</v>
-      </c>
-      <c r="J19" t="n">
-        <v>5.873</v>
-      </c>
       <c r="K19" t="n">
-        <v>-1.101</v>
+        <v>-0.425</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -37607,10 +37607,10 @@
         <v>0.778</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.668</v>
+        <v>-0.667</v>
       </c>
       <c r="R19" t="n">
-        <v>0.508</v>
+        <v>0.507</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -486,7 +486,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>299952</v>
+        <v>299970</v>
       </c>
       <c r="E2" t="n">
         <v>151106</v>
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -683,19 +683,19 @@
         <v>9.765000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>7.753</v>
+        <v>7.754</v>
       </c>
       <c r="J2" t="n">
         <v>-1.52</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.012</v>
+        <v>-2.011</v>
       </c>
       <c r="L2" t="n">
         <v>0.395</v>
       </c>
       <c r="M2" t="n">
-        <v>0.395</v>
+        <v>0.396</v>
       </c>
       <c r="N2" t="n">
         <v>0.476</v>
@@ -704,10 +704,10 @@
         <v>0.866</v>
       </c>
       <c r="P2" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.827</v>
+        <v>0.828</v>
       </c>
       <c r="R2" t="n">
         <v>50</v>
@@ -765,13 +765,13 @@
         <v>7.883</v>
       </c>
       <c r="I3" t="n">
-        <v>5.826</v>
+        <v>5.827</v>
       </c>
       <c r="J3" t="n">
         <v>-2.472</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.057</v>
+        <v>-2.055</v>
       </c>
       <c r="L3" t="n">
         <v>-1.788</v>
@@ -780,13 +780,13 @@
         <v>1.788</v>
       </c>
       <c r="N3" t="n">
-        <v>1.823</v>
+        <v>1.822</v>
       </c>
       <c r="O3" t="n">
         <v>0.89</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.607</v>
+        <v>-4.605</v>
       </c>
       <c r="Q3" t="n">
         <v>0.758</v>
@@ -847,13 +847,13 @@
         <v>7.691</v>
       </c>
       <c r="I4" t="n">
-        <v>4.845</v>
+        <v>4.843</v>
       </c>
       <c r="J4" t="n">
         <v>-3.405</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.846</v>
+        <v>-2.848</v>
       </c>
       <c r="L4" t="n">
         <v>-0.075</v>
@@ -868,7 +868,7 @@
         <v>0.9409999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.833</v>
+        <v>0.834</v>
       </c>
       <c r="Q4" t="n">
         <v>0.834</v>
@@ -929,31 +929,31 @@
         <v>7.178</v>
       </c>
       <c r="I5" t="n">
-        <v>5.967</v>
+        <v>5.968</v>
       </c>
       <c r="J5" t="n">
         <v>-2.275</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.211</v>
+        <v>-1.21</v>
       </c>
       <c r="L5" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="M5" t="n">
         <v>0.338</v>
       </c>
       <c r="N5" t="n">
-        <v>0.489</v>
+        <v>0.49</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.931</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.57</v>
+        <v>0.569</v>
       </c>
       <c r="R5" t="n">
         <v>55.172</v>
@@ -1011,7 +1011,7 @@
         <v>8.468</v>
       </c>
       <c r="I6" t="n">
-        <v>6.229</v>
+        <v>6.23</v>
       </c>
       <c r="J6" t="n">
         <v>-2.07</v>
@@ -1032,10 +1032,10 @@
         <v>0.872</v>
       </c>
       <c r="P6" t="n">
-        <v>0.732</v>
+        <v>0.731</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.739</v>
+        <v>0.738</v>
       </c>
       <c r="R6" t="n">
         <v>31.034</v>
@@ -1093,13 +1093,13 @@
         <v>9.374000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.204000000000001</v>
+        <v>8.205</v>
       </c>
       <c r="J7" t="n">
         <v>-2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.171</v>
+        <v>-1.169</v>
       </c>
       <c r="L7" t="n">
         <v>-0.667</v>
@@ -1114,7 +1114,7 @@
         <v>0.711</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.356</v>
+        <v>-0.355</v>
       </c>
       <c r="Q7" t="n">
         <v>0.507</v>
@@ -1175,13 +1175,13 @@
         <v>9.863</v>
       </c>
       <c r="I8" t="n">
-        <v>7.933</v>
+        <v>7.935</v>
       </c>
       <c r="J8" t="n">
         <v>-2.008</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.929</v>
+        <v>-1.928</v>
       </c>
       <c r="L8" t="n">
         <v>5.81</v>
@@ -1196,7 +1196,7 @@
         <v>0.831</v>
       </c>
       <c r="P8" t="n">
-        <v>-45.919</v>
+        <v>-45.924</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.023</v>
@@ -1275,10 +1275,10 @@
         <v>0.949</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.665</v>
+        <v>-0.666</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.042</v>
@@ -1339,31 +1339,31 @@
         <v>11.017</v>
       </c>
       <c r="I10" t="n">
-        <v>11.484</v>
+        <v>11.49</v>
       </c>
       <c r="J10" t="n">
         <v>-1.39</v>
       </c>
       <c r="K10" t="n">
-        <v>0.468</v>
+        <v>0.473</v>
       </c>
       <c r="L10" t="n">
-        <v>3.915</v>
+        <v>3.916</v>
       </c>
       <c r="M10" t="n">
-        <v>3.915</v>
+        <v>3.916</v>
       </c>
       <c r="N10" t="n">
-        <v>4.211</v>
+        <v>4.212</v>
       </c>
       <c r="O10" t="n">
         <v>-0.491</v>
       </c>
       <c r="P10" t="n">
-        <v>-105.431</v>
+        <v>-105.463</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.725</v>
+        <v>-1.726</v>
       </c>
       <c r="R10" t="n">
         <v>41.379</v>
@@ -1418,10 +1418,10 @@
         <v>5.32</v>
       </c>
       <c r="H11" t="n">
-        <v>112.885</v>
+        <v>112.887</v>
       </c>
       <c r="I11" t="n">
-        <v>108.396</v>
+        <v>108.398</v>
       </c>
       <c r="J11" t="n">
         <v>-1.68</v>
@@ -1430,16 +1430,16 @@
         <v>-4.489</v>
       </c>
       <c r="L11" t="n">
-        <v>88.684</v>
+        <v>88.685</v>
       </c>
       <c r="M11" t="n">
-        <v>88.684</v>
+        <v>88.685</v>
       </c>
       <c r="N11" t="n">
-        <v>92.01300000000001</v>
+        <v>92.014</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.358</v>
+        <v>-0.357</v>
       </c>
       <c r="P11" t="n">
         <v>-13.682</v>
@@ -1462,13 +1462,13 @@
         <v>0.129</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.738</v>
+        <v>-0.737</v>
       </c>
       <c r="W11" t="n">
         <v>0.129</v>
       </c>
       <c r="X11" t="n">
-        <v>36.19</v>
+        <v>36.187</v>
       </c>
     </row>
     <row r="12">
@@ -1585,13 +1585,13 @@
         <v>5.956</v>
       </c>
       <c r="I13" t="n">
-        <v>5.126</v>
+        <v>5.124</v>
       </c>
       <c r="J13" t="n">
         <v>-0.6919999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.83</v>
+        <v>-0.831</v>
       </c>
       <c r="L13" t="n">
         <v>0.261</v>
@@ -1603,10 +1603,10 @@
         <v>0.514</v>
       </c>
       <c r="O13" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.089</v>
       </c>
       <c r="Q13" t="n">
         <v>0.215</v>
@@ -1667,13 +1667,13 @@
         <v>7.097</v>
       </c>
       <c r="I14" t="n">
-        <v>5.203</v>
+        <v>5.205</v>
       </c>
       <c r="J14" t="n">
         <v>-2.422</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.894</v>
+        <v>-1.892</v>
       </c>
       <c r="L14" t="n">
         <v>2.035</v>
@@ -1688,7 +1688,7 @@
         <v>0.615</v>
       </c>
       <c r="P14" t="n">
-        <v>-10.089</v>
+        <v>-10.09</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.553</v>
@@ -1708,7 +1708,7 @@
         <v>0.521</v>
       </c>
       <c r="V14" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="W14" t="n">
         <v>0.518</v>
@@ -1749,31 +1749,31 @@
         <v>8.144</v>
       </c>
       <c r="I15" t="n">
-        <v>6.352</v>
+        <v>6.353</v>
       </c>
       <c r="J15" t="n">
         <v>-1.525</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.792</v>
+        <v>-1.79</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.24</v>
+        <v>-0.239</v>
       </c>
       <c r="M15" t="n">
         <v>0.372</v>
       </c>
       <c r="N15" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.202</v>
+        <v>-0.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.395</v>
+        <v>0.396</v>
       </c>
       <c r="R15" t="n">
         <v>41.379</v>
@@ -1919,25 +1919,25 @@
         <v>-2.425</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.352</v>
+        <v>-1.351</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.506</v>
+        <v>-1.505</v>
       </c>
       <c r="M17" t="n">
-        <v>1.506</v>
+        <v>1.505</v>
       </c>
       <c r="N17" t="n">
-        <v>1.626</v>
+        <v>1.625</v>
       </c>
       <c r="O17" t="n">
-        <v>0.604</v>
+        <v>0.603</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.683</v>
+        <v>-3.681</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.284</v>
+        <v>0.283</v>
       </c>
       <c r="R17" t="n">
         <v>31.034</v>
@@ -1995,7 +1995,7 @@
         <v>7.154</v>
       </c>
       <c r="I18" t="n">
-        <v>6.292</v>
+        <v>6.293</v>
       </c>
       <c r="J18" t="n">
         <v>-1.55</v>
@@ -2004,10 +2004,10 @@
         <v>-0.862</v>
       </c>
       <c r="L18" t="n">
-        <v>1.538</v>
+        <v>1.539</v>
       </c>
       <c r="M18" t="n">
-        <v>1.538</v>
+        <v>1.539</v>
       </c>
       <c r="N18" t="n">
         <v>1.726</v>
@@ -2016,7 +2016,7 @@
         <v>0.61</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.627</v>
+        <v>-6.629</v>
       </c>
       <c r="Q18" t="n">
         <v>0.23</v>
@@ -2074,34 +2074,34 @@
         <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.49</v>
+        <v>3.493</v>
       </c>
       <c r="I19" t="n">
-        <v>3.106</v>
+        <v>3.108</v>
       </c>
       <c r="J19" t="n">
         <v>-1.34</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.384</v>
+        <v>-0.385</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.158</v>
+        <v>-0.157</v>
       </c>
       <c r="M19" t="n">
         <v>0.371</v>
       </c>
       <c r="N19" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.42</v>
+        <v>-0.416</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.11</v>
+        <v>-0.109</v>
       </c>
       <c r="R19" t="n">
         <v>46.154</v>
@@ -3392,10 +3392,10 @@
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.853399433427762</v>
+        <v>0.8535031847133758</v>
       </c>
       <c r="H18" t="n">
-        <v>8.170276203966006</v>
+        <v>8.170605095541401</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>5.715276203966006</v>
+        <v>5.715605095541401</v>
       </c>
       <c r="N18" t="n">
-        <v>5.715276203966006</v>
+        <v>5.715605095541401</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1374999999999997</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7297518268679113</v>
+        <v>-0.7294229352925168</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8505665722379604</v>
+        <v>0.8506723283793347</v>
       </c>
       <c r="H19" t="n">
-        <v>8.15722202549575</v>
+        <v>8.157473460721869</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3485,16 +3485,16 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.744722025495751</v>
+        <v>5.744973460721869</v>
       </c>
       <c r="N19" t="n">
-        <v>5.744722025495751</v>
+        <v>5.744973460721869</v>
       </c>
       <c r="O19" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.01305417847025581</v>
+        <v>-0.01313163481953161</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8463172804532578</v>
+        <v>0.8464260438782731</v>
       </c>
       <c r="H20" t="n">
-        <v>8.13206444759207</v>
+        <v>8.132926397735316</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3556,16 +3556,16 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>5.732064447592069</v>
+        <v>5.732926397735316</v>
       </c>
       <c r="N20" t="n">
-        <v>5.732064447592069</v>
+        <v>5.732926397735316</v>
       </c>
       <c r="O20" t="n">
         <v>-0.01250000000000018</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.02515757790368056</v>
+        <v>-0.02454706298655296</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8434844192634561</v>
+        <v>0.8435951875442321</v>
       </c>
       <c r="H21" t="n">
-        <v>8.118845609065156</v>
+        <v>8.119196744515214</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>5.948845609065156</v>
+        <v>5.949196744515215</v>
       </c>
       <c r="N21" t="n">
-        <v>5.948845609065156</v>
+        <v>5.949196744515215</v>
       </c>
       <c r="O21" t="n">
         <v>-0.23</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.01321883852691386</v>
+        <v>-0.01372965322010167</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8385269121813032</v>
+        <v>0.8386411889596603</v>
       </c>
       <c r="H22" t="n">
-        <v>8.096260623229462</v>
+        <v>8.096985138004246</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3698,16 +3698,16 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>6.116260623229461</v>
+        <v>6.116985138004246</v>
       </c>
       <c r="N22" t="n">
-        <v>6.116260623229461</v>
+        <v>6.116985138004246</v>
       </c>
       <c r="O22" t="n">
         <v>-0.1899999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.02258498583569413</v>
+        <v>-0.0222116065109681</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8335694050991501</v>
+        <v>0.8336871903750884</v>
       </c>
       <c r="H23" t="n">
-        <v>8.059660056657224</v>
+        <v>8.061153573956121</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3769,16 +3769,16 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>6.009660056657224</v>
+        <v>6.011153573956121</v>
       </c>
       <c r="N23" t="n">
-        <v>6.009660056657224</v>
+        <v>6.011153573956121</v>
       </c>
       <c r="O23" t="n">
         <v>0.06999999999999984</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.03660056657223798</v>
+        <v>-0.03583156404812549</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3818,10 +3818,10 @@
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8271954674220963</v>
+        <v>0.8273177636234961</v>
       </c>
       <c r="H24" t="n">
-        <v>8.029999999999999</v>
+        <v>8.030000000000001</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3840,16 +3840,16 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>5.809999999999999</v>
+        <v>5.81</v>
       </c>
       <c r="N24" t="n">
-        <v>5.809999999999999</v>
+        <v>5.81</v>
       </c>
       <c r="O24" t="n">
         <v>0.1700000000000004</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.02966005665722449</v>
+        <v>-0.03115357395611973</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8222379603399433</v>
+        <v>0.8223637650389243</v>
       </c>
       <c r="H25" t="n">
-        <v>8.013247167138809</v>
+        <v>8.013446567586694</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3911,16 +3911,16 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>5.66324716713881</v>
+        <v>5.663446567586695</v>
       </c>
       <c r="N25" t="n">
-        <v>5.66324716713881</v>
+        <v>5.663446567586695</v>
       </c>
       <c r="O25" t="n">
         <v>0.1299999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01675283286119011</v>
+        <v>-0.01655343241330698</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3960,10 +3960,10 @@
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8194050991501416</v>
+        <v>0.8195329087048833</v>
       </c>
       <c r="H26" t="n">
-        <v>8.001271246458924</v>
+        <v>8.001878980891719</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3982,16 +3982,16 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>5.701271246458924</v>
+        <v>5.70187898089172</v>
       </c>
       <c r="N26" t="n">
-        <v>5.701271246458924</v>
+        <v>5.70187898089172</v>
       </c>
       <c r="O26" t="n">
         <v>-0.05000000000000027</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.01197592067988573</v>
+        <v>-0.01156758669497471</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8158640226628895</v>
+        <v>0.8159943382873319</v>
       </c>
       <c r="H27" t="n">
-        <v>7.974511331444758</v>
+        <v>7.975957183297948</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4053,16 +4053,16 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>5.744511331444759</v>
+        <v>5.745957183297948</v>
       </c>
       <c r="N27" t="n">
-        <v>5.744511331444759</v>
+        <v>5.745957183297948</v>
       </c>
       <c r="O27" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.02675991501416508</v>
+        <v>-0.02592179759377178</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8116147308781869</v>
+        <v>0.8117480537862704</v>
       </c>
       <c r="H28" t="n">
-        <v>7.947818696883853</v>
+        <v>7.948241330502477</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>5.887818696883853</v>
+        <v>5.888241330502478</v>
       </c>
       <c r="N28" t="n">
-        <v>5.887818696883853</v>
+        <v>5.888241330502478</v>
       </c>
       <c r="O28" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.02669263456090576</v>
+        <v>-0.0277158527954704</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8123229461756374</v>
+        <v>0.8124557678697806</v>
       </c>
       <c r="H29" t="n">
-        <v>7.950159348441927</v>
+        <v>7.951211960368012</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4195,16 +4195,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>6.000159348441927</v>
+        <v>6.001211960368011</v>
       </c>
       <c r="N29" t="n">
-        <v>6.000159348441927</v>
+        <v>6.001211960368011</v>
       </c>
       <c r="O29" t="n">
         <v>-0.1100000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>0.002340651558074391</v>
+        <v>0.002970629865534313</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8130311614730878</v>
+        <v>0.8131634819532909</v>
       </c>
       <c r="H30" t="n">
-        <v>7.955771954674221</v>
+        <v>7.956820594479829</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4266,16 +4266,16 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.255771954674221</v>
+        <v>5.256820594479829</v>
       </c>
       <c r="N30" t="n">
-        <v>5.255771954674221</v>
+        <v>5.256820594479829</v>
       </c>
       <c r="O30" t="n">
         <v>0.7500000000000002</v>
       </c>
       <c r="P30" t="n">
-        <v>0.005612606232293871</v>
+        <v>0.005608634111817778</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8094900849858357</v>
+        <v>0.8096249115357396</v>
       </c>
       <c r="H31" t="n">
-        <v>7.933250708215298</v>
+        <v>7.934532908704884</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4337,16 +4337,16 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.133250708215298</v>
+        <v>5.134532908704884</v>
       </c>
       <c r="N31" t="n">
-        <v>5.133250708215298</v>
+        <v>5.134532908704884</v>
       </c>
       <c r="O31" t="n">
         <v>0.09999999999999964</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.02252124645892284</v>
+        <v>-0.02228768577494566</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6487252124645893</v>
+        <v>0.6489738145789101</v>
       </c>
       <c r="H48" t="n">
-        <v>6.159074893767706</v>
+        <v>6.159169984076433</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5538,16 +5538,16 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1284251062322941</v>
+        <v>-0.1283300159235665</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1284251062322941</v>
+        <v>0.1283300159235665</v>
       </c>
       <c r="O48" t="n">
         <v>-0.09250000000000114</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.6248143844383209</v>
+        <v>-0.6247192941295934</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6423512747875354</v>
+        <v>0.6426043878273178</v>
       </c>
       <c r="H49" t="n">
-        <v>6.145594900849859</v>
+        <v>6.146369426751592</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5609,16 +5609,16 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.02440509915014122</v>
+        <v>-0.02363057324840767</v>
       </c>
       <c r="N49" t="n">
-        <v>0.02440509915014122</v>
+        <v>0.02363057324840767</v>
       </c>
       <c r="O49" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.01347999291784685</v>
+        <v>-0.01280055732484087</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5658,10 +5658,10 @@
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>0.6345609065155807</v>
+        <v>0.6348195329087049</v>
       </c>
       <c r="H50" t="n">
-        <v>6.123405099150141</v>
+        <v>6.12403821656051</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5680,16 +5680,16 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.03340509915014156</v>
+        <v>0.03403821656050976</v>
       </c>
       <c r="N50" t="n">
-        <v>0.03340509915014156</v>
+        <v>0.03403821656050976</v>
       </c>
       <c r="O50" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.02218980169971729</v>
+        <v>-0.02233121019108264</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5729,10 +5729,10 @@
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6331444759206799</v>
+        <v>0.6334041047416844</v>
       </c>
       <c r="H51" t="n">
-        <v>6.11998052407932</v>
+        <v>6.120573248407643</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5751,16 +5751,16 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.25998052407932</v>
+        <v>0.2605732484076428</v>
       </c>
       <c r="N51" t="n">
-        <v>0.25998052407932</v>
+        <v>0.2605732484076428</v>
       </c>
       <c r="O51" t="n">
         <v>-0.2299999999999995</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.003424575070821056</v>
+        <v>-0.003464968152866454</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>0.6444759206798867</v>
+        <v>0.6447275300778486</v>
       </c>
       <c r="H52" t="n">
-        <v>6.15628895184136</v>
+        <v>6.157545780254778</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5822,16 +5822,16 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4962889518413602</v>
+        <v>0.4975457802547778</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4962889518413602</v>
+        <v>0.4975457802547778</v>
       </c>
       <c r="O52" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P52" t="n">
-        <v>0.03630842776204002</v>
+        <v>0.03697253184713478</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6522662889518414</v>
+        <v>0.6525123849964615</v>
       </c>
       <c r="H53" t="n">
-        <v>6.165934844192635</v>
+        <v>6.166687898089172</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5893,16 +5893,16 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.535934844192635</v>
+        <v>0.5366878980891725</v>
       </c>
       <c r="N53" t="n">
-        <v>0.535934844192635</v>
+        <v>0.5366878980891725</v>
       </c>
       <c r="O53" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P53" t="n">
-        <v>0.009645892351274554</v>
+        <v>0.009142117834394448</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6621813031161473</v>
+        <v>0.6624203821656051</v>
       </c>
       <c r="H54" t="n">
-        <v>6.205033050047215</v>
+        <v>6.206008492569002</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5964,16 +5964,16 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6150330500472148</v>
+        <v>0.6160084925690024</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6150330500472148</v>
+        <v>0.6160084925690024</v>
       </c>
       <c r="O54" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P54" t="n">
-        <v>0.03909820585457968</v>
+        <v>0.03932059447982983</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6685552407932012</v>
+        <v>0.6687898089171974</v>
       </c>
       <c r="H55" t="n">
-        <v>6.217889518413598</v>
+        <v>6.218248407643312</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6035,16 +6035,16 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7678895184135976</v>
+        <v>0.7682484076433118</v>
       </c>
       <c r="N55" t="n">
-        <v>0.7678895184135976</v>
+        <v>0.7682484076433118</v>
       </c>
       <c r="O55" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01285646836638321</v>
+        <v>0.01223991507430977</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6650141643059491</v>
+        <v>0.6652512384996462</v>
       </c>
       <c r="H56" t="n">
-        <v>6.212471671388102</v>
+        <v>6.212834394904458</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6106,16 +6106,16 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8124716713881019</v>
+        <v>0.8128343949044581</v>
       </c>
       <c r="N56" t="n">
-        <v>0.8124716713881019</v>
+        <v>0.8128343949044581</v>
       </c>
       <c r="O56" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.005417847025495526</v>
+        <v>-0.005414012738853557</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
         <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6536827195467422</v>
+        <v>0.6539278131634819</v>
       </c>
       <c r="H57" t="n">
-        <v>6.170538243626062</v>
+        <v>6.172038216560509</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.800538243626062</v>
+        <v>0.8020382165605087</v>
       </c>
       <c r="N57" t="n">
-        <v>0.800538243626062</v>
+        <v>0.8020382165605087</v>
       </c>
       <c r="O57" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.04193342776204023</v>
+        <v>-0.04079617834394966</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6226,10 +6226,10 @@
         <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6381019830028328</v>
+        <v>0.6383581033262562</v>
       </c>
       <c r="H58" t="n">
-        <v>6.135061378659112</v>
+        <v>6.135583864118896</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6248,16 +6248,16 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8050613786591123</v>
+        <v>0.8055838641188959</v>
       </c>
       <c r="N58" t="n">
-        <v>0.8050613786591123</v>
+        <v>0.8055838641188959</v>
       </c>
       <c r="O58" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.03547686496694968</v>
+        <v>-0.03645435244161277</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6297,10 +6297,10 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6196883852691218</v>
+        <v>0.6199575371549894</v>
       </c>
       <c r="H59" t="n">
-        <v>6.074995278564684</v>
+        <v>6.076093418259023</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6319,16 +6319,16 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9249952785646833</v>
+        <v>0.9260934182590228</v>
       </c>
       <c r="N59" t="n">
-        <v>0.9249952785646833</v>
+        <v>0.9260934182590228</v>
       </c>
       <c r="O59" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.0600661000944287</v>
+        <v>-0.05949044585987284</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6055240793201133</v>
+        <v>0.6058032554847842</v>
       </c>
       <c r="H60" t="n">
-        <v>6.027903682719547</v>
+        <v>6.02875796178344</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6390,16 +6390,16 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1.057903682719547</v>
+        <v>1.05875796178344</v>
       </c>
       <c r="N60" t="n">
-        <v>1.057903682719547</v>
+        <v>1.05875796178344</v>
       </c>
       <c r="O60" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.04709159584513678</v>
+        <v>-0.04733545647558302</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6439,10 +6439,10 @@
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5906515580736544</v>
+        <v>0.5909412597310687</v>
       </c>
       <c r="H61" t="n">
-        <v>5.966525023607177</v>
+        <v>5.967707006369427</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6461,16 +6461,16 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1.136525023607176</v>
+        <v>1.137707006369427</v>
       </c>
       <c r="N61" t="n">
-        <v>1.136525023607176</v>
+        <v>1.137707006369427</v>
       </c>
       <c r="O61" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.06137865911237039</v>
+        <v>-0.06105095541401351</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -7640,10 +7640,10 @@
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8973087818696884</v>
+        <v>0.897381457891012</v>
       </c>
       <c r="H78" t="n">
-        <v>5.87672804532578</v>
+        <v>5.87757254069356</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7662,16 +7662,16 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1.18922804532578</v>
+        <v>1.19007254069356</v>
       </c>
       <c r="N78" t="n">
-        <v>1.18922804532578</v>
+        <v>1.19007254069356</v>
       </c>
       <c r="O78" t="n">
         <v>0.2725</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.06509746273308537</v>
+        <v>-0.06425296736530495</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8682719546742209</v>
+        <v>0.8683651804670913</v>
       </c>
       <c r="H79" t="n">
-        <v>5.689660056657225</v>
+        <v>5.690403397027602</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7733,16 +7733,16 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>1.277160056657225</v>
+        <v>1.277903397027602</v>
       </c>
       <c r="N79" t="n">
-        <v>1.277160056657225</v>
+        <v>1.277903397027602</v>
       </c>
       <c r="O79" t="n">
         <v>-0.2750000000000004</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.1870679886685549</v>
+        <v>-0.1871691436659582</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8257790368271954</v>
+        <v>0.8259023354564756</v>
       </c>
       <c r="H80" t="n">
-        <v>5.412776203966005</v>
+        <v>5.413492569002123</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7804,16 +7804,16 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7627762039660047</v>
+        <v>0.763492569002123</v>
       </c>
       <c r="N80" t="n">
-        <v>0.7627762039660047</v>
+        <v>0.763492569002123</v>
       </c>
       <c r="O80" t="n">
         <v>0.2375000000000007</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.2768838526912196</v>
+        <v>-0.2769108280254784</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7790368271954674</v>
+        <v>0.7791932059447984</v>
       </c>
       <c r="H81" t="n">
-        <v>5.151203966005665</v>
+        <v>5.152112526539279</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7875,16 +7875,16 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>0.4512039660056653</v>
+        <v>0.4521125265392785</v>
       </c>
       <c r="N81" t="n">
-        <v>0.4512039660056653</v>
+        <v>0.4521125265392785</v>
       </c>
       <c r="O81" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.2615722379603396</v>
+        <v>-0.2613800424628447</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7330028328611898</v>
+        <v>0.7331917905166313</v>
       </c>
       <c r="H82" t="n">
-        <v>4.993746458923513</v>
+        <v>4.994844302901628</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7946,16 +7946,16 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5887464589235138</v>
+        <v>0.5898443029016285</v>
       </c>
       <c r="N82" t="n">
-        <v>0.5887464589235138</v>
+        <v>0.5898443029016285</v>
       </c>
       <c r="O82" t="n">
         <v>-0.2950000000000008</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.1574575070821522</v>
+        <v>-0.1572682236376508</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -7995,10 +7995,10 @@
         <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7067988668555241</v>
+        <v>0.7070063694267515</v>
       </c>
       <c r="H83" t="n">
-        <v>4.86766761095373</v>
+        <v>4.868471337579618</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8017,16 +8017,16 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>0.770167610953731</v>
+        <v>0.7709713375796188</v>
       </c>
       <c r="N83" t="n">
-        <v>0.770167610953731</v>
+        <v>0.7709713375796188</v>
       </c>
       <c r="O83" t="n">
         <v>-0.3075000000000001</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.126078847969783</v>
+        <v>-0.1263729653220098</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -8066,10 +8066,10 @@
         <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>0.6749291784702549</v>
+        <v>0.6751592356687898</v>
       </c>
       <c r="H84" t="n">
-        <v>4.784668150546337</v>
+        <v>4.785050045495906</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8088,16 +8088,16 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>0.934668150546337</v>
+        <v>0.9350500454959056</v>
       </c>
       <c r="N84" t="n">
-        <v>0.934668150546337</v>
+        <v>0.9350500454959056</v>
       </c>
       <c r="O84" t="n">
         <v>-0.2474999999999992</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.08299946040739314</v>
+        <v>-0.0834212920837123</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6402266288951841</v>
+        <v>0.640481245576787</v>
       </c>
       <c r="H85" t="n">
-        <v>4.687287535410765</v>
+        <v>4.687699339466856</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8159,16 +8159,16 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9072875354107652</v>
+        <v>0.907699339466856</v>
       </c>
       <c r="N85" t="n">
-        <v>0.9072875354107652</v>
+        <v>0.907699339466856</v>
       </c>
       <c r="O85" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.09738061513557206</v>
+        <v>-0.09735070602904994</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6048158640226629</v>
+        <v>0.6043878273177636</v>
       </c>
       <c r="H86" t="n">
-        <v>4.551990084985835</v>
+        <v>4.550746638358103</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8230,16 +8230,16 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.2480099150141655</v>
+        <v>-0.2492533616418973</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2480099150141655</v>
+        <v>0.2492533616418973</v>
       </c>
       <c r="O86" t="n">
         <v>1.020000000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.1352974504249298</v>
+        <v>-0.1369527011087524</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -8279,10 +8279,10 @@
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>0.5977337110481586</v>
+        <v>0.5973106864826611</v>
       </c>
       <c r="H87" t="n">
-        <v>4.521416430594901</v>
+        <v>4.52018754423213</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8301,16 +8301,16 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.1785835694050997</v>
+        <v>-0.1798124557678706</v>
       </c>
       <c r="N87" t="n">
-        <v>0.1785835694050997</v>
+        <v>0.1798124557678706</v>
       </c>
       <c r="O87" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.03057365439093473</v>
+        <v>-0.03055909412597391</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -8350,10 +8350,10 @@
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6147308781869688</v>
+        <v>0.6142958244869073</v>
       </c>
       <c r="H88" t="n">
-        <v>4.574390934844192</v>
+        <v>4.572705826845954</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8372,16 +8372,16 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.6256090651558077</v>
+        <v>-0.6272941731540458</v>
       </c>
       <c r="N88" t="n">
-        <v>0.6256090651558077</v>
+        <v>0.6272941731540458</v>
       </c>
       <c r="O88" t="n">
         <v>0.5</v>
       </c>
       <c r="P88" t="n">
-        <v>0.05297450424929195</v>
+        <v>0.05251828261382485</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6579320113314447</v>
+        <v>0.6581740976645435</v>
       </c>
       <c r="H89" t="n">
-        <v>4.721292492917847</v>
+        <v>4.7219957537155</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8443,16 +8443,16 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.778707507082153</v>
+        <v>-0.7780042462845005</v>
       </c>
       <c r="N89" t="n">
-        <v>0.778707507082153</v>
+        <v>0.7780042462845005</v>
       </c>
       <c r="O89" t="n">
         <v>0.2999999999999998</v>
       </c>
       <c r="P89" t="n">
-        <v>0.1469015580736546</v>
+        <v>0.1492899268695451</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8492,10 +8492,10 @@
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6813031161473088</v>
+        <v>0.6815286624203821</v>
       </c>
       <c r="H90" t="n">
-        <v>4.794592776203966</v>
+        <v>4.794920382165605</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8514,16 +8514,16 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-1.085407223796034</v>
+        <v>-1.085079617834395</v>
       </c>
       <c r="N90" t="n">
-        <v>1.085407223796034</v>
+        <v>1.085079617834395</v>
       </c>
       <c r="O90" t="n">
         <v>0.3799999999999999</v>
       </c>
       <c r="P90" t="n">
-        <v>0.07330028328611871</v>
+        <v>0.07292462845010572</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8563,10 +8563,10 @@
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6841359773371105</v>
+        <v>0.6843595187544232</v>
       </c>
       <c r="H91" t="n">
-        <v>4.798707507082153</v>
+        <v>4.7990322009908</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -8585,16 +8585,16 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.221292492917847</v>
+        <v>-0.2209677990092</v>
       </c>
       <c r="N91" t="n">
-        <v>0.221292492917847</v>
+        <v>0.2209677990092</v>
       </c>
       <c r="O91" t="n">
         <v>-0.8600000000000003</v>
       </c>
       <c r="P91" t="n">
-        <v>0.004114730878186812</v>
+        <v>0.004111818825194291</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -9764,10 +9764,10 @@
         <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8909348441926346</v>
+        <v>0.8910120311394196</v>
       </c>
       <c r="H108" t="n">
-        <v>12.38269121813031</v>
+        <v>12.38285562632696</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -9786,16 +9786,16 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>5.312691218130312</v>
+        <v>5.312855626326965</v>
       </c>
       <c r="N108" t="n">
-        <v>5.312691218130312</v>
+        <v>5.312855626326965</v>
       </c>
       <c r="O108" t="n">
         <v>-0.1250000000000009</v>
       </c>
       <c r="P108" t="n">
-        <v>4.413111680639073</v>
+        <v>4.413276088835726</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -9835,10 +9835,10 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>0.886685552407932</v>
+        <v>0.8867657466383581</v>
       </c>
       <c r="H109" t="n">
-        <v>12.33504249291785</v>
+        <v>12.33692144373673</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -9857,16 +9857,16 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>5.465042492917846</v>
+        <v>5.466921443736729</v>
       </c>
       <c r="N109" t="n">
-        <v>5.465042492917846</v>
+        <v>5.466921443736729</v>
       </c>
       <c r="O109" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.04764872521246488</v>
+        <v>-0.0459341825902353</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -9906,10 +9906,10 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8845609065155807</v>
+        <v>0.8846426043878273</v>
       </c>
       <c r="H110" t="n">
-        <v>12.28984419263456</v>
+        <v>12.29036624203822</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -9928,16 +9928,16 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>5.549844192634561</v>
+        <v>5.550366242038216</v>
       </c>
       <c r="N110" t="n">
-        <v>5.549844192634561</v>
+        <v>5.550366242038216</v>
       </c>
       <c r="O110" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.04519830028328542</v>
+        <v>-0.04655520169851357</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -9977,10 +9977,10 @@
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>0.8824362606232294</v>
+        <v>0.8825194621372965</v>
       </c>
       <c r="H111" t="n">
-        <v>12.27441926345609</v>
+        <v>12.27574840764331</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -9999,16 +9999,16 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>5.674419263456091</v>
+        <v>5.675748407643312</v>
       </c>
       <c r="N111" t="n">
-        <v>5.674419263456091</v>
+        <v>5.675748407643312</v>
       </c>
       <c r="O111" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P111" t="n">
-        <v>-0.01542492917847049</v>
+        <v>-0.01461783439490461</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -10048,10 +10048,10 @@
         <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8760623229461756</v>
+        <v>0.8761500353857041</v>
       </c>
       <c r="H112" t="n">
-        <v>12.22202549575071</v>
+        <v>12.2223991507431</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10070,16 +10070,16 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>5.362025495750708</v>
+        <v>5.362399150743101</v>
       </c>
       <c r="N112" t="n">
-        <v>5.362025495750708</v>
+        <v>5.362399150743101</v>
       </c>
       <c r="O112" t="n">
         <v>0.2600000000000007</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.05239376770538229</v>
+        <v>-0.05334925690021031</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>0.8675637393767706</v>
+        <v>0.867657466383581</v>
       </c>
       <c r="H113" t="n">
-        <v>12.19041076487252</v>
+        <v>12.19061040339703</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -10141,16 +10141,16 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>5.21041076487252</v>
+        <v>5.210610403397027</v>
       </c>
       <c r="N113" t="n">
-        <v>5.21041076487252</v>
+        <v>5.210610403397027</v>
       </c>
       <c r="O113" t="n">
         <v>0.1200000000000001</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.03161473087818756</v>
+        <v>-0.03178874734607362</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -10190,10 +10190,10 @@
         <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8569405099150141</v>
+        <v>0.8570417551309271</v>
       </c>
       <c r="H114" t="n">
-        <v>12.11669971671388</v>
+        <v>12.11799363057325</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -10212,16 +10212,16 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>5.26669971671388</v>
+        <v>5.267993630573248</v>
       </c>
       <c r="N114" t="n">
-        <v>5.26669971671388</v>
+        <v>5.267993630573248</v>
       </c>
       <c r="O114" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P114" t="n">
-        <v>-0.07371104815864093</v>
+        <v>-0.0726167728237801</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
         <v>8</v>
       </c>
       <c r="G115" t="n">
-        <v>0.8463172804532578</v>
+        <v>0.8464260438782731</v>
       </c>
       <c r="H115" t="n">
-        <v>12.07531161473088</v>
+        <v>12.07577494692144</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -10283,16 +10283,16 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>5.335311614730879</v>
+        <v>5.335774946921443</v>
       </c>
       <c r="N115" t="n">
-        <v>5.335311614730879</v>
+        <v>5.335774946921443</v>
       </c>
       <c r="O115" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.04138810198300114</v>
+        <v>-0.0422186836518037</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -10332,10 +10332,10 @@
         <v>8</v>
       </c>
       <c r="G116" t="n">
-        <v>0.8243626062322946</v>
+        <v>0.8244869072894551</v>
       </c>
       <c r="H116" t="n">
-        <v>11.86178470254957</v>
+        <v>11.86231422505308</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -10354,16 +10354,16 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>5.256784702549574</v>
+        <v>5.257314225053078</v>
       </c>
       <c r="N116" t="n">
-        <v>5.256784702549574</v>
+        <v>5.257314225053078</v>
       </c>
       <c r="O116" t="n">
         <v>-0.1349999999999998</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.2135269121813046</v>
+        <v>-0.2134607218683655</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10403,10 +10403,10 @@
         <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>0.8094900849858357</v>
+        <v>0.8096249115357396</v>
       </c>
       <c r="H117" t="n">
-        <v>11.80764164305949</v>
+        <v>11.80850318471338</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -10425,16 +10425,16 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>5.42764164305949</v>
+        <v>5.428503184713377</v>
       </c>
       <c r="N117" t="n">
-        <v>5.42764164305949</v>
+        <v>5.428503184713377</v>
       </c>
       <c r="O117" t="n">
         <v>-0.2250000000000005</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.0541430594900838</v>
+        <v>-0.05381104033970097</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10474,10 +10474,10 @@
         <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7953257790368272</v>
+        <v>0.7954706298655343</v>
       </c>
       <c r="H118" t="n">
-        <v>11.72404390934844</v>
+        <v>11.72435244161359</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -10496,16 +10496,16 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>5.484043909348442</v>
+        <v>5.484352441613588</v>
       </c>
       <c r="N118" t="n">
-        <v>5.484043909348442</v>
+        <v>5.484352441613588</v>
       </c>
       <c r="O118" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.08359773371104851</v>
+        <v>-0.08415074309978898</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10545,10 +10545,10 @@
         <v>8</v>
       </c>
       <c r="G119" t="n">
-        <v>0.7818696883852692</v>
+        <v>0.7820240622788394</v>
       </c>
       <c r="H119" t="n">
-        <v>11.65864730878187</v>
+        <v>11.65963375796178</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -10567,16 +10567,16 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>5.538647308781871</v>
+        <v>5.539633757961783</v>
       </c>
       <c r="N119" t="n">
-        <v>5.538647308781871</v>
+        <v>5.539633757961783</v>
       </c>
       <c r="O119" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.06539660056657048</v>
+        <v>-0.06471868365180455</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -10616,10 +10616,10 @@
         <v>8</v>
       </c>
       <c r="G120" t="n">
-        <v>0.7677053824362606</v>
+        <v>0.7678697806086341</v>
       </c>
       <c r="H120" t="n">
-        <v>11.55521246458924</v>
+        <v>11.55556263269639</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10638,16 +10638,16 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>5.485212464589235</v>
+        <v>5.485562632696389</v>
       </c>
       <c r="N120" t="n">
-        <v>5.485212464589235</v>
+        <v>5.485562632696389</v>
       </c>
       <c r="O120" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.1034348441926358</v>
+        <v>-0.1040711252653939</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         <v>8</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7592067988668555</v>
+        <v>0.7593772116065109</v>
       </c>
       <c r="H121" t="n">
-        <v>11.48415722379603</v>
+        <v>11.48960191082802</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -10709,16 +10709,16 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.454157223796032</v>
+        <v>5.459601910828025</v>
       </c>
       <c r="N121" t="n">
-        <v>5.454157223796032</v>
+        <v>5.459601910828025</v>
       </c>
       <c r="O121" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.07105524079320347</v>
+        <v>-0.06596072186836466</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>8</v>
       </c>
       <c r="G122" t="n">
-        <v>0.9596317280453258</v>
+        <v>0.9596602972399151</v>
       </c>
       <c r="H122" t="n">
-        <v>112.8852620396601</v>
+        <v>112.8869639065817</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>105.8852620396601</v>
+        <v>105.8869639065817</v>
       </c>
       <c r="N122" t="n">
-        <v>105.8852620396601</v>
+        <v>105.8869639065817</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         <v>8</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9355524079320113</v>
+        <v>0.9355980184005662</v>
       </c>
       <c r="H123" t="n">
-        <v>112.4615509915014</v>
+        <v>112.4619391365888</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -10845,16 +10845,16 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>105.6515509915014</v>
+        <v>105.6519391365888</v>
       </c>
       <c r="N123" t="n">
-        <v>105.6515509915014</v>
+        <v>105.6519391365888</v>
       </c>
       <c r="O123" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.4237110481586512</v>
+        <v>-0.4250247699929304</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -10894,10 +10894,10 @@
         <v>8</v>
       </c>
       <c r="G124" t="n">
-        <v>0.9178470254957507</v>
+        <v>0.9179051663128096</v>
       </c>
       <c r="H124" t="n">
-        <v>112.1408781869688</v>
+        <v>112.141372965322</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -10916,16 +10916,16 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>105.5308781869688</v>
+        <v>105.531372965322</v>
       </c>
       <c r="N124" t="n">
-        <v>105.5308781869688</v>
+        <v>105.531372965322</v>
       </c>
       <c r="O124" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P124" t="n">
-        <v>-0.3206728045325633</v>
+        <v>-0.3205661712667904</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -10965,10 +10965,10 @@
         <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>0.9008498583569405</v>
+        <v>0.9009200283085633</v>
       </c>
       <c r="H125" t="n">
-        <v>111.9981161473088</v>
+        <v>111.9984147204529</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -10987,16 +10987,16 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>105.5781161473088</v>
+        <v>105.5784147204529</v>
       </c>
       <c r="N125" t="n">
-        <v>105.5781161473088</v>
+        <v>105.5784147204529</v>
       </c>
       <c r="O125" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P125" t="n">
-        <v>-0.1427620396600702</v>
+        <v>-0.142958244869078</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -11036,10 +11036,10 @@
         <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>0.8576487252124646</v>
+        <v>0.8577494692144374</v>
       </c>
       <c r="H126" t="n">
-        <v>111.6728859773371</v>
+        <v>111.6741719745223</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -11058,16 +11058,16 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>105.4428859773371</v>
+        <v>105.4441719745223</v>
       </c>
       <c r="N126" t="n">
-        <v>105.4428859773371</v>
+        <v>105.4441719745223</v>
       </c>
       <c r="O126" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.3252301699716753</v>
+        <v>-0.3242427459306469</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -11107,10 +11107,10 @@
         <v>8</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8116147308781869</v>
+        <v>0.8117480537862704</v>
       </c>
       <c r="H127" t="n">
-        <v>111.4322804532578</v>
+        <v>111.4326586459071</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -11129,16 +11129,16 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>105.3722804532578</v>
+        <v>105.3726586459071</v>
       </c>
       <c r="N127" t="n">
-        <v>105.3722804532578</v>
+        <v>105.3726586459071</v>
       </c>
       <c r="O127" t="n">
         <v>-0.1700000000000008</v>
       </c>
       <c r="P127" t="n">
-        <v>-0.2406055240793137</v>
+        <v>-0.2415133286152411</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -11178,10 +11178,10 @@
         <v>8</v>
       </c>
       <c r="G128" t="n">
-        <v>0.7528328611898017</v>
+        <v>0.7530077848549186</v>
       </c>
       <c r="H128" t="n">
-        <v>111.1632152974504</v>
+        <v>111.1661924982307</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -11200,16 +11200,16 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>105.2332152974504</v>
+        <v>105.2361924982307</v>
       </c>
       <c r="N128" t="n">
-        <v>105.2332152974504</v>
+        <v>105.2361924982307</v>
       </c>
       <c r="O128" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.269065155807354</v>
+        <v>-0.2664661476763399</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -11249,10 +11249,10 @@
         <v>8</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6749291784702549</v>
+        <v>0.6751592356687898</v>
       </c>
       <c r="H129" t="n">
-        <v>110.7554709631728</v>
+        <v>110.7584076433121</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -11271,16 +11271,16 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>52.3904709631728</v>
+        <v>52.39340764331209</v>
       </c>
       <c r="N129" t="n">
-        <v>52.3904709631728</v>
+        <v>52.39340764331209</v>
       </c>
       <c r="O129" t="n">
         <v>52.435</v>
       </c>
       <c r="P129" t="n">
-        <v>-0.4077443342776377</v>
+        <v>-0.4077848549186172</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -11320,10 +11320,10 @@
         <v>8</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5970254957507082</v>
+        <v>0.5973106864826611</v>
       </c>
       <c r="H130" t="n">
-        <v>110.3703434844193</v>
+        <v>110.3715569709837</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -11342,16 +11342,16 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>52.07534348441926</v>
+        <v>52.07655697098373</v>
       </c>
       <c r="N130" t="n">
-        <v>52.07534348441926</v>
+        <v>52.07655697098373</v>
       </c>
       <c r="O130" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.3851274787535317</v>
+        <v>-0.3868506723283645</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         <v>8</v>
       </c>
       <c r="G131" t="n">
-        <v>0.5162889518413598</v>
+        <v>0.5166312809624911</v>
       </c>
       <c r="H131" t="n">
-        <v>109.96787299339</v>
+        <v>109.9688440669969</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -11413,16 +11413,16 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>51.78287299338999</v>
+        <v>51.78384406699693</v>
       </c>
       <c r="N131" t="n">
-        <v>51.78287299338999</v>
+        <v>51.78384406699693</v>
       </c>
       <c r="O131" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.4024704910292769</v>
+        <v>-0.4027129039867958</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -11462,10 +11462,10 @@
         <v>8</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4313031161473088</v>
+        <v>0.4317055909412597</v>
       </c>
       <c r="H132" t="n">
-        <v>109.4469263456091</v>
+        <v>109.4492097192734</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -11484,16 +11484,16 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>51.40192634560906</v>
+        <v>51.40420971927341</v>
       </c>
       <c r="N132" t="n">
-        <v>51.40192634560906</v>
+        <v>51.40420971927341</v>
       </c>
       <c r="O132" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.5209466477809315</v>
+        <v>-0.5196343477235246</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -11533,10 +11533,10 @@
         <v>8</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3505665722379603</v>
+        <v>0.3510261854210899</v>
       </c>
       <c r="H133" t="n">
-        <v>108.9066607648725</v>
+        <v>108.9086164189667</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -11555,16 +11555,16 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>103.4666607648725</v>
+        <v>103.4686164189667</v>
       </c>
       <c r="N133" t="n">
-        <v>103.4666607648725</v>
+        <v>103.4686164189667</v>
       </c>
       <c r="O133" t="n">
         <v>-52.605</v>
       </c>
       <c r="P133" t="n">
-        <v>-0.5402655807365306</v>
+        <v>-0.5405933003066679</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -11604,10 +11604,10 @@
         <v>8</v>
       </c>
       <c r="G134" t="n">
-        <v>0.2669971671388102</v>
+        <v>0.267515923566879</v>
       </c>
       <c r="H134" t="n">
-        <v>108.3960729461756</v>
+        <v>108.3982802547771</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -11626,16 +11626,16 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>103.0760729461756</v>
+        <v>103.0782802547771</v>
       </c>
       <c r="N134" t="n">
-        <v>103.0760729461756</v>
+        <v>103.0782802547771</v>
       </c>
       <c r="O134" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P134" t="n">
-        <v>-0.5105878186968908</v>
+        <v>-0.5103361641896669</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
         <v>8</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9313031161473088</v>
+        <v>0.9313517338995047</v>
       </c>
       <c r="H154" t="n">
-        <v>9.031763456090651</v>
+        <v>9.031832979476292</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -13034,16 +13034,16 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>0.5717634560906504</v>
+        <v>0.5718329794762909</v>
       </c>
       <c r="N154" t="n">
-        <v>0.5717634560906504</v>
+        <v>0.5718329794762909</v>
       </c>
       <c r="O154" t="n">
         <v>0.005000000000000782</v>
       </c>
       <c r="P154" t="n">
-        <v>0.5827541708769175</v>
+        <v>0.582823694262558</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>8</v>
       </c>
       <c r="G155" t="n">
-        <v>0.9213881019830028</v>
+        <v>0.921443736730361</v>
       </c>
       <c r="H155" t="n">
         <v>9.009999999999998</v>
@@ -13114,7 +13114,7 @@
         <v>-0.03000000000000114</v>
       </c>
       <c r="P155" t="n">
-        <v>-0.02176345609065322</v>
+        <v>-0.0218329794762937</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -13154,10 +13154,10 @@
         <v>8</v>
       </c>
       <c r="G156" t="n">
-        <v>0.9143059490084986</v>
+        <v>0.9143665958952583</v>
       </c>
       <c r="H156" t="n">
-        <v>8.967202549575072</v>
+        <v>8.967544232130221</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -13176,16 +13176,16 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0.5572025495750719</v>
+        <v>0.5575442321302209</v>
       </c>
       <c r="N156" t="n">
-        <v>0.5572025495750719</v>
+        <v>0.5575442321302209</v>
       </c>
       <c r="O156" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P156" t="n">
-        <v>-0.042797450424926</v>
+        <v>-0.04245576786977701</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -13225,10 +13225,10 @@
         <v>8</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9050991501416431</v>
+        <v>0.9051663128096249</v>
       </c>
       <c r="H157" t="n">
-        <v>8.9210835694051</v>
+        <v>8.921275654635528</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -13247,16 +13247,16 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>0.6210835694050996</v>
+        <v>0.6212756546355269</v>
       </c>
       <c r="N157" t="n">
-        <v>0.6210835694050996</v>
+        <v>0.6212756546355269</v>
       </c>
       <c r="O157" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P157" t="n">
-        <v>-0.04611898016997173</v>
+        <v>-0.04626857749469337</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>8</v>
       </c>
       <c r="G158" t="n">
-        <v>0.8951841359773371</v>
+        <v>0.8952583156404812</v>
       </c>
       <c r="H158" t="n">
-        <v>8.857613314447594</v>
+        <v>8.85771939136589</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -13318,16 +13318,16 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>0.687613314447594</v>
+        <v>0.6877193913658903</v>
       </c>
       <c r="N158" t="n">
-        <v>0.687613314447594</v>
+        <v>0.6877193913658903</v>
       </c>
       <c r="O158" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P158" t="n">
-        <v>-0.06347025495750636</v>
+        <v>-0.06355626326963737</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -13367,10 +13367,10 @@
         <v>8</v>
       </c>
       <c r="G159" t="n">
-        <v>0.8888101983002833</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="H159" t="n">
-        <v>8.789490084985836</v>
+        <v>8.790277777777776</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -13389,16 +13389,16 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>0.8394900849858358</v>
+        <v>0.8402777777777759</v>
       </c>
       <c r="N159" t="n">
-        <v>0.8394900849858358</v>
+        <v>0.8402777777777759</v>
       </c>
       <c r="O159" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P159" t="n">
-        <v>-0.06812322946175797</v>
+        <v>-0.06744161358811418</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -13438,10 +13438,10 @@
         <v>8</v>
       </c>
       <c r="G160" t="n">
-        <v>0.8654390934844193</v>
+        <v>0.8655343241330502</v>
       </c>
       <c r="H160" t="n">
-        <v>8.430545325779036</v>
+        <v>8.431498584571832</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -13460,16 +13460,16 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>0.6605453257790366</v>
+        <v>0.6614985845718326</v>
       </c>
       <c r="N160" t="n">
-        <v>0.6605453257790366</v>
+        <v>0.6614985845718326</v>
       </c>
       <c r="O160" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P160" t="n">
-        <v>-0.3589447592067998</v>
+        <v>-0.3587791932059439</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -13509,10 +13509,10 @@
         <v>8</v>
       </c>
       <c r="G161" t="n">
-        <v>0.8583569405099151</v>
+        <v>0.8584571832979476</v>
       </c>
       <c r="H161" t="n">
-        <v>8.226359773371106</v>
+        <v>8.230219391365887</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -13531,16 +13531,16 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>0.4963597733711058</v>
+        <v>0.5002193913658868</v>
       </c>
       <c r="N161" t="n">
-        <v>0.4963597733711058</v>
+        <v>0.5002193913658868</v>
       </c>
       <c r="O161" t="n">
         <v>-0.03999999999999915</v>
       </c>
       <c r="P161" t="n">
-        <v>-0.2041855524079299</v>
+        <v>-0.201279193205945</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -13580,10 +13580,10 @@
         <v>8</v>
       </c>
       <c r="G162" t="n">
-        <v>0.8491501416430595</v>
+        <v>0.8492569002123143</v>
       </c>
       <c r="H162" t="n">
-        <v>8.006416430594898</v>
+        <v>8.008248407643311</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -13602,16 +13602,16 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>0.306416430594898</v>
+        <v>0.308248407643311</v>
       </c>
       <c r="N162" t="n">
-        <v>0.306416430594898</v>
+        <v>0.308248407643311</v>
       </c>
       <c r="O162" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P162" t="n">
-        <v>-0.2199433427762081</v>
+        <v>-0.2219709837225761</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -13651,10 +13651,10 @@
         <v>8</v>
       </c>
       <c r="G163" t="n">
-        <v>0.8441926345609065</v>
+        <v>0.8443029016277424</v>
       </c>
       <c r="H163" t="n">
-        <v>7.945432011331446</v>
+        <v>7.947797239915074</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -13673,16 +13673,16 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>0.3054320113314466</v>
+        <v>0.3077972399150743</v>
       </c>
       <c r="N163" t="n">
-        <v>0.3054320113314466</v>
+        <v>0.3077972399150743</v>
       </c>
       <c r="O163" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P163" t="n">
-        <v>-0.06098441926345188</v>
+        <v>-0.06045116772823711</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -13722,10 +13722,10 @@
         <v>8</v>
       </c>
       <c r="G164" t="n">
-        <v>0.8378186968838527</v>
+        <v>0.83793347487615</v>
       </c>
       <c r="H164" t="n">
-        <v>7.838307365439094</v>
+        <v>7.839948690728945</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -13744,16 +13744,16 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>0.278307365439094</v>
+        <v>0.2799486907289452</v>
       </c>
       <c r="N164" t="n">
-        <v>0.278307365439094</v>
+        <v>0.2799486907289452</v>
       </c>
       <c r="O164" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P164" t="n">
-        <v>-0.1071246458923527</v>
+        <v>-0.1078485491861292</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -13793,10 +13793,10 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>0.8349858356940509</v>
+        <v>0.835102618542109</v>
       </c>
       <c r="H165" t="n">
-        <v>7.829029745042493</v>
+        <v>7.829196744515216</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -13815,16 +13815,16 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>0.3490297450424924</v>
+        <v>0.3491967445152158</v>
       </c>
       <c r="N165" t="n">
-        <v>0.3490297450424924</v>
+        <v>0.3491967445152158</v>
       </c>
       <c r="O165" t="n">
         <v>-0.07999999999999918</v>
       </c>
       <c r="P165" t="n">
-        <v>-0.009277620396600739</v>
+        <v>-0.01075194621372866</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -13864,10 +13864,10 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>0.8264872521246459</v>
+        <v>0.8266100495399858</v>
       </c>
       <c r="H166" t="n">
-        <v>7.752514164305949</v>
+        <v>7.753918966737438</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -13886,16 +13886,16 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>0.3825141643059489</v>
+        <v>0.3839189667374381</v>
       </c>
       <c r="N166" t="n">
-        <v>0.3825141643059489</v>
+        <v>0.3839189667374381</v>
       </c>
       <c r="O166" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P166" t="n">
-        <v>-0.07651558073654385</v>
+        <v>-0.075277777777778</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -15065,10 +15065,10 @@
         <v>8</v>
       </c>
       <c r="G183" t="n">
-        <v>0.8002832861189801</v>
+        <v>0.8004246284501062</v>
       </c>
       <c r="H183" t="n">
-        <v>5.551365084985836</v>
+        <v>5.551422505307856</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -15087,16 +15087,16 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>0.3363650849858359</v>
+        <v>0.3364225053078558</v>
       </c>
       <c r="N183" t="n">
-        <v>0.3363650849858359</v>
+        <v>0.3364225053078558</v>
       </c>
       <c r="O183" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P183" t="n">
-        <v>-0.09271515327625313</v>
+        <v>-0.0926577329542333</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -15136,10 +15136,10 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>0.853399433427762</v>
+        <v>0.8535031847133758</v>
       </c>
       <c r="H184" t="n">
-        <v>5.758548158640227</v>
+        <v>5.758885350318471</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -15158,16 +15158,16 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>0.5935481586402265</v>
+        <v>0.5938853503184713</v>
       </c>
       <c r="N184" t="n">
-        <v>0.5935481586402265</v>
+        <v>0.5938853503184713</v>
       </c>
       <c r="O184" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P184" t="n">
-        <v>0.2071830736543907</v>
+        <v>0.2074628450106157</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -15207,10 +15207,10 @@
         <v>8</v>
       </c>
       <c r="G185" t="n">
-        <v>0.8675637393767706</v>
+        <v>0.867657466383581</v>
       </c>
       <c r="H185" t="n">
-        <v>5.799373229461756</v>
+        <v>5.799830148619957</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -15229,16 +15229,16 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>0.6793732294617563</v>
+        <v>0.6798301486199572</v>
       </c>
       <c r="N185" t="n">
-        <v>0.6793732294617563</v>
+        <v>0.6798301486199572</v>
       </c>
       <c r="O185" t="n">
         <v>-0.04499999999999993</v>
       </c>
       <c r="P185" t="n">
-        <v>0.04082507082152986</v>
+        <v>0.0409447983014859</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -15278,10 +15278,10 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>0.8647308781869688</v>
+        <v>0.86482661004954</v>
       </c>
       <c r="H186" t="n">
-        <v>5.785563031161472</v>
+        <v>5.786029723991507</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -15300,16 +15300,16 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>0.7055630311614722</v>
+        <v>0.7060297239915068</v>
       </c>
       <c r="N186" t="n">
-        <v>0.7055630311614722</v>
+        <v>0.7060297239915068</v>
       </c>
       <c r="O186" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P186" t="n">
-        <v>-0.01381019830028407</v>
+        <v>-0.01380042462845044</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -15349,10 +15349,10 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8434844192634561</v>
+        <v>0.8435951875442321</v>
       </c>
       <c r="H187" t="n">
-        <v>5.683162181303116</v>
+        <v>5.683342179759378</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -15371,16 +15371,16 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>0.2531621813031162</v>
+        <v>0.253342179759378</v>
       </c>
       <c r="N187" t="n">
-        <v>0.2531621813031162</v>
+        <v>0.253342179759378</v>
       </c>
       <c r="O187" t="n">
         <v>0.3499999999999996</v>
       </c>
       <c r="P187" t="n">
-        <v>-0.1024008498583564</v>
+        <v>-0.1026875442321291</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -15420,10 +15420,10 @@
         <v>8</v>
       </c>
       <c r="G188" t="n">
-        <v>0.7960339943342776</v>
+        <v>0.7961783439490446</v>
       </c>
       <c r="H188" t="n">
-        <v>5.542053824362605</v>
+        <v>5.543343949044586</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -15442,16 +15442,16 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.06044617563739507</v>
+        <v>-0.05915605095541387</v>
       </c>
       <c r="N188" t="n">
-        <v>0.06044617563739507</v>
+        <v>0.05915605095541387</v>
       </c>
       <c r="O188" t="n">
         <v>0.1725000000000003</v>
       </c>
       <c r="P188" t="n">
-        <v>-0.1411083569405109</v>
+        <v>-0.1399982307147916</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -15491,10 +15491,10 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>0.7492917847025495</v>
+        <v>0.7494692144373672</v>
       </c>
       <c r="H189" t="n">
-        <v>5.391795325779037</v>
+        <v>5.393381104033971</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -15513,16 +15513,16 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.1582046742209631</v>
+        <v>-0.1566188959660293</v>
       </c>
       <c r="N189" t="n">
-        <v>0.1582046742209631</v>
+        <v>0.1566188959660293</v>
       </c>
       <c r="O189" t="n">
         <v>-0.05250000000000021</v>
       </c>
       <c r="P189" t="n">
-        <v>-0.1502584985835682</v>
+        <v>-0.1499628450106156</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -15562,10 +15562,10 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>0.7216713881019831</v>
+        <v>0.721868365180467</v>
       </c>
       <c r="H190" t="n">
-        <v>5.281358002832861</v>
+        <v>5.281518046709129</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -15584,16 +15584,16 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>0.001358002832860805</v>
+        <v>0.001518046709128917</v>
       </c>
       <c r="N190" t="n">
-        <v>0.001358002832860805</v>
+        <v>0.001518046709128917</v>
       </c>
       <c r="O190" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P190" t="n">
-        <v>-0.1104373229461757</v>
+        <v>-0.1118630573248414</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -15633,10 +15633,10 @@
         <v>8</v>
       </c>
       <c r="G191" t="n">
-        <v>0.71671388101983</v>
+        <v>0.7169143665958952</v>
       </c>
       <c r="H191" t="n">
-        <v>5.278665014164306</v>
+        <v>5.278746461429582</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -15655,16 +15655,16 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>0.2536650141643078</v>
+        <v>0.2537464614295839</v>
       </c>
       <c r="N191" t="n">
-        <v>0.2536650141643078</v>
+        <v>0.2537464614295839</v>
       </c>
       <c r="O191" t="n">
         <v>-0.2550000000000017</v>
       </c>
       <c r="P191" t="n">
-        <v>-0.002692988668554719</v>
+        <v>-0.002771585279546684</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -15704,10 +15704,10 @@
         <v>8</v>
       </c>
       <c r="G192" t="n">
-        <v>0.7252124645892352</v>
+        <v>0.7254069355980184</v>
       </c>
       <c r="H192" t="n">
-        <v>5.292910764872522</v>
+        <v>5.29385881104034</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -15726,16 +15726,16 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>0.4429107648725221</v>
+        <v>0.4438588110403403</v>
       </c>
       <c r="N192" t="n">
-        <v>0.4429107648725221</v>
+        <v>0.4438588110403403</v>
       </c>
       <c r="O192" t="n">
         <v>-0.1749999999999989</v>
       </c>
       <c r="P192" t="n">
-        <v>0.01424575070821543</v>
+        <v>0.01511234961075747</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -15775,10 +15775,10 @@
         <v>8</v>
       </c>
       <c r="G193" t="n">
-        <v>0.7322946175637394</v>
+        <v>0.732484076433121</v>
       </c>
       <c r="H193" t="n">
-        <v>5.337340651558072</v>
+        <v>5.33764331210191</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -15797,16 +15797,16 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>0.7673406515580714</v>
+        <v>0.7676433121019093</v>
       </c>
       <c r="N193" t="n">
-        <v>0.7673406515580714</v>
+        <v>0.7676433121019093</v>
       </c>
       <c r="O193" t="n">
         <v>-0.2799999999999994</v>
       </c>
       <c r="P193" t="n">
-        <v>0.04442988668554992</v>
+        <v>0.04378450106156961</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -15846,10 +15846,10 @@
         <v>8</v>
       </c>
       <c r="G194" t="n">
-        <v>0.7230878186968839</v>
+        <v>0.7232837933474876</v>
       </c>
       <c r="H194" t="n">
-        <v>5.282553116147309</v>
+        <v>5.283508492569002</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15868,16 +15868,16 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>0.852553116147309</v>
+        <v>0.8535084925690022</v>
       </c>
       <c r="N194" t="n">
-        <v>0.852553116147309</v>
+        <v>0.8535084925690022</v>
       </c>
       <c r="O194" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P194" t="n">
-        <v>-0.05478753541076298</v>
+        <v>-0.05413481953290766</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>0.6954674220963173</v>
+        <v>0.6956829440905874</v>
       </c>
       <c r="H195" t="n">
         <v>5.215</v>
@@ -15948,7 +15948,7 @@
         <v>0.05000000000000071</v>
       </c>
       <c r="P195" t="n">
-        <v>-0.06755311614730886</v>
+        <v>-0.06850849256900204</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -15988,10 +15988,10 @@
         <v>8</v>
       </c>
       <c r="G196" t="n">
-        <v>0.6572237960339944</v>
+        <v>0.656758669497523</v>
       </c>
       <c r="H196" t="n">
-        <v>5.125977337110482</v>
+        <v>5.12446567586695</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -16010,16 +16010,16 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>0.3359773371104815</v>
+        <v>0.3344656758669498</v>
       </c>
       <c r="N196" t="n">
-        <v>0.3359773371104815</v>
+        <v>0.3344656758669498</v>
       </c>
       <c r="O196" t="n">
         <v>0.3099999999999996</v>
       </c>
       <c r="P196" t="n">
-        <v>-0.08902266288951832</v>
+        <v>-0.09053432413305007</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -17189,10 +17189,10 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>0.7556657223796034</v>
+        <v>0.7558386411889597</v>
       </c>
       <c r="H213" t="n">
-        <v>5.969959867799811</v>
+        <v>5.97</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -17211,16 +17211,16 @@
         <v>1</v>
       </c>
       <c r="M213" t="n">
-        <v>-2.76754013220019</v>
+        <v>-2.767500000000001</v>
       </c>
       <c r="N213" t="n">
-        <v>2.76754013220019</v>
+        <v>2.767500000000001</v>
       </c>
       <c r="O213" t="n">
         <v>-0.125</v>
       </c>
       <c r="P213" t="n">
-        <v>-1.394993706131514</v>
+        <v>-1.394953573931325</v>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
@@ -17260,10 +17260,10 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>0.7549575070821529</v>
+        <v>0.7551309271054494</v>
       </c>
       <c r="H214" t="n">
-        <v>5.969027384324835</v>
+        <v>5.969255720688841</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -17282,16 +17282,16 @@
         <v>1</v>
       </c>
       <c r="M214" t="n">
-        <v>-2.618472615675164</v>
+        <v>-2.618244279311157</v>
       </c>
       <c r="N214" t="n">
-        <v>2.618472615675164</v>
+        <v>2.618244279311157</v>
       </c>
       <c r="O214" t="n">
         <v>-0.1500000000000021</v>
       </c>
       <c r="P214" t="n">
-        <v>-0.000932483474976209</v>
+        <v>-0.0007442793111582802</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>0.7655807365439093</v>
+        <v>0.7657466383581033</v>
       </c>
       <c r="H215" t="n">
-        <v>6.008087818696884</v>
+        <v>6.009398443029016</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -17353,16 +17353,16 @@
         <v>1</v>
       </c>
       <c r="M215" t="n">
-        <v>-2.471912181303116</v>
+        <v>-2.470601556970984</v>
       </c>
       <c r="N215" t="n">
-        <v>2.471912181303116</v>
+        <v>2.470601556970984</v>
       </c>
       <c r="O215" t="n">
         <v>-0.1074999999999982</v>
       </c>
       <c r="P215" t="n">
-        <v>0.03906043437204954</v>
+        <v>0.04014272234017469</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -17402,10 +17402,10 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>0.7861189801699717</v>
+        <v>0.7862703467799009</v>
       </c>
       <c r="H216" t="n">
-        <v>6.100339943342776</v>
+        <v>6.101535739561218</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -17424,16 +17424,16 @@
         <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>-2.109660056657225</v>
+        <v>-2.108464260438783</v>
       </c>
       <c r="N216" t="n">
-        <v>2.109660056657225</v>
+        <v>2.108464260438783</v>
       </c>
       <c r="O216" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P216" t="n">
-        <v>0.09225212464589205</v>
+        <v>0.0921372965322016</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -17473,10 +17473,10 @@
         <v>8</v>
       </c>
       <c r="G217" t="n">
-        <v>0.8087818696883853</v>
+        <v>0.8089171974522293</v>
       </c>
       <c r="H217" t="n">
-        <v>6.199584513692162</v>
+        <v>6.200445859872612</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -17495,16 +17495,16 @@
         <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>-1.960415486307838</v>
+        <v>-1.959554140127388</v>
       </c>
       <c r="N217" t="n">
-        <v>1.960415486307838</v>
+        <v>1.959554140127388</v>
       </c>
       <c r="O217" t="n">
         <v>-0.05000000000000071</v>
       </c>
       <c r="P217" t="n">
-        <v>0.09924457034938605</v>
+        <v>0.09891012031139468</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -17544,10 +17544,10 @@
         <v>8</v>
       </c>
       <c r="G218" t="n">
-        <v>0.8271954674220963</v>
+        <v>0.8273177636234961</v>
       </c>
       <c r="H218" t="n">
-        <v>6.293229461756374</v>
+        <v>6.293873555083746</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -17566,16 +17566,16 @@
         <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>-1.636770538243626</v>
+        <v>-1.636126444916254</v>
       </c>
       <c r="N218" t="n">
-        <v>1.636770538243626</v>
+        <v>1.636126444916254</v>
       </c>
       <c r="O218" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P218" t="n">
-        <v>0.09364494806421142</v>
+        <v>0.09342769521113325</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -17615,10 +17615,10 @@
         <v>8</v>
       </c>
       <c r="G219" t="n">
-        <v>0.8441926345609065</v>
+        <v>0.8443029016277424</v>
       </c>
       <c r="H219" t="n">
-        <v>6.384780453257791</v>
+        <v>6.384998230714791</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -17637,16 +17637,16 @@
         <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>-1.60521954674221</v>
+        <v>-1.605001769285209</v>
       </c>
       <c r="N219" t="n">
-        <v>1.60521954674221</v>
+        <v>1.605001769285209</v>
       </c>
       <c r="O219" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P219" t="n">
-        <v>0.09155099150141677</v>
+        <v>0.09112467563104509</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -17686,10 +17686,10 @@
         <v>8</v>
       </c>
       <c r="G220" t="n">
-        <v>0.8512747875354107</v>
+        <v>0.851380042462845</v>
       </c>
       <c r="H220" t="n">
-        <v>6.445212464589235</v>
+        <v>6.447707006369428</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -17708,16 +17708,16 @@
         <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>-1.544787535410765</v>
+        <v>-1.542292993630572</v>
       </c>
       <c r="N220" t="n">
-        <v>1.544787535410765</v>
+        <v>1.542292993630572</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
       </c>
       <c r="P220" t="n">
-        <v>0.06043201133144471</v>
+        <v>0.06270877565463717</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -17757,10 +17757,10 @@
         <v>8</v>
       </c>
       <c r="G221" t="n">
-        <v>0.8420679886685553</v>
+        <v>0.8421797593772116</v>
       </c>
       <c r="H221" t="n">
-        <v>6.380584277620397</v>
+        <v>6.380805024769993</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -17779,16 +17779,16 @@
         <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>-1.476915722379603</v>
+        <v>-1.476694975230007</v>
       </c>
       <c r="N221" t="n">
-        <v>1.476915722379603</v>
+        <v>1.476694975230007</v>
       </c>
       <c r="O221" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P221" t="n">
-        <v>-0.06462818696883854</v>
+        <v>-0.06690198159943517</v>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
@@ -17828,10 +17828,10 @@
         <v>8</v>
       </c>
       <c r="G222" t="n">
-        <v>0.8222379603399433</v>
+        <v>0.8223637650389243</v>
       </c>
       <c r="H222" t="n">
-        <v>6.248559962228518</v>
+        <v>6.248891247935834</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -17850,16 +17850,16 @@
         <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>-1.491440037771483</v>
+        <v>-1.491108752064166</v>
       </c>
       <c r="N222" t="n">
-        <v>1.491440037771483</v>
+        <v>1.491108752064166</v>
       </c>
       <c r="O222" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.1320243153918792</v>
+        <v>-0.1319137768341587</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -17899,10 +17899,10 @@
         <v>8</v>
       </c>
       <c r="G223" t="n">
-        <v>0.8045325779036827</v>
+        <v>0.8046709129511678</v>
       </c>
       <c r="H223" t="n">
-        <v>6.178602455146364</v>
+        <v>6.178966737438075</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -17921,16 +17921,16 @@
         <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>-1.441397544853636</v>
+        <v>-1.441033262561925</v>
       </c>
       <c r="N223" t="n">
-        <v>1.441397544853636</v>
+        <v>1.441033262561925</v>
       </c>
       <c r="O223" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.06995750708215365</v>
+        <v>-0.06992451049775905</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -17970,10 +17970,10 @@
         <v>8</v>
       </c>
       <c r="G224" t="n">
-        <v>0.7797450424929179</v>
+        <v>0.7799009200283086</v>
       </c>
       <c r="H224" t="n">
-        <v>6.076248229461756</v>
+        <v>6.076402158527954</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -17992,16 +17992,16 @@
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>-1.323751770538244</v>
+        <v>-1.323597841472046</v>
       </c>
       <c r="N224" t="n">
-        <v>1.323751770538244</v>
+        <v>1.323597841472046</v>
       </c>
       <c r="O224" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.1023542256846079</v>
+        <v>-0.1025645789101208</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -18041,10 +18041,10 @@
         <v>8</v>
       </c>
       <c r="G225" t="n">
-        <v>0.7521246458923513</v>
+        <v>0.7523000707714084</v>
       </c>
       <c r="H225" t="n">
-        <v>5.965297450424929</v>
+        <v>5.965528426515688</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -18063,16 +18063,16 @@
         <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>-1.394702549575071</v>
+        <v>-1.394471573484313</v>
       </c>
       <c r="N225" t="n">
-        <v>1.394702549575071</v>
+        <v>1.394471573484313</v>
       </c>
       <c r="O225" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.1109507790368269</v>
+        <v>-0.1108737320122666</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>8</v>
       </c>
       <c r="G226" t="n">
-        <v>0.7273371104815864</v>
+        <v>0.7275300778485492</v>
       </c>
       <c r="H226" t="n">
-        <v>5.825963172804533</v>
+        <v>5.827487615003538</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -18134,16 +18134,16 @@
         <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>-1.554036827195467</v>
+        <v>-1.552512384996461</v>
       </c>
       <c r="N226" t="n">
-        <v>1.554036827195467</v>
+        <v>1.552512384996461</v>
       </c>
       <c r="O226" t="n">
         <v>0.01999999999999957</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.1393342776203959</v>
+        <v>-0.1380408115121492</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -19313,10 +19313,10 @@
         <v>8</v>
       </c>
       <c r="G243" t="n">
-        <v>0.8286118980169972</v>
+        <v>0.8287331917905166</v>
       </c>
       <c r="H243" t="n">
-        <v>5.563590651558073</v>
+        <v>5.566003184713375</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -19335,16 +19335,16 @@
         <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>1.573590651558073</v>
+        <v>1.576003184713374</v>
       </c>
       <c r="N243" t="n">
-        <v>1.573590651558073</v>
+        <v>1.576003184713374</v>
       </c>
       <c r="O243" t="n">
         <v>-0.1624999999999996</v>
       </c>
       <c r="P243" t="n">
-        <v>-1.597327358252719</v>
+        <v>-1.594914825097417</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -19384,10 +19384,10 @@
         <v>8</v>
       </c>
       <c r="G244" t="n">
-        <v>0.7046742209631728</v>
+        <v>0.7048832271762208</v>
       </c>
       <c r="H244" t="n">
-        <v>4.931303116147308</v>
+        <v>4.931942675159235</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -19406,16 +19406,16 @@
         <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>1.108803116147309</v>
+        <v>1.109442675159236</v>
       </c>
       <c r="N244" t="n">
-        <v>1.108803116147309</v>
+        <v>1.109442675159236</v>
       </c>
       <c r="O244" t="n">
         <v>-0.1675000000000004</v>
       </c>
       <c r="P244" t="n">
-        <v>-0.6322875354107644</v>
+        <v>-0.6340605095541392</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -19455,10 +19455,10 @@
         <v>8</v>
       </c>
       <c r="G245" t="n">
-        <v>0.6154390934844193</v>
+        <v>0.6157112526539278</v>
       </c>
       <c r="H245" t="n">
-        <v>4.630247875354108</v>
+        <v>4.630525477707007</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -19477,16 +19477,16 @@
         <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>0.8502478753541083</v>
+        <v>0.850525477707007</v>
       </c>
       <c r="N245" t="n">
-        <v>0.8502478753541083</v>
+        <v>0.850525477707007</v>
       </c>
       <c r="O245" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.3010552407932003</v>
+        <v>-0.3014171974522286</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -19526,10 +19526,10 @@
         <v>8</v>
       </c>
       <c r="G246" t="n">
-        <v>0.5934844192634561</v>
+        <v>0.5937721160651097</v>
       </c>
       <c r="H246" t="n">
-        <v>4.561041076487252</v>
+        <v>4.563975583864119</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -19548,16 +19548,16 @@
         <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>0.8810410764872523</v>
+        <v>0.8839755838641188</v>
       </c>
       <c r="N246" t="n">
-        <v>0.8810410764872523</v>
+        <v>0.8839755838641188</v>
       </c>
       <c r="O246" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.06920679886685566</v>
+        <v>-0.0665498938428879</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -19597,10 +19597,10 @@
         <v>8</v>
       </c>
       <c r="G247" t="n">
-        <v>0.6338526912181303</v>
+        <v>0.6341118188251946</v>
       </c>
       <c r="H247" t="n">
-        <v>4.722089235127479</v>
+        <v>4.722882165605096</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -19619,16 +19619,16 @@
         <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>1.142089235127479</v>
+        <v>1.142882165605096</v>
       </c>
       <c r="N247" t="n">
-        <v>1.142089235127479</v>
+        <v>1.142882165605096</v>
       </c>
       <c r="O247" t="n">
         <v>-0.1000000000000001</v>
       </c>
       <c r="P247" t="n">
-        <v>0.1610481586402264</v>
+        <v>0.1589065817409772</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -19668,10 +19668,10 @@
         <v>8</v>
       </c>
       <c r="G248" t="n">
-        <v>0.646600566572238</v>
+        <v>0.6468506723283793</v>
       </c>
       <c r="H248" t="n">
-        <v>4.759532577903682</v>
+        <v>4.759787685774946</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19690,16 +19690,16 @@
         <v>1</v>
       </c>
       <c r="M248" t="n">
-        <v>1.367032577903682</v>
+        <v>1.367287685774946</v>
       </c>
       <c r="N248" t="n">
-        <v>1.367032577903682</v>
+        <v>1.367287685774946</v>
       </c>
       <c r="O248" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P248" t="n">
-        <v>0.03744334277620354</v>
+        <v>0.03690552016985027</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -19739,10 +19739,10 @@
         <v>8</v>
       </c>
       <c r="G249" t="n">
-        <v>0.5963172804532578</v>
+        <v>0.5966029723991507</v>
       </c>
       <c r="H249" t="n">
-        <v>4.589936260623229</v>
+        <v>4.592850318471338</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19761,16 +19761,16 @@
         <v>1</v>
       </c>
       <c r="M249" t="n">
-        <v>1.30993626062323</v>
+        <v>1.312850318471338</v>
       </c>
       <c r="N249" t="n">
-        <v>1.30993626062323</v>
+        <v>1.312850318471338</v>
       </c>
       <c r="O249" t="n">
         <v>-0.1125000000000003</v>
       </c>
       <c r="P249" t="n">
-        <v>-0.1695963172804529</v>
+        <v>-0.1669373673036088</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -19810,10 +19810,10 @@
         <v>8</v>
       </c>
       <c r="G250" t="n">
-        <v>0.4907932011331445</v>
+        <v>0.4904458598726115</v>
       </c>
       <c r="H250" t="n">
-        <v>4.151154390934845</v>
+        <v>4.149028662420382</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19832,16 +19832,16 @@
         <v>1</v>
       </c>
       <c r="M250" t="n">
-        <v>1.001154390934845</v>
+        <v>0.9990286624203821</v>
       </c>
       <c r="N250" t="n">
-        <v>1.001154390934845</v>
+        <v>0.9990286624203821</v>
       </c>
       <c r="O250" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P250" t="n">
-        <v>-0.438781869688385</v>
+        <v>-0.4438216560509556</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -19881,10 +19881,10 @@
         <v>8</v>
       </c>
       <c r="G251" t="n">
-        <v>0.391643059490085</v>
+        <v>0.3913658881811748</v>
       </c>
       <c r="H251" t="n">
-        <v>3.80592776203966</v>
+        <v>3.805079617834395</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19903,16 +19903,16 @@
         <v>1</v>
       </c>
       <c r="M251" t="n">
-        <v>0.8609277620396605</v>
+        <v>0.860079617834395</v>
       </c>
       <c r="N251" t="n">
-        <v>0.8609277620396605</v>
+        <v>0.860079617834395</v>
       </c>
       <c r="O251" t="n">
         <v>-0.2050000000000001</v>
       </c>
       <c r="P251" t="n">
-        <v>-0.3452266288951842</v>
+        <v>-0.3439490445859872</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         <v>8</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3371104815864023</v>
+        <v>0.3368719037508847</v>
       </c>
       <c r="H252" t="n">
-        <v>3.642842304060435</v>
+        <v>3.642031139419675</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19974,16 +19974,16 @@
         <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>0.8028423040604347</v>
+        <v>0.8020311394196749</v>
       </c>
       <c r="N252" t="n">
-        <v>0.8028423040604347</v>
+        <v>0.8020311394196749</v>
       </c>
       <c r="O252" t="n">
         <v>-0.105</v>
       </c>
       <c r="P252" t="n">
-        <v>-0.1630854579792258</v>
+        <v>-0.1630484784147201</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -20023,10 +20023,10 @@
         <v>8</v>
       </c>
       <c r="G253" t="n">
-        <v>0.3477337110481586</v>
+        <v>0.3474876150035386</v>
       </c>
       <c r="H253" t="n">
-        <v>3.678961284230406</v>
+        <v>3.678124557678698</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -20045,16 +20045,16 @@
         <v>1</v>
       </c>
       <c r="M253" t="n">
-        <v>0.9089612842304065</v>
+        <v>0.9081245576786983</v>
       </c>
       <c r="N253" t="n">
-        <v>0.9089612842304065</v>
+        <v>0.9081245576786983</v>
       </c>
       <c r="O253" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P253" t="n">
-        <v>0.03611898016997195</v>
+        <v>0.03609341825902357</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -20094,10 +20094,10 @@
         <v>8</v>
       </c>
       <c r="G254" t="n">
-        <v>0.495042492917847</v>
+        <v>0.494692144373673</v>
       </c>
       <c r="H254" t="n">
-        <v>4.177160056657224</v>
+        <v>4.175015923566879</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -20116,16 +20116,16 @@
         <v>1</v>
       </c>
       <c r="M254" t="n">
-        <v>1.357160056657224</v>
+        <v>1.355015923566879</v>
       </c>
       <c r="N254" t="n">
-        <v>1.357160056657224</v>
+        <v>1.355015923566879</v>
       </c>
       <c r="O254" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P254" t="n">
-        <v>0.4981987724268171</v>
+        <v>0.4968913658881808</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -20165,10 +20165,10 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>0.6961756373937678</v>
+        <v>0.6963906581740976</v>
       </c>
       <c r="H255" t="n">
-        <v>4.905297450424929</v>
+        <v>4.905955414012739</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -20187,16 +20187,16 @@
         <v>1</v>
       </c>
       <c r="M255" t="n">
-        <v>2.155297450424929</v>
+        <v>2.155955414012739</v>
       </c>
       <c r="N255" t="n">
-        <v>2.155297450424929</v>
+        <v>2.155955414012739</v>
       </c>
       <c r="O255" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P255" t="n">
-        <v>0.7281373937677058</v>
+        <v>0.7309394904458602</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
@@ -20236,10 +20236,10 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>0.7882436260623229</v>
+        <v>0.7883934890304317</v>
       </c>
       <c r="H256" t="n">
-        <v>5.203080736543908</v>
+        <v>5.204532908704882</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -20258,16 +20258,16 @@
         <v>1</v>
       </c>
       <c r="M256" t="n">
-        <v>2.453080736543908</v>
+        <v>2.454532908704882</v>
       </c>
       <c r="N256" t="n">
-        <v>2.453080736543908</v>
+        <v>2.454532908704882</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
       </c>
       <c r="P256" t="n">
-        <v>0.2977832861189782</v>
+        <v>0.2985774946921431</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -21437,10 +21437,10 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>0.9426345609065155</v>
+        <v>0.9426751592356688</v>
       </c>
       <c r="H273" t="n">
-        <v>6.913055949008498</v>
+        <v>6.91328025477707</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -21459,16 +21459,16 @@
         <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>-0.8519440509915013</v>
+        <v>-0.8517197452229297</v>
       </c>
       <c r="N273" t="n">
-        <v>0.8519440509915013</v>
+        <v>0.8517197452229297</v>
       </c>
       <c r="O273" t="n">
         <v>0.0550000000000006</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.9778784121220783</v>
+        <v>-0.9776541063535067</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -21508,10 +21508,10 @@
         <v>8</v>
       </c>
       <c r="G274" t="n">
-        <v>0.9390934844192634</v>
+        <v>0.9391365888181175</v>
       </c>
       <c r="H274" t="n">
-        <v>6.84849150141643</v>
+        <v>6.848729653220099</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -21530,16 +21530,16 @@
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>-0.93150849858357</v>
+        <v>-0.9312703467799013</v>
       </c>
       <c r="N274" t="n">
-        <v>0.93150849858357</v>
+        <v>0.9312703467799013</v>
       </c>
       <c r="O274" t="n">
         <v>0.01500000000000057</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.06456444759206814</v>
+        <v>-0.06455060155697101</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -21579,10 +21579,10 @@
         <v>8</v>
       </c>
       <c r="G275" t="n">
-        <v>0.9355524079320113</v>
+        <v>0.9355980184005662</v>
       </c>
       <c r="H275" t="n">
-        <v>6.829463526912181</v>
+        <v>6.829589525831564</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -21601,16 +21601,16 @@
         <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>-0.9405364730878185</v>
+        <v>-0.9404104741684352</v>
       </c>
       <c r="N275" t="n">
-        <v>0.9405364730878185</v>
+        <v>0.9404104741684352</v>
       </c>
       <c r="O275" t="n">
         <v>-0.01000000000000068</v>
       </c>
       <c r="P275" t="n">
-        <v>-0.0190279745042492</v>
+        <v>-0.01914012738853454</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -21650,10 +21650,10 @@
         <v>8</v>
       </c>
       <c r="G276" t="n">
-        <v>0.9320113314447592</v>
+        <v>0.9320594479830149</v>
       </c>
       <c r="H276" t="n">
-        <v>6.81872521246459</v>
+        <v>6.819256900212315</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -21672,16 +21672,16 @@
         <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>-0.8812747875354106</v>
+        <v>-0.8807430997876855</v>
       </c>
       <c r="N276" t="n">
-        <v>0.8812747875354106</v>
+        <v>0.8807430997876855</v>
       </c>
       <c r="O276" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P276" t="n">
-        <v>-0.01073831444759143</v>
+        <v>-0.01033262561924975</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -21721,10 +21721,10 @@
         <v>8</v>
       </c>
       <c r="G277" t="n">
-        <v>0.9284702549575071</v>
+        <v>0.9285208775654635</v>
       </c>
       <c r="H277" t="n">
-        <v>6.779596317280453</v>
+        <v>6.780077848549186</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -21743,16 +21743,16 @@
         <v>1</v>
       </c>
       <c r="M277" t="n">
-        <v>-0.8104036827195467</v>
+        <v>-0.8099221514508139</v>
       </c>
       <c r="N277" t="n">
-        <v>0.8104036827195467</v>
+        <v>0.8099221514508139</v>
       </c>
       <c r="O277" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P277" t="n">
-        <v>-0.03912889518413643</v>
+        <v>-0.03917905166312874</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -21792,10 +21792,10 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>0.9249291784702549</v>
+        <v>0.9249823071479123</v>
       </c>
       <c r="H278" t="n">
-        <v>6.750233711048158</v>
+        <v>6.750527246992215</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -21814,16 +21814,16 @@
         <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>-0.6997662889518423</v>
+        <v>-0.6994727530077851</v>
       </c>
       <c r="N278" t="n">
-        <v>0.6997662889518423</v>
+        <v>0.6994727530077851</v>
       </c>
       <c r="O278" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P278" t="n">
-        <v>-0.02936260623229536</v>
+        <v>-0.02955060155697087</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -21863,10 +21863,10 @@
         <v>8</v>
       </c>
       <c r="G279" t="n">
-        <v>0.9213881019830028</v>
+        <v>0.921443736730361</v>
       </c>
       <c r="H279" t="n">
-        <v>6.713779508970727</v>
+        <v>6.713984430290163</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -21885,16 +21885,16 @@
         <v>1</v>
       </c>
       <c r="M279" t="n">
-        <v>-0.6562204910292735</v>
+        <v>-0.6560155697098375</v>
       </c>
       <c r="N279" t="n">
-        <v>0.6562204910292735</v>
+        <v>0.6560155697098375</v>
       </c>
       <c r="O279" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P279" t="n">
-        <v>-0.03645420207743122</v>
+        <v>-0.03654281670205251</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -21934,10 +21934,10 @@
         <v>8</v>
       </c>
       <c r="G280" t="n">
-        <v>0.9178470254957507</v>
+        <v>0.9179051663128096</v>
       </c>
       <c r="H280" t="n">
-        <v>6.674419263456092</v>
+        <v>6.675704175513093</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -21956,16 +21956,16 @@
         <v>1</v>
       </c>
       <c r="M280" t="n">
-        <v>-0.5955807365439076</v>
+        <v>-0.5942958244869061</v>
       </c>
       <c r="N280" t="n">
-        <v>0.5955807365439076</v>
+        <v>0.5942958244869061</v>
       </c>
       <c r="O280" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P280" t="n">
-        <v>-0.03936024551463468</v>
+        <v>-0.03828025477706909</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -22005,10 +22005,10 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>0.9143059490084986</v>
+        <v>0.9143665958952583</v>
       </c>
       <c r="H281" t="n">
-        <v>6.62308073654391</v>
+        <v>6.623750884642604</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -22027,16 +22027,16 @@
         <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>-0.6369192634560896</v>
+        <v>-0.6362491153573959</v>
       </c>
       <c r="N281" t="n">
-        <v>0.6369192634560896</v>
+        <v>0.6362491153573959</v>
       </c>
       <c r="O281" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P281" t="n">
-        <v>-0.05133852691218177</v>
+        <v>-0.05195329087048961</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -22076,10 +22076,10 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>0.9107648725212465</v>
+        <v>0.910828025477707</v>
       </c>
       <c r="H282" t="n">
-        <v>6.546975920679887</v>
+        <v>6.547324840764332</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -22098,16 +22098,16 @@
         <v>1</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.5630240793201136</v>
+        <v>-0.5626751592356687</v>
       </c>
       <c r="N282" t="n">
-        <v>0.5630240793201136</v>
+        <v>0.5626751592356687</v>
       </c>
       <c r="O282" t="n">
         <v>-0.1499999999999995</v>
       </c>
       <c r="P282" t="n">
-        <v>-0.0761048158640234</v>
+        <v>-0.07642604387827223</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -22147,10 +22147,10 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>0.9072237960339944</v>
+        <v>0.9072894550601557</v>
       </c>
       <c r="H283" t="n">
-        <v>6.509645892351275</v>
+        <v>6.511096956829441</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -22169,16 +22169,16 @@
         <v>1</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.5003541076487243</v>
+        <v>-0.498903043170559</v>
       </c>
       <c r="N283" t="n">
-        <v>0.5003541076487243</v>
+        <v>0.498903043170559</v>
       </c>
       <c r="O283" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P283" t="n">
-        <v>-0.03733002832861132</v>
+        <v>-0.03622788393489085</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -22218,10 +22218,10 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>0.9050991501416431</v>
+        <v>0.9051663128096249</v>
       </c>
       <c r="H284" t="n">
-        <v>6.428073654390937</v>
+        <v>6.432526539278131</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -22240,16 +22240,16 @@
         <v>1</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.3919263456090629</v>
+        <v>-0.3874734607218695</v>
       </c>
       <c r="N284" t="n">
-        <v>0.3919263456090629</v>
+        <v>0.3874734607218695</v>
       </c>
       <c r="O284" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P284" t="n">
-        <v>-0.08157223796033808</v>
+        <v>-0.07857041755131</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -22289,10 +22289,10 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>0.9015580736543909</v>
+        <v>0.9016277423920736</v>
       </c>
       <c r="H285" t="n">
-        <v>6.40110835694051</v>
+        <v>6.401493276716207</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -22311,16 +22311,16 @@
         <v>1</v>
       </c>
       <c r="M285" t="n">
-        <v>-0.2988916430594903</v>
+        <v>-0.2985067232837935</v>
       </c>
       <c r="N285" t="n">
-        <v>0.2988916430594903</v>
+        <v>0.2985067232837935</v>
       </c>
       <c r="O285" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P285" t="n">
-        <v>-0.02696529745042753</v>
+        <v>-0.03103326256192407</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
@@ -22360,10 +22360,10 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>0.8987252124645893</v>
+        <v>0.8987968860580325</v>
       </c>
       <c r="H286" t="n">
-        <v>6.351827195467422</v>
+        <v>6.353411181882518</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -22382,16 +22382,16 @@
         <v>1</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.1881728045325781</v>
+        <v>-0.1865888181174817</v>
       </c>
       <c r="N286" t="n">
-        <v>0.1881728045325781</v>
+        <v>0.1865888181174817</v>
       </c>
       <c r="O286" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P286" t="n">
-        <v>-0.04928116147308792</v>
+        <v>-0.04808209483368842</v>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
@@ -25685,10 +25685,10 @@
         <v>8</v>
       </c>
       <c r="G333" t="n">
-        <v>0.7634560906515581</v>
+        <v>0.7636234961075725</v>
       </c>
       <c r="H333" t="n">
-        <v>6.482344192634561</v>
+        <v>6.483290870488323</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -25707,16 +25707,16 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.7801558073654391</v>
+        <v>-0.7792091295116776</v>
       </c>
       <c r="N333" t="n">
-        <v>0.7801558073654391</v>
+        <v>0.7792091295116776</v>
       </c>
       <c r="O333" t="n">
         <v>-0.4400000000000004</v>
       </c>
       <c r="P333" t="n">
-        <v>-0.9851610631467977</v>
+        <v>-0.9842143852930363</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -25756,10 +25756,10 @@
         <v>8</v>
       </c>
       <c r="G334" t="n">
-        <v>0.7719546742209632</v>
+        <v>0.7721160651096957</v>
       </c>
       <c r="H334" t="n">
-        <v>6.53640138101983</v>
+        <v>6.536743630573248</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -25778,16 +25778,16 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.4385986189801701</v>
+        <v>-0.4382563694267514</v>
       </c>
       <c r="N334" t="n">
-        <v>0.4385986189801701</v>
+        <v>0.4382563694267514</v>
       </c>
       <c r="O334" t="n">
         <v>-0.2875000000000005</v>
       </c>
       <c r="P334" t="n">
-        <v>0.05405718838526852</v>
+        <v>0.05345276008492572</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -25827,10 +25827,10 @@
         <v>8</v>
       </c>
       <c r="G335" t="n">
-        <v>0.7917847025495751</v>
+        <v>0.7919320594479831</v>
       </c>
       <c r="H335" t="n">
-        <v>6.641271246458923</v>
+        <v>6.641687898089172</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -25849,16 +25849,16 @@
         <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.1587287535410766</v>
+        <v>-0.1583121019108278</v>
       </c>
       <c r="N335" t="n">
-        <v>0.1587287535410766</v>
+        <v>0.1583121019108278</v>
       </c>
       <c r="O335" t="n">
         <v>-0.1749999999999998</v>
       </c>
       <c r="P335" t="n">
-        <v>0.1048698654390936</v>
+        <v>0.1049442675159238</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -25898,10 +25898,10 @@
         <v>8</v>
       </c>
       <c r="G336" t="n">
-        <v>0.8144475920679887</v>
+        <v>0.8145789101203114</v>
       </c>
       <c r="H336" t="n">
-        <v>6.845701133144476</v>
+        <v>6.846443736730361</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -25920,16 +25920,16 @@
         <v>1</v>
       </c>
       <c r="M336" t="n">
-        <v>0.215701133144476</v>
+        <v>0.2164437367303611</v>
       </c>
       <c r="N336" t="n">
-        <v>0.215701133144476</v>
+        <v>0.2164437367303611</v>
       </c>
       <c r="O336" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P336" t="n">
-        <v>0.2044298866855527</v>
+        <v>0.204755838641189</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -25969,10 +25969,10 @@
         <v>8</v>
       </c>
       <c r="G337" t="n">
-        <v>0.8342776203966006</v>
+        <v>0.8343949044585988</v>
       </c>
       <c r="H337" t="n">
-        <v>7.062839943342777</v>
+        <v>7.063503184713376</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -25991,16 +25991,16 @@
         <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>0.5728399433427764</v>
+        <v>0.5735031847133758</v>
       </c>
       <c r="N337" t="n">
-        <v>0.5728399433427764</v>
+        <v>0.5735031847133758</v>
       </c>
       <c r="O337" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P337" t="n">
-        <v>0.2171388101983007</v>
+        <v>0.217059447983015</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>8</v>
       </c>
       <c r="G338" t="n">
-        <v>0.8505665722379604</v>
+        <v>0.8506723283793347</v>
       </c>
       <c r="H338" t="n">
-        <v>7.147990793201133</v>
+        <v>7.148110403397028</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -26062,16 +26062,16 @@
         <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>0.6679907932011329</v>
+        <v>0.6681104033970273</v>
       </c>
       <c r="N338" t="n">
-        <v>0.6679907932011329</v>
+        <v>0.6681104033970273</v>
       </c>
       <c r="O338" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P338" t="n">
-        <v>0.08515084985835664</v>
+        <v>0.08460721868365173</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -26111,10 +26111,10 @@
         <v>8</v>
       </c>
       <c r="G339" t="n">
-        <v>0.8576487252124646</v>
+        <v>0.8577494692144374</v>
       </c>
       <c r="H339" t="n">
-        <v>7.202503541076488</v>
+        <v>7.203073248407644</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -26133,16 +26133,16 @@
         <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>0.6525035410764879</v>
+        <v>0.6530732484076438</v>
       </c>
       <c r="N339" t="n">
-        <v>0.6525035410764879</v>
+        <v>0.6530732484076438</v>
       </c>
       <c r="O339" t="n">
         <v>0.0699999999999994</v>
       </c>
       <c r="P339" t="n">
-        <v>0.05451274787535443</v>
+        <v>0.05496284501061588</v>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
@@ -26182,10 +26182,10 @@
         <v>8</v>
       </c>
       <c r="G340" t="n">
-        <v>0.8498583569405099</v>
+        <v>0.8499646142958245</v>
       </c>
       <c r="H340" t="n">
-        <v>7.147189801699716</v>
+        <v>7.147309978768577</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -26204,16 +26204,16 @@
         <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>0.6171898016997162</v>
+        <v>0.617309978768577</v>
       </c>
       <c r="N340" t="n">
-        <v>0.6171898016997162</v>
+        <v>0.617309978768577</v>
       </c>
       <c r="O340" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P340" t="n">
-        <v>-0.05531373937677131</v>
+        <v>-0.05576326963906642</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -26253,10 +26253,10 @@
         <v>8</v>
       </c>
       <c r="G341" t="n">
-        <v>0.830028328611898</v>
+        <v>0.8301486199575372</v>
       </c>
       <c r="H341" t="n">
-        <v>7.021746931067044</v>
+        <v>7.022653927813163</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -26275,16 +26275,16 @@
         <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>0.6892469310670446</v>
+        <v>0.6901539278131636</v>
       </c>
       <c r="N341" t="n">
-        <v>0.6892469310670446</v>
+        <v>0.6901539278131636</v>
       </c>
       <c r="O341" t="n">
         <v>-0.1975000000000007</v>
       </c>
       <c r="P341" t="n">
-        <v>-0.1254428706326722</v>
+        <v>-0.124656050955414</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -26324,10 +26324,10 @@
         <v>8</v>
       </c>
       <c r="G342" t="n">
-        <v>0.8101983002832861</v>
+        <v>0.8103326256192498</v>
       </c>
       <c r="H342" t="n">
-        <v>6.819167847025496</v>
+        <v>6.819357749469215</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -26346,16 +26346,16 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>0.6291678470254958</v>
+        <v>0.6293577494692144</v>
       </c>
       <c r="N342" t="n">
-        <v>0.6291678470254958</v>
+        <v>0.6293577494692144</v>
       </c>
       <c r="O342" t="n">
         <v>-0.1424999999999992</v>
       </c>
       <c r="P342" t="n">
-        <v>-0.202579084041548</v>
+        <v>-0.2032961783439484</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -26395,10 +26395,10 @@
         <v>8</v>
       </c>
       <c r="G343" t="n">
-        <v>0.7868271954674221</v>
+        <v>0.7869780608634112</v>
       </c>
       <c r="H343" t="n">
-        <v>6.618031161473086</v>
+        <v>6.619999999999999</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
@@ -26417,16 +26417,16 @@
         <v>1</v>
       </c>
       <c r="M343" t="n">
-        <v>0.6280311614730856</v>
+        <v>0.629999999999999</v>
       </c>
       <c r="N343" t="n">
-        <v>0.6280311614730856</v>
+        <v>0.629999999999999</v>
       </c>
       <c r="O343" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P343" t="n">
-        <v>-0.2011366855524104</v>
+        <v>-0.1993577494692156</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -26466,10 +26466,10 @@
         <v>8</v>
       </c>
       <c r="G344" t="n">
-        <v>0.7627478753541076</v>
+        <v>0.7629157820240623</v>
       </c>
       <c r="H344" t="n">
-        <v>6.478892823418319</v>
+        <v>6.479525831564048</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -26488,16 +26488,16 @@
         <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5588928234183195</v>
+        <v>0.5595258315640486</v>
       </c>
       <c r="N344" t="n">
-        <v>0.5588928234183195</v>
+        <v>0.5595258315640486</v>
       </c>
       <c r="O344" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P344" t="n">
-        <v>-0.1391383380547664</v>
+        <v>-0.1404741684359507</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -26537,10 +26537,10 @@
         <v>8</v>
       </c>
       <c r="G345" t="n">
-        <v>0.7407932011331445</v>
+        <v>0.7409766454352441</v>
       </c>
       <c r="H345" t="n">
-        <v>6.378371104815865</v>
+        <v>6.38</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
@@ -26559,16 +26559,16 @@
         <v>1</v>
       </c>
       <c r="M345" t="n">
-        <v>0.3983711048158645</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="N345" t="n">
-        <v>0.3983711048158645</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="O345" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P345" t="n">
-        <v>-0.1005217186024545</v>
+        <v>-0.09952583156404859</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -26608,10 +26608,10 @@
         <v>8</v>
       </c>
       <c r="G346" t="n">
-        <v>0.7174220963172805</v>
+        <v>0.7176220806794055</v>
       </c>
       <c r="H346" t="n">
-        <v>6.229255488668556</v>
+        <v>6.22953821656051</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -26630,16 +26630,16 @@
         <v>1</v>
       </c>
       <c r="M346" t="n">
-        <v>0.1092554886685555</v>
+        <v>0.1095382165605097</v>
       </c>
       <c r="N346" t="n">
-        <v>0.1092554886685555</v>
+        <v>0.1095382165605097</v>
       </c>
       <c r="O346" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P346" t="n">
-        <v>-0.1491156161473093</v>
+        <v>-0.1504617834394901</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -27809,10 +27809,10 @@
         <v>8</v>
       </c>
       <c r="G363" t="n">
-        <v>0.6444759206798867</v>
+        <v>0.6447275300778486</v>
       </c>
       <c r="H363" t="n">
-        <v>6.968999645892351</v>
+        <v>6.969218860580326</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -27831,16 +27831,16 @@
         <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>-1.493500354107649</v>
+        <v>-1.493281139419675</v>
       </c>
       <c r="N363" t="n">
-        <v>1.493500354107649</v>
+        <v>1.493281139419675</v>
       </c>
       <c r="O363" t="n">
         <v>-0.254999999999999</v>
       </c>
       <c r="P363" t="n">
-        <v>0.1264190572448394</v>
+        <v>0.1266382719328139</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -27880,10 +27880,10 @@
         <v>8</v>
       </c>
       <c r="G364" t="n">
-        <v>0.6529745042492918</v>
+        <v>0.6532200990799717</v>
       </c>
       <c r="H364" t="n">
-        <v>7.001232294617564</v>
+        <v>7.002944090587403</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -27902,16 +27902,16 @@
         <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>-1.311267705382436</v>
+        <v>-1.309555909412597</v>
       </c>
       <c r="N364" t="n">
-        <v>1.311267705382436</v>
+        <v>1.309555909412597</v>
       </c>
       <c r="O364" t="n">
         <v>-0.1500000000000004</v>
       </c>
       <c r="P364" t="n">
-        <v>0.0322326487252127</v>
+        <v>0.03372523000707695</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -27951,10 +27951,10 @@
         <v>8</v>
       </c>
       <c r="G365" t="n">
-        <v>0.6657223796033994</v>
+        <v>0.6659589525831564</v>
       </c>
       <c r="H365" t="n">
-        <v>7.065042492917848</v>
+        <v>7.065866949752301</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -27973,16 +27973,16 @@
         <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>-1.064957507082153</v>
+        <v>-1.0641330502477</v>
       </c>
       <c r="N365" t="n">
-        <v>1.064957507082153</v>
+        <v>1.0641330502477</v>
       </c>
       <c r="O365" t="n">
         <v>-0.1824999999999992</v>
       </c>
       <c r="P365" t="n">
-        <v>0.06381019830028389</v>
+        <v>0.06292285916489782</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -28022,10 +28022,10 @@
         <v>8</v>
       </c>
       <c r="G366" t="n">
-        <v>0.6798866855524079</v>
+        <v>0.6801132342533617</v>
       </c>
       <c r="H366" t="n">
-        <v>7.162455736543909</v>
+        <v>7.163343949044585</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -28044,16 +28044,16 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.9250442634560914</v>
+        <v>-0.924156050955415</v>
       </c>
       <c r="N366" t="n">
-        <v>0.9250442634560914</v>
+        <v>0.924156050955415</v>
       </c>
       <c r="O366" t="n">
         <v>-0.04250000000000043</v>
       </c>
       <c r="P366" t="n">
-        <v>0.09741324362606107</v>
+        <v>0.09747699929228482</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -28093,10 +28093,10 @@
         <v>8</v>
       </c>
       <c r="G367" t="n">
-        <v>0.6876770538243626</v>
+        <v>0.6878980891719745</v>
       </c>
       <c r="H367" t="n">
-        <v>7.191638633144477</v>
+        <v>7.191831210191084</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -28115,16 +28115,16 @@
         <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>-1.038361366855524</v>
+        <v>-1.038168789808917</v>
       </c>
       <c r="N367" t="n">
-        <v>1.038361366855524</v>
+        <v>1.038168789808917</v>
       </c>
       <c r="O367" t="n">
         <v>0.1425000000000001</v>
       </c>
       <c r="P367" t="n">
-        <v>0.02918289660056761</v>
+        <v>0.02848726114649835</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -28164,10 +28164,10 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>0.6890934844192634</v>
+        <v>0.689313517338995</v>
       </c>
       <c r="H368" t="n">
-        <v>7.194239258734656</v>
+        <v>7.195133875914131</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -28186,16 +28186,16 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.8482607412653449</v>
+        <v>-0.8473661240858696</v>
       </c>
       <c r="N368" t="n">
-        <v>0.8482607412653449</v>
+        <v>0.8473661240858696</v>
       </c>
       <c r="O368" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P368" t="n">
-        <v>0.002600625590178929</v>
+        <v>0.003302665723047049</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -28235,10 +28235,10 @@
         <v>8</v>
       </c>
       <c r="G369" t="n">
-        <v>0.68342776203966</v>
+        <v>0.6836518046709129</v>
       </c>
       <c r="H369" t="n">
-        <v>7.176338969546742</v>
+        <v>7.177217356687898</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -28257,16 +28257,16 @@
         <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.7736610304532583</v>
+        <v>-0.7727826433121026</v>
       </c>
       <c r="N369" t="n">
-        <v>0.7736610304532583</v>
+        <v>0.7727826433121026</v>
       </c>
       <c r="O369" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P369" t="n">
-        <v>-0.01790028918791364</v>
+        <v>-0.01791651922623316</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -28306,10 +28306,10 @@
         <v>8</v>
       </c>
       <c r="G370" t="n">
-        <v>0.6713881019830028</v>
+        <v>0.6716206652512385</v>
       </c>
       <c r="H370" t="n">
-        <v>7.109150141643059</v>
+        <v>7.110598018400567</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -28328,16 +28328,16 @@
         <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.8708498583569417</v>
+        <v>-0.8694019815994336</v>
       </c>
       <c r="N370" t="n">
-        <v>0.8708498583569417</v>
+        <v>0.8694019815994336</v>
       </c>
       <c r="O370" t="n">
         <v>0.03000000000000025</v>
       </c>
       <c r="P370" t="n">
-        <v>-0.06718882790368319</v>
+        <v>-0.0666193382873308</v>
       </c>
       <c r="Q370" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>8</v>
       </c>
       <c r="G371" t="n">
-        <v>0.6522662889518414</v>
+        <v>0.6525123849964615</v>
       </c>
       <c r="H371" t="n">
-        <v>6.996296033994335</v>
+        <v>6.998011323425336</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -28399,16 +28399,16 @@
         <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>-1.038703966005666</v>
+        <v>-1.036988676574664</v>
       </c>
       <c r="N371" t="n">
-        <v>1.038703966005666</v>
+        <v>1.036988676574664</v>
       </c>
       <c r="O371" t="n">
         <v>0.05499999999999972</v>
       </c>
       <c r="P371" t="n">
-        <v>-0.1128541076487242</v>
+        <v>-0.1125866949752306</v>
       </c>
       <c r="Q371" t="inlineStr">
         <is>
@@ -28448,10 +28448,10 @@
         <v>8</v>
       </c>
       <c r="G372" t="n">
-        <v>0.6303116147308782</v>
+        <v>0.6305732484076433</v>
       </c>
       <c r="H372" t="n">
-        <v>6.93413597733711</v>
+        <v>6.935047770700637</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -28470,16 +28470,16 @@
         <v>1</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.9758640226628899</v>
+        <v>-0.9749522292993635</v>
       </c>
       <c r="N372" t="n">
-        <v>0.9758640226628899</v>
+        <v>0.9749522292993635</v>
       </c>
       <c r="O372" t="n">
         <v>-0.125</v>
       </c>
       <c r="P372" t="n">
-        <v>-0.06216005665722424</v>
+        <v>-0.06296355272469967</v>
       </c>
       <c r="Q372" t="inlineStr">
         <is>
@@ -28519,10 +28519,10 @@
         <v>8</v>
       </c>
       <c r="G373" t="n">
-        <v>0.6154390934844193</v>
+        <v>0.6157112526539278</v>
       </c>
       <c r="H373" t="n">
-        <v>6.877159171388103</v>
+        <v>6.878442144373674</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -28541,16 +28541,16 @@
         <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.8128408286118978</v>
+        <v>-0.8115578556263268</v>
       </c>
       <c r="N373" t="n">
-        <v>0.8128408286118978</v>
+        <v>0.8115578556263268</v>
       </c>
       <c r="O373" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P373" t="n">
-        <v>-0.05697680594900767</v>
+        <v>-0.05660562632696298</v>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
@@ -28590,10 +28590,10 @@
         <v>8</v>
       </c>
       <c r="G374" t="n">
-        <v>0.5977337110481586</v>
+        <v>0.5980184005661713</v>
       </c>
       <c r="H374" t="n">
-        <v>6.798275495750708</v>
+        <v>6.798523531493277</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -28612,16 +28612,16 @@
         <v>1</v>
       </c>
       <c r="M374" t="n">
-        <v>-0.6617245042492916</v>
+        <v>-0.6614764685067227</v>
       </c>
       <c r="N374" t="n">
-        <v>0.6617245042492916</v>
+        <v>0.6614764685067227</v>
       </c>
       <c r="O374" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P374" t="n">
-        <v>-0.07888367563739429</v>
+        <v>-0.07991861288039637</v>
       </c>
       <c r="Q374" t="inlineStr">
         <is>
@@ -28661,10 +28661,10 @@
         <v>8</v>
       </c>
       <c r="G375" t="n">
-        <v>0.5828611898016998</v>
+        <v>0.5831564048124558</v>
       </c>
       <c r="H375" t="n">
-        <v>6.760317811614731</v>
+        <v>6.760575017692852</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -28683,16 +28683,16 @@
         <v>1</v>
       </c>
       <c r="M375" t="n">
-        <v>-0.5196821883852696</v>
+        <v>-0.5194249823071484</v>
       </c>
       <c r="N375" t="n">
-        <v>0.5196821883852696</v>
+        <v>0.5194249823071484</v>
       </c>
       <c r="O375" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.03795768413597767</v>
+        <v>-0.03794851380042541</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
@@ -28732,10 +28732,10 @@
         <v>8</v>
       </c>
       <c r="G376" t="n">
-        <v>0.5644475920679887</v>
+        <v>0.5647558386411889</v>
       </c>
       <c r="H376" t="n">
-        <v>6.67854992917847</v>
+        <v>6.679087048832272</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -28754,16 +28754,16 @@
         <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>-0.4314500708215308</v>
+        <v>-0.4309129511677288</v>
       </c>
       <c r="N376" t="n">
-        <v>0.4314500708215308</v>
+        <v>0.4309129511677288</v>
       </c>
       <c r="O376" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.0817678824362611</v>
+        <v>-0.0814879688605803</v>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
@@ -29933,10 +29933,10 @@
         <v>8</v>
       </c>
       <c r="G393" t="n">
-        <v>0.6586402266288952</v>
+        <v>0.6588818117480538</v>
       </c>
       <c r="H393" t="n">
-        <v>5.818342776203966</v>
+        <v>5.822154989384289</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -29955,16 +29955,16 @@
         <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>1.028342776203965</v>
+        <v>1.032154989384289</v>
       </c>
       <c r="N393" t="n">
-        <v>1.028342776203965</v>
+        <v>1.032154989384289</v>
       </c>
       <c r="O393" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P393" t="n">
-        <v>-0.6471792980777433</v>
+        <v>-0.6433670848974202</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
@@ -30004,10 +30004,10 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>0.5644475920679887</v>
+        <v>0.5647558386411889</v>
       </c>
       <c r="H394" t="n">
-        <v>5.500872875354108</v>
+        <v>5.501480891719745</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -30026,16 +30026,16 @@
         <v>1</v>
       </c>
       <c r="M394" t="n">
-        <v>0.8308728753541077</v>
+        <v>0.8314808917197452</v>
       </c>
       <c r="N394" t="n">
-        <v>0.8308728753541077</v>
+        <v>0.8314808917197452</v>
       </c>
       <c r="O394" t="n">
         <v>-0.120000000000001</v>
       </c>
       <c r="P394" t="n">
-        <v>-0.3174699008498587</v>
+        <v>-0.3206740976645444</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -30075,10 +30075,10 @@
         <v>8</v>
       </c>
       <c r="G395" t="n">
-        <v>0.5424929178470255</v>
+        <v>0.5428167020523709</v>
       </c>
       <c r="H395" t="n">
-        <v>5.456689093484419</v>
+        <v>5.456901981599434</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -30097,16 +30097,16 @@
         <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>0.9166890934844192</v>
+        <v>0.9169019815994339</v>
       </c>
       <c r="N395" t="n">
-        <v>0.9166890934844192</v>
+        <v>0.9169019815994339</v>
       </c>
       <c r="O395" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P395" t="n">
-        <v>-0.04418378186968841</v>
+        <v>-0.04457891012031112</v>
       </c>
       <c r="Q395" t="inlineStr">
         <is>
@@ -30146,10 +30146,10 @@
         <v>8</v>
       </c>
       <c r="G396" t="n">
-        <v>0.5956090651558074</v>
+        <v>0.5958952583156405</v>
       </c>
       <c r="H396" t="n">
-        <v>5.636612960339943</v>
+        <v>5.636801132342534</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -30168,16 +30168,16 @@
         <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>1.196612960339943</v>
+        <v>1.196801132342533</v>
       </c>
       <c r="N396" t="n">
-        <v>1.196612960339943</v>
+        <v>1.196801132342533</v>
       </c>
       <c r="O396" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P396" t="n">
-        <v>0.1799238668555239</v>
+        <v>0.1798991507430996</v>
       </c>
       <c r="Q396" t="inlineStr">
         <is>
@@ -30217,10 +30217,10 @@
         <v>8</v>
       </c>
       <c r="G397" t="n">
-        <v>0.6338526912181303</v>
+        <v>0.6341118188251946</v>
       </c>
       <c r="H397" t="n">
-        <v>5.756758144475921</v>
+        <v>5.756928520877566</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -30239,16 +30239,16 @@
         <v>1</v>
       </c>
       <c r="M397" t="n">
-        <v>1.316758144475921</v>
+        <v>1.316928520877566</v>
       </c>
       <c r="N397" t="n">
-        <v>1.316758144475921</v>
+        <v>1.316928520877566</v>
       </c>
       <c r="O397" t="n">
         <v>0</v>
       </c>
       <c r="P397" t="n">
-        <v>0.1201451841359784</v>
+        <v>0.1201273885350327</v>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>8</v>
       </c>
       <c r="G398" t="n">
-        <v>0.5941926345609065</v>
+        <v>0.5944798301486199</v>
       </c>
       <c r="H398" t="n">
-        <v>5.635681657223796</v>
+        <v>5.635870488322718</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -30310,16 +30310,16 @@
         <v>1</v>
       </c>
       <c r="M398" t="n">
-        <v>1.235681657223796</v>
+        <v>1.235870488322718</v>
       </c>
       <c r="N398" t="n">
-        <v>1.235681657223796</v>
+        <v>1.235870488322718</v>
       </c>
       <c r="O398" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P398" t="n">
-        <v>-0.1210764872521253</v>
+        <v>-0.1210580325548483</v>
       </c>
       <c r="Q398" t="inlineStr">
         <is>
@@ -30359,10 +30359,10 @@
         <v>8</v>
       </c>
       <c r="G399" t="n">
-        <v>0.4787535410764873</v>
+        <v>0.4791224345364473</v>
       </c>
       <c r="H399" t="n">
-        <v>5.189780453257791</v>
+        <v>5.190138004246285</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -30381,16 +30381,16 @@
         <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>0.8097804532577912</v>
+        <v>0.8101380042462853</v>
       </c>
       <c r="N399" t="n">
-        <v>0.8097804532577912</v>
+        <v>0.8101380042462853</v>
       </c>
       <c r="O399" t="n">
         <v>-0.02000000000000046</v>
       </c>
       <c r="P399" t="n">
-        <v>-0.4459012039660051</v>
+        <v>-0.4457324840764327</v>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
@@ -30430,10 +30430,10 @@
         <v>8</v>
       </c>
       <c r="G400" t="n">
-        <v>0.3703966005665723</v>
+        <v>0.3701344656758669</v>
       </c>
       <c r="H400" t="n">
-        <v>4.843535764872521</v>
+        <v>4.843363411181882</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -30452,16 +30452,16 @@
         <v>1</v>
       </c>
       <c r="M400" t="n">
-        <v>0.7035357648725213</v>
+        <v>0.7033634111818827</v>
       </c>
       <c r="N400" t="n">
-        <v>0.7035357648725213</v>
+        <v>0.7033634111818827</v>
       </c>
       <c r="O400" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P400" t="n">
-        <v>-0.3462446883852701</v>
+        <v>-0.3467745930644028</v>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
@@ -30501,10 +30501,10 @@
         <v>8</v>
       </c>
       <c r="G401" t="n">
-        <v>0.3257790368271954</v>
+        <v>0.3255484784147205</v>
       </c>
       <c r="H401" t="n">
-        <v>4.702896600566572</v>
+        <v>4.701077494692145</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -30523,16 +30523,16 @@
         <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>0.8328966005665723</v>
+        <v>0.8310774946921446</v>
       </c>
       <c r="N401" t="n">
-        <v>0.8328966005665723</v>
+        <v>0.8310774946921446</v>
       </c>
       <c r="O401" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P401" t="n">
-        <v>-0.1406391643059486</v>
+        <v>-0.1422859164897377</v>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
@@ -30572,10 +30572,10 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>0.3519830028328612</v>
+        <v>0.3517338995046002</v>
       </c>
       <c r="H402" t="n">
-        <v>4.806428824362606</v>
+        <v>4.806265038924274</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -30594,16 +30594,16 @@
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>1.086428824362606</v>
+        <v>1.086265038924274</v>
       </c>
       <c r="N402" t="n">
-        <v>1.086428824362606</v>
+        <v>1.086265038924274</v>
       </c>
       <c r="O402" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P402" t="n">
-        <v>0.1035322237960337</v>
+        <v>0.1051875442321295</v>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -30643,10 +30643,10 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>0.5297450424929179</v>
+        <v>0.5300778485491862</v>
       </c>
       <c r="H403" t="n">
-        <v>5.441614730878187</v>
+        <v>5.44205237084218</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -30665,16 +30665,16 @@
         <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>1.741614730878187</v>
+        <v>1.742052370842179</v>
       </c>
       <c r="N403" t="n">
-        <v>1.741614730878187</v>
+        <v>1.742052370842179</v>
       </c>
       <c r="O403" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P403" t="n">
-        <v>0.6351859065155807</v>
+        <v>0.6357873319179053</v>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>8</v>
       </c>
       <c r="G404" t="n">
-        <v>0.7606232294617564</v>
+        <v>0.7607926397735315</v>
       </c>
       <c r="H404" t="n">
-        <v>6.100878186968838</v>
+        <v>6.101769285208776</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -30736,16 +30736,16 @@
         <v>1</v>
       </c>
       <c r="M404" t="n">
-        <v>2.260878186968839</v>
+        <v>2.261769285208776</v>
       </c>
       <c r="N404" t="n">
-        <v>2.260878186968839</v>
+        <v>2.261769285208776</v>
       </c>
       <c r="O404" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P404" t="n">
-        <v>0.6592634560906516</v>
+        <v>0.6597169143665962</v>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
@@ -30785,10 +30785,10 @@
         <v>8</v>
       </c>
       <c r="G405" t="n">
-        <v>0.8314447592067988</v>
+        <v>0.8315640481245576</v>
       </c>
       <c r="H405" t="n">
-        <v>6.345074362606232</v>
+        <v>6.34578025477707</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -30807,16 +30807,16 @@
         <v>1</v>
       </c>
       <c r="M405" t="n">
-        <v>2.325074362606233</v>
+        <v>2.325780254777071</v>
       </c>
       <c r="N405" t="n">
-        <v>2.325074362606233</v>
+        <v>2.325780254777071</v>
       </c>
       <c r="O405" t="n">
         <v>0.1799999999999997</v>
       </c>
       <c r="P405" t="n">
-        <v>0.244196175637394</v>
+        <v>0.2440109695682944</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
@@ -30856,10 +30856,10 @@
         <v>8</v>
       </c>
       <c r="G406" t="n">
-        <v>0.8158640226628895</v>
+        <v>0.8159943382873319</v>
       </c>
       <c r="H406" t="n">
-        <v>6.291805949008499</v>
+        <v>6.292662774239208</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -30878,16 +30878,16 @@
         <v>1</v>
       </c>
       <c r="M406" t="n">
-        <v>2.191805949008499</v>
+        <v>2.192662774239208</v>
       </c>
       <c r="N406" t="n">
-        <v>2.191805949008499</v>
+        <v>2.192662774239208</v>
       </c>
       <c r="O406" t="n">
         <v>0.08000000000000007</v>
       </c>
       <c r="P406" t="n">
-        <v>-0.05326841359773393</v>
+        <v>-0.05311748053786225</v>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
@@ -32057,10 +32057,10 @@
         <v>8</v>
       </c>
       <c r="G423" t="n">
-        <v>0.8293201133144475</v>
+        <v>0.8294409058740269</v>
       </c>
       <c r="H423" t="n">
-        <v>5.562894830028328</v>
+        <v>5.563673036093418</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -32079,16 +32079,16 @@
         <v>1</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.8046051699716719</v>
+        <v>-0.803826963906582</v>
       </c>
       <c r="N423" t="n">
-        <v>0.8046051699716719</v>
+        <v>0.803826963906582</v>
       </c>
       <c r="O423" t="n">
         <v>-0.07500000000000018</v>
       </c>
       <c r="P423" t="n">
-        <v>-1.476034742501454</v>
+        <v>-1.475256536436365</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
@@ -32128,10 +32128,10 @@
         <v>8</v>
       </c>
       <c r="G424" t="n">
-        <v>0.8271954674220963</v>
+        <v>0.8273177636234961</v>
       </c>
       <c r="H424" t="n">
-        <v>5.547804532577904</v>
+        <v>5.548329794762916</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -32150,16 +32150,16 @@
         <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>-0.7696954674220962</v>
+        <v>-0.7691702052370841</v>
       </c>
       <c r="N424" t="n">
-        <v>0.7696954674220962</v>
+        <v>0.7691702052370841</v>
       </c>
       <c r="O424" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P424" t="n">
-        <v>-0.01509029745042412</v>
+        <v>-0.01534324133050191</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -32199,10 +32199,10 @@
         <v>8</v>
       </c>
       <c r="G425" t="n">
-        <v>0.8208215297450425</v>
+        <v>0.8209483368719037</v>
       </c>
       <c r="H425" t="n">
-        <v>5.500856940509916</v>
+        <v>5.501946213729653</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -32221,16 +32221,16 @@
         <v>1</v>
       </c>
       <c r="M425" t="n">
-        <v>-0.7591430594900839</v>
+        <v>-0.7580537862703469</v>
       </c>
       <c r="N425" t="n">
-        <v>0.7591430594900839</v>
+        <v>0.7580537862703469</v>
       </c>
       <c r="O425" t="n">
         <v>-0.05750000000000011</v>
       </c>
       <c r="P425" t="n">
-        <v>-0.04694759206798782</v>
+        <v>-0.0463835810332629</v>
       </c>
       <c r="Q425" t="inlineStr">
         <is>
@@ -32270,10 +32270,10 @@
         <v>8</v>
       </c>
       <c r="G426" t="n">
-        <v>0.8179886685552408</v>
+        <v>0.8181174805378627</v>
       </c>
       <c r="H426" t="n">
-        <v>5.487391997167139</v>
+        <v>5.488221868365181</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -32292,16 +32292,16 @@
         <v>1</v>
       </c>
       <c r="M426" t="n">
-        <v>-0.6426080028328611</v>
+        <v>-0.641778131634819</v>
       </c>
       <c r="N426" t="n">
-        <v>0.6426080028328611</v>
+        <v>0.641778131634819</v>
       </c>
       <c r="O426" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P426" t="n">
-        <v>-0.01346494334277715</v>
+        <v>-0.01372434536447198</v>
       </c>
       <c r="Q426" t="inlineStr">
         <is>
@@ -32341,10 +32341,10 @@
         <v>8</v>
       </c>
       <c r="G427" t="n">
-        <v>0.8087818696883853</v>
+        <v>0.8089171974522293</v>
       </c>
       <c r="H427" t="n">
-        <v>5.381859065155806</v>
+        <v>5.382149681528662</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -32363,16 +32363,16 @@
         <v>1</v>
       </c>
       <c r="M427" t="n">
-        <v>-0.6081409348441937</v>
+        <v>-0.6078503184713382</v>
       </c>
       <c r="N427" t="n">
-        <v>0.6081409348441937</v>
+        <v>0.6078503184713382</v>
       </c>
       <c r="O427" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P427" t="n">
-        <v>-0.1055329320113323</v>
+        <v>-0.1060721868365189</v>
       </c>
       <c r="Q427" t="inlineStr">
         <is>
@@ -32412,10 +32412,10 @@
         <v>8</v>
       </c>
       <c r="G428" t="n">
-        <v>0.7882436260623229</v>
+        <v>0.7883934890304317</v>
       </c>
       <c r="H428" t="n">
-        <v>5.227753186968839</v>
+        <v>5.228075017692852</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -32434,16 +32434,16 @@
         <v>1</v>
       </c>
       <c r="M428" t="n">
-        <v>-0.4797468130311611</v>
+        <v>-0.4794249823071475</v>
       </c>
       <c r="N428" t="n">
-        <v>0.4797468130311611</v>
+        <v>0.4794249823071475</v>
       </c>
       <c r="O428" t="n">
         <v>-0.2825000000000006</v>
       </c>
       <c r="P428" t="n">
-        <v>-0.154105878186968</v>
+        <v>-0.1540746638358099</v>
       </c>
       <c r="Q428" t="inlineStr">
         <is>
@@ -32483,10 +32483,10 @@
         <v>8</v>
       </c>
       <c r="G429" t="n">
-        <v>0.7705382436260623</v>
+        <v>0.7707006369426752</v>
       </c>
       <c r="H429" t="n">
-        <v>5.099327195467422</v>
+        <v>5.10015923566879</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
@@ -32505,16 +32505,16 @@
         <v>1</v>
       </c>
       <c r="M429" t="n">
-        <v>-0.4606728045325781</v>
+        <v>-0.4598407643312097</v>
       </c>
       <c r="N429" t="n">
-        <v>0.4606728045325781</v>
+        <v>0.4598407643312097</v>
       </c>
       <c r="O429" t="n">
         <v>-0.1475</v>
       </c>
       <c r="P429" t="n">
-        <v>-0.128425991501417</v>
+        <v>-0.1279157820240622</v>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
@@ -32554,10 +32554,10 @@
         <v>8</v>
       </c>
       <c r="G430" t="n">
-        <v>0.7457507082152974</v>
+        <v>0.745930644019816</v>
       </c>
       <c r="H430" t="n">
-        <v>4.947999291784702</v>
+        <v>4.948772116065109</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -32576,16 +32576,16 @@
         <v>1</v>
       </c>
       <c r="M430" t="n">
-        <v>-0.3920007082152974</v>
+        <v>-0.3912278839348904</v>
       </c>
       <c r="N430" t="n">
-        <v>0.3920007082152974</v>
+        <v>0.3912278839348904</v>
       </c>
       <c r="O430" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P430" t="n">
-        <v>-0.1513279036827191</v>
+        <v>-0.1513871196036805</v>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
@@ -32625,10 +32625,10 @@
         <v>8</v>
       </c>
       <c r="G431" t="n">
-        <v>0.7195467422096318</v>
+        <v>0.719037508846426</v>
       </c>
       <c r="H431" t="n">
-        <v>4.820453257790369</v>
+        <v>4.82</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
@@ -32647,16 +32647,16 @@
         <v>1</v>
       </c>
       <c r="M431" t="n">
-        <v>-0.2920467422096307</v>
+        <v>-0.2924999999999995</v>
       </c>
       <c r="N431" t="n">
-        <v>0.2920467422096307</v>
+        <v>0.2924999999999995</v>
       </c>
       <c r="O431" t="n">
         <v>-0.2275</v>
       </c>
       <c r="P431" t="n">
-        <v>-0.1275460339943333</v>
+        <v>-0.1287721160651092</v>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
@@ -32696,10 +32696,10 @@
         <v>8</v>
       </c>
       <c r="G432" t="n">
-        <v>0.6954674220963173</v>
+        <v>0.6949752300070772</v>
       </c>
       <c r="H432" t="n">
-        <v>4.654024433427762</v>
+        <v>4.652459306440198</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -32718,16 +32718,16 @@
         <v>1</v>
       </c>
       <c r="M432" t="n">
-        <v>-0.3559755665722379</v>
+        <v>-0.3575406935598018</v>
       </c>
       <c r="N432" t="n">
-        <v>0.3559755665722379</v>
+        <v>0.3575406935598018</v>
       </c>
       <c r="O432" t="n">
         <v>-0.1025</v>
       </c>
       <c r="P432" t="n">
-        <v>-0.1664288243626073</v>
+        <v>-0.1675406935598023</v>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
@@ -32767,10 +32767,10 @@
         <v>8</v>
       </c>
       <c r="G433" t="n">
-        <v>0.6855524079320113</v>
+        <v>0.6850672328379335</v>
       </c>
       <c r="H433" t="n">
-        <v>4.622361898016996</v>
+        <v>4.621840941259731</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -32789,16 +32789,16 @@
         <v>1</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.2176381019830034</v>
+        <v>-0.2181590587402686</v>
       </c>
       <c r="N433" t="n">
-        <v>0.2176381019830034</v>
+        <v>0.2181590587402686</v>
       </c>
       <c r="O433" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P433" t="n">
-        <v>-0.03166253541076536</v>
+        <v>-0.03061836518046679</v>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
@@ -32838,10 +32838,10 @@
         <v>8</v>
       </c>
       <c r="G434" t="n">
-        <v>0.6905099150141643</v>
+        <v>0.6900212314225053</v>
       </c>
       <c r="H434" t="n">
-        <v>4.640493389990556</v>
+        <v>4.639094125973107</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -32860,16 +32860,16 @@
         <v>1</v>
       </c>
       <c r="M434" t="n">
-        <v>-0.07950661000944326</v>
+        <v>-0.08090587402689309</v>
       </c>
       <c r="N434" t="n">
-        <v>0.07950661000944326</v>
+        <v>0.08090587402689309</v>
       </c>
       <c r="O434" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P434" t="n">
-        <v>0.01813149197356001</v>
+        <v>0.01725318471337545</v>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
@@ -32909,10 +32909,10 @@
         <v>8</v>
       </c>
       <c r="G435" t="n">
-        <v>0.7096317280453258</v>
+        <v>0.7091295116772823</v>
       </c>
       <c r="H435" t="n">
-        <v>4.747157695939566</v>
+        <v>4.744281670205237</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -32931,16 +32931,16 @@
         <v>1</v>
       </c>
       <c r="M435" t="n">
-        <v>0.1871576959395664</v>
+        <v>0.1842816702052374</v>
       </c>
       <c r="N435" t="n">
-        <v>0.1871576959395664</v>
+        <v>0.1842816702052374</v>
       </c>
       <c r="O435" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P435" t="n">
-        <v>0.1066643059490096</v>
+        <v>0.1051875442321304</v>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
@@ -32980,10 +32980,10 @@
         <v>8</v>
       </c>
       <c r="G436" t="n">
-        <v>0.7252124645892352</v>
+        <v>0.7246992215145082</v>
       </c>
       <c r="H436" t="n">
-        <v>4.844787535410765</v>
+        <v>4.842583156404812</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -33002,16 +33002,16 @@
         <v>1</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4547875354107651</v>
+        <v>0.4525831564048124</v>
       </c>
       <c r="N436" t="n">
-        <v>0.4547875354107651</v>
+        <v>0.4525831564048124</v>
       </c>
       <c r="O436" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P436" t="n">
-        <v>0.09762983947119874</v>
+        <v>0.09830148619957502</v>
       </c>
       <c r="Q436" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>8</v>
       </c>
       <c r="G437" t="n">
-        <v>0.8229461756373938</v>
+        <v>0.8230714791224345</v>
       </c>
       <c r="H437" t="n">
-        <v>3.489546742209632</v>
+        <v>3.492929936305731</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -33073,10 +33073,10 @@
         <v>1</v>
       </c>
       <c r="M437" t="n">
-        <v>-0.9504532577903682</v>
+        <v>-0.9470700636942695</v>
       </c>
       <c r="N437" t="n">
-        <v>0.9504532577903682</v>
+        <v>0.9470700636942695</v>
       </c>
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
@@ -33116,10 +33116,10 @@
         <v>8</v>
       </c>
       <c r="G438" t="n">
-        <v>0.8087818696883853</v>
+        <v>0.8089171974522293</v>
       </c>
       <c r="H438" t="n">
-        <v>3.347422096317281</v>
+        <v>3.348152866242039</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -33138,16 +33138,16 @@
         <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>-0.8950779036827199</v>
+        <v>-0.8943471337579618</v>
       </c>
       <c r="N438" t="n">
-        <v>0.8950779036827199</v>
+        <v>0.8943471337579618</v>
       </c>
       <c r="O438" t="n">
         <v>-0.1974999999999998</v>
       </c>
       <c r="P438" t="n">
-        <v>-0.1421246458923515</v>
+        <v>-0.1447770700636921</v>
       </c>
       <c r="Q438" t="inlineStr">
         <is>
@@ -33187,10 +33187,10 @@
         <v>8</v>
       </c>
       <c r="G439" t="n">
-        <v>0.7995750708215298</v>
+        <v>0.7997169143665959</v>
       </c>
       <c r="H439" t="n">
-        <v>3.293852691218131</v>
+        <v>3.294235668789809</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -33209,16 +33209,16 @@
         <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>-0.8161473087818698</v>
+        <v>-0.8157643312101914</v>
       </c>
       <c r="N439" t="n">
-        <v>0.8161473087818698</v>
+        <v>0.8157643312101914</v>
       </c>
       <c r="O439" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P439" t="n">
-        <v>-0.0535694050991502</v>
+        <v>-0.05391719745222989</v>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
@@ -33258,10 +33258,10 @@
         <v>8</v>
       </c>
       <c r="G440" t="n">
-        <v>0.8038243626062322</v>
+        <v>0.8039631988676574</v>
       </c>
       <c r="H440" t="n">
-        <v>3.311303116147308</v>
+        <v>3.3128025477707</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -33280,16 +33280,16 @@
         <v>1</v>
       </c>
       <c r="M440" t="n">
-        <v>-0.6586968838526919</v>
+        <v>-0.6571974522292998</v>
       </c>
       <c r="N440" t="n">
-        <v>0.6586968838526919</v>
+        <v>0.6571974522292998</v>
       </c>
       <c r="O440" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P440" t="n">
-        <v>0.01745042492917781</v>
+        <v>0.01856687898089149</v>
       </c>
       <c r="Q440" t="inlineStr">
         <is>
@@ -33329,10 +33329,10 @@
         <v>8</v>
       </c>
       <c r="G441" t="n">
-        <v>0.8215297450424929</v>
+        <v>0.8216560509554141</v>
       </c>
       <c r="H441" t="n">
-        <v>3.462521246458923</v>
+        <v>3.463885350318472</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -33351,16 +33351,16 @@
         <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>-0.3674787535410768</v>
+        <v>-0.3661146496815282</v>
       </c>
       <c r="N441" t="n">
-        <v>0.3674787535410768</v>
+        <v>0.3661146496815282</v>
       </c>
       <c r="O441" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P441" t="n">
-        <v>0.1512181303116149</v>
+        <v>0.1510828025477715</v>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
@@ -33400,10 +33400,10 @@
         <v>8</v>
       </c>
       <c r="G442" t="n">
-        <v>0.8378186968838527</v>
+        <v>0.83793347487615</v>
       </c>
       <c r="H442" t="n">
-        <v>3.645627950897073</v>
+        <v>3.646454352441614</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -33422,16 +33422,16 @@
         <v>1</v>
       </c>
       <c r="M442" t="n">
-        <v>-0.01437204910292733</v>
+        <v>-0.01354564755838661</v>
       </c>
       <c r="N442" t="n">
-        <v>0.01437204910292733</v>
+        <v>0.01354564755838661</v>
       </c>
       <c r="O442" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P442" t="n">
-        <v>0.1831067044381496</v>
+        <v>0.1825690021231416</v>
       </c>
       <c r="Q442" t="inlineStr">
         <is>
@@ -33471,10 +33471,10 @@
         <v>8</v>
       </c>
       <c r="G443" t="n">
-        <v>0.8477337110481586</v>
+        <v>0.8478414720452937</v>
       </c>
       <c r="H443" t="n">
-        <v>3.721381019830029</v>
+        <v>3.721671974522293</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -33493,16 +33493,16 @@
         <v>1</v>
       </c>
       <c r="M443" t="n">
-        <v>0.08138101983002866</v>
+        <v>0.08167197452229313</v>
       </c>
       <c r="N443" t="n">
-        <v>0.08138101983002866</v>
+        <v>0.08167197452229313</v>
       </c>
       <c r="O443" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P443" t="n">
-        <v>0.07575306893295597</v>
+        <v>0.07521762208067972</v>
       </c>
       <c r="Q443" t="inlineStr">
         <is>
@@ -33542,10 +33542,10 @@
         <v>8</v>
       </c>
       <c r="G444" t="n">
-        <v>0.8555240793201133</v>
+        <v>0.8556263269639066</v>
       </c>
       <c r="H444" t="n">
-        <v>3.754830028328612</v>
+        <v>3.755382165605095</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -33564,16 +33564,16 @@
         <v>1</v>
       </c>
       <c r="M444" t="n">
-        <v>0.1548300283286115</v>
+        <v>0.1553821656050953</v>
       </c>
       <c r="N444" t="n">
-        <v>0.1548300283286115</v>
+        <v>0.1553821656050953</v>
       </c>
       <c r="O444" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P444" t="n">
-        <v>0.03344900849858279</v>
+        <v>0.03371019108280215</v>
       </c>
       <c r="Q444" t="inlineStr">
         <is>
@@ -33613,10 +33613,10 @@
         <v>8</v>
       </c>
       <c r="G445" t="n">
-        <v>0.8583569405099151</v>
+        <v>0.8584571832979476</v>
       </c>
       <c r="H445" t="n">
-        <v>3.767563739376771</v>
+        <v>3.767834394904459</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -33635,16 +33635,16 @@
         <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>0.2350637393767707</v>
+        <v>0.2353343949044584</v>
       </c>
       <c r="N445" t="n">
-        <v>0.2350637393767707</v>
+        <v>0.2353343949044584</v>
       </c>
       <c r="O445" t="n">
         <v>-0.06749999999999989</v>
       </c>
       <c r="P445" t="n">
-        <v>0.01273371104815935</v>
+        <v>0.01245222929936318</v>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
@@ -33684,10 +33684,10 @@
         <v>8</v>
       </c>
       <c r="G446" t="n">
-        <v>0.8505665722379604</v>
+        <v>0.8506723283793347</v>
       </c>
       <c r="H446" t="n">
-        <v>3.733059490084986</v>
+        <v>3.733630573248407</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -33706,16 +33706,16 @@
         <v>1</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2930594900849859</v>
+        <v>0.2936305732484072</v>
       </c>
       <c r="N446" t="n">
-        <v>0.2930594900849859</v>
+        <v>0.2936305732484072</v>
       </c>
       <c r="O446" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P446" t="n">
-        <v>-0.03450424929178508</v>
+        <v>-0.0342038216560514</v>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
@@ -33755,10 +33755,10 @@
         <v>8</v>
       </c>
       <c r="G447" t="n">
-        <v>0.839943342776204</v>
+        <v>0.8400566171266808</v>
       </c>
       <c r="H447" t="n">
-        <v>3.662429178470255</v>
+        <v>3.664570063694267</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -33777,16 +33777,16 @@
         <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>0.3724291784702554</v>
+        <v>0.374570063694267</v>
       </c>
       <c r="N447" t="n">
-        <v>0.3724291784702554</v>
+        <v>0.374570063694267</v>
       </c>
       <c r="O447" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.07063031161473043</v>
+        <v>-0.06906050955414011</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
@@ -33826,10 +33826,10 @@
         <v>8</v>
       </c>
       <c r="G448" t="n">
-        <v>0.8151558073654391</v>
+        <v>0.8152866242038217</v>
       </c>
       <c r="H448" t="n">
-        <v>3.415920679886686</v>
+        <v>3.416273885350319</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -33848,16 +33848,16 @@
         <v>1</v>
       </c>
       <c r="M448" t="n">
-        <v>0.2359206798866857</v>
+        <v>0.2362738853503186</v>
       </c>
       <c r="N448" t="n">
-        <v>0.2359206798866857</v>
+        <v>0.2362738853503186</v>
       </c>
       <c r="O448" t="n">
         <v>-0.1099999999999999</v>
       </c>
       <c r="P448" t="n">
-        <v>-0.2465084985835695</v>
+        <v>-0.2482961783439483</v>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
@@ -33897,10 +33897,10 @@
         <v>8</v>
       </c>
       <c r="G449" t="n">
-        <v>0.78328611898017</v>
+        <v>0.7834394904458599</v>
       </c>
       <c r="H449" t="n">
-        <v>3.214745042492918</v>
+        <v>3.215573248407644</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -33919,16 +33919,16 @@
         <v>1</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1147450424929177</v>
+        <v>0.1155732484076437</v>
       </c>
       <c r="N449" t="n">
-        <v>0.1147450424929177</v>
+        <v>0.1155732484076437</v>
       </c>
       <c r="O449" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P449" t="n">
-        <v>-0.2011756373937681</v>
+        <v>-0.2007006369426749</v>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
@@ -33968,10 +33968,10 @@
         <v>8</v>
       </c>
       <c r="G450" t="n">
-        <v>0.7662889518413598</v>
+        <v>0.7664543524416136</v>
       </c>
       <c r="H450" t="n">
-        <v>3.105920679886686</v>
+        <v>3.107707006369427</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -33990,16 +33990,16 @@
         <v>1</v>
       </c>
       <c r="M450" t="n">
-        <v>0.005920679886685765</v>
+        <v>0.007707006369426672</v>
       </c>
       <c r="N450" t="n">
-        <v>0.005920679886685765</v>
+        <v>0.007707006369426672</v>
       </c>
       <c r="O450" t="n">
         <v>0</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.108824362606232</v>
+        <v>-0.107866242038217</v>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
@@ -35311,10 +35311,10 @@
         <v>8</v>
       </c>
       <c r="G469" t="n">
-        <v>0.8427762039660056</v>
+        <v>0.8428874734607219</v>
       </c>
       <c r="H469" t="n">
-        <v>8.548371104815864</v>
+        <v>8.550806794055203</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -35333,16 +35333,16 @@
         <v>1</v>
       </c>
       <c r="M469" t="n">
-        <v>-0.6916288951841363</v>
+        <v>-0.6891932059447967</v>
       </c>
       <c r="N469" t="n">
-        <v>0.6916288951841363</v>
+        <v>0.6891932059447967</v>
       </c>
       <c r="O469" t="n">
         <v>-0.08999999999999986</v>
       </c>
       <c r="P469" t="n">
-        <v>0.2494012379623261</v>
+        <v>0.2518369272016656</v>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
@@ -35382,10 +35382,10 @@
         <v>8</v>
       </c>
       <c r="G470" t="n">
-        <v>0.8257790368271954</v>
+        <v>0.8259023354564756</v>
       </c>
       <c r="H470" t="n">
-        <v>8.279801699716714</v>
+        <v>8.281273885350318</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -35404,16 +35404,16 @@
         <v>1</v>
       </c>
       <c r="M470" t="n">
-        <v>-0.7701983002832868</v>
+        <v>-0.7687261146496827</v>
       </c>
       <c r="N470" t="n">
-        <v>0.7701983002832868</v>
+        <v>0.7687261146496827</v>
       </c>
       <c r="O470" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P470" t="n">
-        <v>-0.2685694050991501</v>
+        <v>-0.2695329087048854</v>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -35453,10 +35453,10 @@
         <v>8</v>
       </c>
       <c r="G471" t="n">
-        <v>0.806657223796034</v>
+        <v>0.8067940552016986</v>
       </c>
       <c r="H471" t="n">
-        <v>7.992974504249292</v>
+        <v>7.996242038216562</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -35475,16 +35475,16 @@
         <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.9170254957507078</v>
+        <v>-0.9137579617834382</v>
       </c>
       <c r="N471" t="n">
-        <v>0.9170254957507078</v>
+        <v>0.9137579617834382</v>
       </c>
       <c r="O471" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P471" t="n">
-        <v>-0.2868271954674215</v>
+        <v>-0.2850318471337561</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
@@ -35524,10 +35524,10 @@
         <v>8</v>
       </c>
       <c r="G472" t="n">
-        <v>0.7946175637393768</v>
+        <v>0.7947629157820241</v>
       </c>
       <c r="H472" t="n">
-        <v>7.893866855524079</v>
+        <v>7.894734607218683</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -35546,16 +35546,16 @@
         <v>1</v>
       </c>
       <c r="M472" t="n">
-        <v>-0.8761331444759204</v>
+        <v>-0.8752653927813165</v>
       </c>
       <c r="N472" t="n">
-        <v>0.8761331444759204</v>
+        <v>0.8752653927813165</v>
       </c>
       <c r="O472" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P472" t="n">
-        <v>-0.09910764872521316</v>
+        <v>-0.101507430997879</v>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
@@ -35595,10 +35595,10 @@
         <v>8</v>
       </c>
       <c r="G473" t="n">
-        <v>0.7924929178470255</v>
+        <v>0.7926397735314933</v>
       </c>
       <c r="H473" t="n">
-        <v>7.872365439093484</v>
+        <v>7.87411889596603</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -35617,16 +35617,16 @@
         <v>1</v>
       </c>
       <c r="M473" t="n">
-        <v>-0.7076345609065164</v>
+        <v>-0.7058811040339705</v>
       </c>
       <c r="N473" t="n">
-        <v>0.7076345609065164</v>
+        <v>0.7058811040339705</v>
       </c>
       <c r="O473" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P473" t="n">
-        <v>-0.02150141643059555</v>
+        <v>-0.02061571125265349</v>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
@@ -35666,10 +35666,10 @@
         <v>8</v>
       </c>
       <c r="G474" t="n">
-        <v>0.8031161473087819</v>
+        <v>0.8032554847841472</v>
       </c>
       <c r="H474" t="n">
-        <v>7.928201133144475</v>
+        <v>7.928478414720453</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -35688,16 +35688,16 @@
         <v>1</v>
       </c>
       <c r="M474" t="n">
-        <v>-0.5217988668555238</v>
+        <v>-0.5215215852795465</v>
       </c>
       <c r="N474" t="n">
-        <v>0.5217988668555238</v>
+        <v>0.5215215852795465</v>
       </c>
       <c r="O474" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P474" t="n">
-        <v>0.05583569405099187</v>
+        <v>0.05435951875442324</v>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
@@ -35737,10 +35737,10 @@
         <v>8</v>
       </c>
       <c r="G475" t="n">
-        <v>0.8158640226628895</v>
+        <v>0.8159943382873319</v>
       </c>
       <c r="H475" t="n">
-        <v>8.193569405099149</v>
+        <v>8.19382873319179</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -35759,16 +35759,16 @@
         <v>1</v>
       </c>
       <c r="M475" t="n">
-        <v>-0.1264305949008513</v>
+        <v>-0.1261712668082104</v>
       </c>
       <c r="N475" t="n">
-        <v>0.1264305949008513</v>
+        <v>0.1261712668082104</v>
       </c>
       <c r="O475" t="n">
         <v>-0.129999999999999</v>
       </c>
       <c r="P475" t="n">
-        <v>0.2653682719546735</v>
+        <v>0.2653503184713371</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
@@ -35808,10 +35808,10 @@
         <v>8</v>
       </c>
       <c r="G476" t="n">
-        <v>0.8279036827195467</v>
+        <v>0.8280254777070064</v>
       </c>
       <c r="H476" t="n">
-        <v>8.305169971671388</v>
+        <v>8.306624203821656</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -35830,16 +35830,16 @@
         <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>0.04516997167138825</v>
+        <v>0.046624203821656</v>
       </c>
       <c r="N476" t="n">
-        <v>0.04516997167138825</v>
+        <v>0.046624203821656</v>
       </c>
       <c r="O476" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P476" t="n">
-        <v>0.111600566572239</v>
+        <v>0.1127954706298659</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
@@ -35879,10 +35879,10 @@
         <v>8</v>
       </c>
       <c r="G477" t="n">
-        <v>0.8364022662889519</v>
+        <v>0.8365180467091295</v>
       </c>
       <c r="H477" t="n">
-        <v>8.458881019830029</v>
+        <v>8.459341825902335</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -35901,16 +35901,16 @@
         <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2588810198300298</v>
+        <v>0.2593418259023359</v>
       </c>
       <c r="N477" t="n">
-        <v>0.2588810198300298</v>
+        <v>0.2593418259023359</v>
       </c>
       <c r="O477" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P477" t="n">
-        <v>0.153711048158641</v>
+        <v>0.1527176220806794</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -35950,10 +35950,10 @@
         <v>8</v>
       </c>
       <c r="G478" t="n">
-        <v>0.8371104815864022</v>
+        <v>0.8372257607926398</v>
       </c>
       <c r="H478" t="n">
-        <v>8.461699716713881</v>
+        <v>8.462158527954706</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -35972,16 +35972,16 @@
         <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>0.4116997167138798</v>
+        <v>0.4121585279547055</v>
       </c>
       <c r="N478" t="n">
-        <v>0.4116997167138798</v>
+        <v>0.4121585279547055</v>
       </c>
       <c r="O478" t="n">
         <v>-0.1499999999999986</v>
       </c>
       <c r="P478" t="n">
-        <v>0.002818696883851501</v>
+        <v>0.002816702052371056</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -36021,10 +36021,10 @@
         <v>8</v>
       </c>
       <c r="G479" t="n">
-        <v>0.8321529745042493</v>
+        <v>0.832271762208068</v>
       </c>
       <c r="H479" t="n">
-        <v>8.39779745042493</v>
+        <v>8.400870488322719</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -36043,16 +36043,16 @@
         <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>0.47779745042493</v>
+        <v>0.4808704883227186</v>
       </c>
       <c r="N479" t="n">
-        <v>0.47779745042493</v>
+        <v>0.4808704883227186</v>
       </c>
       <c r="O479" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P479" t="n">
-        <v>-0.06390226628895057</v>
+        <v>-0.0612880396319877</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -36092,10 +36092,10 @@
         <v>8</v>
       </c>
       <c r="G480" t="n">
-        <v>0.8194050991501416</v>
+        <v>0.8195329087048833</v>
       </c>
       <c r="H480" t="n">
-        <v>8.20369688385269</v>
+        <v>8.205222929936305</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -36114,16 +36114,16 @@
         <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0.4636968838526894</v>
+        <v>0.4652229299363047</v>
       </c>
       <c r="N480" t="n">
-        <v>0.4636968838526894</v>
+        <v>0.4652229299363047</v>
       </c>
       <c r="O480" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P480" t="n">
-        <v>-0.1941005665722404</v>
+        <v>-0.1956475583864137</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -36266,34 +36266,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.73</v>
+        <v>7.772</v>
       </c>
       <c r="G2" t="n">
-        <v>7.805</v>
+        <v>7.846</v>
       </c>
       <c r="H2" t="n">
-        <v>7.881</v>
+        <v>7.893</v>
       </c>
       <c r="I2" t="n">
-        <v>7.881</v>
+        <v>7.879</v>
       </c>
       <c r="J2" t="n">
-        <v>7.755</v>
+        <v>7.816</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.126</v>
+        <v>-0.063</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -36342,12 +36342,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -36357,19 +36357,19 @@
         <v>5.587</v>
       </c>
       <c r="G3" t="n">
-        <v>5.677</v>
+        <v>5.661</v>
       </c>
       <c r="H3" t="n">
-        <v>5.84</v>
+        <v>5.781</v>
       </c>
       <c r="I3" t="n">
-        <v>5.84</v>
+        <v>5.781</v>
       </c>
       <c r="J3" t="n">
         <v>5.588</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.252</v>
+        <v>-0.193</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -36385,16 +36385,16 @@
         <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>0.489</v>
+        <v>0.49</v>
       </c>
       <c r="P3" t="n">
         <v>0.338</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="R3" t="n">
-        <v>0.57</v>
+        <v>0.569</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -36418,34 +36418,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.205</v>
+        <v>4.333</v>
       </c>
       <c r="G4" t="n">
-        <v>4.425</v>
+        <v>4.513</v>
       </c>
       <c r="H4" t="n">
-        <v>4.664</v>
+        <v>4.675</v>
       </c>
       <c r="I4" t="n">
-        <v>4.664</v>
+        <v>4.587</v>
       </c>
       <c r="J4" t="n">
-        <v>4.454</v>
+        <v>4.489</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.21</v>
+        <v>-0.098</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -36494,34 +36494,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.779</v>
+        <v>10.778</v>
       </c>
       <c r="G5" t="n">
-        <v>11.398</v>
+        <v>11.546</v>
       </c>
       <c r="H5" t="n">
-        <v>11.859</v>
+        <v>12.114</v>
       </c>
       <c r="I5" t="n">
-        <v>10.979</v>
+        <v>10.778</v>
       </c>
       <c r="J5" t="n">
-        <v>11.856</v>
+        <v>12.103</v>
       </c>
       <c r="K5" t="n">
-        <v>0.877</v>
+        <v>1.325</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -36537,16 +36537,16 @@
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>4.211</v>
+        <v>4.212</v>
       </c>
       <c r="P5" t="n">
-        <v>3.915</v>
+        <v>3.916</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.915</v>
+        <v>3.916</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.725</v>
+        <v>-1.726</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -36570,34 +36570,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>53.884</v>
+        <v>54.626</v>
       </c>
       <c r="G6" t="n">
-        <v>64.67400000000001</v>
+        <v>87.224</v>
       </c>
       <c r="H6" t="n">
-        <v>110.847</v>
+        <v>112.962</v>
       </c>
       <c r="I6" t="n">
-        <v>58.659</v>
+        <v>58.132</v>
       </c>
       <c r="J6" t="n">
-        <v>82.191</v>
+        <v>110.301</v>
       </c>
       <c r="K6" t="n">
-        <v>23.531</v>
+        <v>52.169</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -36613,13 +36613,13 @@
         <v>13</v>
       </c>
       <c r="O6" t="n">
-        <v>92.01300000000001</v>
+        <v>92.014</v>
       </c>
       <c r="P6" t="n">
-        <v>88.684</v>
+        <v>88.685</v>
       </c>
       <c r="Q6" t="n">
-        <v>88.684</v>
+        <v>88.685</v>
       </c>
       <c r="R6" t="n">
         <v>-3.322</v>
@@ -36646,34 +36646,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.735</v>
+        <v>7.733</v>
       </c>
       <c r="G7" t="n">
-        <v>7.988</v>
+        <v>7.944</v>
       </c>
       <c r="H7" t="n">
-        <v>8.202</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.202</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>7.736</v>
+        <v>7.762</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.466</v>
+        <v>-0.425</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -36722,34 +36722,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.2</v>
+        <v>6.164</v>
       </c>
       <c r="G8" t="n">
-        <v>6.986</v>
+        <v>6.857</v>
       </c>
       <c r="H8" t="n">
-        <v>7.469</v>
+        <v>7.36</v>
       </c>
       <c r="I8" t="n">
-        <v>7.469</v>
+        <v>7.36</v>
       </c>
       <c r="J8" t="n">
-        <v>6.203</v>
+        <v>6.165</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.266</v>
+        <v>-1.195</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -36768,13 +36768,13 @@
         <v>0.476</v>
       </c>
       <c r="P8" t="n">
-        <v>0.395</v>
+        <v>0.396</v>
       </c>
       <c r="Q8" t="n">
         <v>0.395</v>
       </c>
       <c r="R8" t="n">
-        <v>0.827</v>
+        <v>0.828</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -36798,38 +36798,38 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.025</v>
+        <v>5.035</v>
       </c>
       <c r="G9" t="n">
-        <v>5.325</v>
+        <v>5.326</v>
       </c>
       <c r="H9" t="n">
-        <v>5.61</v>
+        <v>5.611</v>
       </c>
       <c r="I9" t="n">
-        <v>5.133</v>
+        <v>5.341</v>
       </c>
       <c r="J9" t="n">
-        <v>5.103</v>
+        <v>5.159</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.03</v>
+        <v>-0.182</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -36874,34 +36874,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.404</v>
+        <v>5.367</v>
       </c>
       <c r="G10" t="n">
-        <v>5.439</v>
+        <v>5.422</v>
       </c>
       <c r="H10" t="n">
-        <v>5.52</v>
+        <v>5.475</v>
       </c>
       <c r="I10" t="n">
-        <v>5.52</v>
+        <v>5.475</v>
       </c>
       <c r="J10" t="n">
-        <v>5.427</v>
+        <v>5.368</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.093</v>
+        <v>-0.107</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>1.823</v>
+        <v>1.822</v>
       </c>
       <c r="P10" t="n">
         <v>1.788</v>
@@ -36950,38 +36950,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.872</v>
+        <v>3.958</v>
       </c>
       <c r="G11" t="n">
-        <v>3.627</v>
+        <v>4.804</v>
       </c>
       <c r="H11" t="n">
-        <v>4.261</v>
+        <v>7.284</v>
       </c>
       <c r="I11" t="n">
-        <v>4.261</v>
+        <v>3.958</v>
       </c>
       <c r="J11" t="n">
-        <v>3.453</v>
+        <v>5.372</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8080000000000001</v>
+        <v>1.414</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -37026,34 +37026,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.024</v>
+        <v>6.012</v>
       </c>
       <c r="G12" t="n">
-        <v>6.103</v>
+        <v>6.077</v>
       </c>
       <c r="H12" t="n">
-        <v>6.237</v>
+        <v>6.153</v>
       </c>
       <c r="I12" t="n">
-        <v>6.237</v>
+        <v>6.153</v>
       </c>
       <c r="J12" t="n">
-        <v>6.025</v>
+        <v>6.013</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.212</v>
+        <v>-0.14</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -37069,16 +37069,16 @@
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="P12" t="n">
         <v>0.372</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.24</v>
+        <v>-0.239</v>
       </c>
       <c r="R12" t="n">
-        <v>0.395</v>
+        <v>0.396</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -37102,34 +37102,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.577999999999999</v>
+        <v>9.632999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>9.861000000000001</v>
+        <v>9.882</v>
       </c>
       <c r="H13" t="n">
-        <v>10.17</v>
+        <v>10.114</v>
       </c>
       <c r="I13" t="n">
-        <v>10.17</v>
+        <v>10.114</v>
       </c>
       <c r="J13" t="n">
-        <v>9.631</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.539</v>
+        <v>-0.379</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -37178,34 +37178,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.741</v>
+        <v>5.672</v>
       </c>
       <c r="G14" t="n">
-        <v>5.851</v>
+        <v>5.828</v>
       </c>
       <c r="H14" t="n">
-        <v>5.943</v>
+        <v>5.906</v>
       </c>
       <c r="I14" t="n">
-        <v>5.943</v>
+        <v>5.881</v>
       </c>
       <c r="J14" t="n">
-        <v>5.742</v>
+        <v>5.677</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.201</v>
+        <v>-0.204</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>0.109</v>
       </c>
       <c r="R14" t="n">
-        <v>0.739</v>
+        <v>0.738</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -37254,38 +37254,38 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.532</v>
+        <v>6.549</v>
       </c>
       <c r="G15" t="n">
-        <v>6.575</v>
+        <v>6.577</v>
       </c>
       <c r="H15" t="n">
-        <v>6.596</v>
+        <v>6.591</v>
       </c>
       <c r="I15" t="n">
-        <v>6.596</v>
+        <v>6.591</v>
       </c>
       <c r="J15" t="n">
-        <v>6.534</v>
+        <v>6.559</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.063</v>
+        <v>-0.032</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -37297,16 +37297,16 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>1.626</v>
+        <v>1.625</v>
       </c>
       <c r="P15" t="n">
-        <v>1.506</v>
+        <v>1.505</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.506</v>
+        <v>-1.505</v>
       </c>
       <c r="R15" t="n">
-        <v>0.284</v>
+        <v>0.283</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -37330,34 +37330,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.058</v>
+        <v>5.174</v>
       </c>
       <c r="G16" t="n">
-        <v>4.848</v>
+        <v>6.059</v>
       </c>
       <c r="H16" t="n">
-        <v>6.288</v>
+        <v>7.22</v>
       </c>
       <c r="I16" t="n">
-        <v>5.155</v>
+        <v>5.506</v>
       </c>
       <c r="J16" t="n">
-        <v>5.648</v>
+        <v>6.289</v>
       </c>
       <c r="K16" t="n">
-        <v>0.493</v>
+        <v>0.783</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -37376,10 +37376,10 @@
         <v>1.726</v>
       </c>
       <c r="P16" t="n">
-        <v>1.538</v>
+        <v>1.539</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.538</v>
+        <v>1.539</v>
       </c>
       <c r="R16" t="n">
         <v>0.23</v>
@@ -37406,34 +37406,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.934</v>
+        <v>3.949</v>
       </c>
       <c r="G17" t="n">
-        <v>4.411</v>
+        <v>4.369</v>
       </c>
       <c r="H17" t="n">
-        <v>4.88</v>
+        <v>4.82</v>
       </c>
       <c r="I17" t="n">
-        <v>4.88</v>
+        <v>4.82</v>
       </c>
       <c r="J17" t="n">
-        <v>3.978</v>
+        <v>3.965</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.901</v>
+        <v>-0.855</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -37482,34 +37482,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.565</v>
+        <v>2.558</v>
       </c>
       <c r="G18" t="n">
-        <v>2.665</v>
+        <v>2.635</v>
       </c>
       <c r="H18" t="n">
-        <v>2.881</v>
+        <v>2.808</v>
       </c>
       <c r="I18" t="n">
-        <v>2.881</v>
+        <v>2.808</v>
       </c>
       <c r="J18" t="n">
-        <v>2.568</v>
+        <v>2.559</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.313</v>
+        <v>-0.249</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -37525,16 +37525,16 @@
         <v>14</v>
       </c>
       <c r="O18" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="P18" t="n">
         <v>0.371</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.158</v>
+        <v>-0.157</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.11</v>
+        <v>-0.109</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -37558,34 +37558,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.767</v>
+        <v>5.806</v>
       </c>
       <c r="G19" t="n">
-        <v>5.909</v>
+        <v>5.907</v>
       </c>
       <c r="H19" t="n">
-        <v>6.207</v>
+        <v>6.099</v>
       </c>
       <c r="I19" t="n">
-        <v>6.207</v>
+        <v>6.099</v>
       </c>
       <c r="J19" t="n">
-        <v>5.782</v>
+        <v>5.834</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.425</v>
+        <v>-0.265</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -486,7 +486,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>299970</v>
+        <v>299988</v>
       </c>
       <c r="E2" t="n">
         <v>151106</v>
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -683,13 +683,13 @@
         <v>9.765000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>7.754</v>
+        <v>7.755</v>
       </c>
       <c r="J2" t="n">
         <v>-1.52</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.011</v>
+        <v>-2.01</v>
       </c>
       <c r="L2" t="n">
         <v>0.395</v>
@@ -698,13 +698,13 @@
         <v>0.396</v>
       </c>
       <c r="N2" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="O2" t="n">
         <v>0.866</v>
       </c>
       <c r="P2" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="Q2" t="n">
         <v>0.828</v>
@@ -765,19 +765,19 @@
         <v>7.883</v>
       </c>
       <c r="I3" t="n">
-        <v>5.827</v>
+        <v>5.829</v>
       </c>
       <c r="J3" t="n">
         <v>-2.472</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.055</v>
+        <v>-2.054</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.788</v>
+        <v>-1.787</v>
       </c>
       <c r="M3" t="n">
-        <v>1.788</v>
+        <v>1.787</v>
       </c>
       <c r="N3" t="n">
         <v>1.822</v>
@@ -786,7 +786,7 @@
         <v>0.89</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.605</v>
+        <v>-4.603</v>
       </c>
       <c r="Q3" t="n">
         <v>0.758</v>
@@ -853,7 +853,7 @@
         <v>-3.405</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.848</v>
+        <v>-2.847</v>
       </c>
       <c r="L4" t="n">
         <v>-0.075</v>
@@ -929,13 +929,13 @@
         <v>7.178</v>
       </c>
       <c r="I5" t="n">
-        <v>5.968</v>
+        <v>5.969</v>
       </c>
       <c r="J5" t="n">
         <v>-2.275</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.21</v>
+        <v>-1.209</v>
       </c>
       <c r="L5" t="n">
         <v>0.317</v>
@@ -950,7 +950,7 @@
         <v>0.931</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="Q5" t="n">
         <v>0.569</v>
@@ -1017,7 +1017,7 @@
         <v>-2.07</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.239</v>
+        <v>-2.238</v>
       </c>
       <c r="L6" t="n">
         <v>0.109</v>
@@ -1093,16 +1093,16 @@
         <v>9.374000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.205</v>
+        <v>8.207000000000001</v>
       </c>
       <c r="J7" t="n">
         <v>-2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.169</v>
+        <v>-1.168</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.667</v>
+        <v>-0.666</v>
       </c>
       <c r="M7" t="n">
         <v>0.778</v>
@@ -1111,13 +1111,13 @@
         <v>0.842</v>
       </c>
       <c r="O7" t="n">
-        <v>0.711</v>
+        <v>0.71</v>
       </c>
       <c r="P7" t="n">
         <v>-0.355</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.507</v>
+        <v>0.506</v>
       </c>
       <c r="R7" t="n">
         <v>20.69</v>
@@ -1175,19 +1175,19 @@
         <v>9.863</v>
       </c>
       <c r="I8" t="n">
-        <v>7.935</v>
+        <v>7.936</v>
       </c>
       <c r="J8" t="n">
         <v>-2.008</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.928</v>
+        <v>-1.927</v>
       </c>
       <c r="L8" t="n">
-        <v>5.81</v>
+        <v>5.811</v>
       </c>
       <c r="M8" t="n">
-        <v>5.81</v>
+        <v>5.811</v>
       </c>
       <c r="N8" t="n">
         <v>5.83</v>
@@ -1196,10 +1196,10 @@
         <v>0.831</v>
       </c>
       <c r="P8" t="n">
-        <v>-45.924</v>
+        <v>-45.929</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.023</v>
+        <v>-1.024</v>
       </c>
       <c r="R8" t="n">
         <v>41.379</v>
@@ -1278,7 +1278,7 @@
         <v>-0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.666</v>
+        <v>-0.667</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.042</v>
@@ -1339,13 +1339,13 @@
         <v>11.017</v>
       </c>
       <c r="I10" t="n">
-        <v>11.49</v>
+        <v>11.493</v>
       </c>
       <c r="J10" t="n">
         <v>-1.39</v>
       </c>
       <c r="K10" t="n">
-        <v>0.473</v>
+        <v>0.476</v>
       </c>
       <c r="L10" t="n">
         <v>3.916</v>
@@ -1360,10 +1360,10 @@
         <v>-0.491</v>
       </c>
       <c r="P10" t="n">
-        <v>-105.463</v>
+        <v>-105.49</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.726</v>
+        <v>-1.727</v>
       </c>
       <c r="R10" t="n">
         <v>41.379</v>
@@ -1418,31 +1418,31 @@
         <v>5.32</v>
       </c>
       <c r="H11" t="n">
-        <v>112.887</v>
+        <v>112.889</v>
       </c>
       <c r="I11" t="n">
-        <v>108.398</v>
+        <v>108.401</v>
       </c>
       <c r="J11" t="n">
         <v>-1.68</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.489</v>
+        <v>-4.488</v>
       </c>
       <c r="L11" t="n">
-        <v>88.685</v>
+        <v>88.687</v>
       </c>
       <c r="M11" t="n">
-        <v>88.685</v>
+        <v>88.687</v>
       </c>
       <c r="N11" t="n">
-        <v>92.014</v>
+        <v>92.01600000000001</v>
       </c>
       <c r="O11" t="n">
         <v>-0.357</v>
       </c>
       <c r="P11" t="n">
-        <v>-13.682</v>
+        <v>-13.683</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.322</v>
@@ -1585,31 +1585,31 @@
         <v>5.956</v>
       </c>
       <c r="I13" t="n">
-        <v>5.124</v>
+        <v>5.123</v>
       </c>
       <c r="J13" t="n">
         <v>-0.6919999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.831</v>
+        <v>-0.833</v>
       </c>
       <c r="L13" t="n">
         <v>0.261</v>
       </c>
       <c r="M13" t="n">
-        <v>0.424</v>
+        <v>0.423</v>
       </c>
       <c r="N13" t="n">
-        <v>0.514</v>
+        <v>0.513</v>
       </c>
       <c r="O13" t="n">
-        <v>0.438</v>
+        <v>0.44</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.089</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.215</v>
+        <v>0.216</v>
       </c>
       <c r="R13" t="n">
         <v>20.69</v>
@@ -1667,13 +1667,13 @@
         <v>7.097</v>
       </c>
       <c r="I14" t="n">
-        <v>5.205</v>
+        <v>5.206</v>
       </c>
       <c r="J14" t="n">
         <v>-2.422</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.892</v>
+        <v>-1.891</v>
       </c>
       <c r="L14" t="n">
         <v>2.035</v>
@@ -1688,7 +1688,7 @@
         <v>0.615</v>
       </c>
       <c r="P14" t="n">
-        <v>-10.09</v>
+        <v>-10.092</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.553</v>
@@ -1749,19 +1749,19 @@
         <v>8.144</v>
       </c>
       <c r="I15" t="n">
-        <v>6.353</v>
+        <v>6.355</v>
       </c>
       <c r="J15" t="n">
         <v>-1.525</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.79</v>
+        <v>-1.789</v>
       </c>
       <c r="L15" t="n">
         <v>-0.239</v>
       </c>
       <c r="M15" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="N15" t="n">
         <v>0.483</v>
@@ -1770,10 +1770,10 @@
         <v>0.8169999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2</v>
+        <v>-0.198</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.396</v>
+        <v>0.397</v>
       </c>
       <c r="R15" t="n">
         <v>41.379</v>
@@ -1913,7 +1913,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>6.679</v>
+        <v>6.68</v>
       </c>
       <c r="J17" t="n">
         <v>-2.425</v>
@@ -1931,10 +1931,10 @@
         <v>1.625</v>
       </c>
       <c r="O17" t="n">
-        <v>0.603</v>
+        <v>0.602</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.681</v>
+        <v>-3.68</v>
       </c>
       <c r="Q17" t="n">
         <v>0.283</v>
@@ -1995,13 +1995,13 @@
         <v>7.154</v>
       </c>
       <c r="I18" t="n">
-        <v>6.293</v>
+        <v>6.294</v>
       </c>
       <c r="J18" t="n">
         <v>-1.55</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.862</v>
+        <v>-0.861</v>
       </c>
       <c r="L18" t="n">
         <v>1.539</v>
@@ -2010,13 +2010,13 @@
         <v>1.539</v>
       </c>
       <c r="N18" t="n">
-        <v>1.726</v>
+        <v>1.727</v>
       </c>
       <c r="O18" t="n">
         <v>0.61</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.629</v>
+        <v>-6.63</v>
       </c>
       <c r="Q18" t="n">
         <v>0.23</v>
@@ -2074,19 +2074,19 @@
         <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.493</v>
+        <v>3.496</v>
       </c>
       <c r="I19" t="n">
-        <v>3.108</v>
+        <v>3.109</v>
       </c>
       <c r="J19" t="n">
         <v>-1.34</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.385</v>
+        <v>-0.386</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.157</v>
+        <v>-0.156</v>
       </c>
       <c r="M19" t="n">
         <v>0.371</v>
@@ -2095,13 +2095,13 @@
         <v>0.486</v>
       </c>
       <c r="O19" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.416</v>
+        <v>-0.413</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.109</v>
+        <v>-0.108</v>
       </c>
       <c r="R19" t="n">
         <v>46.154</v>
@@ -3392,10 +3392,10 @@
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8535031847133758</v>
+        <v>0.8536067892503536</v>
       </c>
       <c r="H18" t="n">
-        <v>8.170605095541401</v>
+        <v>8.170933521923621</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>5.715605095541401</v>
+        <v>5.71593352192362</v>
       </c>
       <c r="N18" t="n">
-        <v>5.715605095541401</v>
+        <v>5.71593352192362</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1374999999999997</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7294229352925168</v>
+        <v>-0.7290945089102969</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8506723283793347</v>
+        <v>0.8507779349363508</v>
       </c>
       <c r="H19" t="n">
-        <v>8.157473460721869</v>
+        <v>8.157724540311174</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3485,16 +3485,16 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.744973460721869</v>
+        <v>5.745224540311174</v>
       </c>
       <c r="N19" t="n">
-        <v>5.744973460721869</v>
+        <v>5.745224540311174</v>
       </c>
       <c r="O19" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.01313163481953161</v>
+        <v>-0.01320898161244699</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8464260438782731</v>
+        <v>0.8465346534653465</v>
       </c>
       <c r="H20" t="n">
-        <v>8.132926397735316</v>
+        <v>8.133787128712871</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3556,16 +3556,16 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>5.732926397735316</v>
+        <v>5.733787128712871</v>
       </c>
       <c r="N20" t="n">
-        <v>5.732926397735316</v>
+        <v>5.733787128712871</v>
       </c>
       <c r="O20" t="n">
         <v>-0.01250000000000018</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.02454706298655296</v>
+        <v>-0.02393741159830221</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8435951875442321</v>
+        <v>0.8437057991513437</v>
       </c>
       <c r="H21" t="n">
-        <v>8.119196744515214</v>
+        <v>8.119547383309758</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>5.949196744515215</v>
+        <v>5.949547383309758</v>
       </c>
       <c r="N21" t="n">
-        <v>5.949196744515215</v>
+        <v>5.949547383309758</v>
       </c>
       <c r="O21" t="n">
         <v>-0.23</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.01372965322010167</v>
+        <v>-0.01423974540311335</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8386411889596603</v>
+        <v>0.8387553041018387</v>
       </c>
       <c r="H22" t="n">
-        <v>8.096985138004246</v>
+        <v>8.097708628005657</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3698,16 +3698,16 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>6.116985138004246</v>
+        <v>6.117708628005657</v>
       </c>
       <c r="N22" t="n">
-        <v>6.116985138004246</v>
+        <v>6.117708628005657</v>
       </c>
       <c r="O22" t="n">
         <v>-0.1899999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.0222116065109681</v>
+        <v>-0.02183875530410084</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8336871903750884</v>
+        <v>0.8338048090523338</v>
       </c>
       <c r="H23" t="n">
-        <v>8.061153573956121</v>
+        <v>8.062644978783592</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3769,16 +3769,16 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>6.011153573956121</v>
+        <v>6.012644978783592</v>
       </c>
       <c r="N23" t="n">
-        <v>6.011153573956121</v>
+        <v>6.012644978783592</v>
       </c>
       <c r="O23" t="n">
         <v>0.06999999999999984</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.03583156404812549</v>
+        <v>-0.03506364922206551</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8273177636234961</v>
+        <v>0.8274398868458275</v>
       </c>
       <c r="H24" t="n">
         <v>8.030000000000001</v>
@@ -3849,7 +3849,7 @@
         <v>0.1700000000000004</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.03115357395611973</v>
+        <v>-0.03264497878359052</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8223637650389243</v>
+        <v>0.8224893917963225</v>
       </c>
       <c r="H25" t="n">
-        <v>8.013446567586694</v>
+        <v>8.013645685997171</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3911,16 +3911,16 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>5.663446567586695</v>
+        <v>5.663645685997171</v>
       </c>
       <c r="N25" t="n">
-        <v>5.663446567586695</v>
+        <v>5.663645685997171</v>
       </c>
       <c r="O25" t="n">
         <v>0.1299999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01655343241330698</v>
+        <v>-0.01635431400283061</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3960,10 +3960,10 @@
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8195329087048833</v>
+        <v>0.8196605374823197</v>
       </c>
       <c r="H26" t="n">
-        <v>8.001878980891719</v>
+        <v>8.00248585572843</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3982,16 +3982,16 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>5.70187898089172</v>
+        <v>5.702485855728431</v>
       </c>
       <c r="N26" t="n">
-        <v>5.70187898089172</v>
+        <v>5.702485855728431</v>
       </c>
       <c r="O26" t="n">
         <v>-0.05000000000000027</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.01156758669497471</v>
+        <v>-0.01115983026874012</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8159943382873319</v>
+        <v>0.8161244695898161</v>
       </c>
       <c r="H27" t="n">
-        <v>7.975957183297948</v>
+        <v>7.977400990099009</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4053,16 +4053,16 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>5.745957183297948</v>
+        <v>5.74740099009901</v>
       </c>
       <c r="N27" t="n">
-        <v>5.745957183297948</v>
+        <v>5.74740099009901</v>
       </c>
       <c r="O27" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.02592179759377178</v>
+        <v>-0.02508486562942114</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8117480537862704</v>
+        <v>0.8118811881188119</v>
       </c>
       <c r="H28" t="n">
-        <v>7.948241330502477</v>
+        <v>7.948663366336635</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>5.888241330502478</v>
+        <v>5.888663366336635</v>
       </c>
       <c r="N28" t="n">
-        <v>5.888241330502478</v>
+        <v>5.888663366336635</v>
       </c>
       <c r="O28" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.0277158527954704</v>
+        <v>-0.02873762376237465</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8124557678697806</v>
+        <v>0.8125884016973126</v>
       </c>
       <c r="H29" t="n">
-        <v>7.951211960368012</v>
+        <v>7.952263083451203</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4195,16 +4195,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>6.001211960368011</v>
+        <v>6.002263083451203</v>
       </c>
       <c r="N29" t="n">
-        <v>6.001211960368011</v>
+        <v>6.002263083451203</v>
       </c>
       <c r="O29" t="n">
         <v>-0.1100000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>0.002970629865534313</v>
+        <v>0.00359971711456808</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8131634819532909</v>
+        <v>0.8132956152758133</v>
       </c>
       <c r="H30" t="n">
-        <v>7.956820594479829</v>
+        <v>7.957867751060819</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4266,16 +4266,16 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.256820594479829</v>
+        <v>5.257867751060819</v>
       </c>
       <c r="N30" t="n">
-        <v>5.256820594479829</v>
+        <v>5.257867751060819</v>
       </c>
       <c r="O30" t="n">
         <v>0.7500000000000002</v>
       </c>
       <c r="P30" t="n">
-        <v>0.005608634111817778</v>
+        <v>0.005604667609616421</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8096249115357396</v>
+        <v>0.8097595473833098</v>
       </c>
       <c r="H31" t="n">
-        <v>7.934532908704884</v>
+        <v>7.935813295615277</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4337,16 +4337,16 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.134532908704884</v>
+        <v>5.135813295615277</v>
       </c>
       <c r="N31" t="n">
-        <v>5.134532908704884</v>
+        <v>5.135813295615277</v>
       </c>
       <c r="O31" t="n">
         <v>0.09999999999999964</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.02228768577494566</v>
+        <v>-0.02205445544554241</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6489738145789101</v>
+        <v>0.6492220650636492</v>
       </c>
       <c r="H48" t="n">
-        <v>6.159169984076433</v>
+        <v>6.159264939886846</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5538,16 +5538,16 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1283300159235665</v>
+        <v>-0.1282350601131537</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1283300159235665</v>
+        <v>0.1282350601131537</v>
       </c>
       <c r="O48" t="n">
         <v>-0.09250000000000114</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.6247192941295934</v>
+        <v>-0.6246243383191805</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6426043878273178</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="H49" t="n">
-        <v>6.146369426751592</v>
+        <v>6.147142857142858</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5609,16 +5609,16 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.02363057324840767</v>
+        <v>-0.02285714285714224</v>
       </c>
       <c r="N49" t="n">
-        <v>0.02363057324840767</v>
+        <v>0.02285714285714224</v>
       </c>
       <c r="O49" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.01280055732484087</v>
+        <v>-0.01212208274398829</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5658,10 +5658,10 @@
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>0.6348195329087049</v>
+        <v>0.635077793493635</v>
       </c>
       <c r="H50" t="n">
-        <v>6.12403821656051</v>
+        <v>6.124670438472418</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5680,16 +5680,16 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.03403821656050976</v>
+        <v>0.03467043847241857</v>
       </c>
       <c r="N50" t="n">
-        <v>0.03403821656050976</v>
+        <v>0.03467043847241857</v>
       </c>
       <c r="O50" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.02233121019108264</v>
+        <v>-0.02247241867043925</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5729,10 +5729,10 @@
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6334041047416844</v>
+        <v>0.6336633663366337</v>
       </c>
       <c r="H51" t="n">
-        <v>6.120573248407643</v>
+        <v>6.121207920792079</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5751,16 +5751,16 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2605732484076428</v>
+        <v>0.2612079207920788</v>
       </c>
       <c r="N51" t="n">
-        <v>0.2605732484076428</v>
+        <v>0.2612079207920788</v>
       </c>
       <c r="O51" t="n">
         <v>-0.2299999999999995</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.003464968152866454</v>
+        <v>-0.003462517680339339</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>0.6447275300778486</v>
+        <v>0.6449787835926449</v>
       </c>
       <c r="H52" t="n">
-        <v>6.157545780254778</v>
+        <v>6.157641884724187</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5822,16 +5822,16 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4975457802547778</v>
+        <v>0.497641884724187</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4975457802547778</v>
+        <v>0.497641884724187</v>
       </c>
       <c r="O52" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P52" t="n">
-        <v>0.03697253184713478</v>
+        <v>0.03643396393210807</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6525123849964615</v>
+        <v>0.6527581329561527</v>
       </c>
       <c r="H53" t="n">
-        <v>6.166687898089172</v>
+        <v>6.167439886845827</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5893,16 +5893,16 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5366878980891725</v>
+        <v>0.537439886845827</v>
       </c>
       <c r="N53" t="n">
-        <v>0.5366878980891725</v>
+        <v>0.537439886845827</v>
       </c>
       <c r="O53" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P53" t="n">
-        <v>0.009142117834394448</v>
+        <v>0.009798002121639726</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6624203821656051</v>
+        <v>0.6626591230551626</v>
       </c>
       <c r="H54" t="n">
-        <v>6.206008492569002</v>
+        <v>6.206982555398397</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5964,16 +5964,16 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6160084925690024</v>
+        <v>0.6169825553983967</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6160084925690024</v>
+        <v>0.6169825553983967</v>
       </c>
       <c r="O54" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P54" t="n">
-        <v>0.03932059447982983</v>
+        <v>0.03954266855256972</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6687898089171974</v>
+        <v>0.669024045261669</v>
       </c>
       <c r="H55" t="n">
-        <v>6.218248407643312</v>
+        <v>6.218606789250353</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6035,16 +6035,16 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7682484076433118</v>
+        <v>0.7686067892503532</v>
       </c>
       <c r="N55" t="n">
-        <v>0.7682484076433118</v>
+        <v>0.7686067892503532</v>
       </c>
       <c r="O55" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01223991507430977</v>
+        <v>0.01162423385195677</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6652512384996462</v>
+        <v>0.6654879773691655</v>
       </c>
       <c r="H56" t="n">
-        <v>6.212834394904458</v>
+        <v>6.213196605374823</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6106,16 +6106,16 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8128343949044581</v>
+        <v>0.8131966053748227</v>
       </c>
       <c r="N56" t="n">
-        <v>0.8128343949044581</v>
+        <v>0.8131966053748227</v>
       </c>
       <c r="O56" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.005414012738853557</v>
+        <v>-0.005410183875530272</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
         <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6539278131634819</v>
+        <v>0.6541725601131542</v>
       </c>
       <c r="H57" t="n">
-        <v>6.172038216560509</v>
+        <v>6.173536067892504</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8020382165605087</v>
+        <v>0.8035360678925034</v>
       </c>
       <c r="N57" t="n">
-        <v>0.8020382165605087</v>
+        <v>0.8035360678925034</v>
       </c>
       <c r="O57" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.04079617834394966</v>
+        <v>-0.03966053748231957</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6226,10 +6226,10 @@
         <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6383581033262562</v>
+        <v>0.6386138613861386</v>
       </c>
       <c r="H58" t="n">
-        <v>6.135583864118896</v>
+        <v>6.136105610561056</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6248,16 +6248,16 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8055838641188959</v>
+        <v>0.8061056105610556</v>
       </c>
       <c r="N58" t="n">
-        <v>0.8055838641188959</v>
+        <v>0.8061056105610556</v>
       </c>
       <c r="O58" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.03645435244161277</v>
+        <v>-0.0374304573314479</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6297,10 +6297,10 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6199575371549894</v>
+        <v>0.6202263083451203</v>
       </c>
       <c r="H59" t="n">
-        <v>6.076093418259023</v>
+        <v>6.077190004714757</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6319,16 +6319,16 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9260934182590228</v>
+        <v>0.927190004714757</v>
       </c>
       <c r="N59" t="n">
-        <v>0.9260934182590228</v>
+        <v>0.927190004714757</v>
       </c>
       <c r="O59" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.05949044585987284</v>
+        <v>-0.05891560584629829</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6058032554847842</v>
+        <v>0.6060820367751061</v>
       </c>
       <c r="H60" t="n">
-        <v>6.02875796178344</v>
+        <v>6.029611032531825</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6390,16 +6390,16 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1.05875796178344</v>
+        <v>1.059611032531826</v>
       </c>
       <c r="N60" t="n">
-        <v>1.05875796178344</v>
+        <v>1.059611032531826</v>
       </c>
       <c r="O60" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.04733545647558302</v>
+        <v>-0.04757897218293206</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6439,10 +6439,10 @@
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5909412597310687</v>
+        <v>0.5912305516265912</v>
       </c>
       <c r="H61" t="n">
-        <v>5.967707006369427</v>
+        <v>5.968887317303158</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6461,16 +6461,16 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1.137707006369427</v>
+        <v>1.138887317303158</v>
       </c>
       <c r="N61" t="n">
-        <v>1.137707006369427</v>
+        <v>1.138887317303158</v>
       </c>
       <c r="O61" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.06105095541401351</v>
+        <v>-0.06072371522866682</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -7640,10 +7640,10 @@
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>0.897381457891012</v>
+        <v>0.8974540311173974</v>
       </c>
       <c r="H78" t="n">
-        <v>5.87757254069356</v>
+        <v>5.878415841584158</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7662,16 +7662,16 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1.19007254069356</v>
+        <v>1.190915841584158</v>
       </c>
       <c r="N78" t="n">
-        <v>1.19007254069356</v>
+        <v>1.190915841584158</v>
       </c>
       <c r="O78" t="n">
         <v>0.2725</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.06425296736530495</v>
+        <v>-0.06340966647470658</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8683651804670913</v>
+        <v>0.8684582743988685</v>
       </c>
       <c r="H79" t="n">
-        <v>5.690403397027602</v>
+        <v>5.691485148514852</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7733,16 +7733,16 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>1.277903397027602</v>
+        <v>1.278985148514852</v>
       </c>
       <c r="N79" t="n">
-        <v>1.277903397027602</v>
+        <v>1.278985148514852</v>
       </c>
       <c r="O79" t="n">
         <v>-0.2750000000000004</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.1871691436659582</v>
+        <v>-0.1869306930693062</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8259023354564756</v>
+        <v>0.826025459688826</v>
       </c>
       <c r="H80" t="n">
-        <v>5.413492569002123</v>
+        <v>5.414207920792079</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7804,16 +7804,16 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>0.763492569002123</v>
+        <v>0.7642079207920789</v>
       </c>
       <c r="N80" t="n">
-        <v>0.763492569002123</v>
+        <v>0.7642079207920789</v>
       </c>
       <c r="O80" t="n">
         <v>0.2375000000000007</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.2769108280254784</v>
+        <v>-0.2772772277227729</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7791932059447984</v>
+        <v>0.7793493635077794</v>
       </c>
       <c r="H81" t="n">
-        <v>5.152112526539279</v>
+        <v>5.153019801980198</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7875,16 +7875,16 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>0.4521125265392785</v>
+        <v>0.4530198019801981</v>
       </c>
       <c r="N81" t="n">
-        <v>0.4521125265392785</v>
+        <v>0.4530198019801981</v>
       </c>
       <c r="O81" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.2613800424628447</v>
+        <v>-0.261188118811881</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7331917905166313</v>
+        <v>0.7333804809052333</v>
       </c>
       <c r="H82" t="n">
-        <v>4.994844302901628</v>
+        <v>4.995940594059406</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7946,16 +7946,16 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5898443029016285</v>
+        <v>0.5909405940594068</v>
       </c>
       <c r="N82" t="n">
-        <v>0.5898443029016285</v>
+        <v>0.5909405940594068</v>
       </c>
       <c r="O82" t="n">
         <v>-0.2950000000000008</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.1572682236376508</v>
+        <v>-0.1570792079207921</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -7995,10 +7995,10 @@
         <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7070063694267515</v>
+        <v>0.7072135785007072</v>
       </c>
       <c r="H83" t="n">
-        <v>4.868471337579618</v>
+        <v>4.869273927392739</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8017,16 +8017,16 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>0.7709713375796188</v>
+        <v>0.77177392739274</v>
       </c>
       <c r="N83" t="n">
-        <v>0.7709713375796188</v>
+        <v>0.77177392739274</v>
       </c>
       <c r="O83" t="n">
         <v>-0.3075000000000001</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.1263729653220098</v>
+        <v>-0.1266666666666669</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -8066,10 +8066,10 @@
         <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>0.6751592356687898</v>
+        <v>0.6753889674681753</v>
       </c>
       <c r="H84" t="n">
-        <v>4.785050045495906</v>
+        <v>4.785431400282885</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8088,16 +8088,16 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>0.9350500454959056</v>
+        <v>0.935431400282885</v>
       </c>
       <c r="N84" t="n">
-        <v>0.9350500454959056</v>
+        <v>0.935431400282885</v>
       </c>
       <c r="O84" t="n">
         <v>-0.2474999999999992</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.0834212920837123</v>
+        <v>-0.08384252710985418</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>0.640481245576787</v>
+        <v>0.6407355021216408</v>
       </c>
       <c r="H85" t="n">
-        <v>4.687699339466856</v>
+        <v>4.687945544554456</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8159,16 +8159,16 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>0.907699339466856</v>
+        <v>0.907945544554456</v>
       </c>
       <c r="N85" t="n">
-        <v>0.907699339466856</v>
+        <v>0.907945544554456</v>
       </c>
       <c r="O85" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.09735070602904994</v>
+        <v>-0.09748585572842927</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6043878273177636</v>
+        <v>0.6039603960396039</v>
       </c>
       <c r="H86" t="n">
-        <v>4.550746638358103</v>
+        <v>4.549009900990098</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8230,16 +8230,16 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.2492533616418973</v>
+        <v>-0.2509900990099023</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2492533616418973</v>
+        <v>0.2509900990099023</v>
       </c>
       <c r="O86" t="n">
         <v>1.020000000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.1369527011087524</v>
+        <v>-0.1389356435643574</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -8279,10 +8279,10 @@
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>0.5973106864826611</v>
+        <v>0.5968882602545968</v>
       </c>
       <c r="H87" t="n">
-        <v>4.52018754423213</v>
+        <v>4.518960396039604</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8301,16 +8301,16 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.1798124557678706</v>
+        <v>-0.1810396039603965</v>
       </c>
       <c r="N87" t="n">
-        <v>0.1798124557678706</v>
+        <v>0.1810396039603965</v>
       </c>
       <c r="O87" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.03055909412597391</v>
+        <v>-0.03004950495049474</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -8350,10 +8350,10 @@
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6142958244869073</v>
+        <v>0.6138613861386139</v>
       </c>
       <c r="H88" t="n">
-        <v>4.572705826845954</v>
+        <v>4.571023102310231</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8372,16 +8372,16 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.6272941731540458</v>
+        <v>-0.6289768976897694</v>
       </c>
       <c r="N88" t="n">
-        <v>0.6272941731540458</v>
+        <v>0.6289768976897694</v>
       </c>
       <c r="O88" t="n">
         <v>0.5</v>
       </c>
       <c r="P88" t="n">
-        <v>0.05251828261382485</v>
+        <v>0.05206270627062715</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6581740976645435</v>
+        <v>0.6584158415841584</v>
       </c>
       <c r="H89" t="n">
-        <v>4.7219957537155</v>
+        <v>4.722698019801981</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8443,16 +8443,16 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.7780042462845005</v>
+        <v>-0.7773019801980192</v>
       </c>
       <c r="N89" t="n">
-        <v>0.7780042462845005</v>
+        <v>0.7773019801980192</v>
       </c>
       <c r="O89" t="n">
         <v>0.2999999999999998</v>
       </c>
       <c r="P89" t="n">
-        <v>0.1492899268695451</v>
+        <v>0.15167491749175</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8492,10 +8492,10 @@
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6815286624203821</v>
+        <v>0.6817538896746818</v>
       </c>
       <c r="H90" t="n">
-        <v>4.794920382165605</v>
+        <v>4.795247524752475</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8514,16 +8514,16 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-1.085079617834395</v>
+        <v>-1.084752475247525</v>
       </c>
       <c r="N90" t="n">
-        <v>1.085079617834395</v>
+        <v>1.084752475247525</v>
       </c>
       <c r="O90" t="n">
         <v>0.3799999999999999</v>
       </c>
       <c r="P90" t="n">
-        <v>0.07292462845010572</v>
+        <v>0.07254950495049428</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8563,10 +8563,10 @@
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6843595187544232</v>
+        <v>0.6845827439886846</v>
       </c>
       <c r="H91" t="n">
-        <v>4.7990322009908</v>
+        <v>4.799356435643564</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -8585,16 +8585,16 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.2209677990092</v>
+        <v>-0.2206435643564353</v>
       </c>
       <c r="N91" t="n">
-        <v>0.2209677990092</v>
+        <v>0.2206435643564353</v>
       </c>
       <c r="O91" t="n">
         <v>-0.8600000000000003</v>
       </c>
       <c r="P91" t="n">
-        <v>0.004111818825194291</v>
+        <v>0.004108910891089224</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -9764,10 +9764,10 @@
         <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8910120311394196</v>
+        <v>0.8910891089108911</v>
       </c>
       <c r="H108" t="n">
-        <v>12.38285562632696</v>
+        <v>12.3830198019802</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -9786,16 +9786,16 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>5.312855626326965</v>
+        <v>5.313019801980199</v>
       </c>
       <c r="N108" t="n">
-        <v>5.312855626326965</v>
+        <v>5.313019801980199</v>
       </c>
       <c r="O108" t="n">
         <v>-0.1250000000000009</v>
       </c>
       <c r="P108" t="n">
-        <v>4.413276088835726</v>
+        <v>4.41344026448896</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -9835,10 +9835,10 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>0.8867657466383581</v>
+        <v>0.8868458274398868</v>
       </c>
       <c r="H109" t="n">
-        <v>12.33692144373673</v>
+        <v>12.33879773691655</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -9857,16 +9857,16 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>5.466921443736729</v>
+        <v>5.468797736916547</v>
       </c>
       <c r="N109" t="n">
-        <v>5.466921443736729</v>
+        <v>5.468797736916547</v>
       </c>
       <c r="O109" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.0459341825902353</v>
+        <v>-0.04422206506365178</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -9906,10 +9906,10 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8846426043878273</v>
+        <v>0.8847241867043847</v>
       </c>
       <c r="H110" t="n">
-        <v>12.29036624203822</v>
+        <v>12.29088755304102</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -9928,16 +9928,16 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>5.550366242038216</v>
+        <v>5.550887553041019</v>
       </c>
       <c r="N110" t="n">
-        <v>5.550366242038216</v>
+        <v>5.550887553041019</v>
       </c>
       <c r="O110" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.04655520169851357</v>
+        <v>-0.04791018387552803</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -9977,10 +9977,10 @@
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>0.8825194621372965</v>
+        <v>0.8826025459688827</v>
       </c>
       <c r="H111" t="n">
-        <v>12.27574840764331</v>
+        <v>12.2770756718529</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -9999,16 +9999,16 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>5.675748407643312</v>
+        <v>5.677075671852901</v>
       </c>
       <c r="N111" t="n">
-        <v>5.675748407643312</v>
+        <v>5.677075671852901</v>
       </c>
       <c r="O111" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P111" t="n">
-        <v>-0.01461783439490461</v>
+        <v>-0.01381188118811849</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -10048,10 +10048,10 @@
         <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8761500353857041</v>
+        <v>0.8762376237623762</v>
       </c>
       <c r="H112" t="n">
-        <v>12.2223991507431</v>
+        <v>12.22277227722772</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10070,16 +10070,16 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>5.362399150743101</v>
+        <v>5.362772277227722</v>
       </c>
       <c r="N112" t="n">
-        <v>5.362399150743101</v>
+        <v>5.362772277227722</v>
       </c>
       <c r="O112" t="n">
         <v>0.2600000000000007</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.05334925690021031</v>
+        <v>-0.05430339462517786</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>0.867657466383581</v>
+        <v>0.8677510608203678</v>
       </c>
       <c r="H113" t="n">
-        <v>12.19061040339703</v>
+        <v>12.19080975954738</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -10141,16 +10141,16 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>5.210610403397027</v>
+        <v>5.210809759547383</v>
       </c>
       <c r="N113" t="n">
-        <v>5.210610403397027</v>
+        <v>5.210809759547383</v>
       </c>
       <c r="O113" t="n">
         <v>0.1200000000000001</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.03178874734607362</v>
+        <v>-0.03196251768033953</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -10190,10 +10190,10 @@
         <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8570417551309271</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="H114" t="n">
-        <v>12.11799363057325</v>
+        <v>12.11928571428571</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -10212,16 +10212,16 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>5.267993630573248</v>
+        <v>5.269285714285713</v>
       </c>
       <c r="N114" t="n">
-        <v>5.267993630573248</v>
+        <v>5.269285714285713</v>
       </c>
       <c r="O114" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P114" t="n">
-        <v>-0.0726167728237801</v>
+        <v>-0.07152404526167011</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
         <v>8</v>
       </c>
       <c r="G115" t="n">
-        <v>0.8464260438782731</v>
+        <v>0.8465346534653465</v>
       </c>
       <c r="H115" t="n">
-        <v>12.07577494692144</v>
+        <v>12.07623762376238</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -10283,16 +10283,16 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>5.335774946921443</v>
+        <v>5.336237623762376</v>
       </c>
       <c r="N115" t="n">
-        <v>5.335774946921443</v>
+        <v>5.336237623762376</v>
       </c>
       <c r="O115" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.0422186836518037</v>
+        <v>-0.04304809052333702</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -10332,10 +10332,10 @@
         <v>8</v>
       </c>
       <c r="G116" t="n">
-        <v>0.8244869072894551</v>
+        <v>0.8246110325318247</v>
       </c>
       <c r="H116" t="n">
-        <v>11.86231422505308</v>
+        <v>11.86284299858557</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -10354,16 +10354,16 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>5.257314225053078</v>
+        <v>5.257842998585572</v>
       </c>
       <c r="N116" t="n">
-        <v>5.257314225053078</v>
+        <v>5.257842998585572</v>
       </c>
       <c r="O116" t="n">
         <v>-0.1349999999999998</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.2134607218683655</v>
+        <v>-0.2133946251768037</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10403,10 +10403,10 @@
         <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>0.8096249115357396</v>
+        <v>0.8097595473833098</v>
       </c>
       <c r="H117" t="n">
-        <v>11.80850318471338</v>
+        <v>11.80936350777935</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -10425,16 +10425,16 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>5.428503184713377</v>
+        <v>5.429363507779351</v>
       </c>
       <c r="N117" t="n">
-        <v>5.428503184713377</v>
+        <v>5.429363507779351</v>
       </c>
       <c r="O117" t="n">
         <v>-0.2250000000000005</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.05381104033970097</v>
+        <v>-0.05347949080622172</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10474,10 +10474,10 @@
         <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7954706298655343</v>
+        <v>0.7956152758132956</v>
       </c>
       <c r="H118" t="n">
-        <v>11.72435244161359</v>
+        <v>11.72466053748232</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -10496,16 +10496,16 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>5.484352441613588</v>
+        <v>5.48466053748232</v>
       </c>
       <c r="N118" t="n">
-        <v>5.484352441613588</v>
+        <v>5.48466053748232</v>
       </c>
       <c r="O118" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.08415074309978898</v>
+        <v>-0.08470297029703033</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10545,10 +10545,10 @@
         <v>8</v>
       </c>
       <c r="G119" t="n">
-        <v>0.7820240622788394</v>
+        <v>0.7821782178217822</v>
       </c>
       <c r="H119" t="n">
-        <v>11.65963375796178</v>
+        <v>11.66061881188119</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -10567,16 +10567,16 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>5.539633757961783</v>
+        <v>5.540618811881187</v>
       </c>
       <c r="N119" t="n">
-        <v>5.539633757961783</v>
+        <v>5.540618811881187</v>
       </c>
       <c r="O119" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.06471868365180455</v>
+        <v>-0.06404172560113253</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -10616,10 +10616,10 @@
         <v>8</v>
       </c>
       <c r="G120" t="n">
-        <v>0.7678697806086341</v>
+        <v>0.768033946251768</v>
       </c>
       <c r="H120" t="n">
-        <v>11.55556263269639</v>
+        <v>11.55591230551627</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10638,16 +10638,16 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>5.485562632696389</v>
+        <v>5.485912305516266</v>
       </c>
       <c r="N120" t="n">
-        <v>5.485562632696389</v>
+        <v>5.485912305516266</v>
       </c>
       <c r="O120" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.1040711252653939</v>
+        <v>-0.1047065063649217</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         <v>8</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7593772116065109</v>
+        <v>0.7595473833097596</v>
       </c>
       <c r="H121" t="n">
-        <v>11.48960191082802</v>
+        <v>11.4926874115983</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -10709,16 +10709,16 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.459601910828025</v>
+        <v>5.462687411598302</v>
       </c>
       <c r="N121" t="n">
-        <v>5.459601910828025</v>
+        <v>5.462687411598302</v>
       </c>
       <c r="O121" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.06596072186836466</v>
+        <v>-0.0632248939179636</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>8</v>
       </c>
       <c r="G122" t="n">
-        <v>0.9596602972399151</v>
+        <v>0.9596888260254597</v>
       </c>
       <c r="H122" t="n">
-        <v>112.8869639065817</v>
+        <v>112.8886633663366</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>105.8869639065817</v>
+        <v>105.8886633663366</v>
       </c>
       <c r="N122" t="n">
-        <v>105.8869639065817</v>
+        <v>105.8886633663366</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         <v>8</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9355980184005662</v>
+        <v>0.9356435643564357</v>
       </c>
       <c r="H123" t="n">
-        <v>112.4619391365888</v>
+        <v>112.4623267326733</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -10845,16 +10845,16 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>105.6519391365888</v>
+        <v>105.6523267326733</v>
       </c>
       <c r="N123" t="n">
-        <v>105.6519391365888</v>
+        <v>105.6523267326733</v>
       </c>
       <c r="O123" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.4250247699929304</v>
+        <v>-0.426336633663368</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -10894,10 +10894,10 @@
         <v>8</v>
       </c>
       <c r="G124" t="n">
-        <v>0.9179051663128096</v>
+        <v>0.917963224893918</v>
       </c>
       <c r="H124" t="n">
-        <v>112.141372965322</v>
+        <v>112.1418670438472</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -10916,16 +10916,16 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>105.531372965322</v>
+        <v>105.5318670438472</v>
       </c>
       <c r="N124" t="n">
-        <v>105.531372965322</v>
+        <v>105.5318670438472</v>
       </c>
       <c r="O124" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P124" t="n">
-        <v>-0.3205661712667904</v>
+        <v>-0.3204596888260198</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -10965,10 +10965,10 @@
         <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>0.9009200283085633</v>
+        <v>0.900990099009901</v>
       </c>
       <c r="H125" t="n">
-        <v>111.9984147204529</v>
+        <v>111.9987128712871</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -10987,16 +10987,16 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>105.5784147204529</v>
+        <v>105.5787128712871</v>
       </c>
       <c r="N125" t="n">
-        <v>105.5784147204529</v>
+        <v>105.5787128712871</v>
       </c>
       <c r="O125" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P125" t="n">
-        <v>-0.142958244869078</v>
+        <v>-0.1431541725601164</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -11036,10 +11036,10 @@
         <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>0.8577494692144374</v>
+        <v>0.8578500707213579</v>
       </c>
       <c r="H126" t="n">
-        <v>111.6741719745223</v>
+        <v>111.6754561527581</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -11058,16 +11058,16 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>105.4441719745223</v>
+        <v>105.4454561527581</v>
       </c>
       <c r="N126" t="n">
-        <v>105.4441719745223</v>
+        <v>105.4454561527581</v>
       </c>
       <c r="O126" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.3242427459306469</v>
+        <v>-0.3232567185289952</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -11107,10 +11107,10 @@
         <v>8</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8117480537862704</v>
+        <v>0.8118811881188119</v>
       </c>
       <c r="H127" t="n">
-        <v>111.4326586459071</v>
+        <v>111.4330363036304</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -11129,16 +11129,16 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>105.3726586459071</v>
+        <v>105.3730363036304</v>
       </c>
       <c r="N127" t="n">
-        <v>105.3726586459071</v>
+        <v>105.3730363036304</v>
       </c>
       <c r="O127" t="n">
         <v>-0.1700000000000008</v>
       </c>
       <c r="P127" t="n">
-        <v>-0.2415133286152411</v>
+        <v>-0.2424198491277565</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -11178,10 +11178,10 @@
         <v>8</v>
       </c>
       <c r="G128" t="n">
-        <v>0.7530077848549186</v>
+        <v>0.7531824611032532</v>
       </c>
       <c r="H128" t="n">
-        <v>111.1661924982307</v>
+        <v>111.1691654879774</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -11200,16 +11200,16 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>105.2361924982307</v>
+        <v>105.2391654879774</v>
       </c>
       <c r="N128" t="n">
-        <v>105.2361924982307</v>
+        <v>105.2391654879774</v>
       </c>
       <c r="O128" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.2664661476763399</v>
+        <v>-0.2638708156530072</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -11249,10 +11249,10 @@
         <v>8</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6751592356687898</v>
+        <v>0.6753889674681753</v>
       </c>
       <c r="H129" t="n">
-        <v>110.7584076433121</v>
+        <v>110.7613401697313</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -11271,16 +11271,16 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>52.39340764331209</v>
+        <v>52.39634016973125</v>
       </c>
       <c r="N129" t="n">
-        <v>52.39340764331209</v>
+        <v>52.39634016973125</v>
       </c>
       <c r="O129" t="n">
         <v>52.435</v>
       </c>
       <c r="P129" t="n">
-        <v>-0.4077848549186172</v>
+        <v>-0.4078253182461111</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -11320,10 +11320,10 @@
         <v>8</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5973106864826611</v>
+        <v>0.5975954738330976</v>
       </c>
       <c r="H130" t="n">
-        <v>110.3715569709837</v>
+        <v>110.3727687411598</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -11342,16 +11342,16 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>52.07655697098373</v>
+        <v>52.07776874115983</v>
       </c>
       <c r="N130" t="n">
-        <v>52.07655697098373</v>
+        <v>52.07776874115983</v>
       </c>
       <c r="O130" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.3868506723283645</v>
+        <v>-0.3885714285714243</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         <v>8</v>
       </c>
       <c r="G131" t="n">
-        <v>0.5166312809624911</v>
+        <v>0.516973125884017</v>
       </c>
       <c r="H131" t="n">
-        <v>109.9688440669969</v>
+        <v>109.969813767091</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -11413,16 +11413,16 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>51.78384406699693</v>
+        <v>51.78481376709099</v>
       </c>
       <c r="N131" t="n">
-        <v>51.78384406699693</v>
+        <v>51.78481376709099</v>
       </c>
       <c r="O131" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.4027129039867958</v>
+        <v>-0.4029549740688338</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -11462,10 +11462,10 @@
         <v>8</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4317055909412597</v>
+        <v>0.4321074964639321</v>
       </c>
       <c r="H132" t="n">
-        <v>109.4492097192734</v>
+        <v>109.451489863272</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -11484,16 +11484,16 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>51.40420971927341</v>
+        <v>51.40648986327203</v>
       </c>
       <c r="N132" t="n">
-        <v>51.40420971927341</v>
+        <v>51.40648986327203</v>
       </c>
       <c r="O132" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.5196343477235246</v>
+        <v>-0.5183239038189669</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -11533,10 +11533,10 @@
         <v>8</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3510261854210899</v>
+        <v>0.3514851485148515</v>
       </c>
       <c r="H133" t="n">
-        <v>108.9086164189667</v>
+        <v>108.9105693069307</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -11555,16 +11555,16 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>103.4686164189667</v>
+        <v>103.4705693069307</v>
       </c>
       <c r="N133" t="n">
-        <v>103.4686164189667</v>
+        <v>103.4705693069307</v>
       </c>
       <c r="O133" t="n">
         <v>-52.605</v>
       </c>
       <c r="P133" t="n">
-        <v>-0.5405933003066679</v>
+        <v>-0.5409205563413337</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -11604,10 +11604,10 @@
         <v>8</v>
       </c>
       <c r="G134" t="n">
-        <v>0.267515923566879</v>
+        <v>0.268033946251768</v>
       </c>
       <c r="H134" t="n">
-        <v>108.3982802547771</v>
+        <v>108.4009688826026</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -11626,16 +11626,16 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>103.0782802547771</v>
+        <v>103.0809688826025</v>
       </c>
       <c r="N134" t="n">
-        <v>103.0782802547771</v>
+        <v>103.0809688826025</v>
       </c>
       <c r="O134" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P134" t="n">
-        <v>-0.5103361641896669</v>
+        <v>-0.5096004243281413</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
         <v>8</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9313517338995047</v>
+        <v>0.9314002828854314</v>
       </c>
       <c r="H154" t="n">
-        <v>9.031832979476292</v>
+        <v>9.031902404526168</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -13034,16 +13034,16 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>0.5718329794762909</v>
+        <v>0.5719024045261669</v>
       </c>
       <c r="N154" t="n">
-        <v>0.5718329794762909</v>
+        <v>0.5719024045261669</v>
       </c>
       <c r="O154" t="n">
         <v>0.005000000000000782</v>
       </c>
       <c r="P154" t="n">
-        <v>0.582823694262558</v>
+        <v>0.582893119312434</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>8</v>
       </c>
       <c r="G155" t="n">
-        <v>0.921443736730361</v>
+        <v>0.9214992927864215</v>
       </c>
       <c r="H155" t="n">
         <v>9.009999999999998</v>
@@ -13114,7 +13114,7 @@
         <v>-0.03000000000000114</v>
       </c>
       <c r="P155" t="n">
-        <v>-0.0218329794762937</v>
+        <v>-0.02190240452616976</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -13154,10 +13154,10 @@
         <v>8</v>
       </c>
       <c r="G156" t="n">
-        <v>0.9143665958952583</v>
+        <v>0.9144271570014144</v>
       </c>
       <c r="H156" t="n">
-        <v>8.967544232130221</v>
+        <v>8.967630834512024</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -13176,16 +13176,16 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0.5575442321302209</v>
+        <v>0.5576308345120236</v>
       </c>
       <c r="N156" t="n">
-        <v>0.5575442321302209</v>
+        <v>0.5576308345120236</v>
       </c>
       <c r="O156" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P156" t="n">
-        <v>-0.04245576786977701</v>
+        <v>-0.04236916548797431</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -13225,10 +13225,10 @@
         <v>8</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9051663128096249</v>
+        <v>0.9052333804809052</v>
       </c>
       <c r="H157" t="n">
-        <v>8.921275654635528</v>
+        <v>8.92146746817539</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -13247,16 +13247,16 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>0.6212756546355269</v>
+        <v>0.6214674681753891</v>
       </c>
       <c r="N157" t="n">
-        <v>0.6212756546355269</v>
+        <v>0.6214674681753891</v>
       </c>
       <c r="O157" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P157" t="n">
-        <v>-0.04626857749469337</v>
+        <v>-0.04616336633663387</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>8</v>
       </c>
       <c r="G158" t="n">
-        <v>0.8952583156404812</v>
+        <v>0.8953323903818954</v>
       </c>
       <c r="H158" t="n">
-        <v>8.85771939136589</v>
+        <v>8.857825318246112</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -13318,16 +13318,16 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>0.6877193913658903</v>
+        <v>0.6878253182461123</v>
       </c>
       <c r="N158" t="n">
-        <v>0.6877193913658903</v>
+        <v>0.6878253182461123</v>
       </c>
       <c r="O158" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P158" t="n">
-        <v>-0.06355626326963737</v>
+        <v>-0.06364214992927764</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -13367,10 +13367,10 @@
         <v>8</v>
       </c>
       <c r="G159" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.888967468175389</v>
       </c>
       <c r="H159" t="n">
-        <v>8.790277777777776</v>
+        <v>8.791064356435642</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -13389,16 +13389,16 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>0.8402777777777759</v>
+        <v>0.8410643564356421</v>
       </c>
       <c r="N159" t="n">
-        <v>0.8402777777777759</v>
+        <v>0.8410643564356421</v>
       </c>
       <c r="O159" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P159" t="n">
-        <v>-0.06744161358811418</v>
+        <v>-0.06676096181046987</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -13438,10 +13438,10 @@
         <v>8</v>
       </c>
       <c r="G160" t="n">
-        <v>0.8655343241330502</v>
+        <v>0.8656294200848657</v>
       </c>
       <c r="H160" t="n">
-        <v>8.431498584571832</v>
+        <v>8.432450495049505</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -13460,16 +13460,16 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>0.6614985845718326</v>
+        <v>0.6624504950495052</v>
       </c>
       <c r="N160" t="n">
-        <v>0.6614985845718326</v>
+        <v>0.6624504950495052</v>
       </c>
       <c r="O160" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P160" t="n">
-        <v>-0.3587791932059439</v>
+        <v>-0.3586138613861376</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -13509,10 +13509,10 @@
         <v>8</v>
       </c>
       <c r="G161" t="n">
-        <v>0.8584571832979476</v>
+        <v>0.8585572842998586</v>
       </c>
       <c r="H161" t="n">
-        <v>8.230219391365887</v>
+        <v>8.234370579915133</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -13531,16 +13531,16 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>0.5002193913658868</v>
+        <v>0.5043705799151326</v>
       </c>
       <c r="N161" t="n">
-        <v>0.5002193913658868</v>
+        <v>0.5043705799151326</v>
       </c>
       <c r="O161" t="n">
         <v>-0.03999999999999915</v>
       </c>
       <c r="P161" t="n">
-        <v>-0.201279193205945</v>
+        <v>-0.1980799151343717</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -13580,10 +13580,10 @@
         <v>8</v>
       </c>
       <c r="G162" t="n">
-        <v>0.8492569002123143</v>
+        <v>0.8493635077793493</v>
       </c>
       <c r="H162" t="n">
-        <v>8.008248407643311</v>
+        <v>8.010077793493632</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -13602,16 +13602,16 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>0.308248407643311</v>
+        <v>0.3100777934936323</v>
       </c>
       <c r="N162" t="n">
-        <v>0.308248407643311</v>
+        <v>0.3100777934936323</v>
       </c>
       <c r="O162" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P162" t="n">
-        <v>-0.2219709837225761</v>
+        <v>-0.2242927864215005</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -13651,10 +13651,10 @@
         <v>8</v>
       </c>
       <c r="G163" t="n">
-        <v>0.8443029016277424</v>
+        <v>0.8444130127298444</v>
       </c>
       <c r="H163" t="n">
-        <v>7.947797239915074</v>
+        <v>7.950031824611033</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -13673,16 +13673,16 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>0.3077972399150743</v>
+        <v>0.3100318246110332</v>
       </c>
       <c r="N163" t="n">
-        <v>0.3077972399150743</v>
+        <v>0.3100318246110332</v>
       </c>
       <c r="O163" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P163" t="n">
-        <v>-0.06045116772823711</v>
+        <v>-0.06004596888259961</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -13722,10 +13722,10 @@
         <v>8</v>
       </c>
       <c r="G164" t="n">
-        <v>0.83793347487615</v>
+        <v>0.8380480905233381</v>
       </c>
       <c r="H164" t="n">
-        <v>7.839948690728945</v>
+        <v>7.841587694483734</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -13744,16 +13744,16 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>0.2799486907289452</v>
+        <v>0.2815876944837346</v>
       </c>
       <c r="N164" t="n">
-        <v>0.2799486907289452</v>
+        <v>0.2815876944837346</v>
       </c>
       <c r="O164" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P164" t="n">
-        <v>-0.1078485491861292</v>
+        <v>-0.1084441301272987</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -13793,10 +13793,10 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>0.835102618542109</v>
+        <v>0.8352192362093352</v>
       </c>
       <c r="H165" t="n">
-        <v>7.829196744515216</v>
+        <v>7.82936350777935</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -13815,16 +13815,16 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>0.3491967445152158</v>
+        <v>0.3493635077793495</v>
       </c>
       <c r="N165" t="n">
-        <v>0.3491967445152158</v>
+        <v>0.3493635077793495</v>
       </c>
       <c r="O165" t="n">
         <v>-0.07999999999999918</v>
       </c>
       <c r="P165" t="n">
-        <v>-0.01075194621372866</v>
+        <v>-0.01222418670438419</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -13864,10 +13864,10 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>0.8266100495399858</v>
+        <v>0.8267326732673267</v>
       </c>
       <c r="H166" t="n">
-        <v>7.753918966737438</v>
+        <v>7.755321782178218</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -13886,16 +13886,16 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>0.3839189667374381</v>
+        <v>0.3853217821782176</v>
       </c>
       <c r="N166" t="n">
-        <v>0.3839189667374381</v>
+        <v>0.3853217821782176</v>
       </c>
       <c r="O166" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P166" t="n">
-        <v>-0.075277777777778</v>
+        <v>-0.07404172560113231</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -15065,10 +15065,10 @@
         <v>8</v>
       </c>
       <c r="G183" t="n">
-        <v>0.8004246284501062</v>
+        <v>0.8005657708628006</v>
       </c>
       <c r="H183" t="n">
-        <v>5.551422505307856</v>
+        <v>5.551479844413013</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -15087,16 +15087,16 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>0.3364225053078558</v>
+        <v>0.336479844413013</v>
       </c>
       <c r="N183" t="n">
-        <v>0.3364225053078558</v>
+        <v>0.336479844413013</v>
       </c>
       <c r="O183" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P183" t="n">
-        <v>-0.0926577329542333</v>
+        <v>-0.09260039384907603</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -15136,10 +15136,10 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>0.8535031847133758</v>
+        <v>0.8536067892503536</v>
       </c>
       <c r="H184" t="n">
-        <v>5.758885350318471</v>
+        <v>5.75922206506365</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -15158,16 +15158,16 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>0.5938853503184713</v>
+        <v>0.5942220650636498</v>
       </c>
       <c r="N184" t="n">
-        <v>0.5938853503184713</v>
+        <v>0.5942220650636498</v>
       </c>
       <c r="O184" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P184" t="n">
-        <v>0.2074628450106157</v>
+        <v>0.207742220650637</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -15207,10 +15207,10 @@
         <v>8</v>
       </c>
       <c r="G185" t="n">
-        <v>0.867657466383581</v>
+        <v>0.8677510608203678</v>
       </c>
       <c r="H185" t="n">
-        <v>5.799830148619957</v>
+        <v>5.800047736916548</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -15229,16 +15229,16 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>0.6798301486199572</v>
+        <v>0.6800477369165483</v>
       </c>
       <c r="N185" t="n">
-        <v>0.6798301486199572</v>
+        <v>0.6800477369165483</v>
       </c>
       <c r="O185" t="n">
         <v>-0.04499999999999993</v>
       </c>
       <c r="P185" t="n">
-        <v>0.0409447983014859</v>
+        <v>0.04082567185289854</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -15278,10 +15278,10 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>0.86482661004954</v>
+        <v>0.864922206506365</v>
       </c>
       <c r="H186" t="n">
-        <v>5.786029723991507</v>
+        <v>5.786495756718529</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -15300,16 +15300,16 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>0.7060297239915068</v>
+        <v>0.706495756718529</v>
       </c>
       <c r="N186" t="n">
-        <v>0.7060297239915068</v>
+        <v>0.706495756718529</v>
       </c>
       <c r="O186" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P186" t="n">
-        <v>-0.01380042462845044</v>
+        <v>-0.01355198019801929</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -15349,10 +15349,10 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8435951875442321</v>
+        <v>0.8437057991513437</v>
       </c>
       <c r="H187" t="n">
-        <v>5.683342179759378</v>
+        <v>5.683521923620933</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -15371,16 +15371,16 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>0.253342179759378</v>
+        <v>0.2535219236209336</v>
       </c>
       <c r="N187" t="n">
-        <v>0.253342179759378</v>
+        <v>0.2535219236209336</v>
       </c>
       <c r="O187" t="n">
         <v>0.3499999999999996</v>
       </c>
       <c r="P187" t="n">
-        <v>-0.1026875442321291</v>
+        <v>-0.1029738330975958</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -15420,10 +15420,10 @@
         <v>8</v>
       </c>
       <c r="G188" t="n">
-        <v>0.7961783439490446</v>
+        <v>0.7963224893917963</v>
       </c>
       <c r="H188" t="n">
-        <v>5.543343949044586</v>
+        <v>5.544632248939179</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -15442,16 +15442,16 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.05915605095541387</v>
+        <v>-0.05786775106082143</v>
       </c>
       <c r="N188" t="n">
-        <v>0.05915605095541387</v>
+        <v>0.05786775106082143</v>
       </c>
       <c r="O188" t="n">
         <v>0.1725000000000003</v>
       </c>
       <c r="P188" t="n">
-        <v>-0.1399982307147916</v>
+        <v>-0.1388896746817547</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -15491,10 +15491,10 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>0.7494692144373672</v>
+        <v>0.7496463932107497</v>
       </c>
       <c r="H189" t="n">
-        <v>5.393381104033971</v>
+        <v>5.394964639321076</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -15513,16 +15513,16 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.1566188959660293</v>
+        <v>-0.1550353606789239</v>
       </c>
       <c r="N189" t="n">
-        <v>0.1566188959660293</v>
+        <v>0.1550353606789239</v>
       </c>
       <c r="O189" t="n">
         <v>-0.05250000000000021</v>
       </c>
       <c r="P189" t="n">
-        <v>-0.1499628450106156</v>
+        <v>-0.1496676096181027</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -15562,10 +15562,10 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>0.721868365180467</v>
+        <v>0.7213578500707214</v>
       </c>
       <c r="H190" t="n">
-        <v>5.281518046709129</v>
+        <v>5.281103253182462</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -15584,16 +15584,16 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>0.001518046709128917</v>
+        <v>0.001103253182461295</v>
       </c>
       <c r="N190" t="n">
-        <v>0.001518046709128917</v>
+        <v>0.001103253182461295</v>
       </c>
       <c r="O190" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P190" t="n">
-        <v>-0.1118630573248414</v>
+        <v>-0.1138613861386144</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -15633,10 +15633,10 @@
         <v>8</v>
       </c>
       <c r="G191" t="n">
-        <v>0.7169143665958952</v>
+        <v>0.7164073550212164</v>
       </c>
       <c r="H191" t="n">
-        <v>5.278746461429582</v>
+        <v>5.278540487977369</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -15655,16 +15655,16 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>0.2537464614295839</v>
+        <v>0.2535404879773706</v>
       </c>
       <c r="N191" t="n">
-        <v>0.2537464614295839</v>
+        <v>0.2535404879773706</v>
       </c>
       <c r="O191" t="n">
         <v>-0.2550000000000017</v>
       </c>
       <c r="P191" t="n">
-        <v>-0.002771585279546684</v>
+        <v>-0.002562765205092354</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -15704,10 +15704,10 @@
         <v>8</v>
       </c>
       <c r="G192" t="n">
-        <v>0.7254069355980184</v>
+        <v>0.7248939179632249</v>
       </c>
       <c r="H192" t="n">
-        <v>5.29385881104034</v>
+        <v>5.291357850070721</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -15726,16 +15726,16 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>0.4438588110403403</v>
+        <v>0.4413578500707214</v>
       </c>
       <c r="N192" t="n">
-        <v>0.4438588110403403</v>
+        <v>0.4413578500707214</v>
       </c>
       <c r="O192" t="n">
         <v>-0.1749999999999989</v>
       </c>
       <c r="P192" t="n">
-        <v>0.01511234961075747</v>
+        <v>0.01281736209335183</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -15775,10 +15775,10 @@
         <v>8</v>
       </c>
       <c r="G193" t="n">
-        <v>0.732484076433121</v>
+        <v>0.731966053748232</v>
       </c>
       <c r="H193" t="n">
-        <v>5.33764331210191</v>
+        <v>5.333336280056576</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -15797,16 +15797,16 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>0.7676433121019093</v>
+        <v>0.7633362800565759</v>
       </c>
       <c r="N193" t="n">
-        <v>0.7676433121019093</v>
+        <v>0.7633362800565759</v>
       </c>
       <c r="O193" t="n">
         <v>-0.2799999999999994</v>
       </c>
       <c r="P193" t="n">
-        <v>0.04378450106156961</v>
+        <v>0.04197842998585521</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -15846,10 +15846,10 @@
         <v>8</v>
       </c>
       <c r="G194" t="n">
-        <v>0.7232837933474876</v>
+        <v>0.7227722772277227</v>
       </c>
       <c r="H194" t="n">
-        <v>5.283508492569002</v>
+        <v>5.282252475247525</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15868,16 +15868,16 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>0.8535084925690022</v>
+        <v>0.8522524752475249</v>
       </c>
       <c r="N194" t="n">
-        <v>0.8535084925690022</v>
+        <v>0.8522524752475249</v>
       </c>
       <c r="O194" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P194" t="n">
-        <v>-0.05413481953290766</v>
+        <v>-0.05108380480905161</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -15917,10 +15917,10 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>0.6956829440905874</v>
+        <v>0.6951909476661952</v>
       </c>
       <c r="H195" t="n">
-        <v>5.215</v>
+        <v>5.214685289957567</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -15939,16 +15939,16 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>0.7349999999999994</v>
+        <v>0.7346852899575662</v>
       </c>
       <c r="N195" t="n">
-        <v>0.7349999999999994</v>
+        <v>0.7346852899575662</v>
       </c>
       <c r="O195" t="n">
         <v>0.05000000000000071</v>
       </c>
       <c r="P195" t="n">
-        <v>-0.06850849256900204</v>
+        <v>-0.06756718528995798</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -15988,10 +15988,10 @@
         <v>8</v>
       </c>
       <c r="G196" t="n">
-        <v>0.656758669497523</v>
+        <v>0.6562942008486563</v>
       </c>
       <c r="H196" t="n">
-        <v>5.12446567586695</v>
+        <v>5.122956152758134</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -16010,16 +16010,16 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>0.3344656758669498</v>
+        <v>0.3329561527581335</v>
       </c>
       <c r="N196" t="n">
-        <v>0.3344656758669498</v>
+        <v>0.3329561527581335</v>
       </c>
       <c r="O196" t="n">
         <v>0.3099999999999996</v>
       </c>
       <c r="P196" t="n">
-        <v>-0.09053432413305007</v>
+        <v>-0.0917291371994331</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>0.7558386411889597</v>
+        <v>0.756011315417256</v>
       </c>
       <c r="H213" t="n">
         <v>5.97</v>
@@ -17260,10 +17260,10 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>0.7551309271054494</v>
+        <v>0.7553041018387553</v>
       </c>
       <c r="H214" t="n">
-        <v>5.969255720688841</v>
+        <v>5.969483734087694</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -17282,16 +17282,16 @@
         <v>1</v>
       </c>
       <c r="M214" t="n">
-        <v>-2.618244279311157</v>
+        <v>-2.618016265912305</v>
       </c>
       <c r="N214" t="n">
-        <v>2.618244279311157</v>
+        <v>2.618016265912305</v>
       </c>
       <c r="O214" t="n">
         <v>-0.1500000000000021</v>
       </c>
       <c r="P214" t="n">
-        <v>-0.0007442793111582802</v>
+        <v>-0.0005162659123056912</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>0.7657466383581033</v>
+        <v>0.7659123055162659</v>
       </c>
       <c r="H215" t="n">
-        <v>6.009398443029016</v>
+        <v>6.010530410183875</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -17353,16 +17353,16 @@
         <v>1</v>
       </c>
       <c r="M215" t="n">
-        <v>-2.470601556970984</v>
+        <v>-2.469469589816125</v>
       </c>
       <c r="N215" t="n">
-        <v>2.470601556970984</v>
+        <v>2.469469589816125</v>
       </c>
       <c r="O215" t="n">
         <v>-0.1074999999999982</v>
       </c>
       <c r="P215" t="n">
-        <v>0.04014272234017469</v>
+        <v>0.0410466760961814</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -17402,10 +17402,10 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>0.7862703467799009</v>
+        <v>0.7864214992927864</v>
       </c>
       <c r="H216" t="n">
-        <v>6.101535739561218</v>
+        <v>6.102729844413012</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -17424,16 +17424,16 @@
         <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>-2.108464260438783</v>
+        <v>-2.107270155586988</v>
       </c>
       <c r="N216" t="n">
-        <v>2.108464260438783</v>
+        <v>2.107270155586988</v>
       </c>
       <c r="O216" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P216" t="n">
-        <v>0.0921372965322016</v>
+        <v>0.09219943422913701</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -17473,10 +17473,10 @@
         <v>8</v>
       </c>
       <c r="G217" t="n">
-        <v>0.8089171974522293</v>
+        <v>0.809052333804809</v>
       </c>
       <c r="H217" t="n">
-        <v>6.200445859872612</v>
+        <v>6.201513437057992</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -17495,16 +17495,16 @@
         <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>-1.959554140127388</v>
+        <v>-1.958486562942008</v>
       </c>
       <c r="N217" t="n">
-        <v>1.959554140127388</v>
+        <v>1.958486562942008</v>
       </c>
       <c r="O217" t="n">
         <v>-0.05000000000000071</v>
       </c>
       <c r="P217" t="n">
-        <v>0.09891012031139468</v>
+        <v>0.09878359264497938</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -17544,10 +17544,10 @@
         <v>8</v>
       </c>
       <c r="G218" t="n">
-        <v>0.8273177636234961</v>
+        <v>0.8274398868458275</v>
       </c>
       <c r="H218" t="n">
-        <v>6.293873555083746</v>
+        <v>6.294516737388025</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -17566,16 +17566,16 @@
         <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>-1.636126444916254</v>
+        <v>-1.635483262611975</v>
       </c>
       <c r="N218" t="n">
-        <v>1.636126444916254</v>
+        <v>1.635483262611975</v>
       </c>
       <c r="O218" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P218" t="n">
-        <v>0.09342769521113325</v>
+        <v>0.09300330033003323</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -17615,10 +17615,10 @@
         <v>8</v>
       </c>
       <c r="G219" t="n">
-        <v>0.8443029016277424</v>
+        <v>0.8444130127298444</v>
       </c>
       <c r="H219" t="n">
-        <v>6.384998230714791</v>
+        <v>6.385215700141442</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -17637,16 +17637,16 @@
         <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>-1.605001769285209</v>
+        <v>-1.604784299858558</v>
       </c>
       <c r="N219" t="n">
-        <v>1.605001769285209</v>
+        <v>1.604784299858558</v>
       </c>
       <c r="O219" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P219" t="n">
-        <v>0.09112467563104509</v>
+        <v>0.09069896275341716</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -17686,10 +17686,10 @@
         <v>8</v>
       </c>
       <c r="G220" t="n">
-        <v>0.851380042462845</v>
+        <v>0.8514851485148515</v>
       </c>
       <c r="H220" t="n">
-        <v>6.447707006369428</v>
+        <v>6.45019801980198</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -17708,16 +17708,16 @@
         <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>-1.542292993630572</v>
+        <v>-1.53980198019802</v>
       </c>
       <c r="N220" t="n">
-        <v>1.542292993630572</v>
+        <v>1.53980198019802</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
       </c>
       <c r="P220" t="n">
-        <v>0.06270877565463717</v>
+        <v>0.06498231966053769</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -17757,10 +17757,10 @@
         <v>8</v>
       </c>
       <c r="G221" t="n">
-        <v>0.8421797593772116</v>
+        <v>0.8422913719943423</v>
       </c>
       <c r="H221" t="n">
-        <v>6.380805024769993</v>
+        <v>6.381025459688826</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -17779,16 +17779,16 @@
         <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>-1.476694975230007</v>
+        <v>-1.476474540311174</v>
       </c>
       <c r="N221" t="n">
-        <v>1.476694975230007</v>
+        <v>1.476474540311174</v>
       </c>
       <c r="O221" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P221" t="n">
-        <v>-0.06690198159943517</v>
+        <v>-0.06917256011315409</v>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
@@ -17828,10 +17828,10 @@
         <v>8</v>
       </c>
       <c r="G222" t="n">
-        <v>0.8223637650389243</v>
+        <v>0.8224893917963225</v>
       </c>
       <c r="H222" t="n">
-        <v>6.248891247935834</v>
+        <v>6.249222065063649</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -17850,16 +17850,16 @@
         <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>-1.491108752064166</v>
+        <v>-1.490777934936351</v>
       </c>
       <c r="N222" t="n">
-        <v>1.491108752064166</v>
+        <v>1.490777934936351</v>
       </c>
       <c r="O222" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.1319137768341587</v>
+        <v>-0.1318033946251767</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -17899,10 +17899,10 @@
         <v>8</v>
       </c>
       <c r="G223" t="n">
-        <v>0.8046709129511678</v>
+        <v>0.8048090523338048</v>
       </c>
       <c r="H223" t="n">
-        <v>6.178966737438075</v>
+        <v>6.17933050447902</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -17921,16 +17921,16 @@
         <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>-1.441033262561925</v>
+        <v>-1.44066949552098</v>
       </c>
       <c r="N223" t="n">
-        <v>1.441033262561925</v>
+        <v>1.44066949552098</v>
       </c>
       <c r="O223" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.06992451049775905</v>
+        <v>-0.06989156058462953</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -17970,10 +17970,10 @@
         <v>8</v>
       </c>
       <c r="G224" t="n">
-        <v>0.7799009200283086</v>
+        <v>0.7800565770862801</v>
       </c>
       <c r="H224" t="n">
-        <v>6.076402158527954</v>
+        <v>6.076555869872701</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -17992,16 +17992,16 @@
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>-1.323597841472046</v>
+        <v>-1.323444130127299</v>
       </c>
       <c r="N224" t="n">
-        <v>1.323597841472046</v>
+        <v>1.323444130127299</v>
       </c>
       <c r="O224" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.1025645789101208</v>
+        <v>-0.1027746346063187</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -18041,10 +18041,10 @@
         <v>8</v>
       </c>
       <c r="G225" t="n">
-        <v>0.7523000707714084</v>
+        <v>0.7524752475247525</v>
       </c>
       <c r="H225" t="n">
-        <v>5.965528426515688</v>
+        <v>5.965759075907591</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -18063,16 +18063,16 @@
         <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>-1.394471573484313</v>
+        <v>-1.39424092409241</v>
       </c>
       <c r="N225" t="n">
-        <v>1.394471573484313</v>
+        <v>1.39424092409241</v>
       </c>
       <c r="O225" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.1108737320122666</v>
+        <v>-0.1107967939651102</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>8</v>
       </c>
       <c r="G226" t="n">
-        <v>0.7275300778485492</v>
+        <v>0.7277227722772277</v>
       </c>
       <c r="H226" t="n">
-        <v>5.827487615003538</v>
+        <v>5.829009900990099</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -18134,16 +18134,16 @@
         <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>-1.552512384996461</v>
+        <v>-1.550990099009901</v>
       </c>
       <c r="N226" t="n">
-        <v>1.552512384996461</v>
+        <v>1.550990099009901</v>
       </c>
       <c r="O226" t="n">
         <v>0.01999999999999957</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.1380408115121492</v>
+        <v>-0.1367491749174921</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -19313,10 +19313,10 @@
         <v>8</v>
       </c>
       <c r="G243" t="n">
-        <v>0.8287331917905166</v>
+        <v>0.8288543140028288</v>
       </c>
       <c r="H243" t="n">
-        <v>5.566003184713375</v>
+        <v>5.568412305516264</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -19335,16 +19335,16 @@
         <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>1.576003184713374</v>
+        <v>1.578412305516264</v>
       </c>
       <c r="N243" t="n">
-        <v>1.576003184713374</v>
+        <v>1.578412305516264</v>
       </c>
       <c r="O243" t="n">
         <v>-0.1624999999999996</v>
       </c>
       <c r="P243" t="n">
-        <v>-1.594914825097417</v>
+        <v>-1.592505704294528</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -19384,10 +19384,10 @@
         <v>8</v>
       </c>
       <c r="G244" t="n">
-        <v>0.7048832271762208</v>
+        <v>0.7050919377652051</v>
       </c>
       <c r="H244" t="n">
-        <v>4.931942675159235</v>
+        <v>4.932581329561527</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -19406,16 +19406,16 @@
         <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>1.109442675159236</v>
+        <v>1.110081329561527</v>
       </c>
       <c r="N244" t="n">
-        <v>1.109442675159236</v>
+        <v>1.110081329561527</v>
       </c>
       <c r="O244" t="n">
         <v>-0.1675000000000004</v>
       </c>
       <c r="P244" t="n">
-        <v>-0.6340605095541392</v>
+        <v>-0.6358309759547369</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -19455,10 +19455,10 @@
         <v>8</v>
       </c>
       <c r="G245" t="n">
-        <v>0.6157112526539278</v>
+        <v>0.615983026874116</v>
       </c>
       <c r="H245" t="n">
-        <v>4.630525477707007</v>
+        <v>4.630802687411599</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -19477,16 +19477,16 @@
         <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>0.850525477707007</v>
+        <v>0.850802687411599</v>
       </c>
       <c r="N245" t="n">
-        <v>0.850525477707007</v>
+        <v>0.850802687411599</v>
       </c>
       <c r="O245" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.3014171974522286</v>
+        <v>-0.3017786421499284</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -19526,10 +19526,10 @@
         <v>8</v>
       </c>
       <c r="G246" t="n">
-        <v>0.5937721160651097</v>
+        <v>0.594059405940594</v>
       </c>
       <c r="H246" t="n">
-        <v>4.563975583864119</v>
+        <v>4.566905940594059</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -19548,16 +19548,16 @@
         <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>0.8839755838641188</v>
+        <v>0.8869059405940587</v>
       </c>
       <c r="N246" t="n">
-        <v>0.8839755838641188</v>
+        <v>0.8869059405940587</v>
       </c>
       <c r="O246" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.0665498938428879</v>
+        <v>-0.06389674681753998</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -19597,10 +19597,10 @@
         <v>8</v>
       </c>
       <c r="G247" t="n">
-        <v>0.6341118188251946</v>
+        <v>0.6343705799151343</v>
       </c>
       <c r="H247" t="n">
-        <v>4.722882165605096</v>
+        <v>4.723673974540311</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -19619,16 +19619,16 @@
         <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>1.142882165605096</v>
+        <v>1.143673974540311</v>
       </c>
       <c r="N247" t="n">
-        <v>1.142882165605096</v>
+        <v>1.143673974540311</v>
       </c>
       <c r="O247" t="n">
         <v>-0.1000000000000001</v>
       </c>
       <c r="P247" t="n">
-        <v>0.1589065817409772</v>
+        <v>0.1567680339462525</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -19668,10 +19668,10 @@
         <v>8</v>
       </c>
       <c r="G248" t="n">
-        <v>0.6468506723283793</v>
+        <v>0.6471004243281471</v>
       </c>
       <c r="H248" t="n">
-        <v>4.759787685774946</v>
+        <v>4.76008486562942</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19690,16 +19690,16 @@
         <v>1</v>
       </c>
       <c r="M248" t="n">
-        <v>1.367287685774946</v>
+        <v>1.36758486562942</v>
       </c>
       <c r="N248" t="n">
-        <v>1.367287685774946</v>
+        <v>1.36758486562942</v>
       </c>
       <c r="O248" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P248" t="n">
-        <v>0.03690552016985027</v>
+        <v>0.03641089108910833</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -19739,10 +19739,10 @@
         <v>8</v>
       </c>
       <c r="G249" t="n">
-        <v>0.5966029723991507</v>
+        <v>0.5968882602545968</v>
       </c>
       <c r="H249" t="n">
-        <v>4.592850318471338</v>
+        <v>4.595760254596888</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19761,16 +19761,16 @@
         <v>1</v>
       </c>
       <c r="M249" t="n">
-        <v>1.312850318471338</v>
+        <v>1.315760254596888</v>
       </c>
       <c r="N249" t="n">
-        <v>1.312850318471338</v>
+        <v>1.315760254596888</v>
       </c>
       <c r="O249" t="n">
         <v>-0.1125000000000003</v>
       </c>
       <c r="P249" t="n">
-        <v>-0.1669373673036088</v>
+        <v>-0.1643246110325318</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -19810,10 +19810,10 @@
         <v>8</v>
       </c>
       <c r="G250" t="n">
-        <v>0.4904458598726115</v>
+        <v>0.4908062234794908</v>
       </c>
       <c r="H250" t="n">
-        <v>4.149028662420382</v>
+        <v>4.151234087694484</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19832,16 +19832,16 @@
         <v>1</v>
       </c>
       <c r="M250" t="n">
-        <v>0.9990286624203821</v>
+        <v>1.001234087694484</v>
       </c>
       <c r="N250" t="n">
-        <v>0.9990286624203821</v>
+        <v>1.001234087694484</v>
       </c>
       <c r="O250" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P250" t="n">
-        <v>-0.4438216560509556</v>
+        <v>-0.4445261669024037</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -19881,10 +19881,10 @@
         <v>8</v>
       </c>
       <c r="G251" t="n">
-        <v>0.3913658881811748</v>
+        <v>0.3910891089108911</v>
       </c>
       <c r="H251" t="n">
-        <v>3.805079617834395</v>
+        <v>3.804232673267327</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19903,16 +19903,16 @@
         <v>1</v>
       </c>
       <c r="M251" t="n">
-        <v>0.860079617834395</v>
+        <v>0.8592326732673272</v>
       </c>
       <c r="N251" t="n">
-        <v>0.860079617834395</v>
+        <v>0.8592326732673272</v>
       </c>
       <c r="O251" t="n">
         <v>-0.2050000000000001</v>
       </c>
       <c r="P251" t="n">
-        <v>-0.3439490445859872</v>
+        <v>-0.3470014144271572</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         <v>8</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3368719037508847</v>
+        <v>0.3366336633663367</v>
       </c>
       <c r="H252" t="n">
-        <v>3.642031139419675</v>
+        <v>3.641221122112211</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19974,16 +19974,16 @@
         <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>0.8020311394196749</v>
+        <v>0.8012211221122114</v>
       </c>
       <c r="N252" t="n">
-        <v>0.8020311394196749</v>
+        <v>0.8012211221122114</v>
       </c>
       <c r="O252" t="n">
         <v>-0.105</v>
       </c>
       <c r="P252" t="n">
-        <v>-0.1630484784147201</v>
+        <v>-0.1630115511551158</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -20023,10 +20023,10 @@
         <v>8</v>
       </c>
       <c r="G253" t="n">
-        <v>0.3474876150035386</v>
+        <v>0.3472418670438472</v>
       </c>
       <c r="H253" t="n">
-        <v>3.678124557678698</v>
+        <v>3.677289014615747</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -20045,16 +20045,16 @@
         <v>1</v>
       </c>
       <c r="M253" t="n">
-        <v>0.9081245576786983</v>
+        <v>0.9072890146157473</v>
       </c>
       <c r="N253" t="n">
-        <v>0.9081245576786983</v>
+        <v>0.9072890146157473</v>
       </c>
       <c r="O253" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P253" t="n">
-        <v>0.03609341825902357</v>
+        <v>0.03606789250353604</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -20094,10 +20094,10 @@
         <v>8</v>
       </c>
       <c r="G254" t="n">
-        <v>0.494692144373673</v>
+        <v>0.495049504950495</v>
       </c>
       <c r="H254" t="n">
-        <v>4.175015923566879</v>
+        <v>4.17720297029703</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -20116,16 +20116,16 @@
         <v>1</v>
       </c>
       <c r="M254" t="n">
-        <v>1.355015923566879</v>
+        <v>1.35720297029703</v>
       </c>
       <c r="N254" t="n">
-        <v>1.355015923566879</v>
+        <v>1.35720297029703</v>
       </c>
       <c r="O254" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P254" t="n">
-        <v>0.4968913658881808</v>
+        <v>0.4999139556812824</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -20165,10 +20165,10 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>0.6963906581740976</v>
+        <v>0.6966053748231966</v>
       </c>
       <c r="H255" t="n">
-        <v>4.905955414012739</v>
+        <v>4.906612446958982</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -20187,16 +20187,16 @@
         <v>1</v>
       </c>
       <c r="M255" t="n">
-        <v>2.155955414012739</v>
+        <v>2.156612446958982</v>
       </c>
       <c r="N255" t="n">
-        <v>2.155955414012739</v>
+        <v>2.156612446958982</v>
       </c>
       <c r="O255" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P255" t="n">
-        <v>0.7309394904458602</v>
+        <v>0.7294094766619521</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
@@ -20236,10 +20236,10 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>0.7883934890304317</v>
+        <v>0.7885431400282885</v>
       </c>
       <c r="H256" t="n">
-        <v>5.204532908704882</v>
+        <v>5.205983026874114</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -20258,16 +20258,16 @@
         <v>1</v>
       </c>
       <c r="M256" t="n">
-        <v>2.454532908704882</v>
+        <v>2.455983026874114</v>
       </c>
       <c r="N256" t="n">
-        <v>2.454532908704882</v>
+        <v>2.455983026874114</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
       </c>
       <c r="P256" t="n">
-        <v>0.2985774946921431</v>
+        <v>0.2993705799151325</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -21437,10 +21437,10 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>0.9426751592356688</v>
+        <v>0.9427157001414427</v>
       </c>
       <c r="H273" t="n">
-        <v>6.91328025477707</v>
+        <v>6.913504243281471</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -21459,16 +21459,16 @@
         <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>-0.8517197452229297</v>
+        <v>-0.8514957567185286</v>
       </c>
       <c r="N273" t="n">
-        <v>0.8517197452229297</v>
+        <v>0.8514957567185286</v>
       </c>
       <c r="O273" t="n">
         <v>0.0550000000000006</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.9776541063535067</v>
+        <v>-0.9774301178491056</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -21508,10 +21508,10 @@
         <v>8</v>
       </c>
       <c r="G274" t="n">
-        <v>0.9391365888181175</v>
+        <v>0.9391796322489392</v>
       </c>
       <c r="H274" t="n">
-        <v>6.848729653220099</v>
+        <v>6.848967468175389</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -21530,16 +21530,16 @@
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>-0.9312703467799013</v>
+        <v>-0.9310325318246111</v>
       </c>
       <c r="N274" t="n">
-        <v>0.9312703467799013</v>
+        <v>0.9310325318246111</v>
       </c>
       <c r="O274" t="n">
         <v>0.01500000000000057</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.06455060155697101</v>
+        <v>-0.06453677510608191</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -21579,10 +21579,10 @@
         <v>8</v>
       </c>
       <c r="G275" t="n">
-        <v>0.9355980184005662</v>
+        <v>0.9356435643564357</v>
       </c>
       <c r="H275" t="n">
-        <v>6.829589525831564</v>
+        <v>6.829715346534654</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -21601,16 +21601,16 @@
         <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>-0.9404104741684352</v>
+        <v>-0.940284653465346</v>
       </c>
       <c r="N275" t="n">
-        <v>0.9404104741684352</v>
+        <v>0.940284653465346</v>
       </c>
       <c r="O275" t="n">
         <v>-0.01000000000000068</v>
       </c>
       <c r="P275" t="n">
-        <v>-0.01914012738853454</v>
+        <v>-0.01925212164073553</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -21650,10 +21650,10 @@
         <v>8</v>
       </c>
       <c r="G276" t="n">
-        <v>0.9320594479830149</v>
+        <v>0.9321074964639321</v>
       </c>
       <c r="H276" t="n">
-        <v>6.819256900212315</v>
+        <v>6.81978783592645</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -21672,16 +21672,16 @@
         <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>-0.8807430997876855</v>
+        <v>-0.8802121640735505</v>
       </c>
       <c r="N276" t="n">
-        <v>0.8807430997876855</v>
+        <v>0.8802121640735505</v>
       </c>
       <c r="O276" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P276" t="n">
-        <v>-0.01033262561924975</v>
+        <v>-0.00992751060820396</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -21721,10 +21721,10 @@
         <v>8</v>
       </c>
       <c r="G277" t="n">
-        <v>0.9285208775654635</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="H277" t="n">
-        <v>6.780077848549186</v>
+        <v>6.780357142857143</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -21743,16 +21743,16 @@
         <v>1</v>
       </c>
       <c r="M277" t="n">
-        <v>-0.8099221514508139</v>
+        <v>-0.8096428571428564</v>
       </c>
       <c r="N277" t="n">
-        <v>0.8099221514508139</v>
+        <v>0.8096428571428564</v>
       </c>
       <c r="O277" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P277" t="n">
-        <v>-0.03917905166312874</v>
+        <v>-0.03943069306930624</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -21792,10 +21792,10 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>0.9249823071479123</v>
+        <v>0.925035360678925</v>
       </c>
       <c r="H278" t="n">
-        <v>6.750527246992215</v>
+        <v>6.750820367751061</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -21814,16 +21814,16 @@
         <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>-0.6994727530077851</v>
+        <v>-0.6991796322489394</v>
       </c>
       <c r="N278" t="n">
-        <v>0.6994727530077851</v>
+        <v>0.6991796322489394</v>
       </c>
       <c r="O278" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P278" t="n">
-        <v>-0.02955060155697087</v>
+        <v>-0.02953677510608266</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -21863,10 +21863,10 @@
         <v>8</v>
       </c>
       <c r="G279" t="n">
-        <v>0.921443736730361</v>
+        <v>0.9214992927864215</v>
       </c>
       <c r="H279" t="n">
-        <v>6.713984430290163</v>
+        <v>6.714189061763319</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -21885,16 +21885,16 @@
         <v>1</v>
       </c>
       <c r="M279" t="n">
-        <v>-0.6560155697098375</v>
+        <v>-0.655810938236681</v>
       </c>
       <c r="N279" t="n">
-        <v>0.6560155697098375</v>
+        <v>0.655810938236681</v>
       </c>
       <c r="O279" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P279" t="n">
-        <v>-0.03654281670205251</v>
+        <v>-0.03663130598774167</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -21934,10 +21934,10 @@
         <v>8</v>
       </c>
       <c r="G280" t="n">
-        <v>0.9179051663128096</v>
+        <v>0.917963224893918</v>
       </c>
       <c r="H280" t="n">
-        <v>6.675704175513093</v>
+        <v>6.67698727015559</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -21956,16 +21956,16 @@
         <v>1</v>
       </c>
       <c r="M280" t="n">
-        <v>-0.5942958244869061</v>
+        <v>-0.5930127298444097</v>
       </c>
       <c r="N280" t="n">
-        <v>0.5942958244869061</v>
+        <v>0.5930127298444097</v>
       </c>
       <c r="O280" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P280" t="n">
-        <v>-0.03828025477706909</v>
+        <v>-0.03720179160772918</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -22005,10 +22005,10 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>0.9143665958952583</v>
+        <v>0.9144271570014144</v>
       </c>
       <c r="H281" t="n">
-        <v>6.623750884642604</v>
+        <v>6.62442008486563</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -22027,16 +22027,16 @@
         <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>-0.6362491153573959</v>
+        <v>-0.63557991513437</v>
       </c>
       <c r="N281" t="n">
-        <v>0.6362491153573959</v>
+        <v>0.63557991513437</v>
       </c>
       <c r="O281" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P281" t="n">
-        <v>-0.05195329087048961</v>
+        <v>-0.05256718528996007</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -22076,10 +22076,10 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>0.910828025477707</v>
+        <v>0.9108910891089109</v>
       </c>
       <c r="H282" t="n">
-        <v>6.547324840764332</v>
+        <v>6.547673267326733</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -22098,16 +22098,16 @@
         <v>1</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.5626751592356687</v>
+        <v>-0.5623267326732675</v>
       </c>
       <c r="N282" t="n">
-        <v>0.5626751592356687</v>
+        <v>0.5623267326732675</v>
       </c>
       <c r="O282" t="n">
         <v>-0.1499999999999995</v>
       </c>
       <c r="P282" t="n">
-        <v>-0.07642604387827223</v>
+        <v>-0.07674681753889701</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -22147,10 +22147,10 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>0.9072894550601557</v>
+        <v>0.9073550212164073</v>
       </c>
       <c r="H283" t="n">
-        <v>6.511096956829441</v>
+        <v>6.512545968882602</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -22169,16 +22169,16 @@
         <v>1</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.498903043170559</v>
+        <v>-0.4974540311173978</v>
       </c>
       <c r="N283" t="n">
-        <v>0.498903043170559</v>
+        <v>0.4974540311173978</v>
       </c>
       <c r="O283" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P283" t="n">
-        <v>-0.03622788393489085</v>
+        <v>-0.03512729844413087</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -22218,10 +22218,10 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>0.9051663128096249</v>
+        <v>0.9052333804809052</v>
       </c>
       <c r="H284" t="n">
-        <v>6.432526539278131</v>
+        <v>6.436973125884013</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -22240,16 +22240,16 @@
         <v>1</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.3874734607218695</v>
+        <v>-0.3830268741159868</v>
       </c>
       <c r="N284" t="n">
-        <v>0.3874734607218695</v>
+        <v>0.3830268741159868</v>
       </c>
       <c r="O284" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P284" t="n">
-        <v>-0.07857041755131</v>
+        <v>-0.07557284299858846</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -22289,10 +22289,10 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>0.9016277423920736</v>
+        <v>0.9016973125884017</v>
       </c>
       <c r="H285" t="n">
-        <v>6.401493276716207</v>
+        <v>6.40187765205092</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -22311,16 +22311,16 @@
         <v>1</v>
       </c>
       <c r="M285" t="n">
-        <v>-0.2985067232837935</v>
+        <v>-0.2981223479490804</v>
       </c>
       <c r="N285" t="n">
-        <v>0.2985067232837935</v>
+        <v>0.2981223479490804</v>
       </c>
       <c r="O285" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P285" t="n">
-        <v>-0.03103326256192407</v>
+        <v>-0.03509547383309375</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
@@ -22360,10 +22360,10 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>0.8987968860580325</v>
+        <v>0.8988684582743989</v>
       </c>
       <c r="H286" t="n">
-        <v>6.353411181882518</v>
+        <v>6.354992927864215</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -22382,16 +22382,16 @@
         <v>1</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.1865888181174817</v>
+        <v>-0.185007072135785</v>
       </c>
       <c r="N286" t="n">
-        <v>0.1865888181174817</v>
+        <v>0.185007072135785</v>
       </c>
       <c r="O286" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P286" t="n">
-        <v>-0.04808209483368842</v>
+        <v>-0.04688472418670475</v>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
@@ -25685,10 +25685,10 @@
         <v>8</v>
       </c>
       <c r="G333" t="n">
-        <v>0.7636234961075725</v>
+        <v>0.7637906647807637</v>
       </c>
       <c r="H333" t="n">
-        <v>6.483290870488323</v>
+        <v>6.484236209335219</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -25707,16 +25707,16 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.7792091295116776</v>
+        <v>-0.7782637906647807</v>
       </c>
       <c r="N333" t="n">
-        <v>0.7792091295116776</v>
+        <v>0.7782637906647807</v>
       </c>
       <c r="O333" t="n">
         <v>-0.4400000000000004</v>
       </c>
       <c r="P333" t="n">
-        <v>-0.9842143852930363</v>
+        <v>-0.9832690464461393</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -25756,10 +25756,10 @@
         <v>8</v>
       </c>
       <c r="G334" t="n">
-        <v>0.7721160651096957</v>
+        <v>0.7722772277227723</v>
       </c>
       <c r="H334" t="n">
-        <v>6.536743630573248</v>
+        <v>6.537085396039604</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -25778,16 +25778,16 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.4382563694267514</v>
+        <v>-0.4379146039603956</v>
       </c>
       <c r="N334" t="n">
-        <v>0.4382563694267514</v>
+        <v>0.4379146039603956</v>
       </c>
       <c r="O334" t="n">
         <v>-0.2875000000000005</v>
       </c>
       <c r="P334" t="n">
-        <v>0.05345276008492572</v>
+        <v>0.05284918670438454</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -25827,10 +25827,10 @@
         <v>8</v>
       </c>
       <c r="G335" t="n">
-        <v>0.7919320594479831</v>
+        <v>0.7920792079207921</v>
       </c>
       <c r="H335" t="n">
-        <v>6.641687898089172</v>
+        <v>6.64210396039604</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -25849,16 +25849,16 @@
         <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.1583121019108278</v>
+        <v>-0.1578960396039601</v>
       </c>
       <c r="N335" t="n">
-        <v>0.1583121019108278</v>
+        <v>0.1578960396039601</v>
       </c>
       <c r="O335" t="n">
         <v>-0.1749999999999998</v>
       </c>
       <c r="P335" t="n">
-        <v>0.1049442675159238</v>
+        <v>0.1050185643564356</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -25898,10 +25898,10 @@
         <v>8</v>
       </c>
       <c r="G336" t="n">
-        <v>0.8145789101203114</v>
+        <v>0.8147100424328148</v>
       </c>
       <c r="H336" t="n">
-        <v>6.846443736730361</v>
+        <v>6.847185289957567</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -25920,16 +25920,16 @@
         <v>1</v>
       </c>
       <c r="M336" t="n">
-        <v>0.2164437367303611</v>
+        <v>0.217185289957567</v>
       </c>
       <c r="N336" t="n">
-        <v>0.2164437367303611</v>
+        <v>0.217185289957567</v>
       </c>
       <c r="O336" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P336" t="n">
-        <v>0.204755838641189</v>
+        <v>0.2050813295615272</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -25969,10 +25969,10 @@
         <v>8</v>
       </c>
       <c r="G337" t="n">
-        <v>0.8343949044585988</v>
+        <v>0.8345120226308345</v>
       </c>
       <c r="H337" t="n">
-        <v>7.063503184713376</v>
+        <v>7.064165487977369</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -25991,16 +25991,16 @@
         <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>0.5735031847133758</v>
+        <v>0.5741654879773685</v>
       </c>
       <c r="N337" t="n">
-        <v>0.5735031847133758</v>
+        <v>0.5741654879773685</v>
       </c>
       <c r="O337" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P337" t="n">
-        <v>0.217059447983015</v>
+        <v>0.2169801980198018</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>8</v>
       </c>
       <c r="G338" t="n">
-        <v>0.8506723283793347</v>
+        <v>0.8507779349363508</v>
       </c>
       <c r="H338" t="n">
-        <v>7.148110403397028</v>
+        <v>7.148229844413013</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -26062,16 +26062,16 @@
         <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>0.6681104033970273</v>
+        <v>0.6682298444130126</v>
       </c>
       <c r="N338" t="n">
-        <v>0.6681104033970273</v>
+        <v>0.6682298444130126</v>
       </c>
       <c r="O338" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P338" t="n">
-        <v>0.08460721868365173</v>
+        <v>0.08406435643564425</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -26111,10 +26111,10 @@
         <v>8</v>
       </c>
       <c r="G339" t="n">
-        <v>0.8577494692144374</v>
+        <v>0.8578500707213579</v>
       </c>
       <c r="H339" t="n">
-        <v>7.203073248407644</v>
+        <v>7.203642149929279</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -26133,16 +26133,16 @@
         <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>0.6530732484076438</v>
+        <v>0.6536421499292793</v>
       </c>
       <c r="N339" t="n">
-        <v>0.6530732484076438</v>
+        <v>0.6536421499292793</v>
       </c>
       <c r="O339" t="n">
         <v>0.0699999999999994</v>
       </c>
       <c r="P339" t="n">
-        <v>0.05496284501061588</v>
+        <v>0.05541230551626608</v>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
@@ -26182,10 +26182,10 @@
         <v>8</v>
       </c>
       <c r="G340" t="n">
-        <v>0.8499646142958245</v>
+        <v>0.8500707213578501</v>
       </c>
       <c r="H340" t="n">
-        <v>7.147309978768577</v>
+        <v>7.147429985855728</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -26204,16 +26204,16 @@
         <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>0.617309978768577</v>
+        <v>0.6174299858557282</v>
       </c>
       <c r="N340" t="n">
-        <v>0.617309978768577</v>
+        <v>0.6174299858557282</v>
       </c>
       <c r="O340" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P340" t="n">
-        <v>-0.05576326963906642</v>
+        <v>-0.05621216407355067</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -26253,10 +26253,10 @@
         <v>8</v>
       </c>
       <c r="G341" t="n">
-        <v>0.8301486199575372</v>
+        <v>0.8302687411598303</v>
       </c>
       <c r="H341" t="n">
-        <v>7.022653927813163</v>
+        <v>7.023559641678453</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -26275,16 +26275,16 @@
         <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>0.6901539278131636</v>
+        <v>0.6910596416784536</v>
       </c>
       <c r="N341" t="n">
-        <v>0.6901539278131636</v>
+        <v>0.6910596416784536</v>
       </c>
       <c r="O341" t="n">
         <v>-0.1975000000000007</v>
       </c>
       <c r="P341" t="n">
-        <v>-0.124656050955414</v>
+        <v>-0.1238703441772753</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -26324,10 +26324,10 @@
         <v>8</v>
       </c>
       <c r="G342" t="n">
-        <v>0.8103326256192498</v>
+        <v>0.8104667609618105</v>
       </c>
       <c r="H342" t="n">
-        <v>6.819357749469215</v>
+        <v>6.81954738330976</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -26346,16 +26346,16 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>0.6293577494692144</v>
+        <v>0.6295473833097596</v>
       </c>
       <c r="N342" t="n">
-        <v>0.6293577494692144</v>
+        <v>0.6295473833097596</v>
       </c>
       <c r="O342" t="n">
         <v>-0.1424999999999992</v>
       </c>
       <c r="P342" t="n">
-        <v>-0.2032961783439484</v>
+        <v>-0.2040122583686932</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>8</v>
       </c>
       <c r="G343" t="n">
-        <v>0.7869780608634112</v>
+        <v>0.7871287128712872</v>
       </c>
       <c r="H343" t="n">
         <v>6.619999999999999</v>
@@ -26426,7 +26426,7 @@
         <v>-0.2000000000000002</v>
       </c>
       <c r="P343" t="n">
-        <v>-0.1993577494692156</v>
+        <v>-0.1995473833097607</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -26466,10 +26466,10 @@
         <v>8</v>
       </c>
       <c r="G344" t="n">
-        <v>0.7629157820240623</v>
+        <v>0.7630834512022631</v>
       </c>
       <c r="H344" t="n">
-        <v>6.479525831564048</v>
+        <v>6.480236916548797</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -26488,16 +26488,16 @@
         <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5595258315640486</v>
+        <v>0.5602369165487975</v>
       </c>
       <c r="N344" t="n">
-        <v>0.5595258315640486</v>
+        <v>0.5602369165487975</v>
       </c>
       <c r="O344" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P344" t="n">
-        <v>-0.1404741684359507</v>
+        <v>-0.1397630834512018</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>8</v>
       </c>
       <c r="G345" t="n">
-        <v>0.7409766454352441</v>
+        <v>0.7411598302687411</v>
       </c>
       <c r="H345" t="n">
         <v>6.38</v>
@@ -26568,7 +26568,7 @@
         <v>0.0600000000000005</v>
       </c>
       <c r="P345" t="n">
-        <v>-0.09952583156404859</v>
+        <v>-0.1002369165487975</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -26608,10 +26608,10 @@
         <v>8</v>
       </c>
       <c r="G346" t="n">
-        <v>0.7176220806794055</v>
+        <v>0.7178217821782178</v>
       </c>
       <c r="H346" t="n">
-        <v>6.22953821656051</v>
+        <v>6.229820544554456</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -26630,16 +26630,16 @@
         <v>1</v>
       </c>
       <c r="M346" t="n">
-        <v>0.1095382165605097</v>
+        <v>0.1098205445544558</v>
       </c>
       <c r="N346" t="n">
-        <v>0.1095382165605097</v>
+        <v>0.1098205445544558</v>
       </c>
       <c r="O346" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P346" t="n">
-        <v>-0.1504617834394901</v>
+        <v>-0.150179455445544</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -27809,10 +27809,10 @@
         <v>8</v>
       </c>
       <c r="G363" t="n">
-        <v>0.6447275300778486</v>
+        <v>0.6449787835926449</v>
       </c>
       <c r="H363" t="n">
-        <v>6.969218860580326</v>
+        <v>6.969437765205091</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -27831,16 +27831,16 @@
         <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>-1.493281139419675</v>
+        <v>-1.493062234794909</v>
       </c>
       <c r="N363" t="n">
-        <v>1.493281139419675</v>
+        <v>1.493062234794909</v>
       </c>
       <c r="O363" t="n">
         <v>-0.254999999999999</v>
       </c>
       <c r="P363" t="n">
-        <v>0.1266382719328139</v>
+        <v>0.1268571765575794</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -27880,10 +27880,10 @@
         <v>8</v>
       </c>
       <c r="G364" t="n">
-        <v>0.6532200990799717</v>
+        <v>0.6534653465346535</v>
       </c>
       <c r="H364" t="n">
-        <v>7.002944090587403</v>
+        <v>7.004653465346535</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -27902,16 +27902,16 @@
         <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>-1.309555909412597</v>
+        <v>-1.307846534653465</v>
       </c>
       <c r="N364" t="n">
-        <v>1.309555909412597</v>
+        <v>1.307846534653465</v>
       </c>
       <c r="O364" t="n">
         <v>-0.1500000000000004</v>
       </c>
       <c r="P364" t="n">
-        <v>0.03372523000707695</v>
+        <v>0.03521570014144348</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -27951,10 +27951,10 @@
         <v>8</v>
       </c>
       <c r="G365" t="n">
-        <v>0.6659589525831564</v>
+        <v>0.6661951909476662</v>
       </c>
       <c r="H365" t="n">
-        <v>7.065866949752301</v>
+        <v>7.066690240452617</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -27973,16 +27973,16 @@
         <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>-1.0641330502477</v>
+        <v>-1.063309759547383</v>
       </c>
       <c r="N365" t="n">
-        <v>1.0641330502477</v>
+        <v>1.063309759547383</v>
       </c>
       <c r="O365" t="n">
         <v>-0.1824999999999992</v>
       </c>
       <c r="P365" t="n">
-        <v>0.06292285916489782</v>
+        <v>0.06203677510608241</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -28022,10 +28022,10 @@
         <v>8</v>
       </c>
       <c r="G366" t="n">
-        <v>0.6801132342533617</v>
+        <v>0.6803394625176803</v>
       </c>
       <c r="H366" t="n">
-        <v>7.163343949044585</v>
+        <v>7.16423090523338</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -28044,16 +28044,16 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.924156050955415</v>
+        <v>-0.9232690947666207</v>
       </c>
       <c r="N366" t="n">
-        <v>0.924156050955415</v>
+        <v>0.9232690947666207</v>
       </c>
       <c r="O366" t="n">
         <v>-0.04250000000000043</v>
       </c>
       <c r="P366" t="n">
-        <v>0.09747699929228482</v>
+        <v>0.0975406647807624</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -28093,10 +28093,10 @@
         <v>8</v>
       </c>
       <c r="G367" t="n">
-        <v>0.6878980891719745</v>
+        <v>0.6881188118811881</v>
       </c>
       <c r="H367" t="n">
-        <v>7.191831210191084</v>
+        <v>7.192023514851486</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -28115,16 +28115,16 @@
         <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>-1.038168789808917</v>
+        <v>-1.037976485148515</v>
       </c>
       <c r="N367" t="n">
-        <v>1.038168789808917</v>
+        <v>1.037976485148515</v>
       </c>
       <c r="O367" t="n">
         <v>0.1425000000000001</v>
       </c>
       <c r="P367" t="n">
-        <v>0.02848726114649835</v>
+        <v>0.02779260961810603</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -28164,10 +28164,10 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>0.689313517338995</v>
+        <v>0.6895332390381895</v>
       </c>
       <c r="H368" t="n">
-        <v>7.195133875914131</v>
+        <v>7.196027227722773</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -28186,16 +28186,16 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.8473661240858696</v>
+        <v>-0.8464727722772274</v>
       </c>
       <c r="N368" t="n">
-        <v>0.8473661240858696</v>
+        <v>0.8464727722772274</v>
       </c>
       <c r="O368" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P368" t="n">
-        <v>0.003302665723047049</v>
+        <v>0.004003712871287313</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -28235,10 +28235,10 @@
         <v>8</v>
       </c>
       <c r="G369" t="n">
-        <v>0.6836518046709129</v>
+        <v>0.6838755304101839</v>
       </c>
       <c r="H369" t="n">
-        <v>7.177217356687898</v>
+        <v>7.178094501414427</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -28257,16 +28257,16 @@
         <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.7727826433121026</v>
+        <v>-0.7719054985855731</v>
       </c>
       <c r="N369" t="n">
-        <v>0.7727826433121026</v>
+        <v>0.7719054985855731</v>
       </c>
       <c r="O369" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P369" t="n">
-        <v>-0.01791651922623316</v>
+        <v>-0.01793272630834597</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -28306,10 +28306,10 @@
         <v>8</v>
       </c>
       <c r="G370" t="n">
-        <v>0.6716206652512385</v>
+        <v>0.6718528995756718</v>
       </c>
       <c r="H370" t="n">
-        <v>7.110598018400567</v>
+        <v>7.111407355021217</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -28328,16 +28328,16 @@
         <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.8694019815994336</v>
+        <v>-0.8685926449787837</v>
       </c>
       <c r="N370" t="n">
-        <v>0.8694019815994336</v>
+        <v>0.8685926449787837</v>
       </c>
       <c r="O370" t="n">
         <v>0.03000000000000025</v>
       </c>
       <c r="P370" t="n">
-        <v>-0.0666193382873308</v>
+        <v>-0.06668714639321038</v>
       </c>
       <c r="Q370" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>8</v>
       </c>
       <c r="G371" t="n">
-        <v>0.6525123849964615</v>
+        <v>0.6527581329561527</v>
       </c>
       <c r="H371" t="n">
-        <v>6.998011323425336</v>
+        <v>6.999724186704384</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -28399,16 +28399,16 @@
         <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>-1.036988676574664</v>
+        <v>-1.035275813295616</v>
       </c>
       <c r="N371" t="n">
-        <v>1.036988676574664</v>
+        <v>1.035275813295616</v>
       </c>
       <c r="O371" t="n">
         <v>0.05499999999999972</v>
       </c>
       <c r="P371" t="n">
-        <v>-0.1125866949752306</v>
+        <v>-0.1116831683168327</v>
       </c>
       <c r="Q371" t="inlineStr">
         <is>
@@ -28448,10 +28448,10 @@
         <v>8</v>
       </c>
       <c r="G372" t="n">
-        <v>0.6305732484076433</v>
+        <v>0.6308345120226309</v>
       </c>
       <c r="H372" t="n">
-        <v>6.935047770700637</v>
+        <v>6.935958274398868</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -28470,16 +28470,16 @@
         <v>1</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.9749522292993635</v>
+        <v>-0.9740417256011318</v>
       </c>
       <c r="N372" t="n">
-        <v>0.9749522292993635</v>
+        <v>0.9740417256011318</v>
       </c>
       <c r="O372" t="n">
         <v>-0.125</v>
       </c>
       <c r="P372" t="n">
-        <v>-0.06296355272469967</v>
+        <v>-0.06376591230551565</v>
       </c>
       <c r="Q372" t="inlineStr">
         <is>
@@ -28519,10 +28519,10 @@
         <v>8</v>
       </c>
       <c r="G373" t="n">
-        <v>0.6157112526539278</v>
+        <v>0.615983026874116</v>
       </c>
       <c r="H373" t="n">
-        <v>6.878442144373674</v>
+        <v>6.879626060820368</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -28541,16 +28541,16 @@
         <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.8115578556263268</v>
+        <v>-0.8103739391796321</v>
       </c>
       <c r="N373" t="n">
-        <v>0.8115578556263268</v>
+        <v>0.8103739391796321</v>
       </c>
       <c r="O373" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P373" t="n">
-        <v>-0.05660562632696298</v>
+        <v>-0.05633221357850005</v>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
@@ -28590,10 +28590,10 @@
         <v>8</v>
       </c>
       <c r="G374" t="n">
-        <v>0.5980184005661713</v>
+        <v>0.5983026874115983</v>
       </c>
       <c r="H374" t="n">
-        <v>6.798523531493277</v>
+        <v>6.798771216407355</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -28612,16 +28612,16 @@
         <v>1</v>
       </c>
       <c r="M374" t="n">
-        <v>-0.6614764685067227</v>
+        <v>-0.6612287835926445</v>
       </c>
       <c r="N374" t="n">
-        <v>0.6614764685067227</v>
+        <v>0.6612287835926445</v>
       </c>
       <c r="O374" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P374" t="n">
-        <v>-0.07991861288039637</v>
+        <v>-0.08085484441301283</v>
       </c>
       <c r="Q374" t="inlineStr">
         <is>
@@ -28661,10 +28661,10 @@
         <v>8</v>
       </c>
       <c r="G375" t="n">
-        <v>0.5831564048124558</v>
+        <v>0.5834512022630834</v>
       </c>
       <c r="H375" t="n">
-        <v>6.760575017692852</v>
+        <v>6.760831859971711</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -28683,16 +28683,16 @@
         <v>1</v>
       </c>
       <c r="M375" t="n">
-        <v>-0.5194249823071484</v>
+        <v>-0.519168140028289</v>
       </c>
       <c r="N375" t="n">
-        <v>0.5194249823071484</v>
+        <v>0.519168140028289</v>
       </c>
       <c r="O375" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.03794851380042541</v>
+        <v>-0.03793935643564428</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
@@ -28732,10 +28732,10 @@
         <v>8</v>
       </c>
       <c r="G376" t="n">
-        <v>0.5647558386411889</v>
+        <v>0.5650636492220651</v>
       </c>
       <c r="H376" t="n">
-        <v>6.679087048832272</v>
+        <v>6.679623408769448</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -28754,16 +28754,16 @@
         <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>-0.4309129511677288</v>
+        <v>-0.4303765912305524</v>
       </c>
       <c r="N376" t="n">
-        <v>0.4309129511677288</v>
+        <v>0.4303765912305524</v>
       </c>
       <c r="O376" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.0814879688605803</v>
+        <v>-0.08120845120226328</v>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
@@ -29933,10 +29933,10 @@
         <v>8</v>
       </c>
       <c r="G393" t="n">
-        <v>0.6588818117480538</v>
+        <v>0.6591230551626591</v>
       </c>
       <c r="H393" t="n">
-        <v>5.822154989384289</v>
+        <v>5.825961810466762</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -29955,16 +29955,16 @@
         <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>1.032154989384289</v>
+        <v>1.035961810466761</v>
       </c>
       <c r="N393" t="n">
-        <v>1.032154989384289</v>
+        <v>1.035961810466761</v>
       </c>
       <c r="O393" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P393" t="n">
-        <v>-0.6433670848974202</v>
+        <v>-0.639560263814948</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
@@ -30004,10 +30004,10 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>0.5647558386411889</v>
+        <v>0.5643564356435643</v>
       </c>
       <c r="H394" t="n">
-        <v>5.501480891719745</v>
+        <v>5.500693069306931</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -30026,16 +30026,16 @@
         <v>1</v>
       </c>
       <c r="M394" t="n">
-        <v>0.8314808917197452</v>
+        <v>0.830693069306931</v>
       </c>
       <c r="N394" t="n">
-        <v>0.8314808917197452</v>
+        <v>0.830693069306931</v>
       </c>
       <c r="O394" t="n">
         <v>-0.120000000000001</v>
       </c>
       <c r="P394" t="n">
-        <v>-0.3206740976645444</v>
+        <v>-0.3252687411598307</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -30075,10 +30075,10 @@
         <v>8</v>
       </c>
       <c r="G395" t="n">
-        <v>0.5428167020523709</v>
+        <v>0.5424328147100425</v>
       </c>
       <c r="H395" t="n">
-        <v>5.456901981599434</v>
+        <v>5.456649575671853</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -30097,16 +30097,16 @@
         <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>0.9169019815994339</v>
+        <v>0.9166495756718529</v>
       </c>
       <c r="N395" t="n">
-        <v>0.9169019815994339</v>
+        <v>0.9166495756718529</v>
       </c>
       <c r="O395" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P395" t="n">
-        <v>-0.04457891012031112</v>
+        <v>-0.04404349363507798</v>
       </c>
       <c r="Q395" t="inlineStr">
         <is>
@@ -30146,10 +30146,10 @@
         <v>8</v>
       </c>
       <c r="G396" t="n">
-        <v>0.5958952583156405</v>
+        <v>0.5961810466760962</v>
       </c>
       <c r="H396" t="n">
-        <v>5.636801132342534</v>
+        <v>5.636989038189533</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -30168,16 +30168,16 @@
         <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>1.196801132342533</v>
+        <v>1.196989038189533</v>
       </c>
       <c r="N396" t="n">
-        <v>1.196801132342533</v>
+        <v>1.196989038189533</v>
       </c>
       <c r="O396" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P396" t="n">
-        <v>0.1798991507430996</v>
+        <v>0.1803394625176802</v>
       </c>
       <c r="Q396" t="inlineStr">
         <is>
@@ -30217,10 +30217,10 @@
         <v>8</v>
       </c>
       <c r="G397" t="n">
-        <v>0.6341118188251946</v>
+        <v>0.6343705799151343</v>
       </c>
       <c r="H397" t="n">
-        <v>5.756928520877566</v>
+        <v>5.757098656294201</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -30239,16 +30239,16 @@
         <v>1</v>
       </c>
       <c r="M397" t="n">
-        <v>1.316928520877566</v>
+        <v>1.317098656294201</v>
       </c>
       <c r="N397" t="n">
-        <v>1.316928520877566</v>
+        <v>1.317098656294201</v>
       </c>
       <c r="O397" t="n">
         <v>0</v>
       </c>
       <c r="P397" t="n">
-        <v>0.1201273885350327</v>
+        <v>0.1201096181046681</v>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>8</v>
       </c>
       <c r="G398" t="n">
-        <v>0.5944798301486199</v>
+        <v>0.5947666195190948</v>
       </c>
       <c r="H398" t="n">
-        <v>5.635870488322718</v>
+        <v>5.636059052333805</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -30310,16 +30310,16 @@
         <v>1</v>
       </c>
       <c r="M398" t="n">
-        <v>1.235870488322718</v>
+        <v>1.236059052333805</v>
       </c>
       <c r="N398" t="n">
-        <v>1.235870488322718</v>
+        <v>1.236059052333805</v>
       </c>
       <c r="O398" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P398" t="n">
-        <v>-0.1210580325548483</v>
+        <v>-0.121039603960396</v>
       </c>
       <c r="Q398" t="inlineStr">
         <is>
@@ -30359,10 +30359,10 @@
         <v>8</v>
       </c>
       <c r="G399" t="n">
-        <v>0.4791224345364473</v>
+        <v>0.4787835926449788</v>
       </c>
       <c r="H399" t="n">
-        <v>5.190138004246285</v>
+        <v>5.189800212164074</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -30381,16 +30381,16 @@
         <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>0.8101380042462853</v>
+        <v>0.8098002121640739</v>
       </c>
       <c r="N399" t="n">
-        <v>0.8101380042462853</v>
+        <v>0.8098002121640739</v>
       </c>
       <c r="O399" t="n">
         <v>-0.02000000000000046</v>
       </c>
       <c r="P399" t="n">
-        <v>-0.4457324840764327</v>
+        <v>-0.4462588401697314</v>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
@@ -30430,10 +30430,10 @@
         <v>8</v>
       </c>
       <c r="G400" t="n">
-        <v>0.3701344656758669</v>
+        <v>0.3698727015558699</v>
       </c>
       <c r="H400" t="n">
-        <v>4.843363411181882</v>
+        <v>4.843191301272984</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -30452,16 +30452,16 @@
         <v>1</v>
       </c>
       <c r="M400" t="n">
-        <v>0.7033634111818827</v>
+        <v>0.7031913012729847</v>
       </c>
       <c r="N400" t="n">
-        <v>0.7033634111818827</v>
+        <v>0.7031913012729847</v>
       </c>
       <c r="O400" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P400" t="n">
-        <v>-0.3467745930644028</v>
+        <v>-0.3466089108910895</v>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
@@ -30501,10 +30501,10 @@
         <v>8</v>
       </c>
       <c r="G401" t="n">
-        <v>0.3255484784147205</v>
+        <v>0.3253182461103253</v>
       </c>
       <c r="H401" t="n">
-        <v>4.701077494692145</v>
+        <v>4.699260961810467</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -30523,16 +30523,16 @@
         <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>0.8310774946921446</v>
+        <v>0.8292609618104674</v>
       </c>
       <c r="N401" t="n">
-        <v>0.8310774946921446</v>
+        <v>0.8292609618104674</v>
       </c>
       <c r="O401" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P401" t="n">
-        <v>-0.1422859164897377</v>
+        <v>-0.1439303394625169</v>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
@@ -30572,10 +30572,10 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>0.3517338995046002</v>
+        <v>0.3514851485148515</v>
       </c>
       <c r="H402" t="n">
-        <v>4.806265038924274</v>
+        <v>4.806101485148515</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -30594,16 +30594,16 @@
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>1.086265038924274</v>
+        <v>1.086101485148515</v>
       </c>
       <c r="N402" t="n">
-        <v>1.086265038924274</v>
+        <v>1.086101485148515</v>
       </c>
       <c r="O402" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P402" t="n">
-        <v>0.1051875442321295</v>
+        <v>0.1068405233380476</v>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -30643,10 +30643,10 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>0.5300778485491862</v>
+        <v>0.5297029702970297</v>
       </c>
       <c r="H403" t="n">
-        <v>5.44205237084218</v>
+        <v>5.441559405940594</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -30665,16 +30665,16 @@
         <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>1.742052370842179</v>
+        <v>1.741559405940594</v>
       </c>
       <c r="N403" t="n">
-        <v>1.742052370842179</v>
+        <v>1.741559405940594</v>
       </c>
       <c r="O403" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P403" t="n">
-        <v>0.6357873319179053</v>
+        <v>0.6354579207920787</v>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>8</v>
       </c>
       <c r="G404" t="n">
-        <v>0.7607926397735315</v>
+        <v>0.7609618104667609</v>
       </c>
       <c r="H404" t="n">
-        <v>6.101769285208776</v>
+        <v>6.102659123055163</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -30736,16 +30736,16 @@
         <v>1</v>
       </c>
       <c r="M404" t="n">
-        <v>2.261769285208776</v>
+        <v>2.262659123055163</v>
       </c>
       <c r="N404" t="n">
-        <v>2.261769285208776</v>
+        <v>2.262659123055163</v>
       </c>
       <c r="O404" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P404" t="n">
-        <v>0.6597169143665962</v>
+        <v>0.6610997171145687</v>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
@@ -30785,10 +30785,10 @@
         <v>8</v>
       </c>
       <c r="G405" t="n">
-        <v>0.8315640481245576</v>
+        <v>0.8316831683168316</v>
       </c>
       <c r="H405" t="n">
-        <v>6.34578025477707</v>
+        <v>6.346485148514851</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -30807,16 +30807,16 @@
         <v>1</v>
       </c>
       <c r="M405" t="n">
-        <v>2.325780254777071</v>
+        <v>2.326485148514852</v>
       </c>
       <c r="N405" t="n">
-        <v>2.325780254777071</v>
+        <v>2.326485148514852</v>
       </c>
       <c r="O405" t="n">
         <v>0.1799999999999997</v>
       </c>
       <c r="P405" t="n">
-        <v>0.2440109695682944</v>
+        <v>0.2438260254596889</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
@@ -30856,10 +30856,10 @@
         <v>8</v>
       </c>
       <c r="G406" t="n">
-        <v>0.8159943382873319</v>
+        <v>0.8161244695898161</v>
       </c>
       <c r="H406" t="n">
-        <v>6.292662774239208</v>
+        <v>6.293518387553041</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -30878,16 +30878,16 @@
         <v>1</v>
       </c>
       <c r="M406" t="n">
-        <v>2.192662774239208</v>
+        <v>2.193518387553041</v>
       </c>
       <c r="N406" t="n">
-        <v>2.192662774239208</v>
+        <v>2.193518387553041</v>
       </c>
       <c r="O406" t="n">
         <v>0.08000000000000007</v>
       </c>
       <c r="P406" t="n">
-        <v>-0.05311748053786225</v>
+        <v>-0.05296676096181052</v>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
@@ -32057,10 +32057,10 @@
         <v>8</v>
       </c>
       <c r="G423" t="n">
-        <v>0.8294409058740269</v>
+        <v>0.8295615275813296</v>
       </c>
       <c r="H423" t="n">
-        <v>5.563673036093418</v>
+        <v>5.564450141442715</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -32079,16 +32079,16 @@
         <v>1</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.803826963906582</v>
+        <v>-0.8030498585572845</v>
       </c>
       <c r="N423" t="n">
-        <v>0.803826963906582</v>
+        <v>0.8030498585572845</v>
       </c>
       <c r="O423" t="n">
         <v>-0.07500000000000018</v>
       </c>
       <c r="P423" t="n">
-        <v>-1.475256536436365</v>
+        <v>-1.474479431087067</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
@@ -32128,10 +32128,10 @@
         <v>8</v>
       </c>
       <c r="G424" t="n">
-        <v>0.8273177636234961</v>
+        <v>0.8274398868458275</v>
       </c>
       <c r="H424" t="n">
-        <v>5.548329794762916</v>
+        <v>5.548854314002829</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -32150,16 +32150,16 @@
         <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>-0.7691702052370841</v>
+        <v>-0.7686456859971713</v>
       </c>
       <c r="N424" t="n">
-        <v>0.7691702052370841</v>
+        <v>0.7686456859971713</v>
       </c>
       <c r="O424" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P424" t="n">
-        <v>-0.01534324133050191</v>
+        <v>-0.01559582743988663</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -32199,10 +32199,10 @@
         <v>8</v>
       </c>
       <c r="G425" t="n">
-        <v>0.8209483368719037</v>
+        <v>0.8210749646393211</v>
       </c>
       <c r="H425" t="n">
-        <v>5.501946213729653</v>
+        <v>5.503033946251768</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -32221,16 +32221,16 @@
         <v>1</v>
       </c>
       <c r="M425" t="n">
-        <v>-0.7580537862703469</v>
+        <v>-0.7569660537482319</v>
       </c>
       <c r="N425" t="n">
-        <v>0.7580537862703469</v>
+        <v>0.7569660537482319</v>
       </c>
       <c r="O425" t="n">
         <v>-0.05750000000000011</v>
       </c>
       <c r="P425" t="n">
-        <v>-0.0463835810332629</v>
+        <v>-0.04582036775106069</v>
       </c>
       <c r="Q425" t="inlineStr">
         <is>
@@ -32270,10 +32270,10 @@
         <v>8</v>
       </c>
       <c r="G426" t="n">
-        <v>0.8181174805378627</v>
+        <v>0.8182461103253182</v>
       </c>
       <c r="H426" t="n">
-        <v>5.488221868365181</v>
+        <v>5.489050565770864</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -32292,16 +32292,16 @@
         <v>1</v>
       </c>
       <c r="M426" t="n">
-        <v>-0.641778131634819</v>
+        <v>-0.6409494342291362</v>
       </c>
       <c r="N426" t="n">
-        <v>0.641778131634819</v>
+        <v>0.6409494342291362</v>
       </c>
       <c r="O426" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P426" t="n">
-        <v>-0.01372434536447198</v>
+        <v>-0.0139833804809042</v>
       </c>
       <c r="Q426" t="inlineStr">
         <is>
@@ -32341,10 +32341,10 @@
         <v>8</v>
       </c>
       <c r="G427" t="n">
-        <v>0.8089171974522293</v>
+        <v>0.809052333804809</v>
       </c>
       <c r="H427" t="n">
-        <v>5.382149681528662</v>
+        <v>5.382439886845827</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -32363,16 +32363,16 @@
         <v>1</v>
       </c>
       <c r="M427" t="n">
-        <v>-0.6078503184713382</v>
+        <v>-0.6075601131541735</v>
       </c>
       <c r="N427" t="n">
-        <v>0.6078503184713382</v>
+        <v>0.6075601131541735</v>
       </c>
       <c r="O427" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P427" t="n">
-        <v>-0.1060721868365189</v>
+        <v>-0.106610678925037</v>
       </c>
       <c r="Q427" t="inlineStr">
         <is>
@@ -32412,10 +32412,10 @@
         <v>8</v>
       </c>
       <c r="G428" t="n">
-        <v>0.7883934890304317</v>
+        <v>0.7885431400282885</v>
       </c>
       <c r="H428" t="n">
-        <v>5.228075017692852</v>
+        <v>5.22839639321075</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -32434,16 +32434,16 @@
         <v>1</v>
       </c>
       <c r="M428" t="n">
-        <v>-0.4794249823071475</v>
+        <v>-0.4791036067892493</v>
       </c>
       <c r="N428" t="n">
-        <v>0.4794249823071475</v>
+        <v>0.4791036067892493</v>
       </c>
       <c r="O428" t="n">
         <v>-0.2825000000000006</v>
       </c>
       <c r="P428" t="n">
-        <v>-0.1540746638358099</v>
+        <v>-0.1540434936350765</v>
       </c>
       <c r="Q428" t="inlineStr">
         <is>
@@ -32483,10 +32483,10 @@
         <v>8</v>
       </c>
       <c r="G429" t="n">
-        <v>0.7707006369426752</v>
+        <v>0.7708628005657708</v>
       </c>
       <c r="H429" t="n">
-        <v>5.10015923566879</v>
+        <v>5.100855728429986</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
@@ -32505,16 +32505,16 @@
         <v>1</v>
       </c>
       <c r="M429" t="n">
-        <v>-0.4598407643312097</v>
+        <v>-0.4591442715700138</v>
       </c>
       <c r="N429" t="n">
-        <v>0.4598407643312097</v>
+        <v>0.4591442715700138</v>
       </c>
       <c r="O429" t="n">
         <v>-0.1475</v>
       </c>
       <c r="P429" t="n">
-        <v>-0.1279157820240622</v>
+        <v>-0.1275406647807644</v>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
@@ -32554,10 +32554,10 @@
         <v>8</v>
       </c>
       <c r="G430" t="n">
-        <v>0.745930644019816</v>
+        <v>0.7461103253182461</v>
       </c>
       <c r="H430" t="n">
-        <v>4.948772116065109</v>
+        <v>4.949543847241867</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -32576,16 +32576,16 @@
         <v>1</v>
       </c>
       <c r="M430" t="n">
-        <v>-0.3912278839348904</v>
+        <v>-0.3904561527581327</v>
       </c>
       <c r="N430" t="n">
-        <v>0.3912278839348904</v>
+        <v>0.3904561527581327</v>
       </c>
       <c r="O430" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P430" t="n">
-        <v>-0.1513871196036805</v>
+        <v>-0.1513118811881187</v>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
@@ -32625,10 +32625,10 @@
         <v>8</v>
       </c>
       <c r="G431" t="n">
-        <v>0.719037508846426</v>
+        <v>0.7185289957567186</v>
       </c>
       <c r="H431" t="n">
-        <v>4.82</v>
+        <v>4.819999999999999</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
@@ -32647,16 +32647,16 @@
         <v>1</v>
       </c>
       <c r="M431" t="n">
-        <v>-0.2924999999999995</v>
+        <v>-0.2925000000000004</v>
       </c>
       <c r="N431" t="n">
-        <v>0.2924999999999995</v>
+        <v>0.2925000000000004</v>
       </c>
       <c r="O431" t="n">
         <v>-0.2275</v>
       </c>
       <c r="P431" t="n">
-        <v>-0.1287721160651092</v>
+        <v>-0.1295438472418677</v>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
@@ -32696,10 +32696,10 @@
         <v>8</v>
       </c>
       <c r="G432" t="n">
-        <v>0.6949752300070772</v>
+        <v>0.6944837340876945</v>
       </c>
       <c r="H432" t="n">
-        <v>4.652459306440198</v>
+        <v>4.651403818953324</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -32718,16 +32718,16 @@
         <v>1</v>
       </c>
       <c r="M432" t="n">
-        <v>-0.3575406935598018</v>
+        <v>-0.3585961810466758</v>
       </c>
       <c r="N432" t="n">
-        <v>0.3575406935598018</v>
+        <v>0.3585961810466758</v>
       </c>
       <c r="O432" t="n">
         <v>-0.1025</v>
       </c>
       <c r="P432" t="n">
-        <v>-0.1675406935598023</v>
+        <v>-0.1685961810466754</v>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
@@ -32767,10 +32767,10 @@
         <v>8</v>
       </c>
       <c r="G433" t="n">
-        <v>0.6850672328379335</v>
+        <v>0.6845827439886846</v>
       </c>
       <c r="H433" t="n">
-        <v>4.621840941259731</v>
+        <v>4.62132072135785</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -32789,16 +32789,16 @@
         <v>1</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.2181590587402686</v>
+        <v>-0.2186792786421501</v>
       </c>
       <c r="N433" t="n">
-        <v>0.2181590587402686</v>
+        <v>0.2186792786421501</v>
       </c>
       <c r="O433" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P433" t="n">
-        <v>-0.03061836518046679</v>
+        <v>-0.03008309759547423</v>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
@@ -32838,10 +32838,10 @@
         <v>8</v>
       </c>
       <c r="G434" t="n">
-        <v>0.6900212314225053</v>
+        <v>0.6895332390381895</v>
       </c>
       <c r="H434" t="n">
-        <v>4.639094125973107</v>
+        <v>4.637696841112683</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -32860,16 +32860,16 @@
         <v>1</v>
       </c>
       <c r="M434" t="n">
-        <v>-0.08090587402689309</v>
+        <v>-0.0823031588873171</v>
       </c>
       <c r="N434" t="n">
-        <v>0.08090587402689309</v>
+        <v>0.0823031588873171</v>
       </c>
       <c r="O434" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P434" t="n">
-        <v>0.01725318471337545</v>
+        <v>0.01637611975483289</v>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
@@ -32909,10 +32909,10 @@
         <v>8</v>
       </c>
       <c r="G435" t="n">
-        <v>0.7091295116772823</v>
+        <v>0.7086280056577087</v>
       </c>
       <c r="H435" t="n">
-        <v>4.744281670205237</v>
+        <v>4.741409712399812</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -32931,16 +32931,16 @@
         <v>1</v>
       </c>
       <c r="M435" t="n">
-        <v>0.1842816702052374</v>
+        <v>0.1814097123998124</v>
       </c>
       <c r="N435" t="n">
-        <v>0.1842816702052374</v>
+        <v>0.1814097123998124</v>
       </c>
       <c r="O435" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P435" t="n">
-        <v>0.1051875442321304</v>
+        <v>0.1037128712871294</v>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
@@ -32980,10 +32980,10 @@
         <v>8</v>
       </c>
       <c r="G436" t="n">
-        <v>0.7246992215145082</v>
+        <v>0.7248939179632249</v>
       </c>
       <c r="H436" t="n">
-        <v>4.842583156404812</v>
+        <v>4.843419377652051</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -33002,16 +33002,16 @@
         <v>1</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4525831564048124</v>
+        <v>0.4534193776520512</v>
       </c>
       <c r="N436" t="n">
-        <v>0.4525831564048124</v>
+        <v>0.4534193776520512</v>
       </c>
       <c r="O436" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P436" t="n">
-        <v>0.09830148619957502</v>
+        <v>0.1020096652522389</v>
       </c>
       <c r="Q436" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>8</v>
       </c>
       <c r="G437" t="n">
-        <v>0.8230714791224345</v>
+        <v>0.8231966053748232</v>
       </c>
       <c r="H437" t="n">
-        <v>3.492929936305731</v>
+        <v>3.495654172560113</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -33073,10 +33073,10 @@
         <v>1</v>
       </c>
       <c r="M437" t="n">
-        <v>-0.9470700636942695</v>
+        <v>-0.9443458274398875</v>
       </c>
       <c r="N437" t="n">
-        <v>0.9470700636942695</v>
+        <v>0.9443458274398875</v>
       </c>
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
@@ -33116,10 +33116,10 @@
         <v>8</v>
       </c>
       <c r="G438" t="n">
-        <v>0.8089171974522293</v>
+        <v>0.809052333804809</v>
       </c>
       <c r="H438" t="n">
-        <v>3.348152866242039</v>
+        <v>3.348882602545969</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -33138,16 +33138,16 @@
         <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>-0.8943471337579618</v>
+        <v>-0.8936173974540318</v>
       </c>
       <c r="N438" t="n">
-        <v>0.8943471337579618</v>
+        <v>0.8936173974540318</v>
       </c>
       <c r="O438" t="n">
         <v>-0.1974999999999998</v>
       </c>
       <c r="P438" t="n">
-        <v>-0.1447770700636921</v>
+        <v>-0.1467715700141441</v>
       </c>
       <c r="Q438" t="inlineStr">
         <is>
@@ -33187,10 +33187,10 @@
         <v>8</v>
       </c>
       <c r="G439" t="n">
-        <v>0.7997169143665959</v>
+        <v>0.7998585572842999</v>
       </c>
       <c r="H439" t="n">
-        <v>3.294235668789809</v>
+        <v>3.29461810466761</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -33209,16 +33209,16 @@
         <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>-0.8157643312101914</v>
+        <v>-0.8153818953323908</v>
       </c>
       <c r="N439" t="n">
-        <v>0.8157643312101914</v>
+        <v>0.8153818953323908</v>
       </c>
       <c r="O439" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P439" t="n">
-        <v>-0.05391719745222989</v>
+        <v>-0.0542644978783593</v>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
@@ -33258,10 +33258,10 @@
         <v>8</v>
       </c>
       <c r="G440" t="n">
-        <v>0.8039631988676574</v>
+        <v>0.8041018387553041</v>
       </c>
       <c r="H440" t="n">
-        <v>3.3128025477707</v>
+        <v>3.314299858557284</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -33280,16 +33280,16 @@
         <v>1</v>
       </c>
       <c r="M440" t="n">
-        <v>-0.6571974522292998</v>
+        <v>-0.6557001414427162</v>
       </c>
       <c r="N440" t="n">
-        <v>0.6571974522292998</v>
+        <v>0.6557001414427162</v>
       </c>
       <c r="O440" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P440" t="n">
-        <v>0.01856687898089149</v>
+        <v>0.01968175388967452</v>
       </c>
       <c r="Q440" t="inlineStr">
         <is>
@@ -33329,10 +33329,10 @@
         <v>8</v>
       </c>
       <c r="G441" t="n">
-        <v>0.8216560509554141</v>
+        <v>0.8217821782178217</v>
       </c>
       <c r="H441" t="n">
-        <v>3.463885350318472</v>
+        <v>3.465247524752475</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -33351,16 +33351,16 @@
         <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>-0.3661146496815282</v>
+        <v>-0.3647524752475251</v>
       </c>
       <c r="N441" t="n">
-        <v>0.3661146496815282</v>
+        <v>0.3647524752475251</v>
       </c>
       <c r="O441" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P441" t="n">
-        <v>0.1510828025477715</v>
+        <v>0.150947666195191</v>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
@@ -33400,10 +33400,10 @@
         <v>8</v>
       </c>
       <c r="G442" t="n">
-        <v>0.83793347487615</v>
+        <v>0.8380480905233381</v>
       </c>
       <c r="H442" t="n">
-        <v>3.646454352441614</v>
+        <v>3.647279585101368</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -33422,16 +33422,16 @@
         <v>1</v>
       </c>
       <c r="M442" t="n">
-        <v>-0.01354564755838661</v>
+        <v>-0.01272041489863263</v>
       </c>
       <c r="N442" t="n">
-        <v>0.01354564755838661</v>
+        <v>0.01272041489863263</v>
       </c>
       <c r="O442" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P442" t="n">
-        <v>0.1825690021231416</v>
+        <v>0.1820320603488925</v>
       </c>
       <c r="Q442" t="inlineStr">
         <is>
@@ -33471,10 +33471,10 @@
         <v>8</v>
       </c>
       <c r="G443" t="n">
-        <v>0.8478414720452937</v>
+        <v>0.847949080622348</v>
       </c>
       <c r="H443" t="n">
-        <v>3.721671974522293</v>
+        <v>3.72196251768034</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -33493,16 +33493,16 @@
         <v>1</v>
       </c>
       <c r="M443" t="n">
-        <v>0.08167197452229313</v>
+        <v>0.0819625176803398</v>
       </c>
       <c r="N443" t="n">
-        <v>0.08167197452229313</v>
+        <v>0.0819625176803398</v>
       </c>
       <c r="O443" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P443" t="n">
-        <v>0.07521762208067972</v>
+        <v>0.07468293257897241</v>
       </c>
       <c r="Q443" t="inlineStr">
         <is>
@@ -33542,10 +33542,10 @@
         <v>8</v>
       </c>
       <c r="G444" t="n">
-        <v>0.8556263269639066</v>
+        <v>0.8557284299858557</v>
       </c>
       <c r="H444" t="n">
-        <v>3.755382165605095</v>
+        <v>3.755933521923621</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -33564,16 +33564,16 @@
         <v>1</v>
       </c>
       <c r="M444" t="n">
-        <v>0.1553821656050953</v>
+        <v>0.1559335219236209</v>
       </c>
       <c r="N444" t="n">
-        <v>0.1553821656050953</v>
+        <v>0.1559335219236209</v>
       </c>
       <c r="O444" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P444" t="n">
-        <v>0.03371019108280215</v>
+        <v>0.03397100424328103</v>
       </c>
       <c r="Q444" t="inlineStr">
         <is>
@@ -33613,10 +33613,10 @@
         <v>8</v>
       </c>
       <c r="G445" t="n">
-        <v>0.8584571832979476</v>
+        <v>0.8585572842998586</v>
       </c>
       <c r="H445" t="n">
-        <v>3.767834394904459</v>
+        <v>3.768104667609618</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -33635,16 +33635,16 @@
         <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>0.2353343949044584</v>
+        <v>0.2356046676096182</v>
       </c>
       <c r="N445" t="n">
-        <v>0.2353343949044584</v>
+        <v>0.2356046676096182</v>
       </c>
       <c r="O445" t="n">
         <v>-0.06749999999999989</v>
       </c>
       <c r="P445" t="n">
-        <v>0.01245222929936318</v>
+        <v>0.01217114568599742</v>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
@@ -33684,10 +33684,10 @@
         <v>8</v>
       </c>
       <c r="G446" t="n">
-        <v>0.8506723283793347</v>
+        <v>0.8507779349363508</v>
       </c>
       <c r="H446" t="n">
-        <v>3.733630573248407</v>
+        <v>3.734200848656294</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -33706,16 +33706,16 @@
         <v>1</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2936305732484072</v>
+        <v>0.2942008486562941</v>
       </c>
       <c r="N446" t="n">
-        <v>0.2936305732484072</v>
+        <v>0.2942008486562941</v>
       </c>
       <c r="O446" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P446" t="n">
-        <v>-0.0342038216560514</v>
+        <v>-0.03390381895332428</v>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
@@ -33755,10 +33755,10 @@
         <v>8</v>
       </c>
       <c r="G447" t="n">
-        <v>0.8400566171266808</v>
+        <v>0.8401697312588402</v>
       </c>
       <c r="H447" t="n">
-        <v>3.664570063694267</v>
+        <v>3.66670792079208</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -33777,16 +33777,16 @@
         <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>0.374570063694267</v>
+        <v>0.37670792079208</v>
       </c>
       <c r="N447" t="n">
-        <v>0.374570063694267</v>
+        <v>0.37670792079208</v>
       </c>
       <c r="O447" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.06906050955414011</v>
+        <v>-0.06749292786421401</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
@@ -33826,10 +33826,10 @@
         <v>8</v>
       </c>
       <c r="G448" t="n">
-        <v>0.8152866242038217</v>
+        <v>0.8154172560113154</v>
       </c>
       <c r="H448" t="n">
-        <v>3.416273885350319</v>
+        <v>3.416626591230552</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -33848,16 +33848,16 @@
         <v>1</v>
       </c>
       <c r="M448" t="n">
-        <v>0.2362738853503186</v>
+        <v>0.2366265912305514</v>
       </c>
       <c r="N448" t="n">
-        <v>0.2362738853503186</v>
+        <v>0.2366265912305514</v>
       </c>
       <c r="O448" t="n">
         <v>-0.1099999999999999</v>
       </c>
       <c r="P448" t="n">
-        <v>-0.2482961783439483</v>
+        <v>-0.2500813295615285</v>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
@@ -33897,10 +33897,10 @@
         <v>8</v>
       </c>
       <c r="G449" t="n">
-        <v>0.7834394904458599</v>
+        <v>0.7835926449787836</v>
       </c>
       <c r="H449" t="n">
-        <v>3.215573248407644</v>
+        <v>3.216400282885431</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -33919,16 +33919,16 @@
         <v>1</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1155732484076437</v>
+        <v>0.1164002828854311</v>
       </c>
       <c r="N449" t="n">
-        <v>0.1155732484076437</v>
+        <v>0.1164002828854311</v>
       </c>
       <c r="O449" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P449" t="n">
-        <v>-0.2007006369426749</v>
+        <v>-0.2002263083451203</v>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
@@ -33968,10 +33968,10 @@
         <v>8</v>
       </c>
       <c r="G450" t="n">
-        <v>0.7664543524416136</v>
+        <v>0.7666195190947667</v>
       </c>
       <c r="H450" t="n">
-        <v>3.107707006369427</v>
+        <v>3.109490806223479</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -33990,16 +33990,16 @@
         <v>1</v>
       </c>
       <c r="M450" t="n">
-        <v>0.007707006369426672</v>
+        <v>0.009490806223479087</v>
       </c>
       <c r="N450" t="n">
-        <v>0.007707006369426672</v>
+        <v>0.009490806223479087</v>
       </c>
       <c r="O450" t="n">
         <v>0</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.107866242038217</v>
+        <v>-0.1069094766619521</v>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
@@ -35311,10 +35311,10 @@
         <v>8</v>
       </c>
       <c r="G469" t="n">
-        <v>0.8428874734607219</v>
+        <v>0.842998585572843</v>
       </c>
       <c r="H469" t="n">
-        <v>8.550806794055203</v>
+        <v>8.553239038189535</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -35333,16 +35333,16 @@
         <v>1</v>
       </c>
       <c r="M469" t="n">
-        <v>-0.6891932059447967</v>
+        <v>-0.6867609618104655</v>
       </c>
       <c r="N469" t="n">
-        <v>0.6891932059447967</v>
+        <v>0.6867609618104655</v>
       </c>
       <c r="O469" t="n">
         <v>-0.08999999999999986</v>
       </c>
       <c r="P469" t="n">
-        <v>0.2518369272016656</v>
+        <v>0.2542691713359968</v>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
@@ -35382,10 +35382,10 @@
         <v>8</v>
       </c>
       <c r="G470" t="n">
-        <v>0.8259023354564756</v>
+        <v>0.826025459688826</v>
       </c>
       <c r="H470" t="n">
-        <v>8.281273885350318</v>
+        <v>8.282743988684583</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -35404,16 +35404,16 @@
         <v>1</v>
       </c>
       <c r="M470" t="n">
-        <v>-0.7687261146496827</v>
+        <v>-0.7672560113154177</v>
       </c>
       <c r="N470" t="n">
-        <v>0.7687261146496827</v>
+        <v>0.7672560113154177</v>
       </c>
       <c r="O470" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P470" t="n">
-        <v>-0.2695329087048854</v>
+        <v>-0.2704950495049516</v>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -35453,10 +35453,10 @@
         <v>8</v>
       </c>
       <c r="G471" t="n">
-        <v>0.8067940552016986</v>
+        <v>0.806930693069307</v>
       </c>
       <c r="H471" t="n">
-        <v>7.996242038216562</v>
+        <v>7.999504950495052</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -35475,16 +35475,16 @@
         <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.9137579617834382</v>
+        <v>-0.9104950495049486</v>
       </c>
       <c r="N471" t="n">
-        <v>0.9137579617834382</v>
+        <v>0.9104950495049486</v>
       </c>
       <c r="O471" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P471" t="n">
-        <v>-0.2850318471337561</v>
+        <v>-0.2832390381895316</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
@@ -35524,10 +35524,10 @@
         <v>8</v>
       </c>
       <c r="G472" t="n">
-        <v>0.7947629157820241</v>
+        <v>0.7949080622347949</v>
       </c>
       <c r="H472" t="n">
-        <v>7.894734607218683</v>
+        <v>7.895601131541725</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -35546,16 +35546,16 @@
         <v>1</v>
       </c>
       <c r="M472" t="n">
-        <v>-0.8752653927813165</v>
+        <v>-0.8743988684582744</v>
       </c>
       <c r="N472" t="n">
-        <v>0.8752653927813165</v>
+        <v>0.8743988684582744</v>
       </c>
       <c r="O472" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P472" t="n">
-        <v>-0.101507430997879</v>
+        <v>-0.1039038189533263</v>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
@@ -35595,10 +35595,10 @@
         <v>8</v>
       </c>
       <c r="G473" t="n">
-        <v>0.7926397735314933</v>
+        <v>0.7927864214992928</v>
       </c>
       <c r="H473" t="n">
-        <v>7.87411889596603</v>
+        <v>7.875869872701556</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -35617,16 +35617,16 @@
         <v>1</v>
       </c>
       <c r="M473" t="n">
-        <v>-0.7058811040339705</v>
+        <v>-0.7041301272984439</v>
       </c>
       <c r="N473" t="n">
-        <v>0.7058811040339705</v>
+        <v>0.7041301272984439</v>
       </c>
       <c r="O473" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P473" t="n">
-        <v>-0.02061571125265349</v>
+        <v>-0.01973125884016902</v>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
@@ -35666,10 +35666,10 @@
         <v>8</v>
       </c>
       <c r="G474" t="n">
-        <v>0.8032554847841472</v>
+        <v>0.8033946251768034</v>
       </c>
       <c r="H474" t="n">
-        <v>7.928478414720453</v>
+        <v>7.928755304101839</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -35688,16 +35688,16 @@
         <v>1</v>
       </c>
       <c r="M474" t="n">
-        <v>-0.5215215852795465</v>
+        <v>-0.5212446958981607</v>
       </c>
       <c r="N474" t="n">
-        <v>0.5215215852795465</v>
+        <v>0.5212446958981607</v>
       </c>
       <c r="O474" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P474" t="n">
-        <v>0.05435951875442324</v>
+        <v>0.05288543140028246</v>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
@@ -35737,10 +35737,10 @@
         <v>8</v>
       </c>
       <c r="G475" t="n">
-        <v>0.8159943382873319</v>
+        <v>0.8161244695898161</v>
       </c>
       <c r="H475" t="n">
-        <v>8.19382873319179</v>
+        <v>8.194087694483734</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -35759,16 +35759,16 @@
         <v>1</v>
       </c>
       <c r="M475" t="n">
-        <v>-0.1261712668082104</v>
+        <v>-0.1259123055162661</v>
       </c>
       <c r="N475" t="n">
-        <v>0.1261712668082104</v>
+        <v>0.1259123055162661</v>
       </c>
       <c r="O475" t="n">
         <v>-0.129999999999999</v>
       </c>
       <c r="P475" t="n">
-        <v>0.2653503184713371</v>
+        <v>0.2653323903818956</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
@@ -35808,10 +35808,10 @@
         <v>8</v>
       </c>
       <c r="G476" t="n">
-        <v>0.8280254777070064</v>
+        <v>0.8281471004243282</v>
       </c>
       <c r="H476" t="n">
-        <v>8.306624203821656</v>
+        <v>8.308076379066478</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -35830,16 +35830,16 @@
         <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>0.046624203821656</v>
+        <v>0.04807637906647777</v>
       </c>
       <c r="N476" t="n">
-        <v>0.046624203821656</v>
+        <v>0.04807637906647777</v>
       </c>
       <c r="O476" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P476" t="n">
-        <v>0.1127954706298659</v>
+        <v>0.1139886845827434</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
@@ -35879,10 +35879,10 @@
         <v>8</v>
       </c>
       <c r="G477" t="n">
-        <v>0.8365180467091295</v>
+        <v>0.8366336633663366</v>
       </c>
       <c r="H477" t="n">
-        <v>8.459341825902335</v>
+        <v>8.459801980198019</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -35901,16 +35901,16 @@
         <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2593418259023359</v>
+        <v>0.25980198019802</v>
       </c>
       <c r="N477" t="n">
-        <v>0.2593418259023359</v>
+        <v>0.25980198019802</v>
       </c>
       <c r="O477" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P477" t="n">
-        <v>0.1527176220806794</v>
+        <v>0.1517256011315418</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -35950,10 +35950,10 @@
         <v>8</v>
       </c>
       <c r="G478" t="n">
-        <v>0.8372257607926398</v>
+        <v>0.8373408769448374</v>
       </c>
       <c r="H478" t="n">
-        <v>8.462158527954706</v>
+        <v>8.462616690240454</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -35972,16 +35972,16 @@
         <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>0.4121585279547055</v>
+        <v>0.4126166902404531</v>
       </c>
       <c r="N478" t="n">
-        <v>0.4121585279547055</v>
+        <v>0.4126166902404531</v>
       </c>
       <c r="O478" t="n">
         <v>-0.1499999999999986</v>
       </c>
       <c r="P478" t="n">
-        <v>0.002816702052371056</v>
+        <v>0.002814710042434498</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -36021,10 +36021,10 @@
         <v>8</v>
       </c>
       <c r="G479" t="n">
-        <v>0.832271762208068</v>
+        <v>0.8323903818953324</v>
       </c>
       <c r="H479" t="n">
-        <v>8.400870488322719</v>
+        <v>8.40393917963225</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -36043,16 +36043,16 @@
         <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>0.4808704883227186</v>
+        <v>0.4839391796322499</v>
       </c>
       <c r="N479" t="n">
-        <v>0.4808704883227186</v>
+        <v>0.4839391796322499</v>
       </c>
       <c r="O479" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P479" t="n">
-        <v>-0.0612880396319877</v>
+        <v>-0.05867751060820403</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -36092,10 +36092,10 @@
         <v>8</v>
       </c>
       <c r="G480" t="n">
-        <v>0.8195329087048833</v>
+        <v>0.8196605374823197</v>
       </c>
       <c r="H480" t="n">
-        <v>8.205222929936305</v>
+        <v>8.206746817538896</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -36114,16 +36114,16 @@
         <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0.4652229299363047</v>
+        <v>0.4667468175388958</v>
       </c>
       <c r="N480" t="n">
-        <v>0.4652229299363047</v>
+        <v>0.4667468175388958</v>
       </c>
       <c r="O480" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P480" t="n">
-        <v>-0.1956475583864137</v>
+        <v>-0.1971923620933538</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -36266,34 +36266,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.772</v>
+        <v>7.729</v>
       </c>
       <c r="G2" t="n">
-        <v>7.846</v>
+        <v>7.867</v>
       </c>
       <c r="H2" t="n">
-        <v>7.893</v>
+        <v>7.954</v>
       </c>
       <c r="I2" t="n">
         <v>7.879</v>
       </c>
       <c r="J2" t="n">
-        <v>7.816</v>
+        <v>7.799</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.063</v>
+        <v>-0.08</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -36312,13 +36312,13 @@
         <v>5.83</v>
       </c>
       <c r="P2" t="n">
-        <v>5.81</v>
+        <v>5.811</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.81</v>
+        <v>5.811</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.023</v>
+        <v>-1.024</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -36342,34 +36342,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.587</v>
+        <v>5.58</v>
       </c>
       <c r="G3" t="n">
-        <v>5.661</v>
+        <v>5.646</v>
       </c>
       <c r="H3" t="n">
-        <v>5.781</v>
+        <v>5.725</v>
       </c>
       <c r="I3" t="n">
-        <v>5.781</v>
+        <v>5.725</v>
       </c>
       <c r="J3" t="n">
-        <v>5.588</v>
+        <v>5.586</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.193</v>
+        <v>-0.139</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -36418,34 +36418,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.333</v>
+        <v>4.37</v>
       </c>
       <c r="G4" t="n">
-        <v>4.513</v>
+        <v>4.482</v>
       </c>
       <c r="H4" t="n">
-        <v>4.675</v>
+        <v>4.557</v>
       </c>
       <c r="I4" t="n">
-        <v>4.587</v>
+        <v>4.557</v>
       </c>
       <c r="J4" t="n">
-        <v>4.489</v>
+        <v>4.412</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.098</v>
+        <v>-0.144</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -36494,34 +36494,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.778</v>
+        <v>10.812</v>
       </c>
       <c r="G5" t="n">
-        <v>11.546</v>
+        <v>11.69</v>
       </c>
       <c r="H5" t="n">
-        <v>12.114</v>
+        <v>12.188</v>
       </c>
       <c r="I5" t="n">
-        <v>10.778</v>
+        <v>10.812</v>
       </c>
       <c r="J5" t="n">
-        <v>12.103</v>
+        <v>12.182</v>
       </c>
       <c r="K5" t="n">
-        <v>1.325</v>
+        <v>1.37</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -36546,7 +36546,7 @@
         <v>3.916</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.726</v>
+        <v>-1.727</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -36570,34 +36570,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>54.626</v>
+        <v>54.621</v>
       </c>
       <c r="G6" t="n">
-        <v>87.224</v>
+        <v>85.768</v>
       </c>
       <c r="H6" t="n">
-        <v>112.962</v>
+        <v>112.044</v>
       </c>
       <c r="I6" t="n">
-        <v>58.132</v>
+        <v>56.939</v>
       </c>
       <c r="J6" t="n">
-        <v>110.301</v>
+        <v>96.152</v>
       </c>
       <c r="K6" t="n">
-        <v>52.169</v>
+        <v>39.213</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -36613,13 +36613,13 @@
         <v>13</v>
       </c>
       <c r="O6" t="n">
-        <v>92.014</v>
+        <v>92.01600000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>88.685</v>
+        <v>88.687</v>
       </c>
       <c r="Q6" t="n">
-        <v>88.685</v>
+        <v>88.687</v>
       </c>
       <c r="R6" t="n">
         <v>-3.322</v>
@@ -36646,34 +36646,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.733</v>
+        <v>7.73</v>
       </c>
       <c r="G7" t="n">
-        <v>7.944</v>
+        <v>7.911</v>
       </c>
       <c r="H7" t="n">
-        <v>8.188000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="I7" t="n">
-        <v>8.188000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="J7" t="n">
-        <v>7.762</v>
+        <v>7.872</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.425</v>
+        <v>-0.278</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -36722,34 +36722,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.164</v>
+        <v>6.154</v>
       </c>
       <c r="G8" t="n">
-        <v>6.857</v>
+        <v>6.735</v>
       </c>
       <c r="H8" t="n">
-        <v>7.36</v>
+        <v>7.328</v>
       </c>
       <c r="I8" t="n">
-        <v>7.36</v>
+        <v>7.327</v>
       </c>
       <c r="J8" t="n">
-        <v>6.165</v>
+        <v>6.161</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.195</v>
+        <v>-1.166</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -36765,7 +36765,7 @@
         <v>29</v>
       </c>
       <c r="O8" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="P8" t="n">
         <v>0.396</v>
@@ -36798,34 +36798,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.035</v>
+        <v>5.034</v>
       </c>
       <c r="G9" t="n">
-        <v>5.326</v>
+        <v>5.303</v>
       </c>
       <c r="H9" t="n">
         <v>5.611</v>
       </c>
       <c r="I9" t="n">
-        <v>5.341</v>
+        <v>5.537</v>
       </c>
       <c r="J9" t="n">
-        <v>5.159</v>
+        <v>5.17</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.182</v>
+        <v>-0.368</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -36841,16 +36841,16 @@
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>0.514</v>
+        <v>0.513</v>
       </c>
       <c r="P9" t="n">
-        <v>0.424</v>
+        <v>0.423</v>
       </c>
       <c r="Q9" t="n">
         <v>0.261</v>
       </c>
       <c r="R9" t="n">
-        <v>0.215</v>
+        <v>0.216</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -36874,34 +36874,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.367</v>
+        <v>5.309</v>
       </c>
       <c r="G10" t="n">
-        <v>5.422</v>
+        <v>5.404</v>
       </c>
       <c r="H10" t="n">
-        <v>5.475</v>
+        <v>5.436</v>
       </c>
       <c r="I10" t="n">
-        <v>5.475</v>
+        <v>5.434</v>
       </c>
       <c r="J10" t="n">
-        <v>5.368</v>
+        <v>5.313</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.107</v>
+        <v>-0.121</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -36920,10 +36920,10 @@
         <v>1.822</v>
       </c>
       <c r="P10" t="n">
-        <v>1.788</v>
+        <v>1.787</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.788</v>
+        <v>-1.787</v>
       </c>
       <c r="R10" t="n">
         <v>0.758</v>
@@ -36950,34 +36950,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.958</v>
+        <v>4.288</v>
       </c>
       <c r="G11" t="n">
-        <v>4.804</v>
+        <v>5.156</v>
       </c>
       <c r="H11" t="n">
-        <v>7.284</v>
+        <v>6.057</v>
       </c>
       <c r="I11" t="n">
-        <v>3.958</v>
+        <v>4.292</v>
       </c>
       <c r="J11" t="n">
-        <v>5.372</v>
+        <v>4.956</v>
       </c>
       <c r="K11" t="n">
-        <v>1.414</v>
+        <v>0.663</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -37026,34 +37026,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.012</v>
+        <v>5.964</v>
       </c>
       <c r="G12" t="n">
-        <v>6.077</v>
+        <v>6.052</v>
       </c>
       <c r="H12" t="n">
-        <v>6.153</v>
+        <v>6.113</v>
       </c>
       <c r="I12" t="n">
-        <v>6.153</v>
+        <v>6.113</v>
       </c>
       <c r="J12" t="n">
-        <v>6.013</v>
+        <v>5.965</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.14</v>
+        <v>-0.148</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -37072,13 +37072,13 @@
         <v>0.483</v>
       </c>
       <c r="P12" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.239</v>
       </c>
       <c r="R12" t="n">
-        <v>0.396</v>
+        <v>0.397</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -37102,34 +37102,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.632999999999999</v>
+        <v>9.686</v>
       </c>
       <c r="G13" t="n">
-        <v>9.882</v>
+        <v>9.849</v>
       </c>
       <c r="H13" t="n">
-        <v>10.114</v>
+        <v>10.081</v>
       </c>
       <c r="I13" t="n">
-        <v>10.114</v>
+        <v>10.081</v>
       </c>
       <c r="J13" t="n">
-        <v>9.734999999999999</v>
+        <v>9.702999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.379</v>
+        <v>-0.377</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -37178,34 +37178,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.672</v>
+        <v>5.626</v>
       </c>
       <c r="G14" t="n">
-        <v>5.828</v>
+        <v>5.803</v>
       </c>
       <c r="H14" t="n">
-        <v>5.906</v>
+        <v>5.91</v>
       </c>
       <c r="I14" t="n">
-        <v>5.881</v>
+        <v>5.811</v>
       </c>
       <c r="J14" t="n">
-        <v>5.677</v>
+        <v>5.631</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.204</v>
+        <v>-0.18</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -37254,34 +37254,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.549</v>
+        <v>6.562</v>
       </c>
       <c r="G15" t="n">
         <v>6.577</v>
       </c>
       <c r="H15" t="n">
-        <v>6.591</v>
+        <v>6.586</v>
       </c>
       <c r="I15" t="n">
-        <v>6.591</v>
+        <v>6.585</v>
       </c>
       <c r="J15" t="n">
-        <v>6.559</v>
+        <v>6.573</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.032</v>
+        <v>-0.013</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -37330,38 +37330,38 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>5.174</v>
+        <v>4.708</v>
       </c>
       <c r="G16" t="n">
-        <v>6.059</v>
+        <v>6.055</v>
       </c>
       <c r="H16" t="n">
-        <v>7.22</v>
+        <v>6.585</v>
       </c>
       <c r="I16" t="n">
-        <v>5.506</v>
+        <v>6.149</v>
       </c>
       <c r="J16" t="n">
-        <v>6.289</v>
+        <v>5.859</v>
       </c>
       <c r="K16" t="n">
-        <v>0.783</v>
+        <v>-0.29</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -37373,7 +37373,7 @@
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>1.726</v>
+        <v>1.727</v>
       </c>
       <c r="P16" t="n">
         <v>1.539</v>
@@ -37406,34 +37406,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.949</v>
+        <v>3.925</v>
       </c>
       <c r="G17" t="n">
-        <v>4.369</v>
+        <v>4.336</v>
       </c>
       <c r="H17" t="n">
-        <v>4.82</v>
+        <v>4.674</v>
       </c>
       <c r="I17" t="n">
-        <v>4.82</v>
+        <v>4.674</v>
       </c>
       <c r="J17" t="n">
-        <v>3.965</v>
+        <v>3.987</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.855</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -37482,34 +37482,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.558</v>
+        <v>2.499</v>
       </c>
       <c r="G18" t="n">
-        <v>2.635</v>
+        <v>2.615</v>
       </c>
       <c r="H18" t="n">
-        <v>2.808</v>
+        <v>2.708</v>
       </c>
       <c r="I18" t="n">
-        <v>2.808</v>
+        <v>2.708</v>
       </c>
       <c r="J18" t="n">
-        <v>2.559</v>
+        <v>2.519</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.249</v>
+        <v>-0.19</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -37531,10 +37531,10 @@
         <v>0.371</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.157</v>
+        <v>-0.156</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.109</v>
+        <v>-0.108</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -37558,34 +37558,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.806</v>
+        <v>5.799</v>
       </c>
       <c r="G19" t="n">
-        <v>5.907</v>
+        <v>5.898</v>
       </c>
       <c r="H19" t="n">
-        <v>6.099</v>
+        <v>6.037</v>
       </c>
       <c r="I19" t="n">
-        <v>6.099</v>
+        <v>6.037</v>
       </c>
       <c r="J19" t="n">
-        <v>5.834</v>
+        <v>5.83</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.265</v>
+        <v>-0.207</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -37607,10 +37607,10 @@
         <v>0.778</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.667</v>
+        <v>-0.666</v>
       </c>
       <c r="R19" t="n">
-        <v>0.507</v>
+        <v>0.506</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -486,7 +486,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>299988</v>
+        <v>300006</v>
       </c>
       <c r="E2" t="n">
         <v>151106</v>
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -683,19 +683,19 @@
         <v>9.765000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>7.755</v>
+        <v>7.757</v>
       </c>
       <c r="J2" t="n">
         <v>-1.52</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.01</v>
+        <v>-2.008</v>
       </c>
       <c r="L2" t="n">
-        <v>0.395</v>
+        <v>0.396</v>
       </c>
       <c r="M2" t="n">
-        <v>0.396</v>
+        <v>0.397</v>
       </c>
       <c r="N2" t="n">
         <v>0.477</v>
@@ -704,7 +704,7 @@
         <v>0.866</v>
       </c>
       <c r="P2" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="Q2" t="n">
         <v>0.828</v>
@@ -765,13 +765,13 @@
         <v>7.883</v>
       </c>
       <c r="I3" t="n">
-        <v>5.829</v>
+        <v>5.831</v>
       </c>
       <c r="J3" t="n">
         <v>-2.472</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.054</v>
+        <v>-2.052</v>
       </c>
       <c r="L3" t="n">
         <v>-1.787</v>
@@ -786,7 +786,7 @@
         <v>0.89</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.603</v>
+        <v>-4.601</v>
       </c>
       <c r="Q3" t="n">
         <v>0.758</v>
@@ -847,13 +847,13 @@
         <v>7.691</v>
       </c>
       <c r="I4" t="n">
-        <v>4.843</v>
+        <v>4.844</v>
       </c>
       <c r="J4" t="n">
         <v>-3.405</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.847</v>
+        <v>-2.846</v>
       </c>
       <c r="L4" t="n">
         <v>-0.075</v>
@@ -929,31 +929,31 @@
         <v>7.178</v>
       </c>
       <c r="I5" t="n">
-        <v>5.969</v>
+        <v>5.97</v>
       </c>
       <c r="J5" t="n">
         <v>-2.275</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.209</v>
+        <v>-1.208</v>
       </c>
       <c r="L5" t="n">
         <v>0.317</v>
       </c>
       <c r="M5" t="n">
-        <v>0.338</v>
+        <v>0.339</v>
       </c>
       <c r="N5" t="n">
-        <v>0.49</v>
+        <v>0.491</v>
       </c>
       <c r="O5" t="n">
         <v>0.931</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.569</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="R5" t="n">
         <v>55.172</v>
@@ -970,7 +970,7 @@
         <v>0.509</v>
       </c>
       <c r="V5" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="W5" t="n">
         <v>0.505</v>
@@ -1011,16 +1011,16 @@
         <v>8.468</v>
       </c>
       <c r="I6" t="n">
-        <v>6.23</v>
+        <v>6.231</v>
       </c>
       <c r="J6" t="n">
         <v>-2.07</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.238</v>
+        <v>-2.237</v>
       </c>
       <c r="L6" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="M6" t="n">
         <v>0.35</v>
@@ -1093,13 +1093,13 @@
         <v>9.374000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.207000000000001</v>
+        <v>8.208</v>
       </c>
       <c r="J7" t="n">
         <v>-2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.168</v>
+        <v>-1.166</v>
       </c>
       <c r="L7" t="n">
         <v>-0.666</v>
@@ -1114,10 +1114,10 @@
         <v>0.71</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.355</v>
+        <v>-0.354</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.506</v>
+        <v>0.505</v>
       </c>
       <c r="R7" t="n">
         <v>20.69</v>
@@ -1175,13 +1175,13 @@
         <v>9.863</v>
       </c>
       <c r="I8" t="n">
-        <v>7.936</v>
+        <v>7.937</v>
       </c>
       <c r="J8" t="n">
         <v>-2.008</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.927</v>
+        <v>-1.926</v>
       </c>
       <c r="L8" t="n">
         <v>5.811</v>
@@ -1190,13 +1190,13 @@
         <v>5.811</v>
       </c>
       <c r="N8" t="n">
-        <v>5.83</v>
+        <v>5.831</v>
       </c>
       <c r="O8" t="n">
         <v>0.831</v>
       </c>
       <c r="P8" t="n">
-        <v>-45.929</v>
+        <v>-45.935</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.024</v>
@@ -1257,25 +1257,25 @@
         <v>5.178</v>
       </c>
       <c r="I9" t="n">
-        <v>4.799</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
         <v>0.04</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.379</v>
+        <v>-0.378</v>
       </c>
       <c r="L9" t="n">
         <v>0.29</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>0.949</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>-0.001</v>
       </c>
       <c r="P9" t="n">
         <v>-0.667</v>
@@ -1298,7 +1298,7 @@
         <v>0.429</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.082</v>
+        <v>-0.083</v>
       </c>
       <c r="W9" t="n">
         <v>0.427</v>
@@ -1339,13 +1339,13 @@
         <v>11.017</v>
       </c>
       <c r="I10" t="n">
-        <v>11.493</v>
+        <v>11.496</v>
       </c>
       <c r="J10" t="n">
         <v>-1.39</v>
       </c>
       <c r="K10" t="n">
-        <v>0.476</v>
+        <v>0.479</v>
       </c>
       <c r="L10" t="n">
         <v>3.916</v>
@@ -1354,13 +1354,13 @@
         <v>3.916</v>
       </c>
       <c r="N10" t="n">
-        <v>4.212</v>
+        <v>4.213</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.491</v>
+        <v>-0.492</v>
       </c>
       <c r="P10" t="n">
-        <v>-105.49</v>
+        <v>-105.515</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.727</v>
@@ -1418,28 +1418,28 @@
         <v>5.32</v>
       </c>
       <c r="H11" t="n">
-        <v>112.889</v>
+        <v>112.89</v>
       </c>
       <c r="I11" t="n">
-        <v>108.401</v>
+        <v>108.405</v>
       </c>
       <c r="J11" t="n">
         <v>-1.68</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.488</v>
+        <v>-4.485</v>
       </c>
       <c r="L11" t="n">
-        <v>88.687</v>
+        <v>88.688</v>
       </c>
       <c r="M11" t="n">
-        <v>88.687</v>
+        <v>88.688</v>
       </c>
       <c r="N11" t="n">
-        <v>92.01600000000001</v>
+        <v>92.017</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.357</v>
+        <v>-0.358</v>
       </c>
       <c r="P11" t="n">
         <v>-13.683</v>
@@ -1468,7 +1468,7 @@
         <v>0.129</v>
       </c>
       <c r="X11" t="n">
-        <v>36.187</v>
+        <v>36.185</v>
       </c>
     </row>
     <row r="12">
@@ -1585,16 +1585,16 @@
         <v>5.956</v>
       </c>
       <c r="I13" t="n">
-        <v>5.123</v>
+        <v>5.121</v>
       </c>
       <c r="J13" t="n">
         <v>-0.6919999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.833</v>
+        <v>-0.834</v>
       </c>
       <c r="L13" t="n">
-        <v>0.261</v>
+        <v>0.26</v>
       </c>
       <c r="M13" t="n">
         <v>0.423</v>
@@ -1603,16 +1603,16 @@
         <v>0.513</v>
       </c>
       <c r="O13" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.216</v>
+        <v>0.218</v>
       </c>
       <c r="R13" t="n">
-        <v>20.69</v>
+        <v>17.241</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1667,19 +1667,19 @@
         <v>7.097</v>
       </c>
       <c r="I14" t="n">
-        <v>5.206</v>
+        <v>5.207</v>
       </c>
       <c r="J14" t="n">
         <v>-2.422</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.891</v>
+        <v>-1.889</v>
       </c>
       <c r="L14" t="n">
-        <v>2.035</v>
+        <v>2.036</v>
       </c>
       <c r="M14" t="n">
-        <v>2.035</v>
+        <v>2.036</v>
       </c>
       <c r="N14" t="n">
         <v>2.52</v>
@@ -1688,7 +1688,7 @@
         <v>0.615</v>
       </c>
       <c r="P14" t="n">
-        <v>-10.092</v>
+        <v>-10.094</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.553</v>
@@ -1749,13 +1749,13 @@
         <v>8.144</v>
       </c>
       <c r="I15" t="n">
-        <v>6.355</v>
+        <v>6.357</v>
       </c>
       <c r="J15" t="n">
         <v>-1.525</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.789</v>
+        <v>-1.787</v>
       </c>
       <c r="L15" t="n">
         <v>-0.239</v>
@@ -1764,16 +1764,16 @@
         <v>0.371</v>
       </c>
       <c r="N15" t="n">
-        <v>0.483</v>
+        <v>0.482</v>
       </c>
       <c r="O15" t="n">
         <v>0.8169999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.198</v>
+        <v>-0.196</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.397</v>
+        <v>0.398</v>
       </c>
       <c r="R15" t="n">
         <v>41.379</v>
@@ -1913,13 +1913,13 @@
         <v>8.029999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>6.68</v>
+        <v>6.681</v>
       </c>
       <c r="J17" t="n">
         <v>-2.425</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.351</v>
+        <v>-1.35</v>
       </c>
       <c r="L17" t="n">
         <v>-1.505</v>
@@ -1931,13 +1931,13 @@
         <v>1.625</v>
       </c>
       <c r="O17" t="n">
-        <v>0.602</v>
+        <v>0.601</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.68</v>
+        <v>-3.679</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.283</v>
+        <v>0.282</v>
       </c>
       <c r="R17" t="n">
         <v>31.034</v>
@@ -2001,22 +2001,22 @@
         <v>-1.55</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.861</v>
+        <v>-0.86</v>
       </c>
       <c r="L18" t="n">
-        <v>1.539</v>
+        <v>1.538</v>
       </c>
       <c r="M18" t="n">
-        <v>1.539</v>
+        <v>1.538</v>
       </c>
       <c r="N18" t="n">
-        <v>1.727</v>
+        <v>1.726</v>
       </c>
       <c r="O18" t="n">
         <v>0.61</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.63</v>
+        <v>-6.629</v>
       </c>
       <c r="Q18" t="n">
         <v>0.23</v>
@@ -2074,31 +2074,31 @@
         <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.496</v>
+        <v>3.497</v>
       </c>
       <c r="I19" t="n">
-        <v>3.109</v>
+        <v>3.11</v>
       </c>
       <c r="J19" t="n">
         <v>-1.34</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.386</v>
+        <v>-0.387</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.156</v>
+        <v>-0.155</v>
       </c>
       <c r="M19" t="n">
         <v>0.371</v>
       </c>
       <c r="N19" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="O19" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.413</v>
+        <v>-0.411</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.108</v>
@@ -3392,10 +3392,10 @@
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8536067892503536</v>
+        <v>0.8537102473498234</v>
       </c>
       <c r="H18" t="n">
-        <v>8.170933521923621</v>
+        <v>8.17126148409894</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>5.71593352192362</v>
+        <v>5.71626148409894</v>
       </c>
       <c r="N18" t="n">
-        <v>5.71593352192362</v>
+        <v>5.71626148409894</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1374999999999997</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7290945089102969</v>
+        <v>-0.7287665467349775</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8507779349363508</v>
+        <v>0.8508833922261484</v>
       </c>
       <c r="H19" t="n">
-        <v>8.157724540311174</v>
+        <v>8.157975265017667</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3485,16 +3485,16 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.745224540311174</v>
+        <v>5.745475265017667</v>
       </c>
       <c r="N19" t="n">
-        <v>5.745224540311174</v>
+        <v>5.745475265017667</v>
       </c>
       <c r="O19" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.01320898161244699</v>
+        <v>-0.01328621908127303</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8465346534653465</v>
+        <v>0.846643109540636</v>
       </c>
       <c r="H20" t="n">
-        <v>8.133787128712871</v>
+        <v>8.134646643109543</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3556,16 +3556,16 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>5.733787128712871</v>
+        <v>5.734646643109542</v>
       </c>
       <c r="N20" t="n">
-        <v>5.733787128712871</v>
+        <v>5.734646643109542</v>
       </c>
       <c r="O20" t="n">
         <v>-0.01250000000000018</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.02393741159830221</v>
+        <v>-0.02332862190812435</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8437057991513437</v>
+        <v>0.8438162544169612</v>
       </c>
       <c r="H21" t="n">
-        <v>8.119547383309758</v>
+        <v>8.119897526501767</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>5.949547383309758</v>
+        <v>5.949897526501767</v>
       </c>
       <c r="N21" t="n">
-        <v>5.949547383309758</v>
+        <v>5.949897526501767</v>
       </c>
       <c r="O21" t="n">
         <v>-0.23</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.01423974540311335</v>
+        <v>-0.014749116607776</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8387553041018387</v>
+        <v>0.83886925795053</v>
       </c>
       <c r="H22" t="n">
-        <v>8.097708628005657</v>
+        <v>8.09843109540636</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3698,16 +3698,16 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>6.117708628005657</v>
+        <v>6.118431095406359</v>
       </c>
       <c r="N22" t="n">
-        <v>6.117708628005657</v>
+        <v>6.118431095406359</v>
       </c>
       <c r="O22" t="n">
         <v>-0.1899999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.02183875530410084</v>
+        <v>-0.02146643109540669</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8338048090523338</v>
+        <v>0.833922261484099</v>
       </c>
       <c r="H23" t="n">
-        <v>8.062644978783592</v>
+        <v>8.064134275618375</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3769,16 +3769,16 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>6.012644978783592</v>
+        <v>6.014134275618376</v>
       </c>
       <c r="N23" t="n">
-        <v>6.012644978783592</v>
+        <v>6.014134275618376</v>
       </c>
       <c r="O23" t="n">
         <v>0.06999999999999984</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.03506364922206551</v>
+        <v>-0.03429681978798449</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8274398868458275</v>
+        <v>0.8275618374558303</v>
       </c>
       <c r="H24" t="n">
         <v>8.030000000000001</v>
@@ -3849,7 +3849,7 @@
         <v>0.1700000000000004</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.03264497878359052</v>
+        <v>-0.03413427561837423</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8224893917963225</v>
+        <v>0.8226148409893993</v>
       </c>
       <c r="H25" t="n">
-        <v>8.013645685997171</v>
+        <v>8.013844522968197</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3911,16 +3911,16 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>5.663645685997171</v>
+        <v>5.663844522968198</v>
       </c>
       <c r="N25" t="n">
-        <v>5.663645685997171</v>
+        <v>5.663844522968198</v>
       </c>
       <c r="O25" t="n">
         <v>0.1299999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01635431400283061</v>
+        <v>-0.01615547703180376</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3960,10 +3960,10 @@
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8196605374823197</v>
+        <v>0.8197879858657244</v>
       </c>
       <c r="H26" t="n">
-        <v>8.00248585572843</v>
+        <v>8.003091872791519</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3982,16 +3982,16 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>5.702485855728431</v>
+        <v>5.703091872791519</v>
       </c>
       <c r="N26" t="n">
-        <v>5.702485855728431</v>
+        <v>5.703091872791519</v>
       </c>
       <c r="O26" t="n">
         <v>-0.05000000000000027</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.01115983026874012</v>
+        <v>-0.01075265017667881</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8161244695898161</v>
+        <v>0.8162544169611308</v>
       </c>
       <c r="H27" t="n">
-        <v>7.977400990099009</v>
+        <v>7.978842756183746</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4053,16 +4053,16 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>5.74740099009901</v>
+        <v>5.748842756183747</v>
       </c>
       <c r="N27" t="n">
-        <v>5.74740099009901</v>
+        <v>5.748842756183747</v>
       </c>
       <c r="O27" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.02508486562942114</v>
+        <v>-0.02424911660777251</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8118811881188119</v>
+        <v>0.8120141342756184</v>
       </c>
       <c r="H28" t="n">
-        <v>7.948663366336635</v>
+        <v>7.949084805653711</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>5.888663366336635</v>
+        <v>5.889084805653711</v>
       </c>
       <c r="N28" t="n">
-        <v>5.888663366336635</v>
+        <v>5.889084805653711</v>
       </c>
       <c r="O28" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.02873762376237465</v>
+        <v>-0.02975795053003516</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8125884016973126</v>
+        <v>0.8127208480565371</v>
       </c>
       <c r="H29" t="n">
-        <v>7.952263083451203</v>
+        <v>7.953312720848056</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4195,16 +4195,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>6.002263083451203</v>
+        <v>6.003312720848056</v>
       </c>
       <c r="N29" t="n">
-        <v>6.002263083451203</v>
+        <v>6.003312720848056</v>
       </c>
       <c r="O29" t="n">
         <v>-0.1100000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>0.00359971711456808</v>
+        <v>0.0042279151943454</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8132956152758133</v>
+        <v>0.8134275618374558</v>
       </c>
       <c r="H30" t="n">
-        <v>7.957867751060819</v>
+        <v>7.958913427561836</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4266,16 +4266,16 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.257867751060819</v>
+        <v>5.258913427561835</v>
       </c>
       <c r="N30" t="n">
-        <v>5.257867751060819</v>
+        <v>5.258913427561835</v>
       </c>
       <c r="O30" t="n">
         <v>0.7500000000000002</v>
       </c>
       <c r="P30" t="n">
-        <v>0.005604667609616421</v>
+        <v>0.005600706713779324</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8097595473833098</v>
+        <v>0.8098939929328622</v>
       </c>
       <c r="H31" t="n">
-        <v>7.935813295615277</v>
+        <v>7.937091872791521</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4337,16 +4337,16 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.135813295615277</v>
+        <v>5.137091872791521</v>
       </c>
       <c r="N31" t="n">
-        <v>5.135813295615277</v>
+        <v>5.137091872791521</v>
       </c>
       <c r="O31" t="n">
         <v>0.09999999999999964</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.02205445544554241</v>
+        <v>-0.02182155477031511</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6492220650636492</v>
+        <v>0.649469964664311</v>
       </c>
       <c r="H48" t="n">
-        <v>6.159264939886846</v>
+        <v>6.159359761484099</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5538,16 +5538,16 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1282350601131537</v>
+        <v>-0.1281402385159005</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1282350601131537</v>
+        <v>0.1281402385159005</v>
       </c>
       <c r="O48" t="n">
         <v>-0.09250000000000114</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.6246243383191805</v>
+        <v>-0.6245295167219274</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6431095406360424</v>
       </c>
       <c r="H49" t="n">
-        <v>6.147142857142858</v>
+        <v>6.14791519434629</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5609,16 +5609,16 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.02285714285714224</v>
+        <v>-0.0220848056537104</v>
       </c>
       <c r="N49" t="n">
-        <v>0.02285714285714224</v>
+        <v>0.0220848056537104</v>
       </c>
       <c r="O49" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.01212208274398829</v>
+        <v>-0.01144456713780961</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5658,10 +5658,10 @@
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>0.635077793493635</v>
+        <v>0.6353356890459364</v>
       </c>
       <c r="H50" t="n">
-        <v>6.124670438472418</v>
+        <v>6.125301766784452</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5680,16 +5680,16 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.03467043847241857</v>
+        <v>0.0353017667844524</v>
       </c>
       <c r="N50" t="n">
-        <v>0.03467043847241857</v>
+        <v>0.0353017667844524</v>
       </c>
       <c r="O50" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.02247241867043925</v>
+        <v>-0.02261342756183726</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5729,10 +5729,10 @@
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6336633663366337</v>
+        <v>0.6339222614840989</v>
       </c>
       <c r="H51" t="n">
-        <v>6.121207920792079</v>
+        <v>6.121841696113075</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5751,16 +5751,16 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2612079207920788</v>
+        <v>0.2618416961130743</v>
       </c>
       <c r="N51" t="n">
-        <v>0.2612079207920788</v>
+        <v>0.2618416961130743</v>
       </c>
       <c r="O51" t="n">
         <v>-0.2299999999999995</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.003462517680339339</v>
+        <v>-0.003460070671377657</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>0.6449787835926449</v>
+        <v>0.6452296819787986</v>
       </c>
       <c r="H52" t="n">
-        <v>6.157641884724187</v>
+        <v>6.157737853356891</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5822,16 +5822,16 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.497641884724187</v>
+        <v>0.4977378533568908</v>
       </c>
       <c r="N52" t="n">
-        <v>0.497641884724187</v>
+        <v>0.4977378533568908</v>
       </c>
       <c r="O52" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P52" t="n">
-        <v>0.03643396393210807</v>
+        <v>0.03589615724381634</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6527581329561527</v>
+        <v>0.6530035335689046</v>
       </c>
       <c r="H53" t="n">
-        <v>6.167439886845827</v>
+        <v>6.168190812720848</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5893,16 +5893,16 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.537439886845827</v>
+        <v>0.5381908127208481</v>
       </c>
       <c r="N53" t="n">
-        <v>0.537439886845827</v>
+        <v>0.5381908127208481</v>
       </c>
       <c r="O53" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P53" t="n">
-        <v>0.009798002121639726</v>
+        <v>0.01045295936395707</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6626591230551626</v>
+        <v>0.6628975265017668</v>
       </c>
       <c r="H54" t="n">
-        <v>6.206982555398397</v>
+        <v>6.207955241460542</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5964,16 +5964,16 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6169825553983967</v>
+        <v>0.6179552414605425</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6169825553983967</v>
+        <v>0.6179552414605425</v>
       </c>
       <c r="O54" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P54" t="n">
-        <v>0.03954266855256972</v>
+        <v>0.03976442873969432</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.669024045261669</v>
+        <v>0.6692579505300353</v>
       </c>
       <c r="H55" t="n">
-        <v>6.218606789250353</v>
+        <v>6.218964664310954</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6035,16 +6035,16 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7686067892503532</v>
+        <v>0.7689646643109533</v>
       </c>
       <c r="N55" t="n">
-        <v>0.7686067892503532</v>
+        <v>0.7689646643109533</v>
       </c>
       <c r="O55" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01162423385195677</v>
+        <v>0.01100942285041118</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6654879773691655</v>
+        <v>0.6657243816254417</v>
       </c>
       <c r="H56" t="n">
-        <v>6.213196605374823</v>
+        <v>6.213558303886925</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6106,16 +6106,16 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8131966053748227</v>
+        <v>0.813558303886925</v>
       </c>
       <c r="N56" t="n">
-        <v>0.8131966053748227</v>
+        <v>0.813558303886925</v>
       </c>
       <c r="O56" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.005410183875530272</v>
+        <v>-0.0054063604240282</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
         <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6541725601131542</v>
+        <v>0.6544169611307421</v>
       </c>
       <c r="H57" t="n">
-        <v>6.173536067892504</v>
+        <v>6.175031802120142</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8035360678925034</v>
+        <v>0.8050318021201415</v>
       </c>
       <c r="N57" t="n">
-        <v>0.8035360678925034</v>
+        <v>0.8050318021201415</v>
       </c>
       <c r="O57" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.03966053748231957</v>
+        <v>-0.03852650176678374</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6226,10 +6226,10 @@
         <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6386138613861386</v>
+        <v>0.6388692579505301</v>
       </c>
       <c r="H58" t="n">
-        <v>6.136105610561056</v>
+        <v>6.136626619552414</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6248,16 +6248,16 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8061056105610556</v>
+        <v>0.8066266195524143</v>
       </c>
       <c r="N58" t="n">
-        <v>0.8061056105610556</v>
+        <v>0.8066266195524143</v>
       </c>
       <c r="O58" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.0374304573314479</v>
+        <v>-0.03840518256772718</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6297,10 +6297,10 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6202263083451203</v>
+        <v>0.6204946996466431</v>
       </c>
       <c r="H59" t="n">
-        <v>6.077190004714757</v>
+        <v>6.07828504122497</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6319,16 +6319,16 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.927190004714757</v>
+        <v>0.9282850412249699</v>
       </c>
       <c r="N59" t="n">
-        <v>0.927190004714757</v>
+        <v>0.9282850412249699</v>
       </c>
       <c r="O59" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.05891560584629829</v>
+        <v>-0.05834157832744413</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6060820367751061</v>
+        <v>0.6063604240282685</v>
       </c>
       <c r="H60" t="n">
-        <v>6.029611032531825</v>
+        <v>6.030925795053004</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6390,16 +6390,16 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1.059611032531826</v>
+        <v>1.060925795053004</v>
       </c>
       <c r="N60" t="n">
-        <v>1.059611032531826</v>
+        <v>1.060925795053004</v>
       </c>
       <c r="O60" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.04757897218293206</v>
+        <v>-0.04735924617196652</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6439,10 +6439,10 @@
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5912305516265912</v>
+        <v>0.5915194346289753</v>
       </c>
       <c r="H61" t="n">
-        <v>5.968887317303158</v>
+        <v>5.970148409893993</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6461,16 +6461,16 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1.138887317303158</v>
+        <v>1.140148409893992</v>
       </c>
       <c r="N61" t="n">
-        <v>1.138887317303158</v>
+        <v>1.140148409893992</v>
       </c>
       <c r="O61" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.06072371522866682</v>
+        <v>-0.06077738515901121</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -7640,10 +7640,10 @@
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8974540311173974</v>
+        <v>0.8975265017667845</v>
       </c>
       <c r="H78" t="n">
-        <v>5.878415841584158</v>
+        <v>5.879257950530036</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7662,16 +7662,16 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1.190915841584158</v>
+        <v>1.191757950530036</v>
       </c>
       <c r="N78" t="n">
-        <v>1.190915841584158</v>
+        <v>1.191757950530036</v>
       </c>
       <c r="O78" t="n">
         <v>0.2725</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.06340966647470658</v>
+        <v>-0.06256755752882892</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8684582743988685</v>
+        <v>0.8685512367491166</v>
       </c>
       <c r="H79" t="n">
-        <v>5.691485148514852</v>
+        <v>5.692565371024735</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7733,16 +7733,16 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>1.278985148514852</v>
+        <v>1.280065371024736</v>
       </c>
       <c r="N79" t="n">
-        <v>1.278985148514852</v>
+        <v>1.280065371024736</v>
       </c>
       <c r="O79" t="n">
         <v>-0.2750000000000004</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.1869306930693062</v>
+        <v>-0.1866925795053005</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>0.826025459688826</v>
+        <v>0.826148409893993</v>
       </c>
       <c r="H80" t="n">
-        <v>5.414207920792079</v>
+        <v>5.414922261484099</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7804,16 +7804,16 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7642079207920789</v>
+        <v>0.7649222614840987</v>
       </c>
       <c r="N80" t="n">
-        <v>0.7642079207920789</v>
+        <v>0.7649222614840987</v>
       </c>
       <c r="O80" t="n">
         <v>0.2375000000000007</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.2772772277227729</v>
+        <v>-0.2776431095406364</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7793493635077794</v>
+        <v>0.7795053003533569</v>
       </c>
       <c r="H81" t="n">
-        <v>5.153019801980198</v>
+        <v>5.153925795053003</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7875,16 +7875,16 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>0.4530198019801981</v>
+        <v>0.4539257950530029</v>
       </c>
       <c r="N81" t="n">
-        <v>0.4530198019801981</v>
+        <v>0.4539257950530029</v>
       </c>
       <c r="O81" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.261188118811881</v>
+        <v>-0.260996466431096</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7333804809052333</v>
+        <v>0.7335689045936395</v>
       </c>
       <c r="H82" t="n">
-        <v>4.995940594059406</v>
+        <v>4.997035335689046</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7946,16 +7946,16 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5909405940594068</v>
+        <v>0.5920353356890464</v>
       </c>
       <c r="N82" t="n">
-        <v>0.5909405940594068</v>
+        <v>0.5920353356890464</v>
       </c>
       <c r="O82" t="n">
         <v>-0.2950000000000008</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.1570792079207921</v>
+        <v>-0.1568904593639573</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -7995,10 +7995,10 @@
         <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7072135785007072</v>
+        <v>0.7074204946996466</v>
       </c>
       <c r="H83" t="n">
-        <v>4.869273927392739</v>
+        <v>4.870113074204947</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8017,16 +8017,16 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>0.77177392739274</v>
+        <v>0.7726130742049477</v>
       </c>
       <c r="N83" t="n">
-        <v>0.77177392739274</v>
+        <v>0.7726130742049477</v>
       </c>
       <c r="O83" t="n">
         <v>-0.3075000000000001</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.1266666666666669</v>
+        <v>-0.1269222614840988</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -8066,10 +8066,10 @@
         <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>0.6753889674681753</v>
+        <v>0.6756183745583039</v>
       </c>
       <c r="H84" t="n">
-        <v>4.785431400282885</v>
+        <v>4.785812216052499</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8088,16 +8088,16 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>0.935431400282885</v>
+        <v>0.9358122160524984</v>
       </c>
       <c r="N84" t="n">
-        <v>0.935431400282885</v>
+        <v>0.9358122160524984</v>
       </c>
       <c r="O84" t="n">
         <v>-0.2474999999999992</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.08384252710985418</v>
+        <v>-0.08430085815244848</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6407355021216408</v>
+        <v>0.6409893992932862</v>
       </c>
       <c r="H85" t="n">
-        <v>4.687945544554456</v>
+        <v>4.688191401648999</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8159,16 +8159,16 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>0.907945544554456</v>
+        <v>0.9081914016489994</v>
       </c>
       <c r="N85" t="n">
-        <v>0.907945544554456</v>
+        <v>0.9081914016489994</v>
       </c>
       <c r="O85" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.09748585572842927</v>
+        <v>-0.09762081440349935</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6039603960396039</v>
+        <v>0.6035335689045936</v>
       </c>
       <c r="H86" t="n">
-        <v>4.549009900990098</v>
+        <v>4.546530035335689</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8230,16 +8230,16 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.2509900990099023</v>
+        <v>-0.2534699646643119</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2509900990099023</v>
+        <v>0.2534699646643119</v>
       </c>
       <c r="O86" t="n">
         <v>1.020000000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.1389356435643574</v>
+        <v>-0.1416613663133104</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -8279,10 +8279,10 @@
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>0.5968882602545968</v>
+        <v>0.5964664310954063</v>
       </c>
       <c r="H87" t="n">
-        <v>4.518960396039604</v>
+        <v>4.517734982332155</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8301,16 +8301,16 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.1810396039603965</v>
+        <v>-0.1822650176678451</v>
       </c>
       <c r="N87" t="n">
-        <v>0.1810396039603965</v>
+        <v>0.1822650176678451</v>
       </c>
       <c r="O87" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.03004950495049474</v>
+        <v>-0.02879505300353369</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -8350,10 +8350,10 @@
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6138613861386139</v>
+        <v>0.6141342756183745</v>
       </c>
       <c r="H88" t="n">
-        <v>4.571023102310231</v>
+        <v>4.572080094228504</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8372,16 +8372,16 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.6289768976897694</v>
+        <v>-0.6279199057714964</v>
       </c>
       <c r="N88" t="n">
-        <v>0.6289768976897694</v>
+        <v>0.6279199057714964</v>
       </c>
       <c r="O88" t="n">
         <v>0.5</v>
       </c>
       <c r="P88" t="n">
-        <v>0.05206270627062715</v>
+        <v>0.05434511189634872</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6584158415841584</v>
+        <v>0.6586572438162545</v>
       </c>
       <c r="H89" t="n">
-        <v>4.722698019801981</v>
+        <v>4.723399293286219</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8443,16 +8443,16 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.7773019801980192</v>
+        <v>-0.776600706713781</v>
       </c>
       <c r="N89" t="n">
-        <v>0.7773019801980192</v>
+        <v>0.776600706713781</v>
       </c>
       <c r="O89" t="n">
         <v>0.2999999999999998</v>
       </c>
       <c r="P89" t="n">
-        <v>0.15167491749175</v>
+        <v>0.1513191990577152</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8492,10 +8492,10 @@
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6817538896746818</v>
+        <v>0.6819787985865724</v>
       </c>
       <c r="H90" t="n">
-        <v>4.795247524752475</v>
+        <v>4.795574204946996</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8514,16 +8514,16 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-1.084752475247525</v>
+        <v>-1.084425795053003</v>
       </c>
       <c r="N90" t="n">
-        <v>1.084752475247525</v>
+        <v>1.084425795053003</v>
       </c>
       <c r="O90" t="n">
         <v>0.3799999999999999</v>
       </c>
       <c r="P90" t="n">
-        <v>0.07254950495049428</v>
+        <v>0.0721749116607775</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8563,10 +8563,10 @@
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6845827439886846</v>
+        <v>0.6848056537102474</v>
       </c>
       <c r="H91" t="n">
-        <v>4.799356435643564</v>
+        <v>4.799680212014134</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -8585,16 +8585,16 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.2206435643564353</v>
+        <v>-0.2203197879858658</v>
       </c>
       <c r="N91" t="n">
-        <v>0.2206435643564353</v>
+        <v>0.2203197879858658</v>
       </c>
       <c r="O91" t="n">
         <v>-0.8600000000000003</v>
       </c>
       <c r="P91" t="n">
-        <v>0.004108910891089224</v>
+        <v>0.004106007067137263</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -9764,10 +9764,10 @@
         <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8910891089108911</v>
+        <v>0.8911660777385159</v>
       </c>
       <c r="H108" t="n">
-        <v>12.3830198019802</v>
+        <v>12.38318374558304</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -9786,16 +9786,16 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>5.313019801980199</v>
+        <v>5.31318374558304</v>
       </c>
       <c r="N108" t="n">
-        <v>5.313019801980199</v>
+        <v>5.31318374558304</v>
       </c>
       <c r="O108" t="n">
         <v>-0.1250000000000009</v>
       </c>
       <c r="P108" t="n">
-        <v>4.41344026448896</v>
+        <v>4.413604208091801</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -9835,10 +9835,10 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>0.8868458274398868</v>
+        <v>0.8869257950530035</v>
       </c>
       <c r="H109" t="n">
-        <v>12.33879773691655</v>
+        <v>12.34067137809187</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -9857,16 +9857,16 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>5.468797736916547</v>
+        <v>5.470671378091871</v>
       </c>
       <c r="N109" t="n">
-        <v>5.468797736916547</v>
+        <v>5.470671378091871</v>
       </c>
       <c r="O109" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.04422206506365178</v>
+        <v>-0.04251236749116849</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -9906,10 +9906,10 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8847241867043847</v>
+        <v>0.8848056537102473</v>
       </c>
       <c r="H110" t="n">
-        <v>12.29088755304102</v>
+        <v>12.29140812720848</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -9928,16 +9928,16 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>5.550887553041019</v>
+        <v>5.551408127208481</v>
       </c>
       <c r="N110" t="n">
-        <v>5.550887553041019</v>
+        <v>5.551408127208481</v>
       </c>
       <c r="O110" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.04791018387552803</v>
+        <v>-0.04926325088339034</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -9977,10 +9977,10 @@
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>0.8826025459688827</v>
+        <v>0.8826855123674912</v>
       </c>
       <c r="H111" t="n">
-        <v>12.2770756718529</v>
+        <v>12.27786042402827</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -9999,16 +9999,16 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>5.677075671852901</v>
+        <v>5.677860424028269</v>
       </c>
       <c r="N111" t="n">
-        <v>5.677075671852901</v>
+        <v>5.677860424028269</v>
       </c>
       <c r="O111" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P111" t="n">
-        <v>-0.01381188118811849</v>
+        <v>-0.01354770318021181</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -10048,10 +10048,10 @@
         <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8762376237623762</v>
+        <v>0.8763250883392226</v>
       </c>
       <c r="H112" t="n">
-        <v>12.22277227722772</v>
+        <v>12.22314487632509</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10070,16 +10070,16 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>5.362772277227722</v>
+        <v>5.363144876325088</v>
       </c>
       <c r="N112" t="n">
-        <v>5.362772277227722</v>
+        <v>5.363144876325088</v>
       </c>
       <c r="O112" t="n">
         <v>0.2600000000000007</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.05430339462517786</v>
+        <v>-0.05471554770318043</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>0.8677510608203678</v>
+        <v>0.8678445229681979</v>
       </c>
       <c r="H113" t="n">
-        <v>12.19080975954738</v>
+        <v>12.19100883392226</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -10141,16 +10141,16 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>5.210809759547383</v>
+        <v>5.211008833922261</v>
       </c>
       <c r="N113" t="n">
-        <v>5.210809759547383</v>
+        <v>5.211008833922261</v>
       </c>
       <c r="O113" t="n">
         <v>0.1200000000000001</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.03196251768033953</v>
+        <v>-0.03213604240282741</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -10190,10 +10190,10 @@
         <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8572438162544169</v>
       </c>
       <c r="H114" t="n">
-        <v>12.11928571428571</v>
+        <v>12.12057597173145</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -10212,16 +10212,16 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>5.269285714285713</v>
+        <v>5.270575971731448</v>
       </c>
       <c r="N114" t="n">
-        <v>5.269285714285713</v>
+        <v>5.270575971731448</v>
       </c>
       <c r="O114" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P114" t="n">
-        <v>-0.07152404526167011</v>
+        <v>-0.07043286219081324</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
         <v>8</v>
       </c>
       <c r="G115" t="n">
-        <v>0.8465346534653465</v>
+        <v>0.846643109540636</v>
       </c>
       <c r="H115" t="n">
-        <v>12.07623762376238</v>
+        <v>12.07669964664311</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -10283,16 +10283,16 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>5.336237623762376</v>
+        <v>5.336699646643108</v>
       </c>
       <c r="N115" t="n">
-        <v>5.336237623762376</v>
+        <v>5.336699646643108</v>
       </c>
       <c r="O115" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.04304809052333702</v>
+        <v>-0.04387632508833939</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -10332,10 +10332,10 @@
         <v>8</v>
       </c>
       <c r="G116" t="n">
-        <v>0.8246110325318247</v>
+        <v>0.8247349823321555</v>
       </c>
       <c r="H116" t="n">
-        <v>11.86284299858557</v>
+        <v>11.86337102473498</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -10354,16 +10354,16 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>5.257842998585572</v>
+        <v>5.258371024734981</v>
       </c>
       <c r="N116" t="n">
-        <v>5.257842998585572</v>
+        <v>5.258371024734981</v>
       </c>
       <c r="O116" t="n">
         <v>-0.1349999999999998</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.2133946251768037</v>
+        <v>-0.2133286219081274</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10403,10 +10403,10 @@
         <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>0.8097595473833098</v>
+        <v>0.8098939929328622</v>
       </c>
       <c r="H117" t="n">
-        <v>11.80936350777935</v>
+        <v>11.810074204947</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -10425,16 +10425,16 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>5.429363507779351</v>
+        <v>5.430074204946997</v>
       </c>
       <c r="N117" t="n">
-        <v>5.429363507779351</v>
+        <v>5.430074204946997</v>
       </c>
       <c r="O117" t="n">
         <v>-0.2250000000000005</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.05347949080622172</v>
+        <v>-0.05329681978798462</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10474,10 +10474,10 @@
         <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7956152758132956</v>
+        <v>0.7957597173144876</v>
       </c>
       <c r="H118" t="n">
-        <v>11.72466053748232</v>
+        <v>11.72496819787986</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -10496,16 +10496,16 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>5.48466053748232</v>
+        <v>5.484968197879859</v>
       </c>
       <c r="N118" t="n">
-        <v>5.48466053748232</v>
+        <v>5.484968197879859</v>
       </c>
       <c r="O118" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.08470297029703033</v>
+        <v>-0.08510600706713767</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10545,10 +10545,10 @@
         <v>8</v>
       </c>
       <c r="G119" t="n">
-        <v>0.7821782178217822</v>
+        <v>0.7823321554770318</v>
       </c>
       <c r="H119" t="n">
-        <v>11.66061881188119</v>
+        <v>11.66160247349823</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -10567,16 +10567,16 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>5.540618811881187</v>
+        <v>5.541602473498233</v>
       </c>
       <c r="N119" t="n">
-        <v>5.540618811881187</v>
+        <v>5.541602473498233</v>
       </c>
       <c r="O119" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.06404172560113253</v>
+        <v>-0.06336572438162591</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -10616,10 +10616,10 @@
         <v>8</v>
       </c>
       <c r="G120" t="n">
-        <v>0.768033946251768</v>
+        <v>0.7681978798586573</v>
       </c>
       <c r="H120" t="n">
-        <v>11.55591230551627</v>
+        <v>11.55626148409894</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10638,16 +10638,16 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>5.485912305516266</v>
+        <v>5.486261484098939</v>
       </c>
       <c r="N120" t="n">
-        <v>5.485912305516266</v>
+        <v>5.486261484098939</v>
       </c>
       <c r="O120" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.1047065063649217</v>
+        <v>-0.1053409893992932</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         <v>8</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7595473833097596</v>
+        <v>0.7597173144876325</v>
       </c>
       <c r="H121" t="n">
-        <v>11.4926874115983</v>
+        <v>11.49558303886926</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -10709,16 +10709,16 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.462687411598302</v>
+        <v>5.465583038869258</v>
       </c>
       <c r="N121" t="n">
-        <v>5.462687411598302</v>
+        <v>5.465583038869258</v>
       </c>
       <c r="O121" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.0632248939179636</v>
+        <v>-0.0606784452296818</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>8</v>
       </c>
       <c r="G122" t="n">
-        <v>0.9596888260254597</v>
+        <v>0.9597173144876325</v>
       </c>
       <c r="H122" t="n">
-        <v>112.8886633663366</v>
+        <v>112.8903604240283</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>105.8886633663366</v>
+        <v>105.8903604240283</v>
       </c>
       <c r="N122" t="n">
-        <v>105.8886633663366</v>
+        <v>105.8903604240283</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         <v>8</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9356435643564357</v>
+        <v>0.9356890459363958</v>
       </c>
       <c r="H123" t="n">
-        <v>112.4623267326733</v>
+        <v>112.4627137809187</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -10845,16 +10845,16 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>105.6523267326733</v>
+        <v>105.6527137809187</v>
       </c>
       <c r="N123" t="n">
-        <v>105.6523267326733</v>
+        <v>105.6527137809187</v>
       </c>
       <c r="O123" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.426336633663368</v>
+        <v>-0.4276466431095542</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -10894,10 +10894,10 @@
         <v>8</v>
       </c>
       <c r="G124" t="n">
-        <v>0.917963224893918</v>
+        <v>0.9180212014134276</v>
       </c>
       <c r="H124" t="n">
-        <v>112.1418670438472</v>
+        <v>112.1423604240283</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -10916,16 +10916,16 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>105.5318670438472</v>
+        <v>105.5323604240283</v>
       </c>
       <c r="N124" t="n">
-        <v>105.5318670438472</v>
+        <v>105.5323604240283</v>
       </c>
       <c r="O124" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P124" t="n">
-        <v>-0.3204596888260198</v>
+        <v>-0.3203533568904504</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -10965,10 +10965,10 @@
         <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>0.900990099009901</v>
+        <v>0.9010600706713781</v>
       </c>
       <c r="H125" t="n">
-        <v>111.9987128712871</v>
+        <v>111.9990106007067</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -10987,16 +10987,16 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>105.5787128712871</v>
+        <v>105.5790106007067</v>
       </c>
       <c r="N125" t="n">
-        <v>105.5787128712871</v>
+        <v>105.5790106007067</v>
       </c>
       <c r="O125" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P125" t="n">
-        <v>-0.1431541725601164</v>
+        <v>-0.1433498233215573</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -11036,10 +11036,10 @@
         <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>0.8578500707213579</v>
+        <v>0.8579505300353357</v>
       </c>
       <c r="H126" t="n">
-        <v>111.6754561527581</v>
+        <v>111.6767385159011</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -11058,16 +11058,16 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>105.4454561527581</v>
+        <v>105.446738515901</v>
       </c>
       <c r="N126" t="n">
-        <v>105.4454561527581</v>
+        <v>105.446738515901</v>
       </c>
       <c r="O126" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.3232567185289952</v>
+        <v>-0.3222720848056611</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -11107,10 +11107,10 @@
         <v>8</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8118811881188119</v>
+        <v>0.8120141342756184</v>
       </c>
       <c r="H127" t="n">
-        <v>111.4330363036304</v>
+        <v>111.4334134275618</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -11129,16 +11129,16 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>105.3730363036304</v>
+        <v>105.3734134275618</v>
       </c>
       <c r="N127" t="n">
-        <v>105.3730363036304</v>
+        <v>105.3734134275618</v>
       </c>
       <c r="O127" t="n">
         <v>-0.1700000000000008</v>
       </c>
       <c r="P127" t="n">
-        <v>-0.2424198491277565</v>
+        <v>-0.2433250883392049</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -11178,10 +11178,10 @@
         <v>8</v>
       </c>
       <c r="G128" t="n">
-        <v>0.7531824611032532</v>
+        <v>0.7533568904593639</v>
       </c>
       <c r="H128" t="n">
-        <v>111.1691654879774</v>
+        <v>111.1702134275618</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -11200,16 +11200,16 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>105.2391654879774</v>
+        <v>105.2402134275618</v>
       </c>
       <c r="N128" t="n">
-        <v>105.2391654879774</v>
+        <v>105.2402134275618</v>
       </c>
       <c r="O128" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.2638708156530072</v>
+        <v>-0.2632000000000119</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -11249,10 +11249,10 @@
         <v>8</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6753889674681753</v>
+        <v>0.6756183745583039</v>
       </c>
       <c r="H129" t="n">
-        <v>110.7613401697313</v>
+        <v>110.7642685512368</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -11271,16 +11271,16 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>52.39634016973125</v>
+        <v>52.39926855123675</v>
       </c>
       <c r="N129" t="n">
-        <v>52.39634016973125</v>
+        <v>52.39926855123675</v>
       </c>
       <c r="O129" t="n">
         <v>52.435</v>
       </c>
       <c r="P129" t="n">
-        <v>-0.4078253182461111</v>
+        <v>-0.4059448763250799</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -11320,10 +11320,10 @@
         <v>8</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5975954738330976</v>
+        <v>0.5978798586572438</v>
       </c>
       <c r="H130" t="n">
-        <v>110.3727687411598</v>
+        <v>110.3739787985866</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -11342,16 +11342,16 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>52.07776874115983</v>
+        <v>52.07897879858658</v>
       </c>
       <c r="N130" t="n">
-        <v>52.07776874115983</v>
+        <v>52.07897879858658</v>
       </c>
       <c r="O130" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.3885714285714243</v>
+        <v>-0.3902897526501761</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         <v>8</v>
       </c>
       <c r="G131" t="n">
-        <v>0.516973125884017</v>
+        <v>0.5173144876325089</v>
       </c>
       <c r="H131" t="n">
-        <v>109.969813767091</v>
+        <v>109.9707038869258</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -11413,16 +11413,16 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>51.78481376709099</v>
+        <v>51.78570388692579</v>
       </c>
       <c r="N131" t="n">
-        <v>51.78481376709099</v>
+        <v>51.78570388692579</v>
       </c>
       <c r="O131" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.4029549740688338</v>
+        <v>-0.4032749116607874</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -11462,10 +11462,10 @@
         <v>8</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4321074964639321</v>
+        <v>0.4325088339222615</v>
       </c>
       <c r="H132" t="n">
-        <v>109.451489863272</v>
+        <v>109.4537667844523</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -11484,16 +11484,16 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>51.40648986327203</v>
+        <v>51.4087667844523</v>
       </c>
       <c r="N132" t="n">
-        <v>51.40648986327203</v>
+        <v>51.4087667844523</v>
       </c>
       <c r="O132" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.5183239038189669</v>
+        <v>-0.5169371024734914</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -11533,10 +11533,10 @@
         <v>8</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3514851485148515</v>
+        <v>0.3519434628975265</v>
       </c>
       <c r="H133" t="n">
-        <v>108.9105693069307</v>
+        <v>108.912519434629</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -11555,16 +11555,16 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>103.4705693069307</v>
+        <v>103.472519434629</v>
       </c>
       <c r="N133" t="n">
-        <v>103.4705693069307</v>
+        <v>103.472519434629</v>
       </c>
       <c r="O133" t="n">
         <v>-52.605</v>
       </c>
       <c r="P133" t="n">
-        <v>-0.5409205563413337</v>
+        <v>-0.5412473498233226</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -11604,10 +11604,10 @@
         <v>8</v>
       </c>
       <c r="G134" t="n">
-        <v>0.268033946251768</v>
+        <v>0.2685512367491166</v>
       </c>
       <c r="H134" t="n">
-        <v>108.4009688826026</v>
+        <v>108.405371024735</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -11626,16 +11626,16 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>103.0809688826025</v>
+        <v>103.085371024735</v>
       </c>
       <c r="N134" t="n">
-        <v>103.0809688826025</v>
+        <v>103.085371024735</v>
       </c>
       <c r="O134" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P134" t="n">
-        <v>-0.5096004243281413</v>
+        <v>-0.5071484098939862</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
         <v>8</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9314002828854314</v>
+        <v>0.9314487632508834</v>
       </c>
       <c r="H154" t="n">
-        <v>9.031902404526168</v>
+        <v>9.031971731448763</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -13034,16 +13034,16 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>0.5719024045261669</v>
+        <v>0.5719717314487625</v>
       </c>
       <c r="N154" t="n">
-        <v>0.5719024045261669</v>
+        <v>0.5719717314487625</v>
       </c>
       <c r="O154" t="n">
         <v>0.005000000000000782</v>
       </c>
       <c r="P154" t="n">
-        <v>0.582893119312434</v>
+        <v>0.5829624462350296</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>8</v>
       </c>
       <c r="G155" t="n">
-        <v>0.9214992927864215</v>
+        <v>0.9215547703180212</v>
       </c>
       <c r="H155" t="n">
         <v>9.009999999999998</v>
@@ -13114,7 +13114,7 @@
         <v>-0.03000000000000114</v>
       </c>
       <c r="P155" t="n">
-        <v>-0.02190240452616976</v>
+        <v>-0.0219717314487653</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -13154,10 +13154,10 @@
         <v>8</v>
       </c>
       <c r="G156" t="n">
-        <v>0.9144271570014144</v>
+        <v>0.9144876325088339</v>
       </c>
       <c r="H156" t="n">
-        <v>8.967630834512024</v>
+        <v>8.967717314487633</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -13176,16 +13176,16 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0.5576308345120236</v>
+        <v>0.5577173144876326</v>
       </c>
       <c r="N156" t="n">
-        <v>0.5576308345120236</v>
+        <v>0.5577173144876326</v>
       </c>
       <c r="O156" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P156" t="n">
-        <v>-0.04236916548797431</v>
+        <v>-0.04228268551236525</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -13225,10 +13225,10 @@
         <v>8</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9052333804809052</v>
+        <v>0.9053003533568904</v>
       </c>
       <c r="H157" t="n">
-        <v>8.92146746817539</v>
+        <v>8.921659010600708</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -13247,16 +13247,16 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>0.6214674681753891</v>
+        <v>0.6216590106007072</v>
       </c>
       <c r="N157" t="n">
-        <v>0.6214674681753891</v>
+        <v>0.6216590106007072</v>
       </c>
       <c r="O157" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P157" t="n">
-        <v>-0.04616336633663387</v>
+        <v>-0.04605830388692489</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>8</v>
       </c>
       <c r="G158" t="n">
-        <v>0.8953323903818954</v>
+        <v>0.8954063604240282</v>
       </c>
       <c r="H158" t="n">
-        <v>8.857825318246112</v>
+        <v>8.857931095406361</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -13318,16 +13318,16 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>0.6878253182461123</v>
+        <v>0.6879310954063609</v>
       </c>
       <c r="N158" t="n">
-        <v>0.6878253182461123</v>
+        <v>0.6879310954063609</v>
       </c>
       <c r="O158" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P158" t="n">
-        <v>-0.06364214992927764</v>
+        <v>-0.06372791519434706</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -13367,10 +13367,10 @@
         <v>8</v>
       </c>
       <c r="G159" t="n">
-        <v>0.888967468175389</v>
+        <v>0.8890459363957597</v>
       </c>
       <c r="H159" t="n">
-        <v>8.791064356435642</v>
+        <v>8.791849823321554</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -13389,16 +13389,16 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>0.8410643564356421</v>
+        <v>0.8418498233215539</v>
       </c>
       <c r="N159" t="n">
-        <v>0.8410643564356421</v>
+        <v>0.8418498233215539</v>
       </c>
       <c r="O159" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P159" t="n">
-        <v>-0.06676096181046987</v>
+        <v>-0.06608127208480674</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -13438,10 +13438,10 @@
         <v>8</v>
       </c>
       <c r="G160" t="n">
-        <v>0.8656294200848657</v>
+        <v>0.8657243816254417</v>
       </c>
       <c r="H160" t="n">
-        <v>8.432450495049505</v>
+        <v>8.433401060070672</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -13460,16 +13460,16 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>0.6624504950495052</v>
+        <v>0.6634010600706723</v>
       </c>
       <c r="N160" t="n">
-        <v>0.6624504950495052</v>
+        <v>0.6634010600706723</v>
       </c>
       <c r="O160" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P160" t="n">
-        <v>-0.3586138613861376</v>
+        <v>-0.3584487632508822</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -13509,10 +13509,10 @@
         <v>8</v>
       </c>
       <c r="G161" t="n">
-        <v>0.8585572842998586</v>
+        <v>0.8586572438162544</v>
       </c>
       <c r="H161" t="n">
-        <v>8.234370579915133</v>
+        <v>8.238515901060071</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -13531,16 +13531,16 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>0.5043705799151326</v>
+        <v>0.5085159010600702</v>
       </c>
       <c r="N161" t="n">
-        <v>0.5043705799151326</v>
+        <v>0.5085159010600702</v>
       </c>
       <c r="O161" t="n">
         <v>-0.03999999999999915</v>
       </c>
       <c r="P161" t="n">
-        <v>-0.1980799151343717</v>
+        <v>-0.1948851590106013</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -13580,10 +13580,10 @@
         <v>8</v>
       </c>
       <c r="G162" t="n">
-        <v>0.8493635077793493</v>
+        <v>0.8494699646643109</v>
       </c>
       <c r="H162" t="n">
-        <v>8.010077793493632</v>
+        <v>8.011904593639573</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -13602,16 +13602,16 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>0.3100777934936323</v>
+        <v>0.3119045936395723</v>
       </c>
       <c r="N162" t="n">
-        <v>0.3100777934936323</v>
+        <v>0.3119045936395723</v>
       </c>
       <c r="O162" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P162" t="n">
-        <v>-0.2242927864215005</v>
+        <v>-0.2266113074204981</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -13651,10 +13651,10 @@
         <v>8</v>
       </c>
       <c r="G163" t="n">
-        <v>0.8444130127298444</v>
+        <v>0.8445229681978799</v>
       </c>
       <c r="H163" t="n">
-        <v>7.950031824611033</v>
+        <v>7.950503533568905</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -13673,16 +13673,16 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>0.3100318246110332</v>
+        <v>0.3105035335689053</v>
       </c>
       <c r="N163" t="n">
-        <v>0.3100318246110332</v>
+        <v>0.3105035335689053</v>
       </c>
       <c r="O163" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P163" t="n">
-        <v>-0.06004596888259961</v>
+        <v>-0.06140106007066759</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -13722,10 +13722,10 @@
         <v>8</v>
       </c>
       <c r="G164" t="n">
-        <v>0.8380480905233381</v>
+        <v>0.8381625441696113</v>
       </c>
       <c r="H164" t="n">
-        <v>7.841587694483734</v>
+        <v>7.843224381625442</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -13744,16 +13744,16 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>0.2815876944837346</v>
+        <v>0.2832243816254421</v>
       </c>
       <c r="N164" t="n">
-        <v>0.2815876944837346</v>
+        <v>0.2832243816254421</v>
       </c>
       <c r="O164" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P164" t="n">
-        <v>-0.1084441301272987</v>
+        <v>-0.1072791519434633</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -13793,10 +13793,10 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>0.8352192362093352</v>
+        <v>0.8353356890459364</v>
       </c>
       <c r="H165" t="n">
-        <v>7.82936350777935</v>
+        <v>7.829530035335689</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -13815,16 +13815,16 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>0.3493635077793495</v>
+        <v>0.3495300353356887</v>
       </c>
       <c r="N165" t="n">
-        <v>0.3493635077793495</v>
+        <v>0.3495300353356887</v>
       </c>
       <c r="O165" t="n">
         <v>-0.07999999999999918</v>
       </c>
       <c r="P165" t="n">
-        <v>-0.01222418670438419</v>
+        <v>-0.01369434628975252</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -13864,10 +13864,10 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>0.8267326732673267</v>
+        <v>0.8268551236749117</v>
       </c>
       <c r="H166" t="n">
-        <v>7.755321782178218</v>
+        <v>7.75672261484099</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -13886,16 +13886,16 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>0.3853217821782176</v>
+        <v>0.3867226148409895</v>
       </c>
       <c r="N166" t="n">
-        <v>0.3853217821782176</v>
+        <v>0.3867226148409895</v>
       </c>
       <c r="O166" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P166" t="n">
-        <v>-0.07404172560113231</v>
+        <v>-0.07280742049469957</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -15065,10 +15065,10 @@
         <v>8</v>
       </c>
       <c r="G183" t="n">
-        <v>0.8005657708628006</v>
+        <v>0.8007067137809187</v>
       </c>
       <c r="H183" t="n">
-        <v>5.551479844413013</v>
+        <v>5.551537102473499</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -15087,16 +15087,16 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>0.336479844413013</v>
+        <v>0.3365371024734989</v>
       </c>
       <c r="N183" t="n">
-        <v>0.336479844413013</v>
+        <v>0.3365371024734989</v>
       </c>
       <c r="O183" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P183" t="n">
-        <v>-0.09260039384907603</v>
+        <v>-0.09254313578859019</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -15136,10 +15136,10 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>0.8536067892503536</v>
+        <v>0.8537102473498234</v>
       </c>
       <c r="H184" t="n">
-        <v>5.75922206506365</v>
+        <v>5.759558303886926</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -15158,16 +15158,16 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>0.5942220650636498</v>
+        <v>0.5945583038869264</v>
       </c>
       <c r="N184" t="n">
-        <v>0.5942220650636498</v>
+        <v>0.5945583038869264</v>
       </c>
       <c r="O184" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P184" t="n">
-        <v>0.207742220650637</v>
+        <v>0.2080212014134277</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -15207,10 +15207,10 @@
         <v>8</v>
       </c>
       <c r="G185" t="n">
-        <v>0.8677510608203678</v>
+        <v>0.8678445229681979</v>
       </c>
       <c r="H185" t="n">
-        <v>5.800047736916548</v>
+        <v>5.800123674911661</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -15229,16 +15229,16 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>0.6800477369165483</v>
+        <v>0.6801236749116608</v>
       </c>
       <c r="N185" t="n">
-        <v>0.6800477369165483</v>
+        <v>0.6801236749116608</v>
       </c>
       <c r="O185" t="n">
         <v>-0.04499999999999993</v>
       </c>
       <c r="P185" t="n">
-        <v>0.04082567185289854</v>
+        <v>0.04056537102473445</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -15278,10 +15278,10 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>0.864922206506365</v>
+        <v>0.8650176678445229</v>
       </c>
       <c r="H186" t="n">
-        <v>5.786495756718529</v>
+        <v>5.786961130742049</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -15300,16 +15300,16 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>0.706495756718529</v>
+        <v>0.7069611307420489</v>
       </c>
       <c r="N186" t="n">
-        <v>0.706495756718529</v>
+        <v>0.7069611307420489</v>
       </c>
       <c r="O186" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P186" t="n">
-        <v>-0.01355198019801929</v>
+        <v>-0.01316254416961193</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -15349,10 +15349,10 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8437057991513437</v>
+        <v>0.8438162544169612</v>
       </c>
       <c r="H187" t="n">
-        <v>5.683521923620933</v>
+        <v>5.683701413427562</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -15371,16 +15371,16 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>0.2535219236209336</v>
+        <v>0.2537014134275619</v>
       </c>
       <c r="N187" t="n">
-        <v>0.2535219236209336</v>
+        <v>0.2537014134275619</v>
       </c>
       <c r="O187" t="n">
         <v>0.3499999999999996</v>
       </c>
       <c r="P187" t="n">
-        <v>-0.1029738330975958</v>
+        <v>-0.1032597173144874</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -15420,10 +15420,10 @@
         <v>8</v>
       </c>
       <c r="G188" t="n">
-        <v>0.7963224893917963</v>
+        <v>0.7964664310954064</v>
       </c>
       <c r="H188" t="n">
-        <v>5.544632248939179</v>
+        <v>5.545918727915194</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -15442,16 +15442,16 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.05786775106082143</v>
+        <v>-0.05658127208480579</v>
       </c>
       <c r="N188" t="n">
-        <v>0.05786775106082143</v>
+        <v>0.05658127208480579</v>
       </c>
       <c r="O188" t="n">
         <v>0.1725000000000003</v>
       </c>
       <c r="P188" t="n">
-        <v>-0.1388896746817547</v>
+        <v>-0.1377826855123674</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -15491,10 +15491,10 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>0.7496463932107497</v>
+        <v>0.7491166077738516</v>
       </c>
       <c r="H189" t="n">
-        <v>5.394964639321076</v>
+        <v>5.390229681978799</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -15513,16 +15513,16 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.1550353606789239</v>
+        <v>-0.1597703180212005</v>
       </c>
       <c r="N189" t="n">
-        <v>0.1550353606789239</v>
+        <v>0.1597703180212005</v>
       </c>
       <c r="O189" t="n">
         <v>-0.05250000000000021</v>
       </c>
       <c r="P189" t="n">
-        <v>-0.1496676096181027</v>
+        <v>-0.1556890459363949</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -15562,10 +15562,10 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>0.7213578500707214</v>
+        <v>0.7208480565371025</v>
       </c>
       <c r="H190" t="n">
-        <v>5.281103253182462</v>
+        <v>5.280689045936396</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -15584,16 +15584,16 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>0.001103253182461295</v>
+        <v>0.0006890459363955159</v>
       </c>
       <c r="N190" t="n">
-        <v>0.001103253182461295</v>
+        <v>0.0006890459363955159</v>
       </c>
       <c r="O190" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P190" t="n">
-        <v>-0.1138613861386144</v>
+        <v>-0.1095406360424036</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -15633,10 +15633,10 @@
         <v>8</v>
       </c>
       <c r="G191" t="n">
-        <v>0.7164073550212164</v>
+        <v>0.7159010600706713</v>
       </c>
       <c r="H191" t="n">
-        <v>5.278540487977369</v>
+        <v>5.27833480565371</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -15655,16 +15655,16 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>0.2535404879773706</v>
+        <v>0.2533348056537115</v>
       </c>
       <c r="N191" t="n">
-        <v>0.2535404879773706</v>
+        <v>0.2533348056537115</v>
       </c>
       <c r="O191" t="n">
         <v>-0.2550000000000017</v>
       </c>
       <c r="P191" t="n">
-        <v>-0.002562765205092354</v>
+        <v>-0.002354240282685716</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -15704,10 +15704,10 @@
         <v>8</v>
       </c>
       <c r="G192" t="n">
-        <v>0.7248939179632249</v>
+        <v>0.7243816254416962</v>
       </c>
       <c r="H192" t="n">
-        <v>5.291357850070721</v>
+        <v>5.288860424028269</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -15726,16 +15726,16 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>0.4413578500707214</v>
+        <v>0.4388604240282694</v>
       </c>
       <c r="N192" t="n">
-        <v>0.4413578500707214</v>
+        <v>0.4388604240282694</v>
       </c>
       <c r="O192" t="n">
         <v>-0.1749999999999989</v>
       </c>
       <c r="P192" t="n">
-        <v>0.01281736209335183</v>
+        <v>0.01052561837455901</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -15775,10 +15775,10 @@
         <v>8</v>
       </c>
       <c r="G193" t="n">
-        <v>0.731966053748232</v>
+        <v>0.7314487632508834</v>
       </c>
       <c r="H193" t="n">
-        <v>5.333336280056576</v>
+        <v>5.32703180212014</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -15797,16 +15797,16 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>0.7633362800565759</v>
+        <v>0.7570318021201397</v>
       </c>
       <c r="N193" t="n">
-        <v>0.7633362800565759</v>
+        <v>0.7570318021201397</v>
       </c>
       <c r="O193" t="n">
         <v>-0.2799999999999994</v>
       </c>
       <c r="P193" t="n">
-        <v>0.04197842998585521</v>
+        <v>0.03817137809187088</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -15846,10 +15846,10 @@
         <v>8</v>
       </c>
       <c r="G194" t="n">
-        <v>0.7227722772277227</v>
+        <v>0.72226148409894</v>
       </c>
       <c r="H194" t="n">
-        <v>5.282252475247525</v>
+        <v>5.281837455830389</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15868,16 +15868,16 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>0.8522524752475249</v>
+        <v>0.8518374558303892</v>
       </c>
       <c r="N194" t="n">
-        <v>0.8522524752475249</v>
+        <v>0.8518374558303892</v>
       </c>
       <c r="O194" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P194" t="n">
-        <v>-0.05108380480905161</v>
+        <v>-0.04519434628975105</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -15886,11 +15886,11 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -15917,10 +15917,10 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>0.6951909476661952</v>
+        <v>0.6946996466431096</v>
       </c>
       <c r="H195" t="n">
-        <v>5.214685289957567</v>
+        <v>5.213886925795054</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -15939,16 +15939,16 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>0.7346852899575662</v>
+        <v>0.7338869257950531</v>
       </c>
       <c r="N195" t="n">
-        <v>0.7346852899575662</v>
+        <v>0.7338869257950531</v>
       </c>
       <c r="O195" t="n">
         <v>0.05000000000000071</v>
       </c>
       <c r="P195" t="n">
-        <v>-0.06756718528995798</v>
+        <v>-0.06795053003533535</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -15988,10 +15988,10 @@
         <v>8</v>
       </c>
       <c r="G196" t="n">
-        <v>0.6562942008486563</v>
+        <v>0.6558303886925795</v>
       </c>
       <c r="H196" t="n">
-        <v>5.122956152758134</v>
+        <v>5.121448763250884</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -16010,16 +16010,16 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>0.3329561527581335</v>
+        <v>0.3314487632508838</v>
       </c>
       <c r="N196" t="n">
-        <v>0.3329561527581335</v>
+        <v>0.3314487632508838</v>
       </c>
       <c r="O196" t="n">
         <v>0.3099999999999996</v>
       </c>
       <c r="P196" t="n">
-        <v>-0.0917291371994331</v>
+        <v>-0.0924381625441697</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>0.756011315417256</v>
+        <v>0.7561837455830389</v>
       </c>
       <c r="H213" t="n">
         <v>5.97</v>
@@ -17260,10 +17260,10 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>0.7553041018387553</v>
+        <v>0.7554770318021201</v>
       </c>
       <c r="H214" t="n">
-        <v>5.969483734087694</v>
+        <v>5.969711425206125</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -17282,16 +17282,16 @@
         <v>1</v>
       </c>
       <c r="M214" t="n">
-        <v>-2.618016265912305</v>
+        <v>-2.617788574793874</v>
       </c>
       <c r="N214" t="n">
-        <v>2.618016265912305</v>
+        <v>2.617788574793874</v>
       </c>
       <c r="O214" t="n">
         <v>-0.1500000000000021</v>
       </c>
       <c r="P214" t="n">
-        <v>-0.0005162659123056912</v>
+        <v>-0.0002885747938750072</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>0.7659123055162659</v>
+        <v>0.7660777385159011</v>
       </c>
       <c r="H215" t="n">
-        <v>6.010530410183875</v>
+        <v>6.011510600706714</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -17353,16 +17353,16 @@
         <v>1</v>
       </c>
       <c r="M215" t="n">
-        <v>-2.469469589816125</v>
+        <v>-2.468489399293286</v>
       </c>
       <c r="N215" t="n">
-        <v>2.469469589816125</v>
+        <v>2.468489399293286</v>
       </c>
       <c r="O215" t="n">
         <v>-0.1074999999999982</v>
       </c>
       <c r="P215" t="n">
-        <v>0.0410466760961814</v>
+        <v>0.04179917550058931</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -17402,10 +17402,10 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>0.7864214992927864</v>
+        <v>0.7865724381625442</v>
       </c>
       <c r="H216" t="n">
-        <v>6.102729844413012</v>
+        <v>6.103922261484099</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -17424,16 +17424,16 @@
         <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>-2.107270155586988</v>
+        <v>-2.106077738515902</v>
       </c>
       <c r="N216" t="n">
-        <v>2.107270155586988</v>
+        <v>2.106077738515902</v>
       </c>
       <c r="O216" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P216" t="n">
-        <v>0.09219943422913701</v>
+        <v>0.09241166077738505</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -17473,10 +17473,10 @@
         <v>8</v>
       </c>
       <c r="G217" t="n">
-        <v>0.809052333804809</v>
+        <v>0.8091872791519434</v>
       </c>
       <c r="H217" t="n">
-        <v>6.201513437057992</v>
+        <v>6.202579505300354</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -17495,16 +17495,16 @@
         <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>-1.958486562942008</v>
+        <v>-1.957420494699647</v>
       </c>
       <c r="N217" t="n">
-        <v>1.958486562942008</v>
+        <v>1.957420494699647</v>
       </c>
       <c r="O217" t="n">
         <v>-0.05000000000000071</v>
       </c>
       <c r="P217" t="n">
-        <v>0.09878359264497938</v>
+        <v>0.09865724381625451</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -17544,10 +17544,10 @@
         <v>8</v>
       </c>
       <c r="G218" t="n">
-        <v>0.8274398868458275</v>
+        <v>0.8275618374558303</v>
       </c>
       <c r="H218" t="n">
-        <v>6.294516737388025</v>
+        <v>6.295159010600707</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -17566,16 +17566,16 @@
         <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>-1.635483262611975</v>
+        <v>-1.634840989399293</v>
       </c>
       <c r="N218" t="n">
-        <v>1.635483262611975</v>
+        <v>1.634840989399293</v>
       </c>
       <c r="O218" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P218" t="n">
-        <v>0.09300330033003323</v>
+        <v>0.0925795053003533</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -17615,10 +17615,10 @@
         <v>8</v>
       </c>
       <c r="G219" t="n">
-        <v>0.8444130127298444</v>
+        <v>0.8445229681978799</v>
       </c>
       <c r="H219" t="n">
-        <v>6.385215700141442</v>
+        <v>6.385432862190813</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -17637,16 +17637,16 @@
         <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>-1.604784299858558</v>
+        <v>-1.604567137809187</v>
       </c>
       <c r="N219" t="n">
-        <v>1.604784299858558</v>
+        <v>1.604567137809187</v>
       </c>
       <c r="O219" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P219" t="n">
-        <v>0.09069896275341716</v>
+        <v>0.09027385159010581</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -17686,10 +17686,10 @@
         <v>8</v>
       </c>
       <c r="G220" t="n">
-        <v>0.8514851485148515</v>
+        <v>0.8515901060070671</v>
       </c>
       <c r="H220" t="n">
-        <v>6.45019801980198</v>
+        <v>6.45268551236749</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -17708,16 +17708,16 @@
         <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>-1.53980198019802</v>
+        <v>-1.53731448763251</v>
       </c>
       <c r="N220" t="n">
-        <v>1.53980198019802</v>
+        <v>1.53731448763251</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
       </c>
       <c r="P220" t="n">
-        <v>0.06498231966053769</v>
+        <v>0.0672526501766777</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -17757,10 +17757,10 @@
         <v>8</v>
       </c>
       <c r="G221" t="n">
-        <v>0.8422913719943423</v>
+        <v>0.8424028268551237</v>
       </c>
       <c r="H221" t="n">
-        <v>6.381025459688826</v>
+        <v>6.381245583038869</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -17779,16 +17779,16 @@
         <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>-1.476474540311174</v>
+        <v>-1.47625441696113</v>
       </c>
       <c r="N221" t="n">
-        <v>1.476474540311174</v>
+        <v>1.47625441696113</v>
       </c>
       <c r="O221" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P221" t="n">
-        <v>-0.06917256011315409</v>
+        <v>-0.07143992932862098</v>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
@@ -17828,10 +17828,10 @@
         <v>8</v>
       </c>
       <c r="G222" t="n">
-        <v>0.8224893917963225</v>
+        <v>0.8226148409893993</v>
       </c>
       <c r="H222" t="n">
-        <v>6.249222065063649</v>
+        <v>6.249552414605418</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -17850,16 +17850,16 @@
         <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>-1.490777934936351</v>
+        <v>-1.490447585394582</v>
       </c>
       <c r="N222" t="n">
-        <v>1.490777934936351</v>
+        <v>1.490447585394582</v>
       </c>
       <c r="O222" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.1318033946251767</v>
+        <v>-0.1316931684334515</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -17899,10 +17899,10 @@
         <v>8</v>
       </c>
       <c r="G223" t="n">
-        <v>0.8048090523338048</v>
+        <v>0.8049469964664311</v>
       </c>
       <c r="H223" t="n">
-        <v>6.17933050447902</v>
+        <v>6.179693757361601</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -17921,16 +17921,16 @@
         <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>-1.44066949552098</v>
+        <v>-1.440306242638399</v>
       </c>
       <c r="N223" t="n">
-        <v>1.44066949552098</v>
+        <v>1.440306242638399</v>
       </c>
       <c r="O223" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.06989156058462953</v>
+        <v>-0.06985865724381668</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -17970,10 +17970,10 @@
         <v>8</v>
       </c>
       <c r="G224" t="n">
-        <v>0.7800565770862801</v>
+        <v>0.7802120141342757</v>
       </c>
       <c r="H224" t="n">
-        <v>6.076555869872701</v>
+        <v>6.076709363957597</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -17992,16 +17992,16 @@
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>-1.323444130127299</v>
+        <v>-1.323290636042404</v>
       </c>
       <c r="N224" t="n">
-        <v>1.323444130127299</v>
+        <v>1.323290636042404</v>
       </c>
       <c r="O224" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.1027746346063187</v>
+        <v>-0.1029843934040047</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -18041,10 +18041,10 @@
         <v>8</v>
       </c>
       <c r="G225" t="n">
-        <v>0.7524752475247525</v>
+        <v>0.7526501766784452</v>
       </c>
       <c r="H225" t="n">
-        <v>5.965759075907591</v>
+        <v>5.965989399293286</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -18063,16 +18063,16 @@
         <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>-1.39424092409241</v>
+        <v>-1.394010600706714</v>
       </c>
       <c r="N225" t="n">
-        <v>1.39424092409241</v>
+        <v>1.394010600706714</v>
       </c>
       <c r="O225" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.1107967939651102</v>
+        <v>-0.1107199646643107</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>8</v>
       </c>
       <c r="G226" t="n">
-        <v>0.7277227722772277</v>
+        <v>0.7279151943462897</v>
       </c>
       <c r="H226" t="n">
-        <v>5.829009900990099</v>
+        <v>5.830530035335689</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -18134,16 +18134,16 @@
         <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>-1.550990099009901</v>
+        <v>-1.549469964664311</v>
       </c>
       <c r="N226" t="n">
-        <v>1.550990099009901</v>
+        <v>1.549469964664311</v>
       </c>
       <c r="O226" t="n">
         <v>0.01999999999999957</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.1367491749174921</v>
+        <v>-0.1354593639575974</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -19313,10 +19313,10 @@
         <v>8</v>
       </c>
       <c r="G243" t="n">
-        <v>0.8288543140028288</v>
+        <v>0.8289752650176678</v>
       </c>
       <c r="H243" t="n">
-        <v>5.568412305516264</v>
+        <v>5.570818021201411</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -19335,16 +19335,16 @@
         <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>1.578412305516264</v>
+        <v>1.580818021201411</v>
       </c>
       <c r="N243" t="n">
-        <v>1.578412305516264</v>
+        <v>1.580818021201411</v>
       </c>
       <c r="O243" t="n">
         <v>-0.1624999999999996</v>
       </c>
       <c r="P243" t="n">
-        <v>-1.592505704294528</v>
+        <v>-1.590099988609381</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -19384,10 +19384,10 @@
         <v>8</v>
       </c>
       <c r="G244" t="n">
-        <v>0.7050919377652051</v>
+        <v>0.7053003533568905</v>
       </c>
       <c r="H244" t="n">
-        <v>4.932581329561527</v>
+        <v>4.933219081272084</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -19406,16 +19406,16 @@
         <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>1.110081329561527</v>
+        <v>1.110719081272085</v>
       </c>
       <c r="N244" t="n">
-        <v>1.110081329561527</v>
+        <v>1.110719081272085</v>
       </c>
       <c r="O244" t="n">
         <v>-0.1675000000000004</v>
       </c>
       <c r="P244" t="n">
-        <v>-0.6358309759547369</v>
+        <v>-0.6375989399293269</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -19455,10 +19455,10 @@
         <v>8</v>
       </c>
       <c r="G245" t="n">
-        <v>0.615983026874116</v>
+        <v>0.6162544169611307</v>
       </c>
       <c r="H245" t="n">
-        <v>4.630802687411599</v>
+        <v>4.631079505300353</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -19477,16 +19477,16 @@
         <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>0.850802687411599</v>
+        <v>0.8510795053003535</v>
       </c>
       <c r="N245" t="n">
-        <v>0.850802687411599</v>
+        <v>0.8510795053003535</v>
       </c>
       <c r="O245" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.3017786421499284</v>
+        <v>-0.3021395759717311</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -19526,10 +19526,10 @@
         <v>8</v>
       </c>
       <c r="G246" t="n">
-        <v>0.594059405940594</v>
+        <v>0.5943462897526501</v>
       </c>
       <c r="H246" t="n">
-        <v>4.566905940594059</v>
+        <v>4.569832155477031</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -19548,16 +19548,16 @@
         <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>0.8869059405940587</v>
+        <v>0.889832155477031</v>
       </c>
       <c r="N246" t="n">
-        <v>0.8869059405940587</v>
+        <v>0.889832155477031</v>
       </c>
       <c r="O246" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.06389674681753998</v>
+        <v>-0.06124734982332214</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -19597,10 +19597,10 @@
         <v>8</v>
       </c>
       <c r="G247" t="n">
-        <v>0.6343705799151343</v>
+        <v>0.6346289752650177</v>
       </c>
       <c r="H247" t="n">
-        <v>4.723673974540311</v>
+        <v>4.724464664310954</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -19619,16 +19619,16 @@
         <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>1.143673974540311</v>
+        <v>1.144464664310954</v>
       </c>
       <c r="N247" t="n">
-        <v>1.143673974540311</v>
+        <v>1.144464664310954</v>
       </c>
       <c r="O247" t="n">
         <v>-0.1000000000000001</v>
       </c>
       <c r="P247" t="n">
-        <v>0.1567680339462525</v>
+        <v>0.1546325088339229</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -19668,10 +19668,10 @@
         <v>8</v>
       </c>
       <c r="G248" t="n">
-        <v>0.6471004243281471</v>
+        <v>0.6473498233215548</v>
       </c>
       <c r="H248" t="n">
-        <v>4.76008486562942</v>
+        <v>4.760593639575972</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19690,16 +19690,16 @@
         <v>1</v>
       </c>
       <c r="M248" t="n">
-        <v>1.36758486562942</v>
+        <v>1.368093639575972</v>
       </c>
       <c r="N248" t="n">
-        <v>1.36758486562942</v>
+        <v>1.368093639575972</v>
       </c>
       <c r="O248" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P248" t="n">
-        <v>0.03641089108910833</v>
+        <v>0.03612897526501779</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -19739,10 +19739,10 @@
         <v>8</v>
       </c>
       <c r="G249" t="n">
-        <v>0.5968882602545968</v>
+        <v>0.5971731448763251</v>
       </c>
       <c r="H249" t="n">
-        <v>4.595760254596888</v>
+        <v>4.598666077738517</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19761,16 +19761,16 @@
         <v>1</v>
       </c>
       <c r="M249" t="n">
-        <v>1.315760254596888</v>
+        <v>1.318666077738517</v>
       </c>
       <c r="N249" t="n">
-        <v>1.315760254596888</v>
+        <v>1.318666077738517</v>
       </c>
       <c r="O249" t="n">
         <v>-0.1125000000000003</v>
       </c>
       <c r="P249" t="n">
-        <v>-0.1643246110325318</v>
+        <v>-0.1619275618374552</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -19810,10 +19810,10 @@
         <v>8</v>
       </c>
       <c r="G250" t="n">
-        <v>0.4908062234794908</v>
+        <v>0.4904593639575971</v>
       </c>
       <c r="H250" t="n">
-        <v>4.151234087694484</v>
+        <v>4.149111307420495</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19832,16 +19832,16 @@
         <v>1</v>
       </c>
       <c r="M250" t="n">
-        <v>1.001234087694484</v>
+        <v>0.9991113074204949</v>
       </c>
       <c r="N250" t="n">
-        <v>1.001234087694484</v>
+        <v>0.9991113074204949</v>
       </c>
       <c r="O250" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P250" t="n">
-        <v>-0.4445261669024037</v>
+        <v>-0.4495547703180218</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -19881,10 +19881,10 @@
         <v>8</v>
       </c>
       <c r="G251" t="n">
-        <v>0.3910891089108911</v>
+        <v>0.3908127208480565</v>
       </c>
       <c r="H251" t="n">
-        <v>3.804232673267327</v>
+        <v>3.803386925795053</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19903,16 +19903,16 @@
         <v>1</v>
       </c>
       <c r="M251" t="n">
-        <v>0.8592326732673272</v>
+        <v>0.8583869257950534</v>
       </c>
       <c r="N251" t="n">
-        <v>0.8592326732673272</v>
+        <v>0.8583869257950534</v>
       </c>
       <c r="O251" t="n">
         <v>-0.2050000000000001</v>
       </c>
       <c r="P251" t="n">
-        <v>-0.3470014144271572</v>
+        <v>-0.3457243816254416</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         <v>8</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3366336633663367</v>
+        <v>0.3363957597173145</v>
       </c>
       <c r="H252" t="n">
-        <v>3.641221122112211</v>
+        <v>3.640412249705536</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19974,16 +19974,16 @@
         <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>0.8012211221122114</v>
+        <v>0.8004122497055359</v>
       </c>
       <c r="N252" t="n">
-        <v>0.8012211221122114</v>
+        <v>0.8004122497055359</v>
       </c>
       <c r="O252" t="n">
         <v>-0.105</v>
       </c>
       <c r="P252" t="n">
-        <v>-0.1630115511551158</v>
+        <v>-0.1629746760895174</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -20023,10 +20023,10 @@
         <v>8</v>
       </c>
       <c r="G253" t="n">
-        <v>0.3472418670438472</v>
+        <v>0.3469964664310954</v>
       </c>
       <c r="H253" t="n">
-        <v>3.677289014615747</v>
+        <v>3.676454652532391</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -20045,16 +20045,16 @@
         <v>1</v>
       </c>
       <c r="M253" t="n">
-        <v>0.9072890146157473</v>
+        <v>0.9064546525323913</v>
       </c>
       <c r="N253" t="n">
-        <v>0.9072890146157473</v>
+        <v>0.9064546525323913</v>
       </c>
       <c r="O253" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P253" t="n">
-        <v>0.03606789250353604</v>
+        <v>0.03604240282685556</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -20094,10 +20094,10 @@
         <v>8</v>
       </c>
       <c r="G254" t="n">
-        <v>0.495049504950495</v>
+        <v>0.4946996466431096</v>
       </c>
       <c r="H254" t="n">
-        <v>4.17720297029703</v>
+        <v>4.17506183745583</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -20116,16 +20116,16 @@
         <v>1</v>
       </c>
       <c r="M254" t="n">
-        <v>1.35720297029703</v>
+        <v>1.355061837455831</v>
       </c>
       <c r="N254" t="n">
-        <v>1.35720297029703</v>
+        <v>1.355061837455831</v>
       </c>
       <c r="O254" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P254" t="n">
-        <v>0.4999139556812824</v>
+        <v>0.498607184923439</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -20165,10 +20165,10 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>0.6966053748231966</v>
+        <v>0.6968197879858657</v>
       </c>
       <c r="H255" t="n">
-        <v>4.906612446958982</v>
+        <v>4.90726855123675</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -20187,16 +20187,16 @@
         <v>1</v>
       </c>
       <c r="M255" t="n">
-        <v>2.156612446958982</v>
+        <v>2.15726855123675</v>
       </c>
       <c r="N255" t="n">
-        <v>2.156612446958982</v>
+        <v>2.15726855123675</v>
       </c>
       <c r="O255" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P255" t="n">
-        <v>0.7294094766619521</v>
+        <v>0.7322067137809194</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
@@ -20236,10 +20236,10 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>0.7885431400282885</v>
+        <v>0.7886925795053004</v>
       </c>
       <c r="H256" t="n">
-        <v>5.205983026874114</v>
+        <v>5.20743109540636</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -20258,16 +20258,16 @@
         <v>1</v>
       </c>
       <c r="M256" t="n">
-        <v>2.455983026874114</v>
+        <v>2.45743109540636</v>
       </c>
       <c r="N256" t="n">
-        <v>2.455983026874114</v>
+        <v>2.45743109540636</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
       </c>
       <c r="P256" t="n">
-        <v>0.2993705799151325</v>
+        <v>0.3001625441696101</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -21437,10 +21437,10 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>0.9427157001414427</v>
+        <v>0.942756183745583</v>
       </c>
       <c r="H273" t="n">
-        <v>6.913504243281471</v>
+        <v>6.913727915194347</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -21459,16 +21459,16 @@
         <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>-0.8514957567185286</v>
+        <v>-0.851272084805653</v>
       </c>
       <c r="N273" t="n">
-        <v>0.8514957567185286</v>
+        <v>0.851272084805653</v>
       </c>
       <c r="O273" t="n">
         <v>0.0550000000000006</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.9774301178491056</v>
+        <v>-0.97720644593623</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -21508,10 +21508,10 @@
         <v>8</v>
       </c>
       <c r="G274" t="n">
-        <v>0.9391796322489392</v>
+        <v>0.9392226148409893</v>
       </c>
       <c r="H274" t="n">
-        <v>6.848967468175389</v>
+        <v>6.849204946996466</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -21530,16 +21530,16 @@
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>-0.9310325318246111</v>
+        <v>-0.9307950530035347</v>
       </c>
       <c r="N274" t="n">
-        <v>0.9310325318246111</v>
+        <v>0.9307950530035347</v>
       </c>
       <c r="O274" t="n">
         <v>0.01500000000000057</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.06453677510608191</v>
+        <v>-0.06452296819788117</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -21579,10 +21579,10 @@
         <v>8</v>
       </c>
       <c r="G275" t="n">
-        <v>0.9356435643564357</v>
+        <v>0.9356890459363958</v>
       </c>
       <c r="H275" t="n">
-        <v>6.829715346534654</v>
+        <v>6.829840989399293</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -21601,16 +21601,16 @@
         <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>-0.940284653465346</v>
+        <v>-0.9401590106007065</v>
       </c>
       <c r="N275" t="n">
-        <v>0.940284653465346</v>
+        <v>0.9401590106007065</v>
       </c>
       <c r="O275" t="n">
         <v>-0.01000000000000068</v>
       </c>
       <c r="P275" t="n">
-        <v>-0.01925212164073553</v>
+        <v>-0.01936395759717247</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -21650,10 +21650,10 @@
         <v>8</v>
       </c>
       <c r="G276" t="n">
-        <v>0.9321074964639321</v>
+        <v>0.9321554770318021</v>
       </c>
       <c r="H276" t="n">
-        <v>6.81978783592645</v>
+        <v>6.820079505300353</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -21672,16 +21672,16 @@
         <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>-0.8802121640735505</v>
+        <v>-0.8799204946996468</v>
       </c>
       <c r="N276" t="n">
-        <v>0.8802121640735505</v>
+        <v>0.8799204946996468</v>
       </c>
       <c r="O276" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P276" t="n">
-        <v>-0.00992751060820396</v>
+        <v>-0.009761484098939732</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -21721,10 +21721,10 @@
         <v>8</v>
       </c>
       <c r="G277" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9286219081272085</v>
       </c>
       <c r="H277" t="n">
-        <v>6.780357142857143</v>
+        <v>6.780636042402826</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -21743,16 +21743,16 @@
         <v>1</v>
       </c>
       <c r="M277" t="n">
-        <v>-0.8096428571428564</v>
+        <v>-0.8093639575971734</v>
       </c>
       <c r="N277" t="n">
-        <v>0.8096428571428564</v>
+        <v>0.8093639575971734</v>
       </c>
       <c r="O277" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P277" t="n">
-        <v>-0.03943069306930624</v>
+        <v>-0.03944346289752687</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -21792,10 +21792,10 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>0.925035360678925</v>
+        <v>0.9250883392226148</v>
       </c>
       <c r="H278" t="n">
-        <v>6.750820367751061</v>
+        <v>6.751113074204946</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -21814,16 +21814,16 @@
         <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>-0.6991796322489394</v>
+        <v>-0.6988869257950538</v>
       </c>
       <c r="N278" t="n">
-        <v>0.6991796322489394</v>
+        <v>0.6988869257950538</v>
       </c>
       <c r="O278" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P278" t="n">
-        <v>-0.02953677510608266</v>
+        <v>-0.02952296819788014</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -21863,10 +21863,10 @@
         <v>8</v>
       </c>
       <c r="G279" t="n">
-        <v>0.9214992927864215</v>
+        <v>0.9215547703180212</v>
       </c>
       <c r="H279" t="n">
-        <v>6.714189061763319</v>
+        <v>6.714393404004712</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -21885,16 +21885,16 @@
         <v>1</v>
       </c>
       <c r="M279" t="n">
-        <v>-0.655810938236681</v>
+        <v>-0.6556065959952884</v>
       </c>
       <c r="N279" t="n">
-        <v>0.655810938236681</v>
+        <v>0.6556065959952884</v>
       </c>
       <c r="O279" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P279" t="n">
-        <v>-0.03663130598774167</v>
+        <v>-0.03671967020023459</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -21934,10 +21934,10 @@
         <v>8</v>
       </c>
       <c r="G280" t="n">
-        <v>0.917963224893918</v>
+        <v>0.9180212014134276</v>
       </c>
       <c r="H280" t="n">
-        <v>6.67698727015559</v>
+        <v>6.678268551236751</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -21956,16 +21956,16 @@
         <v>1</v>
       </c>
       <c r="M280" t="n">
-        <v>-0.5930127298444097</v>
+        <v>-0.591731448763249</v>
       </c>
       <c r="N280" t="n">
-        <v>0.5930127298444097</v>
+        <v>0.591731448763249</v>
       </c>
       <c r="O280" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P280" t="n">
-        <v>-0.03720179160772918</v>
+        <v>-0.03612485276796118</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -22005,10 +22005,10 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>0.9144271570014144</v>
+        <v>0.9144876325088339</v>
       </c>
       <c r="H281" t="n">
-        <v>6.62442008486563</v>
+        <v>6.625088339222615</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -22027,16 +22027,16 @@
         <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>-0.63557991513437</v>
+        <v>-0.6349116607773846</v>
       </c>
       <c r="N281" t="n">
-        <v>0.63557991513437</v>
+        <v>0.6349116607773846</v>
       </c>
       <c r="O281" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P281" t="n">
-        <v>-0.05256718528996007</v>
+        <v>-0.05318021201413536</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -22076,10 +22076,10 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>0.9108910891089109</v>
+        <v>0.9109540636042402</v>
       </c>
       <c r="H282" t="n">
-        <v>6.547673267326733</v>
+        <v>6.548021201413428</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -22098,16 +22098,16 @@
         <v>1</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.5623267326732675</v>
+        <v>-0.5619787985865727</v>
       </c>
       <c r="N282" t="n">
-        <v>0.5623267326732675</v>
+        <v>0.5619787985865727</v>
       </c>
       <c r="O282" t="n">
         <v>-0.1499999999999995</v>
       </c>
       <c r="P282" t="n">
-        <v>-0.07674681753889701</v>
+        <v>-0.07706713780918761</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -22147,10 +22147,10 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>0.9073550212164073</v>
+        <v>0.9074204946996467</v>
       </c>
       <c r="H283" t="n">
-        <v>6.512545968882602</v>
+        <v>6.513992932862192</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -22169,16 +22169,16 @@
         <v>1</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.4974540311173978</v>
+        <v>-0.4960070671378078</v>
       </c>
       <c r="N283" t="n">
-        <v>0.4974540311173978</v>
+        <v>0.4960070671378078</v>
       </c>
       <c r="O283" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P283" t="n">
-        <v>-0.03512729844413087</v>
+        <v>-0.03402826855123564</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -22218,10 +22218,10 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>0.9052333804809052</v>
+        <v>0.9053003533568904</v>
       </c>
       <c r="H284" t="n">
-        <v>6.436973125884013</v>
+        <v>6.441413427561834</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -22240,16 +22240,16 @@
         <v>1</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.3830268741159868</v>
+        <v>-0.3785865724381665</v>
       </c>
       <c r="N284" t="n">
-        <v>0.3830268741159868</v>
+        <v>0.3785865724381665</v>
       </c>
       <c r="O284" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P284" t="n">
-        <v>-0.07557284299858846</v>
+        <v>-0.07257950530035817</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -22289,10 +22289,10 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>0.9016973125884017</v>
+        <v>0.9017667844522969</v>
       </c>
       <c r="H285" t="n">
-        <v>6.40187765205092</v>
+        <v>6.402261484098941</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -22311,16 +22311,16 @@
         <v>1</v>
       </c>
       <c r="M285" t="n">
-        <v>-0.2981223479490804</v>
+        <v>-0.2977385159010595</v>
       </c>
       <c r="N285" t="n">
-        <v>0.2981223479490804</v>
+        <v>0.2977385159010595</v>
       </c>
       <c r="O285" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P285" t="n">
-        <v>-0.03509547383309375</v>
+        <v>-0.03915194346289308</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
@@ -22360,10 +22360,10 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>0.8988684582743989</v>
+        <v>0.8989399293286219</v>
       </c>
       <c r="H286" t="n">
-        <v>6.354992927864215</v>
+        <v>6.356572438162543</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -22382,16 +22382,16 @@
         <v>1</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.185007072135785</v>
+        <v>-0.1834275618374566</v>
       </c>
       <c r="N286" t="n">
-        <v>0.185007072135785</v>
+        <v>0.1834275618374566</v>
       </c>
       <c r="O286" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P286" t="n">
-        <v>-0.04688472418670475</v>
+        <v>-0.04568904593639722</v>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
@@ -25685,10 +25685,10 @@
         <v>8</v>
       </c>
       <c r="G333" t="n">
-        <v>0.7637906647807637</v>
+        <v>0.7639575971731449</v>
       </c>
       <c r="H333" t="n">
-        <v>6.484236209335219</v>
+        <v>6.485180212014135</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -25707,16 +25707,16 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.7782637906647807</v>
+        <v>-0.7773197879858653</v>
       </c>
       <c r="N333" t="n">
-        <v>0.7782637906647807</v>
+        <v>0.7773197879858653</v>
       </c>
       <c r="O333" t="n">
         <v>-0.4400000000000004</v>
       </c>
       <c r="P333" t="n">
-        <v>-0.9832690464461393</v>
+        <v>-0.982325043767224</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -25756,10 +25756,10 @@
         <v>8</v>
       </c>
       <c r="G334" t="n">
-        <v>0.7722772277227723</v>
+        <v>0.7724381625441696</v>
       </c>
       <c r="H334" t="n">
-        <v>6.537085396039604</v>
+        <v>6.53742667844523</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -25778,16 +25778,16 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.4379146039603956</v>
+        <v>-0.4375733215547699</v>
       </c>
       <c r="N334" t="n">
-        <v>0.4379146039603956</v>
+        <v>0.4375733215547699</v>
       </c>
       <c r="O334" t="n">
         <v>-0.2875000000000005</v>
       </c>
       <c r="P334" t="n">
-        <v>0.05284918670438454</v>
+        <v>0.05224646643109487</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -25827,10 +25827,10 @@
         <v>8</v>
       </c>
       <c r="G335" t="n">
-        <v>0.7920792079207921</v>
+        <v>0.792226148409894</v>
       </c>
       <c r="H335" t="n">
-        <v>6.64210396039604</v>
+        <v>6.642694346289753</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -25849,16 +25849,16 @@
         <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.1578960396039601</v>
+        <v>-0.1573056537102469</v>
       </c>
       <c r="N335" t="n">
-        <v>0.1578960396039601</v>
+        <v>0.1573056537102469</v>
       </c>
       <c r="O335" t="n">
         <v>-0.1749999999999998</v>
       </c>
       <c r="P335" t="n">
-        <v>0.1050185643564356</v>
+        <v>0.1052676678445232</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -25898,10 +25898,10 @@
         <v>8</v>
       </c>
       <c r="G336" t="n">
-        <v>0.8147100424328148</v>
+        <v>0.8148409893992933</v>
       </c>
       <c r="H336" t="n">
-        <v>6.847185289957567</v>
+        <v>6.847925795053003</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -25920,16 +25920,16 @@
         <v>1</v>
       </c>
       <c r="M336" t="n">
-        <v>0.217185289957567</v>
+        <v>0.2179257950530031</v>
       </c>
       <c r="N336" t="n">
-        <v>0.217185289957567</v>
+        <v>0.2179257950530031</v>
       </c>
       <c r="O336" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P336" t="n">
-        <v>0.2050813295615272</v>
+        <v>0.2052314487632501</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -25969,10 +25969,10 @@
         <v>8</v>
       </c>
       <c r="G337" t="n">
-        <v>0.8345120226308345</v>
+        <v>0.8346289752650177</v>
       </c>
       <c r="H337" t="n">
-        <v>7.064165487977369</v>
+        <v>7.064826855123675</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -25991,16 +25991,16 @@
         <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>0.5741654879773685</v>
+        <v>0.5748268551236748</v>
       </c>
       <c r="N337" t="n">
-        <v>0.5741654879773685</v>
+        <v>0.5748268551236748</v>
       </c>
       <c r="O337" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P337" t="n">
-        <v>0.2169801980198018</v>
+        <v>0.216901060070672</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>8</v>
       </c>
       <c r="G338" t="n">
-        <v>0.8507779349363508</v>
+        <v>0.8508833922261484</v>
       </c>
       <c r="H338" t="n">
-        <v>7.148229844413013</v>
+        <v>7.148349116607774</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -26062,16 +26062,16 @@
         <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>0.6682298444130126</v>
+        <v>0.6683491166077733</v>
       </c>
       <c r="N338" t="n">
-        <v>0.6682298444130126</v>
+        <v>0.6683491166077733</v>
       </c>
       <c r="O338" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P338" t="n">
-        <v>0.08406435643564425</v>
+        <v>0.08352226148409869</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -26111,10 +26111,10 @@
         <v>8</v>
       </c>
       <c r="G339" t="n">
-        <v>0.8578500707213579</v>
+        <v>0.8579505300353357</v>
       </c>
       <c r="H339" t="n">
-        <v>7.203642149929279</v>
+        <v>7.204210247349824</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -26133,16 +26133,16 @@
         <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>0.6536421499292793</v>
+        <v>0.6542102473498241</v>
       </c>
       <c r="N339" t="n">
-        <v>0.6536421499292793</v>
+        <v>0.6542102473498241</v>
       </c>
       <c r="O339" t="n">
         <v>0.0699999999999994</v>
       </c>
       <c r="P339" t="n">
-        <v>0.05541230551626608</v>
+        <v>0.05586113074205024</v>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
@@ -26182,10 +26182,10 @@
         <v>8</v>
       </c>
       <c r="G340" t="n">
-        <v>0.8500707213578501</v>
+        <v>0.8501766784452297</v>
       </c>
       <c r="H340" t="n">
-        <v>7.147429985855728</v>
+        <v>7.147549823321555</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -26204,16 +26204,16 @@
         <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>0.6174299858557282</v>
+        <v>0.6175498233215544</v>
       </c>
       <c r="N340" t="n">
-        <v>0.6174299858557282</v>
+        <v>0.6175498233215544</v>
       </c>
       <c r="O340" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P340" t="n">
-        <v>-0.05621216407355067</v>
+        <v>-0.05666042402826932</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -26253,10 +26253,10 @@
         <v>8</v>
       </c>
       <c r="G341" t="n">
-        <v>0.8302687411598303</v>
+        <v>0.8303886925795053</v>
       </c>
       <c r="H341" t="n">
-        <v>7.023559641678453</v>
+        <v>7.024464075382803</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -26275,16 +26275,16 @@
         <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>0.6910596416784536</v>
+        <v>0.6919640753828036</v>
       </c>
       <c r="N341" t="n">
-        <v>0.6910596416784536</v>
+        <v>0.6919640753828036</v>
       </c>
       <c r="O341" t="n">
         <v>-0.1975000000000007</v>
       </c>
       <c r="P341" t="n">
-        <v>-0.1238703441772753</v>
+        <v>-0.1230857479387515</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -26324,10 +26324,10 @@
         <v>8</v>
       </c>
       <c r="G342" t="n">
-        <v>0.8104667609618105</v>
+        <v>0.8106007067137809</v>
       </c>
       <c r="H342" t="n">
-        <v>6.81954738330976</v>
+        <v>6.819736749116609</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -26346,16 +26346,16 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>0.6295473833097596</v>
+        <v>0.6297367491166082</v>
       </c>
       <c r="N342" t="n">
-        <v>0.6295473833097596</v>
+        <v>0.6297367491166082</v>
       </c>
       <c r="O342" t="n">
         <v>-0.1424999999999992</v>
       </c>
       <c r="P342" t="n">
-        <v>-0.2040122583686932</v>
+        <v>-0.2047273262661946</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>8</v>
       </c>
       <c r="G343" t="n">
-        <v>0.7871287128712872</v>
+        <v>0.7872791519434629</v>
       </c>
       <c r="H343" t="n">
         <v>6.619999999999999</v>
@@ -26426,7 +26426,7 @@
         <v>-0.2000000000000002</v>
       </c>
       <c r="P343" t="n">
-        <v>-0.1995473833097607</v>
+        <v>-0.1997367491166093</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -26466,10 +26466,10 @@
         <v>8</v>
       </c>
       <c r="G344" t="n">
-        <v>0.7630834512022631</v>
+        <v>0.7632508833922261</v>
       </c>
       <c r="H344" t="n">
-        <v>6.480236916548797</v>
+        <v>6.481183745583039</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -26488,16 +26488,16 @@
         <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5602369165487975</v>
+        <v>0.5611837455830386</v>
       </c>
       <c r="N344" t="n">
-        <v>0.5602369165487975</v>
+        <v>0.5611837455830386</v>
       </c>
       <c r="O344" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P344" t="n">
-        <v>-0.1397630834512018</v>
+        <v>-0.1388162544169607</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>8</v>
       </c>
       <c r="G345" t="n">
-        <v>0.7411598302687411</v>
+        <v>0.7413427561837456</v>
       </c>
       <c r="H345" t="n">
         <v>6.38</v>
@@ -26568,7 +26568,7 @@
         <v>0.0600000000000005</v>
       </c>
       <c r="P345" t="n">
-        <v>-0.1002369165487975</v>
+        <v>-0.1011837455830387</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -26608,10 +26608,10 @@
         <v>8</v>
       </c>
       <c r="G346" t="n">
-        <v>0.7178217821782178</v>
+        <v>0.7180212014134275</v>
       </c>
       <c r="H346" t="n">
-        <v>6.229820544554456</v>
+        <v>6.230614840989399</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -26630,16 +26630,16 @@
         <v>1</v>
       </c>
       <c r="M346" t="n">
-        <v>0.1098205445544558</v>
+        <v>0.110614840989399</v>
       </c>
       <c r="N346" t="n">
-        <v>0.1098205445544558</v>
+        <v>0.110614840989399</v>
       </c>
       <c r="O346" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P346" t="n">
-        <v>-0.150179455445544</v>
+        <v>-0.1493851590106008</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -27809,10 +27809,10 @@
         <v>8</v>
       </c>
       <c r="G363" t="n">
-        <v>0.6449787835926449</v>
+        <v>0.6452296819787986</v>
       </c>
       <c r="H363" t="n">
-        <v>6.969437765205091</v>
+        <v>6.969656360424028</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -27831,16 +27831,16 @@
         <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>-1.493062234794909</v>
+        <v>-1.492843639575972</v>
       </c>
       <c r="N363" t="n">
-        <v>1.493062234794909</v>
+        <v>1.492843639575972</v>
       </c>
       <c r="O363" t="n">
         <v>-0.254999999999999</v>
       </c>
       <c r="P363" t="n">
-        <v>0.1268571765575794</v>
+        <v>0.1270757717765161</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -27880,10 +27880,10 @@
         <v>8</v>
       </c>
       <c r="G364" t="n">
-        <v>0.6534653465346535</v>
+        <v>0.6537102473498233</v>
       </c>
       <c r="H364" t="n">
-        <v>7.004653465346535</v>
+        <v>7.006360424028268</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -27902,16 +27902,16 @@
         <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>-1.307846534653465</v>
+        <v>-1.306139575971732</v>
       </c>
       <c r="N364" t="n">
-        <v>1.307846534653465</v>
+        <v>1.306139575971732</v>
       </c>
       <c r="O364" t="n">
         <v>-0.1500000000000004</v>
       </c>
       <c r="P364" t="n">
-        <v>0.03521570014144348</v>
+        <v>0.03670406360424039</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -27951,10 +27951,10 @@
         <v>8</v>
       </c>
       <c r="G365" t="n">
-        <v>0.6661951909476662</v>
+        <v>0.6664310954063605</v>
       </c>
       <c r="H365" t="n">
-        <v>7.066690240452617</v>
+        <v>7.067512367491167</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -27973,16 +27973,16 @@
         <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>-1.063309759547383</v>
+        <v>-1.062487632508834</v>
       </c>
       <c r="N365" t="n">
-        <v>1.063309759547383</v>
+        <v>1.062487632508834</v>
       </c>
       <c r="O365" t="n">
         <v>-0.1824999999999992</v>
       </c>
       <c r="P365" t="n">
-        <v>0.06203677510608241</v>
+        <v>0.06115194346289865</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -28022,10 +28022,10 @@
         <v>8</v>
       </c>
       <c r="G366" t="n">
-        <v>0.6803394625176803</v>
+        <v>0.680565371024735</v>
       </c>
       <c r="H366" t="n">
-        <v>7.16423090523338</v>
+        <v>7.165116607773851</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -28044,16 +28044,16 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.9232690947666207</v>
+        <v>-0.9223833922261493</v>
       </c>
       <c r="N366" t="n">
-        <v>0.9232690947666207</v>
+        <v>0.9223833922261493</v>
       </c>
       <c r="O366" t="n">
         <v>-0.04250000000000043</v>
       </c>
       <c r="P366" t="n">
-        <v>0.0975406647807624</v>
+        <v>0.097604240282684</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -28093,10 +28093,10 @@
         <v>8</v>
       </c>
       <c r="G367" t="n">
-        <v>0.6881188118811881</v>
+        <v>0.688339222614841</v>
       </c>
       <c r="H367" t="n">
-        <v>7.192023514851486</v>
+        <v>7.192215547703181</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -28115,16 +28115,16 @@
         <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>-1.037976485148515</v>
+        <v>-1.03778445229682</v>
       </c>
       <c r="N367" t="n">
-        <v>1.037976485148515</v>
+        <v>1.03778445229682</v>
       </c>
       <c r="O367" t="n">
         <v>0.1425000000000001</v>
       </c>
       <c r="P367" t="n">
-        <v>0.02779260961810603</v>
+        <v>0.02709893992932955</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -28164,10 +28164,10 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>0.6895332390381895</v>
+        <v>0.6897526501766784</v>
       </c>
       <c r="H368" t="n">
-        <v>7.196027227722773</v>
+        <v>7.196919316843346</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -28186,16 +28186,16 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.8464727722772274</v>
+        <v>-0.8455806831566548</v>
       </c>
       <c r="N368" t="n">
-        <v>0.8464727722772274</v>
+        <v>0.8455806831566548</v>
       </c>
       <c r="O368" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P368" t="n">
-        <v>0.004003712871287313</v>
+        <v>0.004703769140165015</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -28235,10 +28235,10 @@
         <v>8</v>
       </c>
       <c r="G369" t="n">
-        <v>0.6838755304101839</v>
+        <v>0.6840989399293286</v>
       </c>
       <c r="H369" t="n">
-        <v>7.178094501414427</v>
+        <v>7.178970406360424</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -28257,16 +28257,16 @@
         <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.7719054985855731</v>
+        <v>-0.7710295936395761</v>
       </c>
       <c r="N369" t="n">
-        <v>0.7719054985855731</v>
+        <v>0.7710295936395761</v>
       </c>
       <c r="O369" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P369" t="n">
-        <v>-0.01793272630834597</v>
+        <v>-0.01794891048292158</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -28306,10 +28306,10 @@
         <v>8</v>
       </c>
       <c r="G370" t="n">
-        <v>0.6718528995756718</v>
+        <v>0.6720848056537102</v>
       </c>
       <c r="H370" t="n">
-        <v>7.111407355021217</v>
+        <v>7.112215547703181</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -28328,16 +28328,16 @@
         <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.8685926449787837</v>
+        <v>-0.8677844522968199</v>
       </c>
       <c r="N370" t="n">
-        <v>0.8685926449787837</v>
+        <v>0.8677844522968199</v>
       </c>
       <c r="O370" t="n">
         <v>0.03000000000000025</v>
       </c>
       <c r="P370" t="n">
-        <v>-0.06668714639321038</v>
+        <v>-0.06675485865724351</v>
       </c>
       <c r="Q370" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>8</v>
       </c>
       <c r="G371" t="n">
-        <v>0.6527581329561527</v>
+        <v>0.6530035335689046</v>
       </c>
       <c r="H371" t="n">
-        <v>6.999724186704384</v>
+        <v>7.001434628975265</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -28399,16 +28399,16 @@
         <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>-1.035275813295616</v>
+        <v>-1.033565371024735</v>
       </c>
       <c r="N371" t="n">
-        <v>1.035275813295616</v>
+        <v>1.033565371024735</v>
       </c>
       <c r="O371" t="n">
         <v>0.05499999999999972</v>
       </c>
       <c r="P371" t="n">
-        <v>-0.1116831683168327</v>
+        <v>-0.1107809187279152</v>
       </c>
       <c r="Q371" t="inlineStr">
         <is>
@@ -28448,10 +28448,10 @@
         <v>8</v>
       </c>
       <c r="G372" t="n">
-        <v>0.6308345120226309</v>
+        <v>0.631095406360424</v>
       </c>
       <c r="H372" t="n">
-        <v>6.935958274398868</v>
+        <v>6.936867491166078</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -28470,16 +28470,16 @@
         <v>1</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.9740417256011318</v>
+        <v>-0.9731325088339222</v>
       </c>
       <c r="N372" t="n">
-        <v>0.9740417256011318</v>
+        <v>0.9731325088339222</v>
       </c>
       <c r="O372" t="n">
         <v>-0.125</v>
       </c>
       <c r="P372" t="n">
-        <v>-0.06376591230551565</v>
+        <v>-0.06456713780918744</v>
       </c>
       <c r="Q372" t="inlineStr">
         <is>
@@ -28519,10 +28519,10 @@
         <v>8</v>
       </c>
       <c r="G373" t="n">
-        <v>0.615983026874116</v>
+        <v>0.6162544169611307</v>
       </c>
       <c r="H373" t="n">
-        <v>6.879626060820368</v>
+        <v>6.880808303886925</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -28541,16 +28541,16 @@
         <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.8103739391796321</v>
+        <v>-0.809191696113075</v>
       </c>
       <c r="N373" t="n">
-        <v>0.8103739391796321</v>
+        <v>0.809191696113075</v>
       </c>
       <c r="O373" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P373" t="n">
-        <v>-0.05633221357850005</v>
+        <v>-0.05605918727915249</v>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
@@ -28590,10 +28590,10 @@
         <v>8</v>
       </c>
       <c r="G374" t="n">
-        <v>0.5983026874115983</v>
+        <v>0.5985865724381625</v>
       </c>
       <c r="H374" t="n">
-        <v>6.798771216407355</v>
+        <v>6.799018551236749</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -28612,16 +28612,16 @@
         <v>1</v>
       </c>
       <c r="M374" t="n">
-        <v>-0.6612287835926445</v>
+        <v>-0.660981448763251</v>
       </c>
       <c r="N374" t="n">
-        <v>0.6612287835926445</v>
+        <v>0.660981448763251</v>
       </c>
       <c r="O374" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P374" t="n">
-        <v>-0.08085484441301283</v>
+        <v>-0.08178975265017652</v>
       </c>
       <c r="Q374" t="inlineStr">
         <is>
@@ -28661,10 +28661,10 @@
         <v>8</v>
       </c>
       <c r="G375" t="n">
-        <v>0.5834512022630834</v>
+        <v>0.5837455830388693</v>
       </c>
       <c r="H375" t="n">
-        <v>6.760831859971711</v>
+        <v>6.761088339222614</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -28683,16 +28683,16 @@
         <v>1</v>
       </c>
       <c r="M375" t="n">
-        <v>-0.519168140028289</v>
+        <v>-0.5189116607773858</v>
       </c>
       <c r="N375" t="n">
-        <v>0.519168140028289</v>
+        <v>0.5189116607773858</v>
       </c>
       <c r="O375" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.03793935643564428</v>
+        <v>-0.03793021201413449</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
@@ -28732,10 +28732,10 @@
         <v>8</v>
       </c>
       <c r="G376" t="n">
-        <v>0.5650636492220651</v>
+        <v>0.5653710247349824</v>
       </c>
       <c r="H376" t="n">
-        <v>6.679623408769448</v>
+        <v>6.680636042402827</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -28754,16 +28754,16 @@
         <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>-0.4303765912305524</v>
+        <v>-0.4293639575971735</v>
       </c>
       <c r="N376" t="n">
-        <v>0.4303765912305524</v>
+        <v>0.4293639575971735</v>
       </c>
       <c r="O376" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.08120845120226328</v>
+        <v>-0.08045229681978761</v>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
@@ -29933,10 +29933,10 @@
         <v>8</v>
       </c>
       <c r="G393" t="n">
-        <v>0.6591230551626591</v>
+        <v>0.6586572438162545</v>
       </c>
       <c r="H393" t="n">
-        <v>5.825961810466762</v>
+        <v>5.818611307420496</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -29955,16 +29955,16 @@
         <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>1.035961810466761</v>
+        <v>1.028611307420495</v>
       </c>
       <c r="N393" t="n">
-        <v>1.035961810466761</v>
+        <v>1.028611307420495</v>
       </c>
       <c r="O393" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P393" t="n">
-        <v>-0.639560263814948</v>
+        <v>-0.6469107668612137</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
@@ -30004,10 +30004,10 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>0.5643564356435643</v>
+        <v>0.5639575971731449</v>
       </c>
       <c r="H394" t="n">
-        <v>5.500693069306931</v>
+        <v>5.499906360424029</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -30026,16 +30026,16 @@
         <v>1</v>
       </c>
       <c r="M394" t="n">
-        <v>0.830693069306931</v>
+        <v>0.8299063604240287</v>
       </c>
       <c r="N394" t="n">
-        <v>0.830693069306931</v>
+        <v>0.8299063604240287</v>
       </c>
       <c r="O394" t="n">
         <v>-0.120000000000001</v>
       </c>
       <c r="P394" t="n">
-        <v>-0.3252687411598307</v>
+        <v>-0.3187049469964673</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -30075,10 +30075,10 @@
         <v>8</v>
       </c>
       <c r="G395" t="n">
-        <v>0.5424328147100425</v>
+        <v>0.5420494699646643</v>
       </c>
       <c r="H395" t="n">
-        <v>5.456649575671853</v>
+        <v>5.456397526501767</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -30097,16 +30097,16 @@
         <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>0.9166495756718529</v>
+        <v>0.9163975265017665</v>
       </c>
       <c r="N395" t="n">
-        <v>0.9166495756718529</v>
+        <v>0.9163975265017665</v>
       </c>
       <c r="O395" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P395" t="n">
-        <v>-0.04404349363507798</v>
+        <v>-0.04350883392226201</v>
       </c>
       <c r="Q395" t="inlineStr">
         <is>
@@ -30146,10 +30146,10 @@
         <v>8</v>
       </c>
       <c r="G396" t="n">
-        <v>0.5961810466760962</v>
+        <v>0.5957597173144876</v>
       </c>
       <c r="H396" t="n">
-        <v>5.636989038189533</v>
+        <v>5.636712014134275</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -30168,16 +30168,16 @@
         <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>1.196989038189533</v>
+        <v>1.196712014134275</v>
       </c>
       <c r="N396" t="n">
-        <v>1.196989038189533</v>
+        <v>1.196712014134275</v>
       </c>
       <c r="O396" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P396" t="n">
-        <v>0.1803394625176802</v>
+        <v>0.1803144876325087</v>
       </c>
       <c r="Q396" t="inlineStr">
         <is>
@@ -30217,10 +30217,10 @@
         <v>8</v>
       </c>
       <c r="G397" t="n">
-        <v>0.6343705799151343</v>
+        <v>0.6339222614840989</v>
       </c>
       <c r="H397" t="n">
-        <v>5.757098656294201</v>
+        <v>5.756803886925796</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -30239,16 +30239,16 @@
         <v>1</v>
       </c>
       <c r="M397" t="n">
-        <v>1.317098656294201</v>
+        <v>1.316803886925795</v>
       </c>
       <c r="N397" t="n">
-        <v>1.317098656294201</v>
+        <v>1.316803886925795</v>
       </c>
       <c r="O397" t="n">
         <v>0</v>
       </c>
       <c r="P397" t="n">
-        <v>0.1201096181046681</v>
+        <v>0.1200918727915203</v>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>8</v>
       </c>
       <c r="G398" t="n">
-        <v>0.5947666195190948</v>
+        <v>0.5943462897526501</v>
       </c>
       <c r="H398" t="n">
-        <v>5.636059052333805</v>
+        <v>5.635782685512368</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -30310,16 +30310,16 @@
         <v>1</v>
       </c>
       <c r="M398" t="n">
-        <v>1.236059052333805</v>
+        <v>1.235782685512367</v>
       </c>
       <c r="N398" t="n">
-        <v>1.236059052333805</v>
+        <v>1.235782685512367</v>
       </c>
       <c r="O398" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P398" t="n">
-        <v>-0.121039603960396</v>
+        <v>-0.121021201413428</v>
       </c>
       <c r="Q398" t="inlineStr">
         <is>
@@ -30359,10 +30359,10 @@
         <v>8</v>
       </c>
       <c r="G399" t="n">
-        <v>0.4787835926449788</v>
+        <v>0.4784452296819788</v>
       </c>
       <c r="H399" t="n">
-        <v>5.189800212164074</v>
+        <v>5.189577738515902</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -30381,16 +30381,16 @@
         <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>0.8098002121640739</v>
+        <v>0.8095777385159018</v>
       </c>
       <c r="N399" t="n">
-        <v>0.8098002121640739</v>
+        <v>0.8095777385159018</v>
       </c>
       <c r="O399" t="n">
         <v>-0.02000000000000046</v>
       </c>
       <c r="P399" t="n">
-        <v>-0.4462588401697314</v>
+        <v>-0.446204946996466</v>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
@@ -30430,10 +30430,10 @@
         <v>8</v>
       </c>
       <c r="G400" t="n">
-        <v>0.3698727015558699</v>
+        <v>0.3696113074204947</v>
       </c>
       <c r="H400" t="n">
-        <v>4.843191301272984</v>
+        <v>4.843019434628975</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -30452,16 +30452,16 @@
         <v>1</v>
       </c>
       <c r="M400" t="n">
-        <v>0.7031913012729847</v>
+        <v>0.7030194346289758</v>
       </c>
       <c r="N400" t="n">
-        <v>0.7031913012729847</v>
+        <v>0.7030194346289758</v>
       </c>
       <c r="O400" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P400" t="n">
-        <v>-0.3466089108910895</v>
+        <v>-0.3465583038869262</v>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
@@ -30501,10 +30501,10 @@
         <v>8</v>
       </c>
       <c r="G401" t="n">
-        <v>0.3253182461103253</v>
+        <v>0.3250883392226148</v>
       </c>
       <c r="H401" t="n">
-        <v>4.699260961810467</v>
+        <v>4.697446996466431</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -30523,16 +30523,16 @@
         <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>0.8292609618104674</v>
+        <v>0.8274469964664313</v>
       </c>
       <c r="N401" t="n">
-        <v>0.8292609618104674</v>
+        <v>0.8274469964664313</v>
       </c>
       <c r="O401" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P401" t="n">
-        <v>-0.1439303394625169</v>
+        <v>-0.1455724381625441</v>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
@@ -30572,10 +30572,10 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>0.3514851485148515</v>
+        <v>0.3512367491166078</v>
       </c>
       <c r="H402" t="n">
-        <v>4.806101485148515</v>
+        <v>4.80593816254417</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -30594,16 +30594,16 @@
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>1.086101485148515</v>
+        <v>1.085938162544169</v>
       </c>
       <c r="N402" t="n">
-        <v>1.086101485148515</v>
+        <v>1.085938162544169</v>
       </c>
       <c r="O402" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P402" t="n">
-        <v>0.1068405233380476</v>
+        <v>0.1084911660777381</v>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -30643,10 +30643,10 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>0.5297029702970297</v>
+        <v>0.5293286219081272</v>
       </c>
       <c r="H403" t="n">
-        <v>5.441559405940594</v>
+        <v>5.441067137809187</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -30665,16 +30665,16 @@
         <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>1.741559405940594</v>
+        <v>1.741067137809187</v>
       </c>
       <c r="N403" t="n">
-        <v>1.741559405940594</v>
+        <v>1.741067137809187</v>
       </c>
       <c r="O403" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P403" t="n">
-        <v>0.6354579207920787</v>
+        <v>0.635128975265018</v>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>8</v>
       </c>
       <c r="G404" t="n">
-        <v>0.7609618104667609</v>
+        <v>0.76113074204947</v>
       </c>
       <c r="H404" t="n">
-        <v>6.102659123055163</v>
+        <v>6.103547703180212</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -30736,16 +30736,16 @@
         <v>1</v>
       </c>
       <c r="M404" t="n">
-        <v>2.262659123055163</v>
+        <v>2.263547703180212</v>
       </c>
       <c r="N404" t="n">
-        <v>2.262659123055163</v>
+        <v>2.263547703180212</v>
       </c>
       <c r="O404" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P404" t="n">
-        <v>0.6610997171145687</v>
+        <v>0.6624805653710242</v>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
@@ -30785,10 +30785,10 @@
         <v>8</v>
       </c>
       <c r="G405" t="n">
-        <v>0.8316831683168316</v>
+        <v>0.8318021201413428</v>
       </c>
       <c r="H405" t="n">
-        <v>6.346485148514851</v>
+        <v>6.347189045936396</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -30807,16 +30807,16 @@
         <v>1</v>
       </c>
       <c r="M405" t="n">
-        <v>2.326485148514852</v>
+        <v>2.327189045936397</v>
       </c>
       <c r="N405" t="n">
-        <v>2.326485148514852</v>
+        <v>2.327189045936397</v>
       </c>
       <c r="O405" t="n">
         <v>0.1799999999999997</v>
       </c>
       <c r="P405" t="n">
-        <v>0.2438260254596889</v>
+        <v>0.2436413427561845</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
@@ -30856,10 +30856,10 @@
         <v>8</v>
       </c>
       <c r="G406" t="n">
-        <v>0.8161244695898161</v>
+        <v>0.8162544169611308</v>
       </c>
       <c r="H406" t="n">
-        <v>6.293518387553041</v>
+        <v>6.294372791519435</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -30878,16 +30878,16 @@
         <v>1</v>
       </c>
       <c r="M406" t="n">
-        <v>2.193518387553041</v>
+        <v>2.194372791519435</v>
       </c>
       <c r="N406" t="n">
-        <v>2.193518387553041</v>
+        <v>2.194372791519435</v>
       </c>
       <c r="O406" t="n">
         <v>0.08000000000000007</v>
       </c>
       <c r="P406" t="n">
-        <v>-0.05296676096181052</v>
+        <v>-0.05281625441696125</v>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
@@ -32057,10 +32057,10 @@
         <v>8</v>
       </c>
       <c r="G423" t="n">
-        <v>0.8295615275813296</v>
+        <v>0.8296819787985866</v>
       </c>
       <c r="H423" t="n">
-        <v>5.564450141442715</v>
+        <v>5.565226148409893</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -32079,16 +32079,16 @@
         <v>1</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.8030498585572845</v>
+        <v>-0.8022738515901064</v>
       </c>
       <c r="N423" t="n">
-        <v>0.8030498585572845</v>
+        <v>0.8022738515901064</v>
       </c>
       <c r="O423" t="n">
         <v>-0.07500000000000018</v>
       </c>
       <c r="P423" t="n">
-        <v>-1.474479431087067</v>
+        <v>-1.473703424119889</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
@@ -32128,10 +32128,10 @@
         <v>8</v>
       </c>
       <c r="G424" t="n">
-        <v>0.8274398868458275</v>
+        <v>0.8275618374558303</v>
       </c>
       <c r="H424" t="n">
-        <v>5.548854314002829</v>
+        <v>5.549378091872791</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -32150,16 +32150,16 @@
         <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>-0.7686456859971713</v>
+        <v>-0.7681219081272088</v>
       </c>
       <c r="N424" t="n">
-        <v>0.7686456859971713</v>
+        <v>0.7681219081272088</v>
       </c>
       <c r="O424" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P424" t="n">
-        <v>-0.01559582743988663</v>
+        <v>-0.0158480565371022</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -32199,10 +32199,10 @@
         <v>8</v>
       </c>
       <c r="G425" t="n">
-        <v>0.8210749646393211</v>
+        <v>0.8212014134275618</v>
       </c>
       <c r="H425" t="n">
-        <v>5.503033946251768</v>
+        <v>5.504120141342757</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -32221,16 +32221,16 @@
         <v>1</v>
       </c>
       <c r="M425" t="n">
-        <v>-0.7569660537482319</v>
+        <v>-0.7558798586572433</v>
       </c>
       <c r="N425" t="n">
-        <v>0.7569660537482319</v>
+        <v>0.7558798586572433</v>
       </c>
       <c r="O425" t="n">
         <v>-0.05750000000000011</v>
       </c>
       <c r="P425" t="n">
-        <v>-0.04582036775106069</v>
+        <v>-0.04525795053003456</v>
       </c>
       <c r="Q425" t="inlineStr">
         <is>
@@ -32270,10 +32270,10 @@
         <v>8</v>
       </c>
       <c r="G426" t="n">
-        <v>0.8182461103253182</v>
+        <v>0.8183745583038869</v>
       </c>
       <c r="H426" t="n">
-        <v>5.489050565770864</v>
+        <v>5.489878091872792</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -32292,16 +32292,16 @@
         <v>1</v>
       </c>
       <c r="M426" t="n">
-        <v>-0.6409494342291362</v>
+        <v>-0.6401219081272078</v>
       </c>
       <c r="N426" t="n">
-        <v>0.6409494342291362</v>
+        <v>0.6401219081272078</v>
       </c>
       <c r="O426" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P426" t="n">
-        <v>-0.0139833804809042</v>
+        <v>-0.01424204946996444</v>
       </c>
       <c r="Q426" t="inlineStr">
         <is>
@@ -32341,10 +32341,10 @@
         <v>8</v>
       </c>
       <c r="G427" t="n">
-        <v>0.809052333804809</v>
+        <v>0.8091872791519434</v>
       </c>
       <c r="H427" t="n">
-        <v>5.382439886845827</v>
+        <v>5.382844522968197</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -32363,16 +32363,16 @@
         <v>1</v>
       </c>
       <c r="M427" t="n">
-        <v>-0.6075601131541735</v>
+        <v>-0.6071554770318031</v>
       </c>
       <c r="N427" t="n">
-        <v>0.6075601131541735</v>
+        <v>0.6071554770318031</v>
       </c>
       <c r="O427" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P427" t="n">
-        <v>-0.106610678925037</v>
+        <v>-0.1070335689045949</v>
       </c>
       <c r="Q427" t="inlineStr">
         <is>
@@ -32412,10 +32412,10 @@
         <v>8</v>
       </c>
       <c r="G428" t="n">
-        <v>0.7885431400282885</v>
+        <v>0.7886925795053004</v>
       </c>
       <c r="H428" t="n">
-        <v>5.22839639321075</v>
+        <v>5.228717314487633</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -32434,16 +32434,16 @@
         <v>1</v>
       </c>
       <c r="M428" t="n">
-        <v>-0.4791036067892493</v>
+        <v>-0.4787826855123667</v>
       </c>
       <c r="N428" t="n">
-        <v>0.4791036067892493</v>
+        <v>0.4787826855123667</v>
       </c>
       <c r="O428" t="n">
         <v>-0.2825000000000006</v>
       </c>
       <c r="P428" t="n">
-        <v>-0.1540434936350765</v>
+        <v>-0.1541272084805643</v>
       </c>
       <c r="Q428" t="inlineStr">
         <is>
@@ -32483,10 +32483,10 @@
         <v>8</v>
       </c>
       <c r="G429" t="n">
-        <v>0.7708628005657708</v>
+        <v>0.7710247349823321</v>
       </c>
       <c r="H429" t="n">
-        <v>5.100855728429986</v>
+        <v>5.101551236749116</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
@@ -32505,16 +32505,16 @@
         <v>1</v>
       </c>
       <c r="M429" t="n">
-        <v>-0.4591442715700138</v>
+        <v>-0.4584487632508836</v>
       </c>
       <c r="N429" t="n">
-        <v>0.4591442715700138</v>
+        <v>0.4584487632508836</v>
       </c>
       <c r="O429" t="n">
         <v>-0.1475</v>
       </c>
       <c r="P429" t="n">
-        <v>-0.1275406647807644</v>
+        <v>-0.1271660777385168</v>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
@@ -32554,10 +32554,10 @@
         <v>8</v>
       </c>
       <c r="G430" t="n">
-        <v>0.7461103253182461</v>
+        <v>0.7462897526501767</v>
       </c>
       <c r="H430" t="n">
-        <v>4.949543847241867</v>
+        <v>4.950314487632509</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -32576,16 +32576,16 @@
         <v>1</v>
       </c>
       <c r="M430" t="n">
-        <v>-0.3904561527581327</v>
+        <v>-0.3896855123674907</v>
       </c>
       <c r="N430" t="n">
-        <v>0.3904561527581327</v>
+        <v>0.3896855123674907</v>
       </c>
       <c r="O430" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P430" t="n">
-        <v>-0.1513118811881187</v>
+        <v>-0.1512367491166069</v>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>8</v>
       </c>
       <c r="G431" t="n">
-        <v>0.7185289957567186</v>
+        <v>0.7187279151943463</v>
       </c>
       <c r="H431" t="n">
         <v>4.819999999999999</v>
@@ -32656,7 +32656,7 @@
         <v>-0.2275</v>
       </c>
       <c r="P431" t="n">
-        <v>-0.1295438472418677</v>
+        <v>-0.1303144876325097</v>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
@@ -32696,10 +32696,10 @@
         <v>8</v>
       </c>
       <c r="G432" t="n">
-        <v>0.6944837340876945</v>
+        <v>0.6939929328621908</v>
       </c>
       <c r="H432" t="n">
-        <v>4.651403818953324</v>
+        <v>4.650349823321555</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -32718,16 +32718,16 @@
         <v>1</v>
       </c>
       <c r="M432" t="n">
-        <v>-0.3585961810466758</v>
+        <v>-0.3596501766784446</v>
       </c>
       <c r="N432" t="n">
-        <v>0.3585961810466758</v>
+        <v>0.3596501766784446</v>
       </c>
       <c r="O432" t="n">
         <v>-0.1025</v>
       </c>
       <c r="P432" t="n">
-        <v>-0.1685961810466754</v>
+        <v>-0.1696501766784442</v>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
@@ -32767,10 +32767,10 @@
         <v>8</v>
       </c>
       <c r="G433" t="n">
-        <v>0.6845827439886846</v>
+        <v>0.6840989399293286</v>
       </c>
       <c r="H433" t="n">
-        <v>4.62132072135785</v>
+        <v>4.620801236749116</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -32789,16 +32789,16 @@
         <v>1</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.2186792786421501</v>
+        <v>-0.2191987632508834</v>
       </c>
       <c r="N433" t="n">
-        <v>0.2186792786421501</v>
+        <v>0.2191987632508834</v>
       </c>
       <c r="O433" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P433" t="n">
-        <v>-0.03008309759547423</v>
+        <v>-0.02954858657243875</v>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
@@ -32838,10 +32838,10 @@
         <v>8</v>
       </c>
       <c r="G434" t="n">
-        <v>0.6895332390381895</v>
+        <v>0.6890459363957597</v>
       </c>
       <c r="H434" t="n">
-        <v>4.637696841112683</v>
+        <v>4.636301531213192</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -32860,16 +32860,16 @@
         <v>1</v>
       </c>
       <c r="M434" t="n">
-        <v>-0.0823031588873171</v>
+        <v>-0.08369846878680764</v>
       </c>
       <c r="N434" t="n">
-        <v>0.0823031588873171</v>
+        <v>0.08369846878680764</v>
       </c>
       <c r="O434" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P434" t="n">
-        <v>0.01637611975483289</v>
+        <v>0.01550029446407564</v>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
@@ -32909,10 +32909,10 @@
         <v>8</v>
       </c>
       <c r="G435" t="n">
-        <v>0.7086280056577087</v>
+        <v>0.7088339222614841</v>
       </c>
       <c r="H435" t="n">
-        <v>4.741409712399812</v>
+        <v>4.742588928150766</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -32931,16 +32931,16 @@
         <v>1</v>
       </c>
       <c r="M435" t="n">
-        <v>0.1814097123998124</v>
+        <v>0.182588928150766</v>
       </c>
       <c r="N435" t="n">
-        <v>0.1814097123998124</v>
+        <v>0.182588928150766</v>
       </c>
       <c r="O435" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P435" t="n">
-        <v>0.1037128712871294</v>
+        <v>0.1062873969375735</v>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
@@ -32980,10 +32980,10 @@
         <v>8</v>
       </c>
       <c r="G436" t="n">
-        <v>0.7248939179632249</v>
+        <v>0.7250883392226148</v>
       </c>
       <c r="H436" t="n">
-        <v>4.843419377652051</v>
+        <v>4.844254416961131</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -33002,16 +33002,16 @@
         <v>1</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4534193776520512</v>
+        <v>0.4542544169611311</v>
       </c>
       <c r="N436" t="n">
-        <v>0.4534193776520512</v>
+        <v>0.4542544169611311</v>
       </c>
       <c r="O436" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P436" t="n">
-        <v>0.1020096652522389</v>
+        <v>0.1016654888103652</v>
       </c>
       <c r="Q436" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>8</v>
       </c>
       <c r="G437" t="n">
-        <v>0.8231966053748232</v>
+        <v>0.823321554770318</v>
       </c>
       <c r="H437" t="n">
-        <v>3.495654172560113</v>
+        <v>3.497340989399293</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -33073,10 +33073,10 @@
         <v>1</v>
       </c>
       <c r="M437" t="n">
-        <v>-0.9443458274398875</v>
+        <v>-0.9426590106007078</v>
       </c>
       <c r="N437" t="n">
-        <v>0.9443458274398875</v>
+        <v>0.9426590106007078</v>
       </c>
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
@@ -33116,10 +33116,10 @@
         <v>8</v>
       </c>
       <c r="G438" t="n">
-        <v>0.809052333804809</v>
+        <v>0.8091872791519434</v>
       </c>
       <c r="H438" t="n">
-        <v>3.348882602545969</v>
+        <v>3.349611307420495</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -33138,16 +33138,16 @@
         <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>-0.8936173974540318</v>
+        <v>-0.8928886925795059</v>
       </c>
       <c r="N438" t="n">
-        <v>0.8936173974540318</v>
+        <v>0.8928886925795059</v>
       </c>
       <c r="O438" t="n">
         <v>-0.1974999999999998</v>
       </c>
       <c r="P438" t="n">
-        <v>-0.1467715700141441</v>
+        <v>-0.1477296819787979</v>
       </c>
       <c r="Q438" t="inlineStr">
         <is>
@@ -33187,10 +33187,10 @@
         <v>8</v>
       </c>
       <c r="G439" t="n">
-        <v>0.7998585572842999</v>
+        <v>0.8</v>
       </c>
       <c r="H439" t="n">
-        <v>3.29461810466761</v>
+        <v>3.295</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -33209,16 +33209,16 @@
         <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>-0.8153818953323908</v>
+        <v>-0.8150000000000004</v>
       </c>
       <c r="N439" t="n">
-        <v>0.8153818953323908</v>
+        <v>0.8150000000000004</v>
       </c>
       <c r="O439" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P439" t="n">
-        <v>-0.0542644978783593</v>
+        <v>-0.0546113074204948</v>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
@@ -33258,10 +33258,10 @@
         <v>8</v>
       </c>
       <c r="G440" t="n">
-        <v>0.8041018387553041</v>
+        <v>0.8042402826855124</v>
       </c>
       <c r="H440" t="n">
-        <v>3.314299858557284</v>
+        <v>3.315795053003534</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -33280,16 +33280,16 @@
         <v>1</v>
       </c>
       <c r="M440" t="n">
-        <v>-0.6557001414427162</v>
+        <v>-0.6542049469964661</v>
       </c>
       <c r="N440" t="n">
-        <v>0.6557001414427162</v>
+        <v>0.6542049469964661</v>
       </c>
       <c r="O440" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P440" t="n">
-        <v>0.01968175388967452</v>
+        <v>0.02079505300353413</v>
       </c>
       <c r="Q440" t="inlineStr">
         <is>
@@ -33329,10 +33329,10 @@
         <v>8</v>
       </c>
       <c r="G441" t="n">
-        <v>0.8217821782178217</v>
+        <v>0.8219081272084806</v>
       </c>
       <c r="H441" t="n">
-        <v>3.465247524752475</v>
+        <v>3.466607773851591</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -33351,16 +33351,16 @@
         <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>-0.3647524752475251</v>
+        <v>-0.363392226148409</v>
       </c>
       <c r="N441" t="n">
-        <v>0.3647524752475251</v>
+        <v>0.363392226148409</v>
       </c>
       <c r="O441" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P441" t="n">
-        <v>0.150947666195191</v>
+        <v>0.150812720848057</v>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
@@ -33400,10 +33400,10 @@
         <v>8</v>
       </c>
       <c r="G442" t="n">
-        <v>0.8380480905233381</v>
+        <v>0.8381625441696113</v>
       </c>
       <c r="H442" t="n">
-        <v>3.647279585101368</v>
+        <v>3.648103651354535</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -33422,16 +33422,16 @@
         <v>1</v>
       </c>
       <c r="M442" t="n">
-        <v>-0.01272041489863263</v>
+        <v>-0.01189634864546507</v>
       </c>
       <c r="N442" t="n">
-        <v>0.01272041489863263</v>
+        <v>0.01189634864546507</v>
       </c>
       <c r="O442" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P442" t="n">
-        <v>0.1820320603488925</v>
+        <v>0.181495877502944</v>
       </c>
       <c r="Q442" t="inlineStr">
         <is>
@@ -33471,10 +33471,10 @@
         <v>8</v>
       </c>
       <c r="G443" t="n">
-        <v>0.847949080622348</v>
+        <v>0.8480565371024735</v>
       </c>
       <c r="H443" t="n">
-        <v>3.72196251768034</v>
+        <v>3.722252650176679</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -33493,16 +33493,16 @@
         <v>1</v>
       </c>
       <c r="M443" t="n">
-        <v>0.0819625176803398</v>
+        <v>0.08225265017667871</v>
       </c>
       <c r="N443" t="n">
-        <v>0.0819625176803398</v>
+        <v>0.08225265017667871</v>
       </c>
       <c r="O443" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P443" t="n">
-        <v>0.07468293257897241</v>
+        <v>0.07414899882214376</v>
       </c>
       <c r="Q443" t="inlineStr">
         <is>
@@ -33542,10 +33542,10 @@
         <v>8</v>
       </c>
       <c r="G444" t="n">
-        <v>0.8557284299858557</v>
+        <v>0.8558303886925795</v>
       </c>
       <c r="H444" t="n">
-        <v>3.755933521923621</v>
+        <v>3.75648409893993</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -33564,16 +33564,16 @@
         <v>1</v>
       </c>
       <c r="M444" t="n">
-        <v>0.1559335219236209</v>
+        <v>0.1564840989399294</v>
       </c>
       <c r="N444" t="n">
-        <v>0.1559335219236209</v>
+        <v>0.1564840989399294</v>
       </c>
       <c r="O444" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P444" t="n">
-        <v>0.03397100424328103</v>
+        <v>0.03423144876325068</v>
       </c>
       <c r="Q444" t="inlineStr">
         <is>
@@ -33613,10 +33613,10 @@
         <v>8</v>
       </c>
       <c r="G445" t="n">
-        <v>0.8585572842998586</v>
+        <v>0.8586572438162544</v>
       </c>
       <c r="H445" t="n">
-        <v>3.768104667609618</v>
+        <v>3.768374558303887</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -33635,16 +33635,16 @@
         <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>0.2356046676096182</v>
+        <v>0.235874558303887</v>
       </c>
       <c r="N445" t="n">
-        <v>0.2356046676096182</v>
+        <v>0.235874558303887</v>
       </c>
       <c r="O445" t="n">
         <v>-0.06749999999999989</v>
       </c>
       <c r="P445" t="n">
-        <v>0.01217114568599742</v>
+        <v>0.01189045936395772</v>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
@@ -33684,10 +33684,10 @@
         <v>8</v>
       </c>
       <c r="G446" t="n">
-        <v>0.8507779349363508</v>
+        <v>0.8508833922261484</v>
       </c>
       <c r="H446" t="n">
-        <v>3.734200848656294</v>
+        <v>3.734770318021201</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -33706,16 +33706,16 @@
         <v>1</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2942008486562941</v>
+        <v>0.2947703180212011</v>
       </c>
       <c r="N446" t="n">
-        <v>0.2942008486562941</v>
+        <v>0.2947703180212011</v>
       </c>
       <c r="O446" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P446" t="n">
-        <v>-0.03390381895332428</v>
+        <v>-0.03360424028268616</v>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
@@ -33755,10 +33755,10 @@
         <v>8</v>
       </c>
       <c r="G447" t="n">
-        <v>0.8401697312588402</v>
+        <v>0.8402826855123675</v>
       </c>
       <c r="H447" t="n">
-        <v>3.66670792079208</v>
+        <v>3.668842756183746</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -33777,16 +33777,16 @@
         <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>0.37670792079208</v>
+        <v>0.378842756183746</v>
       </c>
       <c r="N447" t="n">
-        <v>0.37670792079208</v>
+        <v>0.378842756183746</v>
       </c>
       <c r="O447" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.06749292786421401</v>
+        <v>-0.06592756183745507</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
@@ -33826,10 +33826,10 @@
         <v>8</v>
       </c>
       <c r="G448" t="n">
-        <v>0.8154172560113154</v>
+        <v>0.815547703180212</v>
       </c>
       <c r="H448" t="n">
-        <v>3.416626591230552</v>
+        <v>3.416978798586572</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -33848,16 +33848,16 @@
         <v>1</v>
       </c>
       <c r="M448" t="n">
-        <v>0.2366265912305514</v>
+        <v>0.2369787985865721</v>
       </c>
       <c r="N448" t="n">
-        <v>0.2366265912305514</v>
+        <v>0.2369787985865721</v>
       </c>
       <c r="O448" t="n">
         <v>-0.1099999999999999</v>
       </c>
       <c r="P448" t="n">
-        <v>-0.2500813295615285</v>
+        <v>-0.2518639575971737</v>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
@@ -33897,10 +33897,10 @@
         <v>8</v>
       </c>
       <c r="G449" t="n">
-        <v>0.7835926449787836</v>
+        <v>0.7837455830388692</v>
       </c>
       <c r="H449" t="n">
-        <v>3.216400282885431</v>
+        <v>3.217226148409894</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -33919,16 +33919,16 @@
         <v>1</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1164002828854311</v>
+        <v>0.1172261484098938</v>
       </c>
       <c r="N449" t="n">
-        <v>0.1164002828854311</v>
+        <v>0.1172261484098938</v>
       </c>
       <c r="O449" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P449" t="n">
-        <v>-0.2002263083451203</v>
+        <v>-0.1997526501766784</v>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
@@ -33968,10 +33968,10 @@
         <v>8</v>
       </c>
       <c r="G450" t="n">
-        <v>0.7666195190947667</v>
+        <v>0.7667844522968198</v>
       </c>
       <c r="H450" t="n">
-        <v>3.109490806223479</v>
+        <v>3.110424028268551</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -33990,16 +33990,16 @@
         <v>1</v>
       </c>
       <c r="M450" t="n">
-        <v>0.009490806223479087</v>
+        <v>0.01042402826855104</v>
       </c>
       <c r="N450" t="n">
-        <v>0.009490806223479087</v>
+        <v>0.01042402826855104</v>
       </c>
       <c r="O450" t="n">
         <v>0</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.1069094766619521</v>
+        <v>-0.1068021201413427</v>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
@@ -35311,10 +35311,10 @@
         <v>8</v>
       </c>
       <c r="G469" t="n">
-        <v>0.842998585572843</v>
+        <v>0.8431095406360424</v>
       </c>
       <c r="H469" t="n">
-        <v>8.553239038189535</v>
+        <v>8.555667844522969</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -35333,16 +35333,16 @@
         <v>1</v>
       </c>
       <c r="M469" t="n">
-        <v>-0.6867609618104655</v>
+        <v>-0.6843321554770316</v>
       </c>
       <c r="N469" t="n">
-        <v>0.6867609618104655</v>
+        <v>0.6843321554770316</v>
       </c>
       <c r="O469" t="n">
         <v>-0.08999999999999986</v>
       </c>
       <c r="P469" t="n">
-        <v>0.2542691713359968</v>
+        <v>0.2566979776694307</v>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
@@ -35382,10 +35382,10 @@
         <v>8</v>
       </c>
       <c r="G470" t="n">
-        <v>0.826025459688826</v>
+        <v>0.826148409893993</v>
       </c>
       <c r="H470" t="n">
-        <v>8.282743988684583</v>
+        <v>8.284212014134276</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -35404,16 +35404,16 @@
         <v>1</v>
       </c>
       <c r="M470" t="n">
-        <v>-0.7672560113154177</v>
+        <v>-0.7657879858657246</v>
       </c>
       <c r="N470" t="n">
-        <v>0.7672560113154177</v>
+        <v>0.7657879858657246</v>
       </c>
       <c r="O470" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P470" t="n">
-        <v>-0.2704950495049516</v>
+        <v>-0.2714558303886925</v>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -35453,10 +35453,10 @@
         <v>8</v>
       </c>
       <c r="G471" t="n">
-        <v>0.806930693069307</v>
+        <v>0.8070671378091873</v>
       </c>
       <c r="H471" t="n">
-        <v>7.999504950495052</v>
+        <v>8.002763250883392</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -35475,16 +35475,16 @@
         <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.9104950495049486</v>
+        <v>-0.907236749116608</v>
       </c>
       <c r="N471" t="n">
-        <v>0.9104950495049486</v>
+        <v>0.907236749116608</v>
       </c>
       <c r="O471" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P471" t="n">
-        <v>-0.2832390381895316</v>
+        <v>-0.281448763250884</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
@@ -35524,10 +35524,10 @@
         <v>8</v>
       </c>
       <c r="G472" t="n">
-        <v>0.7949080622347949</v>
+        <v>0.7950530035335689</v>
       </c>
       <c r="H472" t="n">
-        <v>7.895601131541725</v>
+        <v>7.896466431095406</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -35546,16 +35546,16 @@
         <v>1</v>
       </c>
       <c r="M472" t="n">
-        <v>-0.8743988684582744</v>
+        <v>-0.8735335689045938</v>
       </c>
       <c r="N472" t="n">
-        <v>0.8743988684582744</v>
+        <v>0.8735335689045938</v>
       </c>
       <c r="O472" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P472" t="n">
-        <v>-0.1039038189533263</v>
+        <v>-0.1062968197879863</v>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
@@ -35595,10 +35595,10 @@
         <v>8</v>
       </c>
       <c r="G473" t="n">
-        <v>0.7927864214992928</v>
+        <v>0.7929328621908127</v>
       </c>
       <c r="H473" t="n">
-        <v>7.875869872701556</v>
+        <v>7.877618374558303</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -35617,16 +35617,16 @@
         <v>1</v>
       </c>
       <c r="M473" t="n">
-        <v>-0.7041301272984439</v>
+        <v>-0.7023816254416966</v>
       </c>
       <c r="N473" t="n">
-        <v>0.7041301272984439</v>
+        <v>0.7023816254416966</v>
       </c>
       <c r="O473" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P473" t="n">
-        <v>-0.01973125884016902</v>
+        <v>-0.01884805653710231</v>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
@@ -35666,10 +35666,10 @@
         <v>8</v>
       </c>
       <c r="G474" t="n">
-        <v>0.8033946251768034</v>
+        <v>0.8035335689045936</v>
       </c>
       <c r="H474" t="n">
-        <v>7.928755304101839</v>
+        <v>7.929031802120141</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -35688,16 +35688,16 @@
         <v>1</v>
       </c>
       <c r="M474" t="n">
-        <v>-0.5212446958981607</v>
+        <v>-0.5209681978798582</v>
       </c>
       <c r="N474" t="n">
-        <v>0.5212446958981607</v>
+        <v>0.5209681978798582</v>
       </c>
       <c r="O474" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P474" t="n">
-        <v>0.05288543140028246</v>
+        <v>0.05141342756183764</v>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
@@ -35737,10 +35737,10 @@
         <v>8</v>
       </c>
       <c r="G475" t="n">
-        <v>0.8161244695898161</v>
+        <v>0.8162544169611308</v>
       </c>
       <c r="H475" t="n">
-        <v>8.194087694483734</v>
+        <v>8.19434628975265</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -35759,16 +35759,16 @@
         <v>1</v>
       </c>
       <c r="M475" t="n">
-        <v>-0.1259123055162661</v>
+        <v>-0.1256537102473505</v>
       </c>
       <c r="N475" t="n">
-        <v>0.1259123055162661</v>
+        <v>0.1256537102473505</v>
       </c>
       <c r="O475" t="n">
         <v>-0.129999999999999</v>
       </c>
       <c r="P475" t="n">
-        <v>0.2653323903818956</v>
+        <v>0.2653144876325086</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
@@ -35808,10 +35808,10 @@
         <v>8</v>
       </c>
       <c r="G476" t="n">
-        <v>0.8281471004243282</v>
+        <v>0.8282685512367491</v>
       </c>
       <c r="H476" t="n">
-        <v>8.308076379066478</v>
+        <v>8.309526501766785</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -35830,16 +35830,16 @@
         <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>0.04807637906647777</v>
+        <v>0.04952650176678475</v>
       </c>
       <c r="N476" t="n">
-        <v>0.04807637906647777</v>
+        <v>0.04952650176678475</v>
       </c>
       <c r="O476" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P476" t="n">
-        <v>0.1139886845827434</v>
+        <v>0.1151802120141348</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
@@ -35879,10 +35879,10 @@
         <v>8</v>
       </c>
       <c r="G477" t="n">
-        <v>0.8366336633663366</v>
+        <v>0.8367491166077738</v>
       </c>
       <c r="H477" t="n">
-        <v>8.459801980198019</v>
+        <v>8.46026148409894</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -35901,16 +35901,16 @@
         <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>0.25980198019802</v>
+        <v>0.2602614840989403</v>
       </c>
       <c r="N477" t="n">
-        <v>0.25980198019802</v>
+        <v>0.2602614840989403</v>
       </c>
       <c r="O477" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P477" t="n">
-        <v>0.1517256011315418</v>
+        <v>0.1507349823321551</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -35950,10 +35950,10 @@
         <v>8</v>
       </c>
       <c r="G478" t="n">
-        <v>0.8373408769448374</v>
+        <v>0.8374558303886925</v>
       </c>
       <c r="H478" t="n">
-        <v>8.462616690240454</v>
+        <v>8.463074204946997</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -35972,16 +35972,16 @@
         <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>0.4126166902404531</v>
+        <v>0.4130742049469962</v>
       </c>
       <c r="N478" t="n">
-        <v>0.4126166902404531</v>
+        <v>0.4130742049469962</v>
       </c>
       <c r="O478" t="n">
         <v>-0.1499999999999986</v>
       </c>
       <c r="P478" t="n">
-        <v>0.002814710042434498</v>
+        <v>0.002812720848057282</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -36021,10 +36021,10 @@
         <v>8</v>
       </c>
       <c r="G479" t="n">
-        <v>0.8323903818953324</v>
+        <v>0.8325088339222615</v>
       </c>
       <c r="H479" t="n">
-        <v>8.40393917963225</v>
+        <v>8.407003533568904</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -36043,16 +36043,16 @@
         <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>0.4839391796322499</v>
+        <v>0.4870035335689042</v>
       </c>
       <c r="N479" t="n">
-        <v>0.4839391796322499</v>
+        <v>0.4870035335689042</v>
       </c>
       <c r="O479" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P479" t="n">
-        <v>-0.05867751060820403</v>
+        <v>-0.05607067137809274</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -36092,10 +36092,10 @@
         <v>8</v>
       </c>
       <c r="G480" t="n">
-        <v>0.8196605374823197</v>
+        <v>0.8197879858657244</v>
       </c>
       <c r="H480" t="n">
-        <v>8.206746817538896</v>
+        <v>8.208268551236749</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -36114,16 +36114,16 @@
         <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0.4667468175388958</v>
+        <v>0.4682685512367488</v>
       </c>
       <c r="N480" t="n">
-        <v>0.4667468175388958</v>
+        <v>0.4682685512367488</v>
       </c>
       <c r="O480" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P480" t="n">
-        <v>-0.1971923620933538</v>
+        <v>-0.1987349823321551</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -36266,34 +36266,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.729</v>
+        <v>7.731</v>
       </c>
       <c r="G2" t="n">
-        <v>7.867</v>
+        <v>7.839</v>
       </c>
       <c r="H2" t="n">
-        <v>7.954</v>
+        <v>7.917</v>
       </c>
       <c r="I2" t="n">
-        <v>7.879</v>
+        <v>7.903</v>
       </c>
       <c r="J2" t="n">
-        <v>7.799</v>
+        <v>7.765</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.08</v>
+        <v>-0.138</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>30</v>
       </c>
       <c r="O2" t="n">
-        <v>5.83</v>
+        <v>5.831</v>
       </c>
       <c r="P2" t="n">
         <v>5.811</v>
@@ -36342,34 +36342,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.58</v>
+        <v>5.577</v>
       </c>
       <c r="G3" t="n">
-        <v>5.646</v>
+        <v>5.633</v>
       </c>
       <c r="H3" t="n">
-        <v>5.725</v>
+        <v>5.692</v>
       </c>
       <c r="I3" t="n">
-        <v>5.725</v>
+        <v>5.692</v>
       </c>
       <c r="J3" t="n">
-        <v>5.586</v>
+        <v>5.601</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.139</v>
+        <v>-0.091</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -36385,16 +36385,16 @@
         <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>0.49</v>
+        <v>0.491</v>
       </c>
       <c r="P3" t="n">
-        <v>0.338</v>
+        <v>0.339</v>
       </c>
       <c r="Q3" t="n">
         <v>0.317</v>
       </c>
       <c r="R3" t="n">
-        <v>0.569</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -36418,34 +36418,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.37</v>
+        <v>4.251</v>
       </c>
       <c r="G4" t="n">
-        <v>4.482</v>
+        <v>4.435</v>
       </c>
       <c r="H4" t="n">
-        <v>4.557</v>
+        <v>4.547</v>
       </c>
       <c r="I4" t="n">
-        <v>4.557</v>
+        <v>4.547</v>
       </c>
       <c r="J4" t="n">
-        <v>4.412</v>
+        <v>4.372</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.144</v>
+        <v>-0.175</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>0.949</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="Q4" t="n">
         <v>0.29</v>
@@ -36494,34 +36494,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.812</v>
+        <v>11.103</v>
       </c>
       <c r="G5" t="n">
-        <v>11.69</v>
+        <v>11.809</v>
       </c>
       <c r="H5" t="n">
-        <v>12.188</v>
+        <v>12.212</v>
       </c>
       <c r="I5" t="n">
-        <v>10.812</v>
+        <v>11.103</v>
       </c>
       <c r="J5" t="n">
-        <v>12.182</v>
+        <v>12.21</v>
       </c>
       <c r="K5" t="n">
-        <v>1.37</v>
+        <v>1.107</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>4.212</v>
+        <v>4.213</v>
       </c>
       <c r="P5" t="n">
         <v>3.916</v>
@@ -36570,34 +36570,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>54.621</v>
+        <v>59.153</v>
       </c>
       <c r="G6" t="n">
-        <v>85.768</v>
+        <v>94.63</v>
       </c>
       <c r="H6" t="n">
-        <v>112.044</v>
+        <v>113.992</v>
       </c>
       <c r="I6" t="n">
-        <v>56.939</v>
+        <v>59.18</v>
       </c>
       <c r="J6" t="n">
-        <v>96.152</v>
+        <v>110.042</v>
       </c>
       <c r="K6" t="n">
-        <v>39.213</v>
+        <v>50.862</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -36613,13 +36613,13 @@
         <v>13</v>
       </c>
       <c r="O6" t="n">
-        <v>92.01600000000001</v>
+        <v>92.017</v>
       </c>
       <c r="P6" t="n">
-        <v>88.687</v>
+        <v>88.688</v>
       </c>
       <c r="Q6" t="n">
-        <v>88.687</v>
+        <v>88.688</v>
       </c>
       <c r="R6" t="n">
         <v>-3.322</v>
@@ -36646,38 +36646,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.73</v>
+        <v>7.725</v>
       </c>
       <c r="G7" t="n">
-        <v>7.911</v>
+        <v>7.899</v>
       </c>
       <c r="H7" t="n">
-        <v>8.15</v>
+        <v>8.092000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.15</v>
+        <v>8.092000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>7.872</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.278</v>
+        <v>-0.043</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -36722,34 +36722,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.154</v>
+        <v>6.15</v>
       </c>
       <c r="G8" t="n">
-        <v>6.735</v>
+        <v>6.608</v>
       </c>
       <c r="H8" t="n">
-        <v>7.328</v>
+        <v>7.245</v>
       </c>
       <c r="I8" t="n">
-        <v>7.327</v>
+        <v>7.244</v>
       </c>
       <c r="J8" t="n">
-        <v>6.161</v>
+        <v>6.205</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.166</v>
+        <v>-1.04</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -36768,10 +36768,10 @@
         <v>0.477</v>
       </c>
       <c r="P8" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0.396</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.395</v>
       </c>
       <c r="R8" t="n">
         <v>0.828</v>
@@ -36798,34 +36798,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.034</v>
+        <v>5.033</v>
       </c>
       <c r="G9" t="n">
-        <v>5.303</v>
+        <v>5.24</v>
       </c>
       <c r="H9" t="n">
         <v>5.611</v>
       </c>
       <c r="I9" t="n">
-        <v>5.537</v>
+        <v>5.611</v>
       </c>
       <c r="J9" t="n">
-        <v>5.17</v>
+        <v>5.069</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.368</v>
+        <v>-0.542</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -36847,10 +36847,10 @@
         <v>0.423</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.261</v>
+        <v>0.26</v>
       </c>
       <c r="R9" t="n">
-        <v>0.216</v>
+        <v>0.218</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -36874,34 +36874,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.309</v>
+        <v>5.216</v>
       </c>
       <c r="G10" t="n">
-        <v>5.404</v>
+        <v>5.378</v>
       </c>
       <c r="H10" t="n">
-        <v>5.436</v>
+        <v>5.437</v>
       </c>
       <c r="I10" t="n">
-        <v>5.434</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>5.313</v>
+        <v>5.217</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.121</v>
+        <v>-0.183</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -36950,34 +36950,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>4.288</v>
+        <v>3.954</v>
       </c>
       <c r="G11" t="n">
-        <v>5.156</v>
+        <v>5.702</v>
       </c>
       <c r="H11" t="n">
-        <v>6.057</v>
+        <v>8.186</v>
       </c>
       <c r="I11" t="n">
-        <v>4.292</v>
+        <v>4.944</v>
       </c>
       <c r="J11" t="n">
-        <v>4.956</v>
+        <v>5.752</v>
       </c>
       <c r="K11" t="n">
-        <v>0.663</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -36996,10 +36996,10 @@
         <v>2.52</v>
       </c>
       <c r="P11" t="n">
-        <v>2.035</v>
+        <v>2.036</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.035</v>
+        <v>2.036</v>
       </c>
       <c r="R11" t="n">
         <v>-0.553</v>
@@ -37026,34 +37026,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.964</v>
+        <v>5.93</v>
       </c>
       <c r="G12" t="n">
-        <v>6.052</v>
+        <v>6.027</v>
       </c>
       <c r="H12" t="n">
-        <v>6.113</v>
+        <v>6.096</v>
       </c>
       <c r="I12" t="n">
-        <v>6.113</v>
+        <v>6.096</v>
       </c>
       <c r="J12" t="n">
-        <v>5.965</v>
+        <v>5.932</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.148</v>
+        <v>-0.164</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>0.483</v>
+        <v>0.482</v>
       </c>
       <c r="P12" t="n">
         <v>0.371</v>
@@ -37078,7 +37078,7 @@
         <v>-0.239</v>
       </c>
       <c r="R12" t="n">
-        <v>0.397</v>
+        <v>0.398</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -37102,34 +37102,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.686</v>
+        <v>9.602</v>
       </c>
       <c r="G13" t="n">
-        <v>9.849</v>
+        <v>9.788</v>
       </c>
       <c r="H13" t="n">
-        <v>10.081</v>
+        <v>9.976000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>10.081</v>
+        <v>9.976000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>9.702999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.377</v>
+        <v>-0.316</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -37178,34 +37178,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.626</v>
+        <v>5.566</v>
       </c>
       <c r="G14" t="n">
-        <v>5.803</v>
+        <v>5.778</v>
       </c>
       <c r="H14" t="n">
-        <v>5.91</v>
+        <v>5.912</v>
       </c>
       <c r="I14" t="n">
-        <v>5.811</v>
+        <v>5.801</v>
       </c>
       <c r="J14" t="n">
-        <v>5.631</v>
+        <v>5.572</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.18</v>
+        <v>-0.229</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -37227,7 +37227,7 @@
         <v>0.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="R14" t="n">
         <v>0.738</v>
@@ -37254,12 +37254,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -37269,19 +37269,19 @@
         <v>6.562</v>
       </c>
       <c r="G15" t="n">
-        <v>6.577</v>
+        <v>6.583</v>
       </c>
       <c r="H15" t="n">
-        <v>6.586</v>
+        <v>6.626</v>
       </c>
       <c r="I15" t="n">
         <v>6.585</v>
       </c>
       <c r="J15" t="n">
-        <v>6.573</v>
+        <v>6.596</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.013</v>
+        <v>0.011</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>-1.505</v>
       </c>
       <c r="R15" t="n">
-        <v>0.283</v>
+        <v>0.282</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -37330,34 +37330,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.708</v>
+        <v>5.189</v>
       </c>
       <c r="G16" t="n">
-        <v>6.055</v>
+        <v>6.307</v>
       </c>
       <c r="H16" t="n">
-        <v>6.585</v>
+        <v>7.077</v>
       </c>
       <c r="I16" t="n">
-        <v>6.149</v>
+        <v>6.422</v>
       </c>
       <c r="J16" t="n">
-        <v>5.859</v>
+        <v>6.092</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -37373,13 +37373,13 @@
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>1.727</v>
+        <v>1.726</v>
       </c>
       <c r="P16" t="n">
-        <v>1.539</v>
+        <v>1.538</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.539</v>
+        <v>1.538</v>
       </c>
       <c r="R16" t="n">
         <v>0.23</v>
@@ -37406,34 +37406,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.925</v>
+        <v>3.886</v>
       </c>
       <c r="G17" t="n">
-        <v>4.336</v>
+        <v>4.259</v>
       </c>
       <c r="H17" t="n">
-        <v>4.674</v>
+        <v>4.608</v>
       </c>
       <c r="I17" t="n">
-        <v>4.674</v>
+        <v>4.608</v>
       </c>
       <c r="J17" t="n">
-        <v>3.987</v>
+        <v>3.935</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.673</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -37482,34 +37482,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.499</v>
+        <v>2.446</v>
       </c>
       <c r="G18" t="n">
-        <v>2.615</v>
+        <v>2.573</v>
       </c>
       <c r="H18" t="n">
-        <v>2.708</v>
+        <v>2.675</v>
       </c>
       <c r="I18" t="n">
-        <v>2.708</v>
+        <v>2.675</v>
       </c>
       <c r="J18" t="n">
-        <v>2.519</v>
+        <v>2.449</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.19</v>
+        <v>-0.226</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -37525,13 +37525,13 @@
         <v>14</v>
       </c>
       <c r="O18" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="P18" t="n">
         <v>0.371</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.156</v>
+        <v>-0.155</v>
       </c>
       <c r="R18" t="n">
         <v>-0.108</v>
@@ -37558,34 +37558,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.799</v>
+        <v>5.771</v>
       </c>
       <c r="G19" t="n">
-        <v>5.898</v>
+        <v>5.891</v>
       </c>
       <c r="H19" t="n">
-        <v>6.037</v>
+        <v>6.096</v>
       </c>
       <c r="I19" t="n">
-        <v>6.037</v>
+        <v>5.963</v>
       </c>
       <c r="J19" t="n">
-        <v>5.83</v>
+        <v>5.857</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.207</v>
+        <v>-0.106</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>-0.666</v>
       </c>
       <c r="R19" t="n">
-        <v>0.506</v>
+        <v>0.505</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -486,7 +486,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>300006</v>
+        <v>300024</v>
       </c>
       <c r="E2" t="n">
         <v>151106</v>
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -683,13 +683,13 @@
         <v>9.765000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>7.757</v>
+        <v>7.758</v>
       </c>
       <c r="J2" t="n">
         <v>-1.52</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.008</v>
+        <v>-2.007</v>
       </c>
       <c r="L2" t="n">
         <v>0.396</v>
@@ -701,13 +701,13 @@
         <v>0.477</v>
       </c>
       <c r="O2" t="n">
-        <v>0.866</v>
+        <v>0.865</v>
       </c>
       <c r="P2" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.828</v>
+        <v>0.829</v>
       </c>
       <c r="R2" t="n">
         <v>50</v>
@@ -765,13 +765,13 @@
         <v>7.883</v>
       </c>
       <c r="I3" t="n">
-        <v>5.831</v>
+        <v>5.832</v>
       </c>
       <c r="J3" t="n">
         <v>-2.472</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.052</v>
+        <v>-2.051</v>
       </c>
       <c r="L3" t="n">
         <v>-1.787</v>
@@ -780,13 +780,13 @@
         <v>1.787</v>
       </c>
       <c r="N3" t="n">
-        <v>1.822</v>
+        <v>1.821</v>
       </c>
       <c r="O3" t="n">
         <v>0.89</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.601</v>
+        <v>-4.599</v>
       </c>
       <c r="Q3" t="n">
         <v>0.758</v>
@@ -847,22 +847,22 @@
         <v>7.691</v>
       </c>
       <c r="I4" t="n">
-        <v>4.844</v>
+        <v>4.845</v>
       </c>
       <c r="J4" t="n">
         <v>-3.405</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.846</v>
+        <v>-2.845</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.075</v>
+        <v>-0.074</v>
       </c>
       <c r="M4" t="n">
         <v>0.338</v>
       </c>
       <c r="N4" t="n">
-        <v>0.405</v>
+        <v>0.404</v>
       </c>
       <c r="O4" t="n">
         <v>0.9409999999999999</v>
@@ -871,7 +871,7 @@
         <v>0.834</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.834</v>
+        <v>0.835</v>
       </c>
       <c r="R4" t="n">
         <v>44.828</v>
@@ -929,28 +929,28 @@
         <v>7.178</v>
       </c>
       <c r="I5" t="n">
-        <v>5.97</v>
+        <v>5.973</v>
       </c>
       <c r="J5" t="n">
         <v>-2.275</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.208</v>
+        <v>-1.205</v>
       </c>
       <c r="L5" t="n">
-        <v>0.317</v>
+        <v>0.318</v>
       </c>
       <c r="M5" t="n">
         <v>0.339</v>
       </c>
       <c r="N5" t="n">
-        <v>0.491</v>
+        <v>0.492</v>
       </c>
       <c r="O5" t="n">
         <v>0.931</v>
       </c>
       <c r="P5" t="n">
-        <v>0.556</v>
+        <v>0.555</v>
       </c>
       <c r="Q5" t="n">
         <v>0.5679999999999999</v>
@@ -1011,13 +1011,13 @@
         <v>8.468</v>
       </c>
       <c r="I6" t="n">
-        <v>6.231</v>
+        <v>6.232</v>
       </c>
       <c r="J6" t="n">
         <v>-2.07</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.237</v>
+        <v>-2.236</v>
       </c>
       <c r="L6" t="n">
         <v>0.11</v>
@@ -1026,7 +1026,7 @@
         <v>0.35</v>
       </c>
       <c r="N6" t="n">
-        <v>0.414</v>
+        <v>0.415</v>
       </c>
       <c r="O6" t="n">
         <v>0.872</v>
@@ -1035,7 +1035,7 @@
         <v>0.731</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="R6" t="n">
         <v>31.034</v>
@@ -1093,31 +1093,31 @@
         <v>9.374000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.208</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="J7" t="n">
         <v>-2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.166</v>
+        <v>-1.165</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.666</v>
+        <v>-0.665</v>
       </c>
       <c r="M7" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="N7" t="n">
-        <v>0.842</v>
+        <v>0.841</v>
       </c>
       <c r="O7" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.354</v>
+        <v>-0.353</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.505</v>
+        <v>0.504</v>
       </c>
       <c r="R7" t="n">
         <v>20.69</v>
@@ -1131,7 +1131,7 @@
         <v>2690</v>
       </c>
       <c r="U7" t="n">
-        <v>0.867</v>
+        <v>0.868</v>
       </c>
       <c r="V7" t="n">
         <v>0.723</v>
@@ -1175,13 +1175,13 @@
         <v>9.863</v>
       </c>
       <c r="I8" t="n">
-        <v>7.937</v>
+        <v>7.938</v>
       </c>
       <c r="J8" t="n">
         <v>-2.008</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.926</v>
+        <v>-1.924</v>
       </c>
       <c r="L8" t="n">
         <v>5.811</v>
@@ -1196,7 +1196,7 @@
         <v>0.831</v>
       </c>
       <c r="P8" t="n">
-        <v>-45.935</v>
+        <v>-45.94</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.024</v>
@@ -1278,7 +1278,7 @@
         <v>-0.001</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.667</v>
+        <v>-0.668</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.042</v>
@@ -1339,19 +1339,19 @@
         <v>11.017</v>
       </c>
       <c r="I10" t="n">
-        <v>11.496</v>
+        <v>11.498</v>
       </c>
       <c r="J10" t="n">
         <v>-1.39</v>
       </c>
       <c r="K10" t="n">
-        <v>0.479</v>
+        <v>0.482</v>
       </c>
       <c r="L10" t="n">
-        <v>3.916</v>
+        <v>3.917</v>
       </c>
       <c r="M10" t="n">
-        <v>3.916</v>
+        <v>3.917</v>
       </c>
       <c r="N10" t="n">
         <v>4.213</v>
@@ -1360,13 +1360,13 @@
         <v>-0.492</v>
       </c>
       <c r="P10" t="n">
-        <v>-105.515</v>
+        <v>-105.539</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.727</v>
+        <v>-1.728</v>
       </c>
       <c r="R10" t="n">
-        <v>41.379</v>
+        <v>44.828</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1418,31 +1418,31 @@
         <v>5.32</v>
       </c>
       <c r="H11" t="n">
-        <v>112.89</v>
+        <v>112.892</v>
       </c>
       <c r="I11" t="n">
-        <v>108.405</v>
+        <v>108.41</v>
       </c>
       <c r="J11" t="n">
         <v>-1.68</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.485</v>
+        <v>-4.482</v>
       </c>
       <c r="L11" t="n">
-        <v>88.688</v>
+        <v>88.69</v>
       </c>
       <c r="M11" t="n">
-        <v>88.688</v>
+        <v>88.69</v>
       </c>
       <c r="N11" t="n">
-        <v>92.017</v>
+        <v>92.018</v>
       </c>
       <c r="O11" t="n">
         <v>-0.358</v>
       </c>
       <c r="P11" t="n">
-        <v>-13.683</v>
+        <v>-13.684</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.322</v>
@@ -1585,31 +1585,31 @@
         <v>5.956</v>
       </c>
       <c r="I13" t="n">
-        <v>5.121</v>
+        <v>5.12</v>
       </c>
       <c r="J13" t="n">
         <v>-0.6919999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.834</v>
+        <v>-0.836</v>
       </c>
       <c r="L13" t="n">
-        <v>0.26</v>
+        <v>0.259</v>
       </c>
       <c r="M13" t="n">
         <v>0.423</v>
       </c>
       <c r="N13" t="n">
-        <v>0.513</v>
+        <v>0.512</v>
       </c>
       <c r="O13" t="n">
         <v>0.441</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.218</v>
+        <v>0.219</v>
       </c>
       <c r="R13" t="n">
         <v>17.241</v>
@@ -1667,19 +1667,19 @@
         <v>7.097</v>
       </c>
       <c r="I14" t="n">
-        <v>5.207</v>
+        <v>5.209</v>
       </c>
       <c r="J14" t="n">
         <v>-2.422</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.889</v>
+        <v>-1.888</v>
       </c>
       <c r="L14" t="n">
-        <v>2.036</v>
+        <v>2.035</v>
       </c>
       <c r="M14" t="n">
-        <v>2.036</v>
+        <v>2.035</v>
       </c>
       <c r="N14" t="n">
         <v>2.52</v>
@@ -1688,10 +1688,10 @@
         <v>0.615</v>
       </c>
       <c r="P14" t="n">
-        <v>-10.094</v>
+        <v>-10.092</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.553</v>
+        <v>-0.554</v>
       </c>
       <c r="R14" t="n">
         <v>55.172</v>
@@ -1749,19 +1749,19 @@
         <v>8.144</v>
       </c>
       <c r="I15" t="n">
-        <v>6.357</v>
+        <v>6.358</v>
       </c>
       <c r="J15" t="n">
         <v>-1.525</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.787</v>
+        <v>-1.786</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.239</v>
+        <v>-0.238</v>
       </c>
       <c r="M15" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="N15" t="n">
         <v>0.482</v>
@@ -1770,10 +1770,10 @@
         <v>0.8169999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.196</v>
+        <v>-0.195</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.398</v>
+        <v>0.399</v>
       </c>
       <c r="R15" t="n">
         <v>41.379</v>
@@ -1793,7 +1793,7 @@
         <v>0.5649999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="X15" t="n">
         <v>2.285</v>
@@ -1913,28 +1913,28 @@
         <v>8.029999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>6.681</v>
+        <v>6.683</v>
       </c>
       <c r="J17" t="n">
         <v>-2.425</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.35</v>
+        <v>-1.348</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.505</v>
+        <v>-1.504</v>
       </c>
       <c r="M17" t="n">
-        <v>1.505</v>
+        <v>1.504</v>
       </c>
       <c r="N17" t="n">
         <v>1.625</v>
       </c>
       <c r="O17" t="n">
-        <v>0.601</v>
+        <v>0.6</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.679</v>
+        <v>-3.677</v>
       </c>
       <c r="Q17" t="n">
         <v>0.282</v>
@@ -1995,13 +1995,13 @@
         <v>7.154</v>
       </c>
       <c r="I18" t="n">
-        <v>6.294</v>
+        <v>6.291</v>
       </c>
       <c r="J18" t="n">
         <v>-1.55</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.86</v>
+        <v>-0.864</v>
       </c>
       <c r="L18" t="n">
         <v>1.538</v>
@@ -2016,10 +2016,10 @@
         <v>0.61</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.629</v>
+        <v>-6.623</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="R18" t="n">
         <v>44.828</v>
@@ -2074,19 +2074,19 @@
         <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.497</v>
+        <v>3.499</v>
       </c>
       <c r="I19" t="n">
-        <v>3.11</v>
+        <v>3.111</v>
       </c>
       <c r="J19" t="n">
         <v>-1.34</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.387</v>
+        <v>-0.388</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.155</v>
+        <v>-0.154</v>
       </c>
       <c r="M19" t="n">
         <v>0.371</v>
@@ -2098,10 +2098,10 @@
         <v>0.003</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.411</v>
+        <v>-0.408</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.108</v>
+        <v>-0.107</v>
       </c>
       <c r="R19" t="n">
         <v>46.154</v>
@@ -3392,10 +3392,10 @@
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8537102473498234</v>
+        <v>0.8538135593220338</v>
       </c>
       <c r="H18" t="n">
-        <v>8.17126148409894</v>
+        <v>8.171588983050848</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>5.71626148409894</v>
+        <v>5.716588983050848</v>
       </c>
       <c r="N18" t="n">
-        <v>5.71626148409894</v>
+        <v>5.716588983050848</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1374999999999997</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7287665467349775</v>
+        <v>-0.7284390477830698</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8508833922261484</v>
+        <v>0.8509887005649718</v>
       </c>
       <c r="H19" t="n">
-        <v>8.157975265017667</v>
+        <v>8.158225635593221</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3485,16 +3485,16 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.745475265017667</v>
+        <v>5.745725635593221</v>
       </c>
       <c r="N19" t="n">
-        <v>5.745475265017667</v>
+        <v>5.745725635593221</v>
       </c>
       <c r="O19" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.01328621908127303</v>
+        <v>-0.01336334745762713</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.846643109540636</v>
+        <v>0.8467514124293786</v>
       </c>
       <c r="H20" t="n">
-        <v>8.134646643109543</v>
+        <v>8.135504943502827</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3556,16 +3556,16 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>5.734646643109542</v>
+        <v>5.735504943502827</v>
       </c>
       <c r="N20" t="n">
-        <v>5.734646643109542</v>
+        <v>5.735504943502827</v>
       </c>
       <c r="O20" t="n">
         <v>-0.01250000000000018</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.02332862190812435</v>
+        <v>-0.02272069209039351</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8438162544169612</v>
+        <v>0.8439265536723164</v>
       </c>
       <c r="H21" t="n">
-        <v>8.119897526501767</v>
+        <v>8.120247175141243</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>5.949897526501767</v>
+        <v>5.950247175141243</v>
       </c>
       <c r="N21" t="n">
-        <v>5.949897526501767</v>
+        <v>5.950247175141243</v>
       </c>
       <c r="O21" t="n">
         <v>-0.23</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.014749116607776</v>
+        <v>-0.01525776836158421</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.83886925795053</v>
+        <v>0.8389830508474576</v>
       </c>
       <c r="H22" t="n">
-        <v>8.09843109540636</v>
+        <v>8.099152542372881</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3698,16 +3698,16 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>6.118431095406359</v>
+        <v>6.119152542372881</v>
       </c>
       <c r="N22" t="n">
-        <v>6.118431095406359</v>
+        <v>6.119152542372881</v>
       </c>
       <c r="O22" t="n">
         <v>-0.1899999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.02146643109540669</v>
+        <v>-0.02109463276836188</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.833922261484099</v>
+        <v>0.8340395480225988</v>
       </c>
       <c r="H23" t="n">
-        <v>8.064134275618375</v>
+        <v>8.065621468926553</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3769,16 +3769,16 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>6.014134275618376</v>
+        <v>6.015621468926553</v>
       </c>
       <c r="N23" t="n">
-        <v>6.014134275618376</v>
+        <v>6.015621468926553</v>
       </c>
       <c r="O23" t="n">
         <v>0.06999999999999984</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.03429681978798449</v>
+        <v>-0.03353107344632811</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8275618374558303</v>
+        <v>0.827683615819209</v>
       </c>
       <c r="H24" t="n">
         <v>8.030000000000001</v>
@@ -3849,7 +3849,7 @@
         <v>0.1700000000000004</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.03413427561837423</v>
+        <v>-0.03562146892655171</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8226148409893993</v>
+        <v>0.8227401129943502</v>
       </c>
       <c r="H25" t="n">
-        <v>8.013844522968197</v>
+        <v>8.014043079096044</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3911,16 +3911,16 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>5.663844522968198</v>
+        <v>5.664043079096045</v>
       </c>
       <c r="N25" t="n">
-        <v>5.663844522968198</v>
+        <v>5.664043079096045</v>
       </c>
       <c r="O25" t="n">
         <v>0.1299999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01615547703180376</v>
+        <v>-0.01595692090395673</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3960,10 +3960,10 @@
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8197879858657244</v>
+        <v>0.8199152542372882</v>
       </c>
       <c r="H26" t="n">
-        <v>8.003091872791519</v>
+        <v>8.003697033898305</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3982,16 +3982,16 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>5.703091872791519</v>
+        <v>5.703697033898306</v>
       </c>
       <c r="N26" t="n">
-        <v>5.703091872791519</v>
+        <v>5.703697033898306</v>
       </c>
       <c r="O26" t="n">
         <v>-0.05000000000000027</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.01075265017667881</v>
+        <v>-0.01034604519773907</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8162544169611308</v>
+        <v>0.8163841807909604</v>
       </c>
       <c r="H27" t="n">
-        <v>7.978842756183746</v>
+        <v>7.980282485875706</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4053,16 +4053,16 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>5.748842756183747</v>
+        <v>5.750282485875706</v>
       </c>
       <c r="N27" t="n">
-        <v>5.748842756183747</v>
+        <v>5.750282485875706</v>
       </c>
       <c r="O27" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.02424911660777251</v>
+        <v>-0.02341454802259957</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8120141342756184</v>
+        <v>0.8121468926553672</v>
       </c>
       <c r="H28" t="n">
-        <v>7.949084805653711</v>
+        <v>7.949505649717515</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>5.889084805653711</v>
+        <v>5.889505649717515</v>
       </c>
       <c r="N28" t="n">
-        <v>5.889084805653711</v>
+        <v>5.889505649717515</v>
       </c>
       <c r="O28" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.02975795053003516</v>
+        <v>-0.03077683615819105</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8127208480565371</v>
+        <v>0.8128531073446328</v>
       </c>
       <c r="H29" t="n">
-        <v>7.953312720848056</v>
+        <v>7.954360875706215</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4195,16 +4195,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>6.003312720848056</v>
+        <v>6.004360875706214</v>
       </c>
       <c r="N29" t="n">
-        <v>6.003312720848056</v>
+        <v>6.004360875706214</v>
       </c>
       <c r="O29" t="n">
         <v>-0.1100000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0042279151943454</v>
+        <v>0.004855225988699807</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8134275618374558</v>
+        <v>0.8135593220338984</v>
       </c>
       <c r="H30" t="n">
-        <v>7.958913427561836</v>
+        <v>7.959957627118643</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4266,16 +4266,16 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.258913427561835</v>
+        <v>5.259957627118643</v>
       </c>
       <c r="N30" t="n">
-        <v>5.258913427561835</v>
+        <v>5.259957627118643</v>
       </c>
       <c r="O30" t="n">
         <v>0.7500000000000002</v>
       </c>
       <c r="P30" t="n">
-        <v>0.005600706713779324</v>
+        <v>0.00559675141242888</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8098939929328622</v>
+        <v>0.8100282485875706</v>
       </c>
       <c r="H31" t="n">
-        <v>7.937091872791521</v>
+        <v>7.938368644067797</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4337,16 +4337,16 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.137091872791521</v>
+        <v>5.138368644067797</v>
       </c>
       <c r="N31" t="n">
-        <v>5.137091872791521</v>
+        <v>5.138368644067797</v>
       </c>
       <c r="O31" t="n">
         <v>0.09999999999999964</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.02182155477031511</v>
+        <v>-0.02158898305084644</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.649469964664311</v>
+        <v>0.6497175141242938</v>
       </c>
       <c r="H48" t="n">
-        <v>6.159359761484099</v>
+        <v>6.159454449152543</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5538,16 +5538,16 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1281402385159005</v>
+        <v>-0.1280455508474567</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1281402385159005</v>
+        <v>0.1280455508474567</v>
       </c>
       <c r="O48" t="n">
         <v>-0.09250000000000114</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.6245295167219274</v>
+        <v>-0.6244348290534836</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6431095406360424</v>
+        <v>0.643361581920904</v>
       </c>
       <c r="H49" t="n">
-        <v>6.14791519434629</v>
+        <v>6.148686440677967</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5609,16 +5609,16 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0220848056537104</v>
+        <v>-0.02131355932203327</v>
       </c>
       <c r="N49" t="n">
-        <v>0.0220848056537104</v>
+        <v>0.02131355932203327</v>
       </c>
       <c r="O49" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.01144456713780961</v>
+        <v>-0.01076800847457626</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5658,10 +5658,10 @@
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>0.6353356890459364</v>
+        <v>0.635593220338983</v>
       </c>
       <c r="H50" t="n">
-        <v>6.125301766784452</v>
+        <v>6.125932203389831</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5680,16 +5680,16 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0353017667844524</v>
+        <v>0.03593220338983105</v>
       </c>
       <c r="N50" t="n">
-        <v>0.0353017667844524</v>
+        <v>0.03593220338983105</v>
       </c>
       <c r="O50" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.02261342756183726</v>
+        <v>-0.02275423728813575</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5729,10 +5729,10 @@
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6339222614840989</v>
+        <v>0.634180790960452</v>
       </c>
       <c r="H51" t="n">
-        <v>6.121841696113075</v>
+        <v>6.122474576271187</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5751,16 +5751,16 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2618416961130743</v>
+        <v>0.2624745762711864</v>
       </c>
       <c r="N51" t="n">
-        <v>0.2618416961130743</v>
+        <v>0.2624745762711864</v>
       </c>
       <c r="O51" t="n">
         <v>-0.2299999999999995</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.003460070671377657</v>
+        <v>-0.003457627118644169</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>0.6452296819787986</v>
+        <v>0.6454802259887006</v>
       </c>
       <c r="H52" t="n">
-        <v>6.157737853356891</v>
+        <v>6.157833686440679</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5822,16 +5822,16 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4977378533568908</v>
+        <v>0.4978336864406785</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4977378533568908</v>
+        <v>0.4978336864406785</v>
       </c>
       <c r="O52" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P52" t="n">
-        <v>0.03589615724381634</v>
+        <v>0.03535911016949189</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6530035335689046</v>
+        <v>0.6532485875706214</v>
       </c>
       <c r="H53" t="n">
-        <v>6.168190812720848</v>
+        <v>6.168940677966101</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5893,16 +5893,16 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5381908127208481</v>
+        <v>0.5389406779661012</v>
       </c>
       <c r="N53" t="n">
-        <v>0.5381908127208481</v>
+        <v>0.5389406779661012</v>
       </c>
       <c r="O53" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P53" t="n">
-        <v>0.01045295936395707</v>
+        <v>0.01110699152542249</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6628975265017668</v>
+        <v>0.663135593220339</v>
       </c>
       <c r="H54" t="n">
-        <v>6.207955241460542</v>
+        <v>6.208926553672317</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5964,16 +5964,16 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6179552414605425</v>
+        <v>0.618926553672317</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6179552414605425</v>
+        <v>0.618926553672317</v>
       </c>
       <c r="O54" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P54" t="n">
-        <v>0.03976442873969432</v>
+        <v>0.0399858757062157</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6692579505300353</v>
+        <v>0.6694915254237288</v>
       </c>
       <c r="H55" t="n">
-        <v>6.218964664310954</v>
+        <v>6.219322033898305</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6035,16 +6035,16 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7689646643109533</v>
+        <v>0.7693220338983044</v>
       </c>
       <c r="N55" t="n">
-        <v>0.7689646643109533</v>
+        <v>0.7693220338983044</v>
       </c>
       <c r="O55" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01100942285041118</v>
+        <v>0.0103954802259878</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6657243816254417</v>
+        <v>0.6659604519774012</v>
       </c>
       <c r="H56" t="n">
-        <v>6.213558303886925</v>
+        <v>6.213919491525424</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6106,16 +6106,16 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0.813558303886925</v>
+        <v>0.8139194915254233</v>
       </c>
       <c r="N56" t="n">
-        <v>0.813558303886925</v>
+        <v>0.8139194915254233</v>
       </c>
       <c r="O56" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.0054063604240282</v>
+        <v>-0.005402542372880959</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
         <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6544169611307421</v>
+        <v>0.6546610169491526</v>
       </c>
       <c r="H57" t="n">
-        <v>6.175031802120142</v>
+        <v>6.176525423728814</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8050318021201415</v>
+        <v>0.8065254237288135</v>
       </c>
       <c r="N57" t="n">
-        <v>0.8050318021201415</v>
+        <v>0.8065254237288135</v>
       </c>
       <c r="O57" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.03852650176678374</v>
+        <v>-0.03739406779661003</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6226,10 +6226,10 @@
         <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6388692579505301</v>
+        <v>0.6391242937853108</v>
       </c>
       <c r="H58" t="n">
-        <v>6.136626619552414</v>
+        <v>6.137146892655367</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6248,16 +6248,16 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8066266195524143</v>
+        <v>0.8071468926553669</v>
       </c>
       <c r="N58" t="n">
-        <v>0.8066266195524143</v>
+        <v>0.8071468926553669</v>
       </c>
       <c r="O58" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.03840518256772718</v>
+        <v>-0.03937853107344669</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6297,10 +6297,10 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6204946996466431</v>
+        <v>0.6207627118644068</v>
       </c>
       <c r="H59" t="n">
-        <v>6.07828504122497</v>
+        <v>6.079378531073447</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6319,16 +6319,16 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9282850412249699</v>
+        <v>0.9293785310734464</v>
       </c>
       <c r="N59" t="n">
-        <v>0.9282850412249699</v>
+        <v>0.9293785310734464</v>
       </c>
       <c r="O59" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.05834157832744413</v>
+        <v>-0.05776836158192022</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6063604240282685</v>
+        <v>0.606638418079096</v>
       </c>
       <c r="H60" t="n">
-        <v>6.030925795053004</v>
+        <v>6.032627118644069</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6390,16 +6390,16 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1.060925795053004</v>
+        <v>1.062627118644069</v>
       </c>
       <c r="N60" t="n">
-        <v>1.060925795053004</v>
+        <v>1.062627118644069</v>
       </c>
       <c r="O60" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.04735924617196652</v>
+        <v>-0.04675141242937819</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6439,10 +6439,10 @@
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5915194346289753</v>
+        <v>0.5918079096045198</v>
       </c>
       <c r="H61" t="n">
-        <v>5.970148409893993</v>
+        <v>5.972796610169492</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6461,16 +6461,16 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1.140148409893992</v>
+        <v>1.142796610169492</v>
       </c>
       <c r="N61" t="n">
-        <v>1.140148409893992</v>
+        <v>1.142796610169492</v>
       </c>
       <c r="O61" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.06077738515901121</v>
+        <v>-0.05983050847457694</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -7640,10 +7640,10 @@
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8975265017667845</v>
+        <v>0.8975988700564972</v>
       </c>
       <c r="H78" t="n">
-        <v>5.879257950530036</v>
+        <v>5.880123587570623</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7662,16 +7662,16 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1.191757950530036</v>
+        <v>1.192623587570623</v>
       </c>
       <c r="N78" t="n">
-        <v>1.191757950530036</v>
+        <v>1.192623587570623</v>
       </c>
       <c r="O78" t="n">
         <v>0.2725</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.06256755752882892</v>
+        <v>-0.0617019204882423</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8685512367491166</v>
+        <v>0.8686440677966102</v>
       </c>
       <c r="H79" t="n">
-        <v>5.692565371024735</v>
+        <v>5.693644067796611</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7733,16 +7733,16 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>1.280065371024736</v>
+        <v>1.281144067796611</v>
       </c>
       <c r="N79" t="n">
-        <v>1.280065371024736</v>
+        <v>1.281144067796611</v>
       </c>
       <c r="O79" t="n">
         <v>-0.2750000000000004</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.1866925795053005</v>
+        <v>-0.1864795197740117</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>0.826148409893993</v>
+        <v>0.826271186440678</v>
       </c>
       <c r="H80" t="n">
-        <v>5.414922261484099</v>
+        <v>5.415635593220339</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7804,16 +7804,16 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7649222614840987</v>
+        <v>0.7656355932203383</v>
       </c>
       <c r="N80" t="n">
-        <v>0.7649222614840987</v>
+        <v>0.7656355932203383</v>
       </c>
       <c r="O80" t="n">
         <v>0.2375000000000007</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.2776431095406364</v>
+        <v>-0.2780084745762723</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7795053003533569</v>
+        <v>0.7796610169491526</v>
       </c>
       <c r="H81" t="n">
-        <v>5.153925795053003</v>
+        <v>5.154830508474576</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7875,16 +7875,16 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>0.4539257950530029</v>
+        <v>0.4548305084745756</v>
       </c>
       <c r="N81" t="n">
-        <v>0.4539257950530029</v>
+        <v>0.4548305084745756</v>
       </c>
       <c r="O81" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.260996466431096</v>
+        <v>-0.2608050847457628</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7335689045936395</v>
+        <v>0.7337570621468926</v>
       </c>
       <c r="H82" t="n">
-        <v>4.997035335689046</v>
+        <v>4.998128531073446</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7946,16 +7946,16 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5920353356890464</v>
+        <v>0.5931285310734467</v>
       </c>
       <c r="N82" t="n">
-        <v>0.5920353356890464</v>
+        <v>0.5931285310734467</v>
       </c>
       <c r="O82" t="n">
         <v>-0.2950000000000008</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.1568904593639573</v>
+        <v>-0.1567019774011298</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -7995,10 +7995,10 @@
         <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7074204946996466</v>
+        <v>0.7076271186440678</v>
       </c>
       <c r="H83" t="n">
-        <v>4.870113074204947</v>
+        <v>4.871313559322034</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8017,16 +8017,16 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>0.7726130742049477</v>
+        <v>0.7738135593220345</v>
       </c>
       <c r="N83" t="n">
-        <v>0.7726130742049477</v>
+        <v>0.7738135593220345</v>
       </c>
       <c r="O83" t="n">
         <v>-0.3075000000000001</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.1269222614840988</v>
+        <v>-0.1268149717514122</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -8066,10 +8066,10 @@
         <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>0.6756183745583039</v>
+        <v>0.6758474576271186</v>
       </c>
       <c r="H84" t="n">
-        <v>4.785812216052499</v>
+        <v>4.786192493946731</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8088,16 +8088,16 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>0.9358122160524984</v>
+        <v>0.9361924939467312</v>
       </c>
       <c r="N84" t="n">
-        <v>0.9358122160524984</v>
+        <v>0.9361924939467312</v>
       </c>
       <c r="O84" t="n">
         <v>-0.2474999999999992</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.08430085815244848</v>
+        <v>-0.08512106537530251</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6409893992932862</v>
+        <v>0.6412429378531074</v>
       </c>
       <c r="H85" t="n">
-        <v>4.688191401648999</v>
+        <v>4.688436911487759</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8159,16 +8159,16 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9081914016489994</v>
+        <v>0.9084369114877595</v>
       </c>
       <c r="N85" t="n">
-        <v>0.9081914016489994</v>
+        <v>0.9084369114877595</v>
       </c>
       <c r="O85" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.09762081440349935</v>
+        <v>-0.09775558245897198</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6035335689045936</v>
+        <v>0.6031073446327684</v>
       </c>
       <c r="H86" t="n">
-        <v>4.546530035335689</v>
+        <v>4.544053672316384</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8230,16 +8230,16 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.2534699646643119</v>
+        <v>-0.2559463276836169</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2534699646643119</v>
+        <v>0.2559463276836169</v>
       </c>
       <c r="O86" t="n">
         <v>1.020000000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.1416613663133104</v>
+        <v>-0.1443832391713755</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -8279,10 +8279,10 @@
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>0.5964664310954063</v>
+        <v>0.596045197740113</v>
       </c>
       <c r="H87" t="n">
-        <v>4.517734982332155</v>
+        <v>4.516511299435028</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8301,16 +8301,16 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.1822650176678451</v>
+        <v>-0.1834887005649719</v>
       </c>
       <c r="N87" t="n">
-        <v>0.1822650176678451</v>
+        <v>0.1834887005649719</v>
       </c>
       <c r="O87" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.02879505300353369</v>
+        <v>-0.02754237288135553</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -8350,10 +8350,10 @@
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6141342756183745</v>
+        <v>0.614406779661017</v>
       </c>
       <c r="H88" t="n">
-        <v>4.572080094228504</v>
+        <v>4.573135593220339</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8372,16 +8372,16 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.6279199057714964</v>
+        <v>-0.6268644067796609</v>
       </c>
       <c r="N88" t="n">
-        <v>0.6279199057714964</v>
+        <v>0.6268644067796609</v>
       </c>
       <c r="O88" t="n">
         <v>0.5</v>
       </c>
       <c r="P88" t="n">
-        <v>0.05434511189634872</v>
+        <v>0.05662429378531098</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6586572438162545</v>
+        <v>0.6588983050847458</v>
       </c>
       <c r="H89" t="n">
-        <v>4.723399293286219</v>
+        <v>4.724099576271186</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8443,16 +8443,16 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.776600706713781</v>
+        <v>-0.7759004237288138</v>
       </c>
       <c r="N89" t="n">
-        <v>0.776600706713781</v>
+        <v>0.7759004237288138</v>
       </c>
       <c r="O89" t="n">
         <v>0.2999999999999998</v>
       </c>
       <c r="P89" t="n">
-        <v>0.1513191990577152</v>
+        <v>0.1509639830508469</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8492,10 +8492,10 @@
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6819787985865724</v>
+        <v>0.6822033898305084</v>
       </c>
       <c r="H90" t="n">
-        <v>4.795574204946996</v>
+        <v>4.795900423728813</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8514,16 +8514,16 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-1.084425795053003</v>
+        <v>-1.084099576271186</v>
       </c>
       <c r="N90" t="n">
-        <v>1.084425795053003</v>
+        <v>1.084099576271186</v>
       </c>
       <c r="O90" t="n">
         <v>0.3799999999999999</v>
       </c>
       <c r="P90" t="n">
-        <v>0.0721749116607775</v>
+        <v>0.07180084745762727</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8563,10 +8563,10 @@
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6848056537102474</v>
+        <v>0.6850282485875706</v>
       </c>
       <c r="H91" t="n">
-        <v>4.799680212014134</v>
+        <v>4.8</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -8585,16 +8585,16 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.2203197879858658</v>
+        <v>-0.2199999999999998</v>
       </c>
       <c r="N91" t="n">
-        <v>0.2203197879858658</v>
+        <v>0.2199999999999998</v>
       </c>
       <c r="O91" t="n">
         <v>-0.8600000000000003</v>
       </c>
       <c r="P91" t="n">
-        <v>0.004106007067137263</v>
+        <v>0.0040995762711864</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -9764,10 +9764,10 @@
         <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8911660777385159</v>
+        <v>0.8912429378531074</v>
       </c>
       <c r="H108" t="n">
-        <v>12.38318374558304</v>
+        <v>12.38334745762712</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -9786,16 +9786,16 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>5.31318374558304</v>
+        <v>5.31334745762712</v>
       </c>
       <c r="N108" t="n">
-        <v>5.31318374558304</v>
+        <v>5.31334745762712</v>
       </c>
       <c r="O108" t="n">
         <v>-0.1250000000000009</v>
       </c>
       <c r="P108" t="n">
-        <v>4.413604208091801</v>
+        <v>4.41376792013588</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -9835,10 +9835,10 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>0.8869257950530035</v>
+        <v>0.8870056497175142</v>
       </c>
       <c r="H109" t="n">
-        <v>12.34067137809187</v>
+        <v>12.34254237288136</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -9857,16 +9857,16 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>5.470671378091871</v>
+        <v>5.472542372881356</v>
       </c>
       <c r="N109" t="n">
-        <v>5.470671378091871</v>
+        <v>5.472542372881356</v>
       </c>
       <c r="O109" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.04251236749116849</v>
+        <v>-0.04080508474576305</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -9906,10 +9906,10 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8848056537102473</v>
+        <v>0.8848870056497176</v>
       </c>
       <c r="H110" t="n">
-        <v>12.29140812720848</v>
+        <v>12.2919279661017</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -9928,16 +9928,16 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>5.551408127208481</v>
+        <v>5.551927966101696</v>
       </c>
       <c r="N110" t="n">
-        <v>5.551408127208481</v>
+        <v>5.551927966101696</v>
       </c>
       <c r="O110" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.04926325088339034</v>
+        <v>-0.05061440677966011</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -9946,11 +9946,11 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -9977,10 +9977,10 @@
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>0.8826855123674912</v>
+        <v>0.882768361581921</v>
       </c>
       <c r="H111" t="n">
-        <v>12.27786042402827</v>
+        <v>12.27838983050848</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -9999,16 +9999,16 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>5.677860424028269</v>
+        <v>5.678389830508475</v>
       </c>
       <c r="N111" t="n">
-        <v>5.677860424028269</v>
+        <v>5.678389830508475</v>
       </c>
       <c r="O111" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P111" t="n">
-        <v>-0.01354770318021181</v>
+        <v>-0.0135381355932207</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -10048,10 +10048,10 @@
         <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8763250883392226</v>
+        <v>0.876412429378531</v>
       </c>
       <c r="H112" t="n">
-        <v>12.22314487632509</v>
+        <v>12.22351694915254</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10070,16 +10070,16 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>5.363144876325088</v>
+        <v>5.363516949152543</v>
       </c>
       <c r="N112" t="n">
-        <v>5.363144876325088</v>
+        <v>5.363516949152543</v>
       </c>
       <c r="O112" t="n">
         <v>0.2600000000000007</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.05471554770318043</v>
+        <v>-0.05487288135593182</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>0.8678445229681979</v>
+        <v>0.8679378531073446</v>
       </c>
       <c r="H113" t="n">
-        <v>12.19100883392226</v>
+        <v>12.19120762711864</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -10141,16 +10141,16 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>5.211008833922261</v>
+        <v>5.211207627118643</v>
       </c>
       <c r="N113" t="n">
-        <v>5.211008833922261</v>
+        <v>5.211207627118643</v>
       </c>
       <c r="O113" t="n">
         <v>0.1200000000000001</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.03213604240282741</v>
+        <v>-0.03230932203389969</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -10190,10 +10190,10 @@
         <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8572438162544169</v>
+        <v>0.8573446327683616</v>
       </c>
       <c r="H114" t="n">
-        <v>12.12057597173145</v>
+        <v>12.12186440677966</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -10212,16 +10212,16 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>5.270575971731448</v>
+        <v>5.271864406779661</v>
       </c>
       <c r="N114" t="n">
-        <v>5.270575971731448</v>
+        <v>5.271864406779661</v>
       </c>
       <c r="O114" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P114" t="n">
-        <v>-0.07043286219081324</v>
+        <v>-0.06934322033898255</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
         <v>8</v>
       </c>
       <c r="G115" t="n">
-        <v>0.846643109540636</v>
+        <v>0.8467514124293786</v>
       </c>
       <c r="H115" t="n">
-        <v>12.07669964664311</v>
+        <v>12.07716101694915</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -10283,16 +10283,16 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>5.336699646643108</v>
+        <v>5.337161016949151</v>
       </c>
       <c r="N115" t="n">
-        <v>5.336699646643108</v>
+        <v>5.337161016949151</v>
       </c>
       <c r="O115" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.04387632508833939</v>
+        <v>-0.04470338983050937</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -10332,10 +10332,10 @@
         <v>8</v>
       </c>
       <c r="G116" t="n">
-        <v>0.8247349823321555</v>
+        <v>0.8248587570621468</v>
       </c>
       <c r="H116" t="n">
-        <v>11.86337102473498</v>
+        <v>11.86389830508474</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -10354,16 +10354,16 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>5.258371024734981</v>
+        <v>5.258898305084744</v>
       </c>
       <c r="N116" t="n">
-        <v>5.258371024734981</v>
+        <v>5.258898305084744</v>
       </c>
       <c r="O116" t="n">
         <v>-0.1349999999999998</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.2133286219081274</v>
+        <v>-0.2132627118644077</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10403,10 +10403,10 @@
         <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>0.8098939929328622</v>
+        <v>0.8100282485875706</v>
       </c>
       <c r="H117" t="n">
-        <v>11.810074204947</v>
+        <v>11.81036016949153</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -10425,16 +10425,16 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>5.430074204946997</v>
+        <v>5.430360169491526</v>
       </c>
       <c r="N117" t="n">
-        <v>5.430074204946997</v>
+        <v>5.430360169491526</v>
       </c>
       <c r="O117" t="n">
         <v>-0.2250000000000005</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.05329681978798462</v>
+        <v>-0.05353813559321807</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10474,10 +10474,10 @@
         <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7957597173144876</v>
+        <v>0.7959039548022598</v>
       </c>
       <c r="H118" t="n">
-        <v>11.72496819787986</v>
+        <v>11.72527542372881</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -10496,16 +10496,16 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>5.484968197879859</v>
+        <v>5.485275423728813</v>
       </c>
       <c r="N118" t="n">
-        <v>5.484968197879859</v>
+        <v>5.485275423728813</v>
       </c>
       <c r="O118" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.08510600706713767</v>
+        <v>-0.08508474576271219</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10545,10 +10545,10 @@
         <v>8</v>
       </c>
       <c r="G119" t="n">
-        <v>0.7823321554770318</v>
+        <v>0.7824858757062146</v>
       </c>
       <c r="H119" t="n">
-        <v>11.66160247349823</v>
+        <v>11.66258474576271</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -10567,16 +10567,16 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>5.541602473498233</v>
+        <v>5.542584745762711</v>
       </c>
       <c r="N119" t="n">
-        <v>5.541602473498233</v>
+        <v>5.542584745762711</v>
       </c>
       <c r="O119" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.06336572438162591</v>
+        <v>-0.06269067796610273</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -10616,10 +10616,10 @@
         <v>8</v>
       </c>
       <c r="G120" t="n">
-        <v>0.7681978798586573</v>
+        <v>0.768361581920904</v>
       </c>
       <c r="H120" t="n">
-        <v>11.55626148409894</v>
+        <v>11.55661016949152</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10638,16 +10638,16 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>5.486261484098939</v>
+        <v>5.486610169491524</v>
       </c>
       <c r="N120" t="n">
-        <v>5.486261484098939</v>
+        <v>5.486610169491524</v>
       </c>
       <c r="O120" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.1053409893992932</v>
+        <v>-0.105974576271187</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         <v>8</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7597173144876325</v>
+        <v>0.7598870056497176</v>
       </c>
       <c r="H121" t="n">
-        <v>11.49558303886926</v>
+        <v>11.49847457627119</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -10709,16 +10709,16 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.465583038869258</v>
+        <v>5.468474576271187</v>
       </c>
       <c r="N121" t="n">
-        <v>5.465583038869258</v>
+        <v>5.468474576271187</v>
       </c>
       <c r="O121" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.0606784452296818</v>
+        <v>-0.0581355932203369</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>8</v>
       </c>
       <c r="G122" t="n">
-        <v>0.9597173144876325</v>
+        <v>0.9597457627118644</v>
       </c>
       <c r="H122" t="n">
-        <v>112.8903604240283</v>
+        <v>112.8920550847458</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>105.8903604240283</v>
+        <v>105.8920550847458</v>
       </c>
       <c r="N122" t="n">
-        <v>105.8903604240283</v>
+        <v>105.8920550847458</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         <v>8</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9356890459363958</v>
+        <v>0.9357344632768362</v>
       </c>
       <c r="H123" t="n">
-        <v>112.4627137809187</v>
+        <v>112.4631002824859</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -10845,16 +10845,16 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>105.6527137809187</v>
+        <v>105.6531002824859</v>
       </c>
       <c r="N123" t="n">
-        <v>105.6527137809187</v>
+        <v>105.6531002824859</v>
       </c>
       <c r="O123" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.4276466431095542</v>
+        <v>-0.428954802259895</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -10894,10 +10894,10 @@
         <v>8</v>
       </c>
       <c r="G124" t="n">
-        <v>0.9180212014134276</v>
+        <v>0.9180790960451978</v>
       </c>
       <c r="H124" t="n">
-        <v>112.1423604240283</v>
+        <v>112.1428531073446</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -10916,16 +10916,16 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>105.5323604240283</v>
+        <v>105.5328531073446</v>
       </c>
       <c r="N124" t="n">
-        <v>105.5323604240283</v>
+        <v>105.5328531073446</v>
       </c>
       <c r="O124" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P124" t="n">
-        <v>-0.3203533568904504</v>
+        <v>-0.3202471751412332</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -10965,10 +10965,10 @@
         <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>0.9010600706713781</v>
+        <v>0.9011299435028248</v>
       </c>
       <c r="H125" t="n">
-        <v>111.9990106007067</v>
+        <v>111.9993079096045</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -10987,16 +10987,16 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>105.5790106007067</v>
+        <v>105.5793079096045</v>
       </c>
       <c r="N125" t="n">
-        <v>105.5790106007067</v>
+        <v>105.5793079096045</v>
       </c>
       <c r="O125" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P125" t="n">
-        <v>-0.1433498233215573</v>
+        <v>-0.1435451977401101</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -11036,10 +11036,10 @@
         <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>0.8579505300353357</v>
+        <v>0.8580508474576272</v>
       </c>
       <c r="H126" t="n">
-        <v>111.6767385159011</v>
+        <v>111.6780190677966</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -11058,16 +11058,16 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>105.446738515901</v>
+        <v>105.4480190677966</v>
       </c>
       <c r="N126" t="n">
-        <v>105.446738515901</v>
+        <v>105.4480190677966</v>
       </c>
       <c r="O126" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.3222720848056611</v>
+        <v>-0.3212888418079132</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -11107,10 +11107,10 @@
         <v>8</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8120141342756184</v>
+        <v>0.8121468926553672</v>
       </c>
       <c r="H127" t="n">
-        <v>111.4334134275618</v>
+        <v>111.4337900188324</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -11129,16 +11129,16 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>105.3734134275618</v>
+        <v>105.3737900188324</v>
       </c>
       <c r="N127" t="n">
-        <v>105.3734134275618</v>
+        <v>105.3737900188324</v>
       </c>
       <c r="O127" t="n">
         <v>-0.1700000000000008</v>
       </c>
       <c r="P127" t="n">
-        <v>-0.2433250883392049</v>
+        <v>-0.2442290489642147</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -11178,10 +11178,10 @@
         <v>8</v>
       </c>
       <c r="G128" t="n">
-        <v>0.7533568904593639</v>
+        <v>0.7535310734463276</v>
       </c>
       <c r="H128" t="n">
-        <v>111.1702134275618</v>
+        <v>111.1705098870057</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -11200,16 +11200,16 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>105.2402134275618</v>
+        <v>105.2405098870057</v>
       </c>
       <c r="N128" t="n">
-        <v>105.2402134275618</v>
+        <v>105.2405098870057</v>
       </c>
       <c r="O128" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.2632000000000119</v>
+        <v>-0.2632801318267468</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -11249,10 +11249,10 @@
         <v>8</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6756183745583039</v>
+        <v>0.6758474576271186</v>
       </c>
       <c r="H129" t="n">
-        <v>110.7642685512368</v>
+        <v>110.7671927966102</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -11271,16 +11271,16 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>52.39926855123675</v>
+        <v>52.40219279661017</v>
       </c>
       <c r="N129" t="n">
-        <v>52.39926855123675</v>
+        <v>52.40219279661017</v>
       </c>
       <c r="O129" t="n">
         <v>52.435</v>
       </c>
       <c r="P129" t="n">
-        <v>-0.4059448763250799</v>
+        <v>-0.4033170903954755</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -11320,10 +11320,10 @@
         <v>8</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5978798586572438</v>
+        <v>0.5981638418079096</v>
       </c>
       <c r="H130" t="n">
-        <v>110.3739787985866</v>
+        <v>110.3751871468927</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -11342,16 +11342,16 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>52.07897879858658</v>
+        <v>52.08018714689265</v>
       </c>
       <c r="N130" t="n">
-        <v>52.07897879858658</v>
+        <v>52.08018714689265</v>
       </c>
       <c r="O130" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.3902897526501761</v>
+        <v>-0.3920056497175182</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         <v>8</v>
       </c>
       <c r="G131" t="n">
-        <v>0.5173144876325089</v>
+        <v>0.5176553672316384</v>
       </c>
       <c r="H131" t="n">
-        <v>109.9707038869258</v>
+        <v>109.9715741525424</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -11413,16 +11413,16 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>51.78570388692579</v>
+        <v>51.78657415254237</v>
       </c>
       <c r="N131" t="n">
-        <v>51.78570388692579</v>
+        <v>51.78657415254237</v>
       </c>
       <c r="O131" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.4032749116607874</v>
+        <v>-0.4036129943502829</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -11462,10 +11462,10 @@
         <v>8</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4325088339222615</v>
+        <v>0.432909604519774</v>
       </c>
       <c r="H132" t="n">
-        <v>109.4537667844523</v>
+        <v>109.4560404896422</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -11484,16 +11484,16 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>51.4087667844523</v>
+        <v>51.41104048964218</v>
       </c>
       <c r="N132" t="n">
-        <v>51.4087667844523</v>
+        <v>51.41104048964218</v>
       </c>
       <c r="O132" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.5169371024734914</v>
+        <v>-0.5155336629001965</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -11533,10 +11533,10 @@
         <v>8</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3519434628975265</v>
+        <v>0.3524011299435028</v>
       </c>
       <c r="H133" t="n">
-        <v>108.912519434629</v>
+        <v>108.9144668079096</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -11555,16 +11555,16 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>103.472519434629</v>
+        <v>103.4744668079096</v>
       </c>
       <c r="N133" t="n">
-        <v>103.472519434629</v>
+        <v>103.4744668079096</v>
       </c>
       <c r="O133" t="n">
         <v>-52.605</v>
       </c>
       <c r="P133" t="n">
-        <v>-0.5412473498233226</v>
+        <v>-0.5415736817325723</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -11604,10 +11604,10 @@
         <v>8</v>
       </c>
       <c r="G134" t="n">
-        <v>0.2685512367491166</v>
+        <v>0.2690677966101695</v>
       </c>
       <c r="H134" t="n">
-        <v>108.405371024735</v>
+        <v>108.4097669491525</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -11626,16 +11626,16 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>103.085371024735</v>
+        <v>103.0897669491525</v>
       </c>
       <c r="N134" t="n">
-        <v>103.085371024735</v>
+        <v>103.0897669491525</v>
       </c>
       <c r="O134" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P134" t="n">
-        <v>-0.5071484098939862</v>
+        <v>-0.5046998587570641</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
         <v>8</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9314487632508834</v>
+        <v>0.931497175141243</v>
       </c>
       <c r="H154" t="n">
-        <v>9.031971731448763</v>
+        <v>9.032040960451978</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -13034,16 +13034,16 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>0.5719717314487625</v>
+        <v>0.5720409604519769</v>
       </c>
       <c r="N154" t="n">
-        <v>0.5719717314487625</v>
+        <v>0.5720409604519769</v>
       </c>
       <c r="O154" t="n">
         <v>0.005000000000000782</v>
       </c>
       <c r="P154" t="n">
-        <v>0.5829624462350296</v>
+        <v>0.5830316752382441</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>8</v>
       </c>
       <c r="G155" t="n">
-        <v>0.9215547703180212</v>
+        <v>0.9216101694915254</v>
       </c>
       <c r="H155" t="n">
         <v>9.009999999999998</v>
@@ -13114,7 +13114,7 @@
         <v>-0.03000000000000114</v>
       </c>
       <c r="P155" t="n">
-        <v>-0.0219717314487653</v>
+        <v>-0.02204096045197979</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -13154,10 +13154,10 @@
         <v>8</v>
       </c>
       <c r="G156" t="n">
-        <v>0.9144876325088339</v>
+        <v>0.91454802259887</v>
       </c>
       <c r="H156" t="n">
-        <v>8.967717314487633</v>
+        <v>8.967803672316386</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -13176,16 +13176,16 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0.5577173144876326</v>
+        <v>0.5578036723163855</v>
       </c>
       <c r="N156" t="n">
-        <v>0.5577173144876326</v>
+        <v>0.5578036723163855</v>
       </c>
       <c r="O156" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P156" t="n">
-        <v>-0.04228268551236525</v>
+        <v>-0.04219632768361237</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -13225,10 +13225,10 @@
         <v>8</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9053003533568904</v>
+        <v>0.905367231638418</v>
       </c>
       <c r="H157" t="n">
-        <v>8.921659010600708</v>
+        <v>8.921850282485876</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -13247,16 +13247,16 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>0.6216590106007072</v>
+        <v>0.6218502824858749</v>
       </c>
       <c r="N157" t="n">
-        <v>0.6216590106007072</v>
+        <v>0.6218502824858749</v>
       </c>
       <c r="O157" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P157" t="n">
-        <v>-0.04605830388692489</v>
+        <v>-0.04595338983051001</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>8</v>
       </c>
       <c r="G158" t="n">
-        <v>0.8954063604240282</v>
+        <v>0.8954802259887006</v>
       </c>
       <c r="H158" t="n">
-        <v>8.857931095406361</v>
+        <v>8.858036723163844</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -13318,16 +13318,16 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>0.6879310954063609</v>
+        <v>0.6880367231638438</v>
       </c>
       <c r="N158" t="n">
-        <v>0.6879310954063609</v>
+        <v>0.6880367231638438</v>
       </c>
       <c r="O158" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P158" t="n">
-        <v>-0.06372791519434706</v>
+        <v>-0.06381355932203192</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -13367,10 +13367,10 @@
         <v>8</v>
       </c>
       <c r="G159" t="n">
-        <v>0.8890459363957597</v>
+        <v>0.8891242937853108</v>
       </c>
       <c r="H159" t="n">
-        <v>8.791849823321554</v>
+        <v>8.79263418079096</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -13389,16 +13389,16 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>0.8418498233215539</v>
+        <v>0.8426341807909603</v>
       </c>
       <c r="N159" t="n">
-        <v>0.8418498233215539</v>
+        <v>0.8426341807909603</v>
       </c>
       <c r="O159" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P159" t="n">
-        <v>-0.06608127208480674</v>
+        <v>-0.06540254237288323</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -13438,10 +13438,10 @@
         <v>8</v>
       </c>
       <c r="G160" t="n">
-        <v>0.8657243816254417</v>
+        <v>0.865819209039548</v>
       </c>
       <c r="H160" t="n">
-        <v>8.433401060070672</v>
+        <v>8.434350282485875</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -13460,16 +13460,16 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>0.6634010600706723</v>
+        <v>0.6643502824858754</v>
       </c>
       <c r="N160" t="n">
-        <v>0.6634010600706723</v>
+        <v>0.6643502824858754</v>
       </c>
       <c r="O160" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P160" t="n">
-        <v>-0.3584487632508822</v>
+        <v>-0.3582838983050856</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -13509,10 +13509,10 @@
         <v>8</v>
       </c>
       <c r="G161" t="n">
-        <v>0.8586572438162544</v>
+        <v>0.8587570621468926</v>
       </c>
       <c r="H161" t="n">
-        <v>8.238515901060071</v>
+        <v>8.242655367231636</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -13531,16 +13531,16 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>0.5085159010600702</v>
+        <v>0.5126553672316359</v>
       </c>
       <c r="N161" t="n">
-        <v>0.5085159010600702</v>
+        <v>0.5126553672316359</v>
       </c>
       <c r="O161" t="n">
         <v>-0.03999999999999915</v>
       </c>
       <c r="P161" t="n">
-        <v>-0.1948851590106013</v>
+        <v>-0.1916949152542387</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -13580,10 +13580,10 @@
         <v>8</v>
       </c>
       <c r="G162" t="n">
-        <v>0.8494699646643109</v>
+        <v>0.8495762711864406</v>
       </c>
       <c r="H162" t="n">
-        <v>8.011904593639573</v>
+        <v>8.01372881355932</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -13602,16 +13602,16 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>0.3119045936395723</v>
+        <v>0.3137288135593197</v>
       </c>
       <c r="N162" t="n">
-        <v>0.3119045936395723</v>
+        <v>0.3137288135593197</v>
       </c>
       <c r="O162" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P162" t="n">
-        <v>-0.2266113074204981</v>
+        <v>-0.2289265536723164</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -13651,10 +13651,10 @@
         <v>8</v>
       </c>
       <c r="G163" t="n">
-        <v>0.8445229681978799</v>
+        <v>0.844632768361582</v>
       </c>
       <c r="H163" t="n">
-        <v>7.950503533568905</v>
+        <v>7.950974576271187</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -13673,16 +13673,16 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>0.3105035335689053</v>
+        <v>0.3109745762711871</v>
       </c>
       <c r="N163" t="n">
-        <v>0.3105035335689053</v>
+        <v>0.3109745762711871</v>
       </c>
       <c r="O163" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P163" t="n">
-        <v>-0.06140106007066759</v>
+        <v>-0.06275423728813312</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -13722,10 +13722,10 @@
         <v>8</v>
       </c>
       <c r="G164" t="n">
-        <v>0.8381625441696113</v>
+        <v>0.838276836158192</v>
       </c>
       <c r="H164" t="n">
-        <v>7.843224381625442</v>
+        <v>7.844858757062146</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -13744,16 +13744,16 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>0.2832243816254421</v>
+        <v>0.2848587570621461</v>
       </c>
       <c r="N164" t="n">
-        <v>0.2832243816254421</v>
+        <v>0.2848587570621461</v>
       </c>
       <c r="O164" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P164" t="n">
-        <v>-0.1072791519434633</v>
+        <v>-0.106115819209041</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -13793,10 +13793,10 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>0.8353356890459364</v>
+        <v>0.83545197740113</v>
       </c>
       <c r="H165" t="n">
-        <v>7.829530035335689</v>
+        <v>7.829696327683616</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -13815,16 +13815,16 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>0.3495300353356887</v>
+        <v>0.3496963276836151</v>
       </c>
       <c r="N165" t="n">
-        <v>0.3495300353356887</v>
+        <v>0.3496963276836151</v>
       </c>
       <c r="O165" t="n">
         <v>-0.07999999999999918</v>
       </c>
       <c r="P165" t="n">
-        <v>-0.01369434628975252</v>
+        <v>-0.01516242937853018</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -13864,10 +13864,10 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>0.8268551236749117</v>
+        <v>0.8269774011299436</v>
       </c>
       <c r="H166" t="n">
-        <v>7.75672261484099</v>
+        <v>7.757888418079096</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -13886,16 +13886,16 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>0.3867226148409895</v>
+        <v>0.387888418079096</v>
       </c>
       <c r="N166" t="n">
-        <v>0.3867226148409895</v>
+        <v>0.387888418079096</v>
       </c>
       <c r="O166" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P166" t="n">
-        <v>-0.07280742049469957</v>
+        <v>-0.07180790960451944</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -15065,10 +15065,10 @@
         <v>8</v>
       </c>
       <c r="G183" t="n">
-        <v>0.8007067137809187</v>
+        <v>0.8001412429378532</v>
       </c>
       <c r="H183" t="n">
-        <v>5.551537102473499</v>
+        <v>5.551307379943503</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -15087,16 +15087,16 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>0.3365371024734989</v>
+        <v>0.336307379943503</v>
       </c>
       <c r="N183" t="n">
-        <v>0.3365371024734989</v>
+        <v>0.336307379943503</v>
       </c>
       <c r="O183" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P183" t="n">
-        <v>-0.09254313578859019</v>
+        <v>-0.09277285831858606</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -15136,10 +15136,10 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>0.8537102473498234</v>
+        <v>0.8538135593220338</v>
       </c>
       <c r="H184" t="n">
-        <v>5.759558303886926</v>
+        <v>5.75989406779661</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -15158,16 +15158,16 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>0.5945583038869264</v>
+        <v>0.5948940677966101</v>
       </c>
       <c r="N184" t="n">
-        <v>0.5945583038869264</v>
+        <v>0.5948940677966101</v>
       </c>
       <c r="O184" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P184" t="n">
-        <v>0.2080212014134277</v>
+        <v>0.2085866878531073</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -15207,10 +15207,10 @@
         <v>8</v>
       </c>
       <c r="G185" t="n">
-        <v>0.8678445229681979</v>
+        <v>0.8679378531073446</v>
       </c>
       <c r="H185" t="n">
-        <v>5.800123674911661</v>
+        <v>5.800199505649718</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -15229,16 +15229,16 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>0.6801236749116608</v>
+        <v>0.6801995056497177</v>
       </c>
       <c r="N185" t="n">
-        <v>0.6801236749116608</v>
+        <v>0.6801995056497177</v>
       </c>
       <c r="O185" t="n">
         <v>-0.04499999999999993</v>
       </c>
       <c r="P185" t="n">
-        <v>0.04056537102473445</v>
+        <v>0.04030543785310758</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -15278,10 +15278,10 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>0.8650176678445229</v>
+        <v>0.8651129943502824</v>
       </c>
       <c r="H186" t="n">
-        <v>5.786961130742049</v>
+        <v>5.787425847457627</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -15300,16 +15300,16 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>0.7069611307420489</v>
+        <v>0.7074258474576265</v>
       </c>
       <c r="N186" t="n">
-        <v>0.7069611307420489</v>
+        <v>0.7074258474576265</v>
       </c>
       <c r="O186" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P186" t="n">
-        <v>-0.01316254416961193</v>
+        <v>-0.0127736581920912</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -15349,10 +15349,10 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8438162544169612</v>
+        <v>0.8439265536723164</v>
       </c>
       <c r="H187" t="n">
-        <v>5.683701413427562</v>
+        <v>5.683880649717514</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -15371,16 +15371,16 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>0.2537014134275619</v>
+        <v>0.2538806497175141</v>
       </c>
       <c r="N187" t="n">
-        <v>0.2537014134275619</v>
+        <v>0.2538806497175141</v>
       </c>
       <c r="O187" t="n">
         <v>0.3499999999999996</v>
       </c>
       <c r="P187" t="n">
-        <v>-0.1032597173144874</v>
+        <v>-0.1035451977401127</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -15420,10 +15420,10 @@
         <v>8</v>
       </c>
       <c r="G188" t="n">
-        <v>0.7964664310954064</v>
+        <v>0.7959039548022598</v>
       </c>
       <c r="H188" t="n">
-        <v>5.545918727915194</v>
+        <v>5.540891596045197</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -15442,16 +15442,16 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.05658127208480579</v>
+        <v>-0.06160840395480349</v>
       </c>
       <c r="N188" t="n">
-        <v>0.05658127208480579</v>
+        <v>0.06160840395480349</v>
       </c>
       <c r="O188" t="n">
         <v>0.1725000000000003</v>
       </c>
       <c r="P188" t="n">
-        <v>-0.1377826855123674</v>
+        <v>-0.1429890536723173</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -15491,10 +15491,10 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>0.7491166077738516</v>
+        <v>0.748587570621469</v>
       </c>
       <c r="H189" t="n">
-        <v>5.390229681978799</v>
+        <v>5.385501412429379</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -15513,16 +15513,16 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.1597703180212005</v>
+        <v>-0.1644985875706206</v>
       </c>
       <c r="N189" t="n">
-        <v>0.1597703180212005</v>
+        <v>0.1644985875706206</v>
       </c>
       <c r="O189" t="n">
         <v>-0.05250000000000021</v>
       </c>
       <c r="P189" t="n">
-        <v>-0.1556890459363949</v>
+        <v>-0.1553901836158174</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -15562,10 +15562,10 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>0.7208480565371025</v>
+        <v>0.7203389830508474</v>
       </c>
       <c r="H190" t="n">
-        <v>5.280689045936396</v>
+        <v>5.280275423728813</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -15584,16 +15584,16 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>0.0006890459363955159</v>
+        <v>0.0002754237288131733</v>
       </c>
       <c r="N190" t="n">
-        <v>0.0006890459363955159</v>
+        <v>0.0002754237288131733</v>
       </c>
       <c r="O190" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P190" t="n">
-        <v>-0.1095406360424036</v>
+        <v>-0.1052259887005658</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -15633,10 +15633,10 @@
         <v>8</v>
       </c>
       <c r="G191" t="n">
-        <v>0.7159010600706713</v>
+        <v>0.7153954802259888</v>
       </c>
       <c r="H191" t="n">
-        <v>5.27833480565371</v>
+        <v>5.278129413841808</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -15655,16 +15655,16 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>0.2533348056537115</v>
+        <v>0.2531294138418092</v>
       </c>
       <c r="N191" t="n">
-        <v>0.2533348056537115</v>
+        <v>0.2531294138418092</v>
       </c>
       <c r="O191" t="n">
         <v>-0.2550000000000017</v>
       </c>
       <c r="P191" t="n">
-        <v>-0.002354240282685716</v>
+        <v>-0.00214600988700564</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -15704,10 +15704,10 @@
         <v>8</v>
       </c>
       <c r="G192" t="n">
-        <v>0.7243816254416962</v>
+        <v>0.7238700564971752</v>
       </c>
       <c r="H192" t="n">
-        <v>5.288860424028269</v>
+        <v>5.286366525423729</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -15726,16 +15726,16 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>0.4388604240282694</v>
+        <v>0.436366525423729</v>
       </c>
       <c r="N192" t="n">
-        <v>0.4388604240282694</v>
+        <v>0.436366525423729</v>
       </c>
       <c r="O192" t="n">
         <v>-0.1749999999999989</v>
       </c>
       <c r="P192" t="n">
-        <v>0.01052561837455901</v>
+        <v>0.008237111581920864</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -15775,10 +15775,10 @@
         <v>8</v>
       </c>
       <c r="G193" t="n">
-        <v>0.7314487632508834</v>
+        <v>0.7309322033898306</v>
       </c>
       <c r="H193" t="n">
-        <v>5.32703180212014</v>
+        <v>5.320736228813559</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -15797,16 +15797,16 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>0.7570318021201397</v>
+        <v>0.7507362288135591</v>
       </c>
       <c r="N193" t="n">
-        <v>0.7570318021201397</v>
+        <v>0.7507362288135591</v>
       </c>
       <c r="O193" t="n">
         <v>-0.2799999999999994</v>
       </c>
       <c r="P193" t="n">
-        <v>0.03817137809187088</v>
+        <v>0.0343697033898307</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -15846,10 +15846,10 @@
         <v>8</v>
       </c>
       <c r="G194" t="n">
-        <v>0.72226148409894</v>
+        <v>0.7217514124293786</v>
       </c>
       <c r="H194" t="n">
-        <v>5.281837455830389</v>
+        <v>5.28142302259887</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15868,16 +15868,16 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>0.8518374558303892</v>
+        <v>0.8514230225988699</v>
       </c>
       <c r="N194" t="n">
-        <v>0.8518374558303892</v>
+        <v>0.8514230225988699</v>
       </c>
       <c r="O194" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P194" t="n">
-        <v>-0.04519434628975105</v>
+        <v>-0.0393132062146897</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -15917,10 +15917,10 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>0.6946996466431096</v>
+        <v>0.6942090395480226</v>
       </c>
       <c r="H195" t="n">
-        <v>5.213886925795054</v>
+        <v>5.213089689265537</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -15939,16 +15939,16 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>0.7338869257950531</v>
+        <v>0.7330896892655367</v>
       </c>
       <c r="N195" t="n">
-        <v>0.7338869257950531</v>
+        <v>0.7330896892655367</v>
       </c>
       <c r="O195" t="n">
         <v>0.05000000000000071</v>
       </c>
       <c r="P195" t="n">
-        <v>-0.06795053003533535</v>
+        <v>-0.06833333333333247</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -15988,10 +15988,10 @@
         <v>8</v>
       </c>
       <c r="G196" t="n">
-        <v>0.6558303886925795</v>
+        <v>0.655367231638418</v>
       </c>
       <c r="H196" t="n">
-        <v>5.121448763250884</v>
+        <v>5.119844632768362</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -16010,16 +16010,16 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>0.3314487632508838</v>
+        <v>0.3298446327683617</v>
       </c>
       <c r="N196" t="n">
-        <v>0.3314487632508838</v>
+        <v>0.3298446327683617</v>
       </c>
       <c r="O196" t="n">
         <v>0.3099999999999996</v>
       </c>
       <c r="P196" t="n">
-        <v>-0.0924381625441697</v>
+        <v>-0.0932450564971754</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -17189,10 +17189,10 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>0.7561837455830389</v>
+        <v>0.7563559322033898</v>
       </c>
       <c r="H213" t="n">
-        <v>5.97</v>
+        <v>5.970000000000001</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -17211,16 +17211,16 @@
         <v>1</v>
       </c>
       <c r="M213" t="n">
-        <v>-2.767500000000001</v>
+        <v>-2.7675</v>
       </c>
       <c r="N213" t="n">
-        <v>2.767500000000001</v>
+        <v>2.7675</v>
       </c>
       <c r="O213" t="n">
         <v>-0.125</v>
       </c>
       <c r="P213" t="n">
-        <v>-1.394953573931325</v>
+        <v>-1.394953573931324</v>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
@@ -17260,10 +17260,10 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>0.7554770318021201</v>
+        <v>0.7556497175141242</v>
       </c>
       <c r="H214" t="n">
-        <v>5.969711425206125</v>
+        <v>5.96993879472693</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -17282,16 +17282,16 @@
         <v>1</v>
       </c>
       <c r="M214" t="n">
-        <v>-2.617788574793874</v>
+        <v>-2.617561205273069</v>
       </c>
       <c r="N214" t="n">
-        <v>2.617788574793874</v>
+        <v>2.617561205273069</v>
       </c>
       <c r="O214" t="n">
         <v>-0.1500000000000021</v>
       </c>
       <c r="P214" t="n">
-        <v>-0.0002885747938750072</v>
+        <v>-6.120527307107437e-05</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>0.7660777385159011</v>
+        <v>0.7662429378531074</v>
       </c>
       <c r="H215" t="n">
-        <v>6.011510600706714</v>
+        <v>6.012489406779661</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -17353,16 +17353,16 @@
         <v>1</v>
       </c>
       <c r="M215" t="n">
-        <v>-2.468489399293286</v>
+        <v>-2.467510593220339</v>
       </c>
       <c r="N215" t="n">
-        <v>2.468489399293286</v>
+        <v>2.467510593220339</v>
       </c>
       <c r="O215" t="n">
         <v>-0.1074999999999982</v>
       </c>
       <c r="P215" t="n">
-        <v>0.04179917550058931</v>
+        <v>0.04255061205273147</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -17402,10 +17402,10 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>0.7865724381625442</v>
+        <v>0.786723163841808</v>
       </c>
       <c r="H216" t="n">
-        <v>6.103922261484099</v>
+        <v>6.105112994350283</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -17424,16 +17424,16 @@
         <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>-2.106077738515902</v>
+        <v>-2.104887005649718</v>
       </c>
       <c r="N216" t="n">
-        <v>2.106077738515902</v>
+        <v>2.104887005649718</v>
       </c>
       <c r="O216" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P216" t="n">
-        <v>0.09241166077738505</v>
+        <v>0.09262358757062206</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -17473,10 +17473,10 @@
         <v>8</v>
       </c>
       <c r="G217" t="n">
-        <v>0.8091872791519434</v>
+        <v>0.809322033898305</v>
       </c>
       <c r="H217" t="n">
-        <v>6.202579505300354</v>
+        <v>6.20364406779661</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -17495,16 +17495,16 @@
         <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>-1.957420494699647</v>
+        <v>-1.95635593220339</v>
       </c>
       <c r="N217" t="n">
-        <v>1.957420494699647</v>
+        <v>1.95635593220339</v>
       </c>
       <c r="O217" t="n">
         <v>-0.05000000000000071</v>
       </c>
       <c r="P217" t="n">
-        <v>0.09865724381625451</v>
+        <v>0.09853107344632672</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -17544,10 +17544,10 @@
         <v>8</v>
       </c>
       <c r="G218" t="n">
-        <v>0.8275618374558303</v>
+        <v>0.827683615819209</v>
       </c>
       <c r="H218" t="n">
-        <v>6.295159010600707</v>
+        <v>6.295800376647835</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -17566,16 +17566,16 @@
         <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>-1.634840989399293</v>
+        <v>-1.634199623352165</v>
       </c>
       <c r="N218" t="n">
-        <v>1.634840989399293</v>
+        <v>1.634199623352165</v>
       </c>
       <c r="O218" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P218" t="n">
-        <v>0.0925795053003533</v>
+        <v>0.09215630885122472</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -17615,10 +17615,10 @@
         <v>8</v>
       </c>
       <c r="G219" t="n">
-        <v>0.8445229681978799</v>
+        <v>0.844632768361582</v>
       </c>
       <c r="H219" t="n">
-        <v>6.385432862190813</v>
+        <v>6.385649717514124</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -17637,16 +17637,16 @@
         <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>-1.604567137809187</v>
+        <v>-1.604350282485876</v>
       </c>
       <c r="N219" t="n">
-        <v>1.604567137809187</v>
+        <v>1.604350282485876</v>
       </c>
       <c r="O219" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P219" t="n">
-        <v>0.09027385159010581</v>
+        <v>0.08984934086628993</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -17686,10 +17686,10 @@
         <v>8</v>
       </c>
       <c r="G220" t="n">
-        <v>0.8515901060070671</v>
+        <v>0.8516949152542372</v>
       </c>
       <c r="H220" t="n">
-        <v>6.45268551236749</v>
+        <v>6.455169491525423</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -17708,16 +17708,16 @@
         <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>-1.53731448763251</v>
+        <v>-1.534830508474577</v>
       </c>
       <c r="N220" t="n">
-        <v>1.53731448763251</v>
+        <v>1.534830508474577</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
       </c>
       <c r="P220" t="n">
-        <v>0.0672526501766777</v>
+        <v>0.06951977401129827</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -17757,10 +17757,10 @@
         <v>8</v>
       </c>
       <c r="G221" t="n">
-        <v>0.8424028268551237</v>
+        <v>0.8425141242937854</v>
       </c>
       <c r="H221" t="n">
-        <v>6.381245583038869</v>
+        <v>6.381465395480226</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -17779,16 +17779,16 @@
         <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>-1.47625441696113</v>
+        <v>-1.476034604519774</v>
       </c>
       <c r="N221" t="n">
-        <v>1.47625441696113</v>
+        <v>1.476034604519774</v>
       </c>
       <c r="O221" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P221" t="n">
-        <v>-0.07143992932862098</v>
+        <v>-0.0737040960451969</v>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
@@ -17828,10 +17828,10 @@
         <v>8</v>
       </c>
       <c r="G222" t="n">
-        <v>0.8226148409893993</v>
+        <v>0.8227401129943502</v>
       </c>
       <c r="H222" t="n">
-        <v>6.249552414605418</v>
+        <v>6.249882297551789</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -17850,16 +17850,16 @@
         <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>-1.490447585394582</v>
+        <v>-1.490117702448211</v>
       </c>
       <c r="N222" t="n">
-        <v>1.490447585394582</v>
+        <v>1.490117702448211</v>
       </c>
       <c r="O222" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.1316931684334515</v>
+        <v>-0.1315830979284369</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -17899,10 +17899,10 @@
         <v>8</v>
       </c>
       <c r="G223" t="n">
-        <v>0.8049469964664311</v>
+        <v>0.8050847457627118</v>
       </c>
       <c r="H223" t="n">
-        <v>6.179693757361601</v>
+        <v>6.180112994350282</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -17921,16 +17921,16 @@
         <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>-1.440306242638399</v>
+        <v>-1.439887005649718</v>
       </c>
       <c r="N223" t="n">
-        <v>1.440306242638399</v>
+        <v>1.439887005649718</v>
       </c>
       <c r="O223" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.06985865724381668</v>
+        <v>-0.06976930320150654</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -17970,10 +17970,10 @@
         <v>8</v>
       </c>
       <c r="G224" t="n">
-        <v>0.7802120141342757</v>
+        <v>0.780367231638418</v>
       </c>
       <c r="H224" t="n">
-        <v>6.076709363957597</v>
+        <v>6.076862641242937</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -17992,16 +17992,16 @@
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>-1.323290636042404</v>
+        <v>-1.323137358757063</v>
       </c>
       <c r="N224" t="n">
-        <v>1.323290636042404</v>
+        <v>1.323137358757063</v>
       </c>
       <c r="O224" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.1029843934040047</v>
+        <v>-0.1032503531073452</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -18041,10 +18041,10 @@
         <v>8</v>
       </c>
       <c r="G225" t="n">
-        <v>0.7526501766784452</v>
+        <v>0.7528248587570622</v>
       </c>
       <c r="H225" t="n">
-        <v>5.965989399293286</v>
+        <v>5.966219397363465</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -18063,16 +18063,16 @@
         <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>-1.394010600706714</v>
+        <v>-1.393780602636535</v>
       </c>
       <c r="N225" t="n">
-        <v>1.394010600706714</v>
+        <v>1.393780602636535</v>
       </c>
       <c r="O225" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.1107199646643107</v>
+        <v>-0.1106432438794718</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>8</v>
       </c>
       <c r="G226" t="n">
-        <v>0.7279151943462897</v>
+        <v>0.7281073446327684</v>
       </c>
       <c r="H226" t="n">
-        <v>5.830530035335689</v>
+        <v>5.832048022598871</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -18134,16 +18134,16 @@
         <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>-1.549469964664311</v>
+        <v>-1.547951977401129</v>
       </c>
       <c r="N226" t="n">
-        <v>1.549469964664311</v>
+        <v>1.547951977401129</v>
       </c>
       <c r="O226" t="n">
         <v>0.01999999999999957</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.1354593639575974</v>
+        <v>-0.1341713747645947</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -19313,10 +19313,10 @@
         <v>8</v>
       </c>
       <c r="G243" t="n">
-        <v>0.8289752650176678</v>
+        <v>0.8290960451977402</v>
       </c>
       <c r="H243" t="n">
-        <v>5.570818021201411</v>
+        <v>5.573220338983051</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -19335,16 +19335,16 @@
         <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>1.580818021201411</v>
+        <v>1.58322033898305</v>
       </c>
       <c r="N243" t="n">
-        <v>1.580818021201411</v>
+        <v>1.58322033898305</v>
       </c>
       <c r="O243" t="n">
         <v>-0.1624999999999996</v>
       </c>
       <c r="P243" t="n">
-        <v>-1.590099988609381</v>
+        <v>-1.587697670827741</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -19384,10 +19384,10 @@
         <v>8</v>
       </c>
       <c r="G244" t="n">
-        <v>0.7053003533568905</v>
+        <v>0.7048022598870056</v>
       </c>
       <c r="H244" t="n">
-        <v>4.933219081272084</v>
+        <v>4.931694915254237</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -19406,16 +19406,16 @@
         <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>1.110719081272085</v>
+        <v>1.109194915254237</v>
       </c>
       <c r="N244" t="n">
-        <v>1.110719081272085</v>
+        <v>1.109194915254237</v>
       </c>
       <c r="O244" t="n">
         <v>-0.1675000000000004</v>
       </c>
       <c r="P244" t="n">
-        <v>-0.6375989399293269</v>
+        <v>-0.6415254237288135</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -19455,10 +19455,10 @@
         <v>8</v>
       </c>
       <c r="G245" t="n">
-        <v>0.6162544169611307</v>
+        <v>0.615819209039548</v>
       </c>
       <c r="H245" t="n">
-        <v>4.631079505300353</v>
+        <v>4.630635593220339</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -19477,16 +19477,16 @@
         <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>0.8510795053003535</v>
+        <v>0.8506355932203395</v>
       </c>
       <c r="N245" t="n">
-        <v>0.8510795053003535</v>
+        <v>0.8506355932203395</v>
       </c>
       <c r="O245" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.3021395759717311</v>
+        <v>-0.3010593220338977</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -19526,10 +19526,10 @@
         <v>8</v>
       </c>
       <c r="G246" t="n">
-        <v>0.5943462897526501</v>
+        <v>0.5939265536723164</v>
       </c>
       <c r="H246" t="n">
-        <v>4.569832155477031</v>
+        <v>4.565550847457628</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -19548,16 +19548,16 @@
         <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>0.889832155477031</v>
+        <v>0.8855508474576275</v>
       </c>
       <c r="N246" t="n">
-        <v>0.889832155477031</v>
+        <v>0.8855508474576275</v>
       </c>
       <c r="O246" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.06124734982332214</v>
+        <v>-0.06508474576271173</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -19597,10 +19597,10 @@
         <v>8</v>
       </c>
       <c r="G247" t="n">
-        <v>0.6346289752650177</v>
+        <v>0.634180790960452</v>
       </c>
       <c r="H247" t="n">
-        <v>4.724464664310954</v>
+        <v>4.723093220338983</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -19619,16 +19619,16 @@
         <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>1.144464664310954</v>
+        <v>1.143093220338983</v>
       </c>
       <c r="N247" t="n">
-        <v>1.144464664310954</v>
+        <v>1.143093220338983</v>
       </c>
       <c r="O247" t="n">
         <v>-0.1000000000000001</v>
       </c>
       <c r="P247" t="n">
-        <v>0.1546325088339229</v>
+        <v>0.1575423728813554</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -19668,10 +19668,10 @@
         <v>8</v>
       </c>
       <c r="G248" t="n">
-        <v>0.6473498233215548</v>
+        <v>0.6468926553672316</v>
       </c>
       <c r="H248" t="n">
-        <v>4.760593639575972</v>
+        <v>4.759830508474576</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19690,16 +19690,16 @@
         <v>1</v>
       </c>
       <c r="M248" t="n">
-        <v>1.368093639575972</v>
+        <v>1.367330508474576</v>
       </c>
       <c r="N248" t="n">
-        <v>1.368093639575972</v>
+        <v>1.367330508474576</v>
       </c>
       <c r="O248" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P248" t="n">
-        <v>0.03612897526501779</v>
+        <v>0.03673728813559318</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -19739,10 +19739,10 @@
         <v>8</v>
       </c>
       <c r="G249" t="n">
-        <v>0.5971731448763251</v>
+        <v>0.5967514124293786</v>
       </c>
       <c r="H249" t="n">
-        <v>4.598666077738517</v>
+        <v>4.594364406779661</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19761,16 +19761,16 @@
         <v>1</v>
       </c>
       <c r="M249" t="n">
-        <v>1.318666077738517</v>
+        <v>1.314364406779661</v>
       </c>
       <c r="N249" t="n">
-        <v>1.318666077738517</v>
+        <v>1.314364406779661</v>
       </c>
       <c r="O249" t="n">
         <v>-0.1125000000000003</v>
       </c>
       <c r="P249" t="n">
-        <v>-0.1619275618374552</v>
+        <v>-0.165466101694915</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -19810,10 +19810,10 @@
         <v>8</v>
       </c>
       <c r="G250" t="n">
-        <v>0.4904593639575971</v>
+        <v>0.4901129943502825</v>
       </c>
       <c r="H250" t="n">
-        <v>4.149111307420495</v>
+        <v>4.147161016949153</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19832,16 +19832,16 @@
         <v>1</v>
       </c>
       <c r="M250" t="n">
-        <v>0.9991113074204949</v>
+        <v>0.9971610169491529</v>
       </c>
       <c r="N250" t="n">
-        <v>0.9991113074204949</v>
+        <v>0.9971610169491529</v>
       </c>
       <c r="O250" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P250" t="n">
-        <v>-0.4495547703180218</v>
+        <v>-0.4472033898305083</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -19881,10 +19881,10 @@
         <v>8</v>
       </c>
       <c r="G251" t="n">
-        <v>0.3908127208480565</v>
+        <v>0.3905367231638418</v>
       </c>
       <c r="H251" t="n">
-        <v>3.803386925795053</v>
+        <v>3.802542372881356</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19903,16 +19903,16 @@
         <v>1</v>
       </c>
       <c r="M251" t="n">
-        <v>0.8583869257950534</v>
+        <v>0.857542372881356</v>
       </c>
       <c r="N251" t="n">
-        <v>0.8583869257950534</v>
+        <v>0.857542372881356</v>
       </c>
       <c r="O251" t="n">
         <v>-0.2050000000000001</v>
       </c>
       <c r="P251" t="n">
-        <v>-0.3457243816254416</v>
+        <v>-0.344618644067797</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         <v>8</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3363957597173145</v>
+        <v>0.3361581920903955</v>
       </c>
       <c r="H252" t="n">
-        <v>3.640412249705536</v>
+        <v>3.639604519774011</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19974,16 +19974,16 @@
         <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>0.8004122497055359</v>
+        <v>0.7996045197740114</v>
       </c>
       <c r="N252" t="n">
-        <v>0.8004122497055359</v>
+        <v>0.7996045197740114</v>
       </c>
       <c r="O252" t="n">
         <v>-0.105</v>
       </c>
       <c r="P252" t="n">
-        <v>-0.1629746760895174</v>
+        <v>-0.1629378531073447</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -20023,10 +20023,10 @@
         <v>8</v>
       </c>
       <c r="G253" t="n">
-        <v>0.3469964664310954</v>
+        <v>0.3467514124293785</v>
       </c>
       <c r="H253" t="n">
-        <v>3.676454652532391</v>
+        <v>3.675621468926554</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -20045,16 +20045,16 @@
         <v>1</v>
       </c>
       <c r="M253" t="n">
-        <v>0.9064546525323913</v>
+        <v>0.9056214689265536</v>
       </c>
       <c r="N253" t="n">
-        <v>0.9064546525323913</v>
+        <v>0.9056214689265536</v>
       </c>
       <c r="O253" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P253" t="n">
-        <v>0.03604240282685556</v>
+        <v>0.03601694915254239</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -20094,10 +20094,10 @@
         <v>8</v>
       </c>
       <c r="G254" t="n">
-        <v>0.4946996466431096</v>
+        <v>0.4943502824858757</v>
       </c>
       <c r="H254" t="n">
-        <v>4.17506183745583</v>
+        <v>4.17292372881356</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -20116,16 +20116,16 @@
         <v>1</v>
       </c>
       <c r="M254" t="n">
-        <v>1.355061837455831</v>
+        <v>1.35292372881356</v>
       </c>
       <c r="N254" t="n">
-        <v>1.355061837455831</v>
+        <v>1.35292372881356</v>
       </c>
       <c r="O254" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P254" t="n">
-        <v>0.498607184923439</v>
+        <v>0.497302259887006</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -20165,10 +20165,10 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>0.6968197879858657</v>
+        <v>0.6963276836158192</v>
       </c>
       <c r="H255" t="n">
-        <v>4.90726855123675</v>
+        <v>4.905762711864407</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -20187,16 +20187,16 @@
         <v>1</v>
       </c>
       <c r="M255" t="n">
-        <v>2.15726855123675</v>
+        <v>2.155762711864407</v>
       </c>
       <c r="N255" t="n">
-        <v>2.15726855123675</v>
+        <v>2.155762711864407</v>
       </c>
       <c r="O255" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P255" t="n">
-        <v>0.7322067137809194</v>
+        <v>0.732838983050847</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
@@ -20236,10 +20236,10 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>0.7886925795053004</v>
+        <v>0.7888418079096046</v>
       </c>
       <c r="H256" t="n">
-        <v>5.20743109540636</v>
+        <v>5.208877118644067</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -20258,16 +20258,16 @@
         <v>1</v>
       </c>
       <c r="M256" t="n">
-        <v>2.45743109540636</v>
+        <v>2.458877118644067</v>
       </c>
       <c r="N256" t="n">
-        <v>2.45743109540636</v>
+        <v>2.458877118644067</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
       </c>
       <c r="P256" t="n">
-        <v>0.3001625441696101</v>
+        <v>0.3031144067796605</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -21437,10 +21437,10 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>0.942756183745583</v>
+        <v>0.9427966101694916</v>
       </c>
       <c r="H273" t="n">
-        <v>6.913727915194347</v>
+        <v>6.913951271186441</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -21459,16 +21459,16 @@
         <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>-0.851272084805653</v>
+        <v>-0.8510487288135584</v>
       </c>
       <c r="N273" t="n">
-        <v>0.851272084805653</v>
+        <v>0.8510487288135584</v>
       </c>
       <c r="O273" t="n">
         <v>0.0550000000000006</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.97720644593623</v>
+        <v>-0.9769830899441354</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -21508,10 +21508,10 @@
         <v>8</v>
       </c>
       <c r="G274" t="n">
-        <v>0.9392226148409893</v>
+        <v>0.9392655367231638</v>
       </c>
       <c r="H274" t="n">
-        <v>6.849204946996466</v>
+        <v>6.849442090395479</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -21530,16 +21530,16 @@
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>-0.9307950530035347</v>
+        <v>-0.9305579096045209</v>
       </c>
       <c r="N274" t="n">
-        <v>0.9307950530035347</v>
+        <v>0.9305579096045209</v>
       </c>
       <c r="O274" t="n">
         <v>0.01500000000000057</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.06452296819788117</v>
+        <v>-0.06450918079096191</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -21579,10 +21579,10 @@
         <v>8</v>
       </c>
       <c r="G275" t="n">
-        <v>0.9356890459363958</v>
+        <v>0.9357344632768362</v>
       </c>
       <c r="H275" t="n">
-        <v>6.829840989399293</v>
+        <v>6.82996645480226</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -21601,16 +21601,16 @@
         <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>-0.9401590106007065</v>
+        <v>-0.94003354519774</v>
       </c>
       <c r="N275" t="n">
-        <v>0.9401590106007065</v>
+        <v>0.94003354519774</v>
       </c>
       <c r="O275" t="n">
         <v>-0.01000000000000068</v>
       </c>
       <c r="P275" t="n">
-        <v>-0.01936395759717247</v>
+        <v>-0.01947563559321974</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -21650,10 +21650,10 @@
         <v>8</v>
       </c>
       <c r="G276" t="n">
-        <v>0.9321554770318021</v>
+        <v>0.9322033898305084</v>
       </c>
       <c r="H276" t="n">
-        <v>6.820079505300353</v>
+        <v>6.82021186440678</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -21672,16 +21672,16 @@
         <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>-0.8799204946996468</v>
+        <v>-0.8797881355932207</v>
       </c>
       <c r="N276" t="n">
-        <v>0.8799204946996468</v>
+        <v>0.8797881355932207</v>
       </c>
       <c r="O276" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P276" t="n">
-        <v>-0.009761484098939732</v>
+        <v>-0.009754590395480101</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -21721,10 +21721,10 @@
         <v>8</v>
       </c>
       <c r="G277" t="n">
-        <v>0.9286219081272085</v>
+        <v>0.9286723163841808</v>
       </c>
       <c r="H277" t="n">
-        <v>6.780636042402826</v>
+        <v>6.780914548022599</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -21743,16 +21743,16 @@
         <v>1</v>
       </c>
       <c r="M277" t="n">
-        <v>-0.8093639575971734</v>
+        <v>-0.8090854519774009</v>
       </c>
       <c r="N277" t="n">
-        <v>0.8093639575971734</v>
+        <v>0.8090854519774009</v>
       </c>
       <c r="O277" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P277" t="n">
-        <v>-0.03944346289752687</v>
+        <v>-0.03929731638418055</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -21792,10 +21792,10 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>0.9250883392226148</v>
+        <v>0.9251412429378532</v>
       </c>
       <c r="H278" t="n">
-        <v>6.751113074204946</v>
+        <v>6.751405367231638</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -21814,16 +21814,16 @@
         <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>-0.6988869257950538</v>
+        <v>-0.6985946327683621</v>
       </c>
       <c r="N278" t="n">
-        <v>0.6988869257950538</v>
+        <v>0.6985946327683621</v>
       </c>
       <c r="O278" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P278" t="n">
-        <v>-0.02952296819788014</v>
+        <v>-0.02950918079096088</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -21863,10 +21863,10 @@
         <v>8</v>
       </c>
       <c r="G279" t="n">
-        <v>0.9215547703180212</v>
+        <v>0.9216101694915254</v>
       </c>
       <c r="H279" t="n">
-        <v>6.714393404004712</v>
+        <v>6.714597457627119</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -21885,16 +21885,16 @@
         <v>1</v>
       </c>
       <c r="M279" t="n">
-        <v>-0.6556065959952884</v>
+        <v>-0.6554025423728813</v>
       </c>
       <c r="N279" t="n">
-        <v>0.6556065959952884</v>
+        <v>0.6554025423728813</v>
       </c>
       <c r="O279" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P279" t="n">
-        <v>-0.03671967020023459</v>
+        <v>-0.0368079096045193</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -21934,10 +21934,10 @@
         <v>8</v>
       </c>
       <c r="G280" t="n">
-        <v>0.9180212014134276</v>
+        <v>0.9180790960451978</v>
       </c>
       <c r="H280" t="n">
-        <v>6.678268551236751</v>
+        <v>6.679548022598872</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -21956,16 +21956,16 @@
         <v>1</v>
       </c>
       <c r="M280" t="n">
-        <v>-0.591731448763249</v>
+        <v>-0.5904519774011279</v>
       </c>
       <c r="N280" t="n">
-        <v>0.591731448763249</v>
+        <v>0.5904519774011279</v>
       </c>
       <c r="O280" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P280" t="n">
-        <v>-0.03612485276796118</v>
+        <v>-0.03504943502824709</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -22005,10 +22005,10 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>0.9144876325088339</v>
+        <v>0.91454802259887</v>
       </c>
       <c r="H281" t="n">
-        <v>6.625088339222615</v>
+        <v>6.625755649717514</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -22027,16 +22027,16 @@
         <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>-0.6349116607773846</v>
+        <v>-0.6342443502824855</v>
       </c>
       <c r="N281" t="n">
-        <v>0.6349116607773846</v>
+        <v>0.6342443502824855</v>
       </c>
       <c r="O281" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P281" t="n">
-        <v>-0.05318021201413536</v>
+        <v>-0.05379237288135741</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -22076,10 +22076,10 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>0.9109540636042402</v>
+        <v>0.9110169491525424</v>
       </c>
       <c r="H282" t="n">
-        <v>6.548021201413428</v>
+        <v>6.548368644067796</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -22098,16 +22098,16 @@
         <v>1</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.5619787985865727</v>
+        <v>-0.5616313559322039</v>
       </c>
       <c r="N282" t="n">
-        <v>0.5619787985865727</v>
+        <v>0.5616313559322039</v>
       </c>
       <c r="O282" t="n">
         <v>-0.1499999999999995</v>
       </c>
       <c r="P282" t="n">
-        <v>-0.07706713780918761</v>
+        <v>-0.0773870056497179</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -22147,10 +22147,10 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>0.9074204946996467</v>
+        <v>0.9074858757062146</v>
       </c>
       <c r="H283" t="n">
-        <v>6.513992932862192</v>
+        <v>6.515437853107343</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -22169,16 +22169,16 @@
         <v>1</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.4960070671378078</v>
+        <v>-0.4945621468926564</v>
       </c>
       <c r="N283" t="n">
-        <v>0.4960070671378078</v>
+        <v>0.4945621468926564</v>
       </c>
       <c r="O283" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P283" t="n">
-        <v>-0.03402826855123564</v>
+        <v>-0.03293079096045304</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -22218,10 +22218,10 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>0.9053003533568904</v>
+        <v>0.905367231638418</v>
       </c>
       <c r="H284" t="n">
-        <v>6.441413427561834</v>
+        <v>6.445847457627115</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -22240,16 +22240,16 @@
         <v>1</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.3785865724381665</v>
+        <v>-0.3741525423728849</v>
       </c>
       <c r="N284" t="n">
-        <v>0.3785865724381665</v>
+        <v>0.3741525423728849</v>
       </c>
       <c r="O284" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P284" t="n">
-        <v>-0.07257950530035817</v>
+        <v>-0.06959039548022794</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -22289,10 +22289,10 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>0.9017667844522969</v>
+        <v>0.9018361581920904</v>
       </c>
       <c r="H285" t="n">
-        <v>6.402261484098941</v>
+        <v>6.4026447740113</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -22311,16 +22311,16 @@
         <v>1</v>
       </c>
       <c r="M285" t="n">
-        <v>-0.2977385159010595</v>
+        <v>-0.2973552259887002</v>
       </c>
       <c r="N285" t="n">
-        <v>0.2977385159010595</v>
+        <v>0.2973552259887002</v>
       </c>
       <c r="O285" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P285" t="n">
-        <v>-0.03915194346289308</v>
+        <v>-0.04320268361581547</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
@@ -22360,10 +22360,10 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>0.8989399293286219</v>
+        <v>0.8990112994350282</v>
       </c>
       <c r="H286" t="n">
-        <v>6.356572438162543</v>
+        <v>6.358149717514123</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -22382,16 +22382,16 @@
         <v>1</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.1834275618374566</v>
+        <v>-0.1818502824858772</v>
       </c>
       <c r="N286" t="n">
-        <v>0.1834275618374566</v>
+        <v>0.1818502824858772</v>
       </c>
       <c r="O286" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P286" t="n">
-        <v>-0.04568904593639722</v>
+        <v>-0.04449505649717711</v>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
@@ -25685,10 +25685,10 @@
         <v>8</v>
       </c>
       <c r="G333" t="n">
-        <v>0.7639575971731449</v>
+        <v>0.7641242937853108</v>
       </c>
       <c r="H333" t="n">
-        <v>6.485180212014135</v>
+        <v>6.486122881355933</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -25707,16 +25707,16 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.7773197879858653</v>
+        <v>-0.7763771186440671</v>
       </c>
       <c r="N333" t="n">
-        <v>0.7773197879858653</v>
+        <v>0.7763771186440671</v>
       </c>
       <c r="O333" t="n">
         <v>-0.4400000000000004</v>
       </c>
       <c r="P333" t="n">
-        <v>-0.982325043767224</v>
+        <v>-0.9813823744254258</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -25756,10 +25756,10 @@
         <v>8</v>
       </c>
       <c r="G334" t="n">
-        <v>0.7724381625441696</v>
+        <v>0.7725988700564972</v>
       </c>
       <c r="H334" t="n">
-        <v>6.53742667844523</v>
+        <v>6.537767478813559</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -25778,16 +25778,16 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.4375733215547699</v>
+        <v>-0.4372325211864405</v>
       </c>
       <c r="N334" t="n">
-        <v>0.4375733215547699</v>
+        <v>0.4372325211864405</v>
       </c>
       <c r="O334" t="n">
         <v>-0.2875000000000005</v>
       </c>
       <c r="P334" t="n">
-        <v>0.05224646643109487</v>
+        <v>0.05164459745762606</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -25827,10 +25827,10 @@
         <v>8</v>
       </c>
       <c r="G335" t="n">
-        <v>0.792226148409894</v>
+        <v>0.7923728813559322</v>
       </c>
       <c r="H335" t="n">
-        <v>6.642694346289753</v>
+        <v>6.646843220338982</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -25849,16 +25849,16 @@
         <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.1573056537102469</v>
+        <v>-0.1531567796610176</v>
       </c>
       <c r="N335" t="n">
-        <v>0.1573056537102469</v>
+        <v>0.1531567796610176</v>
       </c>
       <c r="O335" t="n">
         <v>-0.1749999999999998</v>
       </c>
       <c r="P335" t="n">
-        <v>0.1052676678445232</v>
+        <v>0.1090757415254231</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -25898,10 +25898,10 @@
         <v>8</v>
       </c>
       <c r="G336" t="n">
-        <v>0.8148409893992933</v>
+        <v>0.8149717514124294</v>
       </c>
       <c r="H336" t="n">
-        <v>6.847925795053003</v>
+        <v>6.848665254237288</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -25920,16 +25920,16 @@
         <v>1</v>
       </c>
       <c r="M336" t="n">
-        <v>0.2179257950530031</v>
+        <v>0.2186652542372878</v>
       </c>
       <c r="N336" t="n">
-        <v>0.2179257950530031</v>
+        <v>0.2186652542372878</v>
       </c>
       <c r="O336" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P336" t="n">
-        <v>0.2052314487632501</v>
+        <v>0.2018220338983054</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -25969,10 +25969,10 @@
         <v>8</v>
       </c>
       <c r="G337" t="n">
-        <v>0.8346289752650177</v>
+        <v>0.8347457627118644</v>
       </c>
       <c r="H337" t="n">
-        <v>7.064826855123675</v>
+        <v>7.065487288135594</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -25991,16 +25991,16 @@
         <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>0.5748268551236748</v>
+        <v>0.5754872881355935</v>
       </c>
       <c r="N337" t="n">
-        <v>0.5748268551236748</v>
+        <v>0.5754872881355935</v>
       </c>
       <c r="O337" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P337" t="n">
-        <v>0.216901060070672</v>
+        <v>0.216822033898306</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>8</v>
       </c>
       <c r="G338" t="n">
-        <v>0.8508833922261484</v>
+        <v>0.8509887005649718</v>
       </c>
       <c r="H338" t="n">
-        <v>7.148349116607774</v>
+        <v>7.148468220338983</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -26062,16 +26062,16 @@
         <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>0.6683491166077733</v>
+        <v>0.6684682203389825</v>
       </c>
       <c r="N338" t="n">
-        <v>0.6683491166077733</v>
+        <v>0.6684682203389825</v>
       </c>
       <c r="O338" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P338" t="n">
-        <v>0.08352226148409869</v>
+        <v>0.0829809322033892</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -26111,10 +26111,10 @@
         <v>8</v>
       </c>
       <c r="G339" t="n">
-        <v>0.8579505300353357</v>
+        <v>0.8580508474576272</v>
       </c>
       <c r="H339" t="n">
-        <v>7.204210247349824</v>
+        <v>7.204777542372882</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -26133,16 +26133,16 @@
         <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>0.6542102473498241</v>
+        <v>0.6547775423728819</v>
       </c>
       <c r="N339" t="n">
-        <v>0.6542102473498241</v>
+        <v>0.6547775423728819</v>
       </c>
       <c r="O339" t="n">
         <v>0.0699999999999994</v>
       </c>
       <c r="P339" t="n">
-        <v>0.05586113074205024</v>
+        <v>0.05630932203389882</v>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
@@ -26182,10 +26182,10 @@
         <v>8</v>
       </c>
       <c r="G340" t="n">
-        <v>0.8501766784452297</v>
+        <v>0.8502824858757062</v>
       </c>
       <c r="H340" t="n">
-        <v>7.147549823321555</v>
+        <v>7.147669491525424</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -26204,16 +26204,16 @@
         <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>0.6175498233215544</v>
+        <v>0.6176694915254233</v>
       </c>
       <c r="N340" t="n">
-        <v>0.6175498233215544</v>
+        <v>0.6176694915254233</v>
       </c>
       <c r="O340" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P340" t="n">
-        <v>-0.05666042402826932</v>
+        <v>-0.05710805084745818</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -26253,10 +26253,10 @@
         <v>8</v>
       </c>
       <c r="G341" t="n">
-        <v>0.8303886925795053</v>
+        <v>0.8305084745762712</v>
       </c>
       <c r="H341" t="n">
-        <v>7.024464075382803</v>
+        <v>7.025367231638418</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -26275,16 +26275,16 @@
         <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>0.6919640753828036</v>
+        <v>0.6928672316384183</v>
       </c>
       <c r="N341" t="n">
-        <v>0.6919640753828036</v>
+        <v>0.6928672316384183</v>
       </c>
       <c r="O341" t="n">
         <v>-0.1975000000000007</v>
       </c>
       <c r="P341" t="n">
-        <v>-0.1230857479387515</v>
+        <v>-0.1223022598870056</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -26324,10 +26324,10 @@
         <v>8</v>
       </c>
       <c r="G342" t="n">
-        <v>0.8106007067137809</v>
+        <v>0.8107344632768362</v>
       </c>
       <c r="H342" t="n">
-        <v>6.819736749116609</v>
+        <v>6.819925847457627</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -26346,16 +26346,16 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>0.6297367491166082</v>
+        <v>0.6299258474576268</v>
       </c>
       <c r="N342" t="n">
-        <v>0.6297367491166082</v>
+        <v>0.6299258474576268</v>
       </c>
       <c r="O342" t="n">
         <v>-0.1424999999999992</v>
       </c>
       <c r="P342" t="n">
-        <v>-0.2047273262661946</v>
+        <v>-0.2054413841807907</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -26395,10 +26395,10 @@
         <v>8</v>
       </c>
       <c r="G343" t="n">
-        <v>0.7872791519434629</v>
+        <v>0.7874293785310734</v>
       </c>
       <c r="H343" t="n">
-        <v>6.619999999999999</v>
+        <v>6.62</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
@@ -26417,16 +26417,16 @@
         <v>1</v>
       </c>
       <c r="M343" t="n">
-        <v>0.629999999999999</v>
+        <v>0.6299999999999999</v>
       </c>
       <c r="N343" t="n">
-        <v>0.629999999999999</v>
+        <v>0.6299999999999999</v>
       </c>
       <c r="O343" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P343" t="n">
-        <v>-0.1997367491166093</v>
+        <v>-0.1999258474576271</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -26466,10 +26466,10 @@
         <v>8</v>
       </c>
       <c r="G344" t="n">
-        <v>0.7632508833922261</v>
+        <v>0.7634180790960452</v>
       </c>
       <c r="H344" t="n">
-        <v>6.481183745583039</v>
+        <v>6.482129237288136</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -26488,16 +26488,16 @@
         <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5611837455830386</v>
+        <v>0.5621292372881364</v>
       </c>
       <c r="N344" t="n">
-        <v>0.5611837455830386</v>
+        <v>0.5621292372881364</v>
       </c>
       <c r="O344" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P344" t="n">
-        <v>-0.1388162544169607</v>
+        <v>-0.1378707627118638</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -26537,10 +26537,10 @@
         <v>8</v>
       </c>
       <c r="G345" t="n">
-        <v>0.7413427561837456</v>
+        <v>0.7415254237288136</v>
       </c>
       <c r="H345" t="n">
-        <v>6.38</v>
+        <v>6.380000000000001</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
@@ -26559,16 +26559,16 @@
         <v>1</v>
       </c>
       <c r="M345" t="n">
-        <v>0.3999999999999995</v>
+        <v>0.4000000000000004</v>
       </c>
       <c r="N345" t="n">
-        <v>0.3999999999999995</v>
+        <v>0.4000000000000004</v>
       </c>
       <c r="O345" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P345" t="n">
-        <v>-0.1011837455830387</v>
+        <v>-0.1021292372881355</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -26608,10 +26608,10 @@
         <v>8</v>
       </c>
       <c r="G346" t="n">
-        <v>0.7180212014134275</v>
+        <v>0.7182203389830508</v>
       </c>
       <c r="H346" t="n">
-        <v>6.230614840989399</v>
+        <v>6.232304025423729</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -26630,16 +26630,16 @@
         <v>1</v>
       </c>
       <c r="M346" t="n">
-        <v>0.110614840989399</v>
+        <v>0.1123040254237289</v>
       </c>
       <c r="N346" t="n">
-        <v>0.110614840989399</v>
+        <v>0.1123040254237289</v>
       </c>
       <c r="O346" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P346" t="n">
-        <v>-0.1493851590106008</v>
+        <v>-0.1476959745762718</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -27809,10 +27809,10 @@
         <v>8</v>
       </c>
       <c r="G363" t="n">
-        <v>0.6452296819787986</v>
+        <v>0.6454802259887006</v>
       </c>
       <c r="H363" t="n">
-        <v>6.969656360424028</v>
+        <v>6.969874646892655</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -27831,16 +27831,16 @@
         <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>-1.492843639575972</v>
+        <v>-1.492625353107345</v>
       </c>
       <c r="N363" t="n">
-        <v>1.492843639575972</v>
+        <v>1.492625353107345</v>
       </c>
       <c r="O363" t="n">
         <v>-0.254999999999999</v>
       </c>
       <c r="P363" t="n">
-        <v>0.1270757717765161</v>
+        <v>0.1272940582451429</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -27880,10 +27880,10 @@
         <v>8</v>
       </c>
       <c r="G364" t="n">
-        <v>0.6537102473498233</v>
+        <v>0.653954802259887</v>
       </c>
       <c r="H364" t="n">
-        <v>7.006360424028268</v>
+        <v>7.008064971751413</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -27902,16 +27902,16 @@
         <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>-1.306139575971732</v>
+        <v>-1.304435028248587</v>
       </c>
       <c r="N364" t="n">
-        <v>1.306139575971732</v>
+        <v>1.304435028248587</v>
       </c>
       <c r="O364" t="n">
         <v>-0.1500000000000004</v>
       </c>
       <c r="P364" t="n">
-        <v>0.03670406360424039</v>
+        <v>0.03819032485875784</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -27951,10 +27951,10 @@
         <v>8</v>
       </c>
       <c r="G365" t="n">
-        <v>0.6664310954063605</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H365" t="n">
-        <v>7.067512367491167</v>
+        <v>7.068333333333333</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -27973,16 +27973,16 @@
         <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>-1.062487632508834</v>
+        <v>-1.061666666666667</v>
       </c>
       <c r="N365" t="n">
-        <v>1.062487632508834</v>
+        <v>1.061666666666667</v>
       </c>
       <c r="O365" t="n">
         <v>-0.1824999999999992</v>
       </c>
       <c r="P365" t="n">
-        <v>0.06115194346289865</v>
+        <v>0.06026836158192062</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -28022,10 +28022,10 @@
         <v>8</v>
       </c>
       <c r="G366" t="n">
-        <v>0.680565371024735</v>
+        <v>0.6807909604519774</v>
       </c>
       <c r="H366" t="n">
-        <v>7.165116607773851</v>
+        <v>7.166001059322033</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -28044,16 +28044,16 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.9223833922261493</v>
+        <v>-0.9214989406779672</v>
       </c>
       <c r="N366" t="n">
-        <v>0.9223833922261493</v>
+        <v>0.9214989406779672</v>
       </c>
       <c r="O366" t="n">
         <v>-0.04250000000000043</v>
       </c>
       <c r="P366" t="n">
-        <v>0.097604240282684</v>
+        <v>0.09766772598869977</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -28093,10 +28093,10 @@
         <v>8</v>
       </c>
       <c r="G367" t="n">
-        <v>0.688339222614841</v>
+        <v>0.6885593220338984</v>
       </c>
       <c r="H367" t="n">
-        <v>7.192215547703181</v>
+        <v>7.192407309322035</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -28115,16 +28115,16 @@
         <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>-1.03778445229682</v>
+        <v>-1.037592690677966</v>
       </c>
       <c r="N367" t="n">
-        <v>1.03778445229682</v>
+        <v>1.037592690677966</v>
       </c>
       <c r="O367" t="n">
         <v>0.1425000000000001</v>
       </c>
       <c r="P367" t="n">
-        <v>0.02709893992932955</v>
+        <v>0.02640625000000174</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -28164,10 +28164,10 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>0.6897526501766784</v>
+        <v>0.6899717514124294</v>
       </c>
       <c r="H368" t="n">
-        <v>7.196919316843346</v>
+        <v>7.197810145951037</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -28186,16 +28186,16 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.8455806831566548</v>
+        <v>-0.8446898540489638</v>
       </c>
       <c r="N368" t="n">
-        <v>0.8455806831566548</v>
+        <v>0.8446898540489638</v>
       </c>
       <c r="O368" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P368" t="n">
-        <v>0.004703769140165015</v>
+        <v>0.005402836629001762</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -28235,10 +28235,10 @@
         <v>8</v>
       </c>
       <c r="G369" t="n">
-        <v>0.6840989399293286</v>
+        <v>0.684322033898305</v>
       </c>
       <c r="H369" t="n">
-        <v>7.178970406360424</v>
+        <v>7.179845074152542</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -28257,16 +28257,16 @@
         <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.7710295936395761</v>
+        <v>-0.770154925847458</v>
       </c>
       <c r="N369" t="n">
-        <v>0.7710295936395761</v>
+        <v>0.770154925847458</v>
       </c>
       <c r="O369" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P369" t="n">
-        <v>-0.01794891048292158</v>
+        <v>-0.01796507179849449</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -28306,10 +28306,10 @@
         <v>8</v>
       </c>
       <c r="G370" t="n">
-        <v>0.6720848056537102</v>
+        <v>0.672316384180791</v>
       </c>
       <c r="H370" t="n">
-        <v>7.112215547703181</v>
+        <v>7.113022598870057</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -28328,16 +28328,16 @@
         <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.8677844522968199</v>
+        <v>-0.8669774011299438</v>
       </c>
       <c r="N370" t="n">
-        <v>0.8677844522968199</v>
+        <v>0.8669774011299438</v>
       </c>
       <c r="O370" t="n">
         <v>0.03000000000000025</v>
       </c>
       <c r="P370" t="n">
-        <v>-0.06675485865724351</v>
+        <v>-0.06682247528248553</v>
       </c>
       <c r="Q370" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>8</v>
       </c>
       <c r="G371" t="n">
-        <v>0.6530035335689046</v>
+        <v>0.6532485875706214</v>
       </c>
       <c r="H371" t="n">
-        <v>7.001434628975265</v>
+        <v>7.003142655367231</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -28399,16 +28399,16 @@
         <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>-1.033565371024735</v>
+        <v>-1.031857344632769</v>
       </c>
       <c r="N371" t="n">
-        <v>1.033565371024735</v>
+        <v>1.031857344632769</v>
       </c>
       <c r="O371" t="n">
         <v>0.05499999999999972</v>
       </c>
       <c r="P371" t="n">
-        <v>-0.1107809187279152</v>
+        <v>-0.1098799435028255</v>
       </c>
       <c r="Q371" t="inlineStr">
         <is>
@@ -28448,10 +28448,10 @@
         <v>8</v>
       </c>
       <c r="G372" t="n">
-        <v>0.631095406360424</v>
+        <v>0.6313559322033898</v>
       </c>
       <c r="H372" t="n">
-        <v>6.936867491166078</v>
+        <v>6.937637711864407</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -28470,16 +28470,16 @@
         <v>1</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.9731325088339222</v>
+        <v>-0.9723622881355931</v>
       </c>
       <c r="N372" t="n">
-        <v>0.9731325088339222</v>
+        <v>0.9723622881355931</v>
       </c>
       <c r="O372" t="n">
         <v>-0.125</v>
       </c>
       <c r="P372" t="n">
-        <v>-0.06456713780918744</v>
+        <v>-0.0655049435028241</v>
       </c>
       <c r="Q372" t="inlineStr">
         <is>
@@ -28519,10 +28519,10 @@
         <v>8</v>
       </c>
       <c r="G373" t="n">
-        <v>0.6162544169611307</v>
+        <v>0.6165254237288136</v>
       </c>
       <c r="H373" t="n">
-        <v>6.880808303886925</v>
+        <v>6.881988877118644</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -28541,16 +28541,16 @@
         <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.809191696113075</v>
+        <v>-0.8080111228813562</v>
       </c>
       <c r="N373" t="n">
-        <v>0.809191696113075</v>
+        <v>0.8080111228813562</v>
       </c>
       <c r="O373" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P373" t="n">
-        <v>-0.05605918727915249</v>
+        <v>-0.05564883474576288</v>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
@@ -28590,10 +28590,10 @@
         <v>8</v>
       </c>
       <c r="G374" t="n">
-        <v>0.5985865724381625</v>
+        <v>0.5988700564971752</v>
       </c>
       <c r="H374" t="n">
-        <v>6.799018551236749</v>
+        <v>6.799265536723164</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -28612,16 +28612,16 @@
         <v>1</v>
       </c>
       <c r="M374" t="n">
-        <v>-0.660981448763251</v>
+        <v>-0.6607344632768362</v>
       </c>
       <c r="N374" t="n">
-        <v>0.660981448763251</v>
+        <v>0.6607344632768362</v>
       </c>
       <c r="O374" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P374" t="n">
-        <v>-0.08178975265017652</v>
+        <v>-0.08272334039548035</v>
       </c>
       <c r="Q374" t="inlineStr">
         <is>
@@ -28661,10 +28661,10 @@
         <v>8</v>
       </c>
       <c r="G375" t="n">
-        <v>0.5837455830388693</v>
+        <v>0.5840395480225988</v>
       </c>
       <c r="H375" t="n">
-        <v>6.761088339222614</v>
+        <v>6.761344456214689</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -28683,16 +28683,16 @@
         <v>1</v>
       </c>
       <c r="M375" t="n">
-        <v>-0.5189116607773858</v>
+        <v>-0.5186555437853109</v>
       </c>
       <c r="N375" t="n">
-        <v>0.5189116607773858</v>
+        <v>0.5186555437853109</v>
       </c>
       <c r="O375" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.03793021201413449</v>
+        <v>-0.03792108050847443</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
@@ -28732,10 +28732,10 @@
         <v>8</v>
       </c>
       <c r="G376" t="n">
-        <v>0.5653710247349824</v>
+        <v>0.565677966101695</v>
       </c>
       <c r="H376" t="n">
-        <v>6.680636042402827</v>
+        <v>6.682775423728813</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -28754,16 +28754,16 @@
         <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>-0.4293639575971735</v>
+        <v>-0.427224576271187</v>
       </c>
       <c r="N376" t="n">
-        <v>0.4293639575971735</v>
+        <v>0.427224576271187</v>
       </c>
       <c r="O376" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.08045229681978761</v>
+        <v>-0.0785690324858761</v>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
@@ -29933,10 +29933,10 @@
         <v>8</v>
       </c>
       <c r="G393" t="n">
-        <v>0.6586572438162545</v>
+        <v>0.6581920903954802</v>
       </c>
       <c r="H393" t="n">
-        <v>5.818611307420496</v>
+        <v>5.811271186440678</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -29955,16 +29955,16 @@
         <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>1.028611307420495</v>
+        <v>1.021271186440677</v>
       </c>
       <c r="N393" t="n">
-        <v>1.028611307420495</v>
+        <v>1.021271186440677</v>
       </c>
       <c r="O393" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P393" t="n">
-        <v>-0.6469107668612137</v>
+        <v>-0.654250887841032</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
@@ -30004,10 +30004,10 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>0.5639575971731449</v>
+        <v>0.5635593220338984</v>
       </c>
       <c r="H394" t="n">
-        <v>5.499906360424029</v>
+        <v>5.499120762711864</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -30026,16 +30026,16 @@
         <v>1</v>
       </c>
       <c r="M394" t="n">
-        <v>0.8299063604240287</v>
+        <v>0.829120762711864</v>
       </c>
       <c r="N394" t="n">
-        <v>0.8299063604240287</v>
+        <v>0.829120762711864</v>
       </c>
       <c r="O394" t="n">
         <v>-0.120000000000001</v>
       </c>
       <c r="P394" t="n">
-        <v>-0.3187049469964673</v>
+        <v>-0.3121504237288137</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -30075,10 +30075,10 @@
         <v>8</v>
       </c>
       <c r="G395" t="n">
-        <v>0.5420494699646643</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H395" t="n">
-        <v>5.456397526501767</v>
+        <v>5.456145833333333</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -30097,16 +30097,16 @@
         <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>0.9163975265017665</v>
+        <v>0.9161458333333332</v>
       </c>
       <c r="N395" t="n">
-        <v>0.9163975265017665</v>
+        <v>0.9161458333333332</v>
       </c>
       <c r="O395" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P395" t="n">
-        <v>-0.04350883392226201</v>
+        <v>-0.04297492937853065</v>
       </c>
       <c r="Q395" t="inlineStr">
         <is>
@@ -30146,10 +30146,10 @@
         <v>8</v>
       </c>
       <c r="G396" t="n">
-        <v>0.5957597173144876</v>
+        <v>0.5953389830508474</v>
       </c>
       <c r="H396" t="n">
-        <v>5.636712014134275</v>
+        <v>5.636435381355932</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -30168,16 +30168,16 @@
         <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>1.196712014134275</v>
+        <v>1.196435381355932</v>
       </c>
       <c r="N396" t="n">
-        <v>1.196712014134275</v>
+        <v>1.196435381355932</v>
       </c>
       <c r="O396" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P396" t="n">
-        <v>0.1803144876325087</v>
+        <v>0.180289548022599</v>
       </c>
       <c r="Q396" t="inlineStr">
         <is>
@@ -30217,10 +30217,10 @@
         <v>8</v>
       </c>
       <c r="G397" t="n">
-        <v>0.6339222614840989</v>
+        <v>0.6334745762711864</v>
       </c>
       <c r="H397" t="n">
-        <v>5.756803886925796</v>
+        <v>5.756509533898305</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -30239,16 +30239,16 @@
         <v>1</v>
       </c>
       <c r="M397" t="n">
-        <v>1.316803886925795</v>
+        <v>1.316509533898305</v>
       </c>
       <c r="N397" t="n">
-        <v>1.316803886925795</v>
+        <v>1.316509533898305</v>
       </c>
       <c r="O397" t="n">
         <v>0</v>
       </c>
       <c r="P397" t="n">
-        <v>0.1200918727915203</v>
+        <v>0.1200741525423732</v>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>8</v>
       </c>
       <c r="G398" t="n">
-        <v>0.5943462897526501</v>
+        <v>0.5939265536723164</v>
       </c>
       <c r="H398" t="n">
-        <v>5.635782685512368</v>
+        <v>5.635506709039548</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -30310,16 +30310,16 @@
         <v>1</v>
       </c>
       <c r="M398" t="n">
-        <v>1.235782685512367</v>
+        <v>1.235506709039548</v>
       </c>
       <c r="N398" t="n">
-        <v>1.235782685512367</v>
+        <v>1.235506709039548</v>
       </c>
       <c r="O398" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P398" t="n">
-        <v>-0.121021201413428</v>
+        <v>-0.1210028248587571</v>
       </c>
       <c r="Q398" t="inlineStr">
         <is>
@@ -30359,10 +30359,10 @@
         <v>8</v>
       </c>
       <c r="G399" t="n">
-        <v>0.4784452296819788</v>
+        <v>0.4781073446327684</v>
       </c>
       <c r="H399" t="n">
-        <v>5.189577738515902</v>
+        <v>5.189355579096046</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -30381,16 +30381,16 @@
         <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>0.8095777385159018</v>
+        <v>0.8093555790960458</v>
       </c>
       <c r="N399" t="n">
-        <v>0.8095777385159018</v>
+        <v>0.8093555790960458</v>
       </c>
       <c r="O399" t="n">
         <v>-0.02000000000000046</v>
       </c>
       <c r="P399" t="n">
-        <v>-0.446204946996466</v>
+        <v>-0.4461511299435026</v>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
@@ -30430,10 +30430,10 @@
         <v>8</v>
       </c>
       <c r="G400" t="n">
-        <v>0.3696113074204947</v>
+        <v>0.3693502824858757</v>
       </c>
       <c r="H400" t="n">
-        <v>4.843019434628975</v>
+        <v>4.842847810734463</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -30452,16 +30452,16 @@
         <v>1</v>
       </c>
       <c r="M400" t="n">
-        <v>0.7030194346289758</v>
+        <v>0.7028478107344638</v>
       </c>
       <c r="N400" t="n">
-        <v>0.7030194346289758</v>
+        <v>0.7028478107344638</v>
       </c>
       <c r="O400" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P400" t="n">
-        <v>-0.3465583038869262</v>
+        <v>-0.3465077683615823</v>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
@@ -30501,10 +30501,10 @@
         <v>8</v>
       </c>
       <c r="G401" t="n">
-        <v>0.3250883392226148</v>
+        <v>0.3248587570621469</v>
       </c>
       <c r="H401" t="n">
-        <v>4.697446996466431</v>
+        <v>4.695635593220339</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -30523,16 +30523,16 @@
         <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>0.8274469964664313</v>
+        <v>0.8256355932203387</v>
       </c>
       <c r="N401" t="n">
-        <v>0.8274469964664313</v>
+        <v>0.8256355932203387</v>
       </c>
       <c r="O401" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P401" t="n">
-        <v>-0.1455724381625441</v>
+        <v>-0.1472122175141246</v>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
@@ -30572,10 +30572,10 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>0.3512367491166078</v>
+        <v>0.3509887005649718</v>
       </c>
       <c r="H402" t="n">
-        <v>4.80593816254417</v>
+        <v>4.805775070621468</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -30594,16 +30594,16 @@
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>1.085938162544169</v>
+        <v>1.085775070621468</v>
       </c>
       <c r="N402" t="n">
-        <v>1.085938162544169</v>
+        <v>1.085775070621468</v>
       </c>
       <c r="O402" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P402" t="n">
-        <v>0.1084911660777381</v>
+        <v>0.1101394774011295</v>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -30643,10 +30643,10 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>0.5293286219081272</v>
+        <v>0.528954802259887</v>
       </c>
       <c r="H403" t="n">
-        <v>5.441067137809187</v>
+        <v>5.440575564971751</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -30665,16 +30665,16 @@
         <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>1.741067137809187</v>
+        <v>1.740575564971751</v>
       </c>
       <c r="N403" t="n">
-        <v>1.741067137809187</v>
+        <v>1.740575564971751</v>
       </c>
       <c r="O403" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P403" t="n">
-        <v>0.635128975265018</v>
+        <v>0.6348004943502827</v>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>8</v>
       </c>
       <c r="G404" t="n">
-        <v>0.76113074204947</v>
+        <v>0.760593220338983</v>
       </c>
       <c r="H404" t="n">
-        <v>6.103547703180212</v>
+        <v>6.10072033898305</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -30736,16 +30736,16 @@
         <v>1</v>
       </c>
       <c r="M404" t="n">
-        <v>2.263547703180212</v>
+        <v>2.260720338983051</v>
       </c>
       <c r="N404" t="n">
-        <v>2.263547703180212</v>
+        <v>2.260720338983051</v>
       </c>
       <c r="O404" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P404" t="n">
-        <v>0.6624805653710242</v>
+        <v>0.6601447740112993</v>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
@@ -30785,10 +30785,10 @@
         <v>8</v>
       </c>
       <c r="G405" t="n">
-        <v>0.8318021201413428</v>
+        <v>0.8312146892655368</v>
       </c>
       <c r="H405" t="n">
-        <v>6.347189045936396</v>
+        <v>6.343712923728813</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -30807,16 +30807,16 @@
         <v>1</v>
       </c>
       <c r="M405" t="n">
-        <v>2.327189045936397</v>
+        <v>2.323712923728814</v>
       </c>
       <c r="N405" t="n">
-        <v>2.327189045936397</v>
+        <v>2.323712923728814</v>
       </c>
       <c r="O405" t="n">
         <v>0.1799999999999997</v>
       </c>
       <c r="P405" t="n">
-        <v>0.2436413427561845</v>
+        <v>0.242992584745763</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
@@ -30856,10 +30856,10 @@
         <v>8</v>
       </c>
       <c r="G406" t="n">
-        <v>0.8162544169611308</v>
+        <v>0.815677966101695</v>
       </c>
       <c r="H406" t="n">
-        <v>6.294372791519435</v>
+        <v>6.290582627118645</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -30878,16 +30878,16 @@
         <v>1</v>
       </c>
       <c r="M406" t="n">
-        <v>2.194372791519435</v>
+        <v>2.190582627118645</v>
       </c>
       <c r="N406" t="n">
-        <v>2.194372791519435</v>
+        <v>2.190582627118645</v>
       </c>
       <c r="O406" t="n">
         <v>0.08000000000000007</v>
       </c>
       <c r="P406" t="n">
-        <v>-0.05281625441696125</v>
+        <v>-0.05313029661016877</v>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
@@ -32057,10 +32057,10 @@
         <v>8</v>
       </c>
       <c r="G423" t="n">
-        <v>0.8296819787985866</v>
+        <v>0.8298022598870056</v>
       </c>
       <c r="H423" t="n">
-        <v>5.565226148409893</v>
+        <v>5.566001059322033</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -32079,16 +32079,16 @@
         <v>1</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.8022738515901064</v>
+        <v>-0.8014989406779671</v>
       </c>
       <c r="N423" t="n">
-        <v>0.8022738515901064</v>
+        <v>0.8014989406779671</v>
       </c>
       <c r="O423" t="n">
         <v>-0.07500000000000018</v>
       </c>
       <c r="P423" t="n">
-        <v>-1.473703424119889</v>
+        <v>-1.47292851320775</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
@@ -32128,10 +32128,10 @@
         <v>8</v>
       </c>
       <c r="G424" t="n">
-        <v>0.8275618374558303</v>
+        <v>0.827683615819209</v>
       </c>
       <c r="H424" t="n">
-        <v>5.549378091872791</v>
+        <v>5.549901129943502</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -32150,16 +32150,16 @@
         <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>-0.7681219081272088</v>
+        <v>-0.7675988700564975</v>
       </c>
       <c r="N424" t="n">
-        <v>0.7681219081272088</v>
+        <v>0.7675988700564975</v>
       </c>
       <c r="O424" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P424" t="n">
-        <v>-0.0158480565371022</v>
+        <v>-0.01609992937853022</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -32199,10 +32199,10 @@
         <v>8</v>
       </c>
       <c r="G425" t="n">
-        <v>0.8212014134275618</v>
+        <v>0.8213276836158192</v>
       </c>
       <c r="H425" t="n">
-        <v>5.504120141342757</v>
+        <v>5.505204802259887</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -32221,16 +32221,16 @@
         <v>1</v>
       </c>
       <c r="M425" t="n">
-        <v>-0.7558798586572433</v>
+        <v>-0.7547951977401128</v>
       </c>
       <c r="N425" t="n">
-        <v>0.7558798586572433</v>
+        <v>0.7547951977401128</v>
       </c>
       <c r="O425" t="n">
         <v>-0.05750000000000011</v>
       </c>
       <c r="P425" t="n">
-        <v>-0.04525795053003456</v>
+        <v>-0.04469632768361542</v>
       </c>
       <c r="Q425" t="inlineStr">
         <is>
@@ -32270,10 +32270,10 @@
         <v>8</v>
       </c>
       <c r="G426" t="n">
-        <v>0.8183745583038869</v>
+        <v>0.818502824858757</v>
       </c>
       <c r="H426" t="n">
-        <v>5.489878091872792</v>
+        <v>5.490469632768362</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -32292,16 +32292,16 @@
         <v>1</v>
       </c>
       <c r="M426" t="n">
-        <v>-0.6401219081272078</v>
+        <v>-0.6395303672316377</v>
       </c>
       <c r="N426" t="n">
-        <v>0.6401219081272078</v>
+        <v>0.6395303672316377</v>
       </c>
       <c r="O426" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P426" t="n">
-        <v>-0.01424204946996444</v>
+        <v>-0.01473516949152476</v>
       </c>
       <c r="Q426" t="inlineStr">
         <is>
@@ -32341,10 +32341,10 @@
         <v>8</v>
       </c>
       <c r="G427" t="n">
-        <v>0.8091872791519434</v>
+        <v>0.809322033898305</v>
       </c>
       <c r="H427" t="n">
-        <v>5.382844522968197</v>
+        <v>5.383278601694914</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -32363,16 +32363,16 @@
         <v>1</v>
       </c>
       <c r="M427" t="n">
-        <v>-0.6071554770318031</v>
+        <v>-0.6067213983050861</v>
       </c>
       <c r="N427" t="n">
-        <v>0.6071554770318031</v>
+        <v>0.6067213983050861</v>
       </c>
       <c r="O427" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P427" t="n">
-        <v>-0.1070335689045949</v>
+        <v>-0.1071910310734481</v>
       </c>
       <c r="Q427" t="inlineStr">
         <is>
@@ -32412,10 +32412,10 @@
         <v>8</v>
       </c>
       <c r="G428" t="n">
-        <v>0.7886925795053004</v>
+        <v>0.7888418079096046</v>
       </c>
       <c r="H428" t="n">
-        <v>5.228717314487633</v>
+        <v>5.229037782485876</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -32434,16 +32434,16 @@
         <v>1</v>
       </c>
       <c r="M428" t="n">
-        <v>-0.4787826855123667</v>
+        <v>-0.4784622175141235</v>
       </c>
       <c r="N428" t="n">
-        <v>0.4787826855123667</v>
+        <v>0.4784622175141235</v>
       </c>
       <c r="O428" t="n">
         <v>-0.2825000000000006</v>
       </c>
       <c r="P428" t="n">
-        <v>-0.1541272084805643</v>
+        <v>-0.1542408192090381</v>
       </c>
       <c r="Q428" t="inlineStr">
         <is>
@@ -32483,10 +32483,10 @@
         <v>8</v>
       </c>
       <c r="G429" t="n">
-        <v>0.7710247349823321</v>
+        <v>0.7711864406779662</v>
       </c>
       <c r="H429" t="n">
-        <v>5.101551236749116</v>
+        <v>5.102245762711864</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
@@ -32505,16 +32505,16 @@
         <v>1</v>
       </c>
       <c r="M429" t="n">
-        <v>-0.4584487632508836</v>
+        <v>-0.4577542372881354</v>
       </c>
       <c r="N429" t="n">
-        <v>0.4584487632508836</v>
+        <v>0.4577542372881354</v>
       </c>
       <c r="O429" t="n">
         <v>-0.1475</v>
       </c>
       <c r="P429" t="n">
-        <v>-0.1271660777385168</v>
+        <v>-0.1267920197740118</v>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
@@ -32554,10 +32554,10 @@
         <v>8</v>
       </c>
       <c r="G430" t="n">
-        <v>0.7462897526501767</v>
+        <v>0.7464689265536724</v>
       </c>
       <c r="H430" t="n">
-        <v>4.950314487632509</v>
+        <v>4.951084039548022</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -32576,16 +32576,16 @@
         <v>1</v>
       </c>
       <c r="M430" t="n">
-        <v>-0.3896855123674907</v>
+        <v>-0.3889159604519774</v>
       </c>
       <c r="N430" t="n">
-        <v>0.3896855123674907</v>
+        <v>0.3889159604519774</v>
       </c>
       <c r="O430" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P430" t="n">
-        <v>-0.1512367491166069</v>
+        <v>-0.1511617231638418</v>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
@@ -32625,10 +32625,10 @@
         <v>8</v>
       </c>
       <c r="G431" t="n">
-        <v>0.7187279151943463</v>
+        <v>0.7189265536723164</v>
       </c>
       <c r="H431" t="n">
-        <v>4.819999999999999</v>
+        <v>4.82</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
@@ -32647,16 +32647,16 @@
         <v>1</v>
       </c>
       <c r="M431" t="n">
-        <v>-0.2925000000000004</v>
+        <v>-0.2924999999999995</v>
       </c>
       <c r="N431" t="n">
-        <v>0.2925000000000004</v>
+        <v>0.2924999999999995</v>
       </c>
       <c r="O431" t="n">
         <v>-0.2275</v>
       </c>
       <c r="P431" t="n">
-        <v>-0.1303144876325097</v>
+        <v>-0.1310840395480222</v>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
@@ -32696,10 +32696,10 @@
         <v>8</v>
       </c>
       <c r="G432" t="n">
-        <v>0.6939929328621908</v>
+        <v>0.6942090395480226</v>
       </c>
       <c r="H432" t="n">
-        <v>4.650349823321555</v>
+        <v>4.650813912429379</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -32718,16 +32718,16 @@
         <v>1</v>
       </c>
       <c r="M432" t="n">
-        <v>-0.3596501766784446</v>
+        <v>-0.3591860875706212</v>
       </c>
       <c r="N432" t="n">
-        <v>0.3596501766784446</v>
+        <v>0.3591860875706212</v>
       </c>
       <c r="O432" t="n">
         <v>-0.1025</v>
       </c>
       <c r="P432" t="n">
-        <v>-0.1696501766784442</v>
+        <v>-0.1691860875706217</v>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
@@ -32767,10 +32767,10 @@
         <v>8</v>
       </c>
       <c r="G433" t="n">
-        <v>0.6840989399293286</v>
+        <v>0.684322033898305</v>
       </c>
       <c r="H433" t="n">
-        <v>4.620801236749116</v>
+        <v>4.621040783898305</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -32789,16 +32789,16 @@
         <v>1</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.2191987632508834</v>
+        <v>-0.2189592161016947</v>
       </c>
       <c r="N433" t="n">
-        <v>0.2191987632508834</v>
+        <v>0.2189592161016947</v>
       </c>
       <c r="O433" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P433" t="n">
-        <v>-0.02954858657243875</v>
+        <v>-0.02977312853107339</v>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
@@ -32838,10 +32838,10 @@
         <v>8</v>
       </c>
       <c r="G434" t="n">
-        <v>0.6890459363957597</v>
+        <v>0.6892655367231638</v>
       </c>
       <c r="H434" t="n">
-        <v>4.636301531213192</v>
+        <v>4.636930320150659</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -32860,16 +32860,16 @@
         <v>1</v>
       </c>
       <c r="M434" t="n">
-        <v>-0.08369846878680764</v>
+        <v>-0.08306967984934044</v>
       </c>
       <c r="N434" t="n">
-        <v>0.08369846878680764</v>
+        <v>0.08306967984934044</v>
       </c>
       <c r="O434" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P434" t="n">
-        <v>0.01550029446407564</v>
+        <v>0.01588953625235412</v>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
@@ -32909,10 +32909,10 @@
         <v>8</v>
       </c>
       <c r="G435" t="n">
-        <v>0.7088339222614841</v>
+        <v>0.7090395480225988</v>
       </c>
       <c r="H435" t="n">
-        <v>4.742588928150766</v>
+        <v>4.743766478342749</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -32931,16 +32931,16 @@
         <v>1</v>
       </c>
       <c r="M435" t="n">
-        <v>0.182588928150766</v>
+        <v>0.1837664783427497</v>
       </c>
       <c r="N435" t="n">
-        <v>0.182588928150766</v>
+        <v>0.1837664783427497</v>
       </c>
       <c r="O435" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P435" t="n">
-        <v>0.1062873969375735</v>
+        <v>0.10683615819209</v>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
@@ -32980,10 +32980,10 @@
         <v>8</v>
       </c>
       <c r="G436" t="n">
-        <v>0.7250883392226148</v>
+        <v>0.7252824858757062</v>
       </c>
       <c r="H436" t="n">
-        <v>4.844254416961131</v>
+        <v>4.845088276836158</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -33002,16 +33002,16 @@
         <v>1</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4542544169611311</v>
+        <v>0.4550882768361584</v>
       </c>
       <c r="N436" t="n">
-        <v>0.4542544169611311</v>
+        <v>0.4550882768361584</v>
       </c>
       <c r="O436" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P436" t="n">
-        <v>0.1016654888103652</v>
+        <v>0.1013217984934087</v>
       </c>
       <c r="Q436" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>8</v>
       </c>
       <c r="G437" t="n">
-        <v>0.823321554770318</v>
+        <v>0.8234463276836158</v>
       </c>
       <c r="H437" t="n">
-        <v>3.497340989399293</v>
+        <v>3.499025423728813</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -33073,10 +33073,10 @@
         <v>1</v>
       </c>
       <c r="M437" t="n">
-        <v>-0.9426590106007078</v>
+        <v>-0.9409745762711874</v>
       </c>
       <c r="N437" t="n">
-        <v>0.9426590106007078</v>
+        <v>0.9409745762711874</v>
       </c>
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
@@ -33116,10 +33116,10 @@
         <v>8</v>
       </c>
       <c r="G438" t="n">
-        <v>0.8091872791519434</v>
+        <v>0.809322033898305</v>
       </c>
       <c r="H438" t="n">
-        <v>3.349611307420495</v>
+        <v>3.350677966101695</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -33138,16 +33138,16 @@
         <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>-0.8928886925795059</v>
+        <v>-0.8918220338983058</v>
       </c>
       <c r="N438" t="n">
-        <v>0.8928886925795059</v>
+        <v>0.8918220338983058</v>
       </c>
       <c r="O438" t="n">
         <v>-0.1974999999999998</v>
       </c>
       <c r="P438" t="n">
-        <v>-0.1477296819787979</v>
+        <v>-0.1483474576271182</v>
       </c>
       <c r="Q438" t="inlineStr">
         <is>
@@ -33187,10 +33187,10 @@
         <v>8</v>
       </c>
       <c r="G439" t="n">
-        <v>0.8</v>
+        <v>0.8001412429378532</v>
       </c>
       <c r="H439" t="n">
-        <v>3.295</v>
+        <v>3.295381355932203</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -33209,16 +33209,16 @@
         <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>-0.8150000000000004</v>
+        <v>-0.8146186440677972</v>
       </c>
       <c r="N439" t="n">
-        <v>0.8150000000000004</v>
+        <v>0.8146186440677972</v>
       </c>
       <c r="O439" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P439" t="n">
-        <v>-0.0546113074204948</v>
+        <v>-0.05529661016949161</v>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
@@ -33258,10 +33258,10 @@
         <v>8</v>
       </c>
       <c r="G440" t="n">
-        <v>0.8042402826855124</v>
+        <v>0.8043785310734464</v>
       </c>
       <c r="H440" t="n">
-        <v>3.315795053003534</v>
+        <v>3.317288135593221</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -33280,16 +33280,16 @@
         <v>1</v>
       </c>
       <c r="M440" t="n">
-        <v>-0.6542049469964661</v>
+        <v>-0.6527118644067791</v>
       </c>
       <c r="N440" t="n">
-        <v>0.6542049469964661</v>
+        <v>0.6527118644067791</v>
       </c>
       <c r="O440" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P440" t="n">
-        <v>0.02079505300353413</v>
+        <v>0.02190677966101795</v>
       </c>
       <c r="Q440" t="inlineStr">
         <is>
@@ -33329,10 +33329,10 @@
         <v>8</v>
       </c>
       <c r="G441" t="n">
-        <v>0.8219081272084806</v>
+        <v>0.8220338983050848</v>
       </c>
       <c r="H441" t="n">
-        <v>3.466607773851591</v>
+        <v>3.467966101694916</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -33351,16 +33351,16 @@
         <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>-0.363392226148409</v>
+        <v>-0.3620338983050839</v>
       </c>
       <c r="N441" t="n">
-        <v>0.363392226148409</v>
+        <v>0.3620338983050839</v>
       </c>
       <c r="O441" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P441" t="n">
-        <v>0.150812720848057</v>
+        <v>0.150677966101695</v>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
@@ -33400,10 +33400,10 @@
         <v>8</v>
       </c>
       <c r="G442" t="n">
-        <v>0.8381625441696113</v>
+        <v>0.838276836158192</v>
       </c>
       <c r="H442" t="n">
-        <v>3.648103651354535</v>
+        <v>3.648926553672316</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -33422,16 +33422,16 @@
         <v>1</v>
       </c>
       <c r="M442" t="n">
-        <v>-0.01189634864546507</v>
+        <v>-0.01107344632768381</v>
       </c>
       <c r="N442" t="n">
-        <v>0.01189634864546507</v>
+        <v>0.01107344632768381</v>
       </c>
       <c r="O442" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P442" t="n">
-        <v>0.181495877502944</v>
+        <v>0.1809604519774002</v>
       </c>
       <c r="Q442" t="inlineStr">
         <is>
@@ -33471,10 +33471,10 @@
         <v>8</v>
       </c>
       <c r="G443" t="n">
-        <v>0.8480565371024735</v>
+        <v>0.8481638418079096</v>
       </c>
       <c r="H443" t="n">
-        <v>3.722252650176679</v>
+        <v>3.722563559322034</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -33493,16 +33493,16 @@
         <v>1</v>
       </c>
       <c r="M443" t="n">
-        <v>0.08225265017667871</v>
+        <v>0.08256355932203396</v>
       </c>
       <c r="N443" t="n">
-        <v>0.08225265017667871</v>
+        <v>0.08256355932203396</v>
       </c>
       <c r="O443" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P443" t="n">
-        <v>0.07414899882214376</v>
+        <v>0.07363700564971776</v>
       </c>
       <c r="Q443" t="inlineStr">
         <is>
@@ -33542,10 +33542,10 @@
         <v>8</v>
       </c>
       <c r="G444" t="n">
-        <v>0.8558303886925795</v>
+        <v>0.8559322033898306</v>
       </c>
       <c r="H444" t="n">
-        <v>3.75648409893993</v>
+        <v>3.757033898305085</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -33564,16 +33564,16 @@
         <v>1</v>
       </c>
       <c r="M444" t="n">
-        <v>0.1564840989399294</v>
+        <v>0.1570338983050847</v>
       </c>
       <c r="N444" t="n">
-        <v>0.1564840989399294</v>
+        <v>0.1570338983050847</v>
       </c>
       <c r="O444" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P444" t="n">
-        <v>0.03423144876325068</v>
+        <v>0.03447033898305074</v>
       </c>
       <c r="Q444" t="inlineStr">
         <is>
@@ -33613,10 +33613,10 @@
         <v>8</v>
       </c>
       <c r="G445" t="n">
-        <v>0.8586572438162544</v>
+        <v>0.8587570621468926</v>
       </c>
       <c r="H445" t="n">
-        <v>3.768374558303887</v>
+        <v>3.76864406779661</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -33635,16 +33635,16 @@
         <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>0.235874558303887</v>
+        <v>0.23614406779661</v>
       </c>
       <c r="N445" t="n">
-        <v>0.235874558303887</v>
+        <v>0.23614406779661</v>
       </c>
       <c r="O445" t="n">
         <v>-0.06749999999999989</v>
       </c>
       <c r="P445" t="n">
-        <v>0.01189045936395772</v>
+        <v>0.01161016949152538</v>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
@@ -33684,10 +33684,10 @@
         <v>8</v>
       </c>
       <c r="G446" t="n">
-        <v>0.8508833922261484</v>
+        <v>0.8509887005649718</v>
       </c>
       <c r="H446" t="n">
-        <v>3.734770318021201</v>
+        <v>3.735677966101695</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -33706,16 +33706,16 @@
         <v>1</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2947703180212011</v>
+        <v>0.2956779661016946</v>
       </c>
       <c r="N446" t="n">
-        <v>0.2947703180212011</v>
+        <v>0.2956779661016946</v>
       </c>
       <c r="O446" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P446" t="n">
-        <v>-0.03360424028268616</v>
+        <v>-0.03296610169491565</v>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
@@ -33755,10 +33755,10 @@
         <v>8</v>
       </c>
       <c r="G447" t="n">
-        <v>0.8402826855123675</v>
+        <v>0.8403954802259888</v>
       </c>
       <c r="H447" t="n">
-        <v>3.668842756183746</v>
+        <v>3.670974576271187</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -33777,16 +33777,16 @@
         <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>0.378842756183746</v>
+        <v>0.3809745762711874</v>
       </c>
       <c r="N447" t="n">
-        <v>0.378842756183746</v>
+        <v>0.3809745762711874</v>
       </c>
       <c r="O447" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.06592756183745507</v>
+        <v>-0.06470338983050716</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
@@ -33826,10 +33826,10 @@
         <v>8</v>
       </c>
       <c r="G448" t="n">
-        <v>0.815547703180212</v>
+        <v>0.815677966101695</v>
       </c>
       <c r="H448" t="n">
-        <v>3.416978798586572</v>
+        <v>3.417330508474576</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -33848,16 +33848,16 @@
         <v>1</v>
       </c>
       <c r="M448" t="n">
-        <v>0.2369787985865721</v>
+        <v>0.2373305084745763</v>
       </c>
       <c r="N448" t="n">
-        <v>0.2369787985865721</v>
+        <v>0.2373305084745763</v>
       </c>
       <c r="O448" t="n">
         <v>-0.1099999999999999</v>
       </c>
       <c r="P448" t="n">
-        <v>-0.2518639575971737</v>
+        <v>-0.253644067796611</v>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
@@ -33897,10 +33897,10 @@
         <v>8</v>
       </c>
       <c r="G449" t="n">
-        <v>0.7837455830388692</v>
+        <v>0.7838983050847458</v>
       </c>
       <c r="H449" t="n">
-        <v>3.217226148409894</v>
+        <v>3.218050847457627</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -33919,16 +33919,16 @@
         <v>1</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1172261484098938</v>
+        <v>0.1180508474576274</v>
       </c>
       <c r="N449" t="n">
-        <v>0.1172261484098938</v>
+        <v>0.1180508474576274</v>
       </c>
       <c r="O449" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P449" t="n">
-        <v>-0.1997526501766784</v>
+        <v>-0.1992796610169489</v>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
@@ -33968,10 +33968,10 @@
         <v>8</v>
       </c>
       <c r="G450" t="n">
-        <v>0.7667844522968198</v>
+        <v>0.7669491525423728</v>
       </c>
       <c r="H450" t="n">
-        <v>3.110424028268551</v>
+        <v>3.111016949152542</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -33990,16 +33990,16 @@
         <v>1</v>
       </c>
       <c r="M450" t="n">
-        <v>0.01042402826855104</v>
+        <v>0.01101694915254203</v>
       </c>
       <c r="N450" t="n">
-        <v>0.01042402826855104</v>
+        <v>0.01101694915254203</v>
       </c>
       <c r="O450" t="n">
         <v>0</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.1068021201413427</v>
+        <v>-0.1070338983050854</v>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
@@ -35311,10 +35311,10 @@
         <v>8</v>
       </c>
       <c r="G469" t="n">
-        <v>0.8431095406360424</v>
+        <v>0.8432203389830508</v>
       </c>
       <c r="H469" t="n">
-        <v>8.555667844522969</v>
+        <v>8.558093220338982</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -35333,16 +35333,16 @@
         <v>1</v>
       </c>
       <c r="M469" t="n">
-        <v>-0.6843321554770316</v>
+        <v>-0.6819067796610181</v>
       </c>
       <c r="N469" t="n">
-        <v>0.6843321554770316</v>
+        <v>0.6819067796610181</v>
       </c>
       <c r="O469" t="n">
         <v>-0.08999999999999986</v>
       </c>
       <c r="P469" t="n">
-        <v>0.2566979776694307</v>
+        <v>0.2591233534854442</v>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
@@ -35382,10 +35382,10 @@
         <v>8</v>
       </c>
       <c r="G470" t="n">
-        <v>0.826148409893993</v>
+        <v>0.826271186440678</v>
       </c>
       <c r="H470" t="n">
-        <v>8.284212014134276</v>
+        <v>8.285677966101694</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -35404,16 +35404,16 @@
         <v>1</v>
       </c>
       <c r="M470" t="n">
-        <v>-0.7657879858657246</v>
+        <v>-0.7643220338983063</v>
       </c>
       <c r="N470" t="n">
-        <v>0.7657879858657246</v>
+        <v>0.7643220338983063</v>
       </c>
       <c r="O470" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P470" t="n">
-        <v>-0.2714558303886925</v>
+        <v>-0.2724152542372877</v>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -35453,10 +35453,10 @@
         <v>8</v>
       </c>
       <c r="G471" t="n">
-        <v>0.8070671378091873</v>
+        <v>0.8072033898305084</v>
       </c>
       <c r="H471" t="n">
-        <v>8.002763250883392</v>
+        <v>8.006016949152542</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -35475,16 +35475,16 @@
         <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.907236749116608</v>
+        <v>-0.903983050847458</v>
       </c>
       <c r="N471" t="n">
-        <v>0.907236749116608</v>
+        <v>0.903983050847458</v>
       </c>
       <c r="O471" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P471" t="n">
-        <v>-0.281448763250884</v>
+        <v>-0.2796610169491522</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
@@ -35524,10 +35524,10 @@
         <v>8</v>
       </c>
       <c r="G472" t="n">
-        <v>0.7950530035335689</v>
+        <v>0.7951977401129944</v>
       </c>
       <c r="H472" t="n">
-        <v>7.896466431095406</v>
+        <v>7.897330508474576</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -35546,16 +35546,16 @@
         <v>1</v>
       </c>
       <c r="M472" t="n">
-        <v>-0.8735335689045938</v>
+        <v>-0.8726694915254232</v>
       </c>
       <c r="N472" t="n">
-        <v>0.8735335689045938</v>
+        <v>0.8726694915254232</v>
       </c>
       <c r="O472" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P472" t="n">
-        <v>-0.1062968197879863</v>
+        <v>-0.1086864406779657</v>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
@@ -35595,10 +35595,10 @@
         <v>8</v>
       </c>
       <c r="G473" t="n">
-        <v>0.7929328621908127</v>
+        <v>0.7930790960451978</v>
       </c>
       <c r="H473" t="n">
-        <v>7.877618374558303</v>
+        <v>7.879364406779661</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -35617,16 +35617,16 @@
         <v>1</v>
       </c>
       <c r="M473" t="n">
-        <v>-0.7023816254416966</v>
+        <v>-0.7006355932203387</v>
       </c>
       <c r="N473" t="n">
-        <v>0.7023816254416966</v>
+        <v>0.7006355932203387</v>
       </c>
       <c r="O473" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P473" t="n">
-        <v>-0.01884805653710231</v>
+        <v>-0.01796610169491508</v>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
@@ -35666,10 +35666,10 @@
         <v>8</v>
       </c>
       <c r="G474" t="n">
-        <v>0.8035335689045936</v>
+        <v>0.8036723163841808</v>
       </c>
       <c r="H474" t="n">
-        <v>7.929031802120141</v>
+        <v>7.929307909604519</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -35688,16 +35688,16 @@
         <v>1</v>
       </c>
       <c r="M474" t="n">
-        <v>-0.5209681978798582</v>
+        <v>-0.5206920903954799</v>
       </c>
       <c r="N474" t="n">
-        <v>0.5209681978798582</v>
+        <v>0.5206920903954799</v>
       </c>
       <c r="O474" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P474" t="n">
-        <v>0.05141342756183764</v>
+        <v>0.04994350282485804</v>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
       </c>
       <c r="R474" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S474" t="b">
@@ -35737,10 +35737,10 @@
         <v>8</v>
       </c>
       <c r="G475" t="n">
-        <v>0.8162544169611308</v>
+        <v>0.8163841807909604</v>
       </c>
       <c r="H475" t="n">
-        <v>8.19434628975265</v>
+        <v>8.19460451977401</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -35759,16 +35759,16 @@
         <v>1</v>
       </c>
       <c r="M475" t="n">
-        <v>-0.1256537102473505</v>
+        <v>-0.1253954802259898</v>
       </c>
       <c r="N475" t="n">
-        <v>0.1256537102473505</v>
+        <v>0.1253954802259898</v>
       </c>
       <c r="O475" t="n">
         <v>-0.129999999999999</v>
       </c>
       <c r="P475" t="n">
-        <v>0.2653144876325086</v>
+        <v>0.2652966101694911</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
@@ -35808,10 +35808,10 @@
         <v>8</v>
       </c>
       <c r="G476" t="n">
-        <v>0.8282685512367491</v>
+        <v>0.8283898305084746</v>
       </c>
       <c r="H476" t="n">
-        <v>8.309526501766785</v>
+        <v>8.310974576271187</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -35830,16 +35830,16 @@
         <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>0.04952650176678475</v>
+        <v>0.05097457627118729</v>
       </c>
       <c r="N476" t="n">
-        <v>0.04952650176678475</v>
+        <v>0.05097457627118729</v>
       </c>
       <c r="O476" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P476" t="n">
-        <v>0.1151802120141348</v>
+        <v>0.1163700564971766</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
@@ -35879,10 +35879,10 @@
         <v>8</v>
       </c>
       <c r="G477" t="n">
-        <v>0.8367491166077738</v>
+        <v>0.836864406779661</v>
       </c>
       <c r="H477" t="n">
-        <v>8.46026148409894</v>
+        <v>8.460720338983052</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -35901,16 +35901,16 @@
         <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2602614840989403</v>
+        <v>0.2607203389830524</v>
       </c>
       <c r="N477" t="n">
-        <v>0.2602614840989403</v>
+        <v>0.2607203389830524</v>
       </c>
       <c r="O477" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P477" t="n">
-        <v>0.1507349823321551</v>
+        <v>0.1497457627118646</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -35950,10 +35950,10 @@
         <v>8</v>
       </c>
       <c r="G478" t="n">
-        <v>0.8374558303886925</v>
+        <v>0.8375706214689266</v>
       </c>
       <c r="H478" t="n">
-        <v>8.463074204946997</v>
+        <v>8.463531073446328</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -35972,16 +35972,16 @@
         <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>0.4130742049469962</v>
+        <v>0.4135310734463271</v>
       </c>
       <c r="N478" t="n">
-        <v>0.4130742049469962</v>
+        <v>0.4135310734463271</v>
       </c>
       <c r="O478" t="n">
         <v>-0.1499999999999986</v>
       </c>
       <c r="P478" t="n">
-        <v>0.002812720848057282</v>
+        <v>0.002810734463276177</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -36021,10 +36021,10 @@
         <v>8</v>
       </c>
       <c r="G479" t="n">
-        <v>0.8325088339222615</v>
+        <v>0.8326271186440678</v>
       </c>
       <c r="H479" t="n">
-        <v>8.407003533568904</v>
+        <v>8.410063559322035</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -36043,16 +36043,16 @@
         <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>0.4870035335689042</v>
+        <v>0.490063559322035</v>
       </c>
       <c r="N479" t="n">
-        <v>0.4870035335689042</v>
+        <v>0.490063559322035</v>
       </c>
       <c r="O479" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P479" t="n">
-        <v>-0.05607067137809274</v>
+        <v>-0.05346751412429285</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -36092,10 +36092,10 @@
         <v>8</v>
       </c>
       <c r="G480" t="n">
-        <v>0.8197879858657244</v>
+        <v>0.8199152542372882</v>
       </c>
       <c r="H480" t="n">
-        <v>8.208268551236749</v>
+        <v>8.20978813559322</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -36114,16 +36114,16 @@
         <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0.4682685512367488</v>
+        <v>0.4697881355932196</v>
       </c>
       <c r="N480" t="n">
-        <v>0.4682685512367488</v>
+        <v>0.4697881355932196</v>
       </c>
       <c r="O480" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P480" t="n">
-        <v>-0.1987349823321551</v>
+        <v>-0.2002754237288151</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -36266,34 +36266,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.731</v>
+        <v>7.689</v>
       </c>
       <c r="G2" t="n">
-        <v>7.839</v>
+        <v>7.814</v>
       </c>
       <c r="H2" t="n">
-        <v>7.917</v>
+        <v>7.912</v>
       </c>
       <c r="I2" t="n">
-        <v>7.903</v>
+        <v>7.912</v>
       </c>
       <c r="J2" t="n">
-        <v>7.765</v>
+        <v>7.714</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.138</v>
+        <v>-0.198</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -36342,34 +36342,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.577</v>
+        <v>5.574</v>
       </c>
       <c r="G3" t="n">
-        <v>5.633</v>
+        <v>5.617</v>
       </c>
       <c r="H3" t="n">
-        <v>5.692</v>
+        <v>5.668</v>
       </c>
       <c r="I3" t="n">
-        <v>5.692</v>
+        <v>5.668</v>
       </c>
       <c r="J3" t="n">
-        <v>5.601</v>
+        <v>5.586</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.091</v>
+        <v>-0.082</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -36385,13 +36385,13 @@
         <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>0.491</v>
+        <v>0.492</v>
       </c>
       <c r="P3" t="n">
         <v>0.339</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.317</v>
+        <v>0.318</v>
       </c>
       <c r="R3" t="n">
         <v>0.5679999999999999</v>
@@ -36418,34 +36418,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.251</v>
+        <v>4.154</v>
       </c>
       <c r="G4" t="n">
+        <v>4.428</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.797</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.523</v>
+      </c>
+      <c r="J4" t="n">
         <v>4.435</v>
       </c>
-      <c r="H4" t="n">
-        <v>4.547</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4.547</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.372</v>
-      </c>
       <c r="K4" t="n">
-        <v>-0.175</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -36494,34 +36494,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.103</v>
+        <v>11.522</v>
       </c>
       <c r="G5" t="n">
-        <v>11.809</v>
+        <v>11.924</v>
       </c>
       <c r="H5" t="n">
-        <v>12.212</v>
+        <v>12.289</v>
       </c>
       <c r="I5" t="n">
-        <v>11.103</v>
+        <v>11.522</v>
       </c>
       <c r="J5" t="n">
-        <v>12.21</v>
+        <v>12.248</v>
       </c>
       <c r="K5" t="n">
-        <v>1.107</v>
+        <v>0.726</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -36540,13 +36540,13 @@
         <v>4.213</v>
       </c>
       <c r="P5" t="n">
-        <v>3.916</v>
+        <v>3.917</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.916</v>
+        <v>3.917</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.727</v>
+        <v>-1.728</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -36570,34 +36570,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>59.153</v>
+        <v>59.16</v>
       </c>
       <c r="G6" t="n">
-        <v>94.63</v>
+        <v>95.617</v>
       </c>
       <c r="H6" t="n">
-        <v>113.992</v>
+        <v>113.303</v>
       </c>
       <c r="I6" t="n">
-        <v>59.18</v>
+        <v>59.422</v>
       </c>
       <c r="J6" t="n">
-        <v>110.042</v>
+        <v>109.444</v>
       </c>
       <c r="K6" t="n">
-        <v>50.862</v>
+        <v>50.022</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -36613,13 +36613,13 @@
         <v>13</v>
       </c>
       <c r="O6" t="n">
-        <v>92.017</v>
+        <v>92.018</v>
       </c>
       <c r="P6" t="n">
-        <v>88.688</v>
+        <v>88.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>88.688</v>
+        <v>88.69</v>
       </c>
       <c r="R6" t="n">
         <v>-3.322</v>
@@ -36646,38 +36646,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.725</v>
+        <v>7.72</v>
       </c>
       <c r="G7" t="n">
-        <v>7.899</v>
+        <v>7.902</v>
       </c>
       <c r="H7" t="n">
-        <v>8.092000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.092000000000001</v>
+        <v>8.048</v>
       </c>
       <c r="J7" t="n">
-        <v>8.050000000000001</v>
+        <v>8.138999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.043</v>
+        <v>0.091</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -36722,34 +36722,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.15</v>
+        <v>6.126</v>
       </c>
       <c r="G8" t="n">
-        <v>6.608</v>
+        <v>6.526</v>
       </c>
       <c r="H8" t="n">
-        <v>7.245</v>
+        <v>7.117</v>
       </c>
       <c r="I8" t="n">
-        <v>7.244</v>
+        <v>7.117</v>
       </c>
       <c r="J8" t="n">
-        <v>6.205</v>
+        <v>6.527</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.04</v>
+        <v>-0.59</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -36774,7 +36774,7 @@
         <v>0.396</v>
       </c>
       <c r="R8" t="n">
-        <v>0.828</v>
+        <v>0.829</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -36798,34 +36798,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.033</v>
+        <v>5.035</v>
       </c>
       <c r="G9" t="n">
-        <v>5.24</v>
+        <v>5.192</v>
       </c>
       <c r="H9" t="n">
-        <v>5.611</v>
+        <v>5.551</v>
       </c>
       <c r="I9" t="n">
-        <v>5.611</v>
+        <v>5.551</v>
       </c>
       <c r="J9" t="n">
-        <v>5.069</v>
+        <v>5.112</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.542</v>
+        <v>-0.439</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -36841,16 +36841,16 @@
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>0.513</v>
+        <v>0.512</v>
       </c>
       <c r="P9" t="n">
         <v>0.423</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.26</v>
+        <v>0.259</v>
       </c>
       <c r="R9" t="n">
-        <v>0.218</v>
+        <v>0.219</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -36874,34 +36874,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.216</v>
+        <v>5.15</v>
       </c>
       <c r="G10" t="n">
-        <v>5.378</v>
+        <v>5.351</v>
       </c>
       <c r="H10" t="n">
-        <v>5.437</v>
+        <v>5.438</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.37</v>
       </c>
       <c r="J10" t="n">
-        <v>5.217</v>
+        <v>5.152</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.183</v>
+        <v>-0.218</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>1.822</v>
+        <v>1.821</v>
       </c>
       <c r="P10" t="n">
         <v>1.787</v>
@@ -36950,38 +36950,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.954</v>
+        <v>3.596</v>
       </c>
       <c r="G11" t="n">
-        <v>5.702</v>
+        <v>5.456</v>
       </c>
       <c r="H11" t="n">
-        <v>8.186</v>
+        <v>6.939</v>
       </c>
       <c r="I11" t="n">
-        <v>4.944</v>
+        <v>5.679</v>
       </c>
       <c r="J11" t="n">
-        <v>5.752</v>
+        <v>4.978</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8080000000000001</v>
+        <v>-0.701</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -36996,13 +36996,13 @@
         <v>2.52</v>
       </c>
       <c r="P11" t="n">
-        <v>2.036</v>
+        <v>2.035</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.036</v>
+        <v>2.035</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.553</v>
+        <v>-0.554</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -37026,34 +37026,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.93</v>
+        <v>5.884</v>
       </c>
       <c r="G12" t="n">
-        <v>6.027</v>
+        <v>5.994</v>
       </c>
       <c r="H12" t="n">
-        <v>6.096</v>
+        <v>6.073</v>
       </c>
       <c r="I12" t="n">
-        <v>6.096</v>
+        <v>6.073</v>
       </c>
       <c r="J12" t="n">
-        <v>5.932</v>
+        <v>5.885</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.164</v>
+        <v>-0.188</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -37072,13 +37072,13 @@
         <v>0.482</v>
       </c>
       <c r="P12" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.239</v>
+        <v>-0.238</v>
       </c>
       <c r="R12" t="n">
-        <v>0.398</v>
+        <v>0.399</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -37102,34 +37102,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.602</v>
+        <v>9.564</v>
       </c>
       <c r="G13" t="n">
-        <v>9.788</v>
+        <v>9.75</v>
       </c>
       <c r="H13" t="n">
-        <v>9.976000000000001</v>
+        <v>9.920999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>9.976000000000001</v>
+        <v>9.920999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>9.66</v>
+        <v>9.663</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.316</v>
+        <v>-0.258</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -37178,34 +37178,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.566</v>
+        <v>5.489</v>
       </c>
       <c r="G14" t="n">
-        <v>5.778</v>
+        <v>5.746</v>
       </c>
       <c r="H14" t="n">
-        <v>5.912</v>
+        <v>5.913</v>
       </c>
       <c r="I14" t="n">
-        <v>5.801</v>
+        <v>5.813</v>
       </c>
       <c r="J14" t="n">
-        <v>5.572</v>
+        <v>5.489</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.229</v>
+        <v>-0.323</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>0.414</v>
+        <v>0.415</v>
       </c>
       <c r="P14" t="n">
         <v>0.35</v>
@@ -37230,7 +37230,7 @@
         <v>0.11</v>
       </c>
       <c r="R14" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -37254,34 +37254,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.562</v>
+        <v>6.561</v>
       </c>
       <c r="G15" t="n">
-        <v>6.583</v>
+        <v>6.577</v>
       </c>
       <c r="H15" t="n">
-        <v>6.626</v>
+        <v>6.586</v>
       </c>
       <c r="I15" t="n">
-        <v>6.585</v>
+        <v>6.586</v>
       </c>
       <c r="J15" t="n">
-        <v>6.596</v>
+        <v>6.578</v>
       </c>
       <c r="K15" t="n">
-        <v>0.011</v>
+        <v>-0.008</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -37300,10 +37300,10 @@
         <v>1.625</v>
       </c>
       <c r="P15" t="n">
-        <v>1.505</v>
+        <v>1.504</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.505</v>
+        <v>-1.504</v>
       </c>
       <c r="R15" t="n">
         <v>0.282</v>
@@ -37330,34 +37330,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>5.189</v>
+        <v>4.386</v>
       </c>
       <c r="G16" t="n">
-        <v>6.307</v>
+        <v>6.08</v>
       </c>
       <c r="H16" t="n">
-        <v>7.077</v>
+        <v>6.887</v>
       </c>
       <c r="I16" t="n">
-        <v>6.422</v>
+        <v>6.487</v>
       </c>
       <c r="J16" t="n">
-        <v>6.092</v>
+        <v>5.374</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.33</v>
+        <v>-1.113</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>1.538</v>
       </c>
       <c r="R16" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -37406,34 +37406,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.886</v>
+        <v>3.788</v>
       </c>
       <c r="G17" t="n">
-        <v>4.259</v>
+        <v>4.185</v>
       </c>
       <c r="H17" t="n">
-        <v>4.608</v>
+        <v>4.548</v>
       </c>
       <c r="I17" t="n">
-        <v>4.608</v>
+        <v>4.548</v>
       </c>
       <c r="J17" t="n">
-        <v>3.935</v>
+        <v>3.865</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.673</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -37449,16 +37449,16 @@
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>0.405</v>
+        <v>0.404</v>
       </c>
       <c r="P17" t="n">
         <v>0.338</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.075</v>
+        <v>-0.074</v>
       </c>
       <c r="R17" t="n">
-        <v>0.834</v>
+        <v>0.835</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -37482,34 +37482,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.446</v>
+        <v>2.405</v>
       </c>
       <c r="G18" t="n">
-        <v>2.573</v>
+        <v>2.542</v>
       </c>
       <c r="H18" t="n">
-        <v>2.675</v>
+        <v>2.638</v>
       </c>
       <c r="I18" t="n">
-        <v>2.675</v>
+        <v>2.638</v>
       </c>
       <c r="J18" t="n">
-        <v>2.449</v>
+        <v>2.406</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.226</v>
+        <v>-0.232</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -37531,10 +37531,10 @@
         <v>0.371</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.155</v>
+        <v>-0.154</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.108</v>
+        <v>-0.107</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -37558,34 +37558,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.771</v>
+        <v>5.614</v>
       </c>
       <c r="G19" t="n">
-        <v>5.891</v>
+        <v>5.848</v>
       </c>
       <c r="H19" t="n">
-        <v>6.096</v>
+        <v>5.93</v>
       </c>
       <c r="I19" t="n">
-        <v>5.963</v>
+        <v>5.93</v>
       </c>
       <c r="J19" t="n">
-        <v>5.857</v>
+        <v>5.753</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.106</v>
+        <v>-0.177</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -37601,16 +37601,16 @@
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>0.842</v>
+        <v>0.841</v>
       </c>
       <c r="P19" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.666</v>
+        <v>-0.665</v>
       </c>
       <c r="R19" t="n">
-        <v>0.505</v>
+        <v>0.504</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -486,7 +486,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>300024</v>
+        <v>300042</v>
       </c>
       <c r="E2" t="n">
         <v>151106</v>
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -683,28 +683,28 @@
         <v>9.765000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>7.758</v>
+        <v>7.759</v>
       </c>
       <c r="J2" t="n">
         <v>-1.52</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.007</v>
+        <v>-2.006</v>
       </c>
       <c r="L2" t="n">
-        <v>0.396</v>
+        <v>0.397</v>
       </c>
       <c r="M2" t="n">
-        <v>0.397</v>
+        <v>0.398</v>
       </c>
       <c r="N2" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="O2" t="n">
         <v>0.865</v>
       </c>
       <c r="P2" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="Q2" t="n">
         <v>0.829</v>
@@ -765,13 +765,13 @@
         <v>7.883</v>
       </c>
       <c r="I3" t="n">
-        <v>5.832</v>
+        <v>5.834</v>
       </c>
       <c r="J3" t="n">
         <v>-2.472</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.051</v>
+        <v>-2.049</v>
       </c>
       <c r="L3" t="n">
         <v>-1.787</v>
@@ -786,7 +786,7 @@
         <v>0.89</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.599</v>
+        <v>-4.597</v>
       </c>
       <c r="Q3" t="n">
         <v>0.758</v>
@@ -847,7 +847,7 @@
         <v>7.691</v>
       </c>
       <c r="I4" t="n">
-        <v>4.845</v>
+        <v>4.846</v>
       </c>
       <c r="J4" t="n">
         <v>-3.405</v>
@@ -929,13 +929,13 @@
         <v>7.178</v>
       </c>
       <c r="I5" t="n">
-        <v>5.973</v>
+        <v>5.975</v>
       </c>
       <c r="J5" t="n">
         <v>-2.275</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.205</v>
+        <v>-1.202</v>
       </c>
       <c r="L5" t="n">
         <v>0.318</v>
@@ -950,10 +950,10 @@
         <v>0.931</v>
       </c>
       <c r="P5" t="n">
-        <v>0.555</v>
+        <v>0.554</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="R5" t="n">
         <v>55.172</v>
@@ -1011,13 +1011,13 @@
         <v>8.468</v>
       </c>
       <c r="I6" t="n">
-        <v>6.232</v>
+        <v>6.234</v>
       </c>
       <c r="J6" t="n">
         <v>-2.07</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.236</v>
+        <v>-2.234</v>
       </c>
       <c r="L6" t="n">
         <v>0.11</v>
@@ -1093,13 +1093,13 @@
         <v>9.374000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.210000000000001</v>
+        <v>8.211</v>
       </c>
       <c r="J7" t="n">
         <v>-2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.165</v>
+        <v>-1.163</v>
       </c>
       <c r="L7" t="n">
         <v>-0.665</v>
@@ -1175,19 +1175,19 @@
         <v>9.863</v>
       </c>
       <c r="I8" t="n">
-        <v>7.938</v>
+        <v>7.94</v>
       </c>
       <c r="J8" t="n">
         <v>-2.008</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.924</v>
+        <v>-1.923</v>
       </c>
       <c r="L8" t="n">
-        <v>5.811</v>
+        <v>5.812</v>
       </c>
       <c r="M8" t="n">
-        <v>5.811</v>
+        <v>5.812</v>
       </c>
       <c r="N8" t="n">
         <v>5.831</v>
@@ -1196,7 +1196,7 @@
         <v>0.831</v>
       </c>
       <c r="P8" t="n">
-        <v>-45.94</v>
+        <v>-45.945</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.024</v>
@@ -1266,19 +1266,19 @@
         <v>-0.378</v>
       </c>
       <c r="L9" t="n">
-        <v>0.29</v>
+        <v>0.291</v>
       </c>
       <c r="M9" t="n">
         <v>0.8179999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.949</v>
+        <v>0.95</v>
       </c>
       <c r="O9" t="n">
         <v>-0.001</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.668</v>
+        <v>-0.669</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.042</v>
@@ -1339,13 +1339,13 @@
         <v>11.017</v>
       </c>
       <c r="I10" t="n">
-        <v>11.498</v>
+        <v>11.489</v>
       </c>
       <c r="J10" t="n">
         <v>-1.39</v>
       </c>
       <c r="K10" t="n">
-        <v>0.482</v>
+        <v>0.472</v>
       </c>
       <c r="L10" t="n">
         <v>3.917</v>
@@ -1357,10 +1357,10 @@
         <v>4.213</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.492</v>
+        <v>-0.491</v>
       </c>
       <c r="P10" t="n">
-        <v>-105.539</v>
+        <v>-105.534</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.728</v>
@@ -1418,25 +1418,25 @@
         <v>5.32</v>
       </c>
       <c r="H11" t="n">
-        <v>112.892</v>
+        <v>112.894</v>
       </c>
       <c r="I11" t="n">
-        <v>108.41</v>
+        <v>108.414</v>
       </c>
       <c r="J11" t="n">
         <v>-1.68</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.482</v>
+        <v>-4.48</v>
       </c>
       <c r="L11" t="n">
-        <v>88.69</v>
+        <v>88.691</v>
       </c>
       <c r="M11" t="n">
-        <v>88.69</v>
+        <v>88.691</v>
       </c>
       <c r="N11" t="n">
-        <v>92.018</v>
+        <v>92.02</v>
       </c>
       <c r="O11" t="n">
         <v>-0.358</v>
@@ -1459,16 +1459,16 @@
         <v>9965</v>
       </c>
       <c r="U11" t="n">
-        <v>0.129</v>
+        <v>0.128</v>
       </c>
       <c r="V11" t="n">
         <v>-0.737</v>
       </c>
       <c r="W11" t="n">
-        <v>0.129</v>
+        <v>0.128</v>
       </c>
       <c r="X11" t="n">
-        <v>36.185</v>
+        <v>36.187</v>
       </c>
     </row>
     <row r="12">
@@ -1585,13 +1585,13 @@
         <v>5.956</v>
       </c>
       <c r="I13" t="n">
-        <v>5.12</v>
+        <v>5.116</v>
       </c>
       <c r="J13" t="n">
         <v>-0.6919999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.836</v>
+        <v>-0.84</v>
       </c>
       <c r="L13" t="n">
         <v>0.259</v>
@@ -1606,10 +1606,10 @@
         <v>0.441</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.082</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.219</v>
+        <v>0.221</v>
       </c>
       <c r="R13" t="n">
         <v>17.241</v>
@@ -1667,28 +1667,28 @@
         <v>7.097</v>
       </c>
       <c r="I14" t="n">
-        <v>5.209</v>
+        <v>5.203</v>
       </c>
       <c r="J14" t="n">
         <v>-2.422</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.888</v>
+        <v>-1.893</v>
       </c>
       <c r="L14" t="n">
-        <v>2.035</v>
+        <v>2.034</v>
       </c>
       <c r="M14" t="n">
-        <v>2.035</v>
+        <v>2.034</v>
       </c>
       <c r="N14" t="n">
-        <v>2.52</v>
+        <v>2.519</v>
       </c>
       <c r="O14" t="n">
         <v>0.615</v>
       </c>
       <c r="P14" t="n">
-        <v>-10.092</v>
+        <v>-10.085</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.554</v>
@@ -1749,13 +1749,13 @@
         <v>8.144</v>
       </c>
       <c r="I15" t="n">
-        <v>6.358</v>
+        <v>6.36</v>
       </c>
       <c r="J15" t="n">
         <v>-1.525</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.786</v>
+        <v>-1.784</v>
       </c>
       <c r="L15" t="n">
         <v>-0.238</v>
@@ -1767,13 +1767,13 @@
         <v>0.482</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.195</v>
+        <v>-0.193</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.399</v>
+        <v>0.4</v>
       </c>
       <c r="R15" t="n">
         <v>41.379</v>
@@ -1796,7 +1796,7 @@
         <v>0.781</v>
       </c>
       <c r="X15" t="n">
-        <v>2.285</v>
+        <v>2.284</v>
       </c>
     </row>
     <row r="16">
@@ -1913,13 +1913,13 @@
         <v>8.029999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>6.683</v>
+        <v>6.685</v>
       </c>
       <c r="J17" t="n">
         <v>-2.425</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.348</v>
+        <v>-1.345</v>
       </c>
       <c r="L17" t="n">
         <v>-1.504</v>
@@ -1931,13 +1931,13 @@
         <v>1.625</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6</v>
+        <v>0.599</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.677</v>
+        <v>-3.676</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.282</v>
+        <v>0.281</v>
       </c>
       <c r="R17" t="n">
         <v>31.034</v>
@@ -1995,28 +1995,28 @@
         <v>7.154</v>
       </c>
       <c r="I18" t="n">
-        <v>6.291</v>
+        <v>6.287</v>
       </c>
       <c r="J18" t="n">
         <v>-1.55</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.864</v>
+        <v>-0.867</v>
       </c>
       <c r="L18" t="n">
-        <v>1.538</v>
+        <v>1.537</v>
       </c>
       <c r="M18" t="n">
-        <v>1.538</v>
+        <v>1.537</v>
       </c>
       <c r="N18" t="n">
-        <v>1.726</v>
+        <v>1.725</v>
       </c>
       <c r="O18" t="n">
-        <v>0.61</v>
+        <v>0.611</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.623</v>
+        <v>-6.618</v>
       </c>
       <c r="Q18" t="n">
         <v>0.229</v>
@@ -2074,34 +2074,34 @@
         <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.499</v>
+        <v>3.501</v>
       </c>
       <c r="I19" t="n">
-        <v>3.111</v>
+        <v>3.112</v>
       </c>
       <c r="J19" t="n">
         <v>-1.34</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.388</v>
+        <v>-0.389</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.154</v>
+        <v>-0.153</v>
       </c>
       <c r="M19" t="n">
         <v>0.371</v>
       </c>
       <c r="N19" t="n">
-        <v>0.485</v>
+        <v>0.484</v>
       </c>
       <c r="O19" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.408</v>
+        <v>-0.406</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.107</v>
+        <v>-0.106</v>
       </c>
       <c r="R19" t="n">
         <v>46.154</v>
@@ -2121,7 +2121,7 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="X19" t="n">
         <v>1.725</v>
@@ -3392,10 +3392,10 @@
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8538135593220338</v>
+        <v>0.8539167254763586</v>
       </c>
       <c r="H18" t="n">
-        <v>8.171588983050848</v>
+        <v>8.171916019760056</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>5.716588983050848</v>
+        <v>5.716916019760056</v>
       </c>
       <c r="N18" t="n">
-        <v>5.716588983050848</v>
+        <v>5.716916019760056</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1374999999999997</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7284390477830698</v>
+        <v>-0.7281120110738613</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8509887005649718</v>
+        <v>0.8510938602681722</v>
       </c>
       <c r="H19" t="n">
-        <v>8.158225635593221</v>
+        <v>8.15847565278758</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3485,16 +3485,16 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.745725635593221</v>
+        <v>5.74597565278758</v>
       </c>
       <c r="N19" t="n">
-        <v>5.745725635593221</v>
+        <v>5.74597565278758</v>
       </c>
       <c r="O19" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.01336334745762713</v>
+        <v>-0.01344036697247653</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8467514124293786</v>
+        <v>0.8468595624558928</v>
       </c>
       <c r="H20" t="n">
-        <v>8.135504943502827</v>
+        <v>8.136362032462952</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3556,16 +3556,16 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>5.735504943502827</v>
+        <v>5.736362032462951</v>
       </c>
       <c r="N20" t="n">
-        <v>5.735504943502827</v>
+        <v>5.736362032462951</v>
       </c>
       <c r="O20" t="n">
         <v>-0.01250000000000018</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.02272069209039351</v>
+        <v>-0.02211362032462816</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8439265536723164</v>
+        <v>0.8440366972477065</v>
       </c>
       <c r="H21" t="n">
-        <v>8.120247175141243</v>
+        <v>8.120596330275228</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>5.950247175141243</v>
+        <v>5.950596330275228</v>
       </c>
       <c r="N21" t="n">
-        <v>5.950247175141243</v>
+        <v>5.950596330275228</v>
       </c>
       <c r="O21" t="n">
         <v>-0.23</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.01525776836158421</v>
+        <v>-0.01576570218772311</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8389830508474576</v>
+        <v>0.8390966831333804</v>
       </c>
       <c r="H22" t="n">
-        <v>8.099152542372881</v>
+        <v>8.099872971065631</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3698,16 +3698,16 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>6.119152542372881</v>
+        <v>6.119872971065631</v>
       </c>
       <c r="N22" t="n">
-        <v>6.119152542372881</v>
+        <v>6.119872971065631</v>
       </c>
       <c r="O22" t="n">
         <v>-0.1899999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.02109463276836188</v>
+        <v>-0.02072335920959745</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8340395480225988</v>
+        <v>0.8341566690190544</v>
       </c>
       <c r="H23" t="n">
-        <v>8.065621468926553</v>
+        <v>8.067106563161609</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3769,16 +3769,16 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>6.015621468926553</v>
+        <v>6.017106563161609</v>
       </c>
       <c r="N23" t="n">
-        <v>6.015621468926553</v>
+        <v>6.017106563161609</v>
       </c>
       <c r="O23" t="n">
         <v>0.06999999999999984</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.03353107344632811</v>
+        <v>-0.03276640790402219</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.827683615819209</v>
+        <v>0.8278052223006351</v>
       </c>
       <c r="H24" t="n">
         <v>8.030000000000001</v>
@@ -3849,7 +3849,7 @@
         <v>0.1700000000000004</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.03562146892655171</v>
+        <v>-0.03710656316160765</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8227401129943502</v>
+        <v>0.8228652081863091</v>
       </c>
       <c r="H25" t="n">
-        <v>8.014043079096044</v>
+        <v>8.014241354975301</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3911,16 +3911,16 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>5.664043079096045</v>
+        <v>5.664241354975301</v>
       </c>
       <c r="N25" t="n">
-        <v>5.664043079096045</v>
+        <v>5.664241354975301</v>
       </c>
       <c r="O25" t="n">
         <v>0.1299999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01595692090395673</v>
+        <v>-0.01575864502470026</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3960,10 +3960,10 @@
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8199152542372882</v>
+        <v>0.8200423429781228</v>
       </c>
       <c r="H26" t="n">
-        <v>8.003697033898305</v>
+        <v>8.004301340860973</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3982,16 +3982,16 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>5.703697033898306</v>
+        <v>5.704301340860973</v>
       </c>
       <c r="N26" t="n">
-        <v>5.703697033898306</v>
+        <v>5.704301340860973</v>
       </c>
       <c r="O26" t="n">
         <v>-0.05000000000000027</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.01034604519773907</v>
+        <v>-0.009940014114327766</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8163841807909604</v>
+        <v>0.8165137614678899</v>
       </c>
       <c r="H27" t="n">
-        <v>7.980282485875706</v>
+        <v>7.981720183486239</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4053,16 +4053,16 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>5.750282485875706</v>
+        <v>5.751720183486238</v>
       </c>
       <c r="N27" t="n">
-        <v>5.750282485875706</v>
+        <v>5.751720183486238</v>
       </c>
       <c r="O27" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.02341454802259957</v>
+        <v>-0.02258115737473432</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8121468926553672</v>
+        <v>0.8122794636556104</v>
       </c>
       <c r="H28" t="n">
-        <v>7.949505649717515</v>
+        <v>7.949925899788285</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>5.889505649717515</v>
+        <v>5.889925899788285</v>
       </c>
       <c r="N28" t="n">
-        <v>5.889505649717515</v>
+        <v>5.889925899788285</v>
       </c>
       <c r="O28" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.03077683615819105</v>
+        <v>-0.03179428369795367</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8128531073446328</v>
+        <v>0.8129851799576571</v>
       </c>
       <c r="H29" t="n">
-        <v>7.954360875706215</v>
+        <v>7.955407551164432</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4195,16 +4195,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>6.004360875706214</v>
+        <v>6.005407551164431</v>
       </c>
       <c r="N29" t="n">
-        <v>6.004360875706214</v>
+        <v>6.005407551164431</v>
       </c>
       <c r="O29" t="n">
         <v>-0.1100000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>0.004855225988699807</v>
+        <v>0.005481651376146424</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8135593220338984</v>
+        <v>0.8136908962597036</v>
       </c>
       <c r="H30" t="n">
-        <v>7.959957627118643</v>
+        <v>7.961000352858149</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4266,16 +4266,16 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.259957627118643</v>
+        <v>5.261000352858149</v>
       </c>
       <c r="N30" t="n">
-        <v>5.259957627118643</v>
+        <v>5.261000352858149</v>
       </c>
       <c r="O30" t="n">
         <v>0.7500000000000002</v>
       </c>
       <c r="P30" t="n">
-        <v>0.00559675141242888</v>
+        <v>0.005592801693717675</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8100282485875706</v>
+        <v>0.8101623147494708</v>
       </c>
       <c r="H31" t="n">
-        <v>7.938368644067797</v>
+        <v>7.939643613267467</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4337,16 +4337,16 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.138368644067797</v>
+        <v>5.139643613267467</v>
       </c>
       <c r="N31" t="n">
-        <v>5.138368644067797</v>
+        <v>5.139643613267467</v>
       </c>
       <c r="O31" t="n">
         <v>0.09999999999999964</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.02158898305084644</v>
+        <v>-0.02135673959068196</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6497175141242938</v>
+        <v>0.6499647141848977</v>
       </c>
       <c r="H48" t="n">
-        <v>6.159454449152543</v>
+        <v>6.159549003175724</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5538,16 +5538,16 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1280455508474567</v>
+        <v>-0.1279509968242758</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1280455508474567</v>
+        <v>0.1279509968242758</v>
       </c>
       <c r="O48" t="n">
         <v>-0.09250000000000114</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.6244348290534836</v>
+        <v>-0.6243402750303026</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>0.643361581920904</v>
+        <v>0.6436132674664785</v>
       </c>
       <c r="H49" t="n">
-        <v>6.148686440677967</v>
+        <v>6.149456598447425</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5609,16 +5609,16 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.02131355932203327</v>
+        <v>-0.02054340155257517</v>
       </c>
       <c r="N49" t="n">
-        <v>0.02131355932203327</v>
+        <v>0.02054340155257517</v>
       </c>
       <c r="O49" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.01076800847457626</v>
+        <v>-0.01009240472829909</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5658,10 +5658,10 @@
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>0.635593220338983</v>
+        <v>0.6358503881439661</v>
       </c>
       <c r="H50" t="n">
-        <v>6.125932203389831</v>
+        <v>6.126561750176429</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5680,16 +5680,16 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.03593220338983105</v>
+        <v>0.03656175017642926</v>
       </c>
       <c r="N50" t="n">
-        <v>0.03593220338983105</v>
+        <v>0.03656175017642926</v>
       </c>
       <c r="O50" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.02275423728813575</v>
+        <v>-0.02289484827099564</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5729,10 +5729,10 @@
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>0.634180790960452</v>
+        <v>0.634438955539873</v>
       </c>
       <c r="H51" t="n">
-        <v>6.122474576271187</v>
+        <v>6.123106563161609</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5751,16 +5751,16 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2624745762711864</v>
+        <v>0.2631065631616085</v>
       </c>
       <c r="N51" t="n">
-        <v>0.2624745762711864</v>
+        <v>0.2631065631616085</v>
       </c>
       <c r="O51" t="n">
         <v>-0.2299999999999995</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.003457627118644169</v>
+        <v>-0.003455187014820282</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>0.6454802259887006</v>
+        <v>0.6457304163726182</v>
       </c>
       <c r="H52" t="n">
-        <v>6.157833686440679</v>
+        <v>6.157929384262527</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5822,16 +5822,16 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4978336864406785</v>
+        <v>0.4979293842625268</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4978336864406785</v>
+        <v>0.4979293842625268</v>
       </c>
       <c r="O52" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P52" t="n">
-        <v>0.03535911016949189</v>
+        <v>0.03482282110091806</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6532485875706214</v>
+        <v>0.6534932956951306</v>
       </c>
       <c r="H53" t="n">
-        <v>6.168940677966101</v>
+        <v>6.169689484827099</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5893,16 +5893,16 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5389406779661012</v>
+        <v>0.5396894848270994</v>
       </c>
       <c r="N53" t="n">
-        <v>0.5389406779661012</v>
+        <v>0.5396894848270994</v>
       </c>
       <c r="O53" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P53" t="n">
-        <v>0.01110699152542249</v>
+        <v>0.01176010056457244</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.663135593220339</v>
+        <v>0.6633733239237827</v>
       </c>
       <c r="H54" t="n">
-        <v>6.208926553672317</v>
+        <v>6.209896494942367</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5964,16 +5964,16 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.618926553672317</v>
+        <v>0.6198964949423669</v>
       </c>
       <c r="N54" t="n">
-        <v>0.618926553672317</v>
+        <v>0.6198964949423669</v>
       </c>
       <c r="O54" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P54" t="n">
-        <v>0.0399858757062157</v>
+        <v>0.04020701011526739</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6694915254237288</v>
+        <v>0.6697247706422018</v>
       </c>
       <c r="H55" t="n">
-        <v>6.219322033898305</v>
+        <v>6.219678899082568</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6035,16 +6035,16 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7693220338983044</v>
+        <v>0.7696788990825683</v>
       </c>
       <c r="N55" t="n">
-        <v>0.7693220338983044</v>
+        <v>0.7696788990825683</v>
       </c>
       <c r="O55" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P55" t="n">
-        <v>0.0103954802259878</v>
+        <v>0.009782404140201706</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6659604519774012</v>
+        <v>0.666196189131969</v>
       </c>
       <c r="H56" t="n">
-        <v>6.213919491525424</v>
+        <v>6.214280169371913</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6106,16 +6106,16 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8139194915254233</v>
+        <v>0.8142801693719122</v>
       </c>
       <c r="N56" t="n">
-        <v>0.8139194915254233</v>
+        <v>0.8142801693719122</v>
       </c>
       <c r="O56" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.005402542372880959</v>
+        <v>-0.005398729710655914</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
         <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6546610169491526</v>
+        <v>0.6549047282992237</v>
       </c>
       <c r="H57" t="n">
-        <v>6.176525423728814</v>
+        <v>6.178016937191249</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8065254237288135</v>
+        <v>0.8080169371912493</v>
       </c>
       <c r="N57" t="n">
-        <v>0.8065254237288135</v>
+        <v>0.8080169371912493</v>
       </c>
       <c r="O57" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.03739406779661003</v>
+        <v>-0.03626323218066307</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6226,10 +6226,10 @@
         <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6391242937853108</v>
+        <v>0.639378969654199</v>
       </c>
       <c r="H58" t="n">
-        <v>6.137146892655367</v>
+        <v>6.137666431427899</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6248,16 +6248,16 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8071468926553669</v>
+        <v>0.807666431427899</v>
       </c>
       <c r="N58" t="n">
-        <v>0.8071468926553669</v>
+        <v>0.807666431427899</v>
       </c>
       <c r="O58" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.03937853107344669</v>
+        <v>-0.04035050576335042</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6297,10 +6297,10 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6207627118644068</v>
+        <v>0.621030345800988</v>
       </c>
       <c r="H59" t="n">
-        <v>6.079378531073447</v>
+        <v>6.080705716302047</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6319,16 +6319,16 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9293785310734464</v>
+        <v>0.9307057163020467</v>
       </c>
       <c r="N59" t="n">
-        <v>0.9293785310734464</v>
+        <v>0.9307057163020467</v>
       </c>
       <c r="O59" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.05776836158192022</v>
+        <v>-0.05696071512585199</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>0.606638418079096</v>
+        <v>0.6069160197600565</v>
       </c>
       <c r="H60" t="n">
-        <v>6.032627118644069</v>
+        <v>6.034326040931546</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6390,16 +6390,16 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1.062627118644069</v>
+        <v>1.064326040931546</v>
       </c>
       <c r="N60" t="n">
-        <v>1.062627118644069</v>
+        <v>1.064326040931546</v>
       </c>
       <c r="O60" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.04675141242937819</v>
+        <v>-0.04637967537050081</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6439,10 +6439,10 @@
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5918079096045198</v>
+        <v>0.5920959774170783</v>
       </c>
       <c r="H61" t="n">
-        <v>5.972796610169492</v>
+        <v>5.975441072688779</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6461,16 +6461,16 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1.142796610169492</v>
+        <v>1.145441072688778</v>
       </c>
       <c r="N61" t="n">
-        <v>1.142796610169492</v>
+        <v>1.145441072688778</v>
       </c>
       <c r="O61" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.05983050847457694</v>
+        <v>-0.05888496824276768</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -7640,10 +7640,10 @@
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8975988700564972</v>
+        <v>0.8976711362032463</v>
       </c>
       <c r="H78" t="n">
-        <v>5.880123587570623</v>
+        <v>5.881173253352154</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7662,16 +7662,16 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1.192623587570623</v>
+        <v>1.193673253352154</v>
       </c>
       <c r="N78" t="n">
-        <v>1.192623587570623</v>
+        <v>1.193673253352154</v>
       </c>
       <c r="O78" t="n">
         <v>0.2725</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.0617019204882423</v>
+        <v>-0.06065225470671098</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8686440677966102</v>
+        <v>0.8687367678193366</v>
       </c>
       <c r="H79" t="n">
-        <v>5.693644067796611</v>
+        <v>5.694721242060692</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7733,16 +7733,16 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>1.281144067796611</v>
+        <v>1.282221242060692</v>
       </c>
       <c r="N79" t="n">
-        <v>1.281144067796611</v>
+        <v>1.282221242060692</v>
       </c>
       <c r="O79" t="n">
         <v>-0.2750000000000004</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.1864795197740117</v>
+        <v>-0.186452011291462</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>0.826271186440678</v>
+        <v>0.826393789696542</v>
       </c>
       <c r="H80" t="n">
-        <v>5.415635593220339</v>
+        <v>5.416347918136909</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7804,16 +7804,16 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7656355932203383</v>
+        <v>0.7663479181369084</v>
       </c>
       <c r="N80" t="n">
-        <v>0.7656355932203383</v>
+        <v>0.7663479181369084</v>
       </c>
       <c r="O80" t="n">
         <v>0.2375000000000007</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.2780084745762723</v>
+        <v>-0.2783733239237831</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7796610169491526</v>
+        <v>0.7798165137614679</v>
       </c>
       <c r="H81" t="n">
-        <v>5.154830508474576</v>
+        <v>5.155366972477063</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7875,16 +7875,16 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>0.4548305084745756</v>
+        <v>0.455366972477063</v>
       </c>
       <c r="N81" t="n">
-        <v>0.4548305084745756</v>
+        <v>0.455366972477063</v>
       </c>
       <c r="O81" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.2608050847457628</v>
+        <v>-0.2609809456598455</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7337570621468926</v>
+        <v>0.7339449541284404</v>
       </c>
       <c r="H82" t="n">
-        <v>4.998128531073446</v>
+        <v>4.999220183486239</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7946,16 +7946,16 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5931285310734467</v>
+        <v>0.5942201834862395</v>
       </c>
       <c r="N82" t="n">
-        <v>0.5931285310734467</v>
+        <v>0.5942201834862395</v>
       </c>
       <c r="O82" t="n">
         <v>-0.2950000000000008</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.1567019774011298</v>
+        <v>-0.1561467889908243</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -7995,10 +7995,10 @@
         <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7076271186440678</v>
+        <v>0.707833450952717</v>
       </c>
       <c r="H83" t="n">
-        <v>4.871313559322034</v>
+        <v>4.872512350035286</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8017,16 +8017,16 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>0.7738135593220345</v>
+        <v>0.7750123500352863</v>
       </c>
       <c r="N83" t="n">
-        <v>0.7738135593220345</v>
+        <v>0.7750123500352863</v>
       </c>
       <c r="O83" t="n">
         <v>-0.3075000000000001</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.1268149717514122</v>
+        <v>-0.1267078334509533</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -8066,10 +8066,10 @@
         <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>0.6758474576271186</v>
+        <v>0.6760762173606211</v>
       </c>
       <c r="H84" t="n">
-        <v>4.786192493946731</v>
+        <v>4.786572235104345</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8088,16 +8088,16 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>0.9361924939467312</v>
+        <v>0.9365722351043453</v>
       </c>
       <c r="N84" t="n">
-        <v>0.9361924939467312</v>
+        <v>0.9365722351043453</v>
       </c>
       <c r="O84" t="n">
         <v>-0.2474999999999992</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.08512106537530251</v>
+        <v>-0.08594011493094023</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6412429378531074</v>
+        <v>0.6414961185603387</v>
       </c>
       <c r="H85" t="n">
-        <v>4.688436911487759</v>
+        <v>4.688682074805929</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8159,16 +8159,16 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9084369114877595</v>
+        <v>0.9086820748059288</v>
       </c>
       <c r="N85" t="n">
-        <v>0.9084369114877595</v>
+        <v>0.9086820748059288</v>
       </c>
       <c r="O85" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.09775558245897198</v>
+        <v>-0.0978901602984168</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6031073446327684</v>
+        <v>0.6033874382498235</v>
       </c>
       <c r="H86" t="n">
-        <v>4.544053672316384</v>
+        <v>4.545681016231475</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8230,16 +8230,16 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.2559463276836169</v>
+        <v>-0.2543189837685258</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2559463276836169</v>
+        <v>0.2543189837685258</v>
       </c>
       <c r="O86" t="n">
         <v>1.020000000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.1443832391713755</v>
+        <v>-0.1430010585744537</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -8279,10 +8279,10 @@
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>0.596045197740113</v>
+        <v>0.5956245589273113</v>
       </c>
       <c r="H87" t="n">
-        <v>4.516511299435028</v>
+        <v>4.515289343683839</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8301,16 +8301,16 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.1834887005649719</v>
+        <v>-0.1847106563161613</v>
       </c>
       <c r="N87" t="n">
-        <v>0.1834887005649719</v>
+        <v>0.1847106563161613</v>
       </c>
       <c r="O87" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.02754237288135553</v>
+        <v>-0.03039167254763608</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -8350,10 +8350,10 @@
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>0.614406779661017</v>
+        <v>0.6146788990825688</v>
       </c>
       <c r="H88" t="n">
-        <v>4.573135593220339</v>
+        <v>4.574189602446483</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8372,16 +8372,16 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.6268644067796609</v>
+        <v>-0.6258103975535168</v>
       </c>
       <c r="N88" t="n">
-        <v>0.6268644067796609</v>
+        <v>0.6258103975535168</v>
       </c>
       <c r="O88" t="n">
         <v>0.5</v>
       </c>
       <c r="P88" t="n">
-        <v>0.05662429378531098</v>
+        <v>0.0589002587626446</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6588983050847458</v>
+        <v>0.6591390261115032</v>
       </c>
       <c r="H89" t="n">
-        <v>4.724099576271186</v>
+        <v>4.724798870853917</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8443,16 +8443,16 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.7759004237288138</v>
+        <v>-0.7752011291460832</v>
       </c>
       <c r="N89" t="n">
-        <v>0.7759004237288138</v>
+        <v>0.7752011291460832</v>
       </c>
       <c r="O89" t="n">
         <v>0.2999999999999998</v>
       </c>
       <c r="P89" t="n">
-        <v>0.1509639830508469</v>
+        <v>0.1506092684074334</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8492,10 +8492,10 @@
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6822033898305084</v>
+        <v>0.6824276640790402</v>
       </c>
       <c r="H90" t="n">
-        <v>4.795900423728813</v>
+        <v>4.796226182074806</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8514,16 +8514,16 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-1.084099576271186</v>
+        <v>-1.083773817925194</v>
       </c>
       <c r="N90" t="n">
-        <v>1.084099576271186</v>
+        <v>1.083773817925194</v>
       </c>
       <c r="O90" t="n">
         <v>0.3799999999999999</v>
       </c>
       <c r="P90" t="n">
-        <v>0.07180084745762727</v>
+        <v>0.07142731122088897</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6850282485875706</v>
+        <v>0.6852505292872265</v>
       </c>
       <c r="H91" t="n">
         <v>4.8</v>
@@ -8594,7 +8594,7 @@
         <v>-0.8600000000000003</v>
       </c>
       <c r="P91" t="n">
-        <v>0.0040995762711864</v>
+        <v>0.003773817925194045</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -9764,10 +9764,10 @@
         <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8912429378531074</v>
+        <v>0.8913196894848271</v>
       </c>
       <c r="H108" t="n">
-        <v>12.38334745762712</v>
+        <v>12.38351093860268</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -9786,16 +9786,16 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>5.31334745762712</v>
+        <v>5.313510938602682</v>
       </c>
       <c r="N108" t="n">
-        <v>5.31334745762712</v>
+        <v>5.313510938602682</v>
       </c>
       <c r="O108" t="n">
         <v>-0.1250000000000009</v>
       </c>
       <c r="P108" t="n">
-        <v>4.41376792013588</v>
+        <v>4.413931401111443</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -9835,10 +9835,10 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>0.8870056497175142</v>
+        <v>0.8870853916725476</v>
       </c>
       <c r="H109" t="n">
-        <v>12.34254237288136</v>
+        <v>12.34441072688779</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -9857,16 +9857,16 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>5.472542372881356</v>
+        <v>5.474410726887791</v>
       </c>
       <c r="N109" t="n">
-        <v>5.472542372881356</v>
+        <v>5.474410726887791</v>
       </c>
       <c r="O109" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.04080508474576305</v>
+        <v>-0.03910021171489042</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -9906,10 +9906,10 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8848870056497176</v>
+        <v>0.884968242766408</v>
       </c>
       <c r="H110" t="n">
-        <v>12.2919279661017</v>
+        <v>12.29244707127735</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -9928,16 +9928,16 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>5.551927966101696</v>
+        <v>5.552447071277347</v>
       </c>
       <c r="N110" t="n">
-        <v>5.551927966101696</v>
+        <v>5.552447071277347</v>
       </c>
       <c r="O110" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.05061440677966011</v>
+        <v>-0.05196365561044303</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -9977,10 +9977,10 @@
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>0.882768361581921</v>
+        <v>0.8828510938602682</v>
       </c>
       <c r="H111" t="n">
-        <v>12.27838983050848</v>
+        <v>12.27891848976711</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -9999,16 +9999,16 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>5.678389830508475</v>
+        <v>5.678918489767113</v>
       </c>
       <c r="N111" t="n">
-        <v>5.678389830508475</v>
+        <v>5.678918489767113</v>
       </c>
       <c r="O111" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P111" t="n">
-        <v>-0.0135381355932207</v>
+        <v>-0.01352858151023462</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -10048,10 +10048,10 @@
         <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>0.876412429378531</v>
+        <v>0.876499647141849</v>
       </c>
       <c r="H112" t="n">
-        <v>12.22351694915254</v>
+        <v>12.22388849682428</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10070,16 +10070,16 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>5.363516949152543</v>
+        <v>5.363888496824278</v>
       </c>
       <c r="N112" t="n">
-        <v>5.363516949152543</v>
+        <v>5.363888496824278</v>
       </c>
       <c r="O112" t="n">
         <v>0.2600000000000007</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.05487288135593182</v>
+        <v>-0.05502999294283484</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>0.8679378531073446</v>
+        <v>0.8680310515172901</v>
       </c>
       <c r="H113" t="n">
-        <v>12.19120762711864</v>
+        <v>12.19140613973183</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -10141,16 +10141,16 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>5.211207627118643</v>
+        <v>5.211406139731826</v>
       </c>
       <c r="N113" t="n">
-        <v>5.211207627118643</v>
+        <v>5.211406139731826</v>
       </c>
       <c r="O113" t="n">
         <v>0.1200000000000001</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.03230932203389969</v>
+        <v>-0.03248235709245151</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -10190,10 +10190,10 @@
         <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8573446327683616</v>
+        <v>0.8574453069865914</v>
       </c>
       <c r="H114" t="n">
-        <v>12.12186440677966</v>
+        <v>12.12315102328864</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -10212,16 +10212,16 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>5.271864406779661</v>
+        <v>5.273151023288639</v>
       </c>
       <c r="N114" t="n">
-        <v>5.271864406779661</v>
+        <v>5.273151023288639</v>
       </c>
       <c r="O114" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P114" t="n">
-        <v>-0.06934322033898255</v>
+        <v>-0.06825511644318816</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
         <v>8</v>
       </c>
       <c r="G115" t="n">
-        <v>0.8467514124293786</v>
+        <v>0.8468595624558928</v>
       </c>
       <c r="H115" t="n">
-        <v>12.07716101694915</v>
+        <v>12.0776217360621</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -10283,16 +10283,16 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>5.337161016949151</v>
+        <v>5.337621736062102</v>
       </c>
       <c r="N115" t="n">
-        <v>5.337161016949151</v>
+        <v>5.337621736062102</v>
       </c>
       <c r="O115" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.04470338983050937</v>
+        <v>-0.04552928722653604</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -10332,10 +10332,10 @@
         <v>8</v>
       </c>
       <c r="G116" t="n">
-        <v>0.8248587570621468</v>
+        <v>0.8249823570924488</v>
       </c>
       <c r="H116" t="n">
-        <v>11.86389830508474</v>
+        <v>11.86442484121383</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -10354,16 +10354,16 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>5.258898305084744</v>
+        <v>5.25942484121383</v>
       </c>
       <c r="N116" t="n">
-        <v>5.258898305084744</v>
+        <v>5.25942484121383</v>
       </c>
       <c r="O116" t="n">
         <v>-0.1349999999999998</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.2132627118644077</v>
+        <v>-0.2131968948482719</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10403,10 +10403,10 @@
         <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>0.8100282485875706</v>
+        <v>0.8101623147494708</v>
       </c>
       <c r="H117" t="n">
-        <v>11.81036016949153</v>
+        <v>11.81064573041637</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -10425,16 +10425,16 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>5.430360169491526</v>
+        <v>5.430645730416374</v>
       </c>
       <c r="N117" t="n">
-        <v>5.430360169491526</v>
+        <v>5.430645730416374</v>
       </c>
       <c r="O117" t="n">
         <v>-0.2250000000000005</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.05353813559321807</v>
+        <v>-0.05377911079745701</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10474,10 +10474,10 @@
         <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7959039548022598</v>
+        <v>0.7960479887085392</v>
       </c>
       <c r="H118" t="n">
-        <v>11.72527542372881</v>
+        <v>11.72558221594919</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -10496,16 +10496,16 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>5.485275423728813</v>
+        <v>5.485582215949188</v>
       </c>
       <c r="N118" t="n">
-        <v>5.485275423728813</v>
+        <v>5.485582215949188</v>
       </c>
       <c r="O118" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.08508474576271219</v>
+        <v>-0.08506351446718519</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10545,10 +10545,10 @@
         <v>8</v>
       </c>
       <c r="G119" t="n">
-        <v>0.7824858757062146</v>
+        <v>0.7826393789696542</v>
       </c>
       <c r="H119" t="n">
-        <v>11.66258474576271</v>
+        <v>11.66356563161609</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -10567,16 +10567,16 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>5.542584745762711</v>
+        <v>5.543565631616089</v>
       </c>
       <c r="N119" t="n">
-        <v>5.542584745762711</v>
+        <v>5.543565631616089</v>
       </c>
       <c r="O119" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.06269067796610273</v>
+        <v>-0.06201658433309909</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -10616,10 +10616,10 @@
         <v>8</v>
       </c>
       <c r="G120" t="n">
-        <v>0.768361581920904</v>
+        <v>0.7685250529287226</v>
       </c>
       <c r="H120" t="n">
-        <v>11.55661016949152</v>
+        <v>11.55695836273818</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10638,16 +10638,16 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>5.486610169491524</v>
+        <v>5.486958362738179</v>
       </c>
       <c r="N120" t="n">
-        <v>5.486610169491524</v>
+        <v>5.486958362738179</v>
       </c>
       <c r="O120" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.105974576271187</v>
+        <v>-0.1066072688779105</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         <v>8</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7598870056497176</v>
+        <v>0.7593507410021172</v>
       </c>
       <c r="H121" t="n">
-        <v>11.49847457627119</v>
+        <v>11.48875617501764</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -10709,16 +10709,16 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.468474576271187</v>
+        <v>5.458756175017643</v>
       </c>
       <c r="N121" t="n">
-        <v>5.468474576271187</v>
+        <v>5.458756175017643</v>
       </c>
       <c r="O121" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.0581355932203369</v>
+        <v>-0.06820218772053543</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>8</v>
       </c>
       <c r="G122" t="n">
-        <v>0.9597457627118644</v>
+        <v>0.9597741707833451</v>
       </c>
       <c r="H122" t="n">
-        <v>112.8920550847458</v>
+        <v>112.8937473535639</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>105.8920550847458</v>
+        <v>105.8937473535639</v>
       </c>
       <c r="N122" t="n">
-        <v>105.8920550847458</v>
+        <v>105.8937473535639</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         <v>8</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9357344632768362</v>
+        <v>0.9357798165137615</v>
       </c>
       <c r="H123" t="n">
-        <v>112.4631002824859</v>
+        <v>112.4634862385321</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -10845,16 +10845,16 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>105.6531002824859</v>
+        <v>105.6534862385321</v>
       </c>
       <c r="N123" t="n">
-        <v>105.6531002824859</v>
+        <v>105.6534862385321</v>
       </c>
       <c r="O123" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.428954802259895</v>
+        <v>-0.4302611150317546</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -10894,10 +10894,10 @@
         <v>8</v>
       </c>
       <c r="G124" t="n">
-        <v>0.9180790960451978</v>
+        <v>0.918136908962597</v>
       </c>
       <c r="H124" t="n">
-        <v>112.1428531073446</v>
+        <v>112.1433450952717</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -10916,16 +10916,16 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>105.5328531073446</v>
+        <v>105.5333450952717</v>
       </c>
       <c r="N124" t="n">
-        <v>105.5328531073446</v>
+        <v>105.5333450952717</v>
       </c>
       <c r="O124" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P124" t="n">
-        <v>-0.3202471751412332</v>
+        <v>-0.3201411432604004</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -10965,10 +10965,10 @@
         <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>0.9011299435028248</v>
+        <v>0.9011997177134792</v>
       </c>
       <c r="H125" t="n">
-        <v>111.9993079096045</v>
+        <v>111.9996047988708</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -10987,16 +10987,16 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>105.5793079096045</v>
+        <v>105.5796047988708</v>
       </c>
       <c r="N125" t="n">
-        <v>105.5793079096045</v>
+        <v>105.5796047988708</v>
       </c>
       <c r="O125" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P125" t="n">
-        <v>-0.1435451977401101</v>
+        <v>-0.1437402964008641</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -11036,10 +11036,10 @@
         <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>0.8580508474576272</v>
+        <v>0.858151023288638</v>
       </c>
       <c r="H126" t="n">
-        <v>111.6780190677966</v>
+        <v>111.6792978122795</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -11058,16 +11058,16 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>105.4480190677966</v>
+        <v>105.4492978122795</v>
       </c>
       <c r="N126" t="n">
-        <v>105.4480190677966</v>
+        <v>105.4492978122795</v>
       </c>
       <c r="O126" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.3212888418079132</v>
+        <v>-0.3203069865913903</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -11107,10 +11107,10 @@
         <v>8</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8121468926553672</v>
+        <v>0.8122794636556104</v>
       </c>
       <c r="H127" t="n">
-        <v>111.4337900188324</v>
+        <v>111.4341660785697</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -11129,16 +11129,16 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>105.3737900188324</v>
+        <v>105.3741660785697</v>
       </c>
       <c r="N127" t="n">
-        <v>105.3737900188324</v>
+        <v>105.3741660785697</v>
       </c>
       <c r="O127" t="n">
         <v>-0.1700000000000008</v>
       </c>
       <c r="P127" t="n">
-        <v>-0.2442290489642147</v>
+        <v>-0.2451317337097123</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -11178,10 +11178,10 @@
         <v>8</v>
       </c>
       <c r="G128" t="n">
-        <v>0.7535310734463276</v>
+        <v>0.7537050105857446</v>
       </c>
       <c r="H128" t="n">
-        <v>111.1705098870057</v>
+        <v>111.1708059280169</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -11200,16 +11200,16 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>105.2405098870057</v>
+        <v>105.240805928017</v>
       </c>
       <c r="N128" t="n">
-        <v>105.2405098870057</v>
+        <v>105.240805928017</v>
       </c>
       <c r="O128" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.2632801318267468</v>
+        <v>-0.2633601505527992</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -11249,10 +11249,10 @@
         <v>8</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6758474576271186</v>
+        <v>0.6760762173606211</v>
       </c>
       <c r="H129" t="n">
-        <v>110.7671927966102</v>
+        <v>110.7701129146083</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -11271,16 +11271,16 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>52.40219279661017</v>
+        <v>52.40511291460833</v>
       </c>
       <c r="N129" t="n">
-        <v>52.40219279661017</v>
+        <v>52.40511291460833</v>
       </c>
       <c r="O129" t="n">
         <v>52.435</v>
       </c>
       <c r="P129" t="n">
-        <v>-0.4033170903954755</v>
+        <v>-0.4006930134086133</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -11320,10 +11320,10 @@
         <v>8</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5981638418079096</v>
+        <v>0.5984474241354976</v>
       </c>
       <c r="H130" t="n">
-        <v>110.3751871468927</v>
+        <v>110.3763937896965</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -11342,16 +11342,16 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>52.08018714689265</v>
+        <v>52.08139378969653</v>
       </c>
       <c r="N130" t="n">
-        <v>52.08018714689265</v>
+        <v>52.08139378969653</v>
       </c>
       <c r="O130" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.3920056497175182</v>
+        <v>-0.3937191249117973</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         <v>8</v>
       </c>
       <c r="G131" t="n">
-        <v>0.5176553672316384</v>
+        <v>0.5179957657021877</v>
       </c>
       <c r="H131" t="n">
-        <v>109.9715741525424</v>
+        <v>109.9724431898377</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -11413,16 +11413,16 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>51.78657415254237</v>
+        <v>51.78744318983769</v>
       </c>
       <c r="N131" t="n">
-        <v>51.78657415254237</v>
+        <v>51.78744318983769</v>
       </c>
       <c r="O131" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.4036129943502829</v>
+        <v>-0.4039505998588453</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -11462,10 +11462,10 @@
         <v>8</v>
       </c>
       <c r="G132" t="n">
-        <v>0.432909604519774</v>
+        <v>0.4333098094565985</v>
       </c>
       <c r="H132" t="n">
-        <v>109.4560404896422</v>
+        <v>109.4583109856504</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -11484,16 +11484,16 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>51.41104048964218</v>
+        <v>51.41331098565043</v>
       </c>
       <c r="N132" t="n">
-        <v>51.41104048964218</v>
+        <v>51.41331098565043</v>
       </c>
       <c r="O132" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.5155336629001965</v>
+        <v>-0.5141322041872627</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -11533,10 +11533,10 @@
         <v>8</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3524011299435028</v>
+        <v>0.3528581510232887</v>
       </c>
       <c r="H133" t="n">
-        <v>108.9144668079096</v>
+        <v>108.9164114326041</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -11555,16 +11555,16 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>103.4744668079096</v>
+        <v>103.4764114326041</v>
       </c>
       <c r="N133" t="n">
-        <v>103.4744668079096</v>
+        <v>103.4764114326041</v>
       </c>
       <c r="O133" t="n">
         <v>-52.605</v>
       </c>
       <c r="P133" t="n">
-        <v>-0.5415736817325723</v>
+        <v>-0.5418995530463349</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -11604,10 +11604,10 @@
         <v>8</v>
       </c>
       <c r="G134" t="n">
-        <v>0.2690677966101695</v>
+        <v>0.2695836273817925</v>
       </c>
       <c r="H134" t="n">
-        <v>108.4097669491525</v>
+        <v>108.4141566690191</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -11626,16 +11626,16 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>103.0897669491525</v>
+        <v>103.0941566690191</v>
       </c>
       <c r="N134" t="n">
-        <v>103.0897669491525</v>
+        <v>103.0941566690191</v>
       </c>
       <c r="O134" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P134" t="n">
-        <v>-0.5046998587570641</v>
+        <v>-0.5022547635850287</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
         <v>8</v>
       </c>
       <c r="G154" t="n">
-        <v>0.931497175141243</v>
+        <v>0.9315455187014821</v>
       </c>
       <c r="H154" t="n">
-        <v>9.032040960451978</v>
+        <v>9.032110091743119</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -13034,16 +13034,16 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>0.5720409604519769</v>
+        <v>0.5721100917431183</v>
       </c>
       <c r="N154" t="n">
-        <v>0.5720409604519769</v>
+        <v>0.5721100917431183</v>
       </c>
       <c r="O154" t="n">
         <v>0.005000000000000782</v>
       </c>
       <c r="P154" t="n">
-        <v>0.5830316752382441</v>
+        <v>0.5831008065293855</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>8</v>
       </c>
       <c r="G155" t="n">
-        <v>0.9216101694915254</v>
+        <v>0.92166549047283</v>
       </c>
       <c r="H155" t="n">
         <v>9.009999999999998</v>
@@ -13114,7 +13114,7 @@
         <v>-0.03000000000000114</v>
       </c>
       <c r="P155" t="n">
-        <v>-0.02204096045197979</v>
+        <v>-0.02211009174312117</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -13154,10 +13154,10 @@
         <v>8</v>
       </c>
       <c r="G156" t="n">
-        <v>0.91454802259887</v>
+        <v>0.9146083274523642</v>
       </c>
       <c r="H156" t="n">
-        <v>8.967803672316386</v>
+        <v>8.967889908256883</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -13176,16 +13176,16 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0.5578036723163855</v>
+        <v>0.5578899082568824</v>
       </c>
       <c r="N156" t="n">
-        <v>0.5578036723163855</v>
+        <v>0.5578899082568824</v>
       </c>
       <c r="O156" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P156" t="n">
-        <v>-0.04219632768361237</v>
+        <v>-0.04211009174311542</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -13225,10 +13225,10 @@
         <v>8</v>
       </c>
       <c r="G157" t="n">
-        <v>0.905367231638418</v>
+        <v>0.9054340155257586</v>
       </c>
       <c r="H157" t="n">
-        <v>8.921850282485876</v>
+        <v>8.922041284403671</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -13247,16 +13247,16 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>0.6218502824858749</v>
+        <v>0.6220412844036698</v>
       </c>
       <c r="N157" t="n">
-        <v>0.6218502824858749</v>
+        <v>0.6220412844036698</v>
       </c>
       <c r="O157" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P157" t="n">
-        <v>-0.04595338983051001</v>
+        <v>-0.04584862385321209</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>8</v>
       </c>
       <c r="G158" t="n">
-        <v>0.8954802259887006</v>
+        <v>0.8955539872971066</v>
       </c>
       <c r="H158" t="n">
-        <v>8.858036723163844</v>
+        <v>8.858142201834864</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -13318,16 +13318,16 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>0.6880367231638438</v>
+        <v>0.6881422018348644</v>
       </c>
       <c r="N158" t="n">
-        <v>0.6880367231638438</v>
+        <v>0.6881422018348644</v>
       </c>
       <c r="O158" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P158" t="n">
-        <v>-0.06381355932203192</v>
+        <v>-0.06389908256880616</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -13367,10 +13367,10 @@
         <v>8</v>
       </c>
       <c r="G159" t="n">
-        <v>0.8891242937853108</v>
+        <v>0.8892025405786874</v>
       </c>
       <c r="H159" t="n">
-        <v>8.79263418079096</v>
+        <v>8.79341743119266</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -13389,16 +13389,16 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>0.8426341807909603</v>
+        <v>0.8434174311926599</v>
       </c>
       <c r="N159" t="n">
-        <v>0.8426341807909603</v>
+        <v>0.8434174311926599</v>
       </c>
       <c r="O159" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P159" t="n">
-        <v>-0.06540254237288323</v>
+        <v>-0.06472477064220428</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -13438,10 +13438,10 @@
         <v>8</v>
       </c>
       <c r="G160" t="n">
-        <v>0.865819209039548</v>
+        <v>0.8659139026111503</v>
       </c>
       <c r="H160" t="n">
-        <v>8.434350282485875</v>
+        <v>8.435298165137615</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -13460,16 +13460,16 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>0.6643502824858754</v>
+        <v>0.6652981651376155</v>
       </c>
       <c r="N160" t="n">
-        <v>0.6643502824858754</v>
+        <v>0.6652981651376155</v>
       </c>
       <c r="O160" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P160" t="n">
-        <v>-0.3582838983050856</v>
+        <v>-0.358119266055045</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -13509,10 +13509,10 @@
         <v>8</v>
       </c>
       <c r="G161" t="n">
-        <v>0.8587570621468926</v>
+        <v>0.8588567395906845</v>
       </c>
       <c r="H161" t="n">
-        <v>8.242655367231636</v>
+        <v>8.246788990825687</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -13531,16 +13531,16 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>0.5126553672316359</v>
+        <v>0.5167889908256864</v>
       </c>
       <c r="N161" t="n">
-        <v>0.5126553672316359</v>
+        <v>0.5167889908256864</v>
       </c>
       <c r="O161" t="n">
         <v>-0.03999999999999915</v>
       </c>
       <c r="P161" t="n">
-        <v>-0.1916949152542387</v>
+        <v>-0.1885091743119283</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -13580,10 +13580,10 @@
         <v>8</v>
       </c>
       <c r="G162" t="n">
-        <v>0.8495762711864406</v>
+        <v>0.8496824276640791</v>
       </c>
       <c r="H162" t="n">
-        <v>8.01372881355932</v>
+        <v>8.015321100917429</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -13602,16 +13602,16 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>0.3137288135593197</v>
+        <v>0.315321100917429</v>
       </c>
       <c r="N162" t="n">
-        <v>0.3137288135593197</v>
+        <v>0.315321100917429</v>
       </c>
       <c r="O162" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P162" t="n">
-        <v>-0.2289265536723164</v>
+        <v>-0.2314678899082576</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -13651,10 +13651,10 @@
         <v>8</v>
       </c>
       <c r="G163" t="n">
-        <v>0.844632768361582</v>
+        <v>0.844742413549753</v>
       </c>
       <c r="H163" t="n">
-        <v>7.950974576271187</v>
+        <v>7.951444954128441</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -13673,16 +13673,16 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>0.3109745762711871</v>
+        <v>0.311444954128441</v>
       </c>
       <c r="N163" t="n">
-        <v>0.3109745762711871</v>
+        <v>0.311444954128441</v>
       </c>
       <c r="O163" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P163" t="n">
-        <v>-0.06275423728813312</v>
+        <v>-0.06387614678898856</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -13722,10 +13722,10 @@
         <v>8</v>
       </c>
       <c r="G164" t="n">
-        <v>0.838276836158192</v>
+        <v>0.8383909668313339</v>
       </c>
       <c r="H164" t="n">
-        <v>7.844858757062146</v>
+        <v>7.846490825688074</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -13744,16 +13744,16 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>0.2848587570621461</v>
+        <v>0.286490825688074</v>
       </c>
       <c r="N164" t="n">
-        <v>0.2848587570621461</v>
+        <v>0.286490825688074</v>
       </c>
       <c r="O164" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P164" t="n">
-        <v>-0.106115819209041</v>
+        <v>-0.104954128440367</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -13793,10 +13793,10 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>0.83545197740113</v>
+        <v>0.8355681016231475</v>
       </c>
       <c r="H165" t="n">
-        <v>7.829696327683616</v>
+        <v>7.829862385321101</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -13815,16 +13815,16 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>0.3496963276836151</v>
+        <v>0.3498623853211003</v>
       </c>
       <c r="N165" t="n">
-        <v>0.3496963276836151</v>
+        <v>0.3498623853211003</v>
       </c>
       <c r="O165" t="n">
         <v>-0.07999999999999918</v>
       </c>
       <c r="P165" t="n">
-        <v>-0.01516242937853018</v>
+        <v>-0.01662844036697297</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -13864,10 +13864,10 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>0.8269774011299436</v>
+        <v>0.8270995059985886</v>
       </c>
       <c r="H166" t="n">
-        <v>7.757888418079096</v>
+        <v>7.758761467889908</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -13886,16 +13886,16 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>0.387888418079096</v>
+        <v>0.3887614678899078</v>
       </c>
       <c r="N166" t="n">
-        <v>0.387888418079096</v>
+        <v>0.3887614678899078</v>
       </c>
       <c r="O166" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P166" t="n">
-        <v>-0.07180790960451944</v>
+        <v>-0.07110091743119273</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -15065,10 +15065,10 @@
         <v>8</v>
       </c>
       <c r="G183" t="n">
-        <v>0.8001412429378532</v>
+        <v>0.8002822865208187</v>
       </c>
       <c r="H183" t="n">
-        <v>5.551307379943503</v>
+        <v>5.551364678899082</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -15087,16 +15087,16 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>0.336307379943503</v>
+        <v>0.3363646788990824</v>
       </c>
       <c r="N183" t="n">
-        <v>0.336307379943503</v>
+        <v>0.3363646788990824</v>
       </c>
       <c r="O183" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P183" t="n">
-        <v>-0.09277285831858606</v>
+        <v>-0.09271555936300668</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -15136,10 +15136,10 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>0.8538135593220338</v>
+        <v>0.8539167254763586</v>
       </c>
       <c r="H184" t="n">
-        <v>5.75989406779661</v>
+        <v>5.760229357798165</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -15158,16 +15158,16 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>0.5948940677966101</v>
+        <v>0.5952293577981651</v>
       </c>
       <c r="N184" t="n">
-        <v>0.5948940677966101</v>
+        <v>0.5952293577981651</v>
       </c>
       <c r="O184" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P184" t="n">
-        <v>0.2085866878531073</v>
+        <v>0.2088646788990829</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -15207,10 +15207,10 @@
         <v>8</v>
       </c>
       <c r="G185" t="n">
-        <v>0.8679378531073446</v>
+        <v>0.8680310515172901</v>
       </c>
       <c r="H185" t="n">
-        <v>5.800199505649718</v>
+        <v>5.800275229357798</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -15229,16 +15229,16 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>0.6801995056497177</v>
+        <v>0.6802752293577976</v>
       </c>
       <c r="N185" t="n">
-        <v>0.6801995056497177</v>
+        <v>0.6802752293577976</v>
       </c>
       <c r="O185" t="n">
         <v>-0.04499999999999993</v>
       </c>
       <c r="P185" t="n">
-        <v>0.04030543785310758</v>
+        <v>0.04004587155963257</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -15278,10 +15278,10 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>0.8651129943502824</v>
+        <v>0.8652081863091038</v>
       </c>
       <c r="H186" t="n">
-        <v>5.787425847457627</v>
+        <v>5.78788990825688</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -15300,16 +15300,16 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>0.7074258474576265</v>
+        <v>0.7078899082568801</v>
       </c>
       <c r="N186" t="n">
-        <v>0.7074258474576265</v>
+        <v>0.7078899082568801</v>
       </c>
       <c r="O186" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P186" t="n">
-        <v>-0.0127736581920912</v>
+        <v>-0.0123853211009175</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -15349,10 +15349,10 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8439265536723164</v>
+        <v>0.8440366972477065</v>
       </c>
       <c r="H187" t="n">
-        <v>5.683880649717514</v>
+        <v>5.684059633027523</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -15371,16 +15371,16 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>0.2538806497175141</v>
+        <v>0.2540596330275235</v>
       </c>
       <c r="N187" t="n">
-        <v>0.2538806497175141</v>
+        <v>0.2540596330275235</v>
       </c>
       <c r="O187" t="n">
         <v>0.3499999999999996</v>
       </c>
       <c r="P187" t="n">
-        <v>-0.1035451977401127</v>
+        <v>-0.1038302752293569</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -15420,10 +15420,10 @@
         <v>8</v>
       </c>
       <c r="G188" t="n">
-        <v>0.7959039548022598</v>
+        <v>0.7953422724064926</v>
       </c>
       <c r="H188" t="n">
-        <v>5.540891596045197</v>
+        <v>5.535871559633027</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -15442,16 +15442,16 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.06160840395480349</v>
+        <v>-0.0666284403669728</v>
       </c>
       <c r="N188" t="n">
-        <v>0.06160840395480349</v>
+        <v>0.0666284403669728</v>
       </c>
       <c r="O188" t="n">
         <v>0.1725000000000003</v>
       </c>
       <c r="P188" t="n">
-        <v>-0.1429890536723173</v>
+        <v>-0.148188073394496</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -15491,10 +15491,10 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>0.748587570621469</v>
+        <v>0.748059280169372</v>
       </c>
       <c r="H189" t="n">
-        <v>5.385501412429379</v>
+        <v>5.380779816513763</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -15513,16 +15513,16 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.1644985875706206</v>
+        <v>-0.169220183486237</v>
       </c>
       <c r="N189" t="n">
-        <v>0.1644985875706206</v>
+        <v>0.169220183486237</v>
       </c>
       <c r="O189" t="n">
         <v>-0.05250000000000021</v>
       </c>
       <c r="P189" t="n">
-        <v>-0.1553901836158174</v>
+        <v>-0.1550917431192644</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -15562,10 +15562,10 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>0.7203389830508474</v>
+        <v>0.7198306280875089</v>
       </c>
       <c r="H190" t="n">
-        <v>5.280275423728813</v>
+        <v>5.279931192660551</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -15584,16 +15584,16 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>0.0002754237288131733</v>
+        <v>-6.880733944925055e-05</v>
       </c>
       <c r="N190" t="n">
-        <v>0.0002754237288131733</v>
+        <v>6.880733944925055e-05</v>
       </c>
       <c r="O190" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P190" t="n">
-        <v>-0.1052259887005658</v>
+        <v>-0.1008486238532118</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -15633,10 +15633,10 @@
         <v>8</v>
       </c>
       <c r="G191" t="n">
-        <v>0.7153954802259888</v>
+        <v>0.7148906139731828</v>
       </c>
       <c r="H191" t="n">
-        <v>5.278129413841808</v>
+        <v>5.277924311926605</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -15655,16 +15655,16 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>0.2531294138418092</v>
+        <v>0.2529243119266065</v>
       </c>
       <c r="N191" t="n">
-        <v>0.2531294138418092</v>
+        <v>0.2529243119266065</v>
       </c>
       <c r="O191" t="n">
         <v>-0.2550000000000017</v>
       </c>
       <c r="P191" t="n">
-        <v>-0.00214600988700564</v>
+        <v>-0.002006880733945948</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -15704,10 +15704,10 @@
         <v>8</v>
       </c>
       <c r="G192" t="n">
-        <v>0.7238700564971752</v>
+        <v>0.7233592095977417</v>
       </c>
       <c r="H192" t="n">
-        <v>5.286366525423729</v>
+        <v>5.283876146788991</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -15726,16 +15726,16 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>0.436366525423729</v>
+        <v>0.4338761467889913</v>
       </c>
       <c r="N192" t="n">
-        <v>0.436366525423729</v>
+        <v>0.4338761467889913</v>
       </c>
       <c r="O192" t="n">
         <v>-0.1749999999999989</v>
       </c>
       <c r="P192" t="n">
-        <v>0.008237111581920864</v>
+        <v>0.00595183486238593</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -15775,10 +15775,10 @@
         <v>8</v>
       </c>
       <c r="G193" t="n">
-        <v>0.7309322033898306</v>
+        <v>0.7304163726182075</v>
       </c>
       <c r="H193" t="n">
-        <v>5.320736228813559</v>
+        <v>5.314449541284403</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -15797,16 +15797,16 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>0.7507362288135591</v>
+        <v>0.7444495412844025</v>
       </c>
       <c r="N193" t="n">
-        <v>0.7507362288135591</v>
+        <v>0.7444495412844025</v>
       </c>
       <c r="O193" t="n">
         <v>-0.2799999999999994</v>
       </c>
       <c r="P193" t="n">
-        <v>0.0343697033898307</v>
+        <v>0.03057339449541185</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -15846,10 +15846,10 @@
         <v>8</v>
       </c>
       <c r="G194" t="n">
-        <v>0.7217514124293786</v>
+        <v>0.721242060691602</v>
       </c>
       <c r="H194" t="n">
-        <v>5.28142302259887</v>
+        <v>5.281009174311927</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15868,16 +15868,16 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>0.8514230225988699</v>
+        <v>0.851009174311927</v>
       </c>
       <c r="N194" t="n">
-        <v>0.8514230225988699</v>
+        <v>0.851009174311927</v>
       </c>
       <c r="O194" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P194" t="n">
-        <v>-0.0393132062146897</v>
+        <v>-0.0334403669724761</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -15917,10 +15917,10 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>0.6942090395480226</v>
+        <v>0.6937191249117854</v>
       </c>
       <c r="H195" t="n">
-        <v>5.213089689265537</v>
+        <v>5.212293577981652</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -15939,16 +15939,16 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>0.7330896892655367</v>
+        <v>0.7322935779816513</v>
       </c>
       <c r="N195" t="n">
-        <v>0.7330896892655367</v>
+        <v>0.7322935779816513</v>
       </c>
       <c r="O195" t="n">
         <v>0.05000000000000071</v>
       </c>
       <c r="P195" t="n">
-        <v>-0.06833333333333247</v>
+        <v>-0.06871559633027502</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -15988,10 +15988,10 @@
         <v>8</v>
       </c>
       <c r="G196" t="n">
-        <v>0.655367231638418</v>
+        <v>0.6549047282992237</v>
       </c>
       <c r="H196" t="n">
-        <v>5.119844632768362</v>
+        <v>5.115711009174313</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -16010,16 +16010,16 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>0.3298446327683617</v>
+        <v>0.3257110091743129</v>
       </c>
       <c r="N196" t="n">
-        <v>0.3298446327683617</v>
+        <v>0.3257110091743129</v>
       </c>
       <c r="O196" t="n">
         <v>0.3099999999999996</v>
       </c>
       <c r="P196" t="n">
-        <v>-0.0932450564971754</v>
+        <v>-0.09658256880733873</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>0.7563559322033898</v>
+        <v>0.7565278757939309</v>
       </c>
       <c r="H213" t="n">
         <v>5.970000000000001</v>
@@ -17260,10 +17260,10 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>0.7556497175141242</v>
+        <v>0.7558221594918842</v>
       </c>
       <c r="H214" t="n">
-        <v>5.96993879472693</v>
+        <v>5.97</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -17282,16 +17282,16 @@
         <v>1</v>
       </c>
       <c r="M214" t="n">
-        <v>-2.617561205273069</v>
+        <v>-2.617499999999999</v>
       </c>
       <c r="N214" t="n">
-        <v>2.617561205273069</v>
+        <v>2.617499999999999</v>
       </c>
       <c r="O214" t="n">
         <v>-0.1500000000000021</v>
       </c>
       <c r="P214" t="n">
-        <v>-6.120527307107437e-05</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>0.7662429378531074</v>
+        <v>0.766407904022583</v>
       </c>
       <c r="H215" t="n">
-        <v>6.012489406779661</v>
+        <v>6.013466831333804</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -17353,16 +17353,16 @@
         <v>1</v>
       </c>
       <c r="M215" t="n">
-        <v>-2.467510593220339</v>
+        <v>-2.466533168666197</v>
       </c>
       <c r="N215" t="n">
-        <v>2.467510593220339</v>
+        <v>2.466533168666197</v>
       </c>
       <c r="O215" t="n">
         <v>-0.1074999999999982</v>
       </c>
       <c r="P215" t="n">
-        <v>0.04255061205273147</v>
+        <v>0.04346683133380402</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -17402,10 +17402,10 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>0.786723163841808</v>
+        <v>0.7868736767819337</v>
       </c>
       <c r="H216" t="n">
-        <v>6.105112994350283</v>
+        <v>6.106302046577276</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -17424,16 +17424,16 @@
         <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>-2.104887005649718</v>
+        <v>-2.103697953422725</v>
       </c>
       <c r="N216" t="n">
-        <v>2.104887005649718</v>
+        <v>2.103697953422725</v>
       </c>
       <c r="O216" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P216" t="n">
-        <v>0.09262358757062206</v>
+        <v>0.09283521524347194</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -17473,10 +17473,10 @@
         <v>8</v>
       </c>
       <c r="G217" t="n">
-        <v>0.809322033898305</v>
+        <v>0.8094565984474241</v>
       </c>
       <c r="H217" t="n">
-        <v>6.20364406779661</v>
+        <v>6.204707127734651</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -17495,16 +17495,16 @@
         <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>-1.95635593220339</v>
+        <v>-1.955292872265349</v>
       </c>
       <c r="N217" t="n">
-        <v>1.95635593220339</v>
+        <v>1.955292872265349</v>
       </c>
       <c r="O217" t="n">
         <v>-0.05000000000000071</v>
       </c>
       <c r="P217" t="n">
-        <v>0.09853107344632672</v>
+        <v>0.09840508115737556</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -17544,10 +17544,10 @@
         <v>8</v>
       </c>
       <c r="G218" t="n">
-        <v>0.827683615819209</v>
+        <v>0.8278052223006351</v>
       </c>
       <c r="H218" t="n">
-        <v>6.295800376647835</v>
+        <v>6.296440837450012</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -17566,16 +17566,16 @@
         <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>-1.634199623352165</v>
+        <v>-1.633559162549988</v>
       </c>
       <c r="N218" t="n">
-        <v>1.634199623352165</v>
+        <v>1.633559162549988</v>
       </c>
       <c r="O218" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P218" t="n">
-        <v>0.09215630885122472</v>
+        <v>0.09173370971536077</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -17615,10 +17615,10 @@
         <v>8</v>
       </c>
       <c r="G219" t="n">
-        <v>0.844632768361582</v>
+        <v>0.844742413549753</v>
       </c>
       <c r="H219" t="n">
-        <v>6.385649717514124</v>
+        <v>6.385866266760762</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -17637,16 +17637,16 @@
         <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>-1.604350282485876</v>
+        <v>-1.604133733239238</v>
       </c>
       <c r="N219" t="n">
-        <v>1.604350282485876</v>
+        <v>1.604133733239238</v>
       </c>
       <c r="O219" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P219" t="n">
-        <v>0.08984934086628993</v>
+        <v>0.08942542931074993</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -17686,10 +17686,10 @@
         <v>8</v>
       </c>
       <c r="G220" t="n">
-        <v>0.8516949152542372</v>
+        <v>0.8517995765702188</v>
       </c>
       <c r="H220" t="n">
-        <v>6.455169491525423</v>
+        <v>6.457649964714185</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -17708,16 +17708,16 @@
         <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>-1.534830508474577</v>
+        <v>-1.532350035285815</v>
       </c>
       <c r="N220" t="n">
-        <v>1.534830508474577</v>
+        <v>1.532350035285815</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
       </c>
       <c r="P220" t="n">
-        <v>0.06951977401129827</v>
+        <v>0.07178369795342299</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -17757,10 +17757,10 @@
         <v>8</v>
       </c>
       <c r="G221" t="n">
-        <v>0.8425141242937854</v>
+        <v>0.8426252646436133</v>
       </c>
       <c r="H221" t="n">
-        <v>6.381465395480226</v>
+        <v>6.381684897671136</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -17779,16 +17779,16 @@
         <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>-1.476034604519774</v>
+        <v>-1.475815102328863</v>
       </c>
       <c r="N221" t="n">
-        <v>1.476034604519774</v>
+        <v>1.475815102328863</v>
       </c>
       <c r="O221" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P221" t="n">
-        <v>-0.0737040960451969</v>
+        <v>-0.07596506704304851</v>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
@@ -17828,10 +17828,10 @@
         <v>8</v>
       </c>
       <c r="G222" t="n">
-        <v>0.8227401129943502</v>
+        <v>0.8228652081863091</v>
       </c>
       <c r="H222" t="n">
-        <v>6.249882297551789</v>
+        <v>6.250317572335921</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -17850,16 +17850,16 @@
         <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>-1.490117702448211</v>
+        <v>-1.489682427664079</v>
       </c>
       <c r="N222" t="n">
-        <v>1.490117702448211</v>
+        <v>1.489682427664079</v>
       </c>
       <c r="O222" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.1315830979284369</v>
+        <v>-0.1313673253352157</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -17899,10 +17899,10 @@
         <v>8</v>
       </c>
       <c r="G223" t="n">
-        <v>0.8050847457627118</v>
+        <v>0.8052223006351447</v>
       </c>
       <c r="H223" t="n">
-        <v>6.180112994350282</v>
+        <v>6.180837450011762</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -17921,16 +17921,16 @@
         <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>-1.439887005649718</v>
+        <v>-1.439162549988239</v>
       </c>
       <c r="N223" t="n">
-        <v>1.439887005649718</v>
+        <v>1.439162549988239</v>
       </c>
       <c r="O223" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.06976930320150654</v>
+        <v>-0.06948012232415923</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -17970,10 +17970,10 @@
         <v>8</v>
       </c>
       <c r="G224" t="n">
-        <v>0.780367231638418</v>
+        <v>0.7805222300635145</v>
       </c>
       <c r="H224" t="n">
-        <v>6.076862641242937</v>
+        <v>6.07701570218772</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -17992,16 +17992,16 @@
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>-1.323137358757063</v>
+        <v>-1.322984297812281</v>
       </c>
       <c r="N224" t="n">
-        <v>1.323137358757063</v>
+        <v>1.322984297812281</v>
       </c>
       <c r="O224" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.1032503531073452</v>
+        <v>-0.1038217478240417</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -18041,10 +18041,10 @@
         <v>8</v>
       </c>
       <c r="G225" t="n">
-        <v>0.7528248587570622</v>
+        <v>0.7529992942836979</v>
       </c>
       <c r="H225" t="n">
-        <v>5.966219397363465</v>
+        <v>5.966449070806869</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -18063,16 +18063,16 @@
         <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>-1.393780602636535</v>
+        <v>-1.393550929193132</v>
       </c>
       <c r="N225" t="n">
-        <v>1.393780602636535</v>
+        <v>1.393550929193132</v>
       </c>
       <c r="O225" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.1106432438794718</v>
+        <v>-0.1105666313808511</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>8</v>
       </c>
       <c r="G226" t="n">
-        <v>0.7281073446327684</v>
+        <v>0.7282992237120678</v>
       </c>
       <c r="H226" t="n">
-        <v>5.832048022598871</v>
+        <v>5.833563867325336</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -18134,16 +18134,16 @@
         <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>-1.547951977401129</v>
+        <v>-1.546436132674664</v>
       </c>
       <c r="N226" t="n">
-        <v>1.547951977401129</v>
+        <v>1.546436132674664</v>
       </c>
       <c r="O226" t="n">
         <v>0.01999999999999957</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.1341713747645947</v>
+        <v>-0.1328852034815329</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -19313,10 +19313,10 @@
         <v>8</v>
       </c>
       <c r="G243" t="n">
-        <v>0.8290960451977402</v>
+        <v>0.8285109386026818</v>
       </c>
       <c r="H243" t="n">
-        <v>5.573220338983051</v>
+        <v>5.561582568807339</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -19335,16 +19335,16 @@
         <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>1.58322033898305</v>
+        <v>1.571582568807338</v>
       </c>
       <c r="N243" t="n">
-        <v>1.58322033898305</v>
+        <v>1.571582568807338</v>
       </c>
       <c r="O243" t="n">
         <v>-0.1624999999999996</v>
       </c>
       <c r="P243" t="n">
-        <v>-1.587697670827741</v>
+        <v>-1.599335441003453</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -19384,10 +19384,10 @@
         <v>8</v>
       </c>
       <c r="G244" t="n">
-        <v>0.7048022598870056</v>
+        <v>0.7043048694424842</v>
       </c>
       <c r="H244" t="n">
-        <v>4.931694915254237</v>
+        <v>4.930172900494001</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -19406,16 +19406,16 @@
         <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>1.109194915254237</v>
+        <v>1.107672900494001</v>
       </c>
       <c r="N244" t="n">
-        <v>1.109194915254237</v>
+        <v>1.107672900494001</v>
       </c>
       <c r="O244" t="n">
         <v>-0.1675000000000004</v>
       </c>
       <c r="P244" t="n">
-        <v>-0.6415254237288135</v>
+        <v>-0.6314096683133377</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -19455,10 +19455,10 @@
         <v>8</v>
       </c>
       <c r="G245" t="n">
-        <v>0.615819209039548</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="H245" t="n">
-        <v>4.630635593220339</v>
+        <v>4.630192307692308</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -19477,16 +19477,16 @@
         <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>0.8506355932203395</v>
+        <v>0.8501923076923084</v>
       </c>
       <c r="N245" t="n">
-        <v>0.8506355932203395</v>
+        <v>0.8501923076923084</v>
       </c>
       <c r="O245" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.3010593220338977</v>
+        <v>-0.2999805928016928</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -19526,10 +19526,10 @@
         <v>8</v>
       </c>
       <c r="G246" t="n">
-        <v>0.5939265536723164</v>
+        <v>0.5935074100211715</v>
       </c>
       <c r="H246" t="n">
-        <v>4.565550847457628</v>
+        <v>4.561275582215949</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -19548,16 +19548,16 @@
         <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>0.8855508474576275</v>
+        <v>0.8812755822159493</v>
       </c>
       <c r="N246" t="n">
-        <v>0.8855508474576275</v>
+        <v>0.8812755822159493</v>
       </c>
       <c r="O246" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.06508474576271173</v>
+        <v>-0.06891672547635874</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -19597,10 +19597,10 @@
         <v>8</v>
       </c>
       <c r="G247" t="n">
-        <v>0.634180790960452</v>
+        <v>0.6337332392378264</v>
       </c>
       <c r="H247" t="n">
-        <v>4.723093220338983</v>
+        <v>4.72172371206775</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -19619,16 +19619,16 @@
         <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>1.143093220338983</v>
+        <v>1.141723712067749</v>
       </c>
       <c r="N247" t="n">
-        <v>1.143093220338983</v>
+        <v>1.141723712067749</v>
       </c>
       <c r="O247" t="n">
         <v>-0.1000000000000001</v>
       </c>
       <c r="P247" t="n">
-        <v>0.1575423728813554</v>
+        <v>0.1604481298518001</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -19668,10 +19668,10 @@
         <v>8</v>
       </c>
       <c r="G248" t="n">
-        <v>0.6468926553672316</v>
+        <v>0.6464361326746648</v>
       </c>
       <c r="H248" t="n">
-        <v>4.759830508474576</v>
+        <v>4.759364855328158</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19690,16 +19690,16 @@
         <v>1</v>
       </c>
       <c r="M248" t="n">
-        <v>1.367330508474576</v>
+        <v>1.366864855328158</v>
       </c>
       <c r="N248" t="n">
-        <v>1.367330508474576</v>
+        <v>1.366864855328158</v>
       </c>
       <c r="O248" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P248" t="n">
-        <v>0.03673728813559318</v>
+        <v>0.03764114326040868</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -19739,10 +19739,10 @@
         <v>8</v>
       </c>
       <c r="G249" t="n">
-        <v>0.5967514124293786</v>
+        <v>0.5963302752293578</v>
       </c>
       <c r="H249" t="n">
-        <v>4.594364406779661</v>
+        <v>4.590068807339449</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19761,16 +19761,16 @@
         <v>1</v>
       </c>
       <c r="M249" t="n">
-        <v>1.314364406779661</v>
+        <v>1.310068807339449</v>
       </c>
       <c r="N249" t="n">
-        <v>1.314364406779661</v>
+        <v>1.310068807339449</v>
       </c>
       <c r="O249" t="n">
         <v>-0.1125000000000003</v>
       </c>
       <c r="P249" t="n">
-        <v>-0.165466101694915</v>
+        <v>-0.1692960479887091</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -19810,10 +19810,10 @@
         <v>8</v>
       </c>
       <c r="G250" t="n">
-        <v>0.4901129943502825</v>
+        <v>0.4897671136203247</v>
       </c>
       <c r="H250" t="n">
-        <v>4.147161016949153</v>
+        <v>4.145749823570925</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19832,16 +19832,16 @@
         <v>1</v>
       </c>
       <c r="M250" t="n">
-        <v>0.9971610169491529</v>
+        <v>0.9957498235709248</v>
       </c>
       <c r="N250" t="n">
-        <v>0.9971610169491529</v>
+        <v>0.9957498235709248</v>
       </c>
       <c r="O250" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P250" t="n">
-        <v>-0.4472033898305083</v>
+        <v>-0.4443189837685244</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -19881,10 +19881,10 @@
         <v>8</v>
       </c>
       <c r="G251" t="n">
-        <v>0.3905367231638418</v>
+        <v>0.3902611150317573</v>
       </c>
       <c r="H251" t="n">
-        <v>3.802542372881356</v>
+        <v>3.801699011997177</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19903,16 +19903,16 @@
         <v>1</v>
       </c>
       <c r="M251" t="n">
-        <v>0.857542372881356</v>
+        <v>0.8566990119971774</v>
       </c>
       <c r="N251" t="n">
-        <v>0.857542372881356</v>
+        <v>0.8566990119971774</v>
       </c>
       <c r="O251" t="n">
         <v>-0.2050000000000001</v>
       </c>
       <c r="P251" t="n">
-        <v>-0.344618644067797</v>
+        <v>-0.3440508115737475</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         <v>8</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3361581920903955</v>
+        <v>0.3359209597741708</v>
       </c>
       <c r="H252" t="n">
-        <v>3.639604519774011</v>
+        <v>3.638797929898848</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19974,16 +19974,16 @@
         <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>0.7996045197740114</v>
+        <v>0.7987979298988477</v>
       </c>
       <c r="N252" t="n">
-        <v>0.7996045197740114</v>
+        <v>0.7987979298988477</v>
       </c>
       <c r="O252" t="n">
         <v>-0.105</v>
       </c>
       <c r="P252" t="n">
-        <v>-0.1629378531073447</v>
+        <v>-0.1629010820983297</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -20023,10 +20023,10 @@
         <v>8</v>
       </c>
       <c r="G253" t="n">
-        <v>0.3467514124293785</v>
+        <v>0.3465067043048695</v>
       </c>
       <c r="H253" t="n">
-        <v>3.675621468926554</v>
+        <v>3.674789461303223</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -20045,16 +20045,16 @@
         <v>1</v>
       </c>
       <c r="M253" t="n">
-        <v>0.9056214689265536</v>
+        <v>0.9047894613032228</v>
       </c>
       <c r="N253" t="n">
-        <v>0.9056214689265536</v>
+        <v>0.9047894613032228</v>
       </c>
       <c r="O253" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P253" t="n">
-        <v>0.03601694915254239</v>
+        <v>0.03599153140437528</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -20094,10 +20094,10 @@
         <v>8</v>
       </c>
       <c r="G254" t="n">
-        <v>0.4943502824858757</v>
+        <v>0.4940014114326041</v>
       </c>
       <c r="H254" t="n">
-        <v>4.17292372881356</v>
+        <v>4.170788637967537</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -20116,16 +20116,16 @@
         <v>1</v>
       </c>
       <c r="M254" t="n">
-        <v>1.35292372881356</v>
+        <v>1.350788637967538</v>
       </c>
       <c r="N254" t="n">
-        <v>1.35292372881356</v>
+        <v>1.350788637967538</v>
       </c>
       <c r="O254" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P254" t="n">
-        <v>0.497302259887006</v>
+        <v>0.4959991766643146</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -20165,10 +20165,10 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>0.6963276836158192</v>
+        <v>0.6958362738179252</v>
       </c>
       <c r="H255" t="n">
-        <v>4.905762711864407</v>
+        <v>4.904505998588568</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -20187,16 +20187,16 @@
         <v>1</v>
       </c>
       <c r="M255" t="n">
-        <v>2.155762711864407</v>
+        <v>2.154505998588568</v>
       </c>
       <c r="N255" t="n">
-        <v>2.155762711864407</v>
+        <v>2.154505998588568</v>
       </c>
       <c r="O255" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P255" t="n">
-        <v>0.732838983050847</v>
+        <v>0.7337173606210303</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
@@ -20236,10 +20236,10 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>0.7888418079096046</v>
+        <v>0.7882851093860268</v>
       </c>
       <c r="H256" t="n">
-        <v>5.208877118644067</v>
+        <v>5.203482709950599</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -20258,16 +20258,16 @@
         <v>1</v>
       </c>
       <c r="M256" t="n">
-        <v>2.458877118644067</v>
+        <v>2.453482709950599</v>
       </c>
       <c r="N256" t="n">
-        <v>2.458877118644067</v>
+        <v>2.453482709950599</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
       </c>
       <c r="P256" t="n">
-        <v>0.3031144067796605</v>
+        <v>0.2989767113620312</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -21437,10 +21437,10 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>0.9427966101694916</v>
+        <v>0.9428369795342273</v>
       </c>
       <c r="H273" t="n">
-        <v>6.913951271186441</v>
+        <v>6.914174311926606</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -21459,16 +21459,16 @@
         <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>-0.8510487288135584</v>
+        <v>-0.8508256880733933</v>
       </c>
       <c r="N273" t="n">
-        <v>0.8510487288135584</v>
+        <v>0.8508256880733933</v>
       </c>
       <c r="O273" t="n">
         <v>0.0550000000000006</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.9769830899441354</v>
+        <v>-0.9767600492039703</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -21508,10 +21508,10 @@
         <v>8</v>
       </c>
       <c r="G274" t="n">
-        <v>0.9392655367231638</v>
+        <v>0.9393083980239944</v>
       </c>
       <c r="H274" t="n">
-        <v>6.849442090395479</v>
+        <v>6.849678899082568</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -21530,16 +21530,16 @@
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>-0.9305579096045209</v>
+        <v>-0.9303211009174319</v>
       </c>
       <c r="N274" t="n">
-        <v>0.9305579096045209</v>
+        <v>0.9303211009174319</v>
       </c>
       <c r="O274" t="n">
         <v>0.01500000000000057</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.06450918079096191</v>
+        <v>-0.06449541284403804</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -21579,10 +21579,10 @@
         <v>8</v>
       </c>
       <c r="G275" t="n">
-        <v>0.9357344632768362</v>
+        <v>0.9357798165137615</v>
       </c>
       <c r="H275" t="n">
-        <v>6.82996645480226</v>
+        <v>6.830183486238532</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -21601,16 +21601,16 @@
         <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>-0.94003354519774</v>
+        <v>-0.9398165137614676</v>
       </c>
       <c r="N275" t="n">
-        <v>0.94003354519774</v>
+        <v>0.9398165137614676</v>
       </c>
       <c r="O275" t="n">
         <v>-0.01000000000000068</v>
       </c>
       <c r="P275" t="n">
-        <v>-0.01947563559321974</v>
+        <v>-0.01949541284403633</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -21650,10 +21650,10 @@
         <v>8</v>
       </c>
       <c r="G276" t="n">
-        <v>0.9322033898305084</v>
+        <v>0.9322512350035286</v>
       </c>
       <c r="H276" t="n">
-        <v>6.82021186440678</v>
+        <v>6.820344036697248</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -21672,16 +21672,16 @@
         <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>-0.8797881355932207</v>
+        <v>-0.8796559633027519</v>
       </c>
       <c r="N276" t="n">
-        <v>0.8797881355932207</v>
+        <v>0.8796559633027519</v>
       </c>
       <c r="O276" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P276" t="n">
-        <v>-0.009754590395480101</v>
+        <v>-0.009839449541283685</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -21721,10 +21721,10 @@
         <v>8</v>
       </c>
       <c r="G277" t="n">
-        <v>0.9286723163841808</v>
+        <v>0.9287226534932957</v>
       </c>
       <c r="H277" t="n">
-        <v>6.780914548022599</v>
+        <v>6.781192660550459</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -21743,16 +21743,16 @@
         <v>1</v>
       </c>
       <c r="M277" t="n">
-        <v>-0.8090854519774009</v>
+        <v>-0.8088073394495412</v>
       </c>
       <c r="N277" t="n">
-        <v>0.8090854519774009</v>
+        <v>0.8088073394495412</v>
       </c>
       <c r="O277" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P277" t="n">
-        <v>-0.03929731638418055</v>
+        <v>-0.03915137614678965</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -21792,10 +21792,10 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>0.9251412429378532</v>
+        <v>0.9251940719830628</v>
       </c>
       <c r="H278" t="n">
-        <v>6.751405367231638</v>
+        <v>6.751697247706422</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -21814,16 +21814,16 @@
         <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>-0.6985946327683621</v>
+        <v>-0.6983027522935785</v>
       </c>
       <c r="N278" t="n">
-        <v>0.6985946327683621</v>
+        <v>0.6983027522935785</v>
       </c>
       <c r="O278" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P278" t="n">
-        <v>-0.02950918079096088</v>
+        <v>-0.02949541284403701</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -21863,10 +21863,10 @@
         <v>8</v>
       </c>
       <c r="G279" t="n">
-        <v>0.9216101694915254</v>
+        <v>0.92166549047283</v>
       </c>
       <c r="H279" t="n">
-        <v>6.714597457627119</v>
+        <v>6.71480122324159</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -21885,16 +21885,16 @@
         <v>1</v>
       </c>
       <c r="M279" t="n">
-        <v>-0.6554025423728813</v>
+        <v>-0.65519877675841</v>
       </c>
       <c r="N279" t="n">
-        <v>0.6554025423728813</v>
+        <v>0.65519877675841</v>
       </c>
       <c r="O279" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P279" t="n">
-        <v>-0.0368079096045193</v>
+        <v>-0.03689602446483153</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -21934,10 +21934,10 @@
         <v>8</v>
       </c>
       <c r="G280" t="n">
-        <v>0.9180790960451978</v>
+        <v>0.918136908962597</v>
       </c>
       <c r="H280" t="n">
-        <v>6.679548022598872</v>
+        <v>6.680825688073396</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -21956,16 +21956,16 @@
         <v>1</v>
       </c>
       <c r="M280" t="n">
-        <v>-0.5904519774011279</v>
+        <v>-0.5891743119266035</v>
       </c>
       <c r="N280" t="n">
-        <v>0.5904519774011279</v>
+        <v>0.5891743119266035</v>
       </c>
       <c r="O280" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P280" t="n">
-        <v>-0.03504943502824709</v>
+        <v>-0.03397553516819407</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -22005,10 +22005,10 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>0.91454802259887</v>
+        <v>0.9146083274523642</v>
       </c>
       <c r="H281" t="n">
-        <v>6.625755649717514</v>
+        <v>6.626422018348625</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -22027,16 +22027,16 @@
         <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>-0.6342443502824855</v>
+        <v>-0.6335779816513751</v>
       </c>
       <c r="N281" t="n">
-        <v>0.6342443502824855</v>
+        <v>0.6335779816513751</v>
       </c>
       <c r="O281" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P281" t="n">
-        <v>-0.05379237288135741</v>
+        <v>-0.0544036697247714</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -22076,10 +22076,10 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>0.9110169491525424</v>
+        <v>0.9110797459421313</v>
       </c>
       <c r="H282" t="n">
-        <v>6.548368644067796</v>
+        <v>6.548715596330275</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -22098,16 +22098,16 @@
         <v>1</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.5616313559322039</v>
+        <v>-0.5612844036697249</v>
       </c>
       <c r="N282" t="n">
-        <v>0.5616313559322039</v>
+        <v>0.5612844036697249</v>
       </c>
       <c r="O282" t="n">
         <v>-0.1499999999999995</v>
       </c>
       <c r="P282" t="n">
-        <v>-0.0773870056497179</v>
+        <v>-0.07770642201834921</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -22147,10 +22147,10 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>0.9074858757062146</v>
+        <v>0.9075511644318984</v>
       </c>
       <c r="H283" t="n">
-        <v>6.515437853107343</v>
+        <v>6.516880733944955</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -22169,16 +22169,16 @@
         <v>1</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.4945621468926564</v>
+        <v>-0.4931192660550447</v>
       </c>
       <c r="N283" t="n">
-        <v>0.4945621468926564</v>
+        <v>0.4931192660550447</v>
       </c>
       <c r="O283" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P283" t="n">
-        <v>-0.03293079096045304</v>
+        <v>-0.03183486238532041</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -22218,10 +22218,10 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>0.905367231638418</v>
+        <v>0.9054340155257586</v>
       </c>
       <c r="H284" t="n">
-        <v>6.445847457627115</v>
+        <v>6.450275229357798</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -22240,16 +22240,16 @@
         <v>1</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.3741525423728849</v>
+        <v>-0.3697247706422022</v>
       </c>
       <c r="N284" t="n">
-        <v>0.3741525423728849</v>
+        <v>0.3697247706422022</v>
       </c>
       <c r="O284" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P284" t="n">
-        <v>-0.06959039548022794</v>
+        <v>-0.06660550458715697</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -22289,10 +22289,10 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>0.9018361581920904</v>
+        <v>0.9019054340155258</v>
       </c>
       <c r="H285" t="n">
-        <v>6.4026447740113</v>
+        <v>6.403027522935781</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -22311,16 +22311,16 @@
         <v>1</v>
       </c>
       <c r="M285" t="n">
-        <v>-0.2973552259887002</v>
+        <v>-0.2969724770642195</v>
       </c>
       <c r="N285" t="n">
-        <v>0.2973552259887002</v>
+        <v>0.2969724770642195</v>
       </c>
       <c r="O285" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P285" t="n">
-        <v>-0.04320268361581547</v>
+        <v>-0.04724770642201737</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
@@ -22360,10 +22360,10 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>0.8990112994350282</v>
+        <v>0.8990825688073395</v>
       </c>
       <c r="H286" t="n">
-        <v>6.358149717514123</v>
+        <v>6.359724770642202</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -22382,16 +22382,16 @@
         <v>1</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.1818502824858772</v>
+        <v>-0.1802752293577976</v>
       </c>
       <c r="N286" t="n">
-        <v>0.1818502824858772</v>
+        <v>0.1802752293577976</v>
       </c>
       <c r="O286" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P286" t="n">
-        <v>-0.04449505649717711</v>
+        <v>-0.04330275229357827</v>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
@@ -25685,10 +25685,10 @@
         <v>8</v>
       </c>
       <c r="G333" t="n">
-        <v>0.7641242937853108</v>
+        <v>0.7642907551164432</v>
       </c>
       <c r="H333" t="n">
-        <v>6.486122881355933</v>
+        <v>6.487064220183487</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -25707,16 +25707,16 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.7763771186440671</v>
+        <v>-0.7754357798165135</v>
       </c>
       <c r="N333" t="n">
-        <v>0.7763771186440671</v>
+        <v>0.7754357798165135</v>
       </c>
       <c r="O333" t="n">
         <v>-0.4400000000000004</v>
       </c>
       <c r="P333" t="n">
-        <v>-0.9813823744254258</v>
+        <v>-0.9804410355978721</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -25756,10 +25756,10 @@
         <v>8</v>
       </c>
       <c r="G334" t="n">
-        <v>0.7725988700564972</v>
+        <v>0.7727593507410021</v>
       </c>
       <c r="H334" t="n">
-        <v>6.537767478813559</v>
+        <v>6.538107798165138</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -25778,16 +25778,16 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.4372325211864405</v>
+        <v>-0.436892201834862</v>
       </c>
       <c r="N334" t="n">
-        <v>0.4372325211864405</v>
+        <v>0.436892201834862</v>
       </c>
       <c r="O334" t="n">
         <v>-0.2875000000000005</v>
       </c>
       <c r="P334" t="n">
-        <v>0.05164459745762606</v>
+        <v>0.05104357798165093</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -25827,10 +25827,10 @@
         <v>8</v>
       </c>
       <c r="G335" t="n">
-        <v>0.7923728813559322</v>
+        <v>0.7925194071983063</v>
       </c>
       <c r="H335" t="n">
-        <v>6.646843220338982</v>
+        <v>6.650986238532109</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -25849,16 +25849,16 @@
         <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.1531567796610176</v>
+        <v>-0.1490137614678906</v>
       </c>
       <c r="N335" t="n">
-        <v>0.1531567796610176</v>
+        <v>0.1490137614678906</v>
       </c>
       <c r="O335" t="n">
         <v>-0.1749999999999998</v>
       </c>
       <c r="P335" t="n">
-        <v>0.1090757415254231</v>
+        <v>0.1128784403669716</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -25898,10 +25898,10 @@
         <v>8</v>
       </c>
       <c r="G336" t="n">
-        <v>0.8149717514124294</v>
+        <v>0.8151023288637967</v>
       </c>
       <c r="H336" t="n">
-        <v>6.848665254237288</v>
+        <v>6.84940366972477</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -25920,16 +25920,16 @@
         <v>1</v>
       </c>
       <c r="M336" t="n">
-        <v>0.2186652542372878</v>
+        <v>0.2194036697247705</v>
       </c>
       <c r="N336" t="n">
-        <v>0.2186652542372878</v>
+        <v>0.2194036697247705</v>
       </c>
       <c r="O336" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P336" t="n">
-        <v>0.2018220338983054</v>
+        <v>0.1984174311926612</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -25969,10 +25969,10 @@
         <v>8</v>
       </c>
       <c r="G337" t="n">
-        <v>0.8347457627118644</v>
+        <v>0.8348623853211009</v>
       </c>
       <c r="H337" t="n">
-        <v>7.065487288135594</v>
+        <v>7.066146788990825</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -25991,16 +25991,16 @@
         <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>0.5754872881355935</v>
+        <v>0.5761467889908252</v>
       </c>
       <c r="N337" t="n">
-        <v>0.5754872881355935</v>
+        <v>0.5761467889908252</v>
       </c>
       <c r="O337" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P337" t="n">
-        <v>0.216822033898306</v>
+        <v>0.2167431192660549</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>8</v>
       </c>
       <c r="G338" t="n">
-        <v>0.8509887005649718</v>
+        <v>0.8510938602681722</v>
       </c>
       <c r="H338" t="n">
-        <v>7.148468220338983</v>
+        <v>7.148587155963303</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -26062,16 +26062,16 @@
         <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>0.6684682203389825</v>
+        <v>0.6685871559633023</v>
       </c>
       <c r="N338" t="n">
-        <v>0.6684682203389825</v>
+        <v>0.6685871559633023</v>
       </c>
       <c r="O338" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P338" t="n">
-        <v>0.0829809322033892</v>
+        <v>0.08244036697247736</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -26111,10 +26111,10 @@
         <v>8</v>
       </c>
       <c r="G339" t="n">
-        <v>0.8580508474576272</v>
+        <v>0.858151023288638</v>
       </c>
       <c r="H339" t="n">
-        <v>7.204777542372882</v>
+        <v>7.205344036697248</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -26133,16 +26133,16 @@
         <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>0.6547775423728819</v>
+        <v>0.6553440366972483</v>
       </c>
       <c r="N339" t="n">
-        <v>0.6547775423728819</v>
+        <v>0.6553440366972483</v>
       </c>
       <c r="O339" t="n">
         <v>0.0699999999999994</v>
       </c>
       <c r="P339" t="n">
-        <v>0.05630932203389882</v>
+        <v>0.05675688073394536</v>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
@@ -26182,10 +26182,10 @@
         <v>8</v>
       </c>
       <c r="G340" t="n">
-        <v>0.8502824858757062</v>
+        <v>0.8503881439661256</v>
       </c>
       <c r="H340" t="n">
-        <v>7.147669491525424</v>
+        <v>7.147788990825688</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -26204,16 +26204,16 @@
         <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>0.6176694915254233</v>
+        <v>0.6177889908256882</v>
       </c>
       <c r="N340" t="n">
-        <v>0.6176694915254233</v>
+        <v>0.6177889908256882</v>
       </c>
       <c r="O340" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P340" t="n">
-        <v>-0.05710805084745818</v>
+        <v>-0.05755504587155968</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -26253,10 +26253,10 @@
         <v>8</v>
       </c>
       <c r="G341" t="n">
-        <v>0.8305084745762712</v>
+        <v>0.8306280875088214</v>
       </c>
       <c r="H341" t="n">
-        <v>7.025367231638418</v>
+        <v>7.026269113149847</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -26275,16 +26275,16 @@
         <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>0.6928672316384183</v>
+        <v>0.6937691131498473</v>
       </c>
       <c r="N341" t="n">
-        <v>0.6928672316384183</v>
+        <v>0.6937691131498473</v>
       </c>
       <c r="O341" t="n">
         <v>-0.1975000000000007</v>
       </c>
       <c r="P341" t="n">
-        <v>-0.1223022598870056</v>
+        <v>-0.1215198776758415</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -26324,10 +26324,10 @@
         <v>8</v>
       </c>
       <c r="G342" t="n">
-        <v>0.8107344632768362</v>
+        <v>0.8108680310515173</v>
       </c>
       <c r="H342" t="n">
-        <v>6.819925847457627</v>
+        <v>6.820917431192661</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -26346,16 +26346,16 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>0.6299258474576268</v>
+        <v>0.6309174311926604</v>
       </c>
       <c r="N342" t="n">
-        <v>0.6299258474576268</v>
+        <v>0.6309174311926604</v>
       </c>
       <c r="O342" t="n">
         <v>-0.1424999999999992</v>
       </c>
       <c r="P342" t="n">
-        <v>-0.2054413841807907</v>
+        <v>-0.2053516819571861</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>8</v>
       </c>
       <c r="G343" t="n">
-        <v>0.7874293785310734</v>
+        <v>0.7875793930839803</v>
       </c>
       <c r="H343" t="n">
         <v>6.62</v>
@@ -26426,7 +26426,7 @@
         <v>-0.2000000000000002</v>
       </c>
       <c r="P343" t="n">
-        <v>-0.1999258474576271</v>
+        <v>-0.2009174311926607</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -26466,10 +26466,10 @@
         <v>8</v>
       </c>
       <c r="G344" t="n">
-        <v>0.7634180790960452</v>
+        <v>0.7635850388143967</v>
       </c>
       <c r="H344" t="n">
-        <v>6.482129237288136</v>
+        <v>6.483073394495413</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -26488,16 +26488,16 @@
         <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5621292372881364</v>
+        <v>0.5630733944954134</v>
       </c>
       <c r="N344" t="n">
-        <v>0.5621292372881364</v>
+        <v>0.5630733944954134</v>
       </c>
       <c r="O344" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P344" t="n">
-        <v>-0.1378707627118638</v>
+        <v>-0.1369266055045868</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>8</v>
       </c>
       <c r="G345" t="n">
-        <v>0.7415254237288136</v>
+        <v>0.7417078334509527</v>
       </c>
       <c r="H345" t="n">
         <v>6.380000000000001</v>
@@ -26568,7 +26568,7 @@
         <v>0.0600000000000005</v>
       </c>
       <c r="P345" t="n">
-        <v>-0.1021292372881355</v>
+        <v>-0.1030733944954125</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -26608,10 +26608,10 @@
         <v>8</v>
       </c>
       <c r="G346" t="n">
-        <v>0.7182203389830508</v>
+        <v>0.7184191954834157</v>
       </c>
       <c r="H346" t="n">
-        <v>6.232304025423729</v>
+        <v>6.233990825688074</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -26630,16 +26630,16 @@
         <v>1</v>
       </c>
       <c r="M346" t="n">
-        <v>0.1123040254237289</v>
+        <v>0.1139908256880737</v>
       </c>
       <c r="N346" t="n">
-        <v>0.1123040254237289</v>
+        <v>0.1139908256880737</v>
       </c>
       <c r="O346" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P346" t="n">
-        <v>-0.1476959745762718</v>
+        <v>-0.1460091743119269</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -27809,10 +27809,10 @@
         <v>8</v>
       </c>
       <c r="G363" t="n">
-        <v>0.6454802259887006</v>
+        <v>0.6457304163726182</v>
       </c>
       <c r="H363" t="n">
-        <v>6.969874646892655</v>
+        <v>6.970555751587861</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -27831,16 +27831,16 @@
         <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>-1.492625353107345</v>
+        <v>-1.491944248412139</v>
       </c>
       <c r="N363" t="n">
-        <v>1.492625353107345</v>
+        <v>1.491944248412139</v>
       </c>
       <c r="O363" t="n">
         <v>-0.254999999999999</v>
       </c>
       <c r="P363" t="n">
-        <v>0.1272940582451429</v>
+        <v>0.1279751629403494</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -27880,10 +27880,10 @@
         <v>8</v>
       </c>
       <c r="G364" t="n">
-        <v>0.653954802259887</v>
+        <v>0.6541990119971771</v>
       </c>
       <c r="H364" t="n">
-        <v>7.008064971751413</v>
+        <v>7.009767113620325</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -27902,16 +27902,16 @@
         <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>-1.304435028248587</v>
+        <v>-1.302732886379675</v>
       </c>
       <c r="N364" t="n">
-        <v>1.304435028248587</v>
+        <v>1.302732886379675</v>
       </c>
       <c r="O364" t="n">
         <v>-0.1500000000000004</v>
       </c>
       <c r="P364" t="n">
-        <v>0.03819032485875784</v>
+        <v>0.03921136203246345</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -27951,10 +27951,10 @@
         <v>8</v>
       </c>
       <c r="G365" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6669019054340155</v>
       </c>
       <c r="H365" t="n">
-        <v>7.068333333333333</v>
+        <v>7.069153140437544</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -27973,16 +27973,16 @@
         <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>-1.061666666666667</v>
+        <v>-1.060846859562457</v>
       </c>
       <c r="N365" t="n">
-        <v>1.061666666666667</v>
+        <v>1.060846859562457</v>
       </c>
       <c r="O365" t="n">
         <v>-0.1824999999999992</v>
       </c>
       <c r="P365" t="n">
-        <v>0.06026836158192062</v>
+        <v>0.05938602681721949</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -28022,10 +28022,10 @@
         <v>8</v>
       </c>
       <c r="G366" t="n">
-        <v>0.6807909604519774</v>
+        <v>0.6810162314749471</v>
       </c>
       <c r="H366" t="n">
-        <v>7.166001059322033</v>
+        <v>7.166884262526463</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -28044,16 +28044,16 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.9214989406779672</v>
+        <v>-0.9206157374735371</v>
       </c>
       <c r="N366" t="n">
-        <v>0.9214989406779672</v>
+        <v>0.9206157374735371</v>
       </c>
       <c r="O366" t="n">
         <v>-0.04250000000000043</v>
       </c>
       <c r="P366" t="n">
-        <v>0.09766772598869977</v>
+        <v>0.09773112208891899</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -28093,10 +28093,10 @@
         <v>8</v>
       </c>
       <c r="G367" t="n">
-        <v>0.6885593220338984</v>
+        <v>0.6887791107974595</v>
       </c>
       <c r="H367" t="n">
-        <v>7.192407309322035</v>
+        <v>7.192961067984005</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -28115,16 +28115,16 @@
         <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>-1.037592690677966</v>
+        <v>-1.037038932015996</v>
       </c>
       <c r="N367" t="n">
-        <v>1.037592690677966</v>
+        <v>1.037038932015996</v>
       </c>
       <c r="O367" t="n">
         <v>0.1425000000000001</v>
       </c>
       <c r="P367" t="n">
-        <v>0.02640625000000174</v>
+        <v>0.02607680545754132</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -28164,10 +28164,10 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>0.6899717514124294</v>
+        <v>0.6901905434015526</v>
       </c>
       <c r="H368" t="n">
-        <v>7.197810145951037</v>
+        <v>7.198699717713479</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -28186,16 +28186,16 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.8446898540489638</v>
+        <v>-0.8438002822865212</v>
       </c>
       <c r="N368" t="n">
-        <v>0.8446898540489638</v>
+        <v>0.8438002822865212</v>
       </c>
       <c r="O368" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P368" t="n">
-        <v>0.005402836629001762</v>
+        <v>0.005738649729474687</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -28235,10 +28235,10 @@
         <v>8</v>
       </c>
       <c r="G369" t="n">
-        <v>0.684322033898305</v>
+        <v>0.68454481298518</v>
       </c>
       <c r="H369" t="n">
-        <v>7.179845074152542</v>
+        <v>7.181277346506705</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -28257,16 +28257,16 @@
         <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.770154925847458</v>
+        <v>-0.7687226534932954</v>
       </c>
       <c r="N369" t="n">
-        <v>0.770154925847458</v>
+        <v>0.7687226534932954</v>
       </c>
       <c r="O369" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P369" t="n">
-        <v>-0.01796507179849449</v>
+        <v>-0.01742237120677448</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -28306,10 +28306,10 @@
         <v>8</v>
       </c>
       <c r="G370" t="n">
-        <v>0.672316384180791</v>
+        <v>0.6725476358503881</v>
       </c>
       <c r="H370" t="n">
-        <v>7.113022598870057</v>
+        <v>7.113828510938603</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -28328,16 +28328,16 @@
         <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.8669774011299438</v>
+        <v>-0.8661714890613972</v>
       </c>
       <c r="N370" t="n">
-        <v>0.8669774011299438</v>
+        <v>0.8661714890613972</v>
       </c>
       <c r="O370" t="n">
         <v>0.03000000000000025</v>
       </c>
       <c r="P370" t="n">
-        <v>-0.06682247528248553</v>
+        <v>-0.06744883556810155</v>
       </c>
       <c r="Q370" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>8</v>
       </c>
       <c r="G371" t="n">
-        <v>0.6532485875706214</v>
+        <v>0.6534932956951306</v>
       </c>
       <c r="H371" t="n">
-        <v>7.003142655367231</v>
+        <v>7.00484827099506</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -28399,16 +28399,16 @@
         <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>-1.031857344632769</v>
+        <v>-1.03015172900494</v>
       </c>
       <c r="N371" t="n">
-        <v>1.031857344632769</v>
+        <v>1.03015172900494</v>
       </c>
       <c r="O371" t="n">
         <v>0.05499999999999972</v>
       </c>
       <c r="P371" t="n">
-        <v>-0.1098799435028255</v>
+        <v>-0.1089802399435431</v>
       </c>
       <c r="Q371" t="inlineStr">
         <is>
@@ -28448,10 +28448,10 @@
         <v>8</v>
       </c>
       <c r="G372" t="n">
-        <v>0.6313559322033898</v>
+        <v>0.6316160903316866</v>
       </c>
       <c r="H372" t="n">
-        <v>6.937637711864407</v>
+        <v>6.938091037402964</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -28470,16 +28470,16 @@
         <v>1</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.9723622881355931</v>
+        <v>-0.9719089625970359</v>
       </c>
       <c r="N372" t="n">
-        <v>0.9723622881355931</v>
+        <v>0.9719089625970359</v>
       </c>
       <c r="O372" t="n">
         <v>-0.125</v>
       </c>
       <c r="P372" t="n">
-        <v>-0.0655049435028241</v>
+        <v>-0.06675723359209584</v>
       </c>
       <c r="Q372" t="inlineStr">
         <is>
@@ -28519,10 +28519,10 @@
         <v>8</v>
       </c>
       <c r="G373" t="n">
-        <v>0.6165254237288136</v>
+        <v>0.6167960479887086</v>
       </c>
       <c r="H373" t="n">
-        <v>6.881988877118644</v>
+        <v>6.883167784050812</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -28541,16 +28541,16 @@
         <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.8080111228813562</v>
+        <v>-0.8068322159491883</v>
       </c>
       <c r="N373" t="n">
-        <v>0.8080111228813562</v>
+        <v>0.8068322159491883</v>
       </c>
       <c r="O373" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P373" t="n">
-        <v>-0.05564883474576288</v>
+        <v>-0.0549232533521522</v>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
@@ -28590,10 +28590,10 @@
         <v>8</v>
       </c>
       <c r="G374" t="n">
-        <v>0.5988700564971752</v>
+        <v>0.5991531404375441</v>
       </c>
       <c r="H374" t="n">
-        <v>6.799265536723164</v>
+        <v>6.79951217360621</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -28612,16 +28612,16 @@
         <v>1</v>
       </c>
       <c r="M374" t="n">
-        <v>-0.6607344632768362</v>
+        <v>-0.6604878263937897</v>
       </c>
       <c r="N374" t="n">
-        <v>0.6607344632768362</v>
+        <v>0.6604878263937897</v>
       </c>
       <c r="O374" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P374" t="n">
-        <v>-0.08272334039548035</v>
+        <v>-0.08365561044460179</v>
       </c>
       <c r="Q374" t="inlineStr">
         <is>
@@ -28661,10 +28661,10 @@
         <v>8</v>
       </c>
       <c r="G375" t="n">
-        <v>0.5840395480225988</v>
+        <v>0.584333098094566</v>
       </c>
       <c r="H375" t="n">
-        <v>6.761344456214689</v>
+        <v>6.761600211714891</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -28683,16 +28683,16 @@
         <v>1</v>
       </c>
       <c r="M375" t="n">
-        <v>-0.5186555437853109</v>
+        <v>-0.5183997882851097</v>
       </c>
       <c r="N375" t="n">
-        <v>0.5186555437853109</v>
+        <v>0.5183997882851097</v>
       </c>
       <c r="O375" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.03792108050847443</v>
+        <v>-0.03791196189131973</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
@@ -28732,10 +28732,10 @@
         <v>8</v>
       </c>
       <c r="G376" t="n">
-        <v>0.565677966101695</v>
+        <v>0.565984474241355</v>
       </c>
       <c r="H376" t="n">
-        <v>6.682775423728813</v>
+        <v>6.684911785462244</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -28754,16 +28754,16 @@
         <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>-0.427224576271187</v>
+        <v>-0.4250882145377561</v>
       </c>
       <c r="N376" t="n">
-        <v>0.427224576271187</v>
+        <v>0.4250882145377561</v>
       </c>
       <c r="O376" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.0785690324858761</v>
+        <v>-0.07668842625264638</v>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
@@ -29933,10 +29933,10 @@
         <v>8</v>
       </c>
       <c r="G393" t="n">
-        <v>0.6581920903954802</v>
+        <v>0.6577275935074101</v>
       </c>
       <c r="H393" t="n">
-        <v>5.811271186440678</v>
+        <v>5.804911785462244</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -29955,16 +29955,16 @@
         <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>1.021271186440677</v>
+        <v>1.014911785462243</v>
       </c>
       <c r="N393" t="n">
-        <v>1.021271186440677</v>
+        <v>1.014911785462243</v>
       </c>
       <c r="O393" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P393" t="n">
-        <v>-0.654250887841032</v>
+        <v>-0.6606102888194654</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
@@ -30004,10 +30004,10 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>0.5635593220338984</v>
+        <v>0.5631616090331687</v>
       </c>
       <c r="H394" t="n">
-        <v>5.499120762711864</v>
+        <v>5.498336273817925</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -30026,16 +30026,16 @@
         <v>1</v>
       </c>
       <c r="M394" t="n">
-        <v>0.829120762711864</v>
+        <v>0.828336273817925</v>
       </c>
       <c r="N394" t="n">
-        <v>0.829120762711864</v>
+        <v>0.828336273817925</v>
       </c>
       <c r="O394" t="n">
         <v>-0.120000000000001</v>
       </c>
       <c r="P394" t="n">
-        <v>-0.3121504237288137</v>
+        <v>-0.3065755116443194</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -30075,10 +30075,10 @@
         <v>8</v>
       </c>
       <c r="G395" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5412844036697247</v>
       </c>
       <c r="H395" t="n">
-        <v>5.456145833333333</v>
+        <v>5.455894495412844</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -30097,16 +30097,16 @@
         <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>0.9161458333333332</v>
+        <v>0.9158944954128438</v>
       </c>
       <c r="N395" t="n">
-        <v>0.9161458333333332</v>
+        <v>0.9158944954128438</v>
       </c>
       <c r="O395" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P395" t="n">
-        <v>-0.04297492937853065</v>
+        <v>-0.04244177840508101</v>
       </c>
       <c r="Q395" t="inlineStr">
         <is>
@@ -30146,10 +30146,10 @@
         <v>8</v>
       </c>
       <c r="G396" t="n">
-        <v>0.5953389830508474</v>
+        <v>0.5949188426252646</v>
       </c>
       <c r="H396" t="n">
-        <v>5.636435381355932</v>
+        <v>5.636159139026112</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -30168,16 +30168,16 @@
         <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>1.196435381355932</v>
+        <v>1.196159139026111</v>
       </c>
       <c r="N396" t="n">
-        <v>1.196435381355932</v>
+        <v>1.196159139026111</v>
       </c>
       <c r="O396" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P396" t="n">
-        <v>0.180289548022599</v>
+        <v>0.1802646436132678</v>
       </c>
       <c r="Q396" t="inlineStr">
         <is>
@@ -30217,10 +30217,10 @@
         <v>8</v>
       </c>
       <c r="G397" t="n">
-        <v>0.6334745762711864</v>
+        <v>0.6330275229357798</v>
       </c>
       <c r="H397" t="n">
-        <v>5.756509533898305</v>
+        <v>5.756215596330276</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -30239,16 +30239,16 @@
         <v>1</v>
       </c>
       <c r="M397" t="n">
-        <v>1.316509533898305</v>
+        <v>1.316215596330276</v>
       </c>
       <c r="N397" t="n">
-        <v>1.316509533898305</v>
+        <v>1.316215596330276</v>
       </c>
       <c r="O397" t="n">
         <v>0</v>
       </c>
       <c r="P397" t="n">
-        <v>0.1200741525423732</v>
+        <v>0.1200564573041643</v>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>8</v>
       </c>
       <c r="G398" t="n">
-        <v>0.5939265536723164</v>
+        <v>0.5935074100211715</v>
       </c>
       <c r="H398" t="n">
-        <v>5.635506709039548</v>
+        <v>5.63523112208892</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -30310,16 +30310,16 @@
         <v>1</v>
       </c>
       <c r="M398" t="n">
-        <v>1.235506709039548</v>
+        <v>1.23523112208892</v>
       </c>
       <c r="N398" t="n">
-        <v>1.235506709039548</v>
+        <v>1.23523112208892</v>
       </c>
       <c r="O398" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P398" t="n">
-        <v>-0.1210028248587571</v>
+        <v>-0.1209844742413555</v>
       </c>
       <c r="Q398" t="inlineStr">
         <is>
@@ -30359,10 +30359,10 @@
         <v>8</v>
       </c>
       <c r="G399" t="n">
-        <v>0.4781073446327684</v>
+        <v>0.4777699364855328</v>
       </c>
       <c r="H399" t="n">
-        <v>5.189355579096046</v>
+        <v>5.189133733239238</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -30381,16 +30381,16 @@
         <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>0.8093555790960458</v>
+        <v>0.8091337332392383</v>
       </c>
       <c r="N399" t="n">
-        <v>0.8093555790960458</v>
+        <v>0.8091337332392383</v>
       </c>
       <c r="O399" t="n">
         <v>-0.02000000000000046</v>
       </c>
       <c r="P399" t="n">
-        <v>-0.4461511299435026</v>
+        <v>-0.4460973888496822</v>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
@@ -30430,10 +30430,10 @@
         <v>8</v>
       </c>
       <c r="G400" t="n">
-        <v>0.3693502824858757</v>
+        <v>0.3690896259703599</v>
       </c>
       <c r="H400" t="n">
-        <v>4.842847810734463</v>
+        <v>4.842676429075512</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -30452,16 +30452,16 @@
         <v>1</v>
       </c>
       <c r="M400" t="n">
-        <v>0.7028478107344638</v>
+        <v>0.7026764290755123</v>
       </c>
       <c r="N400" t="n">
-        <v>0.7028478107344638</v>
+        <v>0.7026764290755123</v>
       </c>
       <c r="O400" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P400" t="n">
-        <v>-0.3465077683615823</v>
+        <v>-0.3464573041637262</v>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
@@ -30501,10 +30501,10 @@
         <v>8</v>
       </c>
       <c r="G401" t="n">
-        <v>0.3248587570621469</v>
+        <v>0.3246294989414256</v>
       </c>
       <c r="H401" t="n">
-        <v>4.695635593220339</v>
+        <v>4.693826746647848</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -30523,16 +30523,16 @@
         <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>0.8256355932203387</v>
+        <v>0.8238267466478479</v>
       </c>
       <c r="N401" t="n">
-        <v>0.8256355932203387</v>
+        <v>0.8238267466478479</v>
       </c>
       <c r="O401" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P401" t="n">
-        <v>-0.1472122175141246</v>
+        <v>-0.1488496824276639</v>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
@@ -30572,10 +30572,10 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>0.3509887005649718</v>
+        <v>0.3507410021171489</v>
       </c>
       <c r="H402" t="n">
-        <v>4.805775070621468</v>
+        <v>4.805612208892025</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -30594,16 +30594,16 @@
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>1.085775070621468</v>
+        <v>1.085612208892025</v>
       </c>
       <c r="N402" t="n">
-        <v>1.085775070621468</v>
+        <v>1.085612208892025</v>
       </c>
       <c r="O402" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P402" t="n">
-        <v>0.1101394774011295</v>
+        <v>0.1117854622441774</v>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -30643,10 +30643,10 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>0.528954802259887</v>
+        <v>0.5285815102328864</v>
       </c>
       <c r="H403" t="n">
-        <v>5.440575564971751</v>
+        <v>5.440084685956245</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -30665,16 +30665,16 @@
         <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>1.740575564971751</v>
+        <v>1.740084685956245</v>
       </c>
       <c r="N403" t="n">
-        <v>1.740575564971751</v>
+        <v>1.740084685956245</v>
       </c>
       <c r="O403" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P403" t="n">
-        <v>0.6348004943502827</v>
+        <v>0.6344724770642198</v>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>8</v>
       </c>
       <c r="G404" t="n">
-        <v>0.760593220338983</v>
+        <v>0.7600564573041637</v>
       </c>
       <c r="H404" t="n">
-        <v>6.10072033898305</v>
+        <v>6.099737120677488</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -30736,16 +30736,16 @@
         <v>1</v>
       </c>
       <c r="M404" t="n">
-        <v>2.260720338983051</v>
+        <v>2.259737120677488</v>
       </c>
       <c r="N404" t="n">
-        <v>2.260720338983051</v>
+        <v>2.259737120677488</v>
       </c>
       <c r="O404" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P404" t="n">
-        <v>0.6601447740112993</v>
+        <v>0.6596524347212425</v>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
@@ -30785,10 +30785,10 @@
         <v>8</v>
       </c>
       <c r="G405" t="n">
-        <v>0.8312146892655368</v>
+        <v>0.8306280875088214</v>
       </c>
       <c r="H405" t="n">
-        <v>6.343712923728813</v>
+        <v>6.340241707833451</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -30807,16 +30807,16 @@
         <v>1</v>
       </c>
       <c r="M405" t="n">
-        <v>2.323712923728814</v>
+        <v>2.320241707833452</v>
       </c>
       <c r="N405" t="n">
-        <v>2.323712923728814</v>
+        <v>2.320241707833452</v>
       </c>
       <c r="O405" t="n">
         <v>0.1799999999999997</v>
       </c>
       <c r="P405" t="n">
-        <v>0.242992584745763</v>
+        <v>0.2405045871559635</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
@@ -30856,10 +30856,10 @@
         <v>8</v>
       </c>
       <c r="G406" t="n">
-        <v>0.815677966101695</v>
+        <v>0.8151023288637967</v>
       </c>
       <c r="H406" t="n">
-        <v>6.290582627118645</v>
+        <v>6.286797812279464</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -30878,16 +30878,16 @@
         <v>1</v>
       </c>
       <c r="M406" t="n">
-        <v>2.190582627118645</v>
+        <v>2.186797812279464</v>
       </c>
       <c r="N406" t="n">
-        <v>2.190582627118645</v>
+        <v>2.186797812279464</v>
       </c>
       <c r="O406" t="n">
         <v>0.08000000000000007</v>
       </c>
       <c r="P406" t="n">
-        <v>-0.05313029661016877</v>
+        <v>-0.0534438955539871</v>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
@@ -32057,10 +32057,10 @@
         <v>8</v>
       </c>
       <c r="G423" t="n">
-        <v>0.8298022598870056</v>
+        <v>0.8299223712067749</v>
       </c>
       <c r="H423" t="n">
-        <v>5.566001059322033</v>
+        <v>5.566774876499647</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -32079,16 +32079,16 @@
         <v>1</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.8014989406779671</v>
+        <v>-0.800725123500353</v>
       </c>
       <c r="N423" t="n">
-        <v>0.8014989406779671</v>
+        <v>0.800725123500353</v>
       </c>
       <c r="O423" t="n">
         <v>-0.07500000000000018</v>
       </c>
       <c r="P423" t="n">
-        <v>-1.47292851320775</v>
+        <v>-1.472154696030135</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
@@ -32128,10 +32128,10 @@
         <v>8</v>
       </c>
       <c r="G424" t="n">
-        <v>0.827683615819209</v>
+        <v>0.8278052223006351</v>
       </c>
       <c r="H424" t="n">
-        <v>5.549901129943502</v>
+        <v>5.550846859562456</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -32150,16 +32150,16 @@
         <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>-0.7675988700564975</v>
+        <v>-0.7666531404375441</v>
       </c>
       <c r="N424" t="n">
-        <v>0.7675988700564975</v>
+        <v>0.7666531404375441</v>
       </c>
       <c r="O424" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P424" t="n">
-        <v>-0.01609992937853022</v>
+        <v>-0.01592801693719093</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -32199,10 +32199,10 @@
         <v>8</v>
       </c>
       <c r="G425" t="n">
-        <v>0.8213276836158192</v>
+        <v>0.821453775582216</v>
       </c>
       <c r="H425" t="n">
-        <v>5.505204802259887</v>
+        <v>5.506287932251236</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -32221,16 +32221,16 @@
         <v>1</v>
       </c>
       <c r="M425" t="n">
-        <v>-0.7547951977401128</v>
+        <v>-0.7537120677487641</v>
       </c>
       <c r="N425" t="n">
-        <v>0.7547951977401128</v>
+        <v>0.7537120677487641</v>
       </c>
       <c r="O425" t="n">
         <v>-0.05750000000000011</v>
       </c>
       <c r="P425" t="n">
-        <v>-0.04469632768361542</v>
+        <v>-0.04455892731122013</v>
       </c>
       <c r="Q425" t="inlineStr">
         <is>
@@ -32270,10 +32270,10 @@
         <v>8</v>
       </c>
       <c r="G426" t="n">
-        <v>0.818502824858757</v>
+        <v>0.8186309103740297</v>
       </c>
       <c r="H426" t="n">
-        <v>5.490469632768362</v>
+        <v>5.491019760056458</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -32292,16 +32292,16 @@
         <v>1</v>
       </c>
       <c r="M426" t="n">
-        <v>-0.6395303672316377</v>
+        <v>-0.6389802399435416</v>
       </c>
       <c r="N426" t="n">
-        <v>0.6395303672316377</v>
+        <v>0.6389802399435416</v>
       </c>
       <c r="O426" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P426" t="n">
-        <v>-0.01473516949152476</v>
+        <v>-0.01526817219477739</v>
       </c>
       <c r="Q426" t="inlineStr">
         <is>
@@ -32341,10 +32341,10 @@
         <v>8</v>
       </c>
       <c r="G427" t="n">
-        <v>0.809322033898305</v>
+        <v>0.8094565984474241</v>
       </c>
       <c r="H427" t="n">
-        <v>5.383278601694914</v>
+        <v>5.383712067748764</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -32363,16 +32363,16 @@
         <v>1</v>
       </c>
       <c r="M427" t="n">
-        <v>-0.6067213983050861</v>
+        <v>-0.6062879322512362</v>
       </c>
       <c r="N427" t="n">
-        <v>0.6067213983050861</v>
+        <v>0.6062879322512362</v>
       </c>
       <c r="O427" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P427" t="n">
-        <v>-0.1071910310734481</v>
+        <v>-0.1073076923076943</v>
       </c>
       <c r="Q427" t="inlineStr">
         <is>
@@ -32412,10 +32412,10 @@
         <v>8</v>
       </c>
       <c r="G428" t="n">
-        <v>0.7888418079096046</v>
+        <v>0.7889908256880734</v>
       </c>
       <c r="H428" t="n">
-        <v>5.229037782485876</v>
+        <v>5.229357798165138</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -32434,16 +32434,16 @@
         <v>1</v>
       </c>
       <c r="M428" t="n">
-        <v>-0.4784622175141235</v>
+        <v>-0.4781422018348618</v>
       </c>
       <c r="N428" t="n">
-        <v>0.4784622175141235</v>
+        <v>0.4781422018348618</v>
       </c>
       <c r="O428" t="n">
         <v>-0.2825000000000006</v>
       </c>
       <c r="P428" t="n">
-        <v>-0.1542408192090381</v>
+        <v>-0.1543542695836262</v>
       </c>
       <c r="Q428" t="inlineStr">
         <is>
@@ -32483,10 +32483,10 @@
         <v>8</v>
       </c>
       <c r="G429" t="n">
-        <v>0.7711864406779662</v>
+        <v>0.7713479181369089</v>
       </c>
       <c r="H429" t="n">
-        <v>5.102245762711864</v>
+        <v>5.102939308398024</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
@@ -32505,16 +32505,16 @@
         <v>1</v>
       </c>
       <c r="M429" t="n">
-        <v>-0.4577542372881354</v>
+        <v>-0.4570606916019759</v>
       </c>
       <c r="N429" t="n">
-        <v>0.4577542372881354</v>
+        <v>0.4570606916019759</v>
       </c>
       <c r="O429" t="n">
         <v>-0.1475</v>
       </c>
       <c r="P429" t="n">
-        <v>-0.1267920197740118</v>
+        <v>-0.1264184897671141</v>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
@@ -32554,10 +32554,10 @@
         <v>8</v>
       </c>
       <c r="G430" t="n">
-        <v>0.7464689265536724</v>
+        <v>0.7466478475652788</v>
       </c>
       <c r="H430" t="n">
-        <v>4.951084039548022</v>
+        <v>4.951852505292872</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -32576,16 +32576,16 @@
         <v>1</v>
       </c>
       <c r="M430" t="n">
-        <v>-0.3889159604519774</v>
+        <v>-0.3881474947071277</v>
       </c>
       <c r="N430" t="n">
-        <v>0.3889159604519774</v>
+        <v>0.3881474947071277</v>
       </c>
       <c r="O430" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P430" t="n">
-        <v>-0.1511617231638418</v>
+        <v>-0.1510868031051515</v>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>8</v>
       </c>
       <c r="G431" t="n">
-        <v>0.7189265536723164</v>
+        <v>0.7191249117854622</v>
       </c>
       <c r="H431" t="n">
         <v>4.82</v>
@@ -32656,7 +32656,7 @@
         <v>-0.2275</v>
       </c>
       <c r="P431" t="n">
-        <v>-0.1310840395480222</v>
+        <v>-0.1318525052928718</v>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
@@ -32696,10 +32696,10 @@
         <v>8</v>
       </c>
       <c r="G432" t="n">
-        <v>0.6942090395480226</v>
+        <v>0.6944248412138321</v>
       </c>
       <c r="H432" t="n">
-        <v>4.650813912429379</v>
+        <v>4.651277346506705</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -32718,16 +32718,16 @@
         <v>1</v>
       </c>
       <c r="M432" t="n">
-        <v>-0.3591860875706212</v>
+        <v>-0.3587226534932952</v>
       </c>
       <c r="N432" t="n">
-        <v>0.3591860875706212</v>
+        <v>0.3587226534932952</v>
       </c>
       <c r="O432" t="n">
         <v>-0.1025</v>
       </c>
       <c r="P432" t="n">
-        <v>-0.1691860875706217</v>
+        <v>-0.1687226534932957</v>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
@@ -32767,10 +32767,10 @@
         <v>8</v>
       </c>
       <c r="G433" t="n">
-        <v>0.684322033898305</v>
+        <v>0.68454481298518</v>
       </c>
       <c r="H433" t="n">
-        <v>4.621040783898305</v>
+        <v>4.621279992942837</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -32789,16 +32789,16 @@
         <v>1</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.2189592161016947</v>
+        <v>-0.2187200070571631</v>
       </c>
       <c r="N433" t="n">
-        <v>0.2189592161016947</v>
+        <v>0.2187200070571631</v>
       </c>
       <c r="O433" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P433" t="n">
-        <v>-0.02977312853107339</v>
+        <v>-0.02999735356386779</v>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
@@ -32838,10 +32838,10 @@
         <v>8</v>
       </c>
       <c r="G434" t="n">
-        <v>0.6892655367231638</v>
+        <v>0.689484827099506</v>
       </c>
       <c r="H434" t="n">
-        <v>4.636930320150659</v>
+        <v>4.637558221594919</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -32860,16 +32860,16 @@
         <v>1</v>
       </c>
       <c r="M434" t="n">
-        <v>-0.08306967984934044</v>
+        <v>-0.08244177840508105</v>
       </c>
       <c r="N434" t="n">
-        <v>0.08306967984934044</v>
+        <v>0.08244177840508105</v>
       </c>
       <c r="O434" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P434" t="n">
-        <v>0.01588953625235412</v>
+        <v>0.01627822865208195</v>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
@@ -32909,10 +32909,10 @@
         <v>8</v>
       </c>
       <c r="G435" t="n">
-        <v>0.7090395480225988</v>
+        <v>0.7092448835568101</v>
       </c>
       <c r="H435" t="n">
-        <v>4.743766478342749</v>
+        <v>4.744942366501999</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -32931,16 +32931,16 @@
         <v>1</v>
       </c>
       <c r="M435" t="n">
-        <v>0.1837664783427497</v>
+        <v>0.1849423665019998</v>
       </c>
       <c r="N435" t="n">
-        <v>0.1837664783427497</v>
+        <v>0.1849423665019998</v>
       </c>
       <c r="O435" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P435" t="n">
-        <v>0.10683615819209</v>
+        <v>0.1073841449070807</v>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
@@ -32980,10 +32980,10 @@
         <v>8</v>
       </c>
       <c r="G436" t="n">
-        <v>0.7252824858757062</v>
+        <v>0.7254763585038815</v>
       </c>
       <c r="H436" t="n">
-        <v>4.845088276836158</v>
+        <v>4.845920959774171</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -33002,16 +33002,16 @@
         <v>1</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4550882768361584</v>
+        <v>0.4559209597741711</v>
       </c>
       <c r="N436" t="n">
-        <v>0.4550882768361584</v>
+        <v>0.4559209597741711</v>
       </c>
       <c r="O436" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P436" t="n">
-        <v>0.1013217984934087</v>
+        <v>0.1009785932721714</v>
       </c>
       <c r="Q436" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>8</v>
       </c>
       <c r="G437" t="n">
-        <v>0.8234463276836158</v>
+        <v>0.8235709244883557</v>
       </c>
       <c r="H437" t="n">
-        <v>3.499025423728813</v>
+        <v>3.500707480592801</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -33073,10 +33073,10 @@
         <v>1</v>
       </c>
       <c r="M437" t="n">
-        <v>-0.9409745762711874</v>
+        <v>-0.939292519407199</v>
       </c>
       <c r="N437" t="n">
-        <v>0.9409745762711874</v>
+        <v>0.939292519407199</v>
       </c>
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
@@ -33116,10 +33116,10 @@
         <v>8</v>
       </c>
       <c r="G438" t="n">
-        <v>0.809322033898305</v>
+        <v>0.8094565984474241</v>
       </c>
       <c r="H438" t="n">
-        <v>3.350677966101695</v>
+        <v>3.352131263232181</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -33138,16 +33138,16 @@
         <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>-0.8918220338983058</v>
+        <v>-0.8903687367678197</v>
       </c>
       <c r="N438" t="n">
-        <v>0.8918220338983058</v>
+        <v>0.8903687367678197</v>
       </c>
       <c r="O438" t="n">
         <v>-0.1974999999999998</v>
       </c>
       <c r="P438" t="n">
-        <v>-0.1483474576271182</v>
+        <v>-0.1485762173606204</v>
       </c>
       <c r="Q438" t="inlineStr">
         <is>
@@ -33187,10 +33187,10 @@
         <v>8</v>
       </c>
       <c r="G439" t="n">
-        <v>0.8001412429378532</v>
+        <v>0.8002822865208187</v>
       </c>
       <c r="H439" t="n">
-        <v>3.295381355932203</v>
+        <v>3.29576217360621</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -33209,16 +33209,16 @@
         <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>-0.8146186440677972</v>
+        <v>-0.8142378263937902</v>
       </c>
       <c r="N439" t="n">
-        <v>0.8146186440677972</v>
+        <v>0.8142378263937902</v>
       </c>
       <c r="O439" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P439" t="n">
-        <v>-0.05529661016949161</v>
+        <v>-0.05636908962597076</v>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
@@ -33258,10 +33258,10 @@
         <v>8</v>
       </c>
       <c r="G440" t="n">
-        <v>0.8043785310734464</v>
+        <v>0.8045165843330981</v>
       </c>
       <c r="H440" t="n">
-        <v>3.317288135593221</v>
+        <v>3.31877911079746</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -33280,16 +33280,16 @@
         <v>1</v>
       </c>
       <c r="M440" t="n">
-        <v>-0.6527118644067791</v>
+        <v>-0.65122088920254</v>
       </c>
       <c r="N440" t="n">
-        <v>0.6527118644067791</v>
+        <v>0.65122088920254</v>
       </c>
       <c r="O440" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P440" t="n">
-        <v>0.02190677966101795</v>
+        <v>0.02301693719125009</v>
       </c>
       <c r="Q440" t="inlineStr">
         <is>
@@ -33329,10 +33329,10 @@
         <v>8</v>
       </c>
       <c r="G441" t="n">
-        <v>0.8220338983050848</v>
+        <v>0.8221594918842625</v>
       </c>
       <c r="H441" t="n">
-        <v>3.467966101694916</v>
+        <v>3.469322512350036</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -33351,16 +33351,16 @@
         <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>-0.3620338983050839</v>
+        <v>-0.3606774876499643</v>
       </c>
       <c r="N441" t="n">
-        <v>0.3620338983050839</v>
+        <v>0.3606774876499643</v>
       </c>
       <c r="O441" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P441" t="n">
-        <v>0.150677966101695</v>
+        <v>0.1505434015525755</v>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
@@ -33400,10 +33400,10 @@
         <v>8</v>
       </c>
       <c r="G442" t="n">
-        <v>0.838276836158192</v>
+        <v>0.8383909668313339</v>
       </c>
       <c r="H442" t="n">
-        <v>3.648926553672316</v>
+        <v>3.649748294518937</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -33422,16 +33422,16 @@
         <v>1</v>
       </c>
       <c r="M442" t="n">
-        <v>-0.01107344632768381</v>
+        <v>-0.01025170548106269</v>
       </c>
       <c r="N442" t="n">
-        <v>0.01107344632768381</v>
+        <v>0.01025170548106269</v>
       </c>
       <c r="O442" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P442" t="n">
-        <v>0.1809604519774002</v>
+        <v>0.1804257821689017</v>
       </c>
       <c r="Q442" t="inlineStr">
         <is>
@@ -33471,10 +33471,10 @@
         <v>8</v>
       </c>
       <c r="G443" t="n">
-        <v>0.8481638418079096</v>
+        <v>0.8482709950599859</v>
       </c>
       <c r="H443" t="n">
-        <v>3.722563559322034</v>
+        <v>3.722997529992943</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -33493,16 +33493,16 @@
         <v>1</v>
       </c>
       <c r="M443" t="n">
-        <v>0.08256355932203396</v>
+        <v>0.08299752999294308</v>
       </c>
       <c r="N443" t="n">
-        <v>0.08256355932203396</v>
+        <v>0.08299752999294308</v>
       </c>
       <c r="O443" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P443" t="n">
-        <v>0.07363700564971776</v>
+        <v>0.07324923547400575</v>
       </c>
       <c r="Q443" t="inlineStr">
         <is>
@@ -33542,10 +33542,10 @@
         <v>8</v>
       </c>
       <c r="G444" t="n">
-        <v>0.8559322033898306</v>
+        <v>0.8560338743824982</v>
       </c>
       <c r="H444" t="n">
-        <v>3.757033898305085</v>
+        <v>3.75758292166549</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -33564,16 +33564,16 @@
         <v>1</v>
       </c>
       <c r="M444" t="n">
-        <v>0.1570338983050847</v>
+        <v>0.1575829216654903</v>
       </c>
       <c r="N444" t="n">
-        <v>0.1570338983050847</v>
+        <v>0.1575829216654903</v>
       </c>
       <c r="O444" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P444" t="n">
-        <v>0.03447033898305074</v>
+        <v>0.03458539167254715</v>
       </c>
       <c r="Q444" t="inlineStr">
         <is>
@@ -33613,10 +33613,10 @@
         <v>8</v>
       </c>
       <c r="G445" t="n">
-        <v>0.8587570621468926</v>
+        <v>0.8588567395906845</v>
       </c>
       <c r="H445" t="n">
-        <v>3.76864406779661</v>
+        <v>3.768913196894848</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -33635,16 +33635,16 @@
         <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>0.23614406779661</v>
+        <v>0.2364131968948482</v>
       </c>
       <c r="N445" t="n">
-        <v>0.23614406779661</v>
+        <v>0.2364131968948482</v>
       </c>
       <c r="O445" t="n">
         <v>-0.06749999999999989</v>
       </c>
       <c r="P445" t="n">
-        <v>0.01161016949152538</v>
+        <v>0.01133027522935803</v>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
@@ -33684,10 +33684,10 @@
         <v>8</v>
       </c>
       <c r="G446" t="n">
-        <v>0.8509887005649718</v>
+        <v>0.8510938602681722</v>
       </c>
       <c r="H446" t="n">
-        <v>3.735677966101695</v>
+        <v>3.736813690896259</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -33706,16 +33706,16 @@
         <v>1</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2956779661016946</v>
+        <v>0.2968136908962595</v>
       </c>
       <c r="N446" t="n">
-        <v>0.2956779661016946</v>
+        <v>0.2968136908962595</v>
       </c>
       <c r="O446" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P446" t="n">
-        <v>-0.03296610169491565</v>
+        <v>-0.03209950599858891</v>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
@@ -33755,10 +33755,10 @@
         <v>8</v>
       </c>
       <c r="G447" t="n">
-        <v>0.8403954802259888</v>
+        <v>0.8405081157374735</v>
       </c>
       <c r="H447" t="n">
-        <v>3.670974576271187</v>
+        <v>3.673103387438249</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -33777,16 +33777,16 @@
         <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>0.3809745762711874</v>
+        <v>0.3831033874382492</v>
       </c>
       <c r="N447" t="n">
-        <v>0.3809745762711874</v>
+        <v>0.3831033874382492</v>
       </c>
       <c r="O447" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.06470338983050716</v>
+        <v>-0.06371030345801021</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
@@ -33826,10 +33826,10 @@
         <v>8</v>
       </c>
       <c r="G448" t="n">
-        <v>0.815677966101695</v>
+        <v>0.8158080451658434</v>
       </c>
       <c r="H448" t="n">
-        <v>3.417330508474576</v>
+        <v>3.417681721947777</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -33848,16 +33848,16 @@
         <v>1</v>
       </c>
       <c r="M448" t="n">
-        <v>0.2373305084745763</v>
+        <v>0.2376817219477769</v>
       </c>
       <c r="N448" t="n">
-        <v>0.2373305084745763</v>
+        <v>0.2376817219477769</v>
       </c>
       <c r="O448" t="n">
         <v>-0.1099999999999999</v>
       </c>
       <c r="P448" t="n">
-        <v>-0.253644067796611</v>
+        <v>-0.2554216654904722</v>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
@@ -33897,10 +33897,10 @@
         <v>8</v>
       </c>
       <c r="G449" t="n">
-        <v>0.7838983050847458</v>
+        <v>0.7840508115737473</v>
       </c>
       <c r="H449" t="n">
-        <v>3.218050847457627</v>
+        <v>3.218874382498236</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -33919,16 +33919,16 @@
         <v>1</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1180508474576274</v>
+        <v>0.1188743824982361</v>
       </c>
       <c r="N449" t="n">
-        <v>0.1180508474576274</v>
+        <v>0.1188743824982361</v>
       </c>
       <c r="O449" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P449" t="n">
-        <v>-0.1992796610169489</v>
+        <v>-0.1988073394495409</v>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
@@ -33968,10 +33968,10 @@
         <v>8</v>
       </c>
       <c r="G450" t="n">
-        <v>0.7669491525423728</v>
+        <v>0.7671136203246295</v>
       </c>
       <c r="H450" t="n">
-        <v>3.111016949152542</v>
+        <v>3.111609033168666</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -33990,16 +33990,16 @@
         <v>1</v>
       </c>
       <c r="M450" t="n">
-        <v>0.01101694915254203</v>
+        <v>0.01160903316866557</v>
       </c>
       <c r="N450" t="n">
-        <v>0.01101694915254203</v>
+        <v>0.01160903316866557</v>
       </c>
       <c r="O450" t="n">
         <v>0</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.1070338983050854</v>
+        <v>-0.1072653493295705</v>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
@@ -35311,10 +35311,10 @@
         <v>8</v>
       </c>
       <c r="G469" t="n">
-        <v>0.8432203389830508</v>
+        <v>0.8433309809456598</v>
       </c>
       <c r="H469" t="n">
-        <v>8.558093220338982</v>
+        <v>8.560515172900494</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -35333,16 +35333,16 @@
         <v>1</v>
       </c>
       <c r="M469" t="n">
-        <v>-0.6819067796610181</v>
+        <v>-0.6794848270995058</v>
       </c>
       <c r="N469" t="n">
-        <v>0.6819067796610181</v>
+        <v>0.6794848270995058</v>
       </c>
       <c r="O469" t="n">
         <v>-0.08999999999999986</v>
       </c>
       <c r="P469" t="n">
-        <v>0.2591233534854442</v>
+        <v>0.2615453060469566</v>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
@@ -35382,10 +35382,10 @@
         <v>8</v>
       </c>
       <c r="G470" t="n">
-        <v>0.826271186440678</v>
+        <v>0.826393789696542</v>
       </c>
       <c r="H470" t="n">
-        <v>8.285677966101694</v>
+        <v>8.287141848976711</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -35404,16 +35404,16 @@
         <v>1</v>
       </c>
       <c r="M470" t="n">
-        <v>-0.7643220338983063</v>
+        <v>-0.7628581510232895</v>
       </c>
       <c r="N470" t="n">
-        <v>0.7643220338983063</v>
+        <v>0.7628581510232895</v>
       </c>
       <c r="O470" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P470" t="n">
-        <v>-0.2724152542372877</v>
+        <v>-0.2733733239237832</v>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -35453,10 +35453,10 @@
         <v>8</v>
       </c>
       <c r="G471" t="n">
-        <v>0.8072033898305084</v>
+        <v>0.8073394495412844</v>
       </c>
       <c r="H471" t="n">
-        <v>8.006016949152542</v>
+        <v>8.009266055045874</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -35475,16 +35475,16 @@
         <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.903983050847458</v>
+        <v>-0.9007339449541263</v>
       </c>
       <c r="N471" t="n">
-        <v>0.903983050847458</v>
+        <v>0.9007339449541263</v>
       </c>
       <c r="O471" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P471" t="n">
-        <v>-0.2796610169491522</v>
+        <v>-0.2778757939308374</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
@@ -35524,10 +35524,10 @@
         <v>8</v>
       </c>
       <c r="G472" t="n">
-        <v>0.7951977401129944</v>
+        <v>0.7953422724064926</v>
       </c>
       <c r="H472" t="n">
-        <v>7.897330508474576</v>
+        <v>7.89819336626676</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -35546,16 +35546,16 @@
         <v>1</v>
       </c>
       <c r="M472" t="n">
-        <v>-0.8726694915254232</v>
+        <v>-0.8718066337332395</v>
       </c>
       <c r="N472" t="n">
-        <v>0.8726694915254232</v>
+        <v>0.8718066337332395</v>
       </c>
       <c r="O472" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P472" t="n">
-        <v>-0.1086864406779657</v>
+        <v>-0.1110726887791138</v>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
@@ -35595,10 +35595,10 @@
         <v>8</v>
       </c>
       <c r="G473" t="n">
-        <v>0.7930790960451978</v>
+        <v>0.7932251235003529</v>
       </c>
       <c r="H473" t="n">
-        <v>7.879364406779661</v>
+        <v>7.881107974594213</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -35617,16 +35617,16 @@
         <v>1</v>
       </c>
       <c r="M473" t="n">
-        <v>-0.7006355932203387</v>
+        <v>-0.6988920254057867</v>
       </c>
       <c r="N473" t="n">
-        <v>0.7006355932203387</v>
+        <v>0.6988920254057867</v>
       </c>
       <c r="O473" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P473" t="n">
-        <v>-0.01796610169491508</v>
+        <v>-0.01708539167254663</v>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
@@ -35666,10 +35666,10 @@
         <v>8</v>
       </c>
       <c r="G474" t="n">
-        <v>0.8036723163841808</v>
+        <v>0.8038108680310515</v>
       </c>
       <c r="H474" t="n">
-        <v>7.929307909604519</v>
+        <v>7.929583627381792</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -35688,16 +35688,16 @@
         <v>1</v>
       </c>
       <c r="M474" t="n">
-        <v>-0.5206920903954799</v>
+        <v>-0.5204163726182074</v>
       </c>
       <c r="N474" t="n">
-        <v>0.5206920903954799</v>
+        <v>0.5204163726182074</v>
       </c>
       <c r="O474" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P474" t="n">
-        <v>0.04994350282485804</v>
+        <v>0.04847565278757848</v>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
@@ -35737,10 +35737,10 @@
         <v>8</v>
       </c>
       <c r="G475" t="n">
-        <v>0.8163841807909604</v>
+        <v>0.8165137614678899</v>
       </c>
       <c r="H475" t="n">
-        <v>8.19460451977401</v>
+        <v>8.1948623853211</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -35759,16 +35759,16 @@
         <v>1</v>
       </c>
       <c r="M475" t="n">
-        <v>-0.1253954802259898</v>
+        <v>-0.1251376146789003</v>
       </c>
       <c r="N475" t="n">
-        <v>0.1253954802259898</v>
+        <v>0.1251376146789003</v>
       </c>
       <c r="O475" t="n">
         <v>-0.129999999999999</v>
       </c>
       <c r="P475" t="n">
-        <v>0.2652966101694911</v>
+        <v>0.2652787579393081</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
@@ -35808,10 +35808,10 @@
         <v>8</v>
       </c>
       <c r="G476" t="n">
-        <v>0.8283898305084746</v>
+        <v>0.8285109386026818</v>
       </c>
       <c r="H476" t="n">
-        <v>8.310974576271187</v>
+        <v>8.312420606916021</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -35830,16 +35830,16 @@
         <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>0.05097457627118729</v>
+        <v>0.05242060691602113</v>
       </c>
       <c r="N476" t="n">
-        <v>0.05097457627118729</v>
+        <v>0.05242060691602113</v>
       </c>
       <c r="O476" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P476" t="n">
-        <v>0.1163700564971766</v>
+        <v>0.1175582215949209</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
@@ -35879,10 +35879,10 @@
         <v>8</v>
       </c>
       <c r="G477" t="n">
-        <v>0.836864406779661</v>
+        <v>0.8369795342272407</v>
       </c>
       <c r="H477" t="n">
-        <v>8.460720338983052</v>
+        <v>8.461178546224419</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -35901,16 +35901,16 @@
         <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2607203389830524</v>
+        <v>0.2611785462244196</v>
       </c>
       <c r="N477" t="n">
-        <v>0.2607203389830524</v>
+        <v>0.2611785462244196</v>
       </c>
       <c r="O477" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P477" t="n">
-        <v>0.1497457627118646</v>
+        <v>0.148757939308398</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -35950,10 +35950,10 @@
         <v>8</v>
       </c>
       <c r="G478" t="n">
-        <v>0.8375706214689266</v>
+        <v>0.8376852505292872</v>
       </c>
       <c r="H478" t="n">
-        <v>8.463531073446328</v>
+        <v>8.463987297106563</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -35972,16 +35972,16 @@
         <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>0.4135310734463271</v>
+        <v>0.4139872971065621</v>
       </c>
       <c r="N478" t="n">
-        <v>0.4135310734463271</v>
+        <v>0.4139872971065621</v>
       </c>
       <c r="O478" t="n">
         <v>-0.1499999999999986</v>
       </c>
       <c r="P478" t="n">
-        <v>0.002810734463276177</v>
+        <v>0.00280875088214394</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -36021,10 +36021,10 @@
         <v>8</v>
       </c>
       <c r="G479" t="n">
-        <v>0.8326271186440678</v>
+        <v>0.8327452364149612</v>
       </c>
       <c r="H479" t="n">
-        <v>8.410063559322035</v>
+        <v>8.413119266055046</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -36043,16 +36043,16 @@
         <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>0.490063559322035</v>
+        <v>0.4931192660550465</v>
       </c>
       <c r="N479" t="n">
-        <v>0.490063559322035</v>
+        <v>0.4931192660550465</v>
       </c>
       <c r="O479" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P479" t="n">
-        <v>-0.05346751412429285</v>
+        <v>-0.05086803105151638</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -36092,10 +36092,10 @@
         <v>8</v>
       </c>
       <c r="G480" t="n">
-        <v>0.8199152542372882</v>
+        <v>0.8200423429781228</v>
       </c>
       <c r="H480" t="n">
-        <v>8.20978813559322</v>
+        <v>8.211305575158786</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -36114,16 +36114,16 @@
         <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0.4697881355932196</v>
+        <v>0.4713055751587856</v>
       </c>
       <c r="N480" t="n">
-        <v>0.4697881355932196</v>
+        <v>0.4713055751587856</v>
       </c>
       <c r="O480" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P480" t="n">
-        <v>-0.2002754237288151</v>
+        <v>-0.2018136908962607</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -36266,34 +36266,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.689</v>
+        <v>7.66</v>
       </c>
       <c r="G2" t="n">
-        <v>7.814</v>
+        <v>7.798</v>
       </c>
       <c r="H2" t="n">
-        <v>7.912</v>
+        <v>7.896</v>
       </c>
       <c r="I2" t="n">
-        <v>7.912</v>
+        <v>7.896</v>
       </c>
       <c r="J2" t="n">
-        <v>7.714</v>
+        <v>7.682</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.198</v>
+        <v>-0.214</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -36312,10 +36312,10 @@
         <v>5.831</v>
       </c>
       <c r="P2" t="n">
-        <v>5.811</v>
+        <v>5.812</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.811</v>
+        <v>5.812</v>
       </c>
       <c r="R2" t="n">
         <v>-1.024</v>
@@ -36342,34 +36342,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.574</v>
+        <v>5.583</v>
       </c>
       <c r="G3" t="n">
-        <v>5.617</v>
+        <v>5.608</v>
       </c>
       <c r="H3" t="n">
-        <v>5.668</v>
+        <v>5.641</v>
       </c>
       <c r="I3" t="n">
-        <v>5.668</v>
+        <v>5.641</v>
       </c>
       <c r="J3" t="n">
-        <v>5.586</v>
+        <v>5.591</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.082</v>
+        <v>-0.05</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -36394,7 +36394,7 @@
         <v>0.318</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -36418,34 +36418,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.154</v>
+        <v>4.122</v>
       </c>
       <c r="G4" t="n">
-        <v>4.428</v>
+        <v>4.365</v>
       </c>
       <c r="H4" t="n">
-        <v>4.797</v>
+        <v>4.496</v>
       </c>
       <c r="I4" t="n">
-        <v>4.523</v>
+        <v>4.495</v>
       </c>
       <c r="J4" t="n">
-        <v>4.435</v>
+        <v>4.237</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.258</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -36461,13 +36461,13 @@
         <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>0.949</v>
+        <v>0.95</v>
       </c>
       <c r="P4" t="n">
         <v>0.8179999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.29</v>
+        <v>0.291</v>
       </c>
       <c r="R4" t="n">
         <v>-0.042</v>
@@ -36494,34 +36494,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.522</v>
+        <v>11.728</v>
       </c>
       <c r="G5" t="n">
-        <v>11.924</v>
+        <v>11.989</v>
       </c>
       <c r="H5" t="n">
-        <v>12.289</v>
+        <v>12.233</v>
       </c>
       <c r="I5" t="n">
-        <v>11.522</v>
+        <v>11.728</v>
       </c>
       <c r="J5" t="n">
-        <v>12.248</v>
+        <v>12.226</v>
       </c>
       <c r="K5" t="n">
-        <v>0.726</v>
+        <v>0.499</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -36570,34 +36570,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>59.16</v>
+        <v>54.763</v>
       </c>
       <c r="G6" t="n">
-        <v>95.617</v>
+        <v>96.43300000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>113.303</v>
+        <v>111.045</v>
       </c>
       <c r="I6" t="n">
-        <v>59.422</v>
+        <v>65.869</v>
       </c>
       <c r="J6" t="n">
-        <v>109.444</v>
+        <v>82.024</v>
       </c>
       <c r="K6" t="n">
-        <v>50.022</v>
+        <v>16.155</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -36613,13 +36613,13 @@
         <v>13</v>
       </c>
       <c r="O6" t="n">
-        <v>92.018</v>
+        <v>92.02</v>
       </c>
       <c r="P6" t="n">
-        <v>88.69</v>
+        <v>88.691</v>
       </c>
       <c r="Q6" t="n">
-        <v>88.69</v>
+        <v>88.691</v>
       </c>
       <c r="R6" t="n">
         <v>-3.322</v>
@@ -36646,34 +36646,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.72</v>
+        <v>7.719</v>
       </c>
       <c r="G7" t="n">
-        <v>7.902</v>
+        <v>7.912</v>
       </c>
       <c r="H7" t="n">
-        <v>8.140000000000001</v>
+        <v>8.176</v>
       </c>
       <c r="I7" t="n">
-        <v>8.048</v>
+        <v>8.018000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>8.138999999999999</v>
+        <v>8.175000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.091</v>
+        <v>0.157</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -36722,34 +36722,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.126</v>
+        <v>6.125</v>
       </c>
       <c r="G8" t="n">
-        <v>6.526</v>
+        <v>6.501</v>
       </c>
       <c r="H8" t="n">
-        <v>7.117</v>
+        <v>7.056</v>
       </c>
       <c r="I8" t="n">
-        <v>7.117</v>
+        <v>7.056</v>
       </c>
       <c r="J8" t="n">
-        <v>6.527</v>
+        <v>6.86</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.59</v>
+        <v>-0.196</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -36765,13 +36765,13 @@
         <v>29</v>
       </c>
       <c r="O8" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="P8" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0.397</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.396</v>
       </c>
       <c r="R8" t="n">
         <v>0.829</v>
@@ -36798,34 +36798,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.035</v>
+        <v>5.02</v>
       </c>
       <c r="G9" t="n">
-        <v>5.192</v>
+        <v>5.134</v>
       </c>
       <c r="H9" t="n">
-        <v>5.551</v>
+        <v>5.433</v>
       </c>
       <c r="I9" t="n">
-        <v>5.551</v>
+        <v>5.433</v>
       </c>
       <c r="J9" t="n">
-        <v>5.112</v>
+        <v>5.106</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.439</v>
+        <v>-0.327</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>0.259</v>
       </c>
       <c r="R9" t="n">
-        <v>0.219</v>
+        <v>0.221</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -36874,34 +36874,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.15</v>
+        <v>5.134</v>
       </c>
       <c r="G10" t="n">
-        <v>5.351</v>
+        <v>5.328</v>
       </c>
       <c r="H10" t="n">
         <v>5.438</v>
       </c>
       <c r="I10" t="n">
-        <v>5.37</v>
+        <v>5.386</v>
       </c>
       <c r="J10" t="n">
-        <v>5.152</v>
+        <v>5.135</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.218</v>
+        <v>-0.251</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -36950,34 +36950,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.596</v>
+        <v>3.426</v>
       </c>
       <c r="G11" t="n">
-        <v>5.456</v>
+        <v>5.217</v>
       </c>
       <c r="H11" t="n">
-        <v>6.939</v>
+        <v>6.502</v>
       </c>
       <c r="I11" t="n">
-        <v>5.679</v>
+        <v>5.905</v>
       </c>
       <c r="J11" t="n">
-        <v>4.978</v>
+        <v>4.062</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.701</v>
+        <v>-1.843</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -36993,13 +36993,13 @@
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>2.52</v>
+        <v>2.519</v>
       </c>
       <c r="P11" t="n">
-        <v>2.035</v>
+        <v>2.034</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.035</v>
+        <v>2.034</v>
       </c>
       <c r="R11" t="n">
         <v>-0.554</v>
@@ -37026,34 +37026,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.884</v>
+        <v>5.861</v>
       </c>
       <c r="G12" t="n">
-        <v>5.994</v>
+        <v>5.965</v>
       </c>
       <c r="H12" t="n">
-        <v>6.073</v>
+        <v>6.054</v>
       </c>
       <c r="I12" t="n">
-        <v>6.073</v>
+        <v>6.054</v>
       </c>
       <c r="J12" t="n">
-        <v>5.885</v>
+        <v>5.861</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.188</v>
+        <v>-0.193</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>-0.238</v>
       </c>
       <c r="R12" t="n">
-        <v>0.399</v>
+        <v>0.4</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -37102,34 +37102,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.564</v>
+        <v>9.577999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>9.75</v>
+        <v>9.715999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>9.920999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>9.920999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>9.663</v>
+        <v>9.615</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.258</v>
+        <v>-0.245</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -37178,34 +37178,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.489</v>
+        <v>5.434</v>
       </c>
       <c r="G14" t="n">
-        <v>5.746</v>
+        <v>5.71</v>
       </c>
       <c r="H14" t="n">
-        <v>5.913</v>
+        <v>5.914</v>
       </c>
       <c r="I14" t="n">
-        <v>5.813</v>
+        <v>5.83</v>
       </c>
       <c r="J14" t="n">
-        <v>5.489</v>
+        <v>5.458</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.323</v>
+        <v>-0.371</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -37254,34 +37254,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.561</v>
+        <v>6.56</v>
       </c>
       <c r="G15" t="n">
-        <v>6.577</v>
+        <v>6.574</v>
       </c>
       <c r="H15" t="n">
-        <v>6.586</v>
+        <v>6.584</v>
       </c>
       <c r="I15" t="n">
-        <v>6.586</v>
+        <v>6.584</v>
       </c>
       <c r="J15" t="n">
-        <v>6.578</v>
+        <v>6.564</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.008</v>
+        <v>-0.02</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>-1.504</v>
       </c>
       <c r="R15" t="n">
-        <v>0.282</v>
+        <v>0.281</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -37330,34 +37330,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.386</v>
+        <v>4.435</v>
       </c>
       <c r="G16" t="n">
-        <v>6.08</v>
+        <v>5.919</v>
       </c>
       <c r="H16" t="n">
-        <v>6.887</v>
+        <v>6.963</v>
       </c>
       <c r="I16" t="n">
-        <v>6.487</v>
+        <v>6.375</v>
       </c>
       <c r="J16" t="n">
-        <v>5.374</v>
+        <v>4.803</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.113</v>
+        <v>-1.572</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -37373,13 +37373,13 @@
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>1.726</v>
+        <v>1.725</v>
       </c>
       <c r="P16" t="n">
-        <v>1.538</v>
+        <v>1.537</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.538</v>
+        <v>1.537</v>
       </c>
       <c r="R16" t="n">
         <v>0.229</v>
@@ -37406,34 +37406,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.788</v>
+        <v>3.696</v>
       </c>
       <c r="G17" t="n">
-        <v>4.185</v>
+        <v>4.103</v>
       </c>
       <c r="H17" t="n">
-        <v>4.548</v>
+        <v>4.478</v>
       </c>
       <c r="I17" t="n">
-        <v>4.548</v>
+        <v>4.478</v>
       </c>
       <c r="J17" t="n">
-        <v>3.865</v>
+        <v>3.807</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.671</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -37482,34 +37482,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.405</v>
+        <v>2.383</v>
       </c>
       <c r="G18" t="n">
-        <v>2.542</v>
+        <v>2.514</v>
       </c>
       <c r="H18" t="n">
-        <v>2.638</v>
+        <v>2.592</v>
       </c>
       <c r="I18" t="n">
-        <v>2.638</v>
+        <v>2.592</v>
       </c>
       <c r="J18" t="n">
-        <v>2.406</v>
+        <v>2.385</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.232</v>
+        <v>-0.207</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -37525,16 +37525,16 @@
         <v>14</v>
       </c>
       <c r="O18" t="n">
-        <v>0.485</v>
+        <v>0.484</v>
       </c>
       <c r="P18" t="n">
         <v>0.371</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.154</v>
+        <v>-0.153</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.107</v>
+        <v>-0.106</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -37558,34 +37558,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.614</v>
+        <v>5.58</v>
       </c>
       <c r="G19" t="n">
-        <v>5.848</v>
+        <v>5.813</v>
       </c>
       <c r="H19" t="n">
-        <v>5.93</v>
+        <v>5.899</v>
       </c>
       <c r="I19" t="n">
-        <v>5.93</v>
+        <v>5.899</v>
       </c>
       <c r="J19" t="n">
-        <v>5.753</v>
+        <v>5.635</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.177</v>
+        <v>-0.265</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -486,7 +486,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>300042</v>
+        <v>300060</v>
       </c>
       <c r="E2" t="n">
         <v>151106</v>
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -683,13 +683,13 @@
         <v>9.765000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>7.759</v>
+        <v>7.76</v>
       </c>
       <c r="J2" t="n">
         <v>-1.52</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.006</v>
+        <v>-2.005</v>
       </c>
       <c r="L2" t="n">
         <v>0.397</v>
@@ -704,7 +704,7 @@
         <v>0.865</v>
       </c>
       <c r="P2" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="Q2" t="n">
         <v>0.829</v>
@@ -765,19 +765,19 @@
         <v>7.883</v>
       </c>
       <c r="I3" t="n">
-        <v>5.834</v>
+        <v>5.835</v>
       </c>
       <c r="J3" t="n">
         <v>-2.472</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.049</v>
+        <v>-2.048</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.787</v>
+        <v>-1.786</v>
       </c>
       <c r="M3" t="n">
-        <v>1.787</v>
+        <v>1.786</v>
       </c>
       <c r="N3" t="n">
         <v>1.821</v>
@@ -786,7 +786,7 @@
         <v>0.89</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.597</v>
+        <v>-4.595</v>
       </c>
       <c r="Q3" t="n">
         <v>0.758</v>
@@ -847,19 +847,19 @@
         <v>7.691</v>
       </c>
       <c r="I4" t="n">
-        <v>4.846</v>
+        <v>4.847</v>
       </c>
       <c r="J4" t="n">
         <v>-3.405</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.845</v>
+        <v>-2.844</v>
       </c>
       <c r="L4" t="n">
         <v>-0.074</v>
       </c>
       <c r="M4" t="n">
-        <v>0.338</v>
+        <v>0.337</v>
       </c>
       <c r="N4" t="n">
         <v>0.404</v>
@@ -868,7 +868,7 @@
         <v>0.9409999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.834</v>
+        <v>0.835</v>
       </c>
       <c r="Q4" t="n">
         <v>0.835</v>
@@ -929,31 +929,31 @@
         <v>7.178</v>
       </c>
       <c r="I5" t="n">
-        <v>5.975</v>
+        <v>5.978</v>
       </c>
       <c r="J5" t="n">
         <v>-2.275</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.202</v>
+        <v>-1.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="M5" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
       <c r="N5" t="n">
-        <v>0.492</v>
+        <v>0.493</v>
       </c>
       <c r="O5" t="n">
         <v>0.931</v>
       </c>
       <c r="P5" t="n">
-        <v>0.554</v>
+        <v>0.553</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="R5" t="n">
         <v>55.172</v>
@@ -1011,16 +1011,16 @@
         <v>8.468</v>
       </c>
       <c r="I6" t="n">
-        <v>6.234</v>
+        <v>6.236</v>
       </c>
       <c r="J6" t="n">
         <v>-2.07</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.234</v>
+        <v>-2.232</v>
       </c>
       <c r="L6" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="M6" t="n">
         <v>0.35</v>
@@ -1032,10 +1032,10 @@
         <v>0.872</v>
       </c>
       <c r="P6" t="n">
-        <v>0.731</v>
+        <v>0.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.737</v>
+        <v>0.736</v>
       </c>
       <c r="R6" t="n">
         <v>31.034</v>
@@ -1093,16 +1093,16 @@
         <v>9.374000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.211</v>
+        <v>8.212999999999999</v>
       </c>
       <c r="J7" t="n">
         <v>-2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.163</v>
+        <v>-1.161</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.665</v>
+        <v>-0.664</v>
       </c>
       <c r="M7" t="n">
         <v>0.777</v>
@@ -1111,16 +1111,16 @@
         <v>0.841</v>
       </c>
       <c r="O7" t="n">
-        <v>0.709</v>
+        <v>0.708</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.353</v>
+        <v>-0.352</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.504</v>
+        <v>0.503</v>
       </c>
       <c r="R7" t="n">
-        <v>20.69</v>
+        <v>17.241</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1175,13 +1175,13 @@
         <v>9.863</v>
       </c>
       <c r="I8" t="n">
-        <v>7.94</v>
+        <v>7.941</v>
       </c>
       <c r="J8" t="n">
         <v>-2.008</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.923</v>
+        <v>-1.922</v>
       </c>
       <c r="L8" t="n">
         <v>5.812</v>
@@ -1190,13 +1190,13 @@
         <v>5.812</v>
       </c>
       <c r="N8" t="n">
-        <v>5.831</v>
+        <v>5.832</v>
       </c>
       <c r="O8" t="n">
         <v>0.831</v>
       </c>
       <c r="P8" t="n">
-        <v>-45.945</v>
+        <v>-45.951</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.024</v>
@@ -1281,7 +1281,7 @@
         <v>-0.669</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.042</v>
+        <v>-0.043</v>
       </c>
       <c r="R9" t="n">
         <v>44.828</v>
@@ -1339,31 +1339,31 @@
         <v>11.017</v>
       </c>
       <c r="I10" t="n">
-        <v>11.489</v>
+        <v>11.472</v>
       </c>
       <c r="J10" t="n">
         <v>-1.39</v>
       </c>
       <c r="K10" t="n">
-        <v>0.472</v>
+        <v>0.455</v>
       </c>
       <c r="L10" t="n">
-        <v>3.917</v>
+        <v>3.916</v>
       </c>
       <c r="M10" t="n">
-        <v>3.917</v>
+        <v>3.916</v>
       </c>
       <c r="N10" t="n">
         <v>4.213</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.491</v>
+        <v>-0.49</v>
       </c>
       <c r="P10" t="n">
-        <v>-105.534</v>
+        <v>-105.501</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.728</v>
+        <v>-1.727</v>
       </c>
       <c r="R10" t="n">
         <v>44.828</v>
@@ -1418,25 +1418,25 @@
         <v>5.32</v>
       </c>
       <c r="H11" t="n">
-        <v>112.894</v>
+        <v>112.895</v>
       </c>
       <c r="I11" t="n">
-        <v>108.414</v>
+        <v>108.419</v>
       </c>
       <c r="J11" t="n">
         <v>-1.68</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.48</v>
+        <v>-4.477</v>
       </c>
       <c r="L11" t="n">
-        <v>88.691</v>
+        <v>88.69199999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>88.691</v>
+        <v>88.69199999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>92.02</v>
+        <v>92.021</v>
       </c>
       <c r="O11" t="n">
         <v>-0.358</v>
@@ -1468,7 +1468,7 @@
         <v>0.128</v>
       </c>
       <c r="X11" t="n">
-        <v>36.187</v>
+        <v>36.188</v>
       </c>
     </row>
     <row r="12">
@@ -1585,31 +1585,31 @@
         <v>5.956</v>
       </c>
       <c r="I13" t="n">
-        <v>5.116</v>
+        <v>5.112</v>
       </c>
       <c r="J13" t="n">
         <v>-0.6919999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.84</v>
+        <v>-0.844</v>
       </c>
       <c r="L13" t="n">
-        <v>0.259</v>
+        <v>0.258</v>
       </c>
       <c r="M13" t="n">
-        <v>0.423</v>
+        <v>0.422</v>
       </c>
       <c r="N13" t="n">
         <v>0.512</v>
       </c>
       <c r="O13" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.082</v>
+        <v>-0.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.221</v>
+        <v>0.222</v>
       </c>
       <c r="R13" t="n">
         <v>17.241</v>
@@ -1667,31 +1667,31 @@
         <v>7.097</v>
       </c>
       <c r="I14" t="n">
-        <v>5.203</v>
+        <v>5.198</v>
       </c>
       <c r="J14" t="n">
         <v>-2.422</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.893</v>
+        <v>-1.899</v>
       </c>
       <c r="L14" t="n">
-        <v>2.034</v>
+        <v>2.033</v>
       </c>
       <c r="M14" t="n">
-        <v>2.034</v>
+        <v>2.033</v>
       </c>
       <c r="N14" t="n">
         <v>2.519</v>
       </c>
       <c r="O14" t="n">
-        <v>0.615</v>
+        <v>0.616</v>
       </c>
       <c r="P14" t="n">
-        <v>-10.085</v>
+        <v>-10.081</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.554</v>
+        <v>-0.555</v>
       </c>
       <c r="R14" t="n">
         <v>55.172</v>
@@ -1749,34 +1749,34 @@
         <v>8.144</v>
       </c>
       <c r="I15" t="n">
-        <v>6.36</v>
+        <v>6.361</v>
       </c>
       <c r="J15" t="n">
         <v>-1.525</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.784</v>
+        <v>-1.782</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.238</v>
+        <v>-0.237</v>
       </c>
       <c r="M15" t="n">
         <v>0.37</v>
       </c>
       <c r="N15" t="n">
-        <v>0.482</v>
+        <v>0.481</v>
       </c>
       <c r="O15" t="n">
         <v>0.8159999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.193</v>
+        <v>-0.191</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="R15" t="n">
-        <v>41.379</v>
+        <v>44.828</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1913,31 +1913,31 @@
         <v>8.029999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>6.685</v>
+        <v>6.687</v>
       </c>
       <c r="J17" t="n">
         <v>-2.425</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.345</v>
+        <v>-1.343</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.504</v>
+        <v>-1.503</v>
       </c>
       <c r="M17" t="n">
-        <v>1.504</v>
+        <v>1.503</v>
       </c>
       <c r="N17" t="n">
-        <v>1.625</v>
+        <v>1.624</v>
       </c>
       <c r="O17" t="n">
-        <v>0.599</v>
+        <v>0.598</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.676</v>
+        <v>-3.674</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.281</v>
+        <v>0.28</v>
       </c>
       <c r="R17" t="n">
         <v>31.034</v>
@@ -1995,19 +1995,19 @@
         <v>7.154</v>
       </c>
       <c r="I18" t="n">
-        <v>6.287</v>
+        <v>6.283</v>
       </c>
       <c r="J18" t="n">
         <v>-1.55</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.867</v>
+        <v>-0.871</v>
       </c>
       <c r="L18" t="n">
-        <v>1.537</v>
+        <v>1.536</v>
       </c>
       <c r="M18" t="n">
-        <v>1.537</v>
+        <v>1.536</v>
       </c>
       <c r="N18" t="n">
         <v>1.725</v>
@@ -2016,7 +2016,7 @@
         <v>0.611</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.618</v>
+        <v>-6.614</v>
       </c>
       <c r="Q18" t="n">
         <v>0.229</v>
@@ -2074,7 +2074,7 @@
         <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.501</v>
+        <v>3.502</v>
       </c>
       <c r="I19" t="n">
         <v>3.112</v>
@@ -2083,10 +2083,10 @@
         <v>-1.34</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.389</v>
+        <v>-0.39</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.153</v>
+        <v>-0.152</v>
       </c>
       <c r="M19" t="n">
         <v>0.371</v>
@@ -2095,10 +2095,10 @@
         <v>0.484</v>
       </c>
       <c r="O19" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.406</v>
+        <v>-0.403</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.106</v>
@@ -3392,10 +3392,10 @@
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8539167254763586</v>
+        <v>0.8540197461212976</v>
       </c>
       <c r="H18" t="n">
-        <v>8.171916019760056</v>
+        <v>8.172242595204514</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>5.716916019760056</v>
+        <v>5.717242595204514</v>
       </c>
       <c r="N18" t="n">
-        <v>5.716916019760056</v>
+        <v>5.717242595204514</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1374999999999997</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7281120110738613</v>
+        <v>-0.7277854356294036</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8510938602681722</v>
+        <v>0.8511988716502116</v>
       </c>
       <c r="H19" t="n">
-        <v>8.15847565278758</v>
+        <v>8.158725317348377</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3485,16 +3485,16 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.74597565278758</v>
+        <v>5.746225317348378</v>
       </c>
       <c r="N19" t="n">
-        <v>5.74597565278758</v>
+        <v>5.746225317348378</v>
       </c>
       <c r="O19" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.01344036697247653</v>
+        <v>-0.01351727785613654</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8468595624558928</v>
+        <v>0.8469675599435825</v>
       </c>
       <c r="H20" t="n">
-        <v>8.136362032462952</v>
+        <v>8.137217912552893</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3556,16 +3556,16 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>5.736362032462951</v>
+        <v>5.737217912552893</v>
       </c>
       <c r="N20" t="n">
-        <v>5.736362032462951</v>
+        <v>5.737217912552893</v>
       </c>
       <c r="O20" t="n">
         <v>-0.01250000000000018</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.02211362032462816</v>
+        <v>-0.02150740479548396</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8440366972477065</v>
+        <v>0.8441466854724965</v>
       </c>
       <c r="H21" t="n">
-        <v>8.120596330275228</v>
+        <v>8.120944992947813</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>5.950596330275228</v>
+        <v>5.950944992947813</v>
       </c>
       <c r="N21" t="n">
-        <v>5.950596330275228</v>
+        <v>5.950944992947813</v>
       </c>
       <c r="O21" t="n">
         <v>-0.23</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.01576570218772311</v>
+        <v>-0.01627291960508082</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8390966831333804</v>
+        <v>0.8392101551480959</v>
       </c>
       <c r="H22" t="n">
-        <v>8.099872971065631</v>
+        <v>8.100592383638928</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3698,16 +3698,16 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>6.119872971065631</v>
+        <v>6.120592383638927</v>
       </c>
       <c r="N22" t="n">
-        <v>6.119872971065631</v>
+        <v>6.120592383638927</v>
       </c>
       <c r="O22" t="n">
         <v>-0.1899999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.02072335920959745</v>
+        <v>-0.02035260930888505</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8341566690190544</v>
+        <v>0.8342736248236954</v>
       </c>
       <c r="H23" t="n">
-        <v>8.067106563161609</v>
+        <v>8.068589562764457</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3769,16 +3769,16 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>6.017106563161609</v>
+        <v>6.018589562764457</v>
       </c>
       <c r="N23" t="n">
-        <v>6.017106563161609</v>
+        <v>6.018589562764457</v>
       </c>
       <c r="O23" t="n">
         <v>0.06999999999999984</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.03276640790402219</v>
+        <v>-0.03200282087447093</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8278052223006351</v>
+        <v>0.8279266572637518</v>
       </c>
       <c r="H24" t="n">
         <v>8.030000000000001</v>
@@ -3849,7 +3849,7 @@
         <v>0.1700000000000004</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.03710656316160765</v>
+        <v>-0.03858956276445547</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8228652081863091</v>
+        <v>0.8229901269393513</v>
       </c>
       <c r="H25" t="n">
-        <v>8.014241354975301</v>
+        <v>8.014439351198872</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3911,16 +3911,16 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>5.664241354975301</v>
+        <v>5.664439351198872</v>
       </c>
       <c r="N25" t="n">
-        <v>5.664241354975301</v>
+        <v>5.664439351198872</v>
       </c>
       <c r="O25" t="n">
         <v>0.1299999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01575864502470026</v>
+        <v>-0.01556064880112906</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3960,10 +3960,10 @@
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8200423429781228</v>
+        <v>0.8201692524682651</v>
       </c>
       <c r="H26" t="n">
-        <v>8.004301340860973</v>
+        <v>8.004904795486601</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3982,16 +3982,16 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>5.704301340860973</v>
+        <v>5.704904795486601</v>
       </c>
       <c r="N26" t="n">
-        <v>5.704301340860973</v>
+        <v>5.704904795486601</v>
       </c>
       <c r="O26" t="n">
         <v>-0.05000000000000027</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.009940014114327766</v>
+        <v>-0.009534555712271242</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8165137614678899</v>
+        <v>0.8166431593794076</v>
       </c>
       <c r="H27" t="n">
-        <v>7.981720183486239</v>
+        <v>7.983155853314527</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4053,16 +4053,16 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>5.751720183486238</v>
+        <v>5.753155853314528</v>
       </c>
       <c r="N27" t="n">
-        <v>5.751720183486238</v>
+        <v>5.753155853314528</v>
       </c>
       <c r="O27" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.02258115737473432</v>
+        <v>-0.02174894217207335</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8122794636556104</v>
+        <v>0.8124118476727785</v>
       </c>
       <c r="H28" t="n">
-        <v>7.949925899788285</v>
+        <v>7.95086389280677</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>5.889925899788285</v>
+        <v>5.89086389280677</v>
       </c>
       <c r="N28" t="n">
-        <v>5.889925899788285</v>
+        <v>5.89086389280677</v>
       </c>
       <c r="O28" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.03179428369795367</v>
+        <v>-0.03229196050775762</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8129851799576571</v>
+        <v>0.81311706629055</v>
       </c>
       <c r="H29" t="n">
-        <v>7.955407551164432</v>
+        <v>7.956452750352608</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4195,16 +4195,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>6.005407551164431</v>
+        <v>6.006452750352608</v>
       </c>
       <c r="N29" t="n">
-        <v>6.005407551164431</v>
+        <v>6.006452750352608</v>
       </c>
       <c r="O29" t="n">
         <v>-0.1100000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>0.005481651376146424</v>
+        <v>0.005588857545838266</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8136908962597036</v>
+        <v>0.8138222849083215</v>
       </c>
       <c r="H30" t="n">
-        <v>7.961000352858149</v>
+        <v>7.962041607898446</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4266,16 +4266,16 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.261000352858149</v>
+        <v>5.262041607898446</v>
       </c>
       <c r="N30" t="n">
-        <v>5.261000352858149</v>
+        <v>5.262041607898446</v>
       </c>
       <c r="O30" t="n">
         <v>0.7500000000000002</v>
       </c>
       <c r="P30" t="n">
-        <v>0.005592801693717675</v>
+        <v>0.005588857545838266</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8101623147494708</v>
+        <v>0.810296191819464</v>
       </c>
       <c r="H31" t="n">
-        <v>7.939643613267467</v>
+        <v>7.940916784203103</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4337,16 +4337,16 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.139643613267467</v>
+        <v>5.140916784203103</v>
       </c>
       <c r="N31" t="n">
-        <v>5.139643613267467</v>
+        <v>5.140916784203103</v>
       </c>
       <c r="O31" t="n">
         <v>0.09999999999999964</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.02135673959068196</v>
+        <v>-0.02112482369534341</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6499647141848977</v>
+        <v>0.6502115655853314</v>
       </c>
       <c r="H48" t="n">
-        <v>6.159549003175724</v>
+        <v>6.159643423836389</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5538,16 +5538,16 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1279509968242758</v>
+        <v>-0.1278565761636106</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1279509968242758</v>
+        <v>0.1278565761636106</v>
       </c>
       <c r="O48" t="n">
         <v>-0.09250000000000114</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.6243402750303026</v>
+        <v>-0.6242458543696374</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6436132674664785</v>
+        <v>0.6438645980253879</v>
       </c>
       <c r="H49" t="n">
-        <v>6.149456598447425</v>
+        <v>6.150677009873061</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5609,16 +5609,16 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.02054340155257517</v>
+        <v>-0.01932299012693939</v>
       </c>
       <c r="N49" t="n">
-        <v>0.02054340155257517</v>
+        <v>0.01932299012693939</v>
       </c>
       <c r="O49" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.01009240472829909</v>
+        <v>-0.008966413963328534</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5658,10 +5658,10 @@
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>0.6358503881439661</v>
+        <v>0.6361071932299013</v>
       </c>
       <c r="H50" t="n">
-        <v>6.126561750176429</v>
+        <v>6.127190409026799</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5680,16 +5680,16 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.03656175017642926</v>
+        <v>0.03719040902679893</v>
       </c>
       <c r="N50" t="n">
-        <v>0.03656175017642926</v>
+        <v>0.03719040902679893</v>
       </c>
       <c r="O50" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.02289484827099564</v>
+        <v>-0.02348660084626175</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5729,10 +5729,10 @@
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>0.634438955539873</v>
+        <v>0.6346967559943583</v>
       </c>
       <c r="H51" t="n">
-        <v>6.123106563161609</v>
+        <v>6.123737658674189</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5751,16 +5751,16 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2631065631616085</v>
+        <v>0.2637376586741889</v>
       </c>
       <c r="N51" t="n">
-        <v>0.2631065631616085</v>
+        <v>0.2637376586741889</v>
       </c>
       <c r="O51" t="n">
         <v>-0.2299999999999995</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.003455187014820282</v>
+        <v>-0.003452750352609613</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>0.6457304163726182</v>
+        <v>0.6459802538787024</v>
       </c>
       <c r="H52" t="n">
-        <v>6.157929384262527</v>
+        <v>6.158024947108604</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5822,16 +5822,16 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4979293842625268</v>
+        <v>0.498024947108604</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4979293842625268</v>
+        <v>0.498024947108604</v>
       </c>
       <c r="O52" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P52" t="n">
-        <v>0.03482282110091806</v>
+        <v>0.03428728843441498</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6534932956951306</v>
+        <v>0.653737658674189</v>
       </c>
       <c r="H53" t="n">
-        <v>6.169689484827099</v>
+        <v>6.170874471086036</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5893,16 +5893,16 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5396894848270994</v>
+        <v>0.5408744710860365</v>
       </c>
       <c r="N53" t="n">
-        <v>0.5396894848270994</v>
+        <v>0.5408744710860365</v>
       </c>
       <c r="O53" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P53" t="n">
-        <v>0.01176010056457244</v>
+        <v>0.01284952397743222</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6633733239237827</v>
+        <v>0.6636107193229901</v>
       </c>
       <c r="H54" t="n">
-        <v>6.209896494942367</v>
+        <v>6.210324400564175</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5964,16 +5964,16 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6198964949423669</v>
+        <v>0.6203244005641748</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6198964949423669</v>
+        <v>0.6203244005641748</v>
       </c>
       <c r="O54" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P54" t="n">
-        <v>0.04020701011526739</v>
+        <v>0.0394499294781383</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6697247706422018</v>
+        <v>0.6699576868829337</v>
       </c>
       <c r="H55" t="n">
-        <v>6.219678899082568</v>
+        <v>6.220070521861777</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6035,16 +6035,16 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7696788990825683</v>
+        <v>0.7700705218617765</v>
       </c>
       <c r="N55" t="n">
-        <v>0.7696788990825683</v>
+        <v>0.7700705218617765</v>
       </c>
       <c r="O55" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P55" t="n">
-        <v>0.009782404140201706</v>
+        <v>0.009746121297601995</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>0.666196189131969</v>
+        <v>0.6664315937940761</v>
       </c>
       <c r="H56" t="n">
-        <v>6.214280169371913</v>
+        <v>6.214640338504936</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6106,16 +6106,16 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8142801693719122</v>
+        <v>0.8146403385049359</v>
       </c>
       <c r="N56" t="n">
-        <v>0.8142801693719122</v>
+        <v>0.8146403385049359</v>
       </c>
       <c r="O56" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.005398729710655914</v>
+        <v>-0.005430183356840423</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
         <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>0.6549047282992237</v>
+        <v>0.655148095909732</v>
       </c>
       <c r="H57" t="n">
-        <v>6.178016937191249</v>
+        <v>6.17950634696756</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8080169371912493</v>
+        <v>0.8095063469675594</v>
       </c>
       <c r="N57" t="n">
-        <v>0.8080169371912493</v>
+        <v>0.8095063469675594</v>
       </c>
       <c r="O57" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.03626323218066307</v>
+        <v>-0.03513399153737673</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6226,10 +6226,10 @@
         <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>0.639378969654199</v>
+        <v>0.6396332863187588</v>
       </c>
       <c r="H58" t="n">
-        <v>6.137666431427899</v>
+        <v>6.138185237423601</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6248,16 +6248,16 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.807666431427899</v>
+        <v>0.8081852374236007</v>
       </c>
       <c r="N58" t="n">
-        <v>0.807666431427899</v>
+        <v>0.8081852374236007</v>
       </c>
       <c r="O58" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.04035050576335042</v>
+        <v>-0.04132110954395873</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6297,10 +6297,10 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.621030345800988</v>
+        <v>0.6212976022566996</v>
       </c>
       <c r="H59" t="n">
-        <v>6.080705716302047</v>
+        <v>6.082341325811002</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6319,16 +6319,16 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9307057163020467</v>
+        <v>0.9323413258110014</v>
       </c>
       <c r="N59" t="n">
-        <v>0.9307057163020467</v>
+        <v>0.9323413258110014</v>
       </c>
       <c r="O59" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.05696071512585199</v>
+        <v>-0.05584391161259905</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6069160197600565</v>
+        <v>0.6071932299012694</v>
       </c>
       <c r="H60" t="n">
-        <v>6.034326040931546</v>
+        <v>6.036022566995769</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6390,16 +6390,16 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1.064326040931546</v>
+        <v>1.06602256699577</v>
       </c>
       <c r="N60" t="n">
-        <v>1.064326040931546</v>
+        <v>1.06602256699577</v>
       </c>
       <c r="O60" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.04637967537050081</v>
+        <v>-0.04631875881523229</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6439,10 +6439,10 @@
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5920959774170783</v>
+        <v>0.5923836389280677</v>
       </c>
       <c r="H61" t="n">
-        <v>5.975441072688779</v>
+        <v>5.977596967559943</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6461,16 +6461,16 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1.145441072688778</v>
+        <v>1.147596967559943</v>
       </c>
       <c r="N61" t="n">
-        <v>1.145441072688778</v>
+        <v>1.147596967559943</v>
       </c>
       <c r="O61" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.05888496824276768</v>
+        <v>-0.05842559943582604</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -7640,10 +7640,10 @@
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8976711362032463</v>
+        <v>0.8977433004231312</v>
       </c>
       <c r="H78" t="n">
-        <v>5.881173253352154</v>
+        <v>5.882221438645981</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7662,16 +7662,16 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1.193673253352154</v>
+        <v>1.194721438645981</v>
       </c>
       <c r="N78" t="n">
-        <v>1.193673253352154</v>
+        <v>1.194721438645981</v>
       </c>
       <c r="O78" t="n">
         <v>0.2725</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.06065225470671098</v>
+        <v>-0.05960406941288365</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8687367678193366</v>
+        <v>0.8688293370944993</v>
       </c>
       <c r="H79" t="n">
-        <v>5.694721242060692</v>
+        <v>5.695796897038083</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7733,16 +7733,16 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>1.282221242060692</v>
+        <v>1.283296897038083</v>
       </c>
       <c r="N79" t="n">
-        <v>1.282221242060692</v>
+        <v>1.283296897038083</v>
       </c>
       <c r="O79" t="n">
         <v>-0.2750000000000004</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.186452011291462</v>
+        <v>-0.1864245416078987</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>0.826393789696542</v>
+        <v>0.8265162200282088</v>
       </c>
       <c r="H80" t="n">
-        <v>5.416347918136909</v>
+        <v>5.417059238363893</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7804,16 +7804,16 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7663479181369084</v>
+        <v>0.7670592383638928</v>
       </c>
       <c r="N80" t="n">
-        <v>0.7663479181369084</v>
+        <v>0.7670592383638928</v>
       </c>
       <c r="O80" t="n">
         <v>0.2375000000000007</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.2783733239237831</v>
+        <v>-0.2787376586741894</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7798165137614679</v>
+        <v>0.7799717912552891</v>
       </c>
       <c r="H81" t="n">
-        <v>5.155366972477063</v>
+        <v>5.155818053596614</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7875,16 +7875,16 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>0.455366972477063</v>
+        <v>0.4558180535966141</v>
       </c>
       <c r="N81" t="n">
-        <v>0.455366972477063</v>
+        <v>0.4558180535966141</v>
       </c>
       <c r="O81" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.2609809456598455</v>
+        <v>-0.2612411847672789</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7339449541284404</v>
+        <v>0.734132581100141</v>
       </c>
       <c r="H82" t="n">
-        <v>4.999220183486239</v>
+        <v>5.000465444287729</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7946,16 +7946,16 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5942201834862395</v>
+        <v>0.5954654442877292</v>
       </c>
       <c r="N82" t="n">
-        <v>0.5942201834862395</v>
+        <v>0.5954654442877292</v>
       </c>
       <c r="O82" t="n">
         <v>-0.2950000000000008</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.1561467889908243</v>
+        <v>-0.1553526093088857</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -7995,10 +7995,10 @@
         <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.707833450952717</v>
+        <v>0.7080394922425952</v>
       </c>
       <c r="H83" t="n">
-        <v>4.872512350035286</v>
+        <v>4.873709449929478</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8017,16 +8017,16 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>0.7750123500352863</v>
+        <v>0.7762094499294792</v>
       </c>
       <c r="N83" t="n">
-        <v>0.7750123500352863</v>
+        <v>0.7762094499294792</v>
       </c>
       <c r="O83" t="n">
         <v>-0.3075000000000001</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.1267078334509533</v>
+        <v>-0.1267559943582501</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -8066,10 +8066,10 @@
         <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>0.6760762173606211</v>
+        <v>0.6763046544428772</v>
       </c>
       <c r="H84" t="n">
-        <v>4.786572235104345</v>
+        <v>4.78695144066089</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8088,16 +8088,16 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>0.9365722351043453</v>
+        <v>0.9369514406608901</v>
       </c>
       <c r="N84" t="n">
-        <v>0.9365722351043453</v>
+        <v>0.9369514406608901</v>
       </c>
       <c r="O84" t="n">
         <v>-0.2474999999999992</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.08594011493094023</v>
+        <v>-0.08675800926858823</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6414961185603387</v>
+        <v>0.6417489421720733</v>
       </c>
       <c r="H85" t="n">
-        <v>4.688682074805929</v>
+        <v>4.688926892336625</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8159,16 +8159,16 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9086820748059288</v>
+        <v>0.9089268923366247</v>
       </c>
       <c r="N85" t="n">
-        <v>0.9086820748059288</v>
+        <v>0.9089268923366247</v>
       </c>
       <c r="O85" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.0978901602984168</v>
+        <v>-0.09802454832426566</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6033874382498235</v>
+        <v>0.6036671368124118</v>
       </c>
       <c r="H86" t="n">
-        <v>4.545681016231475</v>
+        <v>4.547306064880112</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8230,16 +8230,16 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.2543189837685258</v>
+        <v>-0.2526939351198889</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2543189837685258</v>
+        <v>0.2526939351198889</v>
       </c>
       <c r="O86" t="n">
         <v>1.020000000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.1430010585744537</v>
+        <v>-0.1416208274565127</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -8279,10 +8279,10 @@
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>0.5956245589273113</v>
+        <v>0.5959097320169252</v>
       </c>
       <c r="H87" t="n">
-        <v>4.515289343683839</v>
+        <v>4.516117771509167</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8301,16 +8301,16 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.1847106563161613</v>
+        <v>-0.183882228490833</v>
       </c>
       <c r="N87" t="n">
-        <v>0.1847106563161613</v>
+        <v>0.183882228490833</v>
       </c>
       <c r="O87" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.03039167254763608</v>
+        <v>-0.03118829337094464</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -8350,10 +8350,10 @@
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6146788990825688</v>
+        <v>0.614950634696756</v>
       </c>
       <c r="H88" t="n">
-        <v>4.574189602446483</v>
+        <v>4.575242125058769</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8372,16 +8372,16 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.6258103975535168</v>
+        <v>-0.6247578749412313</v>
       </c>
       <c r="N88" t="n">
-        <v>0.6258103975535168</v>
+        <v>0.6247578749412313</v>
       </c>
       <c r="O88" t="n">
         <v>0.5</v>
       </c>
       <c r="P88" t="n">
-        <v>0.0589002587626446</v>
+        <v>0.05912435354960177</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6591390261115032</v>
+        <v>0.659379407616361</v>
       </c>
       <c r="H89" t="n">
-        <v>4.724798870853917</v>
+        <v>4.725994358251057</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8443,16 +8443,16 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.7752011291460832</v>
+        <v>-0.7740056417489427</v>
       </c>
       <c r="N89" t="n">
-        <v>0.7752011291460832</v>
+        <v>0.7740056417489427</v>
       </c>
       <c r="O89" t="n">
         <v>0.2999999999999998</v>
       </c>
       <c r="P89" t="n">
-        <v>0.1506092684074334</v>
+        <v>0.1507522331922884</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8492,10 +8492,10 @@
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6824276640790402</v>
+        <v>0.6826516220028209</v>
       </c>
       <c r="H90" t="n">
-        <v>4.796226182074806</v>
+        <v>4.796551480959097</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8514,16 +8514,16 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-1.083773817925194</v>
+        <v>-1.083448519040902</v>
       </c>
       <c r="N90" t="n">
-        <v>1.083773817925194</v>
+        <v>1.083448519040902</v>
       </c>
       <c r="O90" t="n">
         <v>0.3799999999999999</v>
       </c>
       <c r="P90" t="n">
-        <v>0.07142731122088897</v>
+        <v>0.07055712270804015</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8563,10 +8563,10 @@
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6852505292872265</v>
+        <v>0.685472496473907</v>
       </c>
       <c r="H91" t="n">
-        <v>4.8</v>
+        <v>4.800000000000001</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -8585,16 +8585,16 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.2199999999999998</v>
+        <v>-0.2199999999999989</v>
       </c>
       <c r="N91" t="n">
-        <v>0.2199999999999998</v>
+        <v>0.2199999999999989</v>
       </c>
       <c r="O91" t="n">
         <v>-0.8600000000000003</v>
       </c>
       <c r="P91" t="n">
-        <v>0.003773817925194045</v>
+        <v>0.003448519040903264</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -9764,10 +9764,10 @@
         <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8913196894848271</v>
+        <v>0.8913963328631875</v>
       </c>
       <c r="H108" t="n">
-        <v>12.38351093860268</v>
+        <v>12.38367418899859</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -9786,16 +9786,16 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>5.313510938602682</v>
+        <v>5.313674188998591</v>
       </c>
       <c r="N108" t="n">
-        <v>5.313510938602682</v>
+        <v>5.313674188998591</v>
       </c>
       <c r="O108" t="n">
         <v>-0.1250000000000009</v>
       </c>
       <c r="P108" t="n">
-        <v>4.413931401111443</v>
+        <v>4.414094651507352</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -9835,10 +9835,10 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>0.8870853916725476</v>
+        <v>0.8871650211565585</v>
       </c>
       <c r="H109" t="n">
-        <v>12.34441072688779</v>
+        <v>12.34627644569816</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -9857,16 +9857,16 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>5.474410726887791</v>
+        <v>5.476276445698164</v>
       </c>
       <c r="N109" t="n">
-        <v>5.474410726887791</v>
+        <v>5.476276445698164</v>
       </c>
       <c r="O109" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.03910021171489042</v>
+        <v>-0.037397743300426</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -9906,10 +9906,10 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>0.884968242766408</v>
+        <v>0.885049365303244</v>
       </c>
       <c r="H110" t="n">
-        <v>12.29244707127735</v>
+        <v>12.29436177715092</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -9928,16 +9928,16 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>5.552447071277347</v>
+        <v>5.554361777150916</v>
       </c>
       <c r="N110" t="n">
-        <v>5.552447071277347</v>
+        <v>5.554361777150916</v>
       </c>
       <c r="O110" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.05196365561044303</v>
+        <v>-0.0519146685472478</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -9977,10 +9977,10 @@
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>0.8828510938602682</v>
+        <v>0.8829337094499294</v>
       </c>
       <c r="H111" t="n">
-        <v>12.27891848976711</v>
+        <v>12.27944640338505</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -9999,16 +9999,16 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>5.678918489767113</v>
+        <v>5.67944640338505</v>
       </c>
       <c r="N111" t="n">
-        <v>5.678918489767113</v>
+        <v>5.67944640338505</v>
       </c>
       <c r="O111" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P111" t="n">
-        <v>-0.01352858151023462</v>
+        <v>-0.01491537376586649</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -10048,10 +10048,10 @@
         <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>0.876499647141849</v>
+        <v>0.8765867418899859</v>
       </c>
       <c r="H112" t="n">
-        <v>12.22388849682428</v>
+        <v>12.22425952045134</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10070,16 +10070,16 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>5.363888496824278</v>
+        <v>5.36425952045134</v>
       </c>
       <c r="N112" t="n">
-        <v>5.363888496824278</v>
+        <v>5.36425952045134</v>
       </c>
       <c r="O112" t="n">
         <v>0.2600000000000007</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.05502999294283484</v>
+        <v>-0.05518688293370921</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>0.8680310515172901</v>
+        <v>0.8681241184767278</v>
       </c>
       <c r="H113" t="n">
-        <v>12.19140613973183</v>
+        <v>12.19160437235543</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -10141,16 +10141,16 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>5.211406139731826</v>
+        <v>5.21160437235543</v>
       </c>
       <c r="N113" t="n">
-        <v>5.211406139731826</v>
+        <v>5.21160437235543</v>
       </c>
       <c r="O113" t="n">
         <v>0.1200000000000001</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.03248235709245151</v>
+        <v>-0.03265514809591075</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -10190,10 +10190,10 @@
         <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8574453069865914</v>
+        <v>0.8575458392101551</v>
       </c>
       <c r="H114" t="n">
-        <v>12.12315102328864</v>
+        <v>12.12443582510578</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -10212,16 +10212,16 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>5.273151023288639</v>
+        <v>5.274435825105783</v>
       </c>
       <c r="N114" t="n">
-        <v>5.273151023288639</v>
+        <v>5.274435825105783</v>
       </c>
       <c r="O114" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P114" t="n">
-        <v>-0.06825511644318816</v>
+        <v>-0.06716854724964705</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
         <v>8</v>
       </c>
       <c r="G115" t="n">
-        <v>0.8468595624558928</v>
+        <v>0.8469675599435825</v>
       </c>
       <c r="H115" t="n">
-        <v>12.0776217360621</v>
+        <v>12.07808180535966</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -10283,16 +10283,16 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>5.337621736062102</v>
+        <v>5.338081805359661</v>
       </c>
       <c r="N115" t="n">
-        <v>5.337621736062102</v>
+        <v>5.338081805359661</v>
       </c>
       <c r="O115" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.04552928722653604</v>
+        <v>-0.04635401974612208</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -10332,10 +10332,10 @@
         <v>8</v>
       </c>
       <c r="G116" t="n">
-        <v>0.8249823570924488</v>
+        <v>0.8251057827926658</v>
       </c>
       <c r="H116" t="n">
-        <v>11.86442484121383</v>
+        <v>11.86495063469676</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -10354,16 +10354,16 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>5.25942484121383</v>
+        <v>5.259950634696756</v>
       </c>
       <c r="N116" t="n">
-        <v>5.25942484121383</v>
+        <v>5.259950634696756</v>
       </c>
       <c r="O116" t="n">
         <v>-0.1349999999999998</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.2131968948482719</v>
+        <v>-0.2131311706629049</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10403,10 +10403,10 @@
         <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>0.8101623147494708</v>
+        <v>0.810296191819464</v>
       </c>
       <c r="H117" t="n">
-        <v>11.81064573041637</v>
+        <v>11.81093088857546</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -10425,16 +10425,16 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>5.430645730416374</v>
+        <v>5.430930888575459</v>
       </c>
       <c r="N117" t="n">
-        <v>5.430645730416374</v>
+        <v>5.430930888575459</v>
       </c>
       <c r="O117" t="n">
         <v>-0.2250000000000005</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.05377911079745701</v>
+        <v>-0.05401974612129656</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10474,10 +10474,10 @@
         <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7960479887085392</v>
+        <v>0.7954866008462623</v>
       </c>
       <c r="H118" t="n">
-        <v>11.72558221594919</v>
+        <v>11.72438645980254</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -10496,16 +10496,16 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>5.485582215949188</v>
+        <v>5.484386459802538</v>
       </c>
       <c r="N118" t="n">
-        <v>5.485582215949188</v>
+        <v>5.484386459802538</v>
       </c>
       <c r="O118" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.08506351446718519</v>
+        <v>-0.08654442877292112</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10545,10 +10545,10 @@
         <v>8</v>
       </c>
       <c r="G119" t="n">
-        <v>0.7826393789696542</v>
+        <v>0.7820874471086037</v>
       </c>
       <c r="H119" t="n">
-        <v>11.66356563161609</v>
+        <v>11.66003878702398</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -10567,16 +10567,16 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>5.543565631616089</v>
+        <v>5.540038787023978</v>
       </c>
       <c r="N119" t="n">
-        <v>5.543565631616089</v>
+        <v>5.540038787023978</v>
       </c>
       <c r="O119" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.06201658433309909</v>
+        <v>-0.06434767277855968</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -10616,10 +10616,10 @@
         <v>8</v>
       </c>
       <c r="G120" t="n">
-        <v>0.7685250529287226</v>
+        <v>0.7679830747531735</v>
       </c>
       <c r="H120" t="n">
-        <v>11.55695836273818</v>
+        <v>11.55580394922426</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10638,16 +10638,16 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>5.486958362738179</v>
+        <v>5.485803949224259</v>
       </c>
       <c r="N120" t="n">
-        <v>5.486958362738179</v>
+        <v>5.485803949224259</v>
       </c>
       <c r="O120" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.1066072688779105</v>
+        <v>-0.1042348377997193</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         <v>8</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7593507410021172</v>
+        <v>0.7588152327221439</v>
       </c>
       <c r="H121" t="n">
-        <v>11.48875617501764</v>
+        <v>11.4716466854725</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -10709,16 +10709,16 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.458756175017643</v>
+        <v>5.441646685472498</v>
       </c>
       <c r="N121" t="n">
-        <v>5.458756175017643</v>
+        <v>5.441646685472498</v>
       </c>
       <c r="O121" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.06820218772053543</v>
+        <v>-0.08415726375176114</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>8</v>
       </c>
       <c r="G122" t="n">
-        <v>0.9597741707833451</v>
+        <v>0.9598025387870239</v>
       </c>
       <c r="H122" t="n">
-        <v>112.8937473535639</v>
+        <v>112.895437235543</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>105.8937473535639</v>
+        <v>105.895437235543</v>
       </c>
       <c r="N122" t="n">
-        <v>105.8937473535639</v>
+        <v>105.895437235543</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         <v>8</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9357798165137615</v>
+        <v>0.9358251057827927</v>
       </c>
       <c r="H123" t="n">
-        <v>112.4634862385321</v>
+        <v>112.4638716502116</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -10845,16 +10845,16 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>105.6534862385321</v>
+        <v>105.6538716502116</v>
       </c>
       <c r="N123" t="n">
-        <v>105.6534862385321</v>
+        <v>105.6538716502116</v>
       </c>
       <c r="O123" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.4302611150317546</v>
+        <v>-0.4315655853314553</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -10894,10 +10894,10 @@
         <v>8</v>
       </c>
       <c r="G124" t="n">
-        <v>0.918136908962597</v>
+        <v>0.918194640338505</v>
       </c>
       <c r="H124" t="n">
-        <v>112.1433450952717</v>
+        <v>112.1438363892807</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -10916,16 +10916,16 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>105.5333450952717</v>
+        <v>105.5338363892807</v>
       </c>
       <c r="N124" t="n">
-        <v>105.5333450952717</v>
+        <v>105.5338363892807</v>
       </c>
       <c r="O124" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P124" t="n">
-        <v>-0.3201411432604004</v>
+        <v>-0.3200352609308794</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -10965,10 +10965,10 @@
         <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>0.9011997177134792</v>
+        <v>0.9012693935119888</v>
       </c>
       <c r="H125" t="n">
-        <v>111.9996047988708</v>
+        <v>111.9999012693935</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -10987,16 +10987,16 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>105.5796047988708</v>
+        <v>105.5799012693935</v>
       </c>
       <c r="N125" t="n">
-        <v>105.5796047988708</v>
+        <v>105.5799012693935</v>
       </c>
       <c r="O125" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P125" t="n">
-        <v>-0.1437402964008641</v>
+        <v>-0.1439351198871606</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -11036,10 +11036,10 @@
         <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>0.858151023288638</v>
+        <v>0.8582510578279267</v>
       </c>
       <c r="H126" t="n">
-        <v>111.6792978122795</v>
+        <v>111.6805747531735</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -11058,16 +11058,16 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>105.4492978122795</v>
+        <v>105.4505747531735</v>
       </c>
       <c r="N126" t="n">
-        <v>105.4492978122795</v>
+        <v>105.4505747531735</v>
       </c>
       <c r="O126" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.3203069865913903</v>
+        <v>-0.3193265162200447</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -11107,10 +11107,10 @@
         <v>8</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8122794636556104</v>
+        <v>0.8124118476727785</v>
       </c>
       <c r="H127" t="n">
-        <v>111.4341660785697</v>
+        <v>111.4345416078985</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -11129,16 +11129,16 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>105.3741660785697</v>
+        <v>105.3745416078985</v>
       </c>
       <c r="N127" t="n">
-        <v>105.3741660785697</v>
+        <v>105.3745416078985</v>
       </c>
       <c r="O127" t="n">
         <v>-0.1700000000000008</v>
       </c>
       <c r="P127" t="n">
-        <v>-0.2451317337097123</v>
+        <v>-0.2460331452750211</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -11178,10 +11178,10 @@
         <v>8</v>
       </c>
       <c r="G128" t="n">
-        <v>0.7537050105857446</v>
+        <v>0.7538787023977433</v>
       </c>
       <c r="H128" t="n">
-        <v>111.1708059280169</v>
+        <v>111.171101551481</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -11200,16 +11200,16 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>105.240805928017</v>
+        <v>105.241101551481</v>
       </c>
       <c r="N128" t="n">
-        <v>105.240805928017</v>
+        <v>105.241101551481</v>
       </c>
       <c r="O128" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.2633601505527992</v>
+        <v>-0.2634400564174939</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -11249,10 +11249,10 @@
         <v>8</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6760762173606211</v>
+        <v>0.6763046544428772</v>
       </c>
       <c r="H129" t="n">
-        <v>110.7701129146083</v>
+        <v>110.7730289139633</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -11271,16 +11271,16 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>52.40511291460833</v>
+        <v>52.40802891396333</v>
       </c>
       <c r="N129" t="n">
-        <v>52.40511291460833</v>
+        <v>52.40802891396333</v>
       </c>
       <c r="O129" t="n">
         <v>52.435</v>
       </c>
       <c r="P129" t="n">
-        <v>-0.4006930134086133</v>
+        <v>-0.3980726375176289</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -11320,10 +11320,10 @@
         <v>8</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5984474241354976</v>
+        <v>0.5987306064880112</v>
       </c>
       <c r="H130" t="n">
-        <v>110.3763937896965</v>
+        <v>110.3775987306065</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -11342,16 +11342,16 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>52.08139378969653</v>
+        <v>52.08259873060648</v>
       </c>
       <c r="N130" t="n">
-        <v>52.08139378969653</v>
+        <v>52.08259873060648</v>
       </c>
       <c r="O130" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.3937191249117973</v>
+        <v>-0.3954301833568508</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         <v>8</v>
       </c>
       <c r="G131" t="n">
-        <v>0.5179957657021877</v>
+        <v>0.5183356840620592</v>
       </c>
       <c r="H131" t="n">
-        <v>109.9724431898377</v>
+        <v>109.9733110014104</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -11413,16 +11413,16 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>51.78744318983769</v>
+        <v>51.78831100141043</v>
       </c>
       <c r="N131" t="n">
-        <v>51.78744318983769</v>
+        <v>51.78831100141043</v>
       </c>
       <c r="O131" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.4039505998588453</v>
+        <v>-0.4042877291960423</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -11462,10 +11462,10 @@
         <v>8</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4333098094565985</v>
+        <v>0.4337094499294781</v>
       </c>
       <c r="H132" t="n">
-        <v>109.4583109856504</v>
+        <v>109.4608674188999</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -11484,16 +11484,16 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>51.41331098565043</v>
+        <v>51.41586741889985</v>
       </c>
       <c r="N132" t="n">
-        <v>51.41331098565043</v>
+        <v>51.41586741889985</v>
       </c>
       <c r="O132" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.5141322041872627</v>
+        <v>-0.5124435825105849</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -11533,10 +11533,10 @@
         <v>8</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3528581510232887</v>
+        <v>0.3533145275035261</v>
       </c>
       <c r="H133" t="n">
-        <v>108.9164114326041</v>
+        <v>108.9183533145275</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -11555,16 +11555,16 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>103.4764114326041</v>
+        <v>103.4783533145275</v>
       </c>
       <c r="N133" t="n">
-        <v>103.4764114326041</v>
+        <v>103.4783533145275</v>
       </c>
       <c r="O133" t="n">
         <v>-52.605</v>
       </c>
       <c r="P133" t="n">
-        <v>-0.5418995530463349</v>
+        <v>-0.5425141043723443</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -11604,10 +11604,10 @@
         <v>8</v>
       </c>
       <c r="G134" t="n">
-        <v>0.2695836273817925</v>
+        <v>0.270098730606488</v>
       </c>
       <c r="H134" t="n">
-        <v>108.4141566690191</v>
+        <v>108.4185401974612</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -11626,16 +11626,16 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>103.0941566690191</v>
+        <v>103.0985401974612</v>
       </c>
       <c r="N134" t="n">
-        <v>103.0941566690191</v>
+        <v>103.0985401974612</v>
       </c>
       <c r="O134" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P134" t="n">
-        <v>-0.5022547635850287</v>
+        <v>-0.4998131170662958</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
         <v>8</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9315455187014821</v>
+        <v>0.9315937940761636</v>
       </c>
       <c r="H154" t="n">
-        <v>9.032110091743119</v>
+        <v>9.032179125528915</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -13034,16 +13034,16 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>0.5721100917431183</v>
+        <v>0.5721791255289137</v>
       </c>
       <c r="N154" t="n">
-        <v>0.5721100917431183</v>
+        <v>0.5721791255289137</v>
       </c>
       <c r="O154" t="n">
         <v>0.005000000000000782</v>
       </c>
       <c r="P154" t="n">
-        <v>0.5831008065293855</v>
+        <v>0.5831698403151808</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>8</v>
       </c>
       <c r="G155" t="n">
-        <v>0.92166549047283</v>
+        <v>0.9217207334273625</v>
       </c>
       <c r="H155" t="n">
         <v>9.009999999999998</v>
@@ -13114,7 +13114,7 @@
         <v>-0.03000000000000114</v>
       </c>
       <c r="P155" t="n">
-        <v>-0.02211009174312117</v>
+        <v>-0.02217912552891654</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -13154,10 +13154,10 @@
         <v>8</v>
       </c>
       <c r="G156" t="n">
-        <v>0.9146083274523642</v>
+        <v>0.9146685472496474</v>
       </c>
       <c r="H156" t="n">
-        <v>8.967889908256883</v>
+        <v>8.967976022566997</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -13176,16 +13176,16 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0.5578899082568824</v>
+        <v>0.5579760225669972</v>
       </c>
       <c r="N156" t="n">
-        <v>0.5578899082568824</v>
+        <v>0.5579760225669972</v>
       </c>
       <c r="O156" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P156" t="n">
-        <v>-0.04211009174311542</v>
+        <v>-0.04202397743300068</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -13225,10 +13225,10 @@
         <v>8</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9054340155257586</v>
+        <v>0.9055007052186178</v>
       </c>
       <c r="H157" t="n">
-        <v>8.922041284403671</v>
+        <v>8.922232016925248</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -13247,16 +13247,16 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>0.6220412844036698</v>
+        <v>0.6222320169252473</v>
       </c>
       <c r="N157" t="n">
-        <v>0.6220412844036698</v>
+        <v>0.6222320169252473</v>
       </c>
       <c r="O157" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P157" t="n">
-        <v>-0.04584862385321209</v>
+        <v>-0.0457440056417493</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>8</v>
       </c>
       <c r="G158" t="n">
-        <v>0.8955539872971066</v>
+        <v>0.8956276445698167</v>
       </c>
       <c r="H158" t="n">
-        <v>8.858142201834864</v>
+        <v>8.85824753173484</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -13318,16 +13318,16 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>0.6881422018348644</v>
+        <v>0.6882475317348398</v>
       </c>
       <c r="N158" t="n">
-        <v>0.6881422018348644</v>
+        <v>0.6882475317348398</v>
       </c>
       <c r="O158" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P158" t="n">
-        <v>-0.06389908256880616</v>
+        <v>-0.06398448519040834</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -13367,10 +13367,10 @@
         <v>8</v>
       </c>
       <c r="G159" t="n">
-        <v>0.8892025405786874</v>
+        <v>0.889280677009873</v>
       </c>
       <c r="H159" t="n">
-        <v>8.79341743119266</v>
+        <v>8.794199576868829</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -13389,16 +13389,16 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>0.8434174311926599</v>
+        <v>0.8441995768688288</v>
       </c>
       <c r="N159" t="n">
-        <v>0.8434174311926599</v>
+        <v>0.8441995768688288</v>
       </c>
       <c r="O159" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P159" t="n">
-        <v>-0.06472477064220428</v>
+        <v>-0.06404795486601067</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -13438,10 +13438,10 @@
         <v>8</v>
       </c>
       <c r="G160" t="n">
-        <v>0.8659139026111503</v>
+        <v>0.8660084626234132</v>
       </c>
       <c r="H160" t="n">
-        <v>8.435298165137615</v>
+        <v>8.436244710860366</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -13460,16 +13460,16 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>0.6652981651376155</v>
+        <v>0.6662447108603669</v>
       </c>
       <c r="N160" t="n">
-        <v>0.6652981651376155</v>
+        <v>0.6662447108603669</v>
       </c>
       <c r="O160" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P160" t="n">
-        <v>-0.358119266055045</v>
+        <v>-0.3579548660084626</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -13509,10 +13509,10 @@
         <v>8</v>
       </c>
       <c r="G161" t="n">
-        <v>0.8588567395906845</v>
+        <v>0.8589562764456982</v>
       </c>
       <c r="H161" t="n">
-        <v>8.246788990825687</v>
+        <v>8.250916784203103</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -13531,16 +13531,16 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>0.5167889908256864</v>
+        <v>0.5209167842031022</v>
       </c>
       <c r="N161" t="n">
-        <v>0.5167889908256864</v>
+        <v>0.5209167842031022</v>
       </c>
       <c r="O161" t="n">
         <v>-0.03999999999999915</v>
       </c>
       <c r="P161" t="n">
-        <v>-0.1885091743119283</v>
+        <v>-0.1853279266572638</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -13580,10 +13580,10 @@
         <v>8</v>
       </c>
       <c r="G162" t="n">
-        <v>0.8496824276640791</v>
+        <v>0.8497884344146686</v>
       </c>
       <c r="H162" t="n">
-        <v>8.015321100917429</v>
+        <v>8.01638222849083</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -13602,16 +13602,16 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>0.315321100917429</v>
+        <v>0.3163822284908298</v>
       </c>
       <c r="N162" t="n">
-        <v>0.315321100917429</v>
+        <v>0.3163822284908298</v>
       </c>
       <c r="O162" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P162" t="n">
-        <v>-0.2314678899082576</v>
+        <v>-0.2345345557122727</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -13651,10 +13651,10 @@
         <v>8</v>
       </c>
       <c r="G163" t="n">
-        <v>0.844742413549753</v>
+        <v>0.844851904090268</v>
       </c>
       <c r="H163" t="n">
-        <v>7.951444954128441</v>
+        <v>7.95191466854725</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -13673,16 +13673,16 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>0.311444954128441</v>
+        <v>0.3119146685472503</v>
       </c>
       <c r="N163" t="n">
-        <v>0.311444954128441</v>
+        <v>0.3119146685472503</v>
       </c>
       <c r="O163" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P163" t="n">
-        <v>-0.06387614678898856</v>
+        <v>-0.06446755994358</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -13722,10 +13722,10 @@
         <v>8</v>
       </c>
       <c r="G164" t="n">
-        <v>0.8383909668313339</v>
+        <v>0.8385049365303244</v>
       </c>
       <c r="H164" t="n">
-        <v>7.846490825688074</v>
+        <v>7.848120592383639</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -13744,16 +13744,16 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>0.286490825688074</v>
+        <v>0.2881205923836392</v>
       </c>
       <c r="N164" t="n">
-        <v>0.286490825688074</v>
+        <v>0.2881205923836392</v>
       </c>
       <c r="O164" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P164" t="n">
-        <v>-0.104954128440367</v>
+        <v>-0.1037940761636111</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -13793,10 +13793,10 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>0.8355681016231475</v>
+        <v>0.8356840620592384</v>
       </c>
       <c r="H165" t="n">
-        <v>7.829862385321101</v>
+        <v>7.830028208744711</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -13815,16 +13815,16 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>0.3498623853211003</v>
+        <v>0.3500282087447104</v>
       </c>
       <c r="N165" t="n">
-        <v>0.3498623853211003</v>
+        <v>0.3500282087447104</v>
       </c>
       <c r="O165" t="n">
         <v>-0.07999999999999918</v>
       </c>
       <c r="P165" t="n">
-        <v>-0.01662844036697297</v>
+        <v>-0.01809238363892796</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -13864,10 +13864,10 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>0.8270995059985886</v>
+        <v>0.8272214386459803</v>
       </c>
       <c r="H166" t="n">
-        <v>7.758761467889908</v>
+        <v>7.759633286318759</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -13886,16 +13886,16 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>0.3887614678899078</v>
+        <v>0.3896332863187588</v>
       </c>
       <c r="N166" t="n">
-        <v>0.3887614678899078</v>
+        <v>0.3896332863187588</v>
       </c>
       <c r="O166" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P166" t="n">
-        <v>-0.07110091743119273</v>
+        <v>-0.07039492242595191</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -15065,10 +15065,10 @@
         <v>8</v>
       </c>
       <c r="G183" t="n">
-        <v>0.8002822865208187</v>
+        <v>0.8004231311706629</v>
       </c>
       <c r="H183" t="n">
-        <v>5.551364678899082</v>
+        <v>5.551421897038082</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -15087,16 +15087,16 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>0.3363646788990824</v>
+        <v>0.3364218970380817</v>
       </c>
       <c r="N183" t="n">
-        <v>0.3363646788990824</v>
+        <v>0.3364218970380817</v>
       </c>
       <c r="O183" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P183" t="n">
-        <v>-0.09271555936300668</v>
+        <v>-0.0926583412240074</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -15136,10 +15136,10 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>0.8539167254763586</v>
+        <v>0.8540197461212976</v>
       </c>
       <c r="H184" t="n">
-        <v>5.760229357798165</v>
+        <v>5.760564174894217</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -15158,16 +15158,16 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>0.5952293577981651</v>
+        <v>0.5955641748942169</v>
       </c>
       <c r="N184" t="n">
-        <v>0.5952293577981651</v>
+        <v>0.5955641748942169</v>
       </c>
       <c r="O184" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P184" t="n">
-        <v>0.2088646788990829</v>
+        <v>0.2091422778561354</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -15207,10 +15207,10 @@
         <v>8</v>
       </c>
       <c r="G185" t="n">
-        <v>0.8680310515172901</v>
+        <v>0.8681241184767278</v>
       </c>
       <c r="H185" t="n">
-        <v>5.800275229357798</v>
+        <v>5.800350846262341</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -15229,16 +15229,16 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>0.6802752293577976</v>
+        <v>0.6803508462623409</v>
       </c>
       <c r="N185" t="n">
-        <v>0.6802752293577976</v>
+        <v>0.6803508462623409</v>
       </c>
       <c r="O185" t="n">
         <v>-0.04499999999999993</v>
       </c>
       <c r="P185" t="n">
-        <v>0.04004587155963257</v>
+        <v>0.03978667136812408</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -15278,10 +15278,10 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>0.8652081863091038</v>
+        <v>0.8653032440056417</v>
       </c>
       <c r="H186" t="n">
-        <v>5.78788990825688</v>
+        <v>5.788353314527503</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -15300,16 +15300,16 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>0.7078899082568801</v>
+        <v>0.7083533145275034</v>
       </c>
       <c r="N186" t="n">
-        <v>0.7078899082568801</v>
+        <v>0.7083533145275034</v>
       </c>
       <c r="O186" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P186" t="n">
-        <v>-0.0123853211009175</v>
+        <v>-0.01199753173483753</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -15349,10 +15349,10 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8440366972477065</v>
+        <v>0.8441466854724965</v>
       </c>
       <c r="H187" t="n">
-        <v>5.684059633027523</v>
+        <v>5.684238363892807</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -15371,16 +15371,16 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>0.2540596330275235</v>
+        <v>0.2542383638928074</v>
       </c>
       <c r="N187" t="n">
-        <v>0.2540596330275235</v>
+        <v>0.2542383638928074</v>
       </c>
       <c r="O187" t="n">
         <v>0.3499999999999996</v>
       </c>
       <c r="P187" t="n">
-        <v>-0.1038302752293569</v>
+        <v>-0.1041149506346963</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -15420,10 +15420,10 @@
         <v>8</v>
       </c>
       <c r="G188" t="n">
-        <v>0.7953422724064926</v>
+        <v>0.7954866008462623</v>
       </c>
       <c r="H188" t="n">
-        <v>5.535871559633027</v>
+        <v>5.53716149506347</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -15442,16 +15442,16 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.0666284403669728</v>
+        <v>-0.06533850493653048</v>
       </c>
       <c r="N188" t="n">
-        <v>0.0666284403669728</v>
+        <v>0.06533850493653048</v>
       </c>
       <c r="O188" t="n">
         <v>0.1725000000000003</v>
       </c>
       <c r="P188" t="n">
-        <v>-0.148188073394496</v>
+        <v>-0.1470768688293376</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -15491,10 +15491,10 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>0.748059280169372</v>
+        <v>0.7475317348377997</v>
       </c>
       <c r="H189" t="n">
-        <v>5.380779816513763</v>
+        <v>5.377239069111424</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -15513,16 +15513,16 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.169220183486237</v>
+        <v>-0.1727609308885754</v>
       </c>
       <c r="N189" t="n">
-        <v>0.169220183486237</v>
+        <v>0.1727609308885754</v>
       </c>
       <c r="O189" t="n">
         <v>-0.05250000000000021</v>
       </c>
       <c r="P189" t="n">
-        <v>-0.1550917431192644</v>
+        <v>-0.1599224259520451</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -15562,10 +15562,10 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>0.7198306280875089</v>
+        <v>0.7193229901269393</v>
       </c>
       <c r="H190" t="n">
-        <v>5.279931192660551</v>
+        <v>5.279724964739069</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -15584,16 +15584,16 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>-6.880733944925055e-05</v>
+        <v>-0.0002750352609313111</v>
       </c>
       <c r="N190" t="n">
-        <v>6.880733944925055e-05</v>
+        <v>0.0002750352609313111</v>
       </c>
       <c r="O190" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P190" t="n">
-        <v>-0.1008486238532118</v>
+        <v>-0.09751410437235553</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -15633,10 +15633,10 @@
         <v>8</v>
       </c>
       <c r="G191" t="n">
-        <v>0.7148906139731828</v>
+        <v>0.7143864598025388</v>
       </c>
       <c r="H191" t="n">
-        <v>5.277924311926605</v>
+        <v>5.277719499294781</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -15655,16 +15655,16 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>0.2529243119266065</v>
+        <v>0.2527194992947823</v>
       </c>
       <c r="N191" t="n">
-        <v>0.2529243119266065</v>
+        <v>0.2527194992947823</v>
       </c>
       <c r="O191" t="n">
         <v>-0.2550000000000017</v>
       </c>
       <c r="P191" t="n">
-        <v>-0.002006880733945948</v>
+        <v>-0.002005465444288035</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -15704,10 +15704,10 @@
         <v>8</v>
       </c>
       <c r="G192" t="n">
-        <v>0.7233592095977417</v>
+        <v>0.7228490832157969</v>
       </c>
       <c r="H192" t="n">
-        <v>5.283876146788991</v>
+        <v>5.282314880112835</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -15726,16 +15726,16 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>0.4338761467889913</v>
+        <v>0.4323148801128349</v>
       </c>
       <c r="N192" t="n">
-        <v>0.4338761467889913</v>
+        <v>0.4323148801128349</v>
       </c>
       <c r="O192" t="n">
         <v>-0.1749999999999989</v>
       </c>
       <c r="P192" t="n">
-        <v>0.00595183486238593</v>
+        <v>0.004595380818053663</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -15775,10 +15775,10 @@
         <v>8</v>
       </c>
       <c r="G193" t="n">
-        <v>0.7304163726182075</v>
+        <v>0.729901269393512</v>
       </c>
       <c r="H193" t="n">
-        <v>5.314449541284403</v>
+        <v>5.308171720733426</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -15797,16 +15797,16 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>0.7444495412844025</v>
+        <v>0.7381717207334262</v>
       </c>
       <c r="N193" t="n">
-        <v>0.7444495412844025</v>
+        <v>0.7381717207334262</v>
       </c>
       <c r="O193" t="n">
         <v>-0.2799999999999994</v>
       </c>
       <c r="P193" t="n">
-        <v>0.03057339449541185</v>
+        <v>0.0258568406205919</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -15846,10 +15846,10 @@
         <v>8</v>
       </c>
       <c r="G194" t="n">
-        <v>0.721242060691602</v>
+        <v>0.7207334273624824</v>
       </c>
       <c r="H194" t="n">
-        <v>5.281009174311927</v>
+        <v>5.280595909732017</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15868,16 +15868,16 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>0.851009174311927</v>
+        <v>0.850595909732017</v>
       </c>
       <c r="N194" t="n">
-        <v>0.851009174311927</v>
+        <v>0.850595909732017</v>
       </c>
       <c r="O194" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P194" t="n">
-        <v>-0.0334403669724761</v>
+        <v>-0.02757581100140971</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -15917,10 +15917,10 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>0.6937191249117854</v>
+        <v>0.6932299012693935</v>
       </c>
       <c r="H195" t="n">
-        <v>5.212293577981652</v>
+        <v>5.211498589562765</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -15939,16 +15939,16 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>0.7322935779816513</v>
+        <v>0.731498589562765</v>
       </c>
       <c r="N195" t="n">
-        <v>0.7322935779816513</v>
+        <v>0.731498589562765</v>
       </c>
       <c r="O195" t="n">
         <v>0.05000000000000071</v>
       </c>
       <c r="P195" t="n">
-        <v>-0.06871559633027502</v>
+        <v>-0.0690973201692513</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -15988,10 +15988,10 @@
         <v>8</v>
       </c>
       <c r="G196" t="n">
-        <v>0.6549047282992237</v>
+        <v>0.6544428772919605</v>
       </c>
       <c r="H196" t="n">
-        <v>5.115711009174313</v>
+        <v>5.111583215796897</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -16010,16 +16010,16 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>0.3257110091743129</v>
+        <v>0.3215832157968972</v>
       </c>
       <c r="N196" t="n">
-        <v>0.3257110091743129</v>
+        <v>0.3215832157968972</v>
       </c>
       <c r="O196" t="n">
         <v>0.3099999999999996</v>
       </c>
       <c r="P196" t="n">
-        <v>-0.09658256880733873</v>
+        <v>-0.09991537376586823</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>0.7565278757939309</v>
+        <v>0.7566995768688294</v>
       </c>
       <c r="H213" t="n">
         <v>5.970000000000001</v>
@@ -17260,7 +17260,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>0.7558221594918842</v>
+        <v>0.7559943582510579</v>
       </c>
       <c r="H214" t="n">
         <v>5.97</v>
@@ -17331,10 +17331,10 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>0.766407904022583</v>
+        <v>0.7665726375176305</v>
       </c>
       <c r="H215" t="n">
-        <v>6.013466831333804</v>
+        <v>6.014442877291961</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -17353,16 +17353,16 @@
         <v>1</v>
       </c>
       <c r="M215" t="n">
-        <v>-2.466533168666197</v>
+        <v>-2.46555712270804</v>
       </c>
       <c r="N215" t="n">
-        <v>2.466533168666197</v>
+        <v>2.46555712270804</v>
       </c>
       <c r="O215" t="n">
         <v>-0.1074999999999982</v>
       </c>
       <c r="P215" t="n">
-        <v>0.04346683133380402</v>
+        <v>0.04444287729196095</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -17402,10 +17402,10 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>0.7868736767819337</v>
+        <v>0.7870239774330042</v>
       </c>
       <c r="H216" t="n">
-        <v>6.106302046577276</v>
+        <v>6.107489421720734</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -17424,16 +17424,16 @@
         <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>-2.103697953422725</v>
+        <v>-2.102510578279267</v>
       </c>
       <c r="N216" t="n">
-        <v>2.103697953422725</v>
+        <v>2.102510578279267</v>
       </c>
       <c r="O216" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P216" t="n">
-        <v>0.09283521524347194</v>
+        <v>0.09304654442877336</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -17473,10 +17473,10 @@
         <v>8</v>
       </c>
       <c r="G217" t="n">
-        <v>0.8094565984474241</v>
+        <v>0.8095909732016925</v>
       </c>
       <c r="H217" t="n">
-        <v>6.204707127734651</v>
+        <v>6.205768688293371</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -17495,16 +17495,16 @@
         <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>-1.955292872265349</v>
+        <v>-1.954231311706629</v>
       </c>
       <c r="N217" t="n">
-        <v>1.955292872265349</v>
+        <v>1.954231311706629</v>
       </c>
       <c r="O217" t="n">
         <v>-0.05000000000000071</v>
       </c>
       <c r="P217" t="n">
-        <v>0.09840508115737556</v>
+        <v>0.09827926657263664</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -17544,10 +17544,10 @@
         <v>8</v>
       </c>
       <c r="G218" t="n">
-        <v>0.8278052223006351</v>
+        <v>0.8279266572637518</v>
       </c>
       <c r="H218" t="n">
-        <v>6.296440837450012</v>
+        <v>6.297080394922427</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -17566,16 +17566,16 @@
         <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>-1.633559162549988</v>
+        <v>-1.632919605077573</v>
       </c>
       <c r="N218" t="n">
-        <v>1.633559162549988</v>
+        <v>1.632919605077573</v>
       </c>
       <c r="O218" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P218" t="n">
-        <v>0.09173370971536077</v>
+        <v>0.09131170662905586</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -17615,10 +17615,10 @@
         <v>8</v>
       </c>
       <c r="G219" t="n">
-        <v>0.844742413549753</v>
+        <v>0.844851904090268</v>
       </c>
       <c r="H219" t="n">
-        <v>6.385866266760762</v>
+        <v>6.386082510578279</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -17637,16 +17637,16 @@
         <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>-1.604133733239238</v>
+        <v>-1.603917489421721</v>
       </c>
       <c r="N219" t="n">
-        <v>1.604133733239238</v>
+        <v>1.603917489421721</v>
       </c>
       <c r="O219" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P219" t="n">
-        <v>0.08942542931074993</v>
+        <v>0.0890021156558527</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -17686,10 +17686,10 @@
         <v>8</v>
       </c>
       <c r="G220" t="n">
-        <v>0.8517995765702188</v>
+        <v>0.8519040902679831</v>
       </c>
       <c r="H220" t="n">
-        <v>6.457649964714185</v>
+        <v>6.460014104372355</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -17708,16 +17708,16 @@
         <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>-1.532350035285815</v>
+        <v>-1.529985895627645</v>
       </c>
       <c r="N220" t="n">
-        <v>1.532350035285815</v>
+        <v>1.529985895627645</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
       </c>
       <c r="P220" t="n">
-        <v>0.07178369795342299</v>
+        <v>0.0739315937940761</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -17757,10 +17757,10 @@
         <v>8</v>
       </c>
       <c r="G221" t="n">
-        <v>0.8426252646436133</v>
+        <v>0.8427362482369535</v>
       </c>
       <c r="H221" t="n">
-        <v>6.381684897671136</v>
+        <v>6.381904090267983</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -17779,16 +17779,16 @@
         <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>-1.475815102328863</v>
+        <v>-1.475595909732017</v>
       </c>
       <c r="N221" t="n">
-        <v>1.475815102328863</v>
+        <v>1.475595909732017</v>
       </c>
       <c r="O221" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P221" t="n">
-        <v>-0.07596506704304851</v>
+        <v>-0.07811001410437246</v>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
@@ -17828,10 +17828,10 @@
         <v>8</v>
       </c>
       <c r="G222" t="n">
-        <v>0.8228652081863091</v>
+        <v>0.8229901269393513</v>
       </c>
       <c r="H222" t="n">
-        <v>6.250317572335921</v>
+        <v>6.250811001410438</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -17850,16 +17850,16 @@
         <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>-1.489682427664079</v>
+        <v>-1.489188998589563</v>
       </c>
       <c r="N222" t="n">
-        <v>1.489682427664079</v>
+        <v>1.489188998589563</v>
       </c>
       <c r="O222" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.1313673253352157</v>
+        <v>-0.1310930888575452</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -17899,10 +17899,10 @@
         <v>8</v>
       </c>
       <c r="G223" t="n">
-        <v>0.8052223006351447</v>
+        <v>0.8053596614950634</v>
       </c>
       <c r="H223" t="n">
-        <v>6.180837450011762</v>
+        <v>6.181560883874001</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -17921,16 +17921,16 @@
         <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>-1.439162549988239</v>
+        <v>-1.438439116125999</v>
       </c>
       <c r="N223" t="n">
-        <v>1.439162549988239</v>
+        <v>1.438439116125999</v>
       </c>
       <c r="O223" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.06948012232415923</v>
+        <v>-0.06925011753643684</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -17970,10 +17970,10 @@
         <v>8</v>
       </c>
       <c r="G224" t="n">
-        <v>0.7805222300635145</v>
+        <v>0.7806770098730607</v>
       </c>
       <c r="H224" t="n">
-        <v>6.07701570218772</v>
+        <v>6.077168547249647</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -17992,16 +17992,16 @@
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>-1.322984297812281</v>
+        <v>-1.322831452750354</v>
       </c>
       <c r="N224" t="n">
-        <v>1.322984297812281</v>
+        <v>1.322831452750354</v>
       </c>
       <c r="O224" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.1038217478240417</v>
+        <v>-0.104392336624354</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -18041,10 +18041,10 @@
         <v>8</v>
       </c>
       <c r="G225" t="n">
-        <v>0.7529992942836979</v>
+        <v>0.7531734837799718</v>
       </c>
       <c r="H225" t="n">
-        <v>5.966449070806869</v>
+        <v>5.966678420310296</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -18063,16 +18063,16 @@
         <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>-1.393550929193132</v>
+        <v>-1.393321579689704</v>
       </c>
       <c r="N225" t="n">
-        <v>1.393550929193132</v>
+        <v>1.393321579689704</v>
       </c>
       <c r="O225" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.1105666313808511</v>
+        <v>-0.110490126939351</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>8</v>
       </c>
       <c r="G226" t="n">
-        <v>0.7282992237120678</v>
+        <v>0.7284908321579689</v>
       </c>
       <c r="H226" t="n">
-        <v>5.833563867325336</v>
+        <v>5.835077574047955</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -18134,16 +18134,16 @@
         <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>-1.546436132674664</v>
+        <v>-1.544922425952045</v>
       </c>
       <c r="N226" t="n">
-        <v>1.546436132674664</v>
+        <v>1.544922425952045</v>
       </c>
       <c r="O226" t="n">
         <v>0.01999999999999957</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.1328852034815329</v>
+        <v>-0.1316008462623408</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -19313,10 +19313,10 @@
         <v>8</v>
       </c>
       <c r="G243" t="n">
-        <v>0.8285109386026818</v>
+        <v>0.8279266572637518</v>
       </c>
       <c r="H243" t="n">
-        <v>5.561582568807339</v>
+        <v>5.559742595204513</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -19335,16 +19335,16 @@
         <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>1.571582568807338</v>
+        <v>1.569742595204513</v>
       </c>
       <c r="N243" t="n">
-        <v>1.571582568807338</v>
+        <v>1.569742595204513</v>
       </c>
       <c r="O243" t="n">
         <v>-0.1624999999999996</v>
       </c>
       <c r="P243" t="n">
-        <v>-1.599335441003453</v>
+        <v>-1.601175414606279</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -19384,10 +19384,10 @@
         <v>8</v>
       </c>
       <c r="G244" t="n">
-        <v>0.7043048694424842</v>
+        <v>0.7038081805359662</v>
       </c>
       <c r="H244" t="n">
-        <v>4.930172900494001</v>
+        <v>4.928653032440057</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -19406,16 +19406,16 @@
         <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>1.107672900494001</v>
+        <v>1.106153032440057</v>
       </c>
       <c r="N244" t="n">
-        <v>1.107672900494001</v>
+        <v>1.106153032440057</v>
       </c>
       <c r="O244" t="n">
         <v>-0.1675000000000004</v>
       </c>
       <c r="P244" t="n">
-        <v>-0.6314096683133377</v>
+        <v>-0.6310895627644566</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -19455,10 +19455,10 @@
         <v>8</v>
       </c>
       <c r="G245" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.614950634696756</v>
       </c>
       <c r="H245" t="n">
-        <v>4.630192307692308</v>
+        <v>4.629749647390692</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -19477,16 +19477,16 @@
         <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>0.8501923076923084</v>
+        <v>0.8497496473906918</v>
       </c>
       <c r="N245" t="n">
-        <v>0.8501923076923084</v>
+        <v>0.8497496473906918</v>
       </c>
       <c r="O245" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.2999805928016928</v>
+        <v>-0.298903385049365</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -19526,10 +19526,10 @@
         <v>8</v>
       </c>
       <c r="G246" t="n">
-        <v>0.5935074100211715</v>
+        <v>0.5930888575458392</v>
       </c>
       <c r="H246" t="n">
-        <v>4.561275582215949</v>
+        <v>4.557302538787024</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -19548,16 +19548,16 @@
         <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>0.8812755822159493</v>
+        <v>0.8773025387870237</v>
       </c>
       <c r="N246" t="n">
-        <v>0.8812755822159493</v>
+        <v>0.8773025387870237</v>
       </c>
       <c r="O246" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.06891672547635874</v>
+        <v>-0.07244710860366776</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -19597,10 +19597,10 @@
         <v>8</v>
       </c>
       <c r="G247" t="n">
-        <v>0.6337332392378264</v>
+        <v>0.6332863187588152</v>
       </c>
       <c r="H247" t="n">
-        <v>4.72172371206775</v>
+        <v>4.720356135401975</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -19619,16 +19619,16 @@
         <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>1.141723712067749</v>
+        <v>1.140356135401975</v>
       </c>
       <c r="N247" t="n">
-        <v>1.141723712067749</v>
+        <v>1.140356135401975</v>
       </c>
       <c r="O247" t="n">
         <v>-0.1000000000000001</v>
       </c>
       <c r="P247" t="n">
-        <v>0.1604481298518001</v>
+        <v>0.1630535966149509</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -19668,10 +19668,10 @@
         <v>8</v>
       </c>
       <c r="G248" t="n">
-        <v>0.6464361326746648</v>
+        <v>0.6459802538787024</v>
       </c>
       <c r="H248" t="n">
-        <v>4.759364855328158</v>
+        <v>4.758899858956276</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19690,16 +19690,16 @@
         <v>1</v>
       </c>
       <c r="M248" t="n">
-        <v>1.366864855328158</v>
+        <v>1.366399858956276</v>
       </c>
       <c r="N248" t="n">
-        <v>1.366864855328158</v>
+        <v>1.366399858956276</v>
       </c>
       <c r="O248" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P248" t="n">
-        <v>0.03764114326040868</v>
+        <v>0.03854372355430158</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -19739,10 +19739,10 @@
         <v>8</v>
       </c>
       <c r="G249" t="n">
-        <v>0.5963302752293578</v>
+        <v>0.5959097320169252</v>
       </c>
       <c r="H249" t="n">
-        <v>4.590068807339449</v>
+        <v>4.585779266572637</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19761,16 +19761,16 @@
         <v>1</v>
       </c>
       <c r="M249" t="n">
-        <v>1.310068807339449</v>
+        <v>1.305779266572638</v>
       </c>
       <c r="N249" t="n">
-        <v>1.310068807339449</v>
+        <v>1.305779266572638</v>
       </c>
       <c r="O249" t="n">
         <v>-0.1125000000000003</v>
       </c>
       <c r="P249" t="n">
-        <v>-0.1692960479887091</v>
+        <v>-0.173120592383639</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -19810,10 +19810,10 @@
         <v>8</v>
       </c>
       <c r="G250" t="n">
-        <v>0.4897671136203247</v>
+        <v>0.4894217207334274</v>
       </c>
       <c r="H250" t="n">
-        <v>4.145749823570925</v>
+        <v>4.144340620592383</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19832,16 +19832,16 @@
         <v>1</v>
       </c>
       <c r="M250" t="n">
-        <v>0.9957498235709248</v>
+        <v>0.9943406205923835</v>
       </c>
       <c r="N250" t="n">
-        <v>0.9957498235709248</v>
+        <v>0.9943406205923835</v>
       </c>
       <c r="O250" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P250" t="n">
-        <v>-0.4443189837685244</v>
+        <v>-0.441438645980254</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -19881,10 +19881,10 @@
         <v>8</v>
       </c>
       <c r="G251" t="n">
-        <v>0.3902611150317573</v>
+        <v>0.3899858956276446</v>
       </c>
       <c r="H251" t="n">
-        <v>3.801699011997177</v>
+        <v>3.800856840620592</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19903,16 +19903,16 @@
         <v>1</v>
       </c>
       <c r="M251" t="n">
-        <v>0.8566990119971774</v>
+        <v>0.8558568406205924</v>
       </c>
       <c r="N251" t="n">
-        <v>0.8566990119971774</v>
+        <v>0.8558568406205924</v>
       </c>
       <c r="O251" t="n">
         <v>-0.2050000000000001</v>
       </c>
       <c r="P251" t="n">
-        <v>-0.3440508115737475</v>
+        <v>-0.3434837799717911</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         <v>8</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3359209597741708</v>
+        <v>0.3356840620592383</v>
       </c>
       <c r="H252" t="n">
-        <v>3.638797929898848</v>
+        <v>3.637992477668077</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19974,16 +19974,16 @@
         <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>0.7987979298988477</v>
+        <v>0.7979924776680773</v>
       </c>
       <c r="N252" t="n">
-        <v>0.7987979298988477</v>
+        <v>0.7979924776680773</v>
       </c>
       <c r="O252" t="n">
         <v>-0.105</v>
       </c>
       <c r="P252" t="n">
-        <v>-0.1629010820983297</v>
+        <v>-0.1628643629525151</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -20023,10 +20023,10 @@
         <v>8</v>
       </c>
       <c r="G253" t="n">
-        <v>0.3465067043048695</v>
+        <v>0.346262341325811</v>
       </c>
       <c r="H253" t="n">
-        <v>3.674789461303223</v>
+        <v>3.673958627174424</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -20045,16 +20045,16 @@
         <v>1</v>
       </c>
       <c r="M253" t="n">
-        <v>0.9047894613032228</v>
+        <v>0.9039586271744242</v>
       </c>
       <c r="N253" t="n">
-        <v>0.9047894613032228</v>
+        <v>0.9039586271744242</v>
       </c>
       <c r="O253" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P253" t="n">
-        <v>0.03599153140437528</v>
+        <v>0.03596614950634702</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -20094,10 +20094,10 @@
         <v>8</v>
       </c>
       <c r="G254" t="n">
-        <v>0.4940014114326041</v>
+        <v>0.4936530324400564</v>
       </c>
       <c r="H254" t="n">
-        <v>4.170788637967537</v>
+        <v>4.168656558533145</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -20116,16 +20116,16 @@
         <v>1</v>
       </c>
       <c r="M254" t="n">
-        <v>1.350788637967538</v>
+        <v>1.348656558533146</v>
       </c>
       <c r="N254" t="n">
-        <v>1.350788637967538</v>
+        <v>1.348656558533146</v>
       </c>
       <c r="O254" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P254" t="n">
-        <v>0.4959991766643146</v>
+        <v>0.4946979313587212</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -20165,10 +20165,10 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>0.6958362738179252</v>
+        <v>0.6953455571227081</v>
       </c>
       <c r="H255" t="n">
-        <v>4.904505998588568</v>
+        <v>4.903504936530324</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -20187,16 +20187,16 @@
         <v>1</v>
       </c>
       <c r="M255" t="n">
-        <v>2.154505998588568</v>
+        <v>2.153504936530324</v>
       </c>
       <c r="N255" t="n">
-        <v>2.154505998588568</v>
+        <v>2.153504936530324</v>
       </c>
       <c r="O255" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P255" t="n">
-        <v>0.7337173606210303</v>
+        <v>0.7348483779971788</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
@@ -20236,10 +20236,10 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>0.7882851093860268</v>
+        <v>0.7877291960507757</v>
       </c>
       <c r="H256" t="n">
-        <v>5.203482709950599</v>
+        <v>5.198095909732016</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -20258,16 +20258,16 @@
         <v>1</v>
       </c>
       <c r="M256" t="n">
-        <v>2.453482709950599</v>
+        <v>2.448095909732016</v>
       </c>
       <c r="N256" t="n">
-        <v>2.453482709950599</v>
+        <v>2.448095909732016</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
       </c>
       <c r="P256" t="n">
-        <v>0.2989767113620312</v>
+        <v>0.294590973201692</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -21437,10 +21437,10 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>0.9428369795342273</v>
+        <v>0.9428772919605077</v>
       </c>
       <c r="H273" t="n">
-        <v>6.914174311926606</v>
+        <v>6.914397038081805</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -21459,16 +21459,16 @@
         <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>-0.8508256880733933</v>
+        <v>-0.8506029619181943</v>
       </c>
       <c r="N273" t="n">
-        <v>0.8508256880733933</v>
+        <v>0.8506029619181943</v>
       </c>
       <c r="O273" t="n">
         <v>0.0550000000000006</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.9767600492039703</v>
+        <v>-0.9765373230487713</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -21508,10 +21508,10 @@
         <v>8</v>
       </c>
       <c r="G274" t="n">
-        <v>0.9393083980239944</v>
+        <v>0.9393511988716502</v>
       </c>
       <c r="H274" t="n">
-        <v>6.849678899082568</v>
+        <v>6.849915373765867</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -21530,16 +21530,16 @@
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>-0.9303211009174319</v>
+        <v>-0.9300846262341329</v>
       </c>
       <c r="N274" t="n">
-        <v>0.9303211009174319</v>
+        <v>0.9300846262341329</v>
       </c>
       <c r="O274" t="n">
         <v>0.01500000000000057</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.06449541284403804</v>
+        <v>-0.06448166431593805</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -21579,10 +21579,10 @@
         <v>8</v>
       </c>
       <c r="G275" t="n">
-        <v>0.9357798165137615</v>
+        <v>0.9358251057827927</v>
       </c>
       <c r="H275" t="n">
-        <v>6.830183486238532</v>
+        <v>6.830433709449929</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -21601,16 +21601,16 @@
         <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>-0.9398165137614676</v>
+        <v>-0.9395662905500703</v>
       </c>
       <c r="N275" t="n">
-        <v>0.9398165137614676</v>
+        <v>0.9395662905500703</v>
       </c>
       <c r="O275" t="n">
         <v>-0.01000000000000068</v>
       </c>
       <c r="P275" t="n">
-        <v>-0.01949541284403633</v>
+        <v>-0.01948166431593812</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -21650,10 +21650,10 @@
         <v>8</v>
       </c>
       <c r="G276" t="n">
-        <v>0.9322512350035286</v>
+        <v>0.9322990126939351</v>
       </c>
       <c r="H276" t="n">
-        <v>6.820344036697248</v>
+        <v>6.820476022566996</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -21672,16 +21672,16 @@
         <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>-0.8796559633027519</v>
+        <v>-0.8795239774330046</v>
       </c>
       <c r="N276" t="n">
-        <v>0.8796559633027519</v>
+        <v>0.8795239774330046</v>
       </c>
       <c r="O276" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P276" t="n">
-        <v>-0.009839449541283685</v>
+        <v>-0.009957686882933636</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -21721,10 +21721,10 @@
         <v>8</v>
       </c>
       <c r="G277" t="n">
-        <v>0.9287226534932957</v>
+        <v>0.9287729196050776</v>
       </c>
       <c r="H277" t="n">
-        <v>6.781192660550459</v>
+        <v>6.781470380818053</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -21743,16 +21743,16 @@
         <v>1</v>
       </c>
       <c r="M277" t="n">
-        <v>-0.8088073394495412</v>
+        <v>-0.8085296191819467</v>
       </c>
       <c r="N277" t="n">
-        <v>0.8088073394495412</v>
+        <v>0.8085296191819467</v>
       </c>
       <c r="O277" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P277" t="n">
-        <v>-0.03915137614678965</v>
+        <v>-0.03900564174894239</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -21792,10 +21792,10 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>0.9251940719830628</v>
+        <v>0.92524682651622</v>
       </c>
       <c r="H278" t="n">
-        <v>6.751697247706422</v>
+        <v>6.751988716502115</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -21814,16 +21814,16 @@
         <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>-0.6983027522935785</v>
+        <v>-0.6980112834978849</v>
       </c>
       <c r="N278" t="n">
-        <v>0.6983027522935785</v>
+        <v>0.6980112834978849</v>
       </c>
       <c r="O278" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P278" t="n">
-        <v>-0.02949541284403701</v>
+        <v>-0.02948166431593791</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -21863,10 +21863,10 @@
         <v>8</v>
       </c>
       <c r="G279" t="n">
-        <v>0.92166549047283</v>
+        <v>0.9217207334273625</v>
       </c>
       <c r="H279" t="n">
-        <v>6.71480122324159</v>
+        <v>6.715004701457452</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -21885,16 +21885,16 @@
         <v>1</v>
       </c>
       <c r="M279" t="n">
-        <v>-0.65519877675841</v>
+        <v>-0.6549952985425485</v>
       </c>
       <c r="N279" t="n">
-        <v>0.65519877675841</v>
+        <v>0.6549952985425485</v>
       </c>
       <c r="O279" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P279" t="n">
-        <v>-0.03689602446483153</v>
+        <v>-0.03698401504466364</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -21934,10 +21934,10 @@
         <v>8</v>
       </c>
       <c r="G280" t="n">
-        <v>0.918136908962597</v>
+        <v>0.918194640338505</v>
       </c>
       <c r="H280" t="n">
-        <v>6.680825688073396</v>
+        <v>6.682101551480961</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -21956,16 +21956,16 @@
         <v>1</v>
       </c>
       <c r="M280" t="n">
-        <v>-0.5891743119266035</v>
+        <v>-0.5878984485190388</v>
       </c>
       <c r="N280" t="n">
-        <v>0.5891743119266035</v>
+        <v>0.5878984485190388</v>
       </c>
       <c r="O280" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P280" t="n">
-        <v>-0.03397553516819407</v>
+        <v>-0.03290314997649091</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -22005,10 +22005,10 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>0.9146083274523642</v>
+        <v>0.9146685472496474</v>
       </c>
       <c r="H281" t="n">
-        <v>6.626422018348625</v>
+        <v>6.627087447108604</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -22027,16 +22027,16 @@
         <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>-0.6335779816513751</v>
+        <v>-0.6329125528913959</v>
       </c>
       <c r="N281" t="n">
-        <v>0.6335779816513751</v>
+        <v>0.6329125528913959</v>
       </c>
       <c r="O281" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P281" t="n">
-        <v>-0.0544036697247714</v>
+        <v>-0.05501410437235688</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -22076,10 +22076,10 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>0.9110797459421313</v>
+        <v>0.9111424541607899</v>
       </c>
       <c r="H282" t="n">
-        <v>6.548715596330275</v>
+        <v>6.549062059238364</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -22098,16 +22098,16 @@
         <v>1</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.5612844036697249</v>
+        <v>-0.5609379407616366</v>
       </c>
       <c r="N282" t="n">
-        <v>0.5612844036697249</v>
+        <v>0.5609379407616366</v>
       </c>
       <c r="O282" t="n">
         <v>-0.1499999999999995</v>
       </c>
       <c r="P282" t="n">
-        <v>-0.07770642201834921</v>
+        <v>-0.07802538787024016</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -22147,10 +22147,10 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>0.9075511644318984</v>
+        <v>0.9076163610719323</v>
       </c>
       <c r="H283" t="n">
-        <v>6.516880733944955</v>
+        <v>6.518321579689704</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -22169,16 +22169,16 @@
         <v>1</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.4931192660550447</v>
+        <v>-0.4916784203102953</v>
       </c>
       <c r="N283" t="n">
-        <v>0.4931192660550447</v>
+        <v>0.4916784203102953</v>
       </c>
       <c r="O283" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P283" t="n">
-        <v>-0.03183486238532041</v>
+        <v>-0.03074047954865922</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -22218,10 +22218,10 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>0.9054340155257586</v>
+        <v>0.9055007052186178</v>
       </c>
       <c r="H284" t="n">
-        <v>6.450275229357798</v>
+        <v>6.454696755994361</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -22240,16 +22240,16 @@
         <v>1</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.3697247706422022</v>
+        <v>-0.3653032440056396</v>
       </c>
       <c r="N284" t="n">
-        <v>0.3697247706422022</v>
+        <v>0.3653032440056396</v>
       </c>
       <c r="O284" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P284" t="n">
-        <v>-0.06660550458715697</v>
+        <v>-0.06362482369534384</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -22289,10 +22289,10 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>0.9019054340155258</v>
+        <v>0.9019746121297603</v>
       </c>
       <c r="H285" t="n">
-        <v>6.403027522935781</v>
+        <v>6.403409732016926</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -22311,16 +22311,16 @@
         <v>1</v>
       </c>
       <c r="M285" t="n">
-        <v>-0.2969724770642195</v>
+        <v>-0.2965902679830741</v>
       </c>
       <c r="N285" t="n">
-        <v>0.2969724770642195</v>
+        <v>0.2965902679830741</v>
       </c>
       <c r="O285" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P285" t="n">
-        <v>-0.04724770642201737</v>
+        <v>-0.05128702397743456</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
@@ -22329,11 +22329,11 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>Estable</t>
+          <t>Descendente</t>
         </is>
       </c>
       <c r="S285" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
@@ -22360,10 +22360,10 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>0.8990825688073395</v>
+        <v>0.8991537376586742</v>
       </c>
       <c r="H286" t="n">
-        <v>6.359724770642202</v>
+        <v>6.3612976022567</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -22382,16 +22382,16 @@
         <v>1</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.1802752293577976</v>
+        <v>-0.1787023977433</v>
       </c>
       <c r="N286" t="n">
-        <v>0.1802752293577976</v>
+        <v>0.1787023977433</v>
       </c>
       <c r="O286" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P286" t="n">
-        <v>-0.04330275229357827</v>
+        <v>-0.04211212976022605</v>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
@@ -25685,10 +25685,10 @@
         <v>8</v>
       </c>
       <c r="G333" t="n">
-        <v>0.7642907551164432</v>
+        <v>0.764456981664316</v>
       </c>
       <c r="H333" t="n">
-        <v>6.487064220183487</v>
+        <v>6.488004231311707</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -25707,16 +25707,16 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.7754357798165135</v>
+        <v>-0.7744957686882934</v>
       </c>
       <c r="N333" t="n">
-        <v>0.7754357798165135</v>
+        <v>0.7744957686882934</v>
       </c>
       <c r="O333" t="n">
         <v>-0.4400000000000004</v>
       </c>
       <c r="P333" t="n">
-        <v>-0.9804410355978721</v>
+        <v>-0.979501024469652</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -25756,10 +25756,10 @@
         <v>8</v>
       </c>
       <c r="G334" t="n">
-        <v>0.7727593507410021</v>
+        <v>0.7729196050775741</v>
       </c>
       <c r="H334" t="n">
-        <v>6.538107798165138</v>
+        <v>6.53844763751763</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -25778,16 +25778,16 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.436892201834862</v>
+        <v>-0.4365523624823693</v>
       </c>
       <c r="N334" t="n">
-        <v>0.436892201834862</v>
+        <v>0.4365523624823693</v>
       </c>
       <c r="O334" t="n">
         <v>-0.2875000000000005</v>
       </c>
       <c r="P334" t="n">
-        <v>0.05104357798165093</v>
+        <v>0.05044340620592358</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -25827,10 +25827,10 @@
         <v>8</v>
       </c>
       <c r="G335" t="n">
-        <v>0.7925194071983063</v>
+        <v>0.7926657263751763</v>
       </c>
       <c r="H335" t="n">
-        <v>6.650986238532109</v>
+        <v>6.655123413258109</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -25849,16 +25849,16 @@
         <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.1490137614678906</v>
+        <v>-0.1448765867418906</v>
       </c>
       <c r="N335" t="n">
-        <v>0.1490137614678906</v>
+        <v>0.1448765867418906</v>
       </c>
       <c r="O335" t="n">
         <v>-0.1749999999999998</v>
       </c>
       <c r="P335" t="n">
-        <v>0.1128784403669716</v>
+        <v>0.1166757757404788</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -25898,10 +25898,10 @@
         <v>8</v>
       </c>
       <c r="G336" t="n">
-        <v>0.8151023288637967</v>
+        <v>0.8152327221438646</v>
       </c>
       <c r="H336" t="n">
-        <v>6.84940366972477</v>
+        <v>6.85021156558533</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -25920,16 +25920,16 @@
         <v>1</v>
       </c>
       <c r="M336" t="n">
-        <v>0.2194036697247705</v>
+        <v>0.2202115655853305</v>
       </c>
       <c r="N336" t="n">
-        <v>0.2194036697247705</v>
+        <v>0.2202115655853305</v>
       </c>
       <c r="O336" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P336" t="n">
-        <v>0.1984174311926612</v>
+        <v>0.1950881523272212</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -25969,10 +25969,10 @@
         <v>8</v>
       </c>
       <c r="G337" t="n">
-        <v>0.8348623853211009</v>
+        <v>0.8349788434414669</v>
       </c>
       <c r="H337" t="n">
-        <v>7.066146788990825</v>
+        <v>7.066805359661495</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -25991,16 +25991,16 @@
         <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>0.5761467889908252</v>
+        <v>0.5768053596614946</v>
       </c>
       <c r="N337" t="n">
-        <v>0.5761467889908252</v>
+        <v>0.5768053596614946</v>
       </c>
       <c r="O337" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P337" t="n">
-        <v>0.2167431192660549</v>
+        <v>0.2165937940761644</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>8</v>
       </c>
       <c r="G338" t="n">
-        <v>0.8510938602681722</v>
+        <v>0.8511988716502116</v>
       </c>
       <c r="H338" t="n">
-        <v>7.148587155963303</v>
+        <v>7.148705923836389</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -26062,16 +26062,16 @@
         <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>0.6685871559633023</v>
+        <v>0.6687059238363888</v>
       </c>
       <c r="N338" t="n">
-        <v>0.6685871559633023</v>
+        <v>0.6687059238363888</v>
       </c>
       <c r="O338" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P338" t="n">
-        <v>0.08244036697247736</v>
+        <v>0.08190056417489444</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -26111,10 +26111,10 @@
         <v>8</v>
       </c>
       <c r="G339" t="n">
-        <v>0.858151023288638</v>
+        <v>0.8582510578279267</v>
       </c>
       <c r="H339" t="n">
-        <v>7.205344036697248</v>
+        <v>7.205909732016925</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -26133,16 +26133,16 @@
         <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>0.6553440366972483</v>
+        <v>0.6559097320169256</v>
       </c>
       <c r="N339" t="n">
-        <v>0.6553440366972483</v>
+        <v>0.6559097320169256</v>
       </c>
       <c r="O339" t="n">
         <v>0.0699999999999994</v>
       </c>
       <c r="P339" t="n">
-        <v>0.05675688073394536</v>
+        <v>0.05720380818053616</v>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
@@ -26182,10 +26182,10 @@
         <v>8</v>
       </c>
       <c r="G340" t="n">
-        <v>0.8503881439661256</v>
+        <v>0.8504936530324401</v>
       </c>
       <c r="H340" t="n">
-        <v>7.147788990825688</v>
+        <v>7.14790832157969</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -26204,16 +26204,16 @@
         <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>0.6177889908256882</v>
+        <v>0.6179083215796899</v>
       </c>
       <c r="N340" t="n">
-        <v>0.6177889908256882</v>
+        <v>0.6179083215796899</v>
       </c>
       <c r="O340" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P340" t="n">
-        <v>-0.05755504587155968</v>
+        <v>-0.05800141043723528</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -26253,10 +26253,10 @@
         <v>8</v>
       </c>
       <c r="G341" t="n">
-        <v>0.8306280875088214</v>
+        <v>0.8307475317348378</v>
       </c>
       <c r="H341" t="n">
-        <v>7.026269113149847</v>
+        <v>7.02716972261401</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -26275,16 +26275,16 @@
         <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>0.6937691131498473</v>
+        <v>0.6946697226140106</v>
       </c>
       <c r="N341" t="n">
-        <v>0.6937691131498473</v>
+        <v>0.6946697226140106</v>
       </c>
       <c r="O341" t="n">
         <v>-0.1975000000000007</v>
       </c>
       <c r="P341" t="n">
-        <v>-0.1215198776758415</v>
+        <v>-0.12073859896568</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -26324,10 +26324,10 @@
         <v>8</v>
       </c>
       <c r="G342" t="n">
-        <v>0.8108680310515173</v>
+        <v>0.8110014104372355</v>
       </c>
       <c r="H342" t="n">
-        <v>6.820917431192661</v>
+        <v>6.822425952045133</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -26346,16 +26346,16 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>0.6309174311926604</v>
+        <v>0.632425952045133</v>
       </c>
       <c r="N342" t="n">
-        <v>0.6309174311926604</v>
+        <v>0.632425952045133</v>
       </c>
       <c r="O342" t="n">
         <v>-0.1424999999999992</v>
       </c>
       <c r="P342" t="n">
-        <v>-0.2053516819571861</v>
+        <v>-0.2047437705688768</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>8</v>
       </c>
       <c r="G343" t="n">
-        <v>0.7875793930839803</v>
+        <v>0.7877291960507757</v>
       </c>
       <c r="H343" t="n">
         <v>6.62</v>
@@ -26426,7 +26426,7 @@
         <v>-0.2000000000000002</v>
       </c>
       <c r="P343" t="n">
-        <v>-0.2009174311926607</v>
+        <v>-0.2024259520451333</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -26466,10 +26466,10 @@
         <v>8</v>
       </c>
       <c r="G344" t="n">
-        <v>0.7635850388143967</v>
+        <v>0.7637517630465445</v>
       </c>
       <c r="H344" t="n">
-        <v>6.483073394495413</v>
+        <v>6.484016220028209</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -26488,16 +26488,16 @@
         <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5630733944954134</v>
+        <v>0.5640162200282095</v>
       </c>
       <c r="N344" t="n">
-        <v>0.5630733944954134</v>
+        <v>0.5640162200282095</v>
       </c>
       <c r="O344" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P344" t="n">
-        <v>-0.1369266055045868</v>
+        <v>-0.1359837799717907</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -26537,10 +26537,10 @@
         <v>8</v>
       </c>
       <c r="G345" t="n">
-        <v>0.7417078334509527</v>
+        <v>0.7418899858956276</v>
       </c>
       <c r="H345" t="n">
-        <v>6.380000000000001</v>
+        <v>6.380290902679832</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
@@ -26559,16 +26559,16 @@
         <v>1</v>
       </c>
       <c r="M345" t="n">
-        <v>0.4000000000000004</v>
+        <v>0.4002909026798314</v>
       </c>
       <c r="N345" t="n">
-        <v>0.4000000000000004</v>
+        <v>0.4002909026798314</v>
       </c>
       <c r="O345" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P345" t="n">
-        <v>-0.1030733944954125</v>
+        <v>-0.1037253173483776</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -26608,10 +26608,10 @@
         <v>8</v>
       </c>
       <c r="G346" t="n">
-        <v>0.7184191954834157</v>
+        <v>0.7186177715091678</v>
       </c>
       <c r="H346" t="n">
-        <v>6.233990825688074</v>
+        <v>6.235675246826516</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -26630,16 +26630,16 @@
         <v>1</v>
       </c>
       <c r="M346" t="n">
-        <v>0.1139908256880737</v>
+        <v>0.1156752468265161</v>
       </c>
       <c r="N346" t="n">
-        <v>0.1139908256880737</v>
+        <v>0.1156752468265161</v>
       </c>
       <c r="O346" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P346" t="n">
-        <v>-0.1460091743119269</v>
+        <v>-0.1446156558533156</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -27809,10 +27809,10 @@
         <v>8</v>
       </c>
       <c r="G363" t="n">
-        <v>0.6457304163726182</v>
+        <v>0.6459802538787024</v>
       </c>
       <c r="H363" t="n">
-        <v>6.970555751587861</v>
+        <v>6.971861777150917</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -27831,16 +27831,16 @@
         <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>-1.491944248412139</v>
+        <v>-1.490638222849084</v>
       </c>
       <c r="N363" t="n">
-        <v>1.491944248412139</v>
+        <v>1.490638222849084</v>
       </c>
       <c r="O363" t="n">
         <v>-0.254999999999999</v>
       </c>
       <c r="P363" t="n">
-        <v>0.1279751629403494</v>
+        <v>0.1292811885034046</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -27880,10 +27880,10 @@
         <v>8</v>
       </c>
       <c r="G364" t="n">
-        <v>0.6541990119971771</v>
+        <v>0.6544428772919605</v>
       </c>
       <c r="H364" t="n">
-        <v>7.009767113620325</v>
+        <v>7.011466854724964</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -27902,16 +27902,16 @@
         <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>-1.302732886379675</v>
+        <v>-1.301033145275036</v>
       </c>
       <c r="N364" t="n">
-        <v>1.302732886379675</v>
+        <v>1.301033145275036</v>
       </c>
       <c r="O364" t="n">
         <v>-0.1500000000000004</v>
       </c>
       <c r="P364" t="n">
-        <v>0.03921136203246345</v>
+        <v>0.03960507757404752</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -27951,10 +27951,10 @@
         <v>8</v>
       </c>
       <c r="G365" t="n">
-        <v>0.6669019054340155</v>
+        <v>0.6671368124118476</v>
       </c>
       <c r="H365" t="n">
-        <v>7.069153140437544</v>
+        <v>7.06997179125529</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -27973,16 +27973,16 @@
         <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>-1.060846859562457</v>
+        <v>-1.060028208744711</v>
       </c>
       <c r="N365" t="n">
-        <v>1.060846859562457</v>
+        <v>1.060028208744711</v>
       </c>
       <c r="O365" t="n">
         <v>-0.1824999999999992</v>
       </c>
       <c r="P365" t="n">
-        <v>0.05938602681721949</v>
+        <v>0.0585049365303254</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -28022,10 +28022,10 @@
         <v>8</v>
       </c>
       <c r="G366" t="n">
-        <v>0.6810162314749471</v>
+        <v>0.6812411847672779</v>
       </c>
       <c r="H366" t="n">
-        <v>7.166884262526463</v>
+        <v>7.167766220028208</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -28044,16 +28044,16 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.9206157374735371</v>
+        <v>-0.919733779971792</v>
       </c>
       <c r="N366" t="n">
-        <v>0.9206157374735371</v>
+        <v>0.919733779971792</v>
       </c>
       <c r="O366" t="n">
         <v>-0.04250000000000043</v>
       </c>
       <c r="P366" t="n">
-        <v>0.09773112208891899</v>
+        <v>0.09779442877291888</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -28093,10 +28093,10 @@
         <v>8</v>
       </c>
       <c r="G367" t="n">
-        <v>0.6887791107974595</v>
+        <v>0.6889985895627645</v>
       </c>
       <c r="H367" t="n">
-        <v>7.192961067984005</v>
+        <v>7.193853432063941</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -28115,16 +28115,16 @@
         <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>-1.037038932015996</v>
+        <v>-1.03614656793606</v>
       </c>
       <c r="N367" t="n">
-        <v>1.037038932015996</v>
+        <v>1.03614656793606</v>
       </c>
       <c r="O367" t="n">
         <v>0.1425000000000001</v>
       </c>
       <c r="P367" t="n">
-        <v>0.02607680545754132</v>
+        <v>0.0260872120357325</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -28164,10 +28164,10 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>0.6901905434015526</v>
+        <v>0.6904090267983075</v>
       </c>
       <c r="H368" t="n">
-        <v>7.198699717713479</v>
+        <v>7.199588034790786</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -28186,16 +28186,16 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.8438002822865212</v>
+        <v>-0.8429119652092147</v>
       </c>
       <c r="N368" t="n">
-        <v>0.8438002822865212</v>
+        <v>0.8429119652092147</v>
       </c>
       <c r="O368" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P368" t="n">
-        <v>0.005738649729474687</v>
+        <v>0.005734602726844784</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -28235,10 +28235,10 @@
         <v>8</v>
       </c>
       <c r="G369" t="n">
-        <v>0.68454481298518</v>
+        <v>0.6847672778561354</v>
       </c>
       <c r="H369" t="n">
-        <v>7.181277346506705</v>
+        <v>7.182827926657264</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -28257,16 +28257,16 @@
         <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.7687226534932954</v>
+        <v>-0.7671720733427358</v>
       </c>
       <c r="N369" t="n">
-        <v>0.7687226534932954</v>
+        <v>0.7671720733427358</v>
       </c>
       <c r="O369" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P369" t="n">
-        <v>-0.01742237120677448</v>
+        <v>-0.01676010813352136</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -28306,10 +28306,10 @@
         <v>8</v>
       </c>
       <c r="G370" t="n">
-        <v>0.6725476358503881</v>
+        <v>0.6727785613540197</v>
       </c>
       <c r="H370" t="n">
-        <v>7.113828510938603</v>
+        <v>7.114633286318759</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -28328,16 +28328,16 @@
         <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.8661714890613972</v>
+        <v>-0.8653667136812411</v>
       </c>
       <c r="N370" t="n">
-        <v>0.8661714890613972</v>
+        <v>0.8653667136812411</v>
       </c>
       <c r="O370" t="n">
         <v>0.03000000000000025</v>
       </c>
       <c r="P370" t="n">
-        <v>-0.06744883556810155</v>
+        <v>-0.06819464033850497</v>
       </c>
       <c r="Q370" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>8</v>
       </c>
       <c r="G371" t="n">
-        <v>0.6534932956951306</v>
+        <v>0.653737658674189</v>
       </c>
       <c r="H371" t="n">
-        <v>7.00484827099506</v>
+        <v>7.006551480959097</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -28399,16 +28399,16 @@
         <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>-1.03015172900494</v>
+        <v>-1.028448519040903</v>
       </c>
       <c r="N371" t="n">
-        <v>1.03015172900494</v>
+        <v>1.028448519040903</v>
       </c>
       <c r="O371" t="n">
         <v>0.05499999999999972</v>
       </c>
       <c r="P371" t="n">
-        <v>-0.1089802399435431</v>
+        <v>-0.1080818053596619</v>
       </c>
       <c r="Q371" t="inlineStr">
         <is>
@@ -28448,10 +28448,10 @@
         <v>8</v>
       </c>
       <c r="G372" t="n">
-        <v>0.6316160903316866</v>
+        <v>0.6318758815232722</v>
       </c>
       <c r="H372" t="n">
-        <v>6.938091037402964</v>
+        <v>6.938543723554302</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -28470,16 +28470,16 @@
         <v>1</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.9719089625970359</v>
+        <v>-0.9714562764456982</v>
       </c>
       <c r="N372" t="n">
-        <v>0.9719089625970359</v>
+        <v>0.9714562764456982</v>
       </c>
       <c r="O372" t="n">
         <v>-0.125</v>
       </c>
       <c r="P372" t="n">
-        <v>-0.06675723359209584</v>
+        <v>-0.06800775740479548</v>
       </c>
       <c r="Q372" t="inlineStr">
         <is>
@@ -28519,10 +28519,10 @@
         <v>8</v>
       </c>
       <c r="G373" t="n">
-        <v>0.6167960479887086</v>
+        <v>0.6170662905500706</v>
       </c>
       <c r="H373" t="n">
-        <v>6.883167784050812</v>
+        <v>6.884345028208744</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -28541,16 +28541,16 @@
         <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.8068322159491883</v>
+        <v>-0.805654971791256</v>
       </c>
       <c r="N373" t="n">
-        <v>0.8068322159491883</v>
+        <v>0.805654971791256</v>
       </c>
       <c r="O373" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P373" t="n">
-        <v>-0.0549232533521522</v>
+        <v>-0.05419869534555755</v>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
@@ -28590,10 +28590,10 @@
         <v>8</v>
       </c>
       <c r="G374" t="n">
-        <v>0.5991531404375441</v>
+        <v>0.5994358251057827</v>
       </c>
       <c r="H374" t="n">
-        <v>6.79951217360621</v>
+        <v>6.799758462623413</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -28612,16 +28612,16 @@
         <v>1</v>
       </c>
       <c r="M374" t="n">
-        <v>-0.6604878263937897</v>
+        <v>-0.6602415373765869</v>
       </c>
       <c r="N374" t="n">
-        <v>0.6604878263937897</v>
+        <v>0.6602415373765869</v>
       </c>
       <c r="O374" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P374" t="n">
-        <v>-0.08365561044460179</v>
+        <v>-0.08458656558533129</v>
       </c>
       <c r="Q374" t="inlineStr">
         <is>
@@ -28661,10 +28661,10 @@
         <v>8</v>
       </c>
       <c r="G375" t="n">
-        <v>0.584333098094566</v>
+        <v>0.5846262341325811</v>
       </c>
       <c r="H375" t="n">
-        <v>6.761600211714891</v>
+        <v>6.761855606488012</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -28683,16 +28683,16 @@
         <v>1</v>
       </c>
       <c r="M375" t="n">
-        <v>-0.5183997882851097</v>
+        <v>-0.5181443935119887</v>
       </c>
       <c r="N375" t="n">
-        <v>0.5183997882851097</v>
+        <v>0.5181443935119887</v>
       </c>
       <c r="O375" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.03791196189131973</v>
+        <v>-0.03790285613540156</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
@@ -28732,10 +28732,10 @@
         <v>8</v>
       </c>
       <c r="G376" t="n">
-        <v>0.565984474241355</v>
+        <v>0.5662905500705219</v>
       </c>
       <c r="H376" t="n">
-        <v>6.684911785462244</v>
+        <v>6.687045133991537</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -28754,16 +28754,16 @@
         <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>-0.4250882145377561</v>
+        <v>-0.422954866008463</v>
       </c>
       <c r="N376" t="n">
-        <v>0.4250882145377561</v>
+        <v>0.422954866008463</v>
       </c>
       <c r="O376" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.07668842625264638</v>
+        <v>-0.07481047249647421</v>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
@@ -29933,10 +29933,10 @@
         <v>8</v>
       </c>
       <c r="G393" t="n">
-        <v>0.6577275935074101</v>
+        <v>0.6572637517630465</v>
       </c>
       <c r="H393" t="n">
-        <v>5.804911785462244</v>
+        <v>5.804301833568406</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -29955,16 +29955,16 @@
         <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>1.014911785462243</v>
+        <v>1.014301833568405</v>
       </c>
       <c r="N393" t="n">
-        <v>1.014911785462243</v>
+        <v>1.014301833568405</v>
       </c>
       <c r="O393" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P393" t="n">
-        <v>-0.6606102888194654</v>
+        <v>-0.6612202407133037</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
@@ -30004,10 +30004,10 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>0.5631616090331687</v>
+        <v>0.5627644569816643</v>
       </c>
       <c r="H394" t="n">
-        <v>5.498336273817925</v>
+        <v>5.497552891396333</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -30026,16 +30026,16 @@
         <v>1</v>
       </c>
       <c r="M394" t="n">
-        <v>0.828336273817925</v>
+        <v>0.8275528913963326</v>
       </c>
       <c r="N394" t="n">
-        <v>0.828336273817925</v>
+        <v>0.8275528913963326</v>
       </c>
       <c r="O394" t="n">
         <v>-0.120000000000001</v>
       </c>
       <c r="P394" t="n">
-        <v>-0.3065755116443194</v>
+        <v>-0.3067489421720735</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -30075,10 +30075,10 @@
         <v>8</v>
       </c>
       <c r="G395" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5409026798307476</v>
       </c>
       <c r="H395" t="n">
-        <v>5.455894495412844</v>
+        <v>5.455643511988717</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -30097,16 +30097,16 @@
         <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>0.9158944954128438</v>
+        <v>0.9156435119887165</v>
       </c>
       <c r="N395" t="n">
-        <v>0.9158944954128438</v>
+        <v>0.9156435119887165</v>
       </c>
       <c r="O395" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P395" t="n">
-        <v>-0.04244177840508101</v>
+        <v>-0.04190937940761597</v>
       </c>
       <c r="Q395" t="inlineStr">
         <is>
@@ -30146,10 +30146,10 @@
         <v>8</v>
       </c>
       <c r="G396" t="n">
-        <v>0.5949188426252646</v>
+        <v>0.5944992947813822</v>
       </c>
       <c r="H396" t="n">
-        <v>5.636159139026112</v>
+        <v>5.635883286318759</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -30168,16 +30168,16 @@
         <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>1.196159139026111</v>
+        <v>1.195883286318758</v>
       </c>
       <c r="N396" t="n">
-        <v>1.196159139026111</v>
+        <v>1.195883286318758</v>
       </c>
       <c r="O396" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P396" t="n">
-        <v>0.1802646436132678</v>
+        <v>0.1802397743300421</v>
       </c>
       <c r="Q396" t="inlineStr">
         <is>
@@ -30217,10 +30217,10 @@
         <v>8</v>
       </c>
       <c r="G397" t="n">
-        <v>0.6330275229357798</v>
+        <v>0.6325811001410437</v>
       </c>
       <c r="H397" t="n">
-        <v>5.756215596330276</v>
+        <v>5.755922073342737</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -30239,16 +30239,16 @@
         <v>1</v>
       </c>
       <c r="M397" t="n">
-        <v>1.316215596330276</v>
+        <v>1.315922073342737</v>
       </c>
       <c r="N397" t="n">
-        <v>1.316215596330276</v>
+        <v>1.315922073342737</v>
       </c>
       <c r="O397" t="n">
         <v>0</v>
       </c>
       <c r="P397" t="n">
-        <v>0.1200564573041643</v>
+        <v>0.1200387870239785</v>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>8</v>
       </c>
       <c r="G398" t="n">
-        <v>0.5935074100211715</v>
+        <v>0.5930888575458392</v>
       </c>
       <c r="H398" t="n">
-        <v>5.63523112208892</v>
+        <v>5.634823695345557</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -30310,16 +30310,16 @@
         <v>1</v>
       </c>
       <c r="M398" t="n">
-        <v>1.23523112208892</v>
+        <v>1.234823695345557</v>
       </c>
       <c r="N398" t="n">
-        <v>1.23523112208892</v>
+        <v>1.234823695345557</v>
       </c>
       <c r="O398" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P398" t="n">
-        <v>-0.1209844742413555</v>
+        <v>-0.1210983779971802</v>
       </c>
       <c r="Q398" t="inlineStr">
         <is>
@@ -30359,10 +30359,10 @@
         <v>8</v>
       </c>
       <c r="G399" t="n">
-        <v>0.4777699364855328</v>
+        <v>0.4774330042313117</v>
       </c>
       <c r="H399" t="n">
-        <v>5.189133733239238</v>
+        <v>5.188912200282088</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -30381,16 +30381,16 @@
         <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>0.8091337332392383</v>
+        <v>0.8089122002820881</v>
       </c>
       <c r="N399" t="n">
-        <v>0.8091337332392383</v>
+        <v>0.8089122002820881</v>
       </c>
       <c r="O399" t="n">
         <v>-0.02000000000000046</v>
       </c>
       <c r="P399" t="n">
-        <v>-0.4460973888496822</v>
+        <v>-0.4459114950634691</v>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
@@ -30430,10 +30430,10 @@
         <v>8</v>
       </c>
       <c r="G400" t="n">
-        <v>0.3690896259703599</v>
+        <v>0.3688293370944993</v>
       </c>
       <c r="H400" t="n">
-        <v>4.842676429075512</v>
+        <v>4.842505289139633</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -30452,16 +30452,16 @@
         <v>1</v>
       </c>
       <c r="M400" t="n">
-        <v>0.7026764290755123</v>
+        <v>0.7025052891396335</v>
       </c>
       <c r="N400" t="n">
-        <v>0.7026764290755123</v>
+        <v>0.7025052891396335</v>
       </c>
       <c r="O400" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P400" t="n">
-        <v>-0.3464573041637262</v>
+        <v>-0.3464069111424548</v>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
@@ -30501,10 +30501,10 @@
         <v>8</v>
       </c>
       <c r="G401" t="n">
-        <v>0.3246294989414256</v>
+        <v>0.3244005641748942</v>
       </c>
       <c r="H401" t="n">
-        <v>4.693826746647848</v>
+        <v>4.692020451339916</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -30523,16 +30523,16 @@
         <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>0.8238267466478479</v>
+        <v>0.8220204513399159</v>
       </c>
       <c r="N401" t="n">
-        <v>0.8238267466478479</v>
+        <v>0.8220204513399159</v>
       </c>
       <c r="O401" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P401" t="n">
-        <v>-0.1488496824276639</v>
+        <v>-0.1504848377997172</v>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
@@ -30572,10 +30572,10 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>0.3507410021171489</v>
+        <v>0.3504936530324401</v>
       </c>
       <c r="H402" t="n">
-        <v>4.805612208892025</v>
+        <v>4.805449576868829</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -30594,16 +30594,16 @@
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>1.085612208892025</v>
+        <v>1.085449576868829</v>
       </c>
       <c r="N402" t="n">
-        <v>1.085612208892025</v>
+        <v>1.085449576868829</v>
       </c>
       <c r="O402" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P402" t="n">
-        <v>0.1117854622441774</v>
+        <v>0.1134291255289135</v>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -30643,10 +30643,10 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>0.5285815102328864</v>
+        <v>0.5282087447108603</v>
       </c>
       <c r="H403" t="n">
-        <v>5.440084685956245</v>
+        <v>5.439594499294781</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -30665,16 +30665,16 @@
         <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>1.740084685956245</v>
+        <v>1.739594499294781</v>
       </c>
       <c r="N403" t="n">
-        <v>1.740084685956245</v>
+        <v>1.739594499294781</v>
       </c>
       <c r="O403" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P403" t="n">
-        <v>0.6344724770642198</v>
+        <v>0.6341449224259517</v>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>8</v>
       </c>
       <c r="G404" t="n">
-        <v>0.7600564573041637</v>
+        <v>0.7595204513399154</v>
       </c>
       <c r="H404" t="n">
-        <v>6.099737120677488</v>
+        <v>6.099384696755994</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -30736,16 +30736,16 @@
         <v>1</v>
       </c>
       <c r="M404" t="n">
-        <v>2.259737120677488</v>
+        <v>2.259384696755994</v>
       </c>
       <c r="N404" t="n">
-        <v>2.259737120677488</v>
+        <v>2.259384696755994</v>
       </c>
       <c r="O404" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P404" t="n">
-        <v>0.6596524347212425</v>
+        <v>0.6597901974612128</v>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
@@ -30785,10 +30785,10 @@
         <v>8</v>
       </c>
       <c r="G405" t="n">
-        <v>0.8306280875088214</v>
+        <v>0.8300423131170663</v>
       </c>
       <c r="H405" t="n">
-        <v>6.340241707833451</v>
+        <v>6.33677538787024</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -30807,16 +30807,16 @@
         <v>1</v>
       </c>
       <c r="M405" t="n">
-        <v>2.320241707833452</v>
+        <v>2.316775387870241</v>
       </c>
       <c r="N405" t="n">
-        <v>2.320241707833452</v>
+        <v>2.316775387870241</v>
       </c>
       <c r="O405" t="n">
         <v>0.1799999999999997</v>
       </c>
       <c r="P405" t="n">
-        <v>0.2405045871559635</v>
+        <v>0.2373906911142463</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
@@ -30856,10 +30856,10 @@
         <v>8</v>
       </c>
       <c r="G406" t="n">
-        <v>0.8151023288637967</v>
+        <v>0.814527503526093</v>
       </c>
       <c r="H406" t="n">
-        <v>6.286797812279464</v>
+        <v>6.283018335684062</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -30878,16 +30878,16 @@
         <v>1</v>
       </c>
       <c r="M406" t="n">
-        <v>2.186797812279464</v>
+        <v>2.183018335684062</v>
       </c>
       <c r="N406" t="n">
-        <v>2.186797812279464</v>
+        <v>2.183018335684062</v>
       </c>
       <c r="O406" t="n">
         <v>0.08000000000000007</v>
       </c>
       <c r="P406" t="n">
-        <v>-0.0534438955539871</v>
+        <v>-0.0537570521861781</v>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
@@ -32057,10 +32057,10 @@
         <v>8</v>
       </c>
       <c r="G423" t="n">
-        <v>0.8299223712067749</v>
+        <v>0.8300423131170663</v>
       </c>
       <c r="H423" t="n">
-        <v>5.566774876499647</v>
+        <v>5.567579337094499</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -32079,16 +32079,16 @@
         <v>1</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.800725123500353</v>
+        <v>-0.7999206629055005</v>
       </c>
       <c r="N423" t="n">
-        <v>0.800725123500353</v>
+        <v>0.7999206629055005</v>
       </c>
       <c r="O423" t="n">
         <v>-0.07500000000000018</v>
       </c>
       <c r="P423" t="n">
-        <v>-1.472154696030135</v>
+        <v>-1.471350235435283</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
@@ -32128,10 +32128,10 @@
         <v>8</v>
       </c>
       <c r="G424" t="n">
-        <v>0.8278052223006351</v>
+        <v>0.8279266572637518</v>
       </c>
       <c r="H424" t="n">
-        <v>5.550846859562456</v>
+        <v>5.551889985895628</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -32150,16 +32150,16 @@
         <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>-0.7666531404375441</v>
+        <v>-0.7656100141043716</v>
       </c>
       <c r="N424" t="n">
-        <v>0.7666531404375441</v>
+        <v>0.7656100141043716</v>
       </c>
       <c r="O424" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P424" t="n">
-        <v>-0.01592801693719093</v>
+        <v>-0.01568935119887094</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -32199,10 +32199,10 @@
         <v>8</v>
       </c>
       <c r="G425" t="n">
-        <v>0.821453775582216</v>
+        <v>0.8215796897038082</v>
       </c>
       <c r="H425" t="n">
-        <v>5.506287932251236</v>
+        <v>5.507369534555713</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -32221,16 +32221,16 @@
         <v>1</v>
       </c>
       <c r="M425" t="n">
-        <v>-0.7537120677487641</v>
+        <v>-0.7526304654442866</v>
       </c>
       <c r="N425" t="n">
-        <v>0.7537120677487641</v>
+        <v>0.7526304654442866</v>
       </c>
       <c r="O425" t="n">
         <v>-0.05750000000000011</v>
       </c>
       <c r="P425" t="n">
-        <v>-0.04455892731122013</v>
+        <v>-0.04452045133991511</v>
       </c>
       <c r="Q425" t="inlineStr">
         <is>
@@ -32270,10 +32270,10 @@
         <v>8</v>
       </c>
       <c r="G426" t="n">
-        <v>0.8186309103740297</v>
+        <v>0.8187588152327221</v>
       </c>
       <c r="H426" t="n">
-        <v>5.491019760056458</v>
+        <v>5.491569111424542</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -32292,16 +32292,16 @@
         <v>1</v>
       </c>
       <c r="M426" t="n">
-        <v>-0.6389802399435416</v>
+        <v>-0.6384308885754582</v>
       </c>
       <c r="N426" t="n">
-        <v>0.6389802399435416</v>
+        <v>0.6384308885754582</v>
       </c>
       <c r="O426" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P426" t="n">
-        <v>-0.01526817219477739</v>
+        <v>-0.01580042313117147</v>
       </c>
       <c r="Q426" t="inlineStr">
         <is>
@@ -32341,10 +32341,10 @@
         <v>8</v>
       </c>
       <c r="G427" t="n">
-        <v>0.8094565984474241</v>
+        <v>0.8095909732016925</v>
       </c>
       <c r="H427" t="n">
-        <v>5.383712067748764</v>
+        <v>5.384144922425952</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -32363,16 +32363,16 @@
         <v>1</v>
       </c>
       <c r="M427" t="n">
-        <v>-0.6062879322512362</v>
+        <v>-0.6058550775740486</v>
       </c>
       <c r="N427" t="n">
-        <v>0.6062879322512362</v>
+        <v>0.6058550775740486</v>
       </c>
       <c r="O427" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P427" t="n">
-        <v>-0.1073076923076943</v>
+        <v>-0.1074241889985901</v>
       </c>
       <c r="Q427" t="inlineStr">
         <is>
@@ -32412,10 +32412,10 @@
         <v>8</v>
       </c>
       <c r="G428" t="n">
-        <v>0.7889908256880734</v>
+        <v>0.7891396332863188</v>
       </c>
       <c r="H428" t="n">
-        <v>5.229357798165138</v>
+        <v>5.22967736248237</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -32434,16 +32434,16 @@
         <v>1</v>
       </c>
       <c r="M428" t="n">
-        <v>-0.4781422018348618</v>
+        <v>-0.4778226375176295</v>
       </c>
       <c r="N428" t="n">
-        <v>0.4781422018348618</v>
+        <v>0.4778226375176295</v>
       </c>
       <c r="O428" t="n">
         <v>-0.2825000000000006</v>
       </c>
       <c r="P428" t="n">
-        <v>-0.1543542695836262</v>
+        <v>-0.1544675599435816</v>
       </c>
       <c r="Q428" t="inlineStr">
         <is>
@@ -32483,10 +32483,10 @@
         <v>8</v>
       </c>
       <c r="G429" t="n">
-        <v>0.7713479181369089</v>
+        <v>0.7715091678420311</v>
       </c>
       <c r="H429" t="n">
-        <v>5.102939308398024</v>
+        <v>5.103631875881523</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
@@ -32505,16 +32505,16 @@
         <v>1</v>
       </c>
       <c r="M429" t="n">
-        <v>-0.4570606916019759</v>
+        <v>-0.4563681241184767</v>
       </c>
       <c r="N429" t="n">
-        <v>0.4570606916019759</v>
+        <v>0.4563681241184767</v>
       </c>
       <c r="O429" t="n">
         <v>-0.1475</v>
       </c>
       <c r="P429" t="n">
-        <v>-0.1264184897671141</v>
+        <v>-0.1260454866008471</v>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
@@ -32554,10 +32554,10 @@
         <v>8</v>
       </c>
       <c r="G430" t="n">
-        <v>0.7466478475652788</v>
+        <v>0.7468265162200282</v>
       </c>
       <c r="H430" t="n">
-        <v>4.951852505292872</v>
+        <v>4.952619887165021</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -32576,16 +32576,16 @@
         <v>1</v>
       </c>
       <c r="M430" t="n">
-        <v>-0.3881474947071277</v>
+        <v>-0.387380112834979</v>
       </c>
       <c r="N430" t="n">
-        <v>0.3881474947071277</v>
+        <v>0.387380112834979</v>
       </c>
       <c r="O430" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P430" t="n">
-        <v>-0.1510868031051515</v>
+        <v>-0.151011988716502</v>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>8</v>
       </c>
       <c r="G431" t="n">
-        <v>0.7191249117854622</v>
+        <v>0.7193229901269393</v>
       </c>
       <c r="H431" t="n">
         <v>4.82</v>
@@ -32656,7 +32656,7 @@
         <v>-0.2275</v>
       </c>
       <c r="P431" t="n">
-        <v>-0.1318525052928718</v>
+        <v>-0.1326198871650206</v>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
@@ -32696,10 +32696,10 @@
         <v>8</v>
       </c>
       <c r="G432" t="n">
-        <v>0.6944248412138321</v>
+        <v>0.6946403385049366</v>
       </c>
       <c r="H432" t="n">
-        <v>4.651277346506705</v>
+        <v>4.651740126939352</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -32718,16 +32718,16 @@
         <v>1</v>
       </c>
       <c r="M432" t="n">
-        <v>-0.3587226534932952</v>
+        <v>-0.3582598730606481</v>
       </c>
       <c r="N432" t="n">
-        <v>0.3587226534932952</v>
+        <v>0.3582598730606481</v>
       </c>
       <c r="O432" t="n">
         <v>-0.1025</v>
       </c>
       <c r="P432" t="n">
-        <v>-0.1687226534932957</v>
+        <v>-0.1682598730606486</v>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
@@ -32767,10 +32767,10 @@
         <v>8</v>
       </c>
       <c r="G433" t="n">
-        <v>0.68454481298518</v>
+        <v>0.6847672778561354</v>
       </c>
       <c r="H433" t="n">
-        <v>4.621279992942837</v>
+        <v>4.621518864598025</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -32789,16 +32789,16 @@
         <v>1</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.2187200070571631</v>
+        <v>-0.2184811354019747</v>
       </c>
       <c r="N433" t="n">
-        <v>0.2187200070571631</v>
+        <v>0.2184811354019747</v>
       </c>
       <c r="O433" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P433" t="n">
-        <v>-0.02999735356386779</v>
+        <v>-0.03022126234132649</v>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
@@ -32838,10 +32838,10 @@
         <v>8</v>
       </c>
       <c r="G434" t="n">
-        <v>0.689484827099506</v>
+        <v>0.689703808180536</v>
       </c>
       <c r="H434" t="n">
-        <v>4.637558221594919</v>
+        <v>4.638185237423602</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -32860,16 +32860,16 @@
         <v>1</v>
       </c>
       <c r="M434" t="n">
-        <v>-0.08244177840508105</v>
+        <v>-0.08181476257639808</v>
       </c>
       <c r="N434" t="n">
-        <v>0.08244177840508105</v>
+        <v>0.08181476257639808</v>
       </c>
       <c r="O434" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P434" t="n">
-        <v>0.01627822865208195</v>
+        <v>0.01666637282557648</v>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
@@ -32909,10 +32909,10 @@
         <v>8</v>
       </c>
       <c r="G435" t="n">
-        <v>0.7092448835568101</v>
+        <v>0.7094499294781382</v>
       </c>
       <c r="H435" t="n">
-        <v>4.744942366501999</v>
+        <v>4.746116596144804</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -32931,16 +32931,16 @@
         <v>1</v>
       </c>
       <c r="M435" t="n">
-        <v>0.1849423665019998</v>
+        <v>0.1861165961448048</v>
       </c>
       <c r="N435" t="n">
-        <v>0.1849423665019998</v>
+        <v>0.1861165961448048</v>
       </c>
       <c r="O435" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P435" t="n">
-        <v>0.1073841449070807</v>
+        <v>0.1079313587212027</v>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
@@ -32980,10 +32980,10 @@
         <v>8</v>
       </c>
       <c r="G436" t="n">
-        <v>0.7254763585038815</v>
+        <v>0.7256699576868829</v>
       </c>
       <c r="H436" t="n">
-        <v>4.845920959774171</v>
+        <v>4.846752468265162</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -33002,16 +33002,16 @@
         <v>1</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4559209597741711</v>
+        <v>0.4567524682651625</v>
       </c>
       <c r="N436" t="n">
-        <v>0.4559209597741711</v>
+        <v>0.4567524682651625</v>
       </c>
       <c r="O436" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P436" t="n">
-        <v>0.1009785932721714</v>
+        <v>0.1006358721203577</v>
       </c>
       <c r="Q436" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>8</v>
       </c>
       <c r="G437" t="n">
-        <v>0.8235709244883557</v>
+        <v>0.8236953455571228</v>
       </c>
       <c r="H437" t="n">
-        <v>3.500707480592801</v>
+        <v>3.502387165021157</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -33073,10 +33073,10 @@
         <v>1</v>
       </c>
       <c r="M437" t="n">
-        <v>-0.939292519407199</v>
+        <v>-0.9376128349788435</v>
       </c>
       <c r="N437" t="n">
-        <v>0.939292519407199</v>
+        <v>0.9376128349788435</v>
       </c>
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
@@ -33116,10 +33116,10 @@
         <v>8</v>
       </c>
       <c r="G438" t="n">
-        <v>0.8094565984474241</v>
+        <v>0.8095909732016925</v>
       </c>
       <c r="H438" t="n">
-        <v>3.352131263232181</v>
+        <v>3.353582510578279</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -33138,16 +33138,16 @@
         <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>-0.8903687367678197</v>
+        <v>-0.8889174894217216</v>
       </c>
       <c r="N438" t="n">
-        <v>0.8903687367678197</v>
+        <v>0.8889174894217216</v>
       </c>
       <c r="O438" t="n">
         <v>-0.1974999999999998</v>
       </c>
       <c r="P438" t="n">
-        <v>-0.1485762173606204</v>
+        <v>-0.1488046544428778</v>
       </c>
       <c r="Q438" t="inlineStr">
         <is>
@@ -33187,10 +33187,10 @@
         <v>8</v>
       </c>
       <c r="G439" t="n">
-        <v>0.8002822865208187</v>
+        <v>0.8004231311706629</v>
       </c>
       <c r="H439" t="n">
-        <v>3.29576217360621</v>
+        <v>3.29614245416079</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -33209,16 +33209,16 @@
         <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>-0.8142378263937902</v>
+        <v>-0.8138575458392108</v>
       </c>
       <c r="N439" t="n">
-        <v>0.8142378263937902</v>
+        <v>0.8138575458392108</v>
       </c>
       <c r="O439" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P439" t="n">
-        <v>-0.05636908962597076</v>
+        <v>-0.0574400564174895</v>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
@@ -33258,10 +33258,10 @@
         <v>8</v>
       </c>
       <c r="G440" t="n">
-        <v>0.8045165843330981</v>
+        <v>0.8046544428772919</v>
       </c>
       <c r="H440" t="n">
-        <v>3.31877911079746</v>
+        <v>3.320200987306065</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -33280,16 +33280,16 @@
         <v>1</v>
       </c>
       <c r="M440" t="n">
-        <v>-0.65122088920254</v>
+        <v>-0.6497990126939355</v>
       </c>
       <c r="N440" t="n">
-        <v>0.65122088920254</v>
+        <v>0.6497990126939355</v>
       </c>
       <c r="O440" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P440" t="n">
-        <v>0.02301693719125009</v>
+        <v>0.02405853314527517</v>
       </c>
       <c r="Q440" t="inlineStr">
         <is>
@@ -33329,10 +33329,10 @@
         <v>8</v>
       </c>
       <c r="G441" t="n">
-        <v>0.8221594918842625</v>
+        <v>0.8222849083215797</v>
       </c>
       <c r="H441" t="n">
-        <v>3.469322512350036</v>
+        <v>3.471692524682654</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -33351,16 +33351,16 @@
         <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>-0.3606774876499643</v>
+        <v>-0.3583074753173459</v>
       </c>
       <c r="N441" t="n">
-        <v>0.3606774876499643</v>
+        <v>0.3583074753173459</v>
       </c>
       <c r="O441" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P441" t="n">
-        <v>0.1505434015525755</v>
+        <v>0.1514915373765895</v>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
@@ -33400,10 +33400,10 @@
         <v>8</v>
       </c>
       <c r="G442" t="n">
-        <v>0.8383909668313339</v>
+        <v>0.8385049365303244</v>
       </c>
       <c r="H442" t="n">
-        <v>3.649748294518937</v>
+        <v>3.65056887635167</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -33422,16 +33422,16 @@
         <v>1</v>
       </c>
       <c r="M442" t="n">
-        <v>-0.01025170548106269</v>
+        <v>-0.009431123648330431</v>
       </c>
       <c r="N442" t="n">
-        <v>0.01025170548106269</v>
+        <v>0.009431123648330431</v>
       </c>
       <c r="O442" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P442" t="n">
-        <v>0.1804257821689017</v>
+        <v>0.1788763516690155</v>
       </c>
       <c r="Q442" t="inlineStr">
         <is>
@@ -33471,10 +33471,10 @@
         <v>8</v>
       </c>
       <c r="G443" t="n">
-        <v>0.8482709950599859</v>
+        <v>0.8483779971791255</v>
       </c>
       <c r="H443" t="n">
-        <v>3.722997529992943</v>
+        <v>3.723430888575459</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -33493,16 +33493,16 @@
         <v>1</v>
       </c>
       <c r="M443" t="n">
-        <v>0.08299752999294308</v>
+        <v>0.08343088857545844</v>
       </c>
       <c r="N443" t="n">
-        <v>0.08299752999294308</v>
+        <v>0.08343088857545844</v>
       </c>
       <c r="O443" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P443" t="n">
-        <v>0.07324923547400575</v>
+        <v>0.07286201222378885</v>
       </c>
       <c r="Q443" t="inlineStr">
         <is>
@@ -33542,10 +33542,10 @@
         <v>8</v>
       </c>
       <c r="G444" t="n">
-        <v>0.8560338743824982</v>
+        <v>0.8561354019746121</v>
       </c>
       <c r="H444" t="n">
-        <v>3.75758292166549</v>
+        <v>3.758131170662905</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -33564,16 +33564,16 @@
         <v>1</v>
       </c>
       <c r="M444" t="n">
-        <v>0.1575829216654903</v>
+        <v>0.1581311706629052</v>
       </c>
       <c r="N444" t="n">
-        <v>0.1575829216654903</v>
+        <v>0.1581311706629052</v>
       </c>
       <c r="O444" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P444" t="n">
-        <v>0.03458539167254715</v>
+        <v>0.03470028208744669</v>
       </c>
       <c r="Q444" t="inlineStr">
         <is>
@@ -33613,10 +33613,10 @@
         <v>8</v>
       </c>
       <c r="G445" t="n">
-        <v>0.8588567395906845</v>
+        <v>0.8589562764456982</v>
       </c>
       <c r="H445" t="n">
-        <v>3.768913196894848</v>
+        <v>3.769181946403385</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -33635,16 +33635,16 @@
         <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>0.2364131968948482</v>
+        <v>0.2366819464033849</v>
       </c>
       <c r="N445" t="n">
-        <v>0.2364131968948482</v>
+        <v>0.2366819464033849</v>
       </c>
       <c r="O445" t="n">
         <v>-0.06749999999999989</v>
       </c>
       <c r="P445" t="n">
-        <v>0.01133027522935803</v>
+        <v>0.01105077574047986</v>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
@@ -33684,10 +33684,10 @@
         <v>8</v>
       </c>
       <c r="G446" t="n">
-        <v>0.8510938602681722</v>
+        <v>0.8511988716502116</v>
       </c>
       <c r="H446" t="n">
-        <v>3.736813690896259</v>
+        <v>3.737947813822284</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -33706,16 +33706,16 @@
         <v>1</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2968136908962595</v>
+        <v>0.2979478138222844</v>
       </c>
       <c r="N446" t="n">
-        <v>0.2968136908962595</v>
+        <v>0.2979478138222844</v>
       </c>
       <c r="O446" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P446" t="n">
-        <v>-0.03209950599858891</v>
+        <v>-0.03123413258110075</v>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
@@ -33755,10 +33755,10 @@
         <v>8</v>
       </c>
       <c r="G447" t="n">
-        <v>0.8405081157374735</v>
+        <v>0.840620592383639</v>
       </c>
       <c r="H447" t="n">
-        <v>3.673103387438249</v>
+        <v>3.675229196050776</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -33777,16 +33777,16 @@
         <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>0.3831033874382492</v>
+        <v>0.3852291960507759</v>
       </c>
       <c r="N447" t="n">
-        <v>0.3831033874382492</v>
+        <v>0.3852291960507759</v>
       </c>
       <c r="O447" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.06371030345801021</v>
+        <v>-0.06271861777150844</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
@@ -33826,10 +33826,10 @@
         <v>8</v>
       </c>
       <c r="G448" t="n">
-        <v>0.8158080451658434</v>
+        <v>0.8159379407616361</v>
       </c>
       <c r="H448" t="n">
-        <v>3.417681721947777</v>
+        <v>3.418032440056417</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -33848,16 +33848,16 @@
         <v>1</v>
       </c>
       <c r="M448" t="n">
-        <v>0.2376817219477769</v>
+        <v>0.2380324400564171</v>
       </c>
       <c r="N448" t="n">
-        <v>0.2376817219477769</v>
+        <v>0.2380324400564171</v>
       </c>
       <c r="O448" t="n">
         <v>-0.1099999999999999</v>
       </c>
       <c r="P448" t="n">
-        <v>-0.2554216654904722</v>
+        <v>-0.2571967559943587</v>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
@@ -33897,10 +33897,10 @@
         <v>8</v>
       </c>
       <c r="G449" t="n">
-        <v>0.7840508115737473</v>
+        <v>0.7842031029619182</v>
       </c>
       <c r="H449" t="n">
-        <v>3.218874382498236</v>
+        <v>3.219696755994359</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -33919,16 +33919,16 @@
         <v>1</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1188743824982361</v>
+        <v>0.1196967559943585</v>
       </c>
       <c r="N449" t="n">
-        <v>0.1188743824982361</v>
+        <v>0.1196967559943585</v>
       </c>
       <c r="O449" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P449" t="n">
-        <v>-0.1988073394495409</v>
+        <v>-0.1983356840620587</v>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
@@ -33968,10 +33968,10 @@
         <v>8</v>
       </c>
       <c r="G450" t="n">
-        <v>0.7671136203246295</v>
+        <v>0.767277856135402</v>
       </c>
       <c r="H450" t="n">
-        <v>3.111609033168666</v>
+        <v>3.112200282087447</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -33990,16 +33990,16 @@
         <v>1</v>
       </c>
       <c r="M450" t="n">
-        <v>0.01160903316866557</v>
+        <v>0.01220028208744672</v>
       </c>
       <c r="N450" t="n">
-        <v>0.01160903316866557</v>
+        <v>0.01220028208744672</v>
       </c>
       <c r="O450" t="n">
         <v>0</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.1072653493295705</v>
+        <v>-0.1074964739069117</v>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
@@ -35311,10 +35311,10 @@
         <v>8</v>
       </c>
       <c r="G469" t="n">
-        <v>0.8433309809456598</v>
+        <v>0.843441466854725</v>
       </c>
       <c r="H469" t="n">
-        <v>8.560515172900494</v>
+        <v>8.562933709449931</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -35333,16 +35333,16 @@
         <v>1</v>
       </c>
       <c r="M469" t="n">
-        <v>-0.6794848270995058</v>
+        <v>-0.6770662905500693</v>
       </c>
       <c r="N469" t="n">
-        <v>0.6794848270995058</v>
+        <v>0.6770662905500693</v>
       </c>
       <c r="O469" t="n">
         <v>-0.08999999999999986</v>
       </c>
       <c r="P469" t="n">
-        <v>0.2615453060469566</v>
+        <v>0.2639638425963931</v>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
@@ -35382,10 +35382,10 @@
         <v>8</v>
       </c>
       <c r="G470" t="n">
-        <v>0.826393789696542</v>
+        <v>0.8265162200282088</v>
       </c>
       <c r="H470" t="n">
-        <v>8.287141848976711</v>
+        <v>8.288603667136814</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -35404,16 +35404,16 @@
         <v>1</v>
       </c>
       <c r="M470" t="n">
-        <v>-0.7628581510232895</v>
+        <v>-0.7613963328631872</v>
       </c>
       <c r="N470" t="n">
-        <v>0.7628581510232895</v>
+        <v>0.7613963328631872</v>
       </c>
       <c r="O470" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P470" t="n">
-        <v>-0.2733733239237832</v>
+        <v>-0.2743300423131174</v>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -35453,10 +35453,10 @@
         <v>8</v>
       </c>
       <c r="G471" t="n">
-        <v>0.8073394495412844</v>
+        <v>0.807475317348378</v>
       </c>
       <c r="H471" t="n">
-        <v>8.009266055045874</v>
+        <v>8.012510578279267</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -35475,16 +35475,16 @@
         <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.9007339449541263</v>
+        <v>-0.8974894217207332</v>
       </c>
       <c r="N471" t="n">
-        <v>0.9007339449541263</v>
+        <v>0.8974894217207332</v>
       </c>
       <c r="O471" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P471" t="n">
-        <v>-0.2778757939308374</v>
+        <v>-0.2760930888575466</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
@@ -35524,10 +35524,10 @@
         <v>8</v>
       </c>
       <c r="G472" t="n">
-        <v>0.7953422724064926</v>
+        <v>0.7954866008462623</v>
       </c>
       <c r="H472" t="n">
-        <v>7.89819336626676</v>
+        <v>7.899055007052186</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -35546,16 +35546,16 @@
         <v>1</v>
       </c>
       <c r="M472" t="n">
-        <v>-0.8718066337332395</v>
+        <v>-0.8709449929478135</v>
       </c>
       <c r="N472" t="n">
-        <v>0.8718066337332395</v>
+        <v>0.8709449929478135</v>
       </c>
       <c r="O472" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P472" t="n">
-        <v>-0.1110726887791138</v>
+        <v>-0.1134555712270808</v>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
@@ -35595,10 +35595,10 @@
         <v>8</v>
       </c>
       <c r="G473" t="n">
-        <v>0.7932251235003529</v>
+        <v>0.7933709449929478</v>
       </c>
       <c r="H473" t="n">
-        <v>7.881107974594213</v>
+        <v>7.882849083215796</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -35617,16 +35617,16 @@
         <v>1</v>
       </c>
       <c r="M473" t="n">
-        <v>-0.6988920254057867</v>
+        <v>-0.6971509167842038</v>
       </c>
       <c r="N473" t="n">
-        <v>0.6988920254057867</v>
+        <v>0.6971509167842038</v>
       </c>
       <c r="O473" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P473" t="n">
-        <v>-0.01708539167254663</v>
+        <v>-0.01620592383638986</v>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
@@ -35666,10 +35666,10 @@
         <v>8</v>
       </c>
       <c r="G474" t="n">
-        <v>0.8038108680310515</v>
+        <v>0.8039492242595204</v>
       </c>
       <c r="H474" t="n">
-        <v>7.929583627381792</v>
+        <v>7.929858956276445</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -35688,16 +35688,16 @@
         <v>1</v>
       </c>
       <c r="M474" t="n">
-        <v>-0.5204163726182074</v>
+        <v>-0.5201410437235543</v>
       </c>
       <c r="N474" t="n">
-        <v>0.5204163726182074</v>
+        <v>0.5201410437235543</v>
       </c>
       <c r="O474" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P474" t="n">
-        <v>0.04847565278757848</v>
+        <v>0.04700987306064874</v>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
@@ -35737,10 +35737,10 @@
         <v>8</v>
       </c>
       <c r="G475" t="n">
-        <v>0.8165137614678899</v>
+        <v>0.8166431593794076</v>
       </c>
       <c r="H475" t="n">
-        <v>8.1948623853211</v>
+        <v>8.195119887165021</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -35759,16 +35759,16 @@
         <v>1</v>
       </c>
       <c r="M475" t="n">
-        <v>-0.1251376146789003</v>
+        <v>-0.1248801128349797</v>
       </c>
       <c r="N475" t="n">
-        <v>0.1251376146789003</v>
+        <v>0.1248801128349797</v>
       </c>
       <c r="O475" t="n">
         <v>-0.129999999999999</v>
       </c>
       <c r="P475" t="n">
-        <v>0.2652787579393081</v>
+        <v>0.2652609308885756</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
@@ -35808,10 +35808,10 @@
         <v>8</v>
       </c>
       <c r="G476" t="n">
-        <v>0.8285109386026818</v>
+        <v>0.8286318758815233</v>
       </c>
       <c r="H476" t="n">
-        <v>8.312420606916021</v>
+        <v>8.313864598025388</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -35830,16 +35830,16 @@
         <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>0.05242060691602113</v>
+        <v>0.05386459802538823</v>
       </c>
       <c r="N476" t="n">
-        <v>0.05242060691602113</v>
+        <v>0.05386459802538823</v>
       </c>
       <c r="O476" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P476" t="n">
-        <v>0.1175582215949209</v>
+        <v>0.1187447108603674</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
@@ -35879,10 +35879,10 @@
         <v>8</v>
       </c>
       <c r="G477" t="n">
-        <v>0.8369795342272407</v>
+        <v>0.8370944992947814</v>
       </c>
       <c r="H477" t="n">
-        <v>8.461178546224419</v>
+        <v>8.461636107193231</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -35901,16 +35901,16 @@
         <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2611785462244196</v>
+        <v>0.2616361071932314</v>
       </c>
       <c r="N477" t="n">
-        <v>0.2611785462244196</v>
+        <v>0.2616361071932314</v>
       </c>
       <c r="O477" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P477" t="n">
-        <v>0.148757939308398</v>
+        <v>0.1477715091678427</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -35950,10 +35950,10 @@
         <v>8</v>
       </c>
       <c r="G478" t="n">
-        <v>0.8376852505292872</v>
+        <v>0.8377997179125529</v>
       </c>
       <c r="H478" t="n">
-        <v>8.463987297106563</v>
+        <v>8.464442877291962</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -35972,16 +35972,16 @@
         <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>0.4139872971065621</v>
+        <v>0.4144428772919611</v>
       </c>
       <c r="N478" t="n">
-        <v>0.4139872971065621</v>
+        <v>0.4144428772919611</v>
       </c>
       <c r="O478" t="n">
         <v>-0.1499999999999986</v>
       </c>
       <c r="P478" t="n">
-        <v>0.00280875088214394</v>
+        <v>0.002806770098731093</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -36021,10 +36021,10 @@
         <v>8</v>
       </c>
       <c r="G479" t="n">
-        <v>0.8327452364149612</v>
+        <v>0.8328631875881524</v>
       </c>
       <c r="H479" t="n">
-        <v>8.413119266055046</v>
+        <v>8.416170662905502</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -36043,16 +36043,16 @@
         <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>0.4931192660550465</v>
+        <v>0.4961706629055023</v>
       </c>
       <c r="N479" t="n">
-        <v>0.4931192660550465</v>
+        <v>0.4961706629055023</v>
       </c>
       <c r="O479" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P479" t="n">
-        <v>-0.05086803105151638</v>
+        <v>-0.04827221438645957</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -36061,11 +36061,11 @@
       </c>
       <c r="R479" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S479" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480">
@@ -36092,10 +36092,10 @@
         <v>8</v>
       </c>
       <c r="G480" t="n">
-        <v>0.8200423429781228</v>
+        <v>0.8201692524682651</v>
       </c>
       <c r="H480" t="n">
-        <v>8.211305575158786</v>
+        <v>8.212820874471085</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -36114,16 +36114,16 @@
         <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0.4713055751587856</v>
+        <v>0.4728208744710845</v>
       </c>
       <c r="N480" t="n">
-        <v>0.4713055751587856</v>
+        <v>0.4728208744710845</v>
       </c>
       <c r="O480" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P480" t="n">
-        <v>-0.2018136908962607</v>
+        <v>-0.2033497884344175</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -36266,34 +36266,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.66</v>
+        <v>7.612</v>
       </c>
       <c r="G2" t="n">
-        <v>7.798</v>
+        <v>7.767</v>
       </c>
       <c r="H2" t="n">
-        <v>7.896</v>
+        <v>7.879</v>
       </c>
       <c r="I2" t="n">
-        <v>7.896</v>
+        <v>7.879</v>
       </c>
       <c r="J2" t="n">
-        <v>7.682</v>
+        <v>7.63</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.214</v>
+        <v>-0.249</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>30</v>
       </c>
       <c r="O2" t="n">
-        <v>5.831</v>
+        <v>5.832</v>
       </c>
       <c r="P2" t="n">
         <v>5.812</v>
@@ -36342,34 +36342,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.583</v>
+        <v>5.528</v>
       </c>
       <c r="G3" t="n">
-        <v>5.608</v>
+        <v>5.592</v>
       </c>
       <c r="H3" t="n">
-        <v>5.641</v>
+        <v>5.637</v>
       </c>
       <c r="I3" t="n">
-        <v>5.641</v>
+        <v>5.637</v>
       </c>
       <c r="J3" t="n">
-        <v>5.591</v>
+        <v>5.528</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.05</v>
+        <v>-0.108</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -36385,16 +36385,16 @@
         <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>0.492</v>
+        <v>0.493</v>
       </c>
       <c r="P3" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -36418,34 +36418,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.122</v>
+        <v>3.856</v>
       </c>
       <c r="G4" t="n">
-        <v>4.365</v>
+        <v>4.371</v>
       </c>
       <c r="H4" t="n">
-        <v>4.496</v>
+        <v>4.577</v>
       </c>
       <c r="I4" t="n">
-        <v>4.495</v>
+        <v>4.425</v>
       </c>
       <c r="J4" t="n">
-        <v>4.237</v>
+        <v>4.111</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.258</v>
+        <v>-0.314</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>0.291</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.042</v>
+        <v>-0.043</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -36494,34 +36494,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.728</v>
+        <v>11.8</v>
       </c>
       <c r="G5" t="n">
-        <v>11.989</v>
+        <v>12.037</v>
       </c>
       <c r="H5" t="n">
         <v>12.233</v>
       </c>
       <c r="I5" t="n">
-        <v>11.728</v>
+        <v>11.8</v>
       </c>
       <c r="J5" t="n">
-        <v>12.226</v>
+        <v>12.203</v>
       </c>
       <c r="K5" t="n">
-        <v>0.499</v>
+        <v>0.403</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -36540,13 +36540,13 @@
         <v>4.213</v>
       </c>
       <c r="P5" t="n">
-        <v>3.917</v>
+        <v>3.916</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.917</v>
+        <v>3.916</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.728</v>
+        <v>-1.727</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -36570,34 +36570,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>54.763</v>
+        <v>54.575</v>
       </c>
       <c r="G6" t="n">
-        <v>96.43300000000001</v>
+        <v>101.092</v>
       </c>
       <c r="H6" t="n">
-        <v>111.045</v>
+        <v>108.892</v>
       </c>
       <c r="I6" t="n">
-        <v>65.869</v>
+        <v>87.554</v>
       </c>
       <c r="J6" t="n">
-        <v>82.024</v>
+        <v>94.515</v>
       </c>
       <c r="K6" t="n">
-        <v>16.155</v>
+        <v>6.961</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -36613,13 +36613,13 @@
         <v>13</v>
       </c>
       <c r="O6" t="n">
-        <v>92.02</v>
+        <v>92.021</v>
       </c>
       <c r="P6" t="n">
-        <v>88.691</v>
+        <v>88.69199999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>88.691</v>
+        <v>88.69199999999999</v>
       </c>
       <c r="R6" t="n">
         <v>-3.322</v>
@@ -36646,34 +36646,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.719</v>
+        <v>7.718</v>
       </c>
       <c r="G7" t="n">
-        <v>7.912</v>
+        <v>7.928</v>
       </c>
       <c r="H7" t="n">
-        <v>8.176</v>
+        <v>8.186</v>
       </c>
       <c r="I7" t="n">
-        <v>8.018000000000001</v>
+        <v>7.859</v>
       </c>
       <c r="J7" t="n">
-        <v>8.175000000000001</v>
+        <v>8.186</v>
       </c>
       <c r="K7" t="n">
-        <v>0.157</v>
+        <v>0.328</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -36722,38 +36722,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.125</v>
+        <v>6.122</v>
       </c>
       <c r="G8" t="n">
-        <v>6.501</v>
+        <v>6.493</v>
       </c>
       <c r="H8" t="n">
-        <v>7.056</v>
+        <v>7.057</v>
       </c>
       <c r="I8" t="n">
-        <v>7.056</v>
+        <v>6.855</v>
       </c>
       <c r="J8" t="n">
-        <v>6.86</v>
+        <v>7.057</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.196</v>
+        <v>0.202</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Descendente</t>
+          <t>Ascendente</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -36798,34 +36798,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.02</v>
+        <v>4.908</v>
       </c>
       <c r="G9" t="n">
-        <v>5.134</v>
+        <v>5.057</v>
       </c>
       <c r="H9" t="n">
-        <v>5.433</v>
+        <v>5.279</v>
       </c>
       <c r="I9" t="n">
-        <v>5.433</v>
+        <v>5.279</v>
       </c>
       <c r="J9" t="n">
-        <v>5.106</v>
+        <v>4.991</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.327</v>
+        <v>-0.288</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -36844,13 +36844,13 @@
         <v>0.512</v>
       </c>
       <c r="P9" t="n">
-        <v>0.423</v>
+        <v>0.422</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.259</v>
+        <v>0.258</v>
       </c>
       <c r="R9" t="n">
-        <v>0.221</v>
+        <v>0.222</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -36874,34 +36874,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.134</v>
+        <v>5.088</v>
       </c>
       <c r="G10" t="n">
-        <v>5.328</v>
+        <v>5.297</v>
       </c>
       <c r="H10" t="n">
-        <v>5.438</v>
+        <v>5.439</v>
       </c>
       <c r="I10" t="n">
-        <v>5.386</v>
+        <v>5.42</v>
       </c>
       <c r="J10" t="n">
-        <v>5.135</v>
+        <v>5.089</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.251</v>
+        <v>-0.331</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -36920,10 +36920,10 @@
         <v>1.821</v>
       </c>
       <c r="P10" t="n">
-        <v>1.787</v>
+        <v>1.786</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.787</v>
+        <v>-1.786</v>
       </c>
       <c r="R10" t="n">
         <v>0.758</v>
@@ -36950,34 +36950,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.426</v>
+        <v>2.68</v>
       </c>
       <c r="G11" t="n">
-        <v>5.217</v>
+        <v>4.452</v>
       </c>
       <c r="H11" t="n">
-        <v>6.502</v>
+        <v>5.606</v>
       </c>
       <c r="I11" t="n">
-        <v>5.905</v>
+        <v>5.599</v>
       </c>
       <c r="J11" t="n">
-        <v>4.062</v>
+        <v>3.294</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.843</v>
+        <v>-2.305</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -36996,13 +36996,13 @@
         <v>2.519</v>
       </c>
       <c r="P11" t="n">
-        <v>2.034</v>
+        <v>2.033</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.034</v>
+        <v>2.033</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.554</v>
+        <v>-0.555</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -37026,34 +37026,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.861</v>
+        <v>5.834</v>
       </c>
       <c r="G12" t="n">
-        <v>5.965</v>
+        <v>5.938</v>
       </c>
       <c r="H12" t="n">
-        <v>6.054</v>
+        <v>6.037</v>
       </c>
       <c r="I12" t="n">
-        <v>6.054</v>
+        <v>6.037</v>
       </c>
       <c r="J12" t="n">
-        <v>5.861</v>
+        <v>5.835</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.193</v>
+        <v>-0.202</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -37069,16 +37069,16 @@
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>0.482</v>
+        <v>0.481</v>
       </c>
       <c r="P12" t="n">
         <v>0.37</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.238</v>
+        <v>-0.237</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -37102,34 +37102,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.577999999999999</v>
+        <v>9.548999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>9.715999999999999</v>
+        <v>9.712</v>
       </c>
       <c r="H13" t="n">
-        <v>9.859999999999999</v>
+        <v>9.834</v>
       </c>
       <c r="I13" t="n">
-        <v>9.859999999999999</v>
+        <v>9.834</v>
       </c>
       <c r="J13" t="n">
-        <v>9.615</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.245</v>
+        <v>-0.204</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -37178,34 +37178,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.434</v>
+        <v>5.443</v>
       </c>
       <c r="G14" t="n">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="H14" t="n">
-        <v>5.914</v>
+        <v>5.916</v>
       </c>
       <c r="I14" t="n">
-        <v>5.83</v>
+        <v>5.892</v>
       </c>
       <c r="J14" t="n">
-        <v>5.458</v>
+        <v>5.463</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.371</v>
+        <v>-0.429</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -37227,10 +37227,10 @@
         <v>0.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="R14" t="n">
-        <v>0.737</v>
+        <v>0.736</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -37254,34 +37254,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.56</v>
+        <v>6.538</v>
       </c>
       <c r="G15" t="n">
-        <v>6.574</v>
+        <v>6.565</v>
       </c>
       <c r="H15" t="n">
-        <v>6.584</v>
+        <v>6.581</v>
       </c>
       <c r="I15" t="n">
-        <v>6.584</v>
+        <v>6.581</v>
       </c>
       <c r="J15" t="n">
-        <v>6.564</v>
+        <v>6.539</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.02</v>
+        <v>-0.043</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -37297,16 +37297,16 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>1.625</v>
+        <v>1.624</v>
       </c>
       <c r="P15" t="n">
-        <v>1.504</v>
+        <v>1.503</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.504</v>
+        <v>-1.503</v>
       </c>
       <c r="R15" t="n">
-        <v>0.281</v>
+        <v>0.28</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -37330,34 +37330,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.435</v>
+        <v>3.549</v>
       </c>
       <c r="G16" t="n">
-        <v>5.919</v>
+        <v>5.271</v>
       </c>
       <c r="H16" t="n">
-        <v>6.963</v>
+        <v>6.15</v>
       </c>
       <c r="I16" t="n">
-        <v>6.375</v>
+        <v>6.11</v>
       </c>
       <c r="J16" t="n">
-        <v>4.803</v>
+        <v>4.255</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.572</v>
+        <v>-1.855</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -37376,10 +37376,10 @@
         <v>1.725</v>
       </c>
       <c r="P16" t="n">
-        <v>1.537</v>
+        <v>1.536</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.537</v>
+        <v>1.536</v>
       </c>
       <c r="R16" t="n">
         <v>0.229</v>
@@ -37406,34 +37406,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.696</v>
+        <v>3.538</v>
       </c>
       <c r="G17" t="n">
-        <v>4.103</v>
+        <v>4.037</v>
       </c>
       <c r="H17" t="n">
-        <v>4.478</v>
+        <v>4.424</v>
       </c>
       <c r="I17" t="n">
-        <v>4.478</v>
+        <v>4.424</v>
       </c>
       <c r="J17" t="n">
-        <v>3.807</v>
+        <v>3.554</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.671</v>
+        <v>-0.871</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>0.404</v>
       </c>
       <c r="P17" t="n">
-        <v>0.338</v>
+        <v>0.337</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.074</v>
@@ -37482,34 +37482,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.383</v>
+        <v>2.364</v>
       </c>
       <c r="G18" t="n">
-        <v>2.514</v>
+        <v>2.486</v>
       </c>
       <c r="H18" t="n">
-        <v>2.592</v>
+        <v>2.565</v>
       </c>
       <c r="I18" t="n">
-        <v>2.592</v>
+        <v>2.563</v>
       </c>
       <c r="J18" t="n">
-        <v>2.385</v>
+        <v>2.365</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.207</v>
+        <v>-0.199</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>0.371</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.153</v>
+        <v>-0.152</v>
       </c>
       <c r="R18" t="n">
         <v>-0.106</v>
@@ -37558,34 +37558,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.58</v>
+        <v>5.498</v>
       </c>
       <c r="G19" t="n">
-        <v>5.813</v>
+        <v>5.751</v>
       </c>
       <c r="H19" t="n">
-        <v>5.899</v>
+        <v>5.87</v>
       </c>
       <c r="I19" t="n">
-        <v>5.899</v>
+        <v>5.87</v>
       </c>
       <c r="J19" t="n">
-        <v>5.635</v>
+        <v>5.532</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.265</v>
+        <v>-0.338</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -37607,10 +37607,10 @@
         <v>0.777</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.665</v>
+        <v>-0.664</v>
       </c>
       <c r="R19" t="n">
-        <v>0.504</v>
+        <v>0.503</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>

--- a/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
+++ b/outputs/validacion_dwlt_hasta_observado_disponible.xlsx
@@ -486,7 +486,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>300060</v>
+        <v>300078</v>
       </c>
       <c r="E2" t="n">
         <v>151106</v>
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -683,13 +683,13 @@
         <v>9.765000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>7.76</v>
+        <v>7.761</v>
       </c>
       <c r="J2" t="n">
         <v>-1.52</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.005</v>
+        <v>-2.004</v>
       </c>
       <c r="L2" t="n">
         <v>0.397</v>
@@ -698,13 +698,13 @@
         <v>0.398</v>
       </c>
       <c r="N2" t="n">
-        <v>0.478</v>
+        <v>0.479</v>
       </c>
       <c r="O2" t="n">
-        <v>0.865</v>
+        <v>0.864</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="Q2" t="n">
         <v>0.829</v>
@@ -765,13 +765,13 @@
         <v>7.883</v>
       </c>
       <c r="I3" t="n">
-        <v>5.835</v>
+        <v>5.837</v>
       </c>
       <c r="J3" t="n">
         <v>-2.472</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.048</v>
+        <v>-2.046</v>
       </c>
       <c r="L3" t="n">
         <v>-1.786</v>
@@ -780,13 +780,13 @@
         <v>1.786</v>
       </c>
       <c r="N3" t="n">
-        <v>1.821</v>
+        <v>1.82</v>
       </c>
       <c r="O3" t="n">
         <v>0.89</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.595</v>
+        <v>-4.594</v>
       </c>
       <c r="Q3" t="n">
         <v>0.758</v>
@@ -847,13 +847,13 @@
         <v>7.691</v>
       </c>
       <c r="I4" t="n">
-        <v>4.847</v>
+        <v>4.848</v>
       </c>
       <c r="J4" t="n">
         <v>-3.405</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.844</v>
+        <v>-2.843</v>
       </c>
       <c r="L4" t="n">
         <v>-0.074</v>
@@ -871,7 +871,7 @@
         <v>0.835</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.835</v>
+        <v>0.836</v>
       </c>
       <c r="R4" t="n">
         <v>44.828</v>
@@ -950,7 +950,7 @@
         <v>0.931</v>
       </c>
       <c r="P5" t="n">
-        <v>0.553</v>
+        <v>0.552</v>
       </c>
       <c r="Q5" t="n">
         <v>0.5659999999999999</v>
@@ -1011,19 +1011,19 @@
         <v>8.468</v>
       </c>
       <c r="I6" t="n">
-        <v>6.236</v>
+        <v>6.237</v>
       </c>
       <c r="J6" t="n">
         <v>-2.07</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.232</v>
+        <v>-2.231</v>
       </c>
       <c r="L6" t="n">
         <v>0.111</v>
       </c>
       <c r="M6" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="N6" t="n">
         <v>0.415</v>
@@ -1093,16 +1093,16 @@
         <v>9.374000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>8.212999999999999</v>
+        <v>8.214</v>
       </c>
       <c r="J7" t="n">
         <v>-2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.161</v>
+        <v>-1.16</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.664</v>
+        <v>-0.663</v>
       </c>
       <c r="M7" t="n">
         <v>0.777</v>
@@ -1114,10 +1114,10 @@
         <v>0.708</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.352</v>
+        <v>-0.351</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.503</v>
+        <v>0.502</v>
       </c>
       <c r="R7" t="n">
         <v>17.241</v>
@@ -1175,19 +1175,19 @@
         <v>9.863</v>
       </c>
       <c r="I8" t="n">
-        <v>7.941</v>
+        <v>7.942</v>
       </c>
       <c r="J8" t="n">
         <v>-2.008</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.922</v>
+        <v>-1.92</v>
       </c>
       <c r="L8" t="n">
-        <v>5.812</v>
+        <v>5.813</v>
       </c>
       <c r="M8" t="n">
-        <v>5.812</v>
+        <v>5.813</v>
       </c>
       <c r="N8" t="n">
         <v>5.832</v>
@@ -1196,7 +1196,7 @@
         <v>0.831</v>
       </c>
       <c r="P8" t="n">
-        <v>-45.951</v>
+        <v>-45.956</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.024</v>
@@ -1339,13 +1339,13 @@
         <v>11.017</v>
       </c>
       <c r="I10" t="n">
-        <v>11.472</v>
+        <v>11.455</v>
       </c>
       <c r="J10" t="n">
         <v>-1.39</v>
       </c>
       <c r="K10" t="n">
-        <v>0.455</v>
+        <v>0.438</v>
       </c>
       <c r="L10" t="n">
         <v>3.916</v>
@@ -1354,16 +1354,16 @@
         <v>3.916</v>
       </c>
       <c r="N10" t="n">
-        <v>4.213</v>
+        <v>4.212</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.49</v>
+        <v>-0.489</v>
       </c>
       <c r="P10" t="n">
-        <v>-105.501</v>
+        <v>-105.469</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.727</v>
+        <v>-1.726</v>
       </c>
       <c r="R10" t="n">
         <v>44.828</v>
@@ -1418,31 +1418,31 @@
         <v>5.32</v>
       </c>
       <c r="H11" t="n">
-        <v>112.895</v>
+        <v>112.897</v>
       </c>
       <c r="I11" t="n">
-        <v>108.419</v>
+        <v>108.422</v>
       </c>
       <c r="J11" t="n">
         <v>-1.68</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.477</v>
+        <v>-4.475</v>
       </c>
       <c r="L11" t="n">
-        <v>88.69199999999999</v>
+        <v>88.694</v>
       </c>
       <c r="M11" t="n">
-        <v>88.69199999999999</v>
+        <v>88.694</v>
       </c>
       <c r="N11" t="n">
-        <v>92.021</v>
+        <v>92.02200000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.358</v>
+        <v>-0.357</v>
       </c>
       <c r="P11" t="n">
-        <v>-13.684</v>
+        <v>-13.685</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.322</v>
@@ -1585,13 +1585,13 @@
         <v>5.956</v>
       </c>
       <c r="I13" t="n">
-        <v>5.112</v>
+        <v>5.107</v>
       </c>
       <c r="J13" t="n">
         <v>-0.6919999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.844</v>
+        <v>-0.848</v>
       </c>
       <c r="L13" t="n">
         <v>0.258</v>
@@ -1609,7 +1609,7 @@
         <v>-0.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.222</v>
+        <v>0.223</v>
       </c>
       <c r="R13" t="n">
         <v>17.241</v>
@@ -1667,19 +1667,19 @@
         <v>7.097</v>
       </c>
       <c r="I14" t="n">
-        <v>5.198</v>
+        <v>5.193</v>
       </c>
       <c r="J14" t="n">
         <v>-2.422</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.899</v>
+        <v>-1.904</v>
       </c>
       <c r="L14" t="n">
-        <v>2.033</v>
+        <v>2.032</v>
       </c>
       <c r="M14" t="n">
-        <v>2.033</v>
+        <v>2.032</v>
       </c>
       <c r="N14" t="n">
         <v>2.519</v>
@@ -1688,7 +1688,7 @@
         <v>0.616</v>
       </c>
       <c r="P14" t="n">
-        <v>-10.081</v>
+        <v>-10.077</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.555</v>
@@ -1749,19 +1749,19 @@
         <v>8.144</v>
       </c>
       <c r="I15" t="n">
-        <v>6.361</v>
+        <v>6.363</v>
       </c>
       <c r="J15" t="n">
         <v>-1.525</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.782</v>
+        <v>-1.781</v>
       </c>
       <c r="L15" t="n">
         <v>-0.237</v>
       </c>
       <c r="M15" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="N15" t="n">
         <v>0.481</v>
@@ -1770,10 +1770,10 @@
         <v>0.8159999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.191</v>
+        <v>-0.189</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.401</v>
+        <v>0.402</v>
       </c>
       <c r="R15" t="n">
         <v>44.828</v>
@@ -1913,13 +1913,13 @@
         <v>8.029999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>6.687</v>
+        <v>6.689</v>
       </c>
       <c r="J17" t="n">
         <v>-2.425</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.343</v>
+        <v>-1.341</v>
       </c>
       <c r="L17" t="n">
         <v>-1.503</v>
@@ -1931,13 +1931,13 @@
         <v>1.624</v>
       </c>
       <c r="O17" t="n">
-        <v>0.598</v>
+        <v>0.597</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.674</v>
+        <v>-3.673</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.28</v>
+        <v>0.279</v>
       </c>
       <c r="R17" t="n">
         <v>31.034</v>
@@ -1995,13 +1995,13 @@
         <v>7.154</v>
       </c>
       <c r="I18" t="n">
-        <v>6.283</v>
+        <v>6.284</v>
       </c>
       <c r="J18" t="n">
         <v>-1.55</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.871</v>
+        <v>-0.87</v>
       </c>
       <c r="L18" t="n">
         <v>1.536</v>
@@ -2016,7 +2016,7 @@
         <v>0.611</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.614</v>
+        <v>-6.613</v>
       </c>
       <c r="Q18" t="n">
         <v>0.229</v>
@@ -2074,34 +2074,34 @@
         <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>3.502</v>
+        <v>3.504</v>
       </c>
       <c r="I19" t="n">
-        <v>3.112</v>
+        <v>3.113</v>
       </c>
       <c r="J19" t="n">
         <v>-1.34</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.39</v>
+        <v>-0.391</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.152</v>
+        <v>-0.151</v>
       </c>
       <c r="M19" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="N19" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="O19" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.403</v>
+        <v>-0.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.106</v>
+        <v>-0.105</v>
       </c>
       <c r="R19" t="n">
         <v>46.154</v>
@@ -3392,10 +3392,10 @@
         <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8540197461212976</v>
+        <v>0.854122621564482</v>
       </c>
       <c r="H18" t="n">
-        <v>8.172242595204514</v>
+        <v>8.172568710359409</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>5.717242595204514</v>
+        <v>5.717568710359409</v>
       </c>
       <c r="N18" t="n">
-        <v>5.717242595204514</v>
+        <v>5.717568710359409</v>
       </c>
       <c r="O18" t="n">
         <v>-0.1374999999999997</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7277854356294036</v>
+        <v>-0.7274593204745088</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8511988716502116</v>
+        <v>0.8513037350246653</v>
       </c>
       <c r="H19" t="n">
-        <v>8.158725317348377</v>
+        <v>8.158974630021142</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -3485,16 +3485,16 @@
         <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.746225317348378</v>
+        <v>5.746474630021142</v>
       </c>
       <c r="N19" t="n">
-        <v>5.746225317348378</v>
+        <v>5.746474630021142</v>
       </c>
       <c r="O19" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.01351727785613654</v>
+        <v>-0.01359408033826703</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
         <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8469675599435825</v>
+        <v>0.8470754052149401</v>
       </c>
       <c r="H20" t="n">
-        <v>8.137217912552893</v>
+        <v>8.138187103594081</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -3556,16 +3556,16 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>5.737217912552893</v>
+        <v>5.738187103594081</v>
       </c>
       <c r="N20" t="n">
-        <v>5.737217912552893</v>
+        <v>5.738187103594081</v>
       </c>
       <c r="O20" t="n">
         <v>-0.01250000000000018</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.02150740479548396</v>
+        <v>-0.0207875264270605</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8441466854724965</v>
+        <v>0.8442565186751233</v>
       </c>
       <c r="H21" t="n">
-        <v>8.120944992947813</v>
+        <v>8.121293164200141</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3627,16 +3627,16 @@
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>5.950944992947813</v>
+        <v>5.951293164200141</v>
       </c>
       <c r="N21" t="n">
-        <v>5.950944992947813</v>
+        <v>5.951293164200141</v>
       </c>
       <c r="O21" t="n">
         <v>-0.23</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.01627291960508082</v>
+        <v>-0.01689393939394002</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8392101551480959</v>
+        <v>0.8393234672304439</v>
       </c>
       <c r="H22" t="n">
-        <v>8.100592383638928</v>
+        <v>8.101310782241015</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3698,16 +3698,16 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>6.120592383638927</v>
+        <v>6.121310782241014</v>
       </c>
       <c r="N22" t="n">
-        <v>6.120592383638927</v>
+        <v>6.121310782241014</v>
       </c>
       <c r="O22" t="n">
         <v>-0.1899999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.02035260930888505</v>
+        <v>-0.01998238195912627</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8342736248236954</v>
+        <v>0.8343904157857647</v>
       </c>
       <c r="H23" t="n">
-        <v>8.068589562764457</v>
+        <v>8.070035236081749</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3769,16 +3769,16 @@
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>6.018589562764457</v>
+        <v>6.020035236081749</v>
       </c>
       <c r="N23" t="n">
-        <v>6.018589562764457</v>
+        <v>6.020035236081749</v>
       </c>
       <c r="O23" t="n">
         <v>0.06999999999999984</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.03200282087447093</v>
+        <v>-0.0312755461592662</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8279266572637518</v>
+        <v>0.8280479210711769</v>
       </c>
       <c r="H24" t="n">
         <v>8.030000000000001</v>
@@ -3849,7 +3849,7 @@
         <v>0.1700000000000004</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.03858956276445547</v>
+        <v>-0.04003523608174753</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8229901269393513</v>
+        <v>0.8231148696264975</v>
       </c>
       <c r="H25" t="n">
-        <v>8.014439351198872</v>
+        <v>8.014637068357999</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3911,16 +3911,16 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>5.664439351198872</v>
+        <v>5.664637068357999</v>
       </c>
       <c r="N25" t="n">
-        <v>5.664439351198872</v>
+        <v>5.664637068357999</v>
       </c>
       <c r="O25" t="n">
         <v>0.1299999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01556064880112906</v>
+        <v>-0.01536293164200231</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3960,10 +3960,10 @@
         <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8201692524682651</v>
+        <v>0.8202959830866807</v>
       </c>
       <c r="H26" t="n">
-        <v>8.004904795486601</v>
+        <v>8.005507399577166</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3982,16 +3982,16 @@
         <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>5.704904795486601</v>
+        <v>5.705507399577166</v>
       </c>
       <c r="N26" t="n">
-        <v>5.704904795486601</v>
+        <v>5.705507399577166</v>
       </c>
       <c r="O26" t="n">
         <v>-0.05000000000000027</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.009534555712271242</v>
+        <v>-0.0091296687808331</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8166431593794076</v>
+        <v>0.8167723749119098</v>
       </c>
       <c r="H27" t="n">
-        <v>7.983155853314527</v>
+        <v>7.984589499647639</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -4053,16 +4053,16 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>5.753155853314528</v>
+        <v>5.75458949964764</v>
       </c>
       <c r="N27" t="n">
-        <v>5.753155853314528</v>
+        <v>5.75458949964764</v>
       </c>
       <c r="O27" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.02174894217207335</v>
+        <v>-0.02091789992952631</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -4102,10 +4102,10 @@
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8124118476727785</v>
+        <v>0.8125440451021846</v>
       </c>
       <c r="H28" t="n">
-        <v>7.95086389280677</v>
+        <v>7.951911557434813</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>5.89086389280677</v>
+        <v>5.891911557434813</v>
       </c>
       <c r="N28" t="n">
-        <v>5.89086389280677</v>
+        <v>5.891911557434813</v>
       </c>
       <c r="O28" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.03229196050775762</v>
+        <v>-0.03267794221282649</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.81311706629055</v>
+        <v>0.8132487667371389</v>
       </c>
       <c r="H29" t="n">
-        <v>7.956452750352608</v>
+        <v>7.957496476391825</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4195,16 +4195,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>6.006452750352608</v>
+        <v>6.007496476391824</v>
       </c>
       <c r="N29" t="n">
-        <v>6.006452750352608</v>
+        <v>6.007496476391824</v>
       </c>
       <c r="O29" t="n">
         <v>-0.1100000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>0.005588857545838266</v>
+        <v>0.005584918957011631</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8138222849083215</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="H30" t="n">
-        <v>7.962041607898446</v>
+        <v>7.962848837209301</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4266,16 +4266,16 @@
         <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.262041607898446</v>
+        <v>5.262848837209301</v>
       </c>
       <c r="N30" t="n">
-        <v>5.262041607898446</v>
+        <v>5.262848837209301</v>
       </c>
       <c r="O30" t="n">
         <v>0.7500000000000002</v>
       </c>
       <c r="P30" t="n">
-        <v>0.005588857545838266</v>
+        <v>0.005352360817476587</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>0.810296191819464</v>
+        <v>0.8104298801973221</v>
       </c>
       <c r="H31" t="n">
-        <v>7.940916784203103</v>
+        <v>7.942188160676534</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4337,16 +4337,16 @@
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.140916784203103</v>
+        <v>5.142188160676534</v>
       </c>
       <c r="N31" t="n">
-        <v>5.140916784203103</v>
+        <v>5.142188160676534</v>
       </c>
       <c r="O31" t="n">
         <v>0.09999999999999964</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.02112482369534341</v>
+        <v>-0.02066067653276704</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6502115655853314</v>
+        <v>0.6504580690627202</v>
       </c>
       <c r="H48" t="n">
-        <v>6.159643423836389</v>
+        <v>6.159737711416491</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -5538,16 +5538,16 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1278565761636106</v>
+        <v>-0.1277622885835088</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1278565761636106</v>
+        <v>0.1277622885835088</v>
       </c>
       <c r="O48" t="n">
         <v>-0.09250000000000114</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.6242458543696374</v>
+        <v>-0.6241515667895357</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6438645980253879</v>
+        <v>0.6441155743481325</v>
       </c>
       <c r="H49" t="n">
-        <v>6.150677009873061</v>
+        <v>6.152980972515857</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -5609,16 +5609,16 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.01932299012693939</v>
+        <v>-0.0170190274841433</v>
       </c>
       <c r="N49" t="n">
-        <v>0.01932299012693939</v>
+        <v>0.0170190274841433</v>
       </c>
       <c r="O49" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.008966413963328534</v>
+        <v>-0.006756738900634218</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -5658,10 +5658,10 @@
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>0.6361071932299013</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="H50" t="n">
-        <v>6.127190409026799</v>
+        <v>6.127818181818182</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -5680,16 +5680,16 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.03719040902679893</v>
+        <v>0.03781818181818242</v>
       </c>
       <c r="N50" t="n">
-        <v>0.03719040902679893</v>
+        <v>0.03781818181818242</v>
       </c>
       <c r="O50" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.02348660084626175</v>
+        <v>-0.02516279069767435</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -5729,10 +5729,10 @@
         <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6346967559943583</v>
+        <v>0.634954193093728</v>
       </c>
       <c r="H51" t="n">
-        <v>6.123737658674189</v>
+        <v>6.124367864693446</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -5751,16 +5751,16 @@
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.2637376586741889</v>
+        <v>0.2643678646934458</v>
       </c>
       <c r="N51" t="n">
-        <v>0.2637376586741889</v>
+        <v>0.2643678646934458</v>
       </c>
       <c r="O51" t="n">
         <v>-0.2299999999999995</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.003452750352609613</v>
+        <v>-0.003450317124736202</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>0.6459802538787024</v>
+        <v>0.6462297392529951</v>
       </c>
       <c r="H52" t="n">
-        <v>6.158024947108604</v>
+        <v>6.158120375264271</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -5822,16 +5822,16 @@
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.498024947108604</v>
+        <v>0.4981203752642713</v>
       </c>
       <c r="N52" t="n">
-        <v>0.498024947108604</v>
+        <v>0.4981203752642713</v>
       </c>
       <c r="O52" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P52" t="n">
-        <v>0.03428728843441498</v>
+        <v>0.0337525105708254</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>0.653737658674189</v>
+        <v>0.6539816772374912</v>
       </c>
       <c r="H53" t="n">
-        <v>6.170874471086036</v>
+        <v>6.172367864693446</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -5893,16 +5893,16 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5408744710860365</v>
+        <v>0.5423678646934462</v>
       </c>
       <c r="N53" t="n">
-        <v>0.5408744710860365</v>
+        <v>0.5423678646934462</v>
       </c>
       <c r="O53" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P53" t="n">
-        <v>0.01284952397743222</v>
+        <v>0.01424748942917464</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6636107193229901</v>
+        <v>0.6638477801268499</v>
       </c>
       <c r="H54" t="n">
-        <v>6.210324400564175</v>
+        <v>6.21068710359408</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -5964,16 +5964,16 @@
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6203244005641748</v>
+        <v>0.6206871035940802</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6203244005641748</v>
+        <v>0.6206871035940802</v>
       </c>
       <c r="O54" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P54" t="n">
-        <v>0.0394499294781383</v>
+        <v>0.03831923890063393</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.6699576868829337</v>
+        <v>0.6701902748414377</v>
       </c>
       <c r="H55" t="n">
-        <v>6.220070521861777</v>
+        <v>6.220782241014799</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6035,16 +6035,16 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7700705218617765</v>
+        <v>0.7707822410147989</v>
       </c>
       <c r="N55" t="n">
-        <v>0.7700705218617765</v>
+        <v>0.7707822410147989</v>
       </c>
       <c r="O55" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P55" t="n">
-        <v>0.009746121297601995</v>
+        <v>0.01009513742071899</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6664315937940761</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H56" t="n">
-        <v>6.214640338504936</v>
+        <v>6.215</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6106,16 +6106,16 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8146403385049359</v>
+        <v>0.8149999999999995</v>
       </c>
       <c r="N56" t="n">
-        <v>0.8146403385049359</v>
+        <v>0.8149999999999995</v>
       </c>
       <c r="O56" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.005430183356840423</v>
+        <v>-0.005782241014799183</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
         <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>0.655148095909732</v>
+        <v>0.6553911205073996</v>
       </c>
       <c r="H57" t="n">
-        <v>6.17950634696756</v>
+        <v>6.180993657505285</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8095063469675594</v>
+        <v>0.8109936575052847</v>
       </c>
       <c r="N57" t="n">
-        <v>0.8095063469675594</v>
+        <v>0.8109936575052847</v>
       </c>
       <c r="O57" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.03513399153737673</v>
+        <v>-0.03400634249471501</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -6226,10 +6226,10 @@
         <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6396332863187588</v>
+        <v>0.6398872445384073</v>
       </c>
       <c r="H58" t="n">
-        <v>6.138185237423601</v>
+        <v>6.138703312191684</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6248,16 +6248,16 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8081852374236007</v>
+        <v>0.8087033121916836</v>
       </c>
       <c r="N58" t="n">
-        <v>0.8081852374236007</v>
+        <v>0.8087033121916836</v>
       </c>
       <c r="O58" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.04132110954395873</v>
+        <v>-0.04229034531360121</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -6297,10 +6297,10 @@
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6212976022566996</v>
+        <v>0.6215644820295984</v>
       </c>
       <c r="H59" t="n">
-        <v>6.082341325811002</v>
+        <v>6.083974630021141</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -6319,16 +6319,16 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0.9323413258110014</v>
+        <v>0.9339746300211411</v>
       </c>
       <c r="N59" t="n">
-        <v>0.9323413258110014</v>
+        <v>0.9339746300211411</v>
       </c>
       <c r="O59" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.05584391161259905</v>
+        <v>-0.05472868217054216</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6071932299012694</v>
+        <v>0.6074700493305144</v>
       </c>
       <c r="H60" t="n">
-        <v>6.036022566995769</v>
+        <v>6.037716701902749</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -6390,16 +6390,16 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1.06602256699577</v>
+        <v>1.067716701902749</v>
       </c>
       <c r="N60" t="n">
-        <v>1.06602256699577</v>
+        <v>1.067716701902749</v>
       </c>
       <c r="O60" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.04631875881523229</v>
+        <v>-0.04625792811839258</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -6439,10 +6439,10 @@
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5923836389280677</v>
+        <v>0.5926708949964764</v>
       </c>
       <c r="H61" t="n">
-        <v>5.977596967559943</v>
+        <v>5.978036469344609</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -6461,16 +6461,16 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1.147596967559943</v>
+        <v>1.148036469344609</v>
       </c>
       <c r="N61" t="n">
-        <v>1.147596967559943</v>
+        <v>1.148036469344609</v>
       </c>
       <c r="O61" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.05842559943582604</v>
+        <v>-0.05968023255814003</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -7640,10 +7640,10 @@
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8977433004231312</v>
+        <v>0.897815362931642</v>
       </c>
       <c r="H78" t="n">
-        <v>5.882221438645981</v>
+        <v>5.8832681465821</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -7662,16 +7662,16 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1.194721438645981</v>
+        <v>1.1957681465821</v>
       </c>
       <c r="N78" t="n">
-        <v>1.194721438645981</v>
+        <v>1.1957681465821</v>
       </c>
       <c r="O78" t="n">
         <v>0.2725</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.05960406941288365</v>
+        <v>-0.05855736147676449</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8688293370944993</v>
+        <v>0.86892177589852</v>
       </c>
       <c r="H79" t="n">
-        <v>5.695796897038083</v>
+        <v>5.696871035940803</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -7733,16 +7733,16 @@
         <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>1.283296897038083</v>
+        <v>1.284371035940803</v>
       </c>
       <c r="N79" t="n">
-        <v>1.283296897038083</v>
+        <v>1.284371035940803</v>
       </c>
       <c r="O79" t="n">
         <v>-0.2750000000000004</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.1864245416078987</v>
+        <v>-0.1863971106412974</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8265162200282088</v>
+        <v>0.8266384778012685</v>
       </c>
       <c r="H80" t="n">
-        <v>5.417059238363893</v>
+        <v>5.41776955602537</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7804,16 +7804,16 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>0.7670592383638928</v>
+        <v>0.7677695560253692</v>
       </c>
       <c r="N80" t="n">
-        <v>0.7670592383638928</v>
+        <v>0.7677695560253692</v>
       </c>
       <c r="O80" t="n">
         <v>0.2375000000000007</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.2787376586741894</v>
+        <v>-0.2791014799154334</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
         <v>8</v>
       </c>
       <c r="G81" t="n">
-        <v>0.7799717912552891</v>
+        <v>0.7801268498942917</v>
       </c>
       <c r="H81" t="n">
-        <v>5.155818053596614</v>
+        <v>5.156268498942917</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -7875,16 +7875,16 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>0.4558180535966141</v>
+        <v>0.4562684989429169</v>
       </c>
       <c r="N81" t="n">
-        <v>0.4558180535966141</v>
+        <v>0.4562684989429169</v>
       </c>
       <c r="O81" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.2612411847672789</v>
+        <v>-0.2615010570824525</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>0.734132581100141</v>
+        <v>0.7343199436222692</v>
       </c>
       <c r="H82" t="n">
-        <v>5.000465444287729</v>
+        <v>5.002098308668076</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -7946,16 +7946,16 @@
         <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5954654442877292</v>
+        <v>0.5970983086680768</v>
       </c>
       <c r="N82" t="n">
-        <v>0.5954654442877292</v>
+        <v>0.5970983086680768</v>
       </c>
       <c r="O82" t="n">
         <v>-0.2950000000000008</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.1553526093088857</v>
+        <v>-0.1541701902748409</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -7995,10 +7995,10 @@
         <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7080394922425952</v>
+        <v>0.7082452431289641</v>
       </c>
       <c r="H83" t="n">
-        <v>4.873709449929478</v>
+        <v>4.874904862579282</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -8017,16 +8017,16 @@
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>0.7762094499294792</v>
+        <v>0.7774048625792824</v>
       </c>
       <c r="N83" t="n">
-        <v>0.7762094499294792</v>
+        <v>0.7774048625792824</v>
       </c>
       <c r="O83" t="n">
         <v>-0.3075000000000001</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.1267559943582501</v>
+        <v>-0.1271934460887945</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -8066,10 +8066,10 @@
         <v>8</v>
       </c>
       <c r="G84" t="n">
-        <v>0.6763046544428772</v>
+        <v>0.6765327695560254</v>
       </c>
       <c r="H84" t="n">
-        <v>4.78695144066089</v>
+        <v>4.787330111748717</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -8088,16 +8088,16 @@
         <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>0.9369514406608901</v>
+        <v>0.9373301117487167</v>
       </c>
       <c r="N84" t="n">
-        <v>0.9369514406608901</v>
+        <v>0.9373301117487167</v>
       </c>
       <c r="O84" t="n">
         <v>-0.2474999999999992</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.08675800926858823</v>
+        <v>-0.08757475083056487</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6417489421720733</v>
+        <v>0.6420014094432699</v>
       </c>
       <c r="H85" t="n">
-        <v>4.688926892336625</v>
+        <v>4.6891713648109</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -8159,16 +8159,16 @@
         <v>1</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9089268923366247</v>
+        <v>0.9091713648108999</v>
       </c>
       <c r="N85" t="n">
-        <v>0.9089268923366247</v>
+        <v>0.9091713648108999</v>
       </c>
       <c r="O85" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.09802454832426566</v>
+        <v>-0.09815874693781712</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6036671368124118</v>
+        <v>0.6039464411557435</v>
       </c>
       <c r="H86" t="n">
-        <v>4.547306064880112</v>
+        <v>4.54892882311487</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -8230,16 +8230,16 @@
         <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.2526939351198889</v>
+        <v>-0.251071176885131</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2526939351198889</v>
+        <v>0.251071176885131</v>
       </c>
       <c r="O86" t="n">
         <v>1.020000000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.1416208274565127</v>
+        <v>-0.14024254169603</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -8279,10 +8279,10 @@
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>0.5959097320169252</v>
+        <v>0.5961945031712473</v>
       </c>
       <c r="H87" t="n">
-        <v>4.516117771509167</v>
+        <v>4.516945031712473</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -8301,16 +8301,16 @@
         <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.183882228490833</v>
+        <v>-0.1830549682875269</v>
       </c>
       <c r="N87" t="n">
-        <v>0.183882228490833</v>
+        <v>0.1830549682875269</v>
       </c>
       <c r="O87" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.03118829337094464</v>
+        <v>-0.03198379140239638</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -8350,10 +8350,10 @@
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>0.614950634696756</v>
+        <v>0.6152219873150105</v>
       </c>
       <c r="H88" t="n">
-        <v>4.575242125058769</v>
+        <v>4.576293164200141</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -8372,16 +8372,16 @@
         <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.6247578749412313</v>
+        <v>-0.623706835799859</v>
       </c>
       <c r="N88" t="n">
-        <v>0.6247578749412313</v>
+        <v>0.623706835799859</v>
       </c>
       <c r="O88" t="n">
         <v>0.5</v>
       </c>
       <c r="P88" t="n">
-        <v>0.05912435354960177</v>
+        <v>0.0593481324876679</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -8421,10 +8421,10 @@
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>0.659379407616361</v>
+        <v>0.6596194503171248</v>
       </c>
       <c r="H89" t="n">
-        <v>4.725994358251057</v>
+        <v>4.727389006342495</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -8443,16 +8443,16 @@
         <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.7740056417489427</v>
+        <v>-0.772610993657505</v>
       </c>
       <c r="N89" t="n">
-        <v>0.7740056417489427</v>
+        <v>0.772610993657505</v>
       </c>
       <c r="O89" t="n">
         <v>0.2999999999999998</v>
       </c>
       <c r="P89" t="n">
-        <v>0.1507522331922884</v>
+        <v>0.1510958421423538</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -8492,10 +8492,10 @@
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6826516220028209</v>
+        <v>0.6828752642706131</v>
       </c>
       <c r="H90" t="n">
-        <v>4.796551480959097</v>
+        <v>4.796876321353065</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -8514,16 +8514,16 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>-1.083448519040902</v>
+        <v>-1.083123678646935</v>
       </c>
       <c r="N90" t="n">
-        <v>1.083448519040902</v>
+        <v>1.083123678646935</v>
       </c>
       <c r="O90" t="n">
         <v>0.3799999999999999</v>
       </c>
       <c r="P90" t="n">
-        <v>0.07055712270804015</v>
+        <v>0.06948731501057015</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>0.685472496473907</v>
+        <v>0.6856941508104298</v>
       </c>
       <c r="H91" t="n">
         <v>4.800000000000001</v>
@@ -8594,7 +8594,7 @@
         <v>-0.8600000000000003</v>
       </c>
       <c r="P91" t="n">
-        <v>0.003448519040903264</v>
+        <v>0.003123678646935524</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -9764,10 +9764,10 @@
         <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8913963328631875</v>
+        <v>0.8914728682170543</v>
       </c>
       <c r="H108" t="n">
-        <v>12.38367418899859</v>
+        <v>12.38383720930233</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -9786,16 +9786,16 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>5.313674188998591</v>
+        <v>5.313837209302327</v>
       </c>
       <c r="N108" t="n">
-        <v>5.313674188998591</v>
+        <v>5.313837209302327</v>
       </c>
       <c r="O108" t="n">
         <v>-0.1250000000000009</v>
       </c>
       <c r="P108" t="n">
-        <v>4.414094651507352</v>
+        <v>4.414257671811088</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -9835,10 +9835,10 @@
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>0.8871650211565585</v>
+        <v>0.8872445384073291</v>
       </c>
       <c r="H109" t="n">
-        <v>12.34627644569816</v>
+        <v>12.34813953488372</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -9857,16 +9857,16 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>5.476276445698164</v>
+        <v>5.478139534883719</v>
       </c>
       <c r="N109" t="n">
-        <v>5.476276445698164</v>
+        <v>5.478139534883719</v>
       </c>
       <c r="O109" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.037397743300426</v>
+        <v>-0.03569767441860705</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -9906,10 +9906,10 @@
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>0.885049365303244</v>
+        <v>0.8851303735024665</v>
       </c>
       <c r="H110" t="n">
-        <v>12.29436177715092</v>
+        <v>12.29643234672304</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -9928,16 +9928,16 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>5.554361777150916</v>
+        <v>5.556432346723044</v>
       </c>
       <c r="N110" t="n">
-        <v>5.554361777150916</v>
+        <v>5.556432346723044</v>
       </c>
       <c r="O110" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.0519146685472478</v>
+        <v>-0.05170718816067499</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -9977,10 +9977,10 @@
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>0.8829337094499294</v>
+        <v>0.883016208597604</v>
       </c>
       <c r="H111" t="n">
-        <v>12.27944640338505</v>
+        <v>12.27997357293869</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -9999,16 +9999,16 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>5.67944640338505</v>
+        <v>5.679973572938691</v>
       </c>
       <c r="N111" t="n">
-        <v>5.67944640338505</v>
+        <v>5.679973572938691</v>
       </c>
       <c r="O111" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P111" t="n">
-        <v>-0.01491537376586649</v>
+        <v>-0.01645877378435401</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -10048,10 +10048,10 @@
         <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8765867418899859</v>
+        <v>0.8766737138830162</v>
       </c>
       <c r="H112" t="n">
-        <v>12.22425952045134</v>
+        <v>12.22463002114165</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10070,16 +10070,16 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>5.36425952045134</v>
+        <v>5.364630021141649</v>
       </c>
       <c r="N112" t="n">
-        <v>5.36425952045134</v>
+        <v>5.364630021141649</v>
       </c>
       <c r="O112" t="n">
         <v>0.2600000000000007</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.05518688293370921</v>
+        <v>-0.05534355179704065</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>0.8681241184767278</v>
+        <v>0.8682170542635659</v>
       </c>
       <c r="H113" t="n">
-        <v>12.19160437235543</v>
+        <v>12.1918023255814</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -10141,16 +10141,16 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>5.21160437235543</v>
+        <v>5.211802325581395</v>
       </c>
       <c r="N113" t="n">
-        <v>5.21160437235543</v>
+        <v>5.211802325581395</v>
       </c>
       <c r="O113" t="n">
         <v>0.1200000000000001</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.03265514809591075</v>
+        <v>-0.032827695560254</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -10190,10 +10190,10 @@
         <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8575458392101551</v>
+        <v>0.857646229739253</v>
       </c>
       <c r="H114" t="n">
-        <v>12.12443582510578</v>
+        <v>12.12571881606765</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -10212,16 +10212,16 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>5.274435825105783</v>
+        <v>5.275718816067654</v>
       </c>
       <c r="N114" t="n">
-        <v>5.274435825105783</v>
+        <v>5.275718816067654</v>
       </c>
       <c r="O114" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P114" t="n">
-        <v>-0.06716854724964705</v>
+        <v>-0.0660835095137422</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
         <v>8</v>
       </c>
       <c r="G115" t="n">
-        <v>0.8469675599435825</v>
+        <v>0.8470754052149401</v>
       </c>
       <c r="H115" t="n">
-        <v>12.07808180535966</v>
+        <v>12.07854122621564</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -10283,16 +10283,16 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>5.338081805359661</v>
+        <v>5.338541226215645</v>
       </c>
       <c r="N115" t="n">
-        <v>5.338081805359661</v>
+        <v>5.338541226215645</v>
       </c>
       <c r="O115" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.04635401974612208</v>
+        <v>-0.04717758985200859</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -10332,10 +10332,10 @@
         <v>8</v>
       </c>
       <c r="G116" t="n">
-        <v>0.8251057827926658</v>
+        <v>0.8252290345313601</v>
       </c>
       <c r="H116" t="n">
-        <v>11.86495063469676</v>
+        <v>11.86547568710359</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -10354,16 +10354,16 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>5.259950634696756</v>
+        <v>5.260475687103593</v>
       </c>
       <c r="N116" t="n">
-        <v>5.259950634696756</v>
+        <v>5.260475687103593</v>
       </c>
       <c r="O116" t="n">
         <v>-0.1349999999999998</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.2131311706629049</v>
+        <v>-0.2130655391120513</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10403,10 +10403,10 @@
         <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>0.810296191819464</v>
+        <v>0.8104298801973221</v>
       </c>
       <c r="H117" t="n">
-        <v>11.81093088857546</v>
+        <v>11.8112156448203</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -10425,16 +10425,16 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>5.430930888575459</v>
+        <v>5.431215644820296</v>
       </c>
       <c r="N117" t="n">
-        <v>5.430930888575459</v>
+        <v>5.431215644820296</v>
       </c>
       <c r="O117" t="n">
         <v>-0.2250000000000005</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.05401974612129656</v>
+        <v>-0.05426004228329795</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10474,10 +10474,10 @@
         <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7954866008462623</v>
+        <v>0.7949260042283298</v>
       </c>
       <c r="H118" t="n">
-        <v>11.72438645980254</v>
+        <v>11.72319238900634</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -10496,16 +10496,16 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>5.484386459802538</v>
+        <v>5.483192389006343</v>
       </c>
       <c r="N118" t="n">
-        <v>5.484386459802538</v>
+        <v>5.483192389006343</v>
       </c>
       <c r="O118" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.08654442877292112</v>
+        <v>-0.08802325581395287</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -10545,10 +10545,10 @@
         <v>8</v>
       </c>
       <c r="G119" t="n">
-        <v>0.7820874471086037</v>
+        <v>0.7815362931642001</v>
       </c>
       <c r="H119" t="n">
-        <v>11.66003878702398</v>
+        <v>11.65717230443975</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -10567,16 +10567,16 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>5.540038787023978</v>
+        <v>5.537172304439747</v>
       </c>
       <c r="N119" t="n">
-        <v>5.540038787023978</v>
+        <v>5.537172304439747</v>
       </c>
       <c r="O119" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.06434767277855968</v>
+        <v>-0.06602008456659547</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -10616,10 +10616,10 @@
         <v>8</v>
       </c>
       <c r="G120" t="n">
-        <v>0.7679830747531735</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="H120" t="n">
-        <v>11.55580394922426</v>
+        <v>11.55447674418605</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10638,16 +10638,16 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>5.485803949224259</v>
+        <v>5.484476744186047</v>
       </c>
       <c r="N120" t="n">
-        <v>5.485803949224259</v>
+        <v>5.484476744186047</v>
       </c>
       <c r="O120" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.1042348377997193</v>
+        <v>-0.1026955602537001</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         <v>8</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7588152327221439</v>
+        <v>0.7582804792107117</v>
       </c>
       <c r="H121" t="n">
-        <v>11.4716466854725</v>
+        <v>11.45456131078224</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -10709,16 +10709,16 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.441646685472498</v>
+        <v>5.424561310782242</v>
       </c>
       <c r="N121" t="n">
-        <v>5.441646685472498</v>
+        <v>5.424561310782242</v>
       </c>
       <c r="O121" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.08415726375176114</v>
+        <v>-0.0999154334038046</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -10758,10 +10758,10 @@
         <v>8</v>
       </c>
       <c r="G122" t="n">
-        <v>0.9598025387870239</v>
+        <v>0.959830866807611</v>
       </c>
       <c r="H122" t="n">
-        <v>112.895437235543</v>
+        <v>112.8971247357294</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -10780,10 +10780,10 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>105.895437235543</v>
+        <v>105.8971247357294</v>
       </c>
       <c r="N122" t="n">
-        <v>105.895437235543</v>
+        <v>105.8971247357294</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         <v>8</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9358251057827927</v>
+        <v>0.9358703312191684</v>
       </c>
       <c r="H123" t="n">
-        <v>112.4638716502116</v>
+        <v>112.4642565186751</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -10845,16 +10845,16 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>105.6538716502116</v>
+        <v>105.6542565186751</v>
       </c>
       <c r="N123" t="n">
-        <v>105.6538716502116</v>
+        <v>105.6542565186751</v>
       </c>
       <c r="O123" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.4315655853314553</v>
+        <v>-0.4328682170542635</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -10894,10 +10894,10 @@
         <v>8</v>
       </c>
       <c r="G124" t="n">
-        <v>0.918194640338505</v>
+        <v>0.9182522903453136</v>
       </c>
       <c r="H124" t="n">
-        <v>112.1438363892807</v>
+        <v>112.1443269908386</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -10916,16 +10916,16 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>105.5338363892807</v>
+        <v>105.5343269908386</v>
       </c>
       <c r="N124" t="n">
-        <v>105.5338363892807</v>
+        <v>105.5343269908386</v>
       </c>
       <c r="O124" t="n">
         <v>-0.1999999999999993</v>
       </c>
       <c r="P124" t="n">
-        <v>-0.3200352609308794</v>
+        <v>-0.3199295278364929</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -10965,10 +10965,10 @@
         <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>0.9012693935119888</v>
+        <v>0.9013389711064129</v>
       </c>
       <c r="H125" t="n">
-        <v>111.9999012693935</v>
+        <v>112.0003946441156</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -10987,16 +10987,16 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>105.5799012693935</v>
+        <v>105.5803946441156</v>
       </c>
       <c r="N125" t="n">
-        <v>105.5799012693935</v>
+        <v>105.5803946441156</v>
       </c>
       <c r="O125" t="n">
         <v>-0.1900000000000004</v>
       </c>
       <c r="P125" t="n">
-        <v>-0.1439351198871606</v>
+        <v>-0.143932346723048</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -11036,10 +11036,10 @@
         <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>0.8582510578279267</v>
+        <v>0.8583509513742071</v>
       </c>
       <c r="H126" t="n">
-        <v>111.6805747531735</v>
+        <v>111.6818498942917</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -11058,16 +11058,16 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>105.4505747531735</v>
+        <v>105.4518498942917</v>
       </c>
       <c r="N126" t="n">
-        <v>105.4505747531735</v>
+        <v>105.4518498942917</v>
       </c>
       <c r="O126" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.3193265162200447</v>
+        <v>-0.318544749823829</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -11107,10 +11107,10 @@
         <v>8</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8124118476727785</v>
+        <v>0.8125440451021846</v>
       </c>
       <c r="H127" t="n">
-        <v>111.4345416078985</v>
+        <v>111.4349166079399</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -11129,16 +11129,16 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>105.3745416078985</v>
+        <v>105.3749166079399</v>
       </c>
       <c r="N127" t="n">
-        <v>105.3745416078985</v>
+        <v>105.3749166079399</v>
       </c>
       <c r="O127" t="n">
         <v>-0.1700000000000008</v>
       </c>
       <c r="P127" t="n">
-        <v>-0.2460331452750211</v>
+        <v>-0.2469332863518758</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -11178,10 +11178,10 @@
         <v>8</v>
       </c>
       <c r="G128" t="n">
-        <v>0.7538787023977433</v>
+        <v>0.7540521494009866</v>
       </c>
       <c r="H128" t="n">
-        <v>111.171101551481</v>
+        <v>111.1713967582805</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -11200,16 +11200,16 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>105.241101551481</v>
+        <v>105.2413967582805</v>
       </c>
       <c r="N128" t="n">
-        <v>105.241101551481</v>
+        <v>105.2413967582805</v>
       </c>
       <c r="O128" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.2634400564174939</v>
+        <v>-0.2635198496593887</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -11249,10 +11249,10 @@
         <v>8</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6763046544428772</v>
+        <v>0.6765327695560254</v>
       </c>
       <c r="H129" t="n">
-        <v>110.7730289139633</v>
+        <v>110.7759408033827</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -11271,16 +11271,16 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>52.40802891396333</v>
+        <v>52.41094080338267</v>
       </c>
       <c r="N129" t="n">
-        <v>52.40802891396333</v>
+        <v>52.41094080338267</v>
       </c>
       <c r="O129" t="n">
         <v>52.435</v>
       </c>
       <c r="P129" t="n">
-        <v>-0.3980726375176289</v>
+        <v>-0.3954559548978125</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -11320,10 +11320,10 @@
         <v>8</v>
       </c>
       <c r="G130" t="n">
-        <v>0.5987306064880112</v>
+        <v>0.5990133897110641</v>
       </c>
       <c r="H130" t="n">
-        <v>110.3775987306065</v>
+        <v>110.3788019732206</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -11342,16 +11342,16 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>52.08259873060648</v>
+        <v>52.08380197322057</v>
       </c>
       <c r="N130" t="n">
-        <v>52.08259873060648</v>
+        <v>52.08380197322057</v>
       </c>
       <c r="O130" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.3954301833568508</v>
+        <v>-0.3971388301620919</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         <v>8</v>
       </c>
       <c r="G131" t="n">
-        <v>0.5183356840620592</v>
+        <v>0.5186751233262861</v>
       </c>
       <c r="H131" t="n">
-        <v>109.9733110014104</v>
+        <v>109.974177589852</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -11413,16 +11413,16 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>51.78831100141043</v>
+        <v>51.789177589852</v>
       </c>
       <c r="N131" t="n">
-        <v>51.78831100141043</v>
+        <v>51.789177589852</v>
       </c>
       <c r="O131" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.4042877291960423</v>
+        <v>-0.4046243833685708</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -11462,10 +11462,10 @@
         <v>8</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4337094499294781</v>
+        <v>0.4341085271317829</v>
       </c>
       <c r="H132" t="n">
-        <v>109.4608674188999</v>
+        <v>109.4642635658915</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -11484,16 +11484,16 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>51.41586741889985</v>
+        <v>51.41926356589147</v>
       </c>
       <c r="N132" t="n">
-        <v>51.41586741889985</v>
+        <v>51.41926356589147</v>
       </c>
       <c r="O132" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.5124435825105849</v>
+        <v>-0.5099140239605333</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -11533,10 +11533,10 @@
         <v>8</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3533145275035261</v>
+        <v>0.3537702607470049</v>
       </c>
       <c r="H133" t="n">
-        <v>108.9183533145275</v>
+        <v>108.920584918957</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -11555,16 +11555,16 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>103.4783533145275</v>
+        <v>103.480584918957</v>
       </c>
       <c r="N133" t="n">
-        <v>103.4783533145275</v>
+        <v>103.480584918957</v>
       </c>
       <c r="O133" t="n">
         <v>-52.605</v>
       </c>
       <c r="P133" t="n">
-        <v>-0.5425141043723443</v>
+        <v>-0.5436786469344526</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -11604,10 +11604,10 @@
         <v>8</v>
       </c>
       <c r="G134" t="n">
-        <v>0.270098730606488</v>
+        <v>0.2706131078224102</v>
       </c>
       <c r="H134" t="n">
-        <v>108.4185401974612</v>
+        <v>108.4219450317125</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -11626,16 +11626,16 @@
         <v>1</v>
       </c>
       <c r="M134" t="n">
-        <v>103.0985401974612</v>
+        <v>103.1019450317125</v>
       </c>
       <c r="N134" t="n">
-        <v>103.0985401974612</v>
+        <v>103.1019450317125</v>
       </c>
       <c r="O134" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P134" t="n">
-        <v>-0.4998131170662958</v>
+        <v>-0.4986398872445506</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
         <v>8</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9315937940761636</v>
+        <v>0.9316420014094433</v>
       </c>
       <c r="H154" t="n">
-        <v>9.032179125528915</v>
+        <v>9.032248062015505</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -13034,16 +13034,16 @@
         <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>0.5721791255289137</v>
+        <v>0.5722480620155039</v>
       </c>
       <c r="N154" t="n">
-        <v>0.5721791255289137</v>
+        <v>0.5722480620155039</v>
       </c>
       <c r="O154" t="n">
         <v>0.005000000000000782</v>
       </c>
       <c r="P154" t="n">
-        <v>0.5831698403151808</v>
+        <v>0.5832387768017711</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>8</v>
       </c>
       <c r="G155" t="n">
-        <v>0.9217207334273625</v>
+        <v>0.9217758985200846</v>
       </c>
       <c r="H155" t="n">
         <v>9.009999999999998</v>
@@ -13114,7 +13114,7 @@
         <v>-0.03000000000000114</v>
       </c>
       <c r="P155" t="n">
-        <v>-0.02217912552891654</v>
+        <v>-0.02224806201550678</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -13154,10 +13154,10 @@
         <v>8</v>
       </c>
       <c r="G156" t="n">
-        <v>0.9146685472496474</v>
+        <v>0.9147286821705426</v>
       </c>
       <c r="H156" t="n">
-        <v>8.967976022566997</v>
+        <v>8.968062015503877</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -13176,16 +13176,16 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0.5579760225669972</v>
+        <v>0.5580620155038769</v>
       </c>
       <c r="N156" t="n">
-        <v>0.5579760225669972</v>
+        <v>0.5580620155038769</v>
       </c>
       <c r="O156" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P156" t="n">
-        <v>-0.04202397743300068</v>
+        <v>-0.04193798449612096</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -13225,10 +13225,10 @@
         <v>8</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9055007052186178</v>
+        <v>0.9055673009161381</v>
       </c>
       <c r="H157" t="n">
-        <v>8.922232016925248</v>
+        <v>8.922422480620156</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -13247,16 +13247,16 @@
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>0.6222320169252473</v>
+        <v>0.6224224806201555</v>
       </c>
       <c r="N157" t="n">
-        <v>0.6222320169252473</v>
+        <v>0.6224224806201555</v>
       </c>
       <c r="O157" t="n">
         <v>-0.1099999999999994</v>
       </c>
       <c r="P157" t="n">
-        <v>-0.0457440056417493</v>
+        <v>-0.04563953488372086</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>8</v>
       </c>
       <c r="G158" t="n">
-        <v>0.8956276445698167</v>
+        <v>0.8957011980267794</v>
       </c>
       <c r="H158" t="n">
-        <v>8.85824753173484</v>
+        <v>8.858352713178295</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -13318,16 +13318,16 @@
         <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>0.6882475317348398</v>
+        <v>0.6883527131782952</v>
       </c>
       <c r="N158" t="n">
-        <v>0.6882475317348398</v>
+        <v>0.6883527131782952</v>
       </c>
       <c r="O158" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P158" t="n">
-        <v>-0.06398448519040834</v>
+        <v>-0.0640697674418611</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -13367,10 +13367,10 @@
         <v>8</v>
       </c>
       <c r="G159" t="n">
-        <v>0.889280677009873</v>
+        <v>0.8893587033121917</v>
       </c>
       <c r="H159" t="n">
-        <v>8.794199576868829</v>
+        <v>8.794980620155039</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -13389,16 +13389,16 @@
         <v>1</v>
       </c>
       <c r="M159" t="n">
-        <v>0.8441995768688288</v>
+        <v>0.8449806201550389</v>
       </c>
       <c r="N159" t="n">
-        <v>0.8441995768688288</v>
+        <v>0.8449806201550389</v>
       </c>
       <c r="O159" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P159" t="n">
-        <v>-0.06404795486601067</v>
+        <v>-0.06337209302325597</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -13438,10 +13438,10 @@
         <v>8</v>
       </c>
       <c r="G160" t="n">
-        <v>0.8660084626234132</v>
+        <v>0.8661028893587033</v>
       </c>
       <c r="H160" t="n">
-        <v>8.436244710860366</v>
+        <v>8.43718992248062</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -13460,16 +13460,16 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>0.6662447108603669</v>
+        <v>0.6671899224806204</v>
       </c>
       <c r="N160" t="n">
-        <v>0.6662447108603669</v>
+        <v>0.6671899224806204</v>
       </c>
       <c r="O160" t="n">
         <v>-0.1800000000000006</v>
       </c>
       <c r="P160" t="n">
-        <v>-0.3579548660084626</v>
+        <v>-0.3577906976744192</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -13509,10 +13509,10 @@
         <v>8</v>
       </c>
       <c r="G161" t="n">
-        <v>0.8589562764456982</v>
+        <v>0.8590556730091614</v>
       </c>
       <c r="H161" t="n">
-        <v>8.250916784203103</v>
+        <v>8.255038759689924</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -13531,16 +13531,16 @@
         <v>1</v>
       </c>
       <c r="M161" t="n">
-        <v>0.5209167842031022</v>
+        <v>0.5250387596899238</v>
       </c>
       <c r="N161" t="n">
-        <v>0.5209167842031022</v>
+        <v>0.5250387596899238</v>
       </c>
       <c r="O161" t="n">
         <v>-0.03999999999999915</v>
       </c>
       <c r="P161" t="n">
-        <v>-0.1853279266572638</v>
+        <v>-0.1821511627906958</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -13580,10 +13580,10 @@
         <v>8</v>
       </c>
       <c r="G162" t="n">
-        <v>0.8497884344146686</v>
+        <v>0.8498942917547568</v>
       </c>
       <c r="H162" t="n">
-        <v>8.01638222849083</v>
+        <v>8.017441860465114</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -13602,16 +13602,16 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>0.3163822284908298</v>
+        <v>0.3174418604651139</v>
       </c>
       <c r="N162" t="n">
-        <v>0.3163822284908298</v>
+        <v>0.3174418604651139</v>
       </c>
       <c r="O162" t="n">
         <v>-0.03000000000000025</v>
       </c>
       <c r="P162" t="n">
-        <v>-0.2345345557122727</v>
+        <v>-0.2375968992248101</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -13651,10 +13651,10 @@
         <v>8</v>
       </c>
       <c r="G163" t="n">
-        <v>0.844851904090268</v>
+        <v>0.8449612403100775</v>
       </c>
       <c r="H163" t="n">
-        <v>7.95191466854725</v>
+        <v>7.952383720930232</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -13673,16 +13673,16 @@
         <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>0.3119146685472503</v>
+        <v>0.3123837209302325</v>
       </c>
       <c r="N163" t="n">
-        <v>0.3119146685472503</v>
+        <v>0.3123837209302325</v>
       </c>
       <c r="O163" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P163" t="n">
-        <v>-0.06446755994358</v>
+        <v>-0.06505813953488193</v>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
@@ -13722,10 +13722,10 @@
         <v>8</v>
       </c>
       <c r="G164" t="n">
-        <v>0.8385049365303244</v>
+        <v>0.8386187455954898</v>
       </c>
       <c r="H164" t="n">
-        <v>7.848120592383639</v>
+        <v>7.849748062015504</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -13744,16 +13744,16 @@
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>0.2881205923836392</v>
+        <v>0.2897480620155042</v>
       </c>
       <c r="N164" t="n">
-        <v>0.2881205923836392</v>
+        <v>0.2897480620155042</v>
       </c>
       <c r="O164" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P164" t="n">
-        <v>-0.1037940761636111</v>
+        <v>-0.1026356589147284</v>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
@@ -13793,10 +13793,10 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>0.8356840620592384</v>
+        <v>0.835799859055673</v>
       </c>
       <c r="H165" t="n">
-        <v>7.830028208744711</v>
+        <v>7.830193798449613</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -13815,16 +13815,16 @@
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>0.3500282087447104</v>
+        <v>0.3501937984496122</v>
       </c>
       <c r="N165" t="n">
-        <v>0.3500282087447104</v>
+        <v>0.3501937984496122</v>
       </c>
       <c r="O165" t="n">
         <v>-0.07999999999999918</v>
       </c>
       <c r="P165" t="n">
-        <v>-0.01809238363892796</v>
+        <v>-0.01955426356589118</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -13864,10 +13864,10 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>0.8272214386459803</v>
+        <v>0.8273431994362227</v>
       </c>
       <c r="H166" t="n">
-        <v>7.759633286318759</v>
+        <v>7.760503875968992</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -13886,16 +13886,16 @@
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>0.3896332863187588</v>
+        <v>0.3905038759689923</v>
       </c>
       <c r="N166" t="n">
-        <v>0.3896332863187588</v>
+        <v>0.3905038759689923</v>
       </c>
       <c r="O166" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P166" t="n">
-        <v>-0.07039492242595191</v>
+        <v>-0.06968992248062023</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
@@ -15065,10 +15065,10 @@
         <v>8</v>
       </c>
       <c r="G183" t="n">
-        <v>0.8004231311706629</v>
+        <v>0.8005637773079634</v>
       </c>
       <c r="H183" t="n">
-        <v>5.551421897038082</v>
+        <v>5.55147903453136</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -15087,16 +15087,16 @@
         <v>1</v>
       </c>
       <c r="M183" t="n">
-        <v>0.3364218970380817</v>
+        <v>0.3364790345313606</v>
       </c>
       <c r="N183" t="n">
-        <v>0.3364218970380817</v>
+        <v>0.3364790345313606</v>
       </c>
       <c r="O183" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P183" t="n">
-        <v>-0.0926583412240074</v>
+        <v>-0.09260120373072844</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -15136,10 +15136,10 @@
         <v>8</v>
       </c>
       <c r="G184" t="n">
-        <v>0.8540197461212976</v>
+        <v>0.854122621564482</v>
       </c>
       <c r="H184" t="n">
-        <v>5.760564174894217</v>
+        <v>5.760898520084567</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -15158,16 +15158,16 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>0.5955641748942169</v>
+        <v>0.5958985200845666</v>
       </c>
       <c r="N184" t="n">
-        <v>0.5955641748942169</v>
+        <v>0.5958985200845666</v>
       </c>
       <c r="O184" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P184" t="n">
-        <v>0.2091422778561354</v>
+        <v>0.2094194855532061</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -15207,10 +15207,10 @@
         <v>8</v>
       </c>
       <c r="G185" t="n">
-        <v>0.8681241184767278</v>
+        <v>0.8682170542635659</v>
       </c>
       <c r="H185" t="n">
-        <v>5.800350846262341</v>
+        <v>5.800426356589147</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -15229,16 +15229,16 @@
         <v>1</v>
       </c>
       <c r="M185" t="n">
-        <v>0.6803508462623409</v>
+        <v>0.6804263565891473</v>
       </c>
       <c r="N185" t="n">
-        <v>0.6803508462623409</v>
+        <v>0.6804263565891473</v>
       </c>
       <c r="O185" t="n">
         <v>-0.04499999999999993</v>
       </c>
       <c r="P185" t="n">
-        <v>0.03978667136812408</v>
+        <v>0.0395278365045808</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
@@ -15278,10 +15278,10 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>0.8653032440056417</v>
+        <v>0.8653981677237491</v>
       </c>
       <c r="H186" t="n">
-        <v>5.788353314527503</v>
+        <v>5.788816067653276</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -15300,16 +15300,16 @@
         <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>0.7083533145275034</v>
+        <v>0.7088160676532764</v>
       </c>
       <c r="N186" t="n">
-        <v>0.7083533145275034</v>
+        <v>0.7088160676532764</v>
       </c>
       <c r="O186" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P186" t="n">
-        <v>-0.01199753173483753</v>
+        <v>-0.0116102889358709</v>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
@@ -15349,10 +15349,10 @@
         <v>8</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8441466854724965</v>
+        <v>0.8442565186751233</v>
       </c>
       <c r="H187" t="n">
-        <v>5.684238363892807</v>
+        <v>5.684416842847075</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -15371,16 +15371,16 @@
         <v>1</v>
       </c>
       <c r="M187" t="n">
-        <v>0.2542383638928074</v>
+        <v>0.2544168428470757</v>
       </c>
       <c r="N187" t="n">
-        <v>0.2542383638928074</v>
+        <v>0.2544168428470757</v>
       </c>
       <c r="O187" t="n">
         <v>0.3499999999999996</v>
       </c>
       <c r="P187" t="n">
-        <v>-0.1041149506346963</v>
+        <v>-0.1043992248062011</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
@@ -15420,10 +15420,10 @@
         <v>8</v>
       </c>
       <c r="G188" t="n">
-        <v>0.7954866008462623</v>
+        <v>0.795630725863284</v>
       </c>
       <c r="H188" t="n">
-        <v>5.53716149506347</v>
+        <v>5.538449612403101</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -15442,16 +15442,16 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>-0.06533850493653048</v>
+        <v>-0.06405038759689941</v>
       </c>
       <c r="N188" t="n">
-        <v>0.06533850493653048</v>
+        <v>0.06405038759689941</v>
       </c>
       <c r="O188" t="n">
         <v>0.1725000000000003</v>
       </c>
       <c r="P188" t="n">
-        <v>-0.1470768688293376</v>
+        <v>-0.1459672304439747</v>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
@@ -15491,10 +15491,10 @@
         <v>8</v>
       </c>
       <c r="G189" t="n">
-        <v>0.7475317348377997</v>
+        <v>0.7477096546863988</v>
       </c>
       <c r="H189" t="n">
-        <v>5.377239069111424</v>
+        <v>5.37765503875969</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -15513,16 +15513,16 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>-0.1727609308885754</v>
+        <v>-0.1723449612403094</v>
       </c>
       <c r="N189" t="n">
-        <v>0.1727609308885754</v>
+        <v>0.1723449612403094</v>
       </c>
       <c r="O189" t="n">
         <v>-0.05250000000000021</v>
       </c>
       <c r="P189" t="n">
-        <v>-0.1599224259520451</v>
+        <v>-0.1607945736434102</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
@@ -15562,10 +15562,10 @@
         <v>8</v>
       </c>
       <c r="G190" t="n">
-        <v>0.7193229901269393</v>
+        <v>0.7195207892882312</v>
       </c>
       <c r="H190" t="n">
-        <v>5.279724964739069</v>
+        <v>5.279805320648344</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -15584,16 +15584,16 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
-        <v>-0.0002750352609313111</v>
+        <v>-0.0001946793516562906</v>
       </c>
       <c r="N190" t="n">
-        <v>0.0002750352609313111</v>
+        <v>0.0001946793516562906</v>
       </c>
       <c r="O190" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P190" t="n">
-        <v>-0.09751410437235553</v>
+        <v>-0.09784971811134646</v>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
@@ -15633,10 +15633,10 @@
         <v>8</v>
       </c>
       <c r="G191" t="n">
-        <v>0.7143864598025388</v>
+        <v>0.7138830162085976</v>
       </c>
       <c r="H191" t="n">
-        <v>5.277719499294781</v>
+        <v>5.277514975334743</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -15655,16 +15655,16 @@
         <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>0.2527194992947823</v>
+        <v>0.2525149753347442</v>
       </c>
       <c r="N191" t="n">
-        <v>0.2527194992947823</v>
+        <v>0.2525149753347442</v>
       </c>
       <c r="O191" t="n">
         <v>-0.2550000000000017</v>
       </c>
       <c r="P191" t="n">
-        <v>-0.002005465444288035</v>
+        <v>-0.002290345313601172</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
@@ -15704,10 +15704,10 @@
         <v>8</v>
       </c>
       <c r="G192" t="n">
-        <v>0.7228490832157969</v>
+        <v>0.7230443974630021</v>
       </c>
       <c r="H192" t="n">
-        <v>5.282314880112835</v>
+        <v>5.282473572938689</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -15726,16 +15726,16 @@
         <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>0.4323148801128349</v>
+        <v>0.4324735729386893</v>
       </c>
       <c r="N192" t="n">
-        <v>0.4323148801128349</v>
+        <v>0.4324735729386893</v>
       </c>
       <c r="O192" t="n">
         <v>-0.1749999999999989</v>
       </c>
       <c r="P192" t="n">
-        <v>0.004595380818053663</v>
+        <v>0.004958597603946124</v>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
@@ -15775,10 +15775,10 @@
         <v>8</v>
       </c>
       <c r="G193" t="n">
-        <v>0.729901269393512</v>
+        <v>0.7300916138125441</v>
       </c>
       <c r="H193" t="n">
-        <v>5.308171720733426</v>
+        <v>5.31049154334038</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -15797,16 +15797,16 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
-        <v>0.7381717207334262</v>
+        <v>0.7404915433403794</v>
       </c>
       <c r="N193" t="n">
-        <v>0.7381717207334262</v>
+        <v>0.7404915433403794</v>
       </c>
       <c r="O193" t="n">
         <v>-0.2799999999999994</v>
       </c>
       <c r="P193" t="n">
-        <v>0.0258568406205919</v>
+        <v>0.02801797040169074</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
@@ -15846,10 +15846,10 @@
         <v>8</v>
       </c>
       <c r="G194" t="n">
-        <v>0.7207334273624824</v>
+        <v>0.7209302325581395</v>
       </c>
       <c r="H194" t="n">
-        <v>5.280595909732017</v>
+        <v>5.280755813953489</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -15868,16 +15868,16 @@
         <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>0.850595909732017</v>
+        <v>0.850755813953489</v>
       </c>
       <c r="N194" t="n">
-        <v>0.850595909732017</v>
+        <v>0.850755813953489</v>
       </c>
       <c r="O194" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P194" t="n">
-        <v>-0.02757581100140971</v>
+        <v>-0.02973572938689095</v>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
@@ -15917,10 +15917,10 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>0.6932299012693935</v>
+        <v>0.6927413671599718</v>
       </c>
       <c r="H195" t="n">
-        <v>5.211498589562765</v>
+        <v>5.210704721634955</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -15939,16 +15939,16 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>0.731498589562765</v>
+        <v>0.7307047216349547</v>
       </c>
       <c r="N195" t="n">
-        <v>0.731498589562765</v>
+        <v>0.7307047216349547</v>
       </c>
       <c r="O195" t="n">
         <v>0.05000000000000071</v>
       </c>
       <c r="P195" t="n">
-        <v>-0.0690973201692513</v>
+        <v>-0.07005109231853357</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
@@ -15988,10 +15988,10 @@
         <v>8</v>
       </c>
       <c r="G196" t="n">
-        <v>0.6544428772919605</v>
+        <v>0.6539816772374912</v>
       </c>
       <c r="H196" t="n">
-        <v>5.111583215796897</v>
+        <v>5.107461240310078</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -16010,16 +16010,16 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>0.3215832157968972</v>
+        <v>0.3174612403100783</v>
       </c>
       <c r="N196" t="n">
-        <v>0.3215832157968972</v>
+        <v>0.3174612403100783</v>
       </c>
       <c r="O196" t="n">
         <v>0.3099999999999996</v>
       </c>
       <c r="P196" t="n">
-        <v>-0.09991537376586823</v>
+        <v>-0.1032434813248768</v>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>8</v>
       </c>
       <c r="G213" t="n">
-        <v>0.7566995768688294</v>
+        <v>0.7568710359408034</v>
       </c>
       <c r="H213" t="n">
         <v>5.970000000000001</v>
@@ -17260,7 +17260,7 @@
         <v>8</v>
       </c>
       <c r="G214" t="n">
-        <v>0.7559943582510579</v>
+        <v>0.7561663143058492</v>
       </c>
       <c r="H214" t="n">
         <v>5.97</v>
@@ -17331,10 +17331,10 @@
         <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>0.7665726375176305</v>
+        <v>0.766737138830162</v>
       </c>
       <c r="H215" t="n">
-        <v>6.014442877291961</v>
+        <v>6.015417547568711</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -17353,16 +17353,16 @@
         <v>1</v>
       </c>
       <c r="M215" t="n">
-        <v>-2.46555712270804</v>
+        <v>-2.46458245243129</v>
       </c>
       <c r="N215" t="n">
-        <v>2.46555712270804</v>
+        <v>2.46458245243129</v>
       </c>
       <c r="O215" t="n">
         <v>-0.1074999999999982</v>
       </c>
       <c r="P215" t="n">
-        <v>0.04444287729196095</v>
+        <v>0.04541754756871086</v>
       </c>
       <c r="Q215" t="inlineStr">
         <is>
@@ -17402,10 +17402,10 @@
         <v>8</v>
       </c>
       <c r="G216" t="n">
-        <v>0.7870239774330042</v>
+        <v>0.7871740662438337</v>
       </c>
       <c r="H216" t="n">
-        <v>6.107489421720734</v>
+        <v>6.108675123326287</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -17424,16 +17424,16 @@
         <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>-2.102510578279267</v>
+        <v>-2.101324876673714</v>
       </c>
       <c r="N216" t="n">
-        <v>2.102510578279267</v>
+        <v>2.101324876673714</v>
       </c>
       <c r="O216" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P216" t="n">
-        <v>0.09304654442877336</v>
+        <v>0.09325757575757621</v>
       </c>
       <c r="Q216" t="inlineStr">
         <is>
@@ -17473,10 +17473,10 @@
         <v>8</v>
       </c>
       <c r="G217" t="n">
-        <v>0.8095909732016925</v>
+        <v>0.8097251585623678</v>
       </c>
       <c r="H217" t="n">
-        <v>6.205768688293371</v>
+        <v>6.206828752642706</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -17495,16 +17495,16 @@
         <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>-1.954231311706629</v>
+        <v>-1.953171247357294</v>
       </c>
       <c r="N217" t="n">
-        <v>1.954231311706629</v>
+        <v>1.953171247357294</v>
       </c>
       <c r="O217" t="n">
         <v>-0.05000000000000071</v>
       </c>
       <c r="P217" t="n">
-        <v>0.09827926657263664</v>
+        <v>0.09815362931641936</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -17544,10 +17544,10 @@
         <v>8</v>
       </c>
       <c r="G218" t="n">
-        <v>0.8279266572637518</v>
+        <v>0.8280479210711769</v>
       </c>
       <c r="H218" t="n">
-        <v>6.297080394922427</v>
+        <v>6.297719050974865</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -17566,16 +17566,16 @@
         <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>-1.632919605077573</v>
+        <v>-1.632280949025135</v>
       </c>
       <c r="N218" t="n">
-        <v>1.632919605077573</v>
+        <v>1.632280949025135</v>
       </c>
       <c r="O218" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P218" t="n">
-        <v>0.09131170662905586</v>
+        <v>0.09089029833215889</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -17615,10 +17615,10 @@
         <v>8</v>
       </c>
       <c r="G219" t="n">
-        <v>0.844851904090268</v>
+        <v>0.8449612403100775</v>
       </c>
       <c r="H219" t="n">
-        <v>6.386082510578279</v>
+        <v>6.386298449612402</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -17637,16 +17637,16 @@
         <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>-1.603917489421721</v>
+        <v>-1.603701550387598</v>
       </c>
       <c r="N219" t="n">
-        <v>1.603917489421721</v>
+        <v>1.603701550387598</v>
       </c>
       <c r="O219" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P219" t="n">
-        <v>0.0890021156558527</v>
+        <v>0.08857939863753739</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -17686,10 +17686,10 @@
         <v>8</v>
       </c>
       <c r="G220" t="n">
-        <v>0.8519040902679831</v>
+        <v>0.8520084566596194</v>
       </c>
       <c r="H220" t="n">
-        <v>6.460014104372355</v>
+        <v>6.460288935870331</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -17708,16 +17708,16 @@
         <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>-1.529985895627645</v>
+        <v>-1.529711064129669</v>
       </c>
       <c r="N220" t="n">
-        <v>1.529985895627645</v>
+        <v>1.529711064129669</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
       </c>
       <c r="P220" t="n">
-        <v>0.0739315937940761</v>
+        <v>0.07399048625792837</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -17757,10 +17757,10 @@
         <v>8</v>
       </c>
       <c r="G221" t="n">
-        <v>0.8427362482369535</v>
+        <v>0.842847075405215</v>
       </c>
       <c r="H221" t="n">
-        <v>6.381904090267983</v>
+        <v>6.382122973925299</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -17779,16 +17779,16 @@
         <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>-1.475595909732017</v>
+        <v>-1.475377026074701</v>
       </c>
       <c r="N221" t="n">
-        <v>1.475595909732017</v>
+        <v>1.475377026074701</v>
       </c>
       <c r="O221" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P221" t="n">
-        <v>-0.07811001410437246</v>
+        <v>-0.07816596194503145</v>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
@@ -17828,10 +17828,10 @@
         <v>8</v>
       </c>
       <c r="G222" t="n">
-        <v>0.8229901269393513</v>
+        <v>0.8231148696264975</v>
       </c>
       <c r="H222" t="n">
-        <v>6.250811001410438</v>
+        <v>6.251303735024665</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -17850,16 +17850,16 @@
         <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>-1.489188998589563</v>
+        <v>-1.488696264975335</v>
       </c>
       <c r="N222" t="n">
-        <v>1.489188998589563</v>
+        <v>1.488696264975335</v>
       </c>
       <c r="O222" t="n">
         <v>-0.1174999999999997</v>
       </c>
       <c r="P222" t="n">
-        <v>-0.1310930888575452</v>
+        <v>-0.1308192389006342</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -17899,10 +17899,10 @@
         <v>8</v>
       </c>
       <c r="G223" t="n">
-        <v>0.8053596614950634</v>
+        <v>0.8054968287526427</v>
       </c>
       <c r="H223" t="n">
-        <v>6.181560883874001</v>
+        <v>6.182283298097252</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -17921,16 +17921,16 @@
         <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>-1.438439116125999</v>
+        <v>-1.437716701902748</v>
       </c>
       <c r="N223" t="n">
-        <v>1.438439116125999</v>
+        <v>1.437716701902748</v>
       </c>
       <c r="O223" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.06925011753643684</v>
+        <v>-0.06902043692741344</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -17970,10 +17970,10 @@
         <v>8</v>
       </c>
       <c r="G224" t="n">
-        <v>0.7806770098730607</v>
+        <v>0.780831571529246</v>
       </c>
       <c r="H224" t="n">
-        <v>6.077168547249647</v>
+        <v>6.07732117688513</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -17992,16 +17992,16 @@
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>-1.322831452750354</v>
+        <v>-1.32267882311487</v>
       </c>
       <c r="N224" t="n">
-        <v>1.322831452750354</v>
+        <v>1.32267882311487</v>
       </c>
       <c r="O224" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.104392336624354</v>
+        <v>-0.1049621212121217</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -18041,10 +18041,10 @@
         <v>8</v>
       </c>
       <c r="G225" t="n">
-        <v>0.7531734837799718</v>
+        <v>0.7533474277660324</v>
       </c>
       <c r="H225" t="n">
-        <v>5.966678420310296</v>
+        <v>5.966907446558609</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -18063,16 +18063,16 @@
         <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>-1.393321579689704</v>
+        <v>-1.393092553441392</v>
       </c>
       <c r="N225" t="n">
-        <v>1.393321579689704</v>
+        <v>1.393092553441392</v>
       </c>
       <c r="O225" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.110490126939351</v>
+        <v>-0.1104137303265214</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>8</v>
       </c>
       <c r="G226" t="n">
-        <v>0.7284908321579689</v>
+        <v>0.7286821705426356</v>
       </c>
       <c r="H226" t="n">
-        <v>5.835077574047955</v>
+        <v>5.836589147286821</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -18134,16 +18134,16 @@
         <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>-1.544922425952045</v>
+        <v>-1.543410852713179</v>
       </c>
       <c r="N226" t="n">
-        <v>1.544922425952045</v>
+        <v>1.543410852713179</v>
       </c>
       <c r="O226" t="n">
         <v>0.01999999999999957</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.1316008462623408</v>
+        <v>-0.1303182992717877</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -19313,10 +19313,10 @@
         <v>8</v>
       </c>
       <c r="G243" t="n">
-        <v>0.8279266572637518</v>
+        <v>0.8273431994362227</v>
       </c>
       <c r="H243" t="n">
-        <v>5.559742595204513</v>
+        <v>5.559445031712473</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -19335,16 +19335,16 @@
         <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>1.569742595204513</v>
+        <v>1.569445031712473</v>
       </c>
       <c r="N243" t="n">
-        <v>1.569742595204513</v>
+        <v>1.569445031712473</v>
       </c>
       <c r="O243" t="n">
         <v>-0.1624999999999996</v>
       </c>
       <c r="P243" t="n">
-        <v>-1.601175414606279</v>
+        <v>-1.601472978098319</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -19384,10 +19384,10 @@
         <v>8</v>
       </c>
       <c r="G244" t="n">
-        <v>0.7038081805359662</v>
+        <v>0.7033121916842847</v>
       </c>
       <c r="H244" t="n">
-        <v>4.928653032440057</v>
+        <v>4.927135306553911</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -19406,16 +19406,16 @@
         <v>1</v>
       </c>
       <c r="M244" t="n">
-        <v>1.106153032440057</v>
+        <v>1.104635306553911</v>
       </c>
       <c r="N244" t="n">
-        <v>1.106153032440057</v>
+        <v>1.104635306553911</v>
       </c>
       <c r="O244" t="n">
         <v>-0.1675000000000004</v>
       </c>
       <c r="P244" t="n">
-        <v>-0.6310895627644566</v>
+        <v>-0.6323097251585619</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -19455,10 +19455,10 @@
         <v>8</v>
       </c>
       <c r="G245" t="n">
-        <v>0.614950634696756</v>
+        <v>0.6145172656800564</v>
       </c>
       <c r="H245" t="n">
-        <v>4.629749647390692</v>
+        <v>4.629307610993658</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -19477,16 +19477,16 @@
         <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>0.8497496473906918</v>
+        <v>0.8493076109936584</v>
       </c>
       <c r="N245" t="n">
-        <v>0.8497496473906918</v>
+        <v>0.8493076109936584</v>
       </c>
       <c r="O245" t="n">
         <v>-0.04249999999999998</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.298903385049365</v>
+        <v>-0.2978276955602528</v>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
@@ -19526,10 +19526,10 @@
         <v>8</v>
       </c>
       <c r="G246" t="n">
-        <v>0.5930888575458392</v>
+        <v>0.5926708949964764</v>
       </c>
       <c r="H246" t="n">
-        <v>4.557302538787024</v>
+        <v>4.555597251585624</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -19548,16 +19548,16 @@
         <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>0.8773025387870237</v>
+        <v>0.8755972515856238</v>
       </c>
       <c r="N246" t="n">
-        <v>0.8773025387870237</v>
+        <v>0.8755972515856238</v>
       </c>
       <c r="O246" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P246" t="n">
-        <v>-0.07244710860366776</v>
+        <v>-0.07371035940803417</v>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
@@ -19597,10 +19597,10 @@
         <v>8</v>
       </c>
       <c r="G247" t="n">
-        <v>0.6332863187588152</v>
+        <v>0.6328400281888654</v>
       </c>
       <c r="H247" t="n">
-        <v>4.720356135401975</v>
+        <v>4.718990486257929</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -19619,16 +19619,16 @@
         <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>1.140356135401975</v>
+        <v>1.138990486257929</v>
       </c>
       <c r="N247" t="n">
-        <v>1.140356135401975</v>
+        <v>1.138990486257929</v>
       </c>
       <c r="O247" t="n">
         <v>-0.1000000000000001</v>
       </c>
       <c r="P247" t="n">
-        <v>0.1630535966149509</v>
+        <v>0.1633932346723048</v>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
@@ -19668,10 +19668,10 @@
         <v>8</v>
       </c>
       <c r="G248" t="n">
-        <v>0.6459802538787024</v>
+        <v>0.6455250176180408</v>
       </c>
       <c r="H248" t="n">
-        <v>4.758899858956276</v>
+        <v>4.758435517970401</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -19690,16 +19690,16 @@
         <v>1</v>
       </c>
       <c r="M248" t="n">
-        <v>1.366399858956276</v>
+        <v>1.365935517970401</v>
       </c>
       <c r="N248" t="n">
-        <v>1.366399858956276</v>
+        <v>1.365935517970401</v>
       </c>
       <c r="O248" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P248" t="n">
-        <v>0.03854372355430158</v>
+        <v>0.03944503171247238</v>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
@@ -19739,10 +19739,10 @@
         <v>8</v>
       </c>
       <c r="G249" t="n">
-        <v>0.5959097320169252</v>
+        <v>0.5954897815362932</v>
       </c>
       <c r="H249" t="n">
-        <v>4.585779266572637</v>
+        <v>4.58149577167019</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -19761,16 +19761,16 @@
         <v>1</v>
       </c>
       <c r="M249" t="n">
-        <v>1.305779266572638</v>
+        <v>1.30149577167019</v>
       </c>
       <c r="N249" t="n">
-        <v>1.305779266572638</v>
+        <v>1.30149577167019</v>
       </c>
       <c r="O249" t="n">
         <v>-0.1125000000000003</v>
       </c>
       <c r="P249" t="n">
-        <v>-0.173120592383639</v>
+        <v>-0.1769397463002109</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
@@ -19810,10 +19810,10 @@
         <v>8</v>
       </c>
       <c r="G250" t="n">
-        <v>0.4894217207334274</v>
+        <v>0.48907681465821</v>
       </c>
       <c r="H250" t="n">
-        <v>4.144340620592383</v>
+        <v>4.142933403805497</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -19832,16 +19832,16 @@
         <v>1</v>
       </c>
       <c r="M250" t="n">
-        <v>0.9943406205923835</v>
+        <v>0.9929334038054969</v>
       </c>
       <c r="N250" t="n">
-        <v>0.9943406205923835</v>
+        <v>0.9929334038054969</v>
       </c>
       <c r="O250" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P250" t="n">
-        <v>-0.441438645980254</v>
+        <v>-0.4385623678646935</v>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
@@ -19881,10 +19881,10 @@
         <v>8</v>
       </c>
       <c r="G251" t="n">
-        <v>0.3899858956276446</v>
+        <v>0.3897110641296688</v>
       </c>
       <c r="H251" t="n">
-        <v>3.800856840620592</v>
+        <v>3.800015856236787</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -19903,16 +19903,16 @@
         <v>1</v>
       </c>
       <c r="M251" t="n">
-        <v>0.8558568406205924</v>
+        <v>0.8550158562367867</v>
       </c>
       <c r="N251" t="n">
-        <v>0.8558568406205924</v>
+        <v>0.8550158562367867</v>
       </c>
       <c r="O251" t="n">
         <v>-0.2050000000000001</v>
       </c>
       <c r="P251" t="n">
-        <v>-0.3434837799717911</v>
+        <v>-0.3429175475687103</v>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
@@ -19952,10 +19952,10 @@
         <v>8</v>
       </c>
       <c r="G252" t="n">
-        <v>0.3356840620592383</v>
+        <v>0.3354474982381959</v>
       </c>
       <c r="H252" t="n">
-        <v>3.637992477668077</v>
+        <v>3.637188160676533</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -19974,16 +19974,16 @@
         <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>0.7979924776680773</v>
+        <v>0.7971881606765328</v>
       </c>
       <c r="N252" t="n">
-        <v>0.7979924776680773</v>
+        <v>0.7971881606765328</v>
       </c>
       <c r="O252" t="n">
         <v>-0.105</v>
       </c>
       <c r="P252" t="n">
-        <v>-0.1628643629525151</v>
+        <v>-0.1628276955602539</v>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
@@ -20023,10 +20023,10 @@
         <v>8</v>
       </c>
       <c r="G253" t="n">
-        <v>0.346262341325811</v>
+        <v>0.3460183227625088</v>
       </c>
       <c r="H253" t="n">
-        <v>3.673958627174424</v>
+        <v>3.673128964059197</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -20045,16 +20045,16 @@
         <v>1</v>
       </c>
       <c r="M253" t="n">
-        <v>0.9039586271744242</v>
+        <v>0.9031289640591966</v>
       </c>
       <c r="N253" t="n">
-        <v>0.9039586271744242</v>
+        <v>0.9031289640591966</v>
       </c>
       <c r="O253" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P253" t="n">
-        <v>0.03596614950634702</v>
+        <v>0.03594080338266403</v>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
@@ -20094,10 +20094,10 @@
         <v>8</v>
       </c>
       <c r="G254" t="n">
-        <v>0.4936530324400564</v>
+        <v>0.4933051444679352</v>
       </c>
       <c r="H254" t="n">
-        <v>4.168656558533145</v>
+        <v>4.166527484143764</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -20116,16 +20116,16 @@
         <v>1</v>
       </c>
       <c r="M254" t="n">
-        <v>1.348656558533146</v>
+        <v>1.346527484143764</v>
       </c>
       <c r="N254" t="n">
-        <v>1.348656558533146</v>
+        <v>1.346527484143764</v>
       </c>
       <c r="O254" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="P254" t="n">
-        <v>0.4946979313587212</v>
+        <v>0.493398520084567</v>
       </c>
       <c r="Q254" t="inlineStr">
         <is>
@@ -20165,10 +20165,10 @@
         <v>8</v>
       </c>
       <c r="G255" t="n">
-        <v>0.6953455571227081</v>
+        <v>0.6948555320648344</v>
       </c>
       <c r="H255" t="n">
-        <v>4.903504936530324</v>
+        <v>4.902505285412262</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -20187,16 +20187,16 @@
         <v>1</v>
       </c>
       <c r="M255" t="n">
-        <v>2.153504936530324</v>
+        <v>2.152505285412262</v>
       </c>
       <c r="N255" t="n">
-        <v>2.153504936530324</v>
+        <v>2.152505285412262</v>
       </c>
       <c r="O255" t="n">
         <v>-0.06999999999999984</v>
       </c>
       <c r="P255" t="n">
-        <v>0.7348483779971788</v>
+        <v>0.7359778012684988</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
@@ -20236,10 +20236,10 @@
         <v>8</v>
       </c>
       <c r="G256" t="n">
-        <v>0.7877291960507757</v>
+        <v>0.7871740662438337</v>
       </c>
       <c r="H256" t="n">
-        <v>5.198095909732016</v>
+        <v>5.192716701902747</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -20258,16 +20258,16 @@
         <v>1</v>
       </c>
       <c r="M256" t="n">
-        <v>2.448095909732016</v>
+        <v>2.442716701902747</v>
       </c>
       <c r="N256" t="n">
-        <v>2.448095909732016</v>
+        <v>2.442716701902747</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
       </c>
       <c r="P256" t="n">
-        <v>0.294590973201692</v>
+        <v>0.290211416490485</v>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
@@ -21437,10 +21437,10 @@
         <v>8</v>
       </c>
       <c r="G273" t="n">
-        <v>0.9428772919605077</v>
+        <v>0.9429175475687104</v>
       </c>
       <c r="H273" t="n">
-        <v>6.914397038081805</v>
+        <v>6.914619450317125</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -21459,16 +21459,16 @@
         <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>-0.8506029619181943</v>
+        <v>-0.8503805496828747</v>
       </c>
       <c r="N273" t="n">
-        <v>0.8506029619181943</v>
+        <v>0.8503805496828747</v>
       </c>
       <c r="O273" t="n">
         <v>0.0550000000000006</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.9765373230487713</v>
+        <v>-0.9763149108134517</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -21508,10 +21508,10 @@
         <v>8</v>
       </c>
       <c r="G274" t="n">
-        <v>0.9393511988716502</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="H274" t="n">
-        <v>6.849915373765867</v>
+        <v>6.850303030303031</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -21530,16 +21530,16 @@
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>-0.9300846262341329</v>
+        <v>-0.9296969696969697</v>
       </c>
       <c r="N274" t="n">
-        <v>0.9300846262341329</v>
+        <v>0.9296969696969697</v>
       </c>
       <c r="O274" t="n">
         <v>0.01500000000000057</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.06448166431593805</v>
+        <v>-0.06431642001409443</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -21579,10 +21579,10 @@
         <v>8</v>
       </c>
       <c r="G275" t="n">
-        <v>0.9358251057827927</v>
+        <v>0.9358703312191684</v>
       </c>
       <c r="H275" t="n">
-        <v>6.830433709449929</v>
+        <v>6.830683579985905</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -21601,16 +21601,16 @@
         <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>-0.9395662905500703</v>
+        <v>-0.9393164200140944</v>
       </c>
       <c r="N275" t="n">
-        <v>0.9395662905500703</v>
+        <v>0.9393164200140944</v>
       </c>
       <c r="O275" t="n">
         <v>-0.01000000000000068</v>
       </c>
       <c r="P275" t="n">
-        <v>-0.01948166431593812</v>
+        <v>-0.01961945031712542</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -21650,10 +21650,10 @@
         <v>8</v>
       </c>
       <c r="G276" t="n">
-        <v>0.9322990126939351</v>
+        <v>0.9323467230443975</v>
       </c>
       <c r="H276" t="n">
-        <v>6.820476022566996</v>
+        <v>6.820607822410148</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -21672,16 +21672,16 @@
         <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>-0.8795239774330046</v>
+        <v>-0.8793921775898523</v>
       </c>
       <c r="N276" t="n">
-        <v>0.8795239774330046</v>
+        <v>0.8793921775898523</v>
       </c>
       <c r="O276" t="n">
         <v>-0.0699999999999994</v>
       </c>
       <c r="P276" t="n">
-        <v>-0.009957686882933636</v>
+        <v>-0.01007575757575729</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -21721,10 +21721,10 @@
         <v>8</v>
       </c>
       <c r="G277" t="n">
-        <v>0.9287729196050776</v>
+        <v>0.9288231148696265</v>
       </c>
       <c r="H277" t="n">
-        <v>6.781470380818053</v>
+        <v>6.781747709654686</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -21743,16 +21743,16 @@
         <v>1</v>
       </c>
       <c r="M277" t="n">
-        <v>-0.8085296191819467</v>
+        <v>-0.8082522903453135</v>
       </c>
       <c r="N277" t="n">
-        <v>0.8085296191819467</v>
+        <v>0.8082522903453135</v>
       </c>
       <c r="O277" t="n">
         <v>-0.1100000000000003</v>
       </c>
       <c r="P277" t="n">
-        <v>-0.03900564174894239</v>
+        <v>-0.03886011275546153</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -21792,10 +21792,10 @@
         <v>8</v>
       </c>
       <c r="G278" t="n">
-        <v>0.92524682651622</v>
+        <v>0.9252995066948555</v>
       </c>
       <c r="H278" t="n">
-        <v>6.751988716502115</v>
+        <v>6.752279774489076</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -21814,16 +21814,16 @@
         <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>-0.6980112834978849</v>
+        <v>-0.6977202255109241</v>
       </c>
       <c r="N278" t="n">
-        <v>0.6980112834978849</v>
+        <v>0.6977202255109241</v>
       </c>
       <c r="O278" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P278" t="n">
-        <v>-0.02948166431593791</v>
+        <v>-0.02946793516561019</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -21863,10 +21863,10 @@
         <v>8</v>
       </c>
       <c r="G279" t="n">
-        <v>0.9217207334273625</v>
+        <v>0.9217758985200846</v>
       </c>
       <c r="H279" t="n">
-        <v>6.715004701457452</v>
+        <v>6.715207892882312</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -21885,16 +21885,16 @@
         <v>1</v>
       </c>
       <c r="M279" t="n">
-        <v>-0.6549952985425485</v>
+        <v>-0.6547921071176885</v>
       </c>
       <c r="N279" t="n">
-        <v>0.6549952985425485</v>
+        <v>0.6547921071176885</v>
       </c>
       <c r="O279" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P279" t="n">
-        <v>-0.03698401504466364</v>
+        <v>-0.03707188160676456</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -21934,10 +21934,10 @@
         <v>8</v>
       </c>
       <c r="G280" t="n">
-        <v>0.918194640338505</v>
+        <v>0.9182522903453136</v>
       </c>
       <c r="H280" t="n">
-        <v>6.682101551480961</v>
+        <v>6.683375616631433</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -21956,16 +21956,16 @@
         <v>1</v>
       </c>
       <c r="M280" t="n">
-        <v>-0.5878984485190388</v>
+        <v>-0.5866243833685667</v>
       </c>
       <c r="N280" t="n">
-        <v>0.5878984485190388</v>
+        <v>0.5866243833685667</v>
       </c>
       <c r="O280" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P280" t="n">
-        <v>-0.03290314997649091</v>
+        <v>-0.0318322762508787</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -22005,10 +22005,10 @@
         <v>8</v>
       </c>
       <c r="G281" t="n">
-        <v>0.9146685472496474</v>
+        <v>0.9147286821705426</v>
       </c>
       <c r="H281" t="n">
-        <v>6.627087447108604</v>
+        <v>6.627751937984496</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -22027,16 +22027,16 @@
         <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>-0.6329125528913959</v>
+        <v>-0.6322480620155035</v>
       </c>
       <c r="N281" t="n">
-        <v>0.6329125528913959</v>
+        <v>0.6322480620155035</v>
       </c>
       <c r="O281" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P281" t="n">
-        <v>-0.05501410437235688</v>
+        <v>-0.05562367864693663</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -22076,10 +22076,10 @@
         <v>8</v>
       </c>
       <c r="G282" t="n">
-        <v>0.9111424541607899</v>
+        <v>0.9112050739957717</v>
       </c>
       <c r="H282" t="n">
-        <v>6.549062059238364</v>
+        <v>6.549408033826638</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -22098,16 +22098,16 @@
         <v>1</v>
       </c>
       <c r="M282" t="n">
-        <v>-0.5609379407616366</v>
+        <v>-0.5605919661733623</v>
       </c>
       <c r="N282" t="n">
-        <v>0.5609379407616366</v>
+        <v>0.5605919661733623</v>
       </c>
       <c r="O282" t="n">
         <v>-0.1499999999999995</v>
       </c>
       <c r="P282" t="n">
-        <v>-0.07802538787024016</v>
+        <v>-0.07834390415785819</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -22147,10 +22147,10 @@
         <v>8</v>
       </c>
       <c r="G283" t="n">
-        <v>0.9076163610719323</v>
+        <v>0.9076814658210007</v>
       </c>
       <c r="H283" t="n">
-        <v>6.518321579689704</v>
+        <v>6.519760394644116</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -22169,16 +22169,16 @@
         <v>1</v>
       </c>
       <c r="M283" t="n">
-        <v>-0.4916784203102953</v>
+        <v>-0.4902396053558835</v>
       </c>
       <c r="N283" t="n">
-        <v>0.4916784203102953</v>
+        <v>0.4902396053558835</v>
       </c>
       <c r="O283" t="n">
         <v>-0.1000000000000005</v>
       </c>
       <c r="P283" t="n">
-        <v>-0.03074047954865922</v>
+        <v>-0.02964763918252178</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -22218,10 +22218,10 @@
         <v>8</v>
       </c>
       <c r="G284" t="n">
-        <v>0.9055007052186178</v>
+        <v>0.9055673009161381</v>
       </c>
       <c r="H284" t="n">
-        <v>6.454696755994361</v>
+        <v>6.459112050739958</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -22240,16 +22240,16 @@
         <v>1</v>
       </c>
       <c r="M284" t="n">
-        <v>-0.3653032440056396</v>
+        <v>-0.3608879492600421</v>
       </c>
       <c r="N284" t="n">
-        <v>0.3653032440056396</v>
+        <v>0.3608879492600421</v>
       </c>
       <c r="O284" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P284" t="n">
-        <v>-0.06362482369534384</v>
+        <v>-0.06064834390415808</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -22289,10 +22289,10 @@
         <v>8</v>
       </c>
       <c r="G285" t="n">
-        <v>0.9019746121297603</v>
+        <v>0.9020436927413672</v>
       </c>
       <c r="H285" t="n">
-        <v>6.403409732016926</v>
+        <v>6.403791402396054</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -22311,16 +22311,16 @@
         <v>1</v>
       </c>
       <c r="M285" t="n">
-        <v>-0.2965902679830741</v>
+        <v>-0.2962085976039459</v>
       </c>
       <c r="N285" t="n">
-        <v>0.2965902679830741</v>
+        <v>0.2962085976039459</v>
       </c>
       <c r="O285" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P285" t="n">
-        <v>-0.05128702397743456</v>
+        <v>-0.05532064834390393</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
@@ -22360,10 +22360,10 @@
         <v>8</v>
       </c>
       <c r="G286" t="n">
-        <v>0.8991537376586742</v>
+        <v>0.8992248062015504</v>
       </c>
       <c r="H286" t="n">
-        <v>6.3612976022567</v>
+        <v>6.362868217054264</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -22382,16 +22382,16 @@
         <v>1</v>
       </c>
       <c r="M286" t="n">
-        <v>-0.1787023977433</v>
+        <v>-0.1771317829457359</v>
       </c>
       <c r="N286" t="n">
-        <v>0.1787023977433</v>
+        <v>0.1771317829457359</v>
       </c>
       <c r="O286" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P286" t="n">
-        <v>-0.04211212976022605</v>
+        <v>-0.04092318534179018</v>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
@@ -25685,10 +25685,10 @@
         <v>8</v>
       </c>
       <c r="G333" t="n">
-        <v>0.764456981664316</v>
+        <v>0.7646229739252995</v>
       </c>
       <c r="H333" t="n">
-        <v>6.488004231311707</v>
+        <v>6.488942917547569</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -25707,16 +25707,16 @@
         <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>-0.7744957686882934</v>
+        <v>-0.7735570824524309</v>
       </c>
       <c r="N333" t="n">
-        <v>0.7744957686882934</v>
+        <v>0.7735570824524309</v>
       </c>
       <c r="O333" t="n">
         <v>-0.4400000000000004</v>
       </c>
       <c r="P333" t="n">
-        <v>-0.979501024469652</v>
+        <v>-0.9785623382337896</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
@@ -25756,10 +25756,10 @@
         <v>8</v>
       </c>
       <c r="G334" t="n">
-        <v>0.7729196050775741</v>
+        <v>0.7730796335447498</v>
       </c>
       <c r="H334" t="n">
-        <v>6.53844763751763</v>
+        <v>6.538786997885835</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -25778,16 +25778,16 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
-        <v>-0.4365523624823693</v>
+        <v>-0.4362130021141644</v>
       </c>
       <c r="N334" t="n">
-        <v>0.4365523624823693</v>
+        <v>0.4362130021141644</v>
       </c>
       <c r="O334" t="n">
         <v>-0.2875000000000005</v>
       </c>
       <c r="P334" t="n">
-        <v>0.05044340620592358</v>
+        <v>0.04984408033826604</v>
       </c>
       <c r="Q334" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>Ascendente</t>
+          <t>Estable</t>
         </is>
       </c>
       <c r="S334" t="b">
@@ -25827,10 +25827,10 @@
         <v>8</v>
       </c>
       <c r="G335" t="n">
-        <v>0.7926657263751763</v>
+        <v>0.7928118393234672</v>
       </c>
       <c r="H335" t="n">
-        <v>6.655123413258109</v>
+        <v>6.659254756871035</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -25849,16 +25849,16 @@
         <v>1</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.1448765867418906</v>
+        <v>-0.1407452431289649</v>
       </c>
       <c r="N335" t="n">
-        <v>0.1448765867418906</v>
+        <v>0.1407452431289649</v>
       </c>
       <c r="O335" t="n">
         <v>-0.1749999999999998</v>
       </c>
       <c r="P335" t="n">
-        <v>0.1166757757404788</v>
+        <v>0.1204677589851997</v>
       </c>
       <c r="Q335" t="inlineStr">
         <is>
@@ -25898,10 +25898,10 @@
         <v>8</v>
       </c>
       <c r="G336" t="n">
-        <v>0.8152327221438646</v>
+        <v>0.8153629316420014</v>
       </c>
       <c r="H336" t="n">
-        <v>6.85021156558533</v>
+        <v>6.851316067653276</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -25920,16 +25920,16 @@
         <v>1</v>
       </c>
       <c r="M336" t="n">
-        <v>0.2202115655853305</v>
+        <v>0.2213160676532766</v>
       </c>
       <c r="N336" t="n">
-        <v>0.2202115655853305</v>
+        <v>0.2213160676532766</v>
       </c>
       <c r="O336" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P336" t="n">
-        <v>0.1950881523272212</v>
+        <v>0.1920613107822415</v>
       </c>
       <c r="Q336" t="inlineStr">
         <is>
@@ -25969,10 +25969,10 @@
         <v>8</v>
       </c>
       <c r="G337" t="n">
-        <v>0.8349788434414669</v>
+        <v>0.8350951374207188</v>
       </c>
       <c r="H337" t="n">
-        <v>7.066805359661495</v>
+        <v>7.067463002114165</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -25991,16 +25991,16 @@
         <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>0.5768053596614946</v>
+        <v>0.5774630021141647</v>
       </c>
       <c r="N337" t="n">
-        <v>0.5768053596614946</v>
+        <v>0.5774630021141647</v>
       </c>
       <c r="O337" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P337" t="n">
-        <v>0.2165937940761644</v>
+        <v>0.2161469344608884</v>
       </c>
       <c r="Q337" t="inlineStr">
         <is>
@@ -26040,10 +26040,10 @@
         <v>8</v>
       </c>
       <c r="G338" t="n">
-        <v>0.8511988716502116</v>
+        <v>0.8513037350246653</v>
       </c>
       <c r="H338" t="n">
-        <v>7.148705923836389</v>
+        <v>7.148824524312897</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -26062,16 +26062,16 @@
         <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>0.6687059238363888</v>
+        <v>0.6688245243128961</v>
       </c>
       <c r="N338" t="n">
-        <v>0.6687059238363888</v>
+        <v>0.6688245243128961</v>
       </c>
       <c r="O338" t="n">
         <v>-0.009999999999999787</v>
       </c>
       <c r="P338" t="n">
-        <v>0.08190056417489444</v>
+        <v>0.08136152219873161</v>
       </c>
       <c r="Q338" t="inlineStr">
         <is>
@@ -26111,10 +26111,10 @@
         <v>8</v>
       </c>
       <c r="G339" t="n">
-        <v>0.8582510578279267</v>
+        <v>0.8583509513742071</v>
       </c>
       <c r="H339" t="n">
-        <v>7.205909732016925</v>
+        <v>7.206474630021141</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -26133,16 +26133,16 @@
         <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>0.6559097320169256</v>
+        <v>0.6564746300211413</v>
       </c>
       <c r="N339" t="n">
-        <v>0.6559097320169256</v>
+        <v>0.6564746300211413</v>
       </c>
       <c r="O339" t="n">
         <v>0.0699999999999994</v>
       </c>
       <c r="P339" t="n">
-        <v>0.05720380818053616</v>
+        <v>0.05765010570824458</v>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
@@ -26182,10 +26182,10 @@
         <v>8</v>
       </c>
       <c r="G340" t="n">
-        <v>0.8504936530324401</v>
+        <v>0.8505990133897111</v>
       </c>
       <c r="H340" t="n">
-        <v>7.14790832157969</v>
+        <v>7.148027484143763</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -26204,16 +26204,16 @@
         <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>0.6179083215796899</v>
+        <v>0.618027484143763</v>
       </c>
       <c r="N340" t="n">
-        <v>0.6179083215796899</v>
+        <v>0.618027484143763</v>
       </c>
       <c r="O340" t="n">
         <v>-0.01999999999999957</v>
       </c>
       <c r="P340" t="n">
-        <v>-0.05800141043723528</v>
+        <v>-0.05844714587737787</v>
       </c>
       <c r="Q340" t="inlineStr">
         <is>
@@ -26253,10 +26253,10 @@
         <v>8</v>
       </c>
       <c r="G341" t="n">
-        <v>0.8307475317348378</v>
+        <v>0.8308668076109936</v>
       </c>
       <c r="H341" t="n">
-        <v>7.02716972261401</v>
+        <v>7.028069062720225</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -26275,16 +26275,16 @@
         <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>0.6946697226140106</v>
+        <v>0.6955690627202253</v>
       </c>
       <c r="N341" t="n">
-        <v>0.6946697226140106</v>
+        <v>0.6955690627202253</v>
       </c>
       <c r="O341" t="n">
         <v>-0.1975000000000007</v>
       </c>
       <c r="P341" t="n">
-        <v>-0.12073859896568</v>
+        <v>-0.1199584214235383</v>
       </c>
       <c r="Q341" t="inlineStr">
         <is>
@@ -26324,10 +26324,10 @@
         <v>8</v>
       </c>
       <c r="G342" t="n">
-        <v>0.8110014104372355</v>
+        <v>0.8111346018322763</v>
       </c>
       <c r="H342" t="n">
-        <v>6.822425952045133</v>
+        <v>6.823932346723044</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -26346,16 +26346,16 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>0.632425952045133</v>
+        <v>0.6339323467230438</v>
       </c>
       <c r="N342" t="n">
-        <v>0.632425952045133</v>
+        <v>0.6339323467230438</v>
       </c>
       <c r="O342" t="n">
         <v>-0.1424999999999992</v>
       </c>
       <c r="P342" t="n">
-        <v>-0.2047437705688768</v>
+        <v>-0.2041367159971808</v>
       </c>
       <c r="Q342" t="inlineStr">
         <is>
@@ -26395,10 +26395,10 @@
         <v>8</v>
       </c>
       <c r="G343" t="n">
-        <v>0.7877291960507757</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="H343" t="n">
-        <v>6.62</v>
+        <v>6.62090909090909</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
@@ -26417,16 +26417,16 @@
         <v>1</v>
       </c>
       <c r="M343" t="n">
-        <v>0.6299999999999999</v>
+        <v>0.63090909090909</v>
       </c>
       <c r="N343" t="n">
-        <v>0.6299999999999999</v>
+        <v>0.63090909090909</v>
       </c>
       <c r="O343" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="P343" t="n">
-        <v>-0.2024259520451333</v>
+        <v>-0.203023255813954</v>
       </c>
       <c r="Q343" t="inlineStr">
         <is>
@@ -26466,10 +26466,10 @@
         <v>8</v>
       </c>
       <c r="G344" t="n">
-        <v>0.7637517630465445</v>
+        <v>0.7639182522903453</v>
       </c>
       <c r="H344" t="n">
-        <v>6.484016220028209</v>
+        <v>6.484957716701903</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -26488,16 +26488,16 @@
         <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>0.5640162200282095</v>
+        <v>0.5649577167019029</v>
       </c>
       <c r="N344" t="n">
-        <v>0.5640162200282095</v>
+        <v>0.5649577167019029</v>
       </c>
       <c r="O344" t="n">
         <v>-0.07000000000000028</v>
       </c>
       <c r="P344" t="n">
-        <v>-0.1359837799717907</v>
+        <v>-0.1359513742071874</v>
       </c>
       <c r="Q344" t="inlineStr">
         <is>
@@ -26537,10 +26537,10 @@
         <v>8</v>
       </c>
       <c r="G345" t="n">
-        <v>0.7418899858956276</v>
+        <v>0.7420718816067653</v>
       </c>
       <c r="H345" t="n">
-        <v>6.380290902679832</v>
+        <v>6.381062367864694</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
@@ -26559,16 +26559,16 @@
         <v>1</v>
       </c>
       <c r="M345" t="n">
-        <v>0.4002909026798314</v>
+        <v>0.4010623678646938</v>
       </c>
       <c r="N345" t="n">
-        <v>0.4002909026798314</v>
+        <v>0.4010623678646938</v>
       </c>
       <c r="O345" t="n">
         <v>0.0600000000000005</v>
       </c>
       <c r="P345" t="n">
-        <v>-0.1037253173483776</v>
+        <v>-0.1038953488372085</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
@@ -26608,10 +26608,10 @@
         <v>8</v>
       </c>
       <c r="G346" t="n">
-        <v>0.7186177715091678</v>
+        <v>0.718816067653277</v>
       </c>
       <c r="H346" t="n">
-        <v>6.235675246826516</v>
+        <v>6.237357293868921</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -26630,16 +26630,16 @@
         <v>1</v>
       </c>
       <c r="M346" t="n">
-        <v>0.1156752468265161</v>
+        <v>0.1173572938689214</v>
       </c>
       <c r="N346" t="n">
-        <v>0.1156752468265161</v>
+        <v>0.1173572938689214</v>
       </c>
       <c r="O346" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P346" t="n">
-        <v>-0.1446156558533156</v>
+        <v>-0.1437050739957728</v>
       </c>
       <c r="Q346" t="inlineStr">
         <is>
@@ -27809,10 +27809,10 @@
         <v>8</v>
       </c>
       <c r="G363" t="n">
-        <v>0.6459802538787024</v>
+        <v>0.6462297392529951</v>
       </c>
       <c r="H363" t="n">
-        <v>6.971861777150917</v>
+        <v>6.973165961945031</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -27831,16 +27831,16 @@
         <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>-1.490638222849084</v>
+        <v>-1.489334038054969</v>
       </c>
       <c r="N363" t="n">
-        <v>1.490638222849084</v>
+        <v>1.489334038054969</v>
       </c>
       <c r="O363" t="n">
         <v>-0.254999999999999</v>
       </c>
       <c r="P363" t="n">
-        <v>0.1292811885034046</v>
+        <v>0.1305853732975191</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
@@ -27880,10 +27880,10 @@
         <v>8</v>
       </c>
       <c r="G364" t="n">
-        <v>0.6544428772919605</v>
+        <v>0.6546863988724454</v>
       </c>
       <c r="H364" t="n">
-        <v>7.011466854724964</v>
+        <v>7.013164200140944</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -27902,16 +27902,16 @@
         <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>-1.301033145275036</v>
+        <v>-1.299335799859056</v>
       </c>
       <c r="N364" t="n">
-        <v>1.301033145275036</v>
+        <v>1.299335799859056</v>
       </c>
       <c r="O364" t="n">
         <v>-0.1500000000000004</v>
       </c>
       <c r="P364" t="n">
-        <v>0.03960507757404752</v>
+        <v>0.03999823819591342</v>
       </c>
       <c r="Q364" t="inlineStr">
         <is>
@@ -27951,10 +27951,10 @@
         <v>8</v>
       </c>
       <c r="G365" t="n">
-        <v>0.6671368124118476</v>
+        <v>0.6673713883016209</v>
       </c>
       <c r="H365" t="n">
-        <v>7.06997179125529</v>
+        <v>7.071578576462298</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -27973,16 +27973,16 @@
         <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>-1.060028208744711</v>
+        <v>-1.058421423537703</v>
       </c>
       <c r="N365" t="n">
-        <v>1.060028208744711</v>
+        <v>1.058421423537703</v>
       </c>
       <c r="O365" t="n">
         <v>-0.1824999999999992</v>
       </c>
       <c r="P365" t="n">
-        <v>0.0585049365303254</v>
+        <v>0.0584143763213536</v>
       </c>
       <c r="Q365" t="inlineStr">
         <is>
@@ -28022,10 +28022,10 @@
         <v>8</v>
       </c>
       <c r="G366" t="n">
-        <v>0.6812411847672779</v>
+        <v>0.6814658210007047</v>
       </c>
       <c r="H366" t="n">
-        <v>7.167766220028208</v>
+        <v>7.168646934460887</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -28044,16 +28044,16 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.919733779971792</v>
+        <v>-0.9188530655391132</v>
       </c>
       <c r="N366" t="n">
-        <v>0.919733779971792</v>
+        <v>0.9188530655391132</v>
       </c>
       <c r="O366" t="n">
         <v>-0.04250000000000043</v>
       </c>
       <c r="P366" t="n">
-        <v>0.09779442877291888</v>
+        <v>0.09706835799858915</v>
       </c>
       <c r="Q366" t="inlineStr">
         <is>
@@ -28093,10 +28093,10 @@
         <v>8</v>
       </c>
       <c r="G367" t="n">
-        <v>0.6889985895627645</v>
+        <v>0.6892177589852009</v>
       </c>
       <c r="H367" t="n">
-        <v>7.193853432063941</v>
+        <v>7.194744538407329</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -28115,16 +28115,16 @@
         <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>-1.03614656793606</v>
+        <v>-1.035255461592671</v>
       </c>
       <c r="N367" t="n">
-        <v>1.03614656793606</v>
+        <v>1.035255461592671</v>
       </c>
       <c r="O367" t="n">
         <v>0.1425000000000001</v>
       </c>
       <c r="P367" t="n">
-        <v>0.0260872120357325</v>
+        <v>0.02609760394644223</v>
       </c>
       <c r="Q367" t="inlineStr">
         <is>
@@ -28164,10 +28164,10 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>0.6904090267983075</v>
+        <v>0.6906272022551092</v>
       </c>
       <c r="H368" t="n">
-        <v>7.199588034790786</v>
+        <v>7.200475099835566</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -28186,16 +28186,16 @@
         <v>1</v>
       </c>
       <c r="M368" t="n">
-        <v>-0.8429119652092147</v>
+        <v>-0.8420249001644349</v>
       </c>
       <c r="N368" t="n">
-        <v>0.8429119652092147</v>
+        <v>0.8420249001644349</v>
       </c>
       <c r="O368" t="n">
         <v>-0.1875</v>
       </c>
       <c r="P368" t="n">
-        <v>0.005734602726844784</v>
+        <v>0.005730561428236136</v>
       </c>
       <c r="Q368" t="inlineStr">
         <is>
@@ -28235,10 +28235,10 @@
         <v>8</v>
       </c>
       <c r="G369" t="n">
-        <v>0.6847672778561354</v>
+        <v>0.6849894291754757</v>
       </c>
       <c r="H369" t="n">
-        <v>7.182827926657264</v>
+        <v>7.184376321353065</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -28257,16 +28257,16 @@
         <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.7671720733427358</v>
+        <v>-0.7656236786469348</v>
       </c>
       <c r="N369" t="n">
-        <v>0.7671720733427358</v>
+        <v>0.7656236786469348</v>
       </c>
       <c r="O369" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P369" t="n">
-        <v>-0.01676010813352136</v>
+        <v>-0.01609877848250019</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
@@ -28306,10 +28306,10 @@
         <v>8</v>
       </c>
       <c r="G370" t="n">
-        <v>0.6727785613540197</v>
+        <v>0.6730091613812544</v>
       </c>
       <c r="H370" t="n">
-        <v>7.114633286318759</v>
+        <v>7.115218463706836</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -28328,16 +28328,16 @@
         <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.8653667136812411</v>
+        <v>-0.8647815362931643</v>
       </c>
       <c r="N370" t="n">
-        <v>0.8653667136812411</v>
+        <v>0.8647815362931643</v>
       </c>
       <c r="O370" t="n">
         <v>0.03000000000000025</v>
       </c>
       <c r="P370" t="n">
-        <v>-0.06819464033850497</v>
+        <v>-0.06915785764622928</v>
       </c>
       <c r="Q370" t="inlineStr">
         <is>
@@ -28377,10 +28377,10 @@
         <v>8</v>
       </c>
       <c r="G371" t="n">
-        <v>0.653737658674189</v>
+        <v>0.6539816772374912</v>
       </c>
       <c r="H371" t="n">
-        <v>7.006551480959097</v>
+        <v>7.008252290345314</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -28399,16 +28399,16 @@
         <v>1</v>
       </c>
       <c r="M371" t="n">
-        <v>-1.028448519040903</v>
+        <v>-1.026747709654686</v>
       </c>
       <c r="N371" t="n">
-        <v>1.028448519040903</v>
+        <v>1.026747709654686</v>
       </c>
       <c r="O371" t="n">
         <v>0.05499999999999972</v>
       </c>
       <c r="P371" t="n">
-        <v>-0.1080818053596619</v>
+        <v>-0.1069661733615224</v>
       </c>
       <c r="Q371" t="inlineStr">
         <is>
@@ -28448,10 +28448,10 @@
         <v>8</v>
       </c>
       <c r="G372" t="n">
-        <v>0.6318758815232722</v>
+        <v>0.6321353065539113</v>
       </c>
       <c r="H372" t="n">
-        <v>6.938543723554302</v>
+        <v>6.93899577167019</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -28470,16 +28470,16 @@
         <v>1</v>
       </c>
       <c r="M372" t="n">
-        <v>-0.9714562764456982</v>
+        <v>-0.9710042283298099</v>
       </c>
       <c r="N372" t="n">
-        <v>0.9714562764456982</v>
+        <v>0.9710042283298099</v>
       </c>
       <c r="O372" t="n">
         <v>-0.125</v>
       </c>
       <c r="P372" t="n">
-        <v>-0.06800775740479548</v>
+        <v>-0.0692565186751235</v>
       </c>
       <c r="Q372" t="inlineStr">
         <is>
@@ -28519,10 +28519,10 @@
         <v>8</v>
       </c>
       <c r="G373" t="n">
-        <v>0.6170662905500706</v>
+        <v>0.6173361522198731</v>
       </c>
       <c r="H373" t="n">
-        <v>6.884345028208744</v>
+        <v>6.885520613107822</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -28541,16 +28541,16 @@
         <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.805654971791256</v>
+        <v>-0.8044793868921785</v>
       </c>
       <c r="N373" t="n">
-        <v>0.805654971791256</v>
+        <v>0.8044793868921785</v>
       </c>
       <c r="O373" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P373" t="n">
-        <v>-0.05419869534555755</v>
+        <v>-0.05347515856236829</v>
       </c>
       <c r="Q373" t="inlineStr">
         <is>
@@ -28590,10 +28590,10 @@
         <v>8</v>
       </c>
       <c r="G374" t="n">
-        <v>0.5994358251057827</v>
+        <v>0.5997181113460183</v>
       </c>
       <c r="H374" t="n">
-        <v>6.799758462623413</v>
+        <v>6.800017618040873</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -28612,16 +28612,16 @@
         <v>1</v>
       </c>
       <c r="M374" t="n">
-        <v>-0.6602415373765869</v>
+        <v>-0.6599823819591268</v>
       </c>
       <c r="N374" t="n">
-        <v>0.6602415373765869</v>
+        <v>0.6599823819591268</v>
       </c>
       <c r="O374" t="n">
         <v>-0.2300000000000004</v>
       </c>
       <c r="P374" t="n">
-        <v>-0.08458656558533129</v>
+        <v>-0.08550299506694881</v>
       </c>
       <c r="Q374" t="inlineStr">
         <is>
@@ -28661,10 +28661,10 @@
         <v>8</v>
       </c>
       <c r="G375" t="n">
-        <v>0.5846262341325811</v>
+        <v>0.5849189570119803</v>
       </c>
       <c r="H375" t="n">
-        <v>6.761855606488012</v>
+        <v>6.762110641296688</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -28683,16 +28683,16 @@
         <v>1</v>
       </c>
       <c r="M375" t="n">
-        <v>-0.5181443935119887</v>
+        <v>-0.5178893587033127</v>
       </c>
       <c r="N375" t="n">
-        <v>0.5181443935119887</v>
+        <v>0.5178893587033127</v>
       </c>
       <c r="O375" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P375" t="n">
-        <v>-0.03790285613540156</v>
+        <v>-0.03790697674418553</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
@@ -28732,10 +28732,10 @@
         <v>8</v>
       </c>
       <c r="G376" t="n">
-        <v>0.5662905500705219</v>
+        <v>0.5665961945031712</v>
       </c>
       <c r="H376" t="n">
-        <v>6.687045133991537</v>
+        <v>6.689175475687104</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -28754,16 +28754,16 @@
         <v>1</v>
       </c>
       <c r="M376" t="n">
-        <v>-0.422954866008463</v>
+        <v>-0.4208245243128967</v>
       </c>
       <c r="N376" t="n">
-        <v>0.422954866008463</v>
+        <v>0.4208245243128967</v>
       </c>
       <c r="O376" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.07481047249647421</v>
+        <v>-0.07293516560958402</v>
       </c>
       <c r="Q376" t="inlineStr">
         <is>
@@ -29933,10 +29933,10 @@
         <v>8</v>
       </c>
       <c r="G393" t="n">
-        <v>0.6572637517630465</v>
+        <v>0.656800563777308</v>
       </c>
       <c r="H393" t="n">
-        <v>5.804301833568406</v>
+        <v>5.80369274136716</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -29955,16 +29955,16 @@
         <v>1</v>
       </c>
       <c r="M393" t="n">
-        <v>1.014301833568405</v>
+        <v>1.013692741367159</v>
       </c>
       <c r="N393" t="n">
-        <v>1.014301833568405</v>
+        <v>1.013692741367159</v>
       </c>
       <c r="O393" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P393" t="n">
-        <v>-0.6612202407133037</v>
+        <v>-0.6618293329145502</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
@@ -30004,10 +30004,10 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>0.5627644569816643</v>
+        <v>0.5623678646934461</v>
       </c>
       <c r="H394" t="n">
-        <v>5.497552891396333</v>
+        <v>5.496041226215644</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -30026,16 +30026,16 @@
         <v>1</v>
       </c>
       <c r="M394" t="n">
-        <v>0.8275528913963326</v>
+        <v>0.8260412262156445</v>
       </c>
       <c r="N394" t="n">
-        <v>0.8275528913963326</v>
+        <v>0.8260412262156445</v>
       </c>
       <c r="O394" t="n">
         <v>-0.120000000000001</v>
       </c>
       <c r="P394" t="n">
-        <v>-0.3067489421720735</v>
+        <v>-0.3076515151515151</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -30075,10 +30075,10 @@
         <v>8</v>
       </c>
       <c r="G395" t="n">
-        <v>0.5409026798307476</v>
+        <v>0.5405214940098662</v>
       </c>
       <c r="H395" t="n">
-        <v>5.455643511988717</v>
+        <v>5.455392882311487</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -30097,16 +30097,16 @@
         <v>1</v>
       </c>
       <c r="M395" t="n">
-        <v>0.9156435119887165</v>
+        <v>0.9153928823114867</v>
       </c>
       <c r="N395" t="n">
-        <v>0.9156435119887165</v>
+        <v>0.9153928823114867</v>
       </c>
       <c r="O395" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P395" t="n">
-        <v>-0.04190937940761597</v>
+        <v>-0.04064834390415761</v>
       </c>
       <c r="Q395" t="inlineStr">
         <is>
@@ -30146,10 +30146,10 @@
         <v>8</v>
       </c>
       <c r="G396" t="n">
-        <v>0.5944992947813822</v>
+        <v>0.5940803382663847</v>
       </c>
       <c r="H396" t="n">
-        <v>5.635883286318759</v>
+        <v>5.635607822410148</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -30168,16 +30168,16 @@
         <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>1.195883286318758</v>
+        <v>1.195607822410148</v>
       </c>
       <c r="N396" t="n">
-        <v>1.195883286318758</v>
+        <v>1.195607822410148</v>
       </c>
       <c r="O396" t="n">
         <v>-0.09999999999999964</v>
       </c>
       <c r="P396" t="n">
-        <v>0.1802397743300421</v>
+        <v>0.1802149400986615</v>
       </c>
       <c r="Q396" t="inlineStr">
         <is>
@@ -30217,10 +30217,10 @@
         <v>8</v>
       </c>
       <c r="G397" t="n">
-        <v>0.6325811001410437</v>
+        <v>0.6321353065539113</v>
       </c>
       <c r="H397" t="n">
-        <v>5.755922073342737</v>
+        <v>5.755628964059198</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -30239,16 +30239,16 @@
         <v>1</v>
       </c>
       <c r="M397" t="n">
-        <v>1.315922073342737</v>
+        <v>1.315628964059197</v>
       </c>
       <c r="N397" t="n">
-        <v>1.315922073342737</v>
+        <v>1.315628964059197</v>
       </c>
       <c r="O397" t="n">
         <v>0</v>
       </c>
       <c r="P397" t="n">
-        <v>0.1200387870239785</v>
+        <v>0.1200211416490493</v>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>8</v>
       </c>
       <c r="G398" t="n">
-        <v>0.5930888575458392</v>
+        <v>0.5926708949964764</v>
       </c>
       <c r="H398" t="n">
-        <v>5.634823695345557</v>
+        <v>5.633724453840733</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -30310,16 +30310,16 @@
         <v>1</v>
       </c>
       <c r="M398" t="n">
-        <v>1.234823695345557</v>
+        <v>1.233724453840733</v>
       </c>
       <c r="N398" t="n">
-        <v>1.234823695345557</v>
+        <v>1.233724453840733</v>
       </c>
       <c r="O398" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P398" t="n">
-        <v>-0.1210983779971802</v>
+        <v>-0.1219045102184646</v>
       </c>
       <c r="Q398" t="inlineStr">
         <is>
@@ -30359,10 +30359,10 @@
         <v>8</v>
       </c>
       <c r="G399" t="n">
-        <v>0.4774330042313117</v>
+        <v>0.4770965468639887</v>
       </c>
       <c r="H399" t="n">
-        <v>5.188912200282088</v>
+        <v>5.188690979563074</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -30381,16 +30381,16 @@
         <v>1</v>
       </c>
       <c r="M399" t="n">
-        <v>0.8089122002820881</v>
+        <v>0.8086909795630737</v>
       </c>
       <c r="N399" t="n">
-        <v>0.8089122002820881</v>
+        <v>0.8086909795630737</v>
       </c>
       <c r="O399" t="n">
         <v>-0.02000000000000046</v>
       </c>
       <c r="P399" t="n">
-        <v>-0.4459114950634691</v>
+        <v>-0.4450334742776594</v>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
@@ -30430,10 +30430,10 @@
         <v>8</v>
       </c>
       <c r="G400" t="n">
-        <v>0.3688293370944993</v>
+        <v>0.368569415081043</v>
       </c>
       <c r="H400" t="n">
-        <v>4.842505289139633</v>
+        <v>4.841671952078929</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -30452,16 +30452,16 @@
         <v>1</v>
       </c>
       <c r="M400" t="n">
-        <v>0.7025052891396335</v>
+        <v>0.7016719520789296</v>
       </c>
       <c r="N400" t="n">
-        <v>0.7025052891396335</v>
+        <v>0.7016719520789296</v>
       </c>
       <c r="O400" t="n">
         <v>-0.2400000000000002</v>
       </c>
       <c r="P400" t="n">
-        <v>-0.3464069111424548</v>
+        <v>-0.3470190274841443</v>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
@@ -30501,10 +30501,10 @@
         <v>8</v>
       </c>
       <c r="G401" t="n">
-        <v>0.3244005641748942</v>
+        <v>0.3241719520789288</v>
       </c>
       <c r="H401" t="n">
-        <v>4.692020451339916</v>
+        <v>4.690216701902749</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -30523,16 +30523,16 @@
         <v>1</v>
       </c>
       <c r="M401" t="n">
-        <v>0.8220204513399159</v>
+        <v>0.8202167019027486</v>
       </c>
       <c r="N401" t="n">
-        <v>0.8220204513399159</v>
+        <v>0.8202167019027486</v>
       </c>
       <c r="O401" t="n">
         <v>-0.2699999999999996</v>
       </c>
       <c r="P401" t="n">
-        <v>-0.1504848377997172</v>
+        <v>-0.1514552501761806</v>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
@@ -30572,10 +30572,10 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>0.3504936530324401</v>
+        <v>0.350246652572234</v>
       </c>
       <c r="H402" t="n">
-        <v>4.805449576868829</v>
+        <v>4.805287174066244</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -30594,16 +30594,16 @@
         <v>1</v>
       </c>
       <c r="M402" t="n">
-        <v>1.085449576868829</v>
+        <v>1.085287174066244</v>
       </c>
       <c r="N402" t="n">
-        <v>1.085449576868829</v>
+        <v>1.085287174066244</v>
       </c>
       <c r="O402" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P402" t="n">
-        <v>0.1134291255289135</v>
+        <v>0.1150704721634952</v>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -30643,10 +30643,10 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>0.5282087447108603</v>
+        <v>0.5278365045806906</v>
       </c>
       <c r="H403" t="n">
-        <v>5.439594499294781</v>
+        <v>5.439105003523608</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -30665,16 +30665,16 @@
         <v>1</v>
       </c>
       <c r="M403" t="n">
-        <v>1.739594499294781</v>
+        <v>1.739105003523608</v>
       </c>
       <c r="N403" t="n">
-        <v>1.739594499294781</v>
+        <v>1.739105003523608</v>
       </c>
       <c r="O403" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P403" t="n">
-        <v>0.6341449224259517</v>
+        <v>0.6338178294573638</v>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
@@ -30714,10 +30714,10 @@
         <v>8</v>
       </c>
       <c r="G404" t="n">
-        <v>0.7595204513399154</v>
+        <v>0.7596899224806202</v>
       </c>
       <c r="H404" t="n">
-        <v>6.099384696755994</v>
+        <v>6.099496124031008</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -30736,16 +30736,16 @@
         <v>1</v>
       </c>
       <c r="M404" t="n">
-        <v>2.259384696755994</v>
+        <v>2.259496124031008</v>
       </c>
       <c r="N404" t="n">
-        <v>2.259384696755994</v>
+        <v>2.259496124031008</v>
       </c>
       <c r="O404" t="n">
         <v>0.1399999999999997</v>
       </c>
       <c r="P404" t="n">
-        <v>0.6597901974612128</v>
+        <v>0.6603911205074002</v>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
@@ -30785,10 +30785,10 @@
         <v>8</v>
       </c>
       <c r="G405" t="n">
-        <v>0.8300423131170663</v>
+        <v>0.8301620859760395</v>
       </c>
       <c r="H405" t="n">
-        <v>6.33677538787024</v>
+        <v>6.337484143763214</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -30807,16 +30807,16 @@
         <v>1</v>
       </c>
       <c r="M405" t="n">
-        <v>2.316775387870241</v>
+        <v>2.317484143763214</v>
       </c>
       <c r="N405" t="n">
-        <v>2.316775387870241</v>
+        <v>2.317484143763214</v>
       </c>
       <c r="O405" t="n">
         <v>0.1799999999999997</v>
       </c>
       <c r="P405" t="n">
-        <v>0.2373906911142463</v>
+        <v>0.2379880197322057</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
@@ -30856,10 +30856,10 @@
         <v>8</v>
       </c>
       <c r="G406" t="n">
-        <v>0.814527503526093</v>
+        <v>0.8146582100070472</v>
       </c>
       <c r="H406" t="n">
-        <v>6.283018335684062</v>
+        <v>6.283877730796336</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -30878,16 +30878,16 @@
         <v>1</v>
       </c>
       <c r="M406" t="n">
-        <v>2.183018335684062</v>
+        <v>2.183877730796336</v>
       </c>
       <c r="N406" t="n">
-        <v>2.183018335684062</v>
+        <v>2.183877730796336</v>
       </c>
       <c r="O406" t="n">
         <v>0.08000000000000007</v>
       </c>
       <c r="P406" t="n">
-        <v>-0.0537570521861781</v>
+        <v>-0.05360641296687785</v>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
@@ -32057,10 +32057,10 @@
         <v>8</v>
       </c>
       <c r="G423" t="n">
-        <v>0.8300423131170663</v>
+        <v>0.8301620859760395</v>
       </c>
       <c r="H423" t="n">
-        <v>5.567579337094499</v>
+        <v>5.568865398167723</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -32079,16 +32079,16 @@
         <v>1</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.7999206629055005</v>
+        <v>-0.7986346018322772</v>
       </c>
       <c r="N423" t="n">
-        <v>0.7999206629055005</v>
+        <v>0.7986346018322772</v>
       </c>
       <c r="O423" t="n">
         <v>-0.07500000000000018</v>
       </c>
       <c r="P423" t="n">
-        <v>-1.471350235435283</v>
+        <v>-1.47006417436206</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
@@ -32128,10 +32128,10 @@
         <v>8</v>
       </c>
       <c r="G424" t="n">
-        <v>0.8279266572637518</v>
+        <v>0.8280479210711769</v>
       </c>
       <c r="H424" t="n">
-        <v>5.551889985895628</v>
+        <v>5.552931642001409</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -32150,16 +32150,16 @@
         <v>1</v>
       </c>
       <c r="M424" t="n">
-        <v>-0.7656100141043716</v>
+        <v>-0.7645683579985905</v>
       </c>
       <c r="N424" t="n">
-        <v>0.7656100141043716</v>
+        <v>0.7645683579985905</v>
       </c>
       <c r="O424" t="n">
         <v>-0.04999999999999982</v>
       </c>
       <c r="P424" t="n">
-        <v>-0.01568935119887094</v>
+        <v>-0.0159337561663131</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
@@ -32199,10 +32199,10 @@
         <v>8</v>
       </c>
       <c r="G425" t="n">
-        <v>0.8215796897038082</v>
+        <v>0.8217054263565892</v>
       </c>
       <c r="H425" t="n">
-        <v>5.507369534555713</v>
+        <v>5.508449612403101</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -32221,16 +32221,16 @@
         <v>1</v>
       </c>
       <c r="M425" t="n">
-        <v>-0.7526304654442866</v>
+        <v>-0.7515503875968985</v>
       </c>
       <c r="N425" t="n">
-        <v>0.7526304654442866</v>
+        <v>0.7515503875968985</v>
       </c>
       <c r="O425" t="n">
         <v>-0.05750000000000011</v>
       </c>
       <c r="P425" t="n">
-        <v>-0.04452045133991511</v>
+        <v>-0.04448202959830816</v>
       </c>
       <c r="Q425" t="inlineStr">
         <is>
@@ -32270,10 +32270,10 @@
         <v>8</v>
       </c>
       <c r="G426" t="n">
-        <v>0.8187588152327221</v>
+        <v>0.8188865398167724</v>
       </c>
       <c r="H426" t="n">
-        <v>5.491569111424542</v>
+        <v>5.492117688513038</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -32292,16 +32292,16 @@
         <v>1</v>
       </c>
       <c r="M426" t="n">
-        <v>-0.6384308885754582</v>
+        <v>-0.6378823114869618</v>
       </c>
       <c r="N426" t="n">
-        <v>0.6384308885754582</v>
+        <v>0.6378823114869618</v>
       </c>
       <c r="O426" t="n">
         <v>-0.1299999999999999</v>
       </c>
       <c r="P426" t="n">
-        <v>-0.01580042313117147</v>
+        <v>-0.01633192389006322</v>
       </c>
       <c r="Q426" t="inlineStr">
         <is>
@@ -32341,10 +32341,10 @@
         <v>8</v>
       </c>
       <c r="G427" t="n">
-        <v>0.8095909732016925</v>
+        <v>0.8097251585623678</v>
       </c>
       <c r="H427" t="n">
-        <v>5.384144922425952</v>
+        <v>5.384577167019026</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -32363,16 +32363,16 @@
         <v>1</v>
       </c>
       <c r="M427" t="n">
-        <v>-0.6058550775740486</v>
+        <v>-0.6054228329809739</v>
       </c>
       <c r="N427" t="n">
-        <v>0.6058550775740486</v>
+        <v>0.6054228329809739</v>
       </c>
       <c r="O427" t="n">
         <v>-0.1399999999999997</v>
       </c>
       <c r="P427" t="n">
-        <v>-0.1074241889985901</v>
+        <v>-0.1075405214940117</v>
       </c>
       <c r="Q427" t="inlineStr">
         <is>
@@ -32412,10 +32412,10 @@
         <v>8</v>
       </c>
       <c r="G428" t="n">
-        <v>0.7891396332863188</v>
+        <v>0.7892882311486963</v>
       </c>
       <c r="H428" t="n">
-        <v>5.22967736248237</v>
+        <v>5.229996476391825</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -32434,16 +32434,16 @@
         <v>1</v>
       </c>
       <c r="M428" t="n">
-        <v>-0.4778226375176295</v>
+        <v>-0.4775035236081742</v>
       </c>
       <c r="N428" t="n">
-        <v>0.4778226375176295</v>
+        <v>0.4775035236081742</v>
       </c>
       <c r="O428" t="n">
         <v>-0.2825000000000006</v>
       </c>
       <c r="P428" t="n">
-        <v>-0.1544675599435816</v>
+        <v>-0.1545806906272009</v>
       </c>
       <c r="Q428" t="inlineStr">
         <is>
@@ -32483,10 +32483,10 @@
         <v>8</v>
       </c>
       <c r="G429" t="n">
-        <v>0.7715091678420311</v>
+        <v>0.7716701902748414</v>
       </c>
       <c r="H429" t="n">
-        <v>5.103631875881523</v>
+        <v>5.104323467230444</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
@@ -32505,16 +32505,16 @@
         <v>1</v>
       </c>
       <c r="M429" t="n">
-        <v>-0.4563681241184767</v>
+        <v>-0.455676532769556</v>
       </c>
       <c r="N429" t="n">
-        <v>0.4563681241184767</v>
+        <v>0.455676532769556</v>
       </c>
       <c r="O429" t="n">
         <v>-0.1475</v>
       </c>
       <c r="P429" t="n">
-        <v>-0.1260454866008471</v>
+        <v>-0.1256730091613818</v>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
@@ -32554,10 +32554,10 @@
         <v>8</v>
       </c>
       <c r="G430" t="n">
-        <v>0.7468265162200282</v>
+        <v>0.7470049330514447</v>
       </c>
       <c r="H430" t="n">
-        <v>4.952619887165021</v>
+        <v>4.953386187455955</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -32576,16 +32576,16 @@
         <v>1</v>
       </c>
       <c r="M430" t="n">
-        <v>-0.387380112834979</v>
+        <v>-0.386613812544045</v>
       </c>
       <c r="N430" t="n">
-        <v>0.387380112834979</v>
+        <v>0.386613812544045</v>
       </c>
       <c r="O430" t="n">
         <v>-0.2199999999999998</v>
       </c>
       <c r="P430" t="n">
-        <v>-0.151011988716502</v>
+        <v>-0.1509372797744888</v>
       </c>
       <c r="Q430" t="inlineStr">
         <is>
@@ -32625,10 +32625,10 @@
         <v>8</v>
       </c>
       <c r="G431" t="n">
-        <v>0.7193229901269393</v>
+        <v>0.7195207892882312</v>
       </c>
       <c r="H431" t="n">
-        <v>4.82</v>
+        <v>4.820341789992954</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
@@ -32647,16 +32647,16 @@
         <v>1</v>
       </c>
       <c r="M431" t="n">
-        <v>-0.2924999999999995</v>
+        <v>-0.2921582100070461</v>
       </c>
       <c r="N431" t="n">
-        <v>0.2924999999999995</v>
+        <v>0.2921582100070461</v>
       </c>
       <c r="O431" t="n">
         <v>-0.2275</v>
       </c>
       <c r="P431" t="n">
-        <v>-0.1326198871650206</v>
+        <v>-0.1330443974630011</v>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
@@ -32696,10 +32696,10 @@
         <v>8</v>
       </c>
       <c r="G432" t="n">
-        <v>0.6946403385049366</v>
+        <v>0.6948555320648344</v>
       </c>
       <c r="H432" t="n">
-        <v>4.651740126939352</v>
+        <v>4.652202255109231</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -32718,16 +32718,16 @@
         <v>1</v>
       </c>
       <c r="M432" t="n">
-        <v>-0.3582598730606481</v>
+        <v>-0.3577977448907683</v>
       </c>
       <c r="N432" t="n">
-        <v>0.3582598730606481</v>
+        <v>0.3577977448907683</v>
       </c>
       <c r="O432" t="n">
         <v>-0.1025</v>
       </c>
       <c r="P432" t="n">
-        <v>-0.1682598730606486</v>
+        <v>-0.1681395348837222</v>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
@@ -32767,10 +32767,10 @@
         <v>8</v>
       </c>
       <c r="G433" t="n">
-        <v>0.6847672778561354</v>
+        <v>0.6849894291754757</v>
       </c>
       <c r="H433" t="n">
-        <v>4.621518864598025</v>
+        <v>4.621757399577167</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
@@ -32789,16 +32789,16 @@
         <v>1</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.2184811354019747</v>
+        <v>-0.2182426004228333</v>
       </c>
       <c r="N433" t="n">
-        <v>0.2184811354019747</v>
+        <v>0.2182426004228333</v>
       </c>
       <c r="O433" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P433" t="n">
-        <v>-0.03022126234132649</v>
+        <v>-0.03044485553206489</v>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
@@ -32838,10 +32838,10 @@
         <v>8</v>
       </c>
       <c r="G434" t="n">
-        <v>0.689703808180536</v>
+        <v>0.689922480620155</v>
       </c>
       <c r="H434" t="n">
-        <v>4.638185237423602</v>
+        <v>4.638811369509043</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -32860,16 +32860,16 @@
         <v>1</v>
       </c>
       <c r="M434" t="n">
-        <v>-0.08181476257639808</v>
+        <v>-0.08118863049095637</v>
       </c>
       <c r="N434" t="n">
-        <v>0.08181476257639808</v>
+        <v>0.08118863049095637</v>
       </c>
       <c r="O434" t="n">
         <v>-0.1200000000000001</v>
       </c>
       <c r="P434" t="n">
-        <v>0.01666637282557648</v>
+        <v>0.0170539699318768</v>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
@@ -32909,10 +32909,10 @@
         <v>8</v>
       </c>
       <c r="G435" t="n">
-        <v>0.7094499294781382</v>
+        <v>0.7096546863988724</v>
       </c>
       <c r="H435" t="n">
-        <v>4.746116596144804</v>
+        <v>4.747289170777543</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -32931,16 +32931,16 @@
         <v>1</v>
       </c>
       <c r="M435" t="n">
-        <v>0.1861165961448048</v>
+        <v>0.187289170777543</v>
       </c>
       <c r="N435" t="n">
-        <v>0.1861165961448048</v>
+        <v>0.187289170777543</v>
       </c>
       <c r="O435" t="n">
         <v>-0.1600000000000001</v>
       </c>
       <c r="P435" t="n">
-        <v>0.1079313587212027</v>
+        <v>0.1084778012684993</v>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
@@ -32980,10 +32980,10 @@
         <v>8</v>
       </c>
       <c r="G436" t="n">
-        <v>0.7256699576868829</v>
+        <v>0.7258632840028189</v>
       </c>
       <c r="H436" t="n">
-        <v>4.846752468265162</v>
+        <v>4.847582804792107</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -33002,16 +33002,16 @@
         <v>1</v>
       </c>
       <c r="M436" t="n">
-        <v>0.4567524682651625</v>
+        <v>0.4575828047921071</v>
       </c>
       <c r="N436" t="n">
-        <v>0.4567524682651625</v>
+        <v>0.4575828047921071</v>
       </c>
       <c r="O436" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P436" t="n">
-        <v>0.1006358721203577</v>
+        <v>0.1002936340145641</v>
       </c>
       <c r="Q436" t="inlineStr">
         <is>
@@ -33051,10 +33051,10 @@
         <v>8</v>
       </c>
       <c r="G437" t="n">
-        <v>0.8236953455571228</v>
+        <v>0.8238195912614518</v>
       </c>
       <c r="H437" t="n">
-        <v>3.502387165021157</v>
+        <v>3.504064482029599</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -33073,10 +33073,10 @@
         <v>1</v>
       </c>
       <c r="M437" t="n">
-        <v>-0.9376128349788435</v>
+        <v>-0.9359355179704019</v>
       </c>
       <c r="N437" t="n">
-        <v>0.9376128349788435</v>
+        <v>0.9359355179704019</v>
       </c>
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
@@ -33116,10 +33116,10 @@
         <v>8</v>
       </c>
       <c r="G438" t="n">
-        <v>0.8095909732016925</v>
+        <v>0.8097251585623678</v>
       </c>
       <c r="H438" t="n">
-        <v>3.353582510578279</v>
+        <v>3.355031712473572</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -33138,16 +33138,16 @@
         <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>-0.8889174894217216</v>
+        <v>-0.8874682875264281</v>
       </c>
       <c r="N438" t="n">
-        <v>0.8889174894217216</v>
+        <v>0.8874682875264281</v>
       </c>
       <c r="O438" t="n">
         <v>-0.1974999999999998</v>
       </c>
       <c r="P438" t="n">
-        <v>-0.1488046544428778</v>
+        <v>-0.1490327695560261</v>
       </c>
       <c r="Q438" t="inlineStr">
         <is>
@@ -33187,10 +33187,10 @@
         <v>8</v>
       </c>
       <c r="G439" t="n">
-        <v>0.8004231311706629</v>
+        <v>0.8005637773079634</v>
       </c>
       <c r="H439" t="n">
-        <v>3.29614245416079</v>
+        <v>3.296522198731501</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -33209,16 +33209,16 @@
         <v>1</v>
       </c>
       <c r="M439" t="n">
-        <v>-0.8138575458392108</v>
+        <v>-0.8134778012684993</v>
       </c>
       <c r="N439" t="n">
-        <v>0.8138575458392108</v>
+        <v>0.8134778012684993</v>
       </c>
       <c r="O439" t="n">
         <v>-0.1325000000000003</v>
       </c>
       <c r="P439" t="n">
-        <v>-0.0574400564174895</v>
+        <v>-0.05850951374207147</v>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
@@ -33258,10 +33258,10 @@
         <v>8</v>
       </c>
       <c r="G440" t="n">
-        <v>0.8046544428772919</v>
+        <v>0.8047921071176886</v>
       </c>
       <c r="H440" t="n">
-        <v>3.320200987306065</v>
+        <v>3.321316067653278</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -33280,16 +33280,16 @@
         <v>1</v>
       </c>
       <c r="M440" t="n">
-        <v>-0.6497990126939355</v>
+        <v>-0.6486839323467226</v>
       </c>
       <c r="N440" t="n">
-        <v>0.6497990126939355</v>
+        <v>0.6486839323467226</v>
       </c>
       <c r="O440" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P440" t="n">
-        <v>0.02405853314527517</v>
+        <v>0.0247938689217766</v>
       </c>
       <c r="Q440" t="inlineStr">
         <is>
@@ -33329,10 +33329,10 @@
         <v>8</v>
       </c>
       <c r="G441" t="n">
-        <v>0.8222849083215797</v>
+        <v>0.8224101479915433</v>
       </c>
       <c r="H441" t="n">
-        <v>3.471692524682654</v>
+        <v>3.475073995771671</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -33351,16 +33351,16 @@
         <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>-0.3583074753173459</v>
+        <v>-0.3549260042283295</v>
       </c>
       <c r="N441" t="n">
-        <v>0.3583074753173459</v>
+        <v>0.3549260042283295</v>
       </c>
       <c r="O441" t="n">
         <v>-0.1400000000000001</v>
       </c>
       <c r="P441" t="n">
-        <v>0.1514915373765895</v>
+        <v>0.153757928118393</v>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
@@ -33400,10 +33400,10 @@
         <v>8</v>
       </c>
       <c r="G442" t="n">
-        <v>0.8385049365303244</v>
+        <v>0.8386187455954898</v>
       </c>
       <c r="H442" t="n">
-        <v>3.65056887635167</v>
+        <v>3.65138830162086</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -33422,16 +33422,16 @@
         <v>1</v>
       </c>
       <c r="M442" t="n">
-        <v>-0.009431123648330431</v>
+        <v>-0.008611698379139998</v>
       </c>
       <c r="N442" t="n">
-        <v>0.009431123648330431</v>
+        <v>0.008611698379139998</v>
       </c>
       <c r="O442" t="n">
         <v>-0.1699999999999999</v>
       </c>
       <c r="P442" t="n">
-        <v>0.1788763516690155</v>
+        <v>0.1763143058491896</v>
       </c>
       <c r="Q442" t="inlineStr">
         <is>
@@ -33471,10 +33471,10 @@
         <v>8</v>
       </c>
       <c r="G443" t="n">
-        <v>0.8483779971791255</v>
+        <v>0.8484848484848485</v>
       </c>
       <c r="H443" t="n">
-        <v>3.723430888575459</v>
+        <v>3.723863636363637</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -33493,16 +33493,16 @@
         <v>1</v>
       </c>
       <c r="M443" t="n">
-        <v>0.08343088857545844</v>
+        <v>0.08386363636363647</v>
       </c>
       <c r="N443" t="n">
-        <v>0.08343088857545844</v>
+        <v>0.08386363636363647</v>
       </c>
       <c r="O443" t="n">
         <v>-0.02000000000000002</v>
       </c>
       <c r="P443" t="n">
-        <v>0.07286201222378885</v>
+        <v>0.07247533474277645</v>
       </c>
       <c r="Q443" t="inlineStr">
         <is>
@@ -33542,10 +33542,10 @@
         <v>8</v>
       </c>
       <c r="G444" t="n">
-        <v>0.8561354019746121</v>
+        <v>0.8562367864693446</v>
       </c>
       <c r="H444" t="n">
-        <v>3.758131170662905</v>
+        <v>3.758678646934461</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -33564,16 +33564,16 @@
         <v>1</v>
       </c>
       <c r="M444" t="n">
-        <v>0.1581311706629052</v>
+        <v>0.1586786469344608</v>
       </c>
       <c r="N444" t="n">
-        <v>0.1581311706629052</v>
+        <v>0.1586786469344608</v>
       </c>
       <c r="O444" t="n">
         <v>-0.04000000000000004</v>
       </c>
       <c r="P444" t="n">
-        <v>0.03470028208744669</v>
+        <v>0.03481501057082426</v>
       </c>
       <c r="Q444" t="inlineStr">
         <is>
@@ -33613,10 +33613,10 @@
         <v>8</v>
       </c>
       <c r="G445" t="n">
-        <v>0.8589562764456982</v>
+        <v>0.8590556730091614</v>
       </c>
       <c r="H445" t="n">
-        <v>3.769181946403385</v>
+        <v>3.769450317124736</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -33635,16 +33635,16 @@
         <v>1</v>
       </c>
       <c r="M445" t="n">
-        <v>0.2366819464033849</v>
+        <v>0.2369503171247356</v>
       </c>
       <c r="N445" t="n">
-        <v>0.2366819464033849</v>
+        <v>0.2369503171247356</v>
       </c>
       <c r="O445" t="n">
         <v>-0.06749999999999989</v>
       </c>
       <c r="P445" t="n">
-        <v>0.01105077574047986</v>
+        <v>0.01077167019027492</v>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
@@ -33684,10 +33684,10 @@
         <v>8</v>
       </c>
       <c r="G446" t="n">
-        <v>0.8511988716502116</v>
+        <v>0.8513037350246653</v>
       </c>
       <c r="H446" t="n">
-        <v>3.737947813822284</v>
+        <v>3.739080338266385</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -33706,16 +33706,16 @@
         <v>1</v>
       </c>
       <c r="M446" t="n">
-        <v>0.2979478138222844</v>
+        <v>0.2990803382663847</v>
       </c>
       <c r="N446" t="n">
-        <v>0.2979478138222844</v>
+        <v>0.2990803382663847</v>
       </c>
       <c r="O446" t="n">
         <v>-0.09250000000000025</v>
       </c>
       <c r="P446" t="n">
-        <v>-0.03123413258110075</v>
+        <v>-0.03036997885835113</v>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
@@ -33755,10 +33755,10 @@
         <v>8</v>
       </c>
       <c r="G447" t="n">
-        <v>0.840620592383639</v>
+        <v>0.8407329105003524</v>
       </c>
       <c r="H447" t="n">
-        <v>3.675229196050776</v>
+        <v>3.677352008456659</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -33777,16 +33777,16 @@
         <v>1</v>
       </c>
       <c r="M447" t="n">
-        <v>0.3852291960507759</v>
+        <v>0.3873520084566593</v>
       </c>
       <c r="N447" t="n">
-        <v>0.3852291960507759</v>
+        <v>0.3873520084566593</v>
       </c>
       <c r="O447" t="n">
         <v>-0.1499999999999999</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.06271861777150844</v>
+        <v>-0.06172832980972531</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
@@ -33826,10 +33826,10 @@
         <v>8</v>
       </c>
       <c r="G448" t="n">
-        <v>0.8159379407616361</v>
+        <v>0.8160676532769556</v>
       </c>
       <c r="H448" t="n">
-        <v>3.418032440056417</v>
+        <v>3.41838266384778</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -33848,16 +33848,16 @@
         <v>1</v>
       </c>
       <c r="M448" t="n">
-        <v>0.2380324400564171</v>
+        <v>0.23838266384778</v>
       </c>
       <c r="N448" t="n">
-        <v>0.2380324400564171</v>
+        <v>0.23838266384778</v>
       </c>
       <c r="O448" t="n">
         <v>-0.1099999999999999</v>
       </c>
       <c r="P448" t="n">
-        <v>-0.2571967559943587</v>
+        <v>-0.2589693446088792</v>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
@@ -33897,10 +33897,10 @@
         <v>8</v>
       </c>
       <c r="G449" t="n">
-        <v>0.7842031029619182</v>
+        <v>0.7843551797040169</v>
       </c>
       <c r="H449" t="n">
-        <v>3.219696755994359</v>
+        <v>3.220517970401692</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -33919,16 +33919,16 @@
         <v>1</v>
       </c>
       <c r="M449" t="n">
-        <v>0.1196967559943585</v>
+        <v>0.1205179704016919</v>
       </c>
       <c r="N449" t="n">
-        <v>0.1196967559943585</v>
+        <v>0.1205179704016919</v>
       </c>
       <c r="O449" t="n">
         <v>-0.08000000000000007</v>
       </c>
       <c r="P449" t="n">
-        <v>-0.1983356840620587</v>
+        <v>-0.1978646934460881</v>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
@@ -33968,10 +33968,10 @@
         <v>8</v>
       </c>
       <c r="G450" t="n">
-        <v>0.767277856135402</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="H450" t="n">
-        <v>3.112200282087447</v>
+        <v>3.112790697674419</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -33990,16 +33990,16 @@
         <v>1</v>
       </c>
       <c r="M450" t="n">
-        <v>0.01220028208744672</v>
+        <v>0.01279069767441854</v>
       </c>
       <c r="N450" t="n">
-        <v>0.01220028208744672</v>
+        <v>0.01279069767441854</v>
       </c>
       <c r="O450" t="n">
         <v>0</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.1074964739069117</v>
+        <v>-0.1077272727272733</v>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
@@ -35311,10 +35311,10 @@
         <v>8</v>
       </c>
       <c r="G469" t="n">
-        <v>0.843441466854725</v>
+        <v>0.8435517970401691</v>
       </c>
       <c r="H469" t="n">
-        <v>8.562933709449931</v>
+        <v>8.565348837209303</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -35333,16 +35333,16 @@
         <v>1</v>
       </c>
       <c r="M469" t="n">
-        <v>-0.6770662905500693</v>
+        <v>-0.6746511627906973</v>
       </c>
       <c r="N469" t="n">
-        <v>0.6770662905500693</v>
+        <v>0.6746511627906973</v>
       </c>
       <c r="O469" t="n">
         <v>-0.08999999999999986</v>
       </c>
       <c r="P469" t="n">
-        <v>0.2639638425963931</v>
+        <v>0.2663789703557651</v>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
@@ -35382,10 +35382,10 @@
         <v>8</v>
       </c>
       <c r="G470" t="n">
-        <v>0.8265162200282088</v>
+        <v>0.8266384778012685</v>
       </c>
       <c r="H470" t="n">
-        <v>8.288603667136814</v>
+        <v>8.290063424947146</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -35404,16 +35404,16 @@
         <v>1</v>
       </c>
       <c r="M470" t="n">
-        <v>-0.7613963328631872</v>
+        <v>-0.7599365750528548</v>
       </c>
       <c r="N470" t="n">
-        <v>0.7613963328631872</v>
+        <v>0.7599365750528548</v>
       </c>
       <c r="O470" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P470" t="n">
-        <v>-0.2743300423131174</v>
+        <v>-0.2752854122621571</v>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -35453,10 +35453,10 @@
         <v>8</v>
       </c>
       <c r="G471" t="n">
-        <v>0.807475317348378</v>
+        <v>0.8076109936575053</v>
       </c>
       <c r="H471" t="n">
-        <v>8.012510578279267</v>
+        <v>8.015750528541227</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -35475,16 +35475,16 @@
         <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.8974894217207332</v>
+        <v>-0.8942494714587728</v>
       </c>
       <c r="N471" t="n">
-        <v>0.8974894217207332</v>
+        <v>0.8942494714587728</v>
       </c>
       <c r="O471" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P471" t="n">
-        <v>-0.2760930888575466</v>
+        <v>-0.2743128964059185</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
@@ -35524,10 +35524,10 @@
         <v>8</v>
       </c>
       <c r="G472" t="n">
-        <v>0.7954866008462623</v>
+        <v>0.795630725863284</v>
       </c>
       <c r="H472" t="n">
-        <v>7.899055007052186</v>
+        <v>7.899915433403805</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -35546,16 +35546,16 @@
         <v>1</v>
       </c>
       <c r="M472" t="n">
-        <v>-0.8709449929478135</v>
+        <v>-0.8700845665961943</v>
       </c>
       <c r="N472" t="n">
-        <v>0.8709449929478135</v>
+        <v>0.8700845665961943</v>
       </c>
       <c r="O472" t="n">
         <v>-0.1400000000000006</v>
       </c>
       <c r="P472" t="n">
-        <v>-0.1134555712270808</v>
+        <v>-0.1158350951374221</v>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
@@ -35595,10 +35595,10 @@
         <v>8</v>
       </c>
       <c r="G473" t="n">
-        <v>0.7933709449929478</v>
+        <v>0.7935165609584214</v>
       </c>
       <c r="H473" t="n">
-        <v>7.882849083215796</v>
+        <v>7.884587737843551</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -35617,16 +35617,16 @@
         <v>1</v>
       </c>
       <c r="M473" t="n">
-        <v>-0.6971509167842038</v>
+        <v>-0.6954122621564487</v>
       </c>
       <c r="N473" t="n">
-        <v>0.6971509167842038</v>
+        <v>0.6954122621564487</v>
       </c>
       <c r="O473" t="n">
         <v>-0.1899999999999995</v>
       </c>
       <c r="P473" t="n">
-        <v>-0.01620592383638986</v>
+        <v>-0.01532769556025393</v>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
@@ -35666,10 +35666,10 @@
         <v>8</v>
       </c>
       <c r="G474" t="n">
-        <v>0.8039492242595204</v>
+        <v>0.8040873854827343</v>
       </c>
       <c r="H474" t="n">
-        <v>7.929858956276445</v>
+        <v>7.931606765327693</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -35688,16 +35688,16 @@
         <v>1</v>
       </c>
       <c r="M474" t="n">
-        <v>-0.5201410437235543</v>
+        <v>-0.5183932346723061</v>
       </c>
       <c r="N474" t="n">
-        <v>0.5201410437235543</v>
+        <v>0.5183932346723061</v>
       </c>
       <c r="O474" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P474" t="n">
-        <v>0.04700987306064874</v>
+        <v>0.04701902748414177</v>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
@@ -35737,10 +35737,10 @@
         <v>8</v>
       </c>
       <c r="G475" t="n">
-        <v>0.8166431593794076</v>
+        <v>0.8167723749119098</v>
       </c>
       <c r="H475" t="n">
-        <v>8.195119887165021</v>
+        <v>8.1953770260747</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -35759,16 +35759,16 @@
         <v>1</v>
       </c>
       <c r="M475" t="n">
-        <v>-0.1248801128349797</v>
+        <v>-0.1246229739253</v>
       </c>
       <c r="N475" t="n">
-        <v>0.1248801128349797</v>
+        <v>0.1246229739253</v>
       </c>
       <c r="O475" t="n">
         <v>-0.129999999999999</v>
       </c>
       <c r="P475" t="n">
-        <v>0.2652609308885756</v>
+        <v>0.2637702607470072</v>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
@@ -35808,10 +35808,10 @@
         <v>8</v>
       </c>
       <c r="G476" t="n">
-        <v>0.8286318758815233</v>
+        <v>0.828752642706131</v>
       </c>
       <c r="H476" t="n">
-        <v>8.313864598025388</v>
+        <v>8.315306553911205</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -35830,16 +35830,16 @@
         <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>0.05386459802538823</v>
+        <v>0.05530655391120476</v>
       </c>
       <c r="N476" t="n">
-        <v>0.05386459802538823</v>
+        <v>0.05530655391120476</v>
       </c>
       <c r="O476" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P476" t="n">
-        <v>0.1187447108603674</v>
+        <v>0.1199295278365042</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
@@ -35879,10 +35879,10 @@
         <v>8</v>
       </c>
       <c r="G477" t="n">
-        <v>0.8370944992947814</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="H477" t="n">
-        <v>8.461636107193231</v>
+        <v>8.462093023255814</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -35901,16 +35901,16 @@
         <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>0.2616361071932314</v>
+        <v>0.2620930232558152</v>
       </c>
       <c r="N477" t="n">
-        <v>0.2616361071932314</v>
+        <v>0.2620930232558152</v>
       </c>
       <c r="O477" t="n">
         <v>-0.0600000000000005</v>
       </c>
       <c r="P477" t="n">
-        <v>0.1477715091678427</v>
+        <v>0.1467864693446099</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
@@ -35950,10 +35950,10 @@
         <v>8</v>
       </c>
       <c r="G478" t="n">
-        <v>0.8377997179125529</v>
+        <v>0.8379140239605356</v>
       </c>
       <c r="H478" t="n">
-        <v>8.464442877291962</v>
+        <v>8.464897815362932</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -35972,16 +35972,16 @@
         <v>1</v>
       </c>
       <c r="M478" t="n">
-        <v>0.4144428772919611</v>
+        <v>0.4148978153629308</v>
       </c>
       <c r="N478" t="n">
-        <v>0.4144428772919611</v>
+        <v>0.4148978153629308</v>
       </c>
       <c r="O478" t="n">
         <v>-0.1499999999999986</v>
       </c>
       <c r="P478" t="n">
-        <v>0.002806770098731093</v>
+        <v>0.002804792107117038</v>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
@@ -36021,10 +36021,10 @@
         <v>8</v>
       </c>
       <c r="G479" t="n">
-        <v>0.8328631875881524</v>
+        <v>0.8329809725158562</v>
       </c>
       <c r="H479" t="n">
-        <v>8.416170662905502</v>
+        <v>8.419217758985202</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -36043,16 +36043,16 @@
         <v>1</v>
       </c>
       <c r="M479" t="n">
-        <v>0.4961706629055023</v>
+        <v>0.4992177589852016</v>
       </c>
       <c r="N479" t="n">
-        <v>0.4961706629055023</v>
+        <v>0.4992177589852016</v>
       </c>
       <c r="O479" t="n">
         <v>-0.1300000000000008</v>
       </c>
       <c r="P479" t="n">
-        <v>-0.04827221438645957</v>
+        <v>-0.04568005637772998</v>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
@@ -36092,10 +36092,10 @@
         <v>8</v>
       </c>
       <c r="G480" t="n">
-        <v>0.8201692524682651</v>
+        <v>0.8202959830866807</v>
       </c>
       <c r="H480" t="n">
-        <v>8.212820874471085</v>
+        <v>8.214334038054968</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -36114,16 +36114,16 @@
         <v>1</v>
       </c>
       <c r="M480" t="n">
-        <v>0.4728208744710845</v>
+        <v>0.4743340380549679</v>
       </c>
       <c r="N480" t="n">
-        <v>0.4728208744710845</v>
+        <v>0.4743340380549679</v>
       </c>
       <c r="O480" t="n">
         <v>-0.1799999999999997</v>
       </c>
       <c r="P480" t="n">
-        <v>-0.2033497884344175</v>
+        <v>-0.2048837209302334</v>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
@@ -36266,34 +36266,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.612</v>
+        <v>7.591</v>
       </c>
       <c r="G2" t="n">
-        <v>7.767</v>
+        <v>7.731</v>
       </c>
       <c r="H2" t="n">
-        <v>7.879</v>
+        <v>7.872</v>
       </c>
       <c r="I2" t="n">
-        <v>7.879</v>
+        <v>7.872</v>
       </c>
       <c r="J2" t="n">
-        <v>7.63</v>
+        <v>7.601</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.249</v>
+        <v>-0.27</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -36312,10 +36312,10 @@
         <v>5.832</v>
       </c>
       <c r="P2" t="n">
-        <v>5.812</v>
+        <v>5.813</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.812</v>
+        <v>5.813</v>
       </c>
       <c r="R2" t="n">
         <v>-1.024</v>
@@ -36342,34 +36342,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.528</v>
+        <v>5.518</v>
       </c>
       <c r="G3" t="n">
-        <v>5.592</v>
+        <v>5.579</v>
       </c>
       <c r="H3" t="n">
-        <v>5.637</v>
+        <v>5.628</v>
       </c>
       <c r="I3" t="n">
-        <v>5.637</v>
+        <v>5.628</v>
       </c>
       <c r="J3" t="n">
-        <v>5.528</v>
+        <v>5.518</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.108</v>
+        <v>-0.11</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -36418,34 +36418,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.856</v>
+        <v>3.795</v>
       </c>
       <c r="G4" t="n">
-        <v>4.371</v>
+        <v>4.269</v>
       </c>
       <c r="H4" t="n">
-        <v>4.577</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>4.425</v>
+        <v>4.391</v>
       </c>
       <c r="J4" t="n">
-        <v>4.111</v>
+        <v>3.943</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.314</v>
+        <v>-0.449</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -36494,34 +36494,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.8</v>
+        <v>11.795</v>
       </c>
       <c r="G5" t="n">
-      